--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -726,6 +726,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -775,6 +776,9 @@
       <c r="N1" s="1" t="n">
         <v>20251212</v>
       </c>
+      <c r="O1" s="1" t="n">
+        <v>20251215</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -823,6 +827,9 @@
       <c r="N2" t="n">
         <v>41</v>
       </c>
+      <c r="O2" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -871,6 +878,9 @@
       <c r="N3" t="n">
         <v>34</v>
       </c>
+      <c r="O3" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -919,6 +929,9 @@
       <c r="N4" t="n">
         <v>21</v>
       </c>
+      <c r="O4" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -967,6 +980,9 @@
       <c r="N5" t="n">
         <v>14</v>
       </c>
+      <c r="O5" t="n">
+        <v>-17</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1015,6 +1031,9 @@
       <c r="N6" t="n">
         <v>42</v>
       </c>
+      <c r="O6" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1063,6 +1082,9 @@
       <c r="N7" t="n">
         <v>53</v>
       </c>
+      <c r="O7" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1111,6 +1133,9 @@
       <c r="N8" t="n">
         <v>40</v>
       </c>
+      <c r="O8" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1159,6 +1184,9 @@
       <c r="N9" t="n">
         <v>27</v>
       </c>
+      <c r="O9" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1207,6 +1235,9 @@
       <c r="N10" t="n">
         <v>19</v>
       </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1255,6 +1286,9 @@
       <c r="N11" t="n">
         <v>55</v>
       </c>
+      <c r="O11" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1303,6 +1337,9 @@
       <c r="N12" t="n">
         <v>56</v>
       </c>
+      <c r="O12" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1351,6 +1388,9 @@
       <c r="N13" t="n">
         <v>62</v>
       </c>
+      <c r="O13" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1399,6 +1439,9 @@
       <c r="N14" t="n">
         <v>36</v>
       </c>
+      <c r="O14" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1447,6 +1490,9 @@
       <c r="N15" t="n">
         <v>58</v>
       </c>
+      <c r="O15" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1495,6 +1541,9 @@
       <c r="N16" t="n">
         <v>48</v>
       </c>
+      <c r="O16" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1543,6 +1592,9 @@
       <c r="N17" t="n">
         <v>44</v>
       </c>
+      <c r="O17" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1591,6 +1643,9 @@
       <c r="N18" t="n">
         <v>38</v>
       </c>
+      <c r="O18" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1638,6 +1693,9 @@
       </c>
       <c r="N19" t="n">
         <v>58</v>
+      </c>
+      <c r="O19" t="n">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1651,7 +1709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB19"/>
+  <dimension ref="A1:BC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1708,6 +1766,7 @@
     <col width="12" customWidth="1" min="52" max="52"/>
     <col width="12" customWidth="1" min="53" max="53"/>
     <col width="12" customWidth="1" min="54" max="54"/>
+    <col width="12" customWidth="1" min="55" max="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1981,6 +2040,11 @@
           <t>20251212</t>
         </is>
       </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>20251215</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2149,6 +2213,9 @@
       <c r="BB2" t="n">
         <v>97</v>
       </c>
+      <c r="BC2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2317,6 +2384,9 @@
       <c r="BB3" t="n">
         <v>102</v>
       </c>
+      <c r="BC3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2485,6 +2555,9 @@
       <c r="BB4" t="n">
         <v>96</v>
       </c>
+      <c r="BC4" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2653,6 +2726,9 @@
       <c r="BB5" t="n">
         <v>100</v>
       </c>
+      <c r="BC5" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2821,6 +2897,9 @@
       <c r="BB6" t="n">
         <v>102</v>
       </c>
+      <c r="BC6" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2989,6 +3068,9 @@
       <c r="BB7" t="n">
         <v>104</v>
       </c>
+      <c r="BC7" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3157,6 +3239,9 @@
       <c r="BB8" t="n">
         <v>103</v>
       </c>
+      <c r="BC8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3325,6 +3410,9 @@
       <c r="BB9" t="n">
         <v>105</v>
       </c>
+      <c r="BC9" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3493,6 +3581,9 @@
       <c r="BB10" t="n">
         <v>99</v>
       </c>
+      <c r="BC10" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3661,6 +3752,9 @@
       <c r="BB11" t="n">
         <v>107</v>
       </c>
+      <c r="BC11" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3829,6 +3923,9 @@
       <c r="BB12" t="n">
         <v>108</v>
       </c>
+      <c r="BC12" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3997,6 +4094,9 @@
       <c r="BB13" t="n">
         <v>110</v>
       </c>
+      <c r="BC13" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4165,6 +4265,9 @@
       <c r="BB14" t="n">
         <v>107</v>
       </c>
+      <c r="BC14" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4333,6 +4436,9 @@
       <c r="BB15" t="n">
         <v>99</v>
       </c>
+      <c r="BC15" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4501,6 +4607,9 @@
       <c r="BB16" t="n">
         <v>106</v>
       </c>
+      <c r="BC16" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4669,6 +4778,9 @@
       <c r="BB17" t="n">
         <v>106</v>
       </c>
+      <c r="BC17" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4837,6 +4949,9 @@
       <c r="BB18" t="n">
         <v>98</v>
       </c>
+      <c r="BC18" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5004,6 +5119,9 @@
       </c>
       <c r="BB19" t="n">
         <v>99</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -5017,7 +5135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI19"/>
+  <dimension ref="A1:AJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5055,6 +5173,7 @@
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
     <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5233,6 +5352,11 @@
           <t>20251212</t>
         </is>
       </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>20251215</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5344,6 +5468,9 @@
       <c r="AI2" t="n">
         <v>-40.21</v>
       </c>
+      <c r="AJ2" t="n">
+        <v>-39.8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5455,6 +5582,9 @@
       <c r="AI3" t="n">
         <v>-16.48</v>
       </c>
+      <c r="AJ3" t="n">
+        <v>-20.83</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5566,6 +5696,9 @@
       <c r="AI4" t="n">
         <v>-34.52</v>
       </c>
+      <c r="AJ4" t="n">
+        <v>-30.2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5677,6 +5810,9 @@
       <c r="AI5" t="n">
         <v>-22.99</v>
       </c>
+      <c r="AJ5" t="n">
+        <v>-27.09</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5788,6 +5924,9 @@
       <c r="AI6" t="n">
         <v>-7.11</v>
       </c>
+      <c r="AJ6" t="n">
+        <v>-9.34</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5899,6 +6038,9 @@
       <c r="AI7" t="n">
         <v>5.44</v>
       </c>
+      <c r="AJ7" t="n">
+        <v>5.55</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6010,6 +6152,9 @@
       <c r="AI8" t="n">
         <v>-12.85</v>
       </c>
+      <c r="AJ8" t="n">
+        <v>-17.08</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6121,6 +6266,9 @@
       <c r="AI9" t="n">
         <v>-31.82</v>
       </c>
+      <c r="AJ9" t="n">
+        <v>-35.54</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6232,6 +6380,9 @@
       <c r="AI10" t="n">
         <v>-7.66</v>
       </c>
+      <c r="AJ10" t="n">
+        <v>-8.25</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6343,6 +6494,9 @@
       <c r="AI11" t="n">
         <v>29.61</v>
       </c>
+      <c r="AJ11" t="n">
+        <v>31.34</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6454,6 +6608,9 @@
       <c r="AI12" t="n">
         <v>30.31</v>
       </c>
+      <c r="AJ12" t="n">
+        <v>32.7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6565,6 +6722,9 @@
       <c r="AI13" t="n">
         <v>45.15</v>
       </c>
+      <c r="AJ13" t="n">
+        <v>46.47</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6676,6 +6836,9 @@
       <c r="AI14" t="n">
         <v>-19.86</v>
       </c>
+      <c r="AJ14" t="n">
+        <v>-20.39</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6787,6 +6950,9 @@
       <c r="AI15" t="n">
         <v>-52.09</v>
       </c>
+      <c r="AJ15" t="n">
+        <v>-50.05</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6898,6 +7064,9 @@
       <c r="AI16" t="n">
         <v>5.77</v>
       </c>
+      <c r="AJ16" t="n">
+        <v>8.380000000000001</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7009,6 +7178,9 @@
       <c r="AI17" t="n">
         <v>0.71</v>
       </c>
+      <c r="AJ17" t="n">
+        <v>2.3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7120,6 +7292,9 @@
       <c r="AI18" t="n">
         <v>-9.880000000000001</v>
       </c>
+      <c r="AJ18" t="n">
+        <v>-5.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7230,6 +7405,9 @@
       </c>
       <c r="AI19" t="n">
         <v>-48.54</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>-46.39</v>
       </c>
     </row>
   </sheetData>
@@ -7243,7 +7421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7260,6 +7438,7 @@
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7333,6 +7512,11 @@
           <t>20251212</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>20251215</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7381,6 +7565,9 @@
       <c r="N2" t="n">
         <v>53</v>
       </c>
+      <c r="O2" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7429,6 +7616,9 @@
       <c r="N3" t="n">
         <v>19</v>
       </c>
+      <c r="O3" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7477,6 +7667,9 @@
       <c r="N4" t="n">
         <v>68</v>
       </c>
+      <c r="O4" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7525,6 +7718,9 @@
       <c r="N5" t="n">
         <v>10</v>
       </c>
+      <c r="O5" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7573,6 +7769,9 @@
       <c r="N6" t="n">
         <v>43</v>
       </c>
+      <c r="O6" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7621,6 +7820,9 @@
       <c r="N7" t="n">
         <v>15</v>
       </c>
+      <c r="O7" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7669,6 +7871,9 @@
       <c r="N8" t="n">
         <v>19</v>
       </c>
+      <c r="O8" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7717,6 +7922,9 @@
       <c r="N9" t="n">
         <v>22</v>
       </c>
+      <c r="O9" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7765,6 +7973,9 @@
       <c r="N10" t="n">
         <v>29</v>
       </c>
+      <c r="O10" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7813,6 +8024,9 @@
       <c r="N11" t="n">
         <v>15</v>
       </c>
+      <c r="O11" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7861,6 +8075,9 @@
       <c r="N12" t="n">
         <v>33</v>
       </c>
+      <c r="O12" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7909,6 +8126,9 @@
       <c r="N13" t="n">
         <v>38</v>
       </c>
+      <c r="O13" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7957,6 +8177,9 @@
       <c r="N14" t="n">
         <v>26</v>
       </c>
+      <c r="O14" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8005,6 +8228,9 @@
       <c r="N15" t="n">
         <v>42</v>
       </c>
+      <c r="O15" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8053,6 +8279,9 @@
       <c r="N16" t="n">
         <v>25</v>
       </c>
+      <c r="O16" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8101,6 +8330,9 @@
       <c r="N17" t="n">
         <v>7</v>
       </c>
+      <c r="O17" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8149,6 +8381,9 @@
       <c r="N18" t="n">
         <v>25</v>
       </c>
+      <c r="O18" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8196,6 +8431,9 @@
       </c>
       <c r="N19" t="n">
         <v>48</v>
+      </c>
+      <c r="O19" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -8209,7 +8447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU19"/>
+  <dimension ref="A1:BV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8285,6 +8523,7 @@
     <col width="12" customWidth="1" min="71" max="71"/>
     <col width="12" customWidth="1" min="72" max="72"/>
     <col width="12" customWidth="1" min="73" max="73"/>
+    <col width="12" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8511,6 +8750,9 @@
       <c r="BU1" s="1" t="n">
         <v>20251212</v>
       </c>
+      <c r="BV1" s="1" t="n">
+        <v>20251215</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8736,6 +8978,9 @@
       <c r="BU2" t="n">
         <v>15510</v>
       </c>
+      <c r="BV2" t="n">
+        <v>15305</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8961,6 +9206,9 @@
       <c r="BU3" t="n">
         <v>57435</v>
       </c>
+      <c r="BV3" t="n">
+        <v>55450</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9186,6 +9434,9 @@
       <c r="BU4" t="n">
         <v>18170</v>
       </c>
+      <c r="BV4" t="n">
+        <v>17675</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9411,6 +9662,9 @@
       <c r="BU5" t="n">
         <v>15960</v>
       </c>
+      <c r="BV5" t="n">
+        <v>15200</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9636,6 +9890,9 @@
       <c r="BU6" t="n">
         <v>17125</v>
       </c>
+      <c r="BV6" t="n">
+        <v>16435</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9861,6 +10118,9 @@
       <c r="BU7" t="n">
         <v>19730</v>
       </c>
+      <c r="BV7" t="n">
+        <v>19105</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10086,6 +10346,9 @@
       <c r="BU8" t="n">
         <v>18520</v>
       </c>
+      <c r="BV8" t="n">
+        <v>17925</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10311,6 +10574,9 @@
       <c r="BU9" t="n">
         <v>1581</v>
       </c>
+      <c r="BV9" t="n">
+        <v>1560</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10536,6 +10802,9 @@
       <c r="BU10" t="n">
         <v>17215</v>
       </c>
+      <c r="BV10" t="n">
+        <v>16385</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10761,6 +11030,9 @@
       <c r="BU11" t="n">
         <v>5620</v>
       </c>
+      <c r="BV11" t="n">
+        <v>5505</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10986,6 +11258,9 @@
       <c r="BU12" t="n">
         <v>6120</v>
       </c>
+      <c r="BV12" t="n">
+        <v>6005</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11211,6 +11486,9 @@
       <c r="BU13" t="n">
         <v>6200</v>
       </c>
+      <c r="BV13" t="n">
+        <v>6065</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11436,6 +11714,9 @@
       <c r="BU14" t="n">
         <v>1761</v>
       </c>
+      <c r="BV14" t="n">
+        <v>1702</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11661,6 +11942,9 @@
       <c r="BU15" t="n">
         <v>19505</v>
       </c>
+      <c r="BV15" t="n">
+        <v>19180</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11886,6 +12170,9 @@
       <c r="BU16" t="n">
         <v>11355</v>
       </c>
+      <c r="BV16" t="n">
+        <v>11250</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12111,6 +12398,9 @@
       <c r="BU17" t="n">
         <v>6740</v>
       </c>
+      <c r="BV17" t="n">
+        <v>6640</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12336,6 +12626,9 @@
       <c r="BU18" t="n">
         <v>18295</v>
       </c>
+      <c r="BV18" t="n">
+        <v>17240</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12560,6 +12853,9 @@
       </c>
       <c r="BU19" t="n">
         <v>16285</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>15945</v>
       </c>
     </row>
   </sheetData>
@@ -12573,7 +12869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU19"/>
+  <dimension ref="A1:BV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12649,6 +12945,7 @@
     <col width="12" customWidth="1" min="71" max="71"/>
     <col width="12" customWidth="1" min="72" max="72"/>
     <col width="12" customWidth="1" min="73" max="73"/>
+    <col width="12" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12875,6 +13172,9 @@
       <c r="BU1" s="1" t="n">
         <v>20251212</v>
       </c>
+      <c r="BV1" s="1" t="n">
+        <v>20251215</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13100,6 +13400,9 @@
       <c r="BU2" t="n">
         <v>15930</v>
       </c>
+      <c r="BV2" t="n">
+        <v>15800</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13325,6 +13628,9 @@
       <c r="BU3" t="n">
         <v>57640</v>
       </c>
+      <c r="BV3" t="n">
+        <v>56475</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13550,6 +13856,9 @@
       <c r="BU4" t="n">
         <v>18315</v>
       </c>
+      <c r="BV4" t="n">
+        <v>18005</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13775,6 +14084,9 @@
       <c r="BU5" t="n">
         <v>15960</v>
       </c>
+      <c r="BV5" t="n">
+        <v>15430</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14000,6 +14312,9 @@
       <c r="BU6" t="n">
         <v>17125</v>
       </c>
+      <c r="BV6" t="n">
+        <v>16610</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14225,6 +14540,9 @@
       <c r="BU7" t="n">
         <v>19855</v>
       </c>
+      <c r="BV7" t="n">
+        <v>19370</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14450,6 +14768,9 @@
       <c r="BU8" t="n">
         <v>18655</v>
       </c>
+      <c r="BV8" t="n">
+        <v>18190</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14675,6 +14996,9 @@
       <c r="BU9" t="n">
         <v>1615</v>
       </c>
+      <c r="BV9" t="n">
+        <v>1630</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14900,6 +15224,9 @@
       <c r="BU10" t="n">
         <v>17285</v>
       </c>
+      <c r="BV10" t="n">
+        <v>16550</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15125,6 +15452,9 @@
       <c r="BU11" t="n">
         <v>5680</v>
       </c>
+      <c r="BV11" t="n">
+        <v>5730</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15350,6 +15680,9 @@
       <c r="BU12" t="n">
         <v>6180</v>
       </c>
+      <c r="BV12" t="n">
+        <v>6230</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15575,6 +15908,9 @@
       <c r="BU13" t="n">
         <v>6250</v>
       </c>
+      <c r="BV13" t="n">
+        <v>6310</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -15800,6 +16136,9 @@
       <c r="BU14" t="n">
         <v>1774</v>
       </c>
+      <c r="BV14" t="n">
+        <v>1797</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -16025,6 +16364,9 @@
       <c r="BU15" t="n">
         <v>19835</v>
       </c>
+      <c r="BV15" t="n">
+        <v>19665</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -16250,6 +16592,9 @@
       <c r="BU16" t="n">
         <v>11465</v>
       </c>
+      <c r="BV16" t="n">
+        <v>11550</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16475,6 +16820,9 @@
       <c r="BU17" t="n">
         <v>6795</v>
       </c>
+      <c r="BV17" t="n">
+        <v>6850</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16700,6 +17048,9 @@
       <c r="BU18" t="n">
         <v>18295</v>
       </c>
+      <c r="BV18" t="n">
+        <v>17450</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -16924,6 +17275,9 @@
       </c>
       <c r="BU19" t="n">
         <v>16440</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>16295</v>
       </c>
     </row>
   </sheetData>
@@ -16937,7 +17291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU19"/>
+  <dimension ref="A1:BV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17013,6 +17367,7 @@
     <col width="12" customWidth="1" min="71" max="71"/>
     <col width="12" customWidth="1" min="72" max="72"/>
     <col width="12" customWidth="1" min="73" max="73"/>
+    <col width="12" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17239,6 +17594,9 @@
       <c r="BU1" s="1" t="n">
         <v>20251212</v>
       </c>
+      <c r="BV1" s="1" t="n">
+        <v>20251215</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17464,6 +17822,9 @@
       <c r="BU2" t="n">
         <v>15405</v>
       </c>
+      <c r="BV2" t="n">
+        <v>15300</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17689,6 +18050,9 @@
       <c r="BU3" t="n">
         <v>57000</v>
       </c>
+      <c r="BV3" t="n">
+        <v>55150</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17914,6 +18278,9 @@
       <c r="BU4" t="n">
         <v>17785</v>
       </c>
+      <c r="BV4" t="n">
+        <v>17665</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18139,6 +18506,9 @@
       <c r="BU5" t="n">
         <v>15690</v>
       </c>
+      <c r="BV5" t="n">
+        <v>15200</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18364,6 +18734,9 @@
       <c r="BU6" t="n">
         <v>16855</v>
       </c>
+      <c r="BV6" t="n">
+        <v>16290</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18589,6 +18962,9 @@
       <c r="BU7" t="n">
         <v>19555</v>
       </c>
+      <c r="BV7" t="n">
+        <v>19025</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18814,6 +19190,9 @@
       <c r="BU8" t="n">
         <v>18415</v>
       </c>
+      <c r="BV8" t="n">
+        <v>17805</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19039,6 +19418,9 @@
       <c r="BU9" t="n">
         <v>1563</v>
       </c>
+      <c r="BV9" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19264,6 +19646,9 @@
       <c r="BU10" t="n">
         <v>16747</v>
       </c>
+      <c r="BV10" t="n">
+        <v>16220</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -19489,6 +19874,9 @@
       <c r="BU11" t="n">
         <v>5570</v>
       </c>
+      <c r="BV11" t="n">
+        <v>5505</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -19714,6 +20102,9 @@
       <c r="BU12" t="n">
         <v>6035</v>
       </c>
+      <c r="BV12" t="n">
+        <v>5960</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -19939,6 +20330,9 @@
       <c r="BU13" t="n">
         <v>6090</v>
       </c>
+      <c r="BV13" t="n">
+        <v>6030</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -20164,6 +20558,9 @@
       <c r="BU14" t="n">
         <v>1732</v>
       </c>
+      <c r="BV14" t="n">
+        <v>1685</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -20389,6 +20786,9 @@
       <c r="BU15" t="n">
         <v>19140</v>
       </c>
+      <c r="BV15" t="n">
+        <v>19090</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -20614,6 +21014,9 @@
       <c r="BU16" t="n">
         <v>11280</v>
       </c>
+      <c r="BV16" t="n">
+        <v>11130</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -20839,6 +21242,9 @@
       <c r="BU17" t="n">
         <v>6660</v>
       </c>
+      <c r="BV17" t="n">
+        <v>6585</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -21064,6 +21470,9 @@
       <c r="BU18" t="n">
         <v>17765</v>
       </c>
+      <c r="BV18" t="n">
+        <v>17020</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -21288,6 +21697,9 @@
       </c>
       <c r="BU19" t="n">
         <v>15935</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>15860</v>
       </c>
     </row>
   </sheetData>
@@ -21301,7 +21713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU19"/>
+  <dimension ref="A1:BV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21377,6 +21789,7 @@
     <col width="12" customWidth="1" min="71" max="71"/>
     <col width="12" customWidth="1" min="72" max="72"/>
     <col width="12" customWidth="1" min="73" max="73"/>
+    <col width="12" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21603,6 +22016,9 @@
       <c r="BU1" s="1" t="n">
         <v>20251212</v>
       </c>
+      <c r="BV1" s="1" t="n">
+        <v>20251215</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21828,6 +22244,9 @@
       <c r="BU2" t="n">
         <v>15470</v>
       </c>
+      <c r="BV2" t="n">
+        <v>15765</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22053,6 +22472,9 @@
       <c r="BU3" t="n">
         <v>57375</v>
       </c>
+      <c r="BV3" t="n">
+        <v>56095</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22278,6 +22700,9 @@
       <c r="BU4" t="n">
         <v>17810</v>
       </c>
+      <c r="BV4" t="n">
+        <v>17905</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22503,6 +22928,9 @@
       <c r="BU5" t="n">
         <v>15905</v>
       </c>
+      <c r="BV5" t="n">
+        <v>15255</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22728,6 +23156,9 @@
       <c r="BU6" t="n">
         <v>16985</v>
       </c>
+      <c r="BV6" t="n">
+        <v>16495</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22953,6 +23384,9 @@
       <c r="BU7" t="n">
         <v>19795</v>
       </c>
+      <c r="BV7" t="n">
+        <v>19220</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23178,6 +23612,9 @@
       <c r="BU8" t="n">
         <v>18625</v>
       </c>
+      <c r="BV8" t="n">
+        <v>18045</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23403,6 +23840,9 @@
       <c r="BU9" t="n">
         <v>1608</v>
       </c>
+      <c r="BV9" t="n">
+        <v>1597</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23628,6 +24068,9 @@
       <c r="BU10" t="n">
         <v>16885</v>
       </c>
+      <c r="BV10" t="n">
+        <v>16495</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23853,6 +24296,9 @@
       <c r="BU11" t="n">
         <v>5645</v>
       </c>
+      <c r="BV11" t="n">
+        <v>5650</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24078,6 +24524,9 @@
       <c r="BU12" t="n">
         <v>6135</v>
       </c>
+      <c r="BV12" t="n">
+        <v>6155</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24303,6 +24752,9 @@
       <c r="BU13" t="n">
         <v>6200</v>
       </c>
+      <c r="BV13" t="n">
+        <v>6230</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24528,6 +24980,9 @@
       <c r="BU14" t="n">
         <v>1767</v>
       </c>
+      <c r="BV14" t="n">
+        <v>1757</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24753,6 +25208,9 @@
       <c r="BU15" t="n">
         <v>19265</v>
       </c>
+      <c r="BV15" t="n">
+        <v>19590</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24978,6 +25436,9 @@
       <c r="BU16" t="n">
         <v>11430</v>
       </c>
+      <c r="BV16" t="n">
+        <v>11430</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -25203,6 +25664,9 @@
       <c r="BU17" t="n">
         <v>6770</v>
       </c>
+      <c r="BV17" t="n">
+        <v>6780</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25428,6 +25892,9 @@
       <c r="BU18" t="n">
         <v>17845</v>
       </c>
+      <c r="BV18" t="n">
+        <v>17365</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25652,6 +26119,9 @@
       </c>
       <c r="BU19" t="n">
         <v>15965</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>16275</v>
       </c>
     </row>
   </sheetData>
@@ -25665,7 +26135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU19"/>
+  <dimension ref="A1:BV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25741,6 +26211,7 @@
     <col width="12" customWidth="1" min="71" max="71"/>
     <col width="12" customWidth="1" min="72" max="72"/>
     <col width="12" customWidth="1" min="73" max="73"/>
+    <col width="12" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25967,6 +26438,9 @@
       <c r="BU1" s="1" t="n">
         <v>20251212</v>
       </c>
+      <c r="BV1" s="1" t="n">
+        <v>20251215</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26192,6 +26666,9 @@
       <c r="BU2" t="n">
         <v>118341</v>
       </c>
+      <c r="BV2" t="n">
+        <v>61069</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26417,6 +26894,9 @@
       <c r="BU3" t="n">
         <v>891170</v>
       </c>
+      <c r="BV3" t="n">
+        <v>1890995</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26642,6 +27122,9 @@
       <c r="BU4" t="n">
         <v>214684</v>
       </c>
+      <c r="BV4" t="n">
+        <v>92711</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26867,6 +27350,9 @@
       <c r="BU5" t="n">
         <v>171804</v>
       </c>
+      <c r="BV5" t="n">
+        <v>355917</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27092,6 +27578,9 @@
       <c r="BU6" t="n">
         <v>1743316</v>
       </c>
+      <c r="BV6" t="n">
+        <v>1362916</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27317,6 +27806,9 @@
       <c r="BU7" t="n">
         <v>1195677</v>
       </c>
+      <c r="BV7" t="n">
+        <v>1801208</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27542,6 +28034,9 @@
       <c r="BU8" t="n">
         <v>3251172</v>
       </c>
+      <c r="BV8" t="n">
+        <v>4682435</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27767,6 +28262,9 @@
       <c r="BU9" t="n">
         <v>3122211</v>
       </c>
+      <c r="BV9" t="n">
+        <v>3449147</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27992,6 +28490,9 @@
       <c r="BU10" t="n">
         <v>858995</v>
       </c>
+      <c r="BV10" t="n">
+        <v>589028</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28217,6 +28718,9 @@
       <c r="BU11" t="n">
         <v>375014</v>
       </c>
+      <c r="BV11" t="n">
+        <v>446617</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28442,6 +28946,9 @@
       <c r="BU12" t="n">
         <v>1854012</v>
       </c>
+      <c r="BV12" t="n">
+        <v>1645650</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28667,6 +29174,9 @@
       <c r="BU13" t="n">
         <v>5110124</v>
       </c>
+      <c r="BV13" t="n">
+        <v>5160285</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -28892,6 +29402,9 @@
       <c r="BU14" t="n">
         <v>26941706</v>
       </c>
+      <c r="BV14" t="n">
+        <v>26438181</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -29117,6 +29630,9 @@
       <c r="BU15" t="n">
         <v>1380324</v>
       </c>
+      <c r="BV15" t="n">
+        <v>751498</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -29342,6 +29858,9 @@
       <c r="BU16" t="n">
         <v>304846</v>
       </c>
+      <c r="BV16" t="n">
+        <v>473598</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -29567,6 +30086,9 @@
       <c r="BU17" t="n">
         <v>33097</v>
       </c>
+      <c r="BV17" t="n">
+        <v>48746</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -29792,6 +30314,9 @@
       <c r="BU18" t="n">
         <v>90188</v>
       </c>
+      <c r="BV18" t="n">
+        <v>71766</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -30016,6 +30541,9 @@
       </c>
       <c r="BU19" t="n">
         <v>45934</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>22828</v>
       </c>
     </row>
   </sheetData>
@@ -30029,7 +30557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB19"/>
+  <dimension ref="A1:BC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -30086,6 +30614,7 @@
     <col width="10" customWidth="1" min="52" max="52"/>
     <col width="10" customWidth="1" min="53" max="53"/>
     <col width="10" customWidth="1" min="54" max="54"/>
+    <col width="10" customWidth="1" min="55" max="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30255,6 +30784,9 @@
       <c r="BB1" s="1" t="n">
         <v>20251212</v>
       </c>
+      <c r="BC1" s="1" t="n">
+        <v>20251215</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30423,6 +30955,9 @@
       <c r="BB2" t="n">
         <v>31</v>
       </c>
+      <c r="BC2" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -30591,6 +31126,9 @@
       <c r="BB3" t="n">
         <v>79</v>
       </c>
+      <c r="BC3" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -30759,6 +31297,9 @@
       <c r="BB4" t="n">
         <v>0</v>
       </c>
+      <c r="BC4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -30927,6 +31468,9 @@
       <c r="BB5" t="n">
         <v>50</v>
       </c>
+      <c r="BC5" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -31095,6 +31639,9 @@
       <c r="BB6" t="n">
         <v>83</v>
       </c>
+      <c r="BC6" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -31263,6 +31810,9 @@
       <c r="BB7" t="n">
         <v>95</v>
       </c>
+      <c r="BC7" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -31431,6 +31981,9 @@
       <c r="BB8" t="n">
         <v>87</v>
       </c>
+      <c r="BC8" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -31599,6 +32152,9 @@
       <c r="BB9" t="n">
         <v>75</v>
       </c>
+      <c r="BC9" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31767,6 +32323,9 @@
       <c r="BB10" t="n">
         <v>54</v>
       </c>
+      <c r="BC10" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -31935,6 +32494,9 @@
       <c r="BB11" t="n">
         <v>86</v>
       </c>
+      <c r="BC11" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32103,6 +32665,9 @@
       <c r="BB12" t="n">
         <v>87</v>
       </c>
+      <c r="BC12" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32271,6 +32836,9 @@
       <c r="BB13" t="n">
         <v>88</v>
       </c>
+      <c r="BC13" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32439,6 +33007,9 @@
       <c r="BB14" t="n">
         <v>87</v>
       </c>
+      <c r="BC14" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32607,6 +33178,9 @@
       <c r="BB15" t="n">
         <v>40</v>
       </c>
+      <c r="BC15" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -32775,6 +33349,9 @@
       <c r="BB16" t="n">
         <v>88</v>
       </c>
+      <c r="BC16" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -32943,6 +33520,9 @@
       <c r="BB17" t="n">
         <v>85</v>
       </c>
+      <c r="BC17" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -33111,6 +33691,9 @@
       <c r="BB18" t="n">
         <v>54</v>
       </c>
+      <c r="BC18" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -33278,6 +33861,9 @@
       </c>
       <c r="BB19" t="n">
         <v>50</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -33291,7 +33877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33308,6 +33894,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33357,6 +33944,9 @@
       <c r="N1" s="1" t="n">
         <v>20251212</v>
       </c>
+      <c r="O1" s="1" t="n">
+        <v>20251215</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33405,6 +33995,9 @@
       <c r="N2" t="n">
         <v>72</v>
       </c>
+      <c r="O2" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -33453,6 +34046,9 @@
       <c r="N3" t="n">
         <v>80</v>
       </c>
+      <c r="O3" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -33501,6 +34097,9 @@
       <c r="N4" t="n">
         <v>61</v>
       </c>
+      <c r="O4" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -33549,6 +34148,9 @@
       <c r="N5" t="n">
         <v>69</v>
       </c>
+      <c r="O5" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -33597,6 +34199,9 @@
       <c r="N6" t="n">
         <v>86</v>
       </c>
+      <c r="O6" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -33645,6 +34250,9 @@
       <c r="N7" t="n">
         <v>93</v>
       </c>
+      <c r="O7" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -33693,6 +34301,9 @@
       <c r="N8" t="n">
         <v>86</v>
       </c>
+      <c r="O8" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33741,6 +34352,9 @@
       <c r="N9" t="n">
         <v>61</v>
       </c>
+      <c r="O9" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -33789,6 +34403,9 @@
       <c r="N10" t="n">
         <v>70</v>
       </c>
+      <c r="O10" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -33837,6 +34454,9 @@
       <c r="N11" t="n">
         <v>93</v>
       </c>
+      <c r="O11" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33885,6 +34505,9 @@
       <c r="N12" t="n">
         <v>93</v>
       </c>
+      <c r="O12" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33933,6 +34556,9 @@
       <c r="N13" t="n">
         <v>94</v>
       </c>
+      <c r="O13" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33981,6 +34607,9 @@
       <c r="N14" t="n">
         <v>70</v>
       </c>
+      <c r="O14" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -34029,6 +34658,9 @@
       <c r="N15" t="n">
         <v>81</v>
       </c>
+      <c r="O15" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -34077,6 +34709,9 @@
       <c r="N16" t="n">
         <v>86</v>
       </c>
+      <c r="O16" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -34125,6 +34760,9 @@
       <c r="N17" t="n">
         <v>82</v>
       </c>
+      <c r="O17" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -34173,6 +34811,9 @@
       <c r="N18" t="n">
         <v>83</v>
       </c>
+      <c r="O18" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -34220,6 +34861,9 @@
       </c>
       <c r="N19" t="n">
         <v>81</v>
+      </c>
+      <c r="O19" t="n">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -34233,7 +34877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB19"/>
+  <dimension ref="A1:BC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34290,6 +34934,7 @@
     <col width="10" customWidth="1" min="52" max="52"/>
     <col width="10" customWidth="1" min="53" max="53"/>
     <col width="10" customWidth="1" min="54" max="54"/>
+    <col width="10" customWidth="1" min="55" max="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34459,6 +35104,9 @@
       <c r="BB1" s="1" t="n">
         <v>20251212</v>
       </c>
+      <c r="BC1" s="1" t="n">
+        <v>20251215</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34627,6 +35275,9 @@
       <c r="BB2" t="n">
         <v>-49</v>
       </c>
+      <c r="BC2" t="n">
+        <v>-11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34795,6 +35446,9 @@
       <c r="BB3" t="n">
         <v>33</v>
       </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34963,6 +35617,9 @@
       <c r="BB4" t="n">
         <v>-78</v>
       </c>
+      <c r="BC4" t="n">
+        <v>-62</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -35131,6 +35788,9 @@
       <c r="BB5" t="n">
         <v>-6</v>
       </c>
+      <c r="BC5" t="n">
+        <v>-87</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -35299,6 +35959,9 @@
       <c r="BB6" t="n">
         <v>32</v>
       </c>
+      <c r="BC6" t="n">
+        <v>-13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35467,6 +36130,9 @@
       <c r="BB7" t="n">
         <v>56</v>
       </c>
+      <c r="BC7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -35635,6 +36301,9 @@
       <c r="BB8" t="n">
         <v>45</v>
       </c>
+      <c r="BC8" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35803,6 +36472,9 @@
       <c r="BB9" t="n">
         <v>43</v>
       </c>
+      <c r="BC9" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35971,6 +36643,9 @@
       <c r="BB10" t="n">
         <v>-23</v>
       </c>
+      <c r="BC10" t="n">
+        <v>-60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -36139,6 +36814,9 @@
       <c r="BB11" t="n">
         <v>61</v>
       </c>
+      <c r="BC11" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -36307,6 +36985,9 @@
       <c r="BB12" t="n">
         <v>63</v>
       </c>
+      <c r="BC12" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36475,6 +37156,9 @@
       <c r="BB13" t="n">
         <v>65</v>
       </c>
+      <c r="BC13" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36643,6 +37327,9 @@
       <c r="BB14" t="n">
         <v>51</v>
       </c>
+      <c r="BC14" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36811,6 +37498,9 @@
       <c r="BB15" t="n">
         <v>-14</v>
       </c>
+      <c r="BC15" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -36979,6 +37669,9 @@
       <c r="BB16" t="n">
         <v>62</v>
       </c>
+      <c r="BC16" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37147,6 +37840,9 @@
       <c r="BB17" t="n">
         <v>56</v>
       </c>
+      <c r="BC17" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -37315,6 +38011,9 @@
       <c r="BB18" t="n">
         <v>-27</v>
       </c>
+      <c r="BC18" t="n">
+        <v>-66</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -37482,6 +38181,9 @@
       </c>
       <c r="BB19" t="n">
         <v>-13</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -727,6 +727,7 @@
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -779,6 +780,9 @@
       <c r="O1" s="1" t="n">
         <v>20251215</v>
       </c>
+      <c r="P1" s="1" t="n">
+        <v>20251216</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -830,6 +834,9 @@
       <c r="O2" t="n">
         <v>51</v>
       </c>
+      <c r="P2" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -881,6 +888,9 @@
       <c r="O3" t="n">
         <v>20</v>
       </c>
+      <c r="P3" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -932,6 +942,9 @@
       <c r="O4" t="n">
         <v>25</v>
       </c>
+      <c r="P4" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -983,6 +996,9 @@
       <c r="O5" t="n">
         <v>-17</v>
       </c>
+      <c r="P5" t="n">
+        <v>-40</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1034,6 +1050,9 @@
       <c r="O6" t="n">
         <v>26</v>
       </c>
+      <c r="P6" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1085,6 +1104,9 @@
       <c r="O7" t="n">
         <v>36</v>
       </c>
+      <c r="P7" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1136,6 +1158,9 @@
       <c r="O8" t="n">
         <v>22</v>
       </c>
+      <c r="P8" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1187,6 +1212,9 @@
       <c r="O9" t="n">
         <v>24</v>
       </c>
+      <c r="P9" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1238,6 +1266,9 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
+      <c r="P10" t="n">
+        <v>-28</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1289,6 +1320,9 @@
       <c r="O11" t="n">
         <v>54</v>
       </c>
+      <c r="P11" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1340,6 +1374,9 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
+      <c r="P12" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1391,6 +1428,9 @@
       <c r="O13" t="n">
         <v>62</v>
       </c>
+      <c r="P13" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1442,6 +1482,9 @@
       <c r="O14" t="n">
         <v>33</v>
       </c>
+      <c r="P14" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1493,6 +1536,9 @@
       <c r="O15" t="n">
         <v>63</v>
       </c>
+      <c r="P15" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1544,6 +1590,9 @@
       <c r="O16" t="n">
         <v>47</v>
       </c>
+      <c r="P16" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1595,6 +1644,9 @@
       <c r="O17" t="n">
         <v>43</v>
       </c>
+      <c r="P17" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1646,6 +1698,9 @@
       <c r="O18" t="n">
         <v>22</v>
       </c>
+      <c r="P18" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1696,6 +1751,9 @@
       </c>
       <c r="O19" t="n">
         <v>66</v>
+      </c>
+      <c r="P19" t="n">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1709,7 +1767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC19"/>
+  <dimension ref="A1:BD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1767,6 +1825,7 @@
     <col width="12" customWidth="1" min="53" max="53"/>
     <col width="12" customWidth="1" min="54" max="54"/>
     <col width="12" customWidth="1" min="55" max="55"/>
+    <col width="12" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2045,6 +2104,11 @@
           <t>20251215</t>
         </is>
       </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>20251216</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2216,6 +2280,9 @@
       <c r="BC2" t="n">
         <v>99</v>
       </c>
+      <c r="BD2" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2387,6 +2454,9 @@
       <c r="BC3" t="n">
         <v>100</v>
       </c>
+      <c r="BD3" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2558,6 +2628,9 @@
       <c r="BC4" t="n">
         <v>97</v>
       </c>
+      <c r="BD4" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2729,6 +2802,9 @@
       <c r="BC5" t="n">
         <v>96</v>
       </c>
+      <c r="BD5" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2900,6 +2976,9 @@
       <c r="BC6" t="n">
         <v>99</v>
       </c>
+      <c r="BD6" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3071,6 +3150,9 @@
       <c r="BC7" t="n">
         <v>101</v>
       </c>
+      <c r="BD7" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3242,6 +3324,9 @@
       <c r="BC8" t="n">
         <v>100</v>
       </c>
+      <c r="BD8" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3413,6 +3498,9 @@
       <c r="BC9" t="n">
         <v>104</v>
       </c>
+      <c r="BD9" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3584,6 +3672,9 @@
       <c r="BC10" t="n">
         <v>97</v>
       </c>
+      <c r="BD10" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3755,6 +3846,9 @@
       <c r="BC11" t="n">
         <v>106</v>
       </c>
+      <c r="BD11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3926,6 +4020,9 @@
       <c r="BC12" t="n">
         <v>108</v>
       </c>
+      <c r="BD12" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4097,6 +4194,9 @@
       <c r="BC13" t="n">
         <v>110</v>
       </c>
+      <c r="BD13" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4268,6 +4368,9 @@
       <c r="BC14" t="n">
         <v>107</v>
       </c>
+      <c r="BD14" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4439,6 +4542,9 @@
       <c r="BC15" t="n">
         <v>101</v>
       </c>
+      <c r="BD15" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4610,6 +4716,9 @@
       <c r="BC16" t="n">
         <v>106</v>
       </c>
+      <c r="BD16" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4781,6 +4890,9 @@
       <c r="BC17" t="n">
         <v>106</v>
       </c>
+      <c r="BD17" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4952,6 +5064,9 @@
       <c r="BC18" t="n">
         <v>96</v>
       </c>
+      <c r="BD18" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5122,6 +5237,9 @@
       </c>
       <c r="BC19" t="n">
         <v>101</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -5135,7 +5253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ19"/>
+  <dimension ref="A1:AK19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5174,6 +5292,7 @@
     <col width="12" customWidth="1" min="34" max="34"/>
     <col width="12" customWidth="1" min="35" max="35"/>
     <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5357,6 +5476,11 @@
           <t>20251215</t>
         </is>
       </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>20251216</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5471,6 +5595,9 @@
       <c r="AJ2" t="n">
         <v>-39.8</v>
       </c>
+      <c r="AK2" t="n">
+        <v>-35.6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5585,6 +5712,9 @@
       <c r="AJ3" t="n">
         <v>-20.83</v>
       </c>
+      <c r="AK3" t="n">
+        <v>-18.19</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5699,6 +5829,9 @@
       <c r="AJ4" t="n">
         <v>-30.2</v>
       </c>
+      <c r="AK4" t="n">
+        <v>-25.06</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5813,6 +5946,9 @@
       <c r="AJ5" t="n">
         <v>-27.09</v>
       </c>
+      <c r="AK5" t="n">
+        <v>-13.26</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5927,6 +6063,9 @@
       <c r="AJ6" t="n">
         <v>-9.34</v>
       </c>
+      <c r="AK6" t="n">
+        <v>-5.34</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6041,6 +6180,9 @@
       <c r="AJ7" t="n">
         <v>5.55</v>
       </c>
+      <c r="AK7" t="n">
+        <v>3.02</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6155,6 +6297,9 @@
       <c r="AJ8" t="n">
         <v>-17.08</v>
       </c>
+      <c r="AK8" t="n">
+        <v>-14.84</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6269,6 +6414,9 @@
       <c r="AJ9" t="n">
         <v>-35.54</v>
       </c>
+      <c r="AK9" t="n">
+        <v>-32.98</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6383,6 +6531,9 @@
       <c r="AJ10" t="n">
         <v>-8.25</v>
       </c>
+      <c r="AK10" t="n">
+        <v>3.26</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6497,6 +6648,9 @@
       <c r="AJ11" t="n">
         <v>31.34</v>
       </c>
+      <c r="AK11" t="n">
+        <v>26.54</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6611,6 +6765,9 @@
       <c r="AJ12" t="n">
         <v>32.7</v>
       </c>
+      <c r="AK12" t="n">
+        <v>27.98</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6725,6 +6882,9 @@
       <c r="AJ13" t="n">
         <v>46.47</v>
       </c>
+      <c r="AK13" t="n">
+        <v>39.39</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6839,6 +6999,9 @@
       <c r="AJ14" t="n">
         <v>-20.39</v>
       </c>
+      <c r="AK14" t="n">
+        <v>-19.58</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6953,6 +7116,9 @@
       <c r="AJ15" t="n">
         <v>-50.05</v>
       </c>
+      <c r="AK15" t="n">
+        <v>-48.32</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7067,6 +7233,9 @@
       <c r="AJ16" t="n">
         <v>8.380000000000001</v>
       </c>
+      <c r="AK16" t="n">
+        <v>6.52</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7181,6 +7350,9 @@
       <c r="AJ17" t="n">
         <v>2.3</v>
       </c>
+      <c r="AK17" t="n">
+        <v>0.99</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7295,6 +7467,9 @@
       <c r="AJ18" t="n">
         <v>-5.1</v>
       </c>
+      <c r="AK18" t="n">
+        <v>8.550000000000001</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7408,6 +7583,9 @@
       </c>
       <c r="AJ19" t="n">
         <v>-46.39</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-44.61</v>
       </c>
     </row>
   </sheetData>
@@ -7421,7 +7599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7439,6 +7617,7 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7517,6 +7696,11 @@
           <t>20251215</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>20251216</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7568,6 +7752,9 @@
       <c r="O2" t="n">
         <v>27</v>
       </c>
+      <c r="P2" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7619,6 +7806,9 @@
       <c r="O3" t="n">
         <v>41</v>
       </c>
+      <c r="P3" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7670,6 +7860,9 @@
       <c r="O4" t="n">
         <v>29</v>
       </c>
+      <c r="P4" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7721,6 +7914,9 @@
       <c r="O5" t="n">
         <v>21</v>
       </c>
+      <c r="P5" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7772,6 +7968,9 @@
       <c r="O6" t="n">
         <v>34</v>
       </c>
+      <c r="P6" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7823,6 +8022,9 @@
       <c r="O7" t="n">
         <v>23</v>
       </c>
+      <c r="P7" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7874,6 +8076,9 @@
       <c r="O8" t="n">
         <v>33</v>
       </c>
+      <c r="P8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7925,6 +8130,9 @@
       <c r="O9" t="n">
         <v>24</v>
       </c>
+      <c r="P9" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7976,6 +8184,9 @@
       <c r="O10" t="n">
         <v>20</v>
       </c>
+      <c r="P10" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8027,6 +8238,9 @@
       <c r="O11" t="n">
         <v>18</v>
       </c>
+      <c r="P11" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8078,6 +8292,9 @@
       <c r="O12" t="n">
         <v>29</v>
       </c>
+      <c r="P12" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8129,6 +8346,9 @@
       <c r="O13" t="n">
         <v>38</v>
       </c>
+      <c r="P13" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8180,6 +8400,9 @@
       <c r="O14" t="n">
         <v>26</v>
       </c>
+      <c r="P14" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8231,6 +8454,9 @@
       <c r="O15" t="n">
         <v>23</v>
       </c>
+      <c r="P15" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8282,6 +8508,9 @@
       <c r="O16" t="n">
         <v>39</v>
       </c>
+      <c r="P16" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8333,6 +8562,9 @@
       <c r="O17" t="n">
         <v>10</v>
       </c>
+      <c r="P17" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8384,6 +8616,9 @@
       <c r="O18" t="n">
         <v>20</v>
       </c>
+      <c r="P18" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8434,6 +8669,9 @@
       </c>
       <c r="O19" t="n">
         <v>24</v>
+      </c>
+      <c r="P19" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -8447,7 +8685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV19"/>
+  <dimension ref="A1:BW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8524,6 +8762,7 @@
     <col width="12" customWidth="1" min="72" max="72"/>
     <col width="12" customWidth="1" min="73" max="73"/>
     <col width="12" customWidth="1" min="74" max="74"/>
+    <col width="12" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8753,6 +8992,9 @@
       <c r="BV1" s="1" t="n">
         <v>20251215</v>
       </c>
+      <c r="BW1" s="1" t="n">
+        <v>20251216</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8981,6 +9223,9 @@
       <c r="BV2" t="n">
         <v>15305</v>
       </c>
+      <c r="BW2" t="n">
+        <v>15980</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9209,6 +9454,9 @@
       <c r="BV3" t="n">
         <v>55450</v>
       </c>
+      <c r="BW3" t="n">
+        <v>55610</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9437,6 +9685,9 @@
       <c r="BV4" t="n">
         <v>17675</v>
       </c>
+      <c r="BW4" t="n">
+        <v>18025</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9665,6 +9916,9 @@
       <c r="BV5" t="n">
         <v>15200</v>
       </c>
+      <c r="BW5" t="n">
+        <v>15255</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9893,6 +10147,9 @@
       <c r="BV6" t="n">
         <v>16435</v>
       </c>
+      <c r="BW6" t="n">
+        <v>16360</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10121,6 +10378,9 @@
       <c r="BV7" t="n">
         <v>19105</v>
       </c>
+      <c r="BW7" t="n">
+        <v>19115</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10349,6 +10609,9 @@
       <c r="BV8" t="n">
         <v>17925</v>
       </c>
+      <c r="BW8" t="n">
+        <v>17915</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10577,6 +10840,9 @@
       <c r="BV9" t="n">
         <v>1560</v>
       </c>
+      <c r="BW9" t="n">
+        <v>1597</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10805,6 +11071,9 @@
       <c r="BV10" t="n">
         <v>16385</v>
       </c>
+      <c r="BW10" t="n">
+        <v>16385</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11033,6 +11302,9 @@
       <c r="BV11" t="n">
         <v>5505</v>
       </c>
+      <c r="BW11" t="n">
+        <v>5665</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11261,6 +11533,9 @@
       <c r="BV12" t="n">
         <v>6005</v>
       </c>
+      <c r="BW12" t="n">
+        <v>6155</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11489,6 +11764,9 @@
       <c r="BV13" t="n">
         <v>6065</v>
       </c>
+      <c r="BW13" t="n">
+        <v>6225</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11717,6 +11995,9 @@
       <c r="BV14" t="n">
         <v>1702</v>
       </c>
+      <c r="BW14" t="n">
+        <v>1756</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11945,6 +12226,9 @@
       <c r="BV15" t="n">
         <v>19180</v>
       </c>
+      <c r="BW15" t="n">
+        <v>19720</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12173,6 +12457,9 @@
       <c r="BV16" t="n">
         <v>11250</v>
       </c>
+      <c r="BW16" t="n">
+        <v>11355</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12401,6 +12688,9 @@
       <c r="BV17" t="n">
         <v>6640</v>
       </c>
+      <c r="BW17" t="n">
+        <v>6780</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12629,6 +12919,9 @@
       <c r="BV18" t="n">
         <v>17240</v>
       </c>
+      <c r="BW18" t="n">
+        <v>17095</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12856,6 +13149,9 @@
       </c>
       <c r="BV19" t="n">
         <v>15945</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>16355</v>
       </c>
     </row>
   </sheetData>
@@ -12869,7 +13165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV19"/>
+  <dimension ref="A1:BW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12946,6 +13242,7 @@
     <col width="12" customWidth="1" min="72" max="72"/>
     <col width="12" customWidth="1" min="73" max="73"/>
     <col width="12" customWidth="1" min="74" max="74"/>
+    <col width="12" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13175,6 +13472,9 @@
       <c r="BV1" s="1" t="n">
         <v>20251215</v>
       </c>
+      <c r="BW1" s="1" t="n">
+        <v>20251216</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13403,6 +13703,9 @@
       <c r="BV2" t="n">
         <v>15800</v>
       </c>
+      <c r="BW2" t="n">
+        <v>16020</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13631,6 +13934,9 @@
       <c r="BV3" t="n">
         <v>56475</v>
       </c>
+      <c r="BW3" t="n">
+        <v>55855</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13859,6 +14165,9 @@
       <c r="BV4" t="n">
         <v>18005</v>
       </c>
+      <c r="BW4" t="n">
+        <v>18050</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14087,6 +14396,9 @@
       <c r="BV5" t="n">
         <v>15430</v>
       </c>
+      <c r="BW5" t="n">
+        <v>15255</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14315,6 +14627,9 @@
       <c r="BV6" t="n">
         <v>16610</v>
       </c>
+      <c r="BW6" t="n">
+        <v>16465</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14543,6 +14858,9 @@
       <c r="BV7" t="n">
         <v>19370</v>
       </c>
+      <c r="BW7" t="n">
+        <v>19230</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14771,6 +15089,9 @@
       <c r="BV8" t="n">
         <v>18190</v>
       </c>
+      <c r="BW8" t="n">
+        <v>18040</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14999,6 +15320,9 @@
       <c r="BV9" t="n">
         <v>1630</v>
       </c>
+      <c r="BW9" t="n">
+        <v>1597</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15227,6 +15551,9 @@
       <c r="BV10" t="n">
         <v>16550</v>
       </c>
+      <c r="BW10" t="n">
+        <v>16390</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15455,6 +15782,9 @@
       <c r="BV11" t="n">
         <v>5730</v>
       </c>
+      <c r="BW11" t="n">
+        <v>5665</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15683,6 +16013,9 @@
       <c r="BV12" t="n">
         <v>6230</v>
       </c>
+      <c r="BW12" t="n">
+        <v>6155</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15911,6 +16244,9 @@
       <c r="BV13" t="n">
         <v>6310</v>
       </c>
+      <c r="BW13" t="n">
+        <v>6225</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16139,6 +16475,9 @@
       <c r="BV14" t="n">
         <v>1797</v>
       </c>
+      <c r="BW14" t="n">
+        <v>1756</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -16367,6 +16706,9 @@
       <c r="BV15" t="n">
         <v>19665</v>
       </c>
+      <c r="BW15" t="n">
+        <v>19795</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -16595,6 +16937,9 @@
       <c r="BV16" t="n">
         <v>11550</v>
       </c>
+      <c r="BW16" t="n">
+        <v>11385</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16823,6 +17168,9 @@
       <c r="BV17" t="n">
         <v>6850</v>
       </c>
+      <c r="BW17" t="n">
+        <v>6780</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17051,6 +17399,9 @@
       <c r="BV18" t="n">
         <v>17450</v>
       </c>
+      <c r="BW18" t="n">
+        <v>17225</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17278,6 +17629,9 @@
       </c>
       <c r="BV19" t="n">
         <v>16295</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>16355</v>
       </c>
     </row>
   </sheetData>
@@ -17291,7 +17645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV19"/>
+  <dimension ref="A1:BW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17368,6 +17722,7 @@
     <col width="12" customWidth="1" min="72" max="72"/>
     <col width="12" customWidth="1" min="73" max="73"/>
     <col width="12" customWidth="1" min="74" max="74"/>
+    <col width="12" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17597,6 +17952,9 @@
       <c r="BV1" s="1" t="n">
         <v>20251215</v>
       </c>
+      <c r="BW1" s="1" t="n">
+        <v>20251216</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17825,6 +18183,9 @@
       <c r="BV2" t="n">
         <v>15300</v>
       </c>
+      <c r="BW2" t="n">
+        <v>15270</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18053,6 +18414,9 @@
       <c r="BV3" t="n">
         <v>55150</v>
       </c>
+      <c r="BW3" t="n">
+        <v>54185</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18281,6 +18645,9 @@
       <c r="BV4" t="n">
         <v>17665</v>
       </c>
+      <c r="BW4" t="n">
+        <v>17650</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18509,6 +18876,9 @@
       <c r="BV5" t="n">
         <v>15200</v>
       </c>
+      <c r="BW5" t="n">
+        <v>14800</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18737,6 +19107,9 @@
       <c r="BV6" t="n">
         <v>16290</v>
       </c>
+      <c r="BW6" t="n">
+        <v>15990</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18965,6 +19338,9 @@
       <c r="BV7" t="n">
         <v>19025</v>
       </c>
+      <c r="BW7" t="n">
+        <v>18640</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19193,6 +19569,9 @@
       <c r="BV8" t="n">
         <v>17805</v>
       </c>
+      <c r="BW8" t="n">
+        <v>17490</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19421,6 +19800,9 @@
       <c r="BV9" t="n">
         <v>1536</v>
       </c>
+      <c r="BW9" t="n">
+        <v>1435</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19649,6 +20031,9 @@
       <c r="BV10" t="n">
         <v>16220</v>
       </c>
+      <c r="BW10" t="n">
+        <v>15905</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -19877,6 +20262,9 @@
       <c r="BV11" t="n">
         <v>5505</v>
       </c>
+      <c r="BW11" t="n">
+        <v>5295</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -20105,6 +20493,9 @@
       <c r="BV12" t="n">
         <v>5960</v>
       </c>
+      <c r="BW12" t="n">
+        <v>5715</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -20333,6 +20724,9 @@
       <c r="BV13" t="n">
         <v>6030</v>
       </c>
+      <c r="BW13" t="n">
+        <v>5765</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -20561,6 +20955,9 @@
       <c r="BV14" t="n">
         <v>1685</v>
       </c>
+      <c r="BW14" t="n">
+        <v>1572</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -20789,6 +21186,9 @@
       <c r="BV15" t="n">
         <v>19090</v>
       </c>
+      <c r="BW15" t="n">
+        <v>19240</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -21017,6 +21417,9 @@
       <c r="BV16" t="n">
         <v>11130</v>
       </c>
+      <c r="BW16" t="n">
+        <v>10735</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -21245,6 +21648,9 @@
       <c r="BV17" t="n">
         <v>6585</v>
       </c>
+      <c r="BW17" t="n">
+        <v>6350</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -21473,6 +21879,9 @@
       <c r="BV18" t="n">
         <v>17020</v>
       </c>
+      <c r="BW18" t="n">
+        <v>16625</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -21700,6 +22109,9 @@
       </c>
       <c r="BV19" t="n">
         <v>15860</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>16015</v>
       </c>
     </row>
   </sheetData>
@@ -21713,7 +22125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV19"/>
+  <dimension ref="A1:BW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21790,6 +22202,7 @@
     <col width="12" customWidth="1" min="72" max="72"/>
     <col width="12" customWidth="1" min="73" max="73"/>
     <col width="12" customWidth="1" min="74" max="74"/>
+    <col width="12" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22019,6 +22432,9 @@
       <c r="BV1" s="1" t="n">
         <v>20251215</v>
       </c>
+      <c r="BW1" s="1" t="n">
+        <v>20251216</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22247,6 +22663,9 @@
       <c r="BV2" t="n">
         <v>15765</v>
       </c>
+      <c r="BW2" t="n">
+        <v>15305</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22475,6 +22894,9 @@
       <c r="BV3" t="n">
         <v>56095</v>
       </c>
+      <c r="BW3" t="n">
+        <v>54205</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22703,6 +23125,9 @@
       <c r="BV4" t="n">
         <v>17905</v>
       </c>
+      <c r="BW4" t="n">
+        <v>17850</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22931,6 +23356,9 @@
       <c r="BV5" t="n">
         <v>15255</v>
       </c>
+      <c r="BW5" t="n">
+        <v>14800</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23159,6 +23587,9 @@
       <c r="BV6" t="n">
         <v>16495</v>
       </c>
+      <c r="BW6" t="n">
+        <v>16000</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23387,6 +23818,9 @@
       <c r="BV7" t="n">
         <v>19220</v>
       </c>
+      <c r="BW7" t="n">
+        <v>18700</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23615,6 +24049,9 @@
       <c r="BV8" t="n">
         <v>18045</v>
       </c>
+      <c r="BW8" t="n">
+        <v>17505</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23843,6 +24280,9 @@
       <c r="BV9" t="n">
         <v>1597</v>
       </c>
+      <c r="BW9" t="n">
+        <v>1450</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24071,6 +24511,9 @@
       <c r="BV10" t="n">
         <v>16495</v>
       </c>
+      <c r="BW10" t="n">
+        <v>15940</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24299,6 +24742,9 @@
       <c r="BV11" t="n">
         <v>5650</v>
       </c>
+      <c r="BW11" t="n">
+        <v>5345</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24527,6 +24973,9 @@
       <c r="BV12" t="n">
         <v>6155</v>
       </c>
+      <c r="BW12" t="n">
+        <v>5770</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24755,6 +25204,9 @@
       <c r="BV13" t="n">
         <v>6230</v>
       </c>
+      <c r="BW13" t="n">
+        <v>5800</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24983,6 +25435,9 @@
       <c r="BV14" t="n">
         <v>1757</v>
       </c>
+      <c r="BW14" t="n">
+        <v>1589</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -25211,6 +25666,9 @@
       <c r="BV15" t="n">
         <v>19590</v>
       </c>
+      <c r="BW15" t="n">
+        <v>19315</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25439,6 +25897,9 @@
       <c r="BV16" t="n">
         <v>11430</v>
       </c>
+      <c r="BW16" t="n">
+        <v>10800</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -25667,6 +26128,9 @@
       <c r="BV17" t="n">
         <v>6780</v>
       </c>
+      <c r="BW17" t="n">
+        <v>6390</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25895,6 +26359,9 @@
       <c r="BV18" t="n">
         <v>17365</v>
       </c>
+      <c r="BW18" t="n">
+        <v>16625</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -26122,6 +26589,9 @@
       </c>
       <c r="BV19" t="n">
         <v>16275</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>16105</v>
       </c>
     </row>
   </sheetData>
@@ -26135,7 +26605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV19"/>
+  <dimension ref="A1:BW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26212,6 +26682,7 @@
     <col width="12" customWidth="1" min="72" max="72"/>
     <col width="12" customWidth="1" min="73" max="73"/>
     <col width="12" customWidth="1" min="74" max="74"/>
+    <col width="12" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26441,6 +26912,9 @@
       <c r="BV1" s="1" t="n">
         <v>20251215</v>
       </c>
+      <c r="BW1" s="1" t="n">
+        <v>20251216</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26669,6 +27143,9 @@
       <c r="BV2" t="n">
         <v>61069</v>
       </c>
+      <c r="BW2" t="n">
+        <v>95386</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26897,6 +27374,9 @@
       <c r="BV3" t="n">
         <v>1890995</v>
       </c>
+      <c r="BW3" t="n">
+        <v>1808751</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -27125,6 +27605,9 @@
       <c r="BV4" t="n">
         <v>92711</v>
       </c>
+      <c r="BW4" t="n">
+        <v>102885</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27353,6 +27836,9 @@
       <c r="BV5" t="n">
         <v>355917</v>
       </c>
+      <c r="BW5" t="n">
+        <v>148732</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27581,6 +28067,9 @@
       <c r="BV6" t="n">
         <v>1362916</v>
       </c>
+      <c r="BW6" t="n">
+        <v>1103940</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27809,6 +28298,9 @@
       <c r="BV7" t="n">
         <v>1801208</v>
       </c>
+      <c r="BW7" t="n">
+        <v>1542023</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28037,6 +28529,9 @@
       <c r="BV8" t="n">
         <v>4682435</v>
       </c>
+      <c r="BW8" t="n">
+        <v>3610469</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28265,6 +28760,9 @@
       <c r="BV9" t="n">
         <v>3449147</v>
       </c>
+      <c r="BW9" t="n">
+        <v>11143633</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28493,6 +28991,9 @@
       <c r="BV10" t="n">
         <v>589028</v>
       </c>
+      <c r="BW10" t="n">
+        <v>497548</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28721,6 +29222,9 @@
       <c r="BV11" t="n">
         <v>446617</v>
       </c>
+      <c r="BW11" t="n">
+        <v>998111</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28949,6 +29453,9 @@
       <c r="BV12" t="n">
         <v>1645650</v>
       </c>
+      <c r="BW12" t="n">
+        <v>2659587</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29177,6 +29684,9 @@
       <c r="BV13" t="n">
         <v>5160285</v>
       </c>
+      <c r="BW13" t="n">
+        <v>6999846</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29405,6 +29915,9 @@
       <c r="BV14" t="n">
         <v>26438181</v>
       </c>
+      <c r="BW14" t="n">
+        <v>42943771</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -29633,6 +30146,9 @@
       <c r="BV15" t="n">
         <v>751498</v>
       </c>
+      <c r="BW15" t="n">
+        <v>774978</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -29861,6 +30377,9 @@
       <c r="BV16" t="n">
         <v>473598</v>
       </c>
+      <c r="BW16" t="n">
+        <v>378057</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -30089,6 +30608,9 @@
       <c r="BV17" t="n">
         <v>48746</v>
       </c>
+      <c r="BW17" t="n">
+        <v>43223</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -30317,6 +30839,9 @@
       <c r="BV18" t="n">
         <v>71766</v>
       </c>
+      <c r="BW18" t="n">
+        <v>53681</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -30544,6 +31069,9 @@
       </c>
       <c r="BV19" t="n">
         <v>22828</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>21341</v>
       </c>
     </row>
   </sheetData>
@@ -30557,7 +31085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC19"/>
+  <dimension ref="A1:BD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -30615,6 +31143,7 @@
     <col width="10" customWidth="1" min="53" max="53"/>
     <col width="10" customWidth="1" min="54" max="54"/>
     <col width="10" customWidth="1" min="55" max="55"/>
+    <col width="10" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30787,6 +31316,9 @@
       <c r="BC1" s="1" t="n">
         <v>20251215</v>
       </c>
+      <c r="BD1" s="1" t="n">
+        <v>20251216</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30958,6 +31490,9 @@
       <c r="BC2" t="n">
         <v>49</v>
       </c>
+      <c r="BD2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31129,6 +31664,9 @@
       <c r="BC3" t="n">
         <v>63</v>
       </c>
+      <c r="BD3" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -31300,6 +31838,9 @@
       <c r="BC4" t="n">
         <v>6</v>
       </c>
+      <c r="BD4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -31471,6 +32012,9 @@
       <c r="BC5" t="n">
         <v>19</v>
       </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -31642,6 +32186,9 @@
       <c r="BC6" t="n">
         <v>56</v>
       </c>
+      <c r="BD6" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -31813,6 +32360,9 @@
       <c r="BC7" t="n">
         <v>71</v>
       </c>
+      <c r="BD7" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -31984,6 +32534,9 @@
       <c r="BC8" t="n">
         <v>61</v>
       </c>
+      <c r="BD8" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -32155,6 +32708,9 @@
       <c r="BC9" t="n">
         <v>80</v>
       </c>
+      <c r="BD9" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -32326,6 +32882,9 @@
       <c r="BC10" t="n">
         <v>34</v>
       </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -32497,6 +33056,9 @@
       <c r="BC11" t="n">
         <v>87</v>
       </c>
+      <c r="BD11" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32668,6 +33230,9 @@
       <c r="BC12" t="n">
         <v>89</v>
       </c>
+      <c r="BD12" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32839,6 +33404,9 @@
       <c r="BC13" t="n">
         <v>91</v>
       </c>
+      <c r="BD13" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33010,6 +33578,9 @@
       <c r="BC14" t="n">
         <v>85</v>
       </c>
+      <c r="BD14" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -33181,6 +33752,9 @@
       <c r="BC15" t="n">
         <v>56</v>
       </c>
+      <c r="BD15" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -33352,6 +33926,9 @@
       <c r="BC16" t="n">
         <v>88</v>
       </c>
+      <c r="BD16" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -33523,6 +34100,9 @@
       <c r="BC17" t="n">
         <v>86</v>
       </c>
+      <c r="BD17" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -33694,6 +34274,9 @@
       <c r="BC18" t="n">
         <v>29</v>
       </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -33864,6 +34447,9 @@
       </c>
       <c r="BC19" t="n">
         <v>70</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -33877,7 +34463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33895,6 +34481,7 @@
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33947,6 +34534,9 @@
       <c r="O1" s="1" t="n">
         <v>20251215</v>
       </c>
+      <c r="P1" s="1" t="n">
+        <v>20251216</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33998,6 +34588,9 @@
       <c r="O2" t="n">
         <v>80</v>
       </c>
+      <c r="P2" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34049,6 +34642,9 @@
       <c r="O3" t="n">
         <v>72</v>
       </c>
+      <c r="P3" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34100,6 +34696,9 @@
       <c r="O4" t="n">
         <v>63</v>
       </c>
+      <c r="P4" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34151,6 +34750,9 @@
       <c r="O5" t="n">
         <v>53</v>
       </c>
+      <c r="P5" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34202,6 +34804,9 @@
       <c r="O6" t="n">
         <v>77</v>
       </c>
+      <c r="P6" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -34253,6 +34858,9 @@
       <c r="O7" t="n">
         <v>83</v>
       </c>
+      <c r="P7" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -34304,6 +34912,9 @@
       <c r="O8" t="n">
         <v>76</v>
       </c>
+      <c r="P8" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -34355,6 +34966,9 @@
       <c r="O9" t="n">
         <v>60</v>
       </c>
+      <c r="P9" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34406,6 +35020,9 @@
       <c r="O10" t="n">
         <v>60</v>
       </c>
+      <c r="P10" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -34457,6 +35074,9 @@
       <c r="O11" t="n">
         <v>93</v>
       </c>
+      <c r="P11" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -34508,6 +35128,9 @@
       <c r="O12" t="n">
         <v>94</v>
       </c>
+      <c r="P12" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34559,6 +35182,9 @@
       <c r="O13" t="n">
         <v>95</v>
       </c>
+      <c r="P13" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34610,6 +35236,9 @@
       <c r="O14" t="n">
         <v>69</v>
       </c>
+      <c r="P14" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -34661,6 +35290,9 @@
       <c r="O15" t="n">
         <v>86</v>
       </c>
+      <c r="P15" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -34712,6 +35344,9 @@
       <c r="O16" t="n">
         <v>86</v>
       </c>
+      <c r="P16" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -34763,6 +35398,9 @@
       <c r="O17" t="n">
         <v>83</v>
       </c>
+      <c r="P17" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -34814,6 +35452,9 @@
       <c r="O18" t="n">
         <v>73</v>
       </c>
+      <c r="P18" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -34864,6 +35505,9 @@
       </c>
       <c r="O19" t="n">
         <v>89</v>
+      </c>
+      <c r="P19" t="n">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -34877,7 +35521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC19"/>
+  <dimension ref="A1:BD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34935,6 +35579,7 @@
     <col width="10" customWidth="1" min="53" max="53"/>
     <col width="10" customWidth="1" min="54" max="54"/>
     <col width="10" customWidth="1" min="55" max="55"/>
+    <col width="10" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35107,6 +35752,9 @@
       <c r="BC1" s="1" t="n">
         <v>20251215</v>
       </c>
+      <c r="BD1" s="1" t="n">
+        <v>20251216</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35278,6 +35926,9 @@
       <c r="BC2" t="n">
         <v>-11</v>
       </c>
+      <c r="BD2" t="n">
+        <v>-61</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -35449,6 +36100,9 @@
       <c r="BC3" t="n">
         <v>0</v>
       </c>
+      <c r="BD3" t="n">
+        <v>-53</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -35620,6 +36274,9 @@
       <c r="BC4" t="n">
         <v>-62</v>
       </c>
+      <c r="BD4" t="n">
+        <v>-60</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -35791,6 +36448,9 @@
       <c r="BC5" t="n">
         <v>-87</v>
       </c>
+      <c r="BD5" t="n">
+        <v>-119</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -35962,6 +36622,9 @@
       <c r="BC6" t="n">
         <v>-13</v>
       </c>
+      <c r="BD6" t="n">
+        <v>-59</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -36133,6 +36796,9 @@
       <c r="BC7" t="n">
         <v>14</v>
       </c>
+      <c r="BD7" t="n">
+        <v>-25</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -36304,6 +36970,9 @@
       <c r="BC8" t="n">
         <v>-2</v>
       </c>
+      <c r="BD8" t="n">
+        <v>-49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -36475,6 +37144,9 @@
       <c r="BC9" t="n">
         <v>42</v>
       </c>
+      <c r="BD9" t="n">
+        <v>-47</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -36646,6 +37318,9 @@
       <c r="BC10" t="n">
         <v>-60</v>
       </c>
+      <c r="BD10" t="n">
+        <v>-103</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -36817,6 +37492,9 @@
       <c r="BC11" t="n">
         <v>57</v>
       </c>
+      <c r="BD11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -36988,6 +37666,9 @@
       <c r="BC12" t="n">
         <v>60</v>
       </c>
+      <c r="BD12" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -37159,6 +37840,9 @@
       <c r="BC13" t="n">
         <v>62</v>
       </c>
+      <c r="BD13" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37330,6 +38014,9 @@
       <c r="BC14" t="n">
         <v>48</v>
       </c>
+      <c r="BD14" t="n">
+        <v>-24</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37501,6 +38188,9 @@
       <c r="BC15" t="n">
         <v>13</v>
       </c>
+      <c r="BD15" t="n">
+        <v>-12</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -37672,6 +38362,9 @@
       <c r="BC16" t="n">
         <v>58</v>
       </c>
+      <c r="BD16" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37843,6 +38536,9 @@
       <c r="BC17" t="n">
         <v>55</v>
       </c>
+      <c r="BD17" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -38014,6 +38710,9 @@
       <c r="BC18" t="n">
         <v>-66</v>
       </c>
+      <c r="BD18" t="n">
+        <v>-113</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -38184,6 +38883,9 @@
       </c>
       <c r="BC19" t="n">
         <v>22</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -728,6 +728,7 @@
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -783,6 +784,9 @@
       <c r="P1" s="1" t="n">
         <v>20251216</v>
       </c>
+      <c r="Q1" s="1" t="n">
+        <v>20251217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -837,6 +841,9 @@
       <c r="P2" t="n">
         <v>32</v>
       </c>
+      <c r="Q2" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -891,6 +898,9 @@
       <c r="P3" t="n">
         <v>-1</v>
       </c>
+      <c r="Q3" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -945,6 +955,9 @@
       <c r="P4" t="n">
         <v>22</v>
       </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -999,6 +1012,9 @@
       <c r="P5" t="n">
         <v>-40</v>
       </c>
+      <c r="Q5" t="n">
+        <v>-11</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1053,6 +1069,9 @@
       <c r="P6" t="n">
         <v>9</v>
       </c>
+      <c r="Q6" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1107,6 +1126,9 @@
       <c r="P7" t="n">
         <v>21</v>
       </c>
+      <c r="Q7" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1161,6 +1183,9 @@
       <c r="P8" t="n">
         <v>5</v>
       </c>
+      <c r="Q8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1215,6 +1240,9 @@
       <c r="P9" t="n">
         <v>-3</v>
       </c>
+      <c r="Q9" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1269,6 +1297,9 @@
       <c r="P10" t="n">
         <v>-28</v>
       </c>
+      <c r="Q10" t="n">
+        <v>-7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1323,6 +1354,9 @@
       <c r="P11" t="n">
         <v>30</v>
       </c>
+      <c r="Q11" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1377,6 +1411,9 @@
       <c r="P12" t="n">
         <v>30</v>
       </c>
+      <c r="Q12" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1431,6 +1468,9 @@
       <c r="P13" t="n">
         <v>35</v>
       </c>
+      <c r="Q13" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1485,6 +1525,9 @@
       <c r="P14" t="n">
         <v>7</v>
       </c>
+      <c r="Q14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1539,6 +1582,9 @@
       <c r="P15" t="n">
         <v>55</v>
       </c>
+      <c r="Q15" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1593,6 +1639,9 @@
       <c r="P16" t="n">
         <v>22</v>
       </c>
+      <c r="Q16" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1647,6 +1696,9 @@
       <c r="P17" t="n">
         <v>19</v>
       </c>
+      <c r="Q17" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1701,6 +1753,9 @@
       <c r="P18" t="n">
         <v>-2</v>
       </c>
+      <c r="Q18" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1754,6 +1809,9 @@
       </c>
       <c r="P19" t="n">
         <v>58</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1767,7 +1825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD19"/>
+  <dimension ref="A1:BE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1826,6 +1884,7 @@
     <col width="12" customWidth="1" min="54" max="54"/>
     <col width="12" customWidth="1" min="55" max="55"/>
     <col width="12" customWidth="1" min="56" max="56"/>
+    <col width="12" customWidth="1" min="57" max="57"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2109,6 +2168,11 @@
           <t>20251216</t>
         </is>
       </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>20251217</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2283,6 +2347,9 @@
       <c r="BD2" t="n">
         <v>97</v>
       </c>
+      <c r="BE2" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2457,6 +2524,9 @@
       <c r="BD3" t="n">
         <v>97</v>
       </c>
+      <c r="BE3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2631,6 +2701,9 @@
       <c r="BD4" t="n">
         <v>96</v>
       </c>
+      <c r="BE4" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2805,6 +2878,9 @@
       <c r="BD5" t="n">
         <v>94</v>
       </c>
+      <c r="BE5" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2979,6 +3055,9 @@
       <c r="BD6" t="n">
         <v>96</v>
       </c>
+      <c r="BE6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3153,6 +3232,9 @@
       <c r="BD7" t="n">
         <v>98</v>
       </c>
+      <c r="BE7" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3327,6 +3409,9 @@
       <c r="BD8" t="n">
         <v>97</v>
       </c>
+      <c r="BE8" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3501,6 +3586,9 @@
       <c r="BD9" t="n">
         <v>95</v>
       </c>
+      <c r="BE9" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3675,6 +3763,9 @@
       <c r="BD10" t="n">
         <v>94</v>
       </c>
+      <c r="BE10" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3849,6 +3940,9 @@
       <c r="BD11" t="n">
         <v>100</v>
       </c>
+      <c r="BE11" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4023,6 +4117,9 @@
       <c r="BD12" t="n">
         <v>101</v>
       </c>
+      <c r="BE12" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4197,6 +4294,9 @@
       <c r="BD13" t="n">
         <v>102</v>
       </c>
+      <c r="BE13" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4371,6 +4471,9 @@
       <c r="BD14" t="n">
         <v>97</v>
       </c>
+      <c r="BE14" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4545,6 +4648,9 @@
       <c r="BD15" t="n">
         <v>99</v>
       </c>
+      <c r="BE15" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4719,6 +4825,9 @@
       <c r="BD16" t="n">
         <v>100</v>
       </c>
+      <c r="BE16" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4893,6 +5002,9 @@
       <c r="BD17" t="n">
         <v>99</v>
       </c>
+      <c r="BE17" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5067,6 +5179,9 @@
       <c r="BD18" t="n">
         <v>92</v>
       </c>
+      <c r="BE18" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5240,6 +5355,9 @@
       </c>
       <c r="BD19" t="n">
         <v>100</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -5253,7 +5371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK19"/>
+  <dimension ref="A1:AL19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5293,6 +5411,7 @@
     <col width="12" customWidth="1" min="35" max="35"/>
     <col width="12" customWidth="1" min="36" max="36"/>
     <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="12" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5481,6 +5600,11 @@
           <t>20251216</t>
         </is>
       </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>20251217</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5598,6 +5722,9 @@
       <c r="AK2" t="n">
         <v>-35.6</v>
       </c>
+      <c r="AL2" t="n">
+        <v>-24</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5715,6 +5842,9 @@
       <c r="AK3" t="n">
         <v>-18.19</v>
       </c>
+      <c r="AL3" t="n">
+        <v>-18.63</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5832,6 +5962,9 @@
       <c r="AK4" t="n">
         <v>-25.06</v>
       </c>
+      <c r="AL4" t="n">
+        <v>-15.2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5949,6 +6082,9 @@
       <c r="AK5" t="n">
         <v>-13.26</v>
       </c>
+      <c r="AL5" t="n">
+        <v>-12.34</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6066,6 +6202,9 @@
       <c r="AK6" t="n">
         <v>-5.34</v>
       </c>
+      <c r="AL6" t="n">
+        <v>-6.34</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6183,6 +6322,9 @@
       <c r="AK7" t="n">
         <v>3.02</v>
       </c>
+      <c r="AL7" t="n">
+        <v>-1.04</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6300,6 +6442,9 @@
       <c r="AK8" t="n">
         <v>-14.84</v>
       </c>
+      <c r="AL8" t="n">
+        <v>-15.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6417,6 +6562,9 @@
       <c r="AK9" t="n">
         <v>-32.98</v>
       </c>
+      <c r="AL9" t="n">
+        <v>-30.97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6534,6 +6682,9 @@
       <c r="AK10" t="n">
         <v>3.26</v>
       </c>
+      <c r="AL10" t="n">
+        <v>4.84</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6651,6 +6802,9 @@
       <c r="AK11" t="n">
         <v>26.54</v>
       </c>
+      <c r="AL11" t="n">
+        <v>22.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6768,6 +6922,9 @@
       <c r="AK12" t="n">
         <v>27.98</v>
       </c>
+      <c r="AL12" t="n">
+        <v>23.35</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6885,6 +7042,9 @@
       <c r="AK13" t="n">
         <v>39.39</v>
       </c>
+      <c r="AL13" t="n">
+        <v>32.74</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7002,6 +7162,9 @@
       <c r="AK14" t="n">
         <v>-19.58</v>
       </c>
+      <c r="AL14" t="n">
+        <v>-18.93</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7119,6 +7282,9 @@
       <c r="AK15" t="n">
         <v>-48.32</v>
       </c>
+      <c r="AL15" t="n">
+        <v>-45.64</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7236,6 +7402,9 @@
       <c r="AK16" t="n">
         <v>6.52</v>
       </c>
+      <c r="AL16" t="n">
+        <v>4.11</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7353,6 +7522,9 @@
       <c r="AK17" t="n">
         <v>0.99</v>
       </c>
+      <c r="AL17" t="n">
+        <v>-0.86</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7470,6 +7642,9 @@
       <c r="AK18" t="n">
         <v>8.550000000000001</v>
       </c>
+      <c r="AL18" t="n">
+        <v>11.73</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7586,6 +7761,9 @@
       </c>
       <c r="AK19" t="n">
         <v>-44.61</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-43.26</v>
       </c>
     </row>
   </sheetData>
@@ -7599,7 +7777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7618,6 +7796,7 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7701,6 +7880,11 @@
           <t>20251216</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>20251217</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7755,6 +7939,9 @@
       <c r="P2" t="n">
         <v>42</v>
       </c>
+      <c r="Q2" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7809,6 +7996,9 @@
       <c r="P3" t="n">
         <v>39</v>
       </c>
+      <c r="Q3" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7863,6 +8053,9 @@
       <c r="P4" t="n">
         <v>32</v>
       </c>
+      <c r="Q4" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7917,6 +8110,9 @@
       <c r="P5" t="n">
         <v>9</v>
       </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7971,6 +8167,9 @@
       <c r="P6" t="n">
         <v>27</v>
       </c>
+      <c r="Q6" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8025,6 +8224,9 @@
       <c r="P7" t="n">
         <v>20</v>
       </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8079,6 +8281,9 @@
       <c r="P8" t="n">
         <v>25</v>
       </c>
+      <c r="Q8" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8133,6 +8338,9 @@
       <c r="P9" t="n">
         <v>76</v>
       </c>
+      <c r="Q9" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8187,6 +8395,9 @@
       <c r="P10" t="n">
         <v>17</v>
       </c>
+      <c r="Q10" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8241,6 +8452,9 @@
       <c r="P11" t="n">
         <v>39</v>
       </c>
+      <c r="Q11" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8295,6 +8509,9 @@
       <c r="P12" t="n">
         <v>47</v>
       </c>
+      <c r="Q12" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8349,6 +8566,9 @@
       <c r="P13" t="n">
         <v>51</v>
       </c>
+      <c r="Q13" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8403,6 +8623,9 @@
       <c r="P14" t="n">
         <v>42</v>
       </c>
+      <c r="Q14" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8457,6 +8680,9 @@
       <c r="P15" t="n">
         <v>23</v>
       </c>
+      <c r="Q15" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8511,6 +8737,9 @@
       <c r="P16" t="n">
         <v>31</v>
       </c>
+      <c r="Q16" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8565,6 +8794,9 @@
       <c r="P17" t="n">
         <v>9</v>
       </c>
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8619,6 +8851,9 @@
       <c r="P18" t="n">
         <v>15</v>
       </c>
+      <c r="Q18" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8672,6 +8907,9 @@
       </c>
       <c r="P19" t="n">
         <v>23</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -8685,7 +8923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW19"/>
+  <dimension ref="A1:BX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8763,6 +9001,7 @@
     <col width="12" customWidth="1" min="73" max="73"/>
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
+    <col width="12" customWidth="1" min="76" max="76"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8995,6 +9234,9 @@
       <c r="BW1" s="1" t="n">
         <v>20251216</v>
       </c>
+      <c r="BX1" s="1" t="n">
+        <v>20251217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9226,6 +9468,9 @@
       <c r="BW2" t="n">
         <v>15980</v>
       </c>
+      <c r="BX2" t="n">
+        <v>15360</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9457,6 +9702,9 @@
       <c r="BW3" t="n">
         <v>55610</v>
       </c>
+      <c r="BX3" t="n">
+        <v>54500</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9688,6 +9936,9 @@
       <c r="BW4" t="n">
         <v>18025</v>
       </c>
+      <c r="BX4" t="n">
+        <v>17980</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9919,6 +10170,9 @@
       <c r="BW5" t="n">
         <v>15255</v>
       </c>
+      <c r="BX5" t="n">
+        <v>14910</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10150,6 +10404,9 @@
       <c r="BW6" t="n">
         <v>16360</v>
       </c>
+      <c r="BX6" t="n">
+        <v>16105</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10381,6 +10638,9 @@
       <c r="BW7" t="n">
         <v>19115</v>
       </c>
+      <c r="BX7" t="n">
+        <v>18775</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10612,6 +10872,9 @@
       <c r="BW8" t="n">
         <v>17915</v>
       </c>
+      <c r="BX8" t="n">
+        <v>17615</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10843,6 +11106,9 @@
       <c r="BW9" t="n">
         <v>1597</v>
       </c>
+      <c r="BX9" t="n">
+        <v>1469</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11074,6 +11340,9 @@
       <c r="BW10" t="n">
         <v>16385</v>
       </c>
+      <c r="BX10" t="n">
+        <v>16015</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11305,6 +11574,9 @@
       <c r="BW11" t="n">
         <v>5665</v>
       </c>
+      <c r="BX11" t="n">
+        <v>5360</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11536,6 +11808,9 @@
       <c r="BW12" t="n">
         <v>6155</v>
       </c>
+      <c r="BX12" t="n">
+        <v>5840</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11767,6 +12042,9 @@
       <c r="BW13" t="n">
         <v>6225</v>
       </c>
+      <c r="BX13" t="n">
+        <v>5880</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11998,6 +12276,9 @@
       <c r="BW14" t="n">
         <v>1756</v>
       </c>
+      <c r="BX14" t="n">
+        <v>1606</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12229,6 +12510,9 @@
       <c r="BW15" t="n">
         <v>19720</v>
       </c>
+      <c r="BX15" t="n">
+        <v>19330</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12460,6 +12744,9 @@
       <c r="BW16" t="n">
         <v>11355</v>
       </c>
+      <c r="BX16" t="n">
+        <v>10880</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12691,6 +12978,9 @@
       <c r="BW17" t="n">
         <v>6780</v>
       </c>
+      <c r="BX17" t="n">
+        <v>6430</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12922,6 +13212,9 @@
       <c r="BW18" t="n">
         <v>17095</v>
       </c>
+      <c r="BX18" t="n">
+        <v>16770</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13152,6 +13445,9 @@
       </c>
       <c r="BW19" t="n">
         <v>16355</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>16140</v>
       </c>
     </row>
   </sheetData>
@@ -13165,7 +13461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW19"/>
+  <dimension ref="A1:BX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13243,6 +13539,7 @@
     <col width="12" customWidth="1" min="73" max="73"/>
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
+    <col width="12" customWidth="1" min="76" max="76"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13475,6 +13772,9 @@
       <c r="BW1" s="1" t="n">
         <v>20251216</v>
       </c>
+      <c r="BX1" s="1" t="n">
+        <v>20251217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13706,6 +14006,9 @@
       <c r="BW2" t="n">
         <v>16020</v>
       </c>
+      <c r="BX2" t="n">
+        <v>15360</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13937,6 +14240,9 @@
       <c r="BW3" t="n">
         <v>55855</v>
       </c>
+      <c r="BX3" t="n">
+        <v>56225</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14168,6 +14474,9 @@
       <c r="BW4" t="n">
         <v>18050</v>
       </c>
+      <c r="BX4" t="n">
+        <v>18005</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14399,6 +14708,9 @@
       <c r="BW5" t="n">
         <v>15255</v>
       </c>
+      <c r="BX5" t="n">
+        <v>15465</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14630,6 +14942,9 @@
       <c r="BW6" t="n">
         <v>16465</v>
       </c>
+      <c r="BX6" t="n">
+        <v>16640</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14861,6 +15176,9 @@
       <c r="BW7" t="n">
         <v>19230</v>
       </c>
+      <c r="BX7" t="n">
+        <v>19330</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15092,6 +15410,9 @@
       <c r="BW8" t="n">
         <v>18040</v>
       </c>
+      <c r="BX8" t="n">
+        <v>18235</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15323,6 +15644,9 @@
       <c r="BW9" t="n">
         <v>1597</v>
       </c>
+      <c r="BX9" t="n">
+        <v>1498</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15554,6 +15878,9 @@
       <c r="BW10" t="n">
         <v>16390</v>
       </c>
+      <c r="BX10" t="n">
+        <v>16470</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15785,6 +16112,9 @@
       <c r="BW11" t="n">
         <v>5665</v>
       </c>
+      <c r="BX11" t="n">
+        <v>5480</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16016,6 +16346,9 @@
       <c r="BW12" t="n">
         <v>6155</v>
       </c>
+      <c r="BX12" t="n">
+        <v>5935</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16247,6 +16580,9 @@
       <c r="BW13" t="n">
         <v>6225</v>
       </c>
+      <c r="BX13" t="n">
+        <v>6000</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16478,6 +16814,9 @@
       <c r="BW14" t="n">
         <v>1756</v>
       </c>
+      <c r="BX14" t="n">
+        <v>1639</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -16709,6 +17048,9 @@
       <c r="BW15" t="n">
         <v>19795</v>
       </c>
+      <c r="BX15" t="n">
+        <v>19345</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -16940,6 +17282,9 @@
       <c r="BW16" t="n">
         <v>11385</v>
       </c>
+      <c r="BX16" t="n">
+        <v>11025</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17171,6 +17516,9 @@
       <c r="BW17" t="n">
         <v>6780</v>
       </c>
+      <c r="BX17" t="n">
+        <v>6525</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17402,6 +17750,9 @@
       <c r="BW18" t="n">
         <v>17225</v>
       </c>
+      <c r="BX18" t="n">
+        <v>17292</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17632,6 +17983,9 @@
       </c>
       <c r="BW19" t="n">
         <v>16355</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>16140</v>
       </c>
     </row>
   </sheetData>
@@ -17645,7 +17999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW19"/>
+  <dimension ref="A1:BX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17723,6 +18077,7 @@
     <col width="12" customWidth="1" min="73" max="73"/>
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
+    <col width="12" customWidth="1" min="76" max="76"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17955,6 +18310,9 @@
       <c r="BW1" s="1" t="n">
         <v>20251216</v>
       </c>
+      <c r="BX1" s="1" t="n">
+        <v>20251217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18186,6 +18544,9 @@
       <c r="BW2" t="n">
         <v>15270</v>
       </c>
+      <c r="BX2" t="n">
+        <v>14780</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18417,6 +18778,9 @@
       <c r="BW3" t="n">
         <v>54185</v>
       </c>
+      <c r="BX3" t="n">
+        <v>54260</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18648,6 +19012,9 @@
       <c r="BW4" t="n">
         <v>17650</v>
       </c>
+      <c r="BX4" t="n">
+        <v>17355</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18879,6 +19246,9 @@
       <c r="BW5" t="n">
         <v>14800</v>
       </c>
+      <c r="BX5" t="n">
+        <v>14825</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19110,6 +19480,9 @@
       <c r="BW6" t="n">
         <v>15990</v>
       </c>
+      <c r="BX6" t="n">
+        <v>15985</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19341,6 +19714,9 @@
       <c r="BW7" t="n">
         <v>18640</v>
       </c>
+      <c r="BX7" t="n">
+        <v>18655</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19572,6 +19948,9 @@
       <c r="BW8" t="n">
         <v>17490</v>
       </c>
+      <c r="BX8" t="n">
+        <v>17520</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19803,6 +20182,9 @@
       <c r="BW9" t="n">
         <v>1435</v>
       </c>
+      <c r="BX9" t="n">
+        <v>1416</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20034,6 +20416,9 @@
       <c r="BW10" t="n">
         <v>15905</v>
       </c>
+      <c r="BX10" t="n">
+        <v>15825</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -20265,6 +20650,9 @@
       <c r="BW11" t="n">
         <v>5295</v>
       </c>
+      <c r="BX11" t="n">
+        <v>5295</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -20496,6 +20884,9 @@
       <c r="BW12" t="n">
         <v>5715</v>
       </c>
+      <c r="BX12" t="n">
+        <v>5695</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -20727,6 +21118,9 @@
       <c r="BW13" t="n">
         <v>5765</v>
       </c>
+      <c r="BX13" t="n">
+        <v>5750</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -20958,6 +21352,9 @@
       <c r="BW14" t="n">
         <v>1572</v>
       </c>
+      <c r="BX14" t="n">
+        <v>1555</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -21189,6 +21586,9 @@
       <c r="BW15" t="n">
         <v>19240</v>
       </c>
+      <c r="BX15" t="n">
+        <v>18590</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -21420,6 +21820,9 @@
       <c r="BW16" t="n">
         <v>10735</v>
       </c>
+      <c r="BX16" t="n">
+        <v>10700</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -21651,6 +22054,9 @@
       <c r="BW17" t="n">
         <v>6350</v>
       </c>
+      <c r="BX17" t="n">
+        <v>6345</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -21882,6 +22288,9 @@
       <c r="BW18" t="n">
         <v>16625</v>
       </c>
+      <c r="BX18" t="n">
+        <v>16610</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -22112,6 +22521,9 @@
       </c>
       <c r="BW19" t="n">
         <v>16015</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>15750</v>
       </c>
     </row>
   </sheetData>
@@ -22125,7 +22537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW19"/>
+  <dimension ref="A1:BX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22203,6 +22615,7 @@
     <col width="12" customWidth="1" min="73" max="73"/>
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
+    <col width="12" customWidth="1" min="76" max="76"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22435,6 +22848,9 @@
       <c r="BW1" s="1" t="n">
         <v>20251216</v>
       </c>
+      <c r="BX1" s="1" t="n">
+        <v>20251217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22666,6 +23082,9 @@
       <c r="BW2" t="n">
         <v>15305</v>
       </c>
+      <c r="BX2" t="n">
+        <v>14800</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22897,6 +23316,9 @@
       <c r="BW3" t="n">
         <v>54205</v>
       </c>
+      <c r="BX3" t="n">
+        <v>56205</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23128,6 +23550,9 @@
       <c r="BW4" t="n">
         <v>17850</v>
       </c>
+      <c r="BX4" t="n">
+        <v>17395</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23359,6 +23784,9 @@
       <c r="BW5" t="n">
         <v>14800</v>
       </c>
+      <c r="BX5" t="n">
+        <v>15465</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23590,6 +24018,9 @@
       <c r="BW6" t="n">
         <v>16000</v>
       </c>
+      <c r="BX6" t="n">
+        <v>16640</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23821,6 +24252,9 @@
       <c r="BW7" t="n">
         <v>18700</v>
       </c>
+      <c r="BX7" t="n">
+        <v>19330</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24052,6 +24486,9 @@
       <c r="BW8" t="n">
         <v>17505</v>
       </c>
+      <c r="BX8" t="n">
+        <v>18220</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24283,6 +24720,9 @@
       <c r="BW9" t="n">
         <v>1450</v>
       </c>
+      <c r="BX9" t="n">
+        <v>1470</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24514,6 +24954,9 @@
       <c r="BW10" t="n">
         <v>15940</v>
       </c>
+      <c r="BX10" t="n">
+        <v>16430</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24745,6 +25188,9 @@
       <c r="BW11" t="n">
         <v>5345</v>
       </c>
+      <c r="BX11" t="n">
+        <v>5410</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24976,6 +25422,9 @@
       <c r="BW12" t="n">
         <v>5770</v>
       </c>
+      <c r="BX12" t="n">
+        <v>5830</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -25207,6 +25656,9 @@
       <c r="BW13" t="n">
         <v>5800</v>
       </c>
+      <c r="BX13" t="n">
+        <v>5915</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -25438,6 +25890,9 @@
       <c r="BW14" t="n">
         <v>1589</v>
       </c>
+      <c r="BX14" t="n">
+        <v>1598</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -25669,6 +26124,9 @@
       <c r="BW15" t="n">
         <v>19315</v>
       </c>
+      <c r="BX15" t="n">
+        <v>18625</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25900,6 +26358,9 @@
       <c r="BW16" t="n">
         <v>10800</v>
       </c>
+      <c r="BX16" t="n">
+        <v>10870</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -26131,6 +26592,9 @@
       <c r="BW17" t="n">
         <v>6390</v>
       </c>
+      <c r="BX17" t="n">
+        <v>6430</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -26362,6 +26826,9 @@
       <c r="BW18" t="n">
         <v>16625</v>
       </c>
+      <c r="BX18" t="n">
+        <v>17200</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -26592,6 +27059,9 @@
       </c>
       <c r="BW19" t="n">
         <v>16105</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>15780</v>
       </c>
     </row>
   </sheetData>
@@ -26605,7 +27075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW19"/>
+  <dimension ref="A1:BX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26683,6 +27153,7 @@
     <col width="12" customWidth="1" min="73" max="73"/>
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
+    <col width="12" customWidth="1" min="76" max="76"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26915,6 +27386,9 @@
       <c r="BW1" s="1" t="n">
         <v>20251216</v>
       </c>
+      <c r="BX1" s="1" t="n">
+        <v>20251217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27146,6 +27620,9 @@
       <c r="BW2" t="n">
         <v>95386</v>
       </c>
+      <c r="BX2" t="n">
+        <v>118248</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27377,6 +27854,9 @@
       <c r="BW3" t="n">
         <v>1808751</v>
       </c>
+      <c r="BX3" t="n">
+        <v>1344452</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -27608,6 +28088,9 @@
       <c r="BW4" t="n">
         <v>102885</v>
       </c>
+      <c r="BX4" t="n">
+        <v>113502</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27839,6 +28322,9 @@
       <c r="BW5" t="n">
         <v>148732</v>
       </c>
+      <c r="BX5" t="n">
+        <v>88928</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28070,6 +28556,9 @@
       <c r="BW6" t="n">
         <v>1103940</v>
       </c>
+      <c r="BX6" t="n">
+        <v>971002</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28301,6 +28790,9 @@
       <c r="BW7" t="n">
         <v>1542023</v>
       </c>
+      <c r="BX7" t="n">
+        <v>801272</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28532,6 +29024,9 @@
       <c r="BW8" t="n">
         <v>3610469</v>
       </c>
+      <c r="BX8" t="n">
+        <v>2944778</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28763,6 +29258,9 @@
       <c r="BW9" t="n">
         <v>11143633</v>
       </c>
+      <c r="BX9" t="n">
+        <v>3250103</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28994,6 +29492,9 @@
       <c r="BW10" t="n">
         <v>497548</v>
       </c>
+      <c r="BX10" t="n">
+        <v>554937</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29225,6 +29726,9 @@
       <c r="BW11" t="n">
         <v>998111</v>
       </c>
+      <c r="BX11" t="n">
+        <v>512870</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29456,6 +29960,9 @@
       <c r="BW12" t="n">
         <v>2659587</v>
       </c>
+      <c r="BX12" t="n">
+        <v>2078371</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29687,6 +30194,9 @@
       <c r="BW13" t="n">
         <v>6999846</v>
       </c>
+      <c r="BX13" t="n">
+        <v>5887251</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29918,6 +30428,9 @@
       <c r="BW14" t="n">
         <v>42943771</v>
       </c>
+      <c r="BX14" t="n">
+        <v>23418740</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -30149,6 +30662,9 @@
       <c r="BW15" t="n">
         <v>774978</v>
       </c>
+      <c r="BX15" t="n">
+        <v>981425</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -30380,6 +30896,9 @@
       <c r="BW16" t="n">
         <v>378057</v>
       </c>
+      <c r="BX16" t="n">
+        <v>216740</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -30611,6 +31130,9 @@
       <c r="BW17" t="n">
         <v>43223</v>
       </c>
+      <c r="BX17" t="n">
+        <v>30056</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -30842,6 +31364,9 @@
       <c r="BW18" t="n">
         <v>53681</v>
       </c>
+      <c r="BX18" t="n">
+        <v>44689</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -31072,6 +31597,9 @@
       </c>
       <c r="BW19" t="n">
         <v>21341</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>31690</v>
       </c>
     </row>
   </sheetData>
@@ -31085,7 +31613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD19"/>
+  <dimension ref="A1:BE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31144,6 +31672,7 @@
     <col width="10" customWidth="1" min="54" max="54"/>
     <col width="10" customWidth="1" min="55" max="55"/>
     <col width="10" customWidth="1" min="56" max="56"/>
+    <col width="10" customWidth="1" min="57" max="57"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31319,6 +31848,9 @@
       <c r="BD1" s="1" t="n">
         <v>20251216</v>
       </c>
+      <c r="BE1" s="1" t="n">
+        <v>20251217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31493,6 +32025,9 @@
       <c r="BD2" t="n">
         <v>20</v>
       </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31667,6 +32202,9 @@
       <c r="BD3" t="n">
         <v>31</v>
       </c>
+      <c r="BE3" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -31841,6 +32379,9 @@
       <c r="BD4" t="n">
         <v>3</v>
       </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32015,6 +32556,9 @@
       <c r="BD5" t="n">
         <v>0</v>
       </c>
+      <c r="BE5" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32189,6 +32733,9 @@
       <c r="BD6" t="n">
         <v>28</v>
       </c>
+      <c r="BE6" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -32363,6 +32910,9 @@
       <c r="BD7" t="n">
         <v>49</v>
       </c>
+      <c r="BE7" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -32537,6 +33087,9 @@
       <c r="BD8" t="n">
         <v>33</v>
       </c>
+      <c r="BE8" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -32711,6 +33264,9 @@
       <c r="BD9" t="n">
         <v>27</v>
       </c>
+      <c r="BE9" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -32885,6 +33441,9 @@
       <c r="BD10" t="n">
         <v>0</v>
       </c>
+      <c r="BE10" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -33059,6 +33618,9 @@
       <c r="BD11" t="n">
         <v>56</v>
       </c>
+      <c r="BE11" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33233,6 +33795,9 @@
       <c r="BD12" t="n">
         <v>56</v>
       </c>
+      <c r="BE12" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33407,6 +33972,9 @@
       <c r="BD13" t="n">
         <v>59</v>
       </c>
+      <c r="BE13" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33581,6 +34149,9 @@
       <c r="BD14" t="n">
         <v>43</v>
       </c>
+      <c r="BE14" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -33755,6 +34326,9 @@
       <c r="BD15" t="n">
         <v>42</v>
       </c>
+      <c r="BE15" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -33929,6 +34503,9 @@
       <c r="BD16" t="n">
         <v>52</v>
       </c>
+      <c r="BE16" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -34103,6 +34680,9 @@
       <c r="BD17" t="n">
         <v>52</v>
       </c>
+      <c r="BE17" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -34277,6 +34857,9 @@
       <c r="BD18" t="n">
         <v>0</v>
       </c>
+      <c r="BE18" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -34450,6 +35033,9 @@
       </c>
       <c r="BD19" t="n">
         <v>59</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -34463,7 +35049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34482,6 +35068,7 @@
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34537,6 +35124,9 @@
       <c r="P1" s="1" t="n">
         <v>20251216</v>
       </c>
+      <c r="Q1" s="1" t="n">
+        <v>20251217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34591,6 +35181,9 @@
       <c r="P2" t="n">
         <v>68</v>
       </c>
+      <c r="Q2" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34645,6 +35238,9 @@
       <c r="P3" t="n">
         <v>62</v>
       </c>
+      <c r="Q3" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34699,6 +35295,9 @@
       <c r="P4" t="n">
         <v>62</v>
       </c>
+      <c r="Q4" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34753,6 +35352,9 @@
       <c r="P5" t="n">
         <v>42</v>
       </c>
+      <c r="Q5" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34807,6 +35409,9 @@
       <c r="P6" t="n">
         <v>68</v>
       </c>
+      <c r="Q6" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -34861,6 +35466,9 @@
       <c r="P7" t="n">
         <v>75</v>
       </c>
+      <c r="Q7" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -34915,6 +35523,9 @@
       <c r="P8" t="n">
         <v>67</v>
       </c>
+      <c r="Q8" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -34969,6 +35580,9 @@
       <c r="P9" t="n">
         <v>45</v>
       </c>
+      <c r="Q9" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35023,6 +35637,9 @@
       <c r="P10" t="n">
         <v>46</v>
       </c>
+      <c r="Q10" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -35077,6 +35694,9 @@
       <c r="P11" t="n">
         <v>78</v>
       </c>
+      <c r="Q11" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -35131,6 +35751,9 @@
       <c r="P12" t="n">
         <v>78</v>
       </c>
+      <c r="Q12" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35185,6 +35808,9 @@
       <c r="P13" t="n">
         <v>78</v>
       </c>
+      <c r="Q13" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35239,6 +35865,9 @@
       <c r="P14" t="n">
         <v>54</v>
       </c>
+      <c r="Q14" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35293,6 +35922,9 @@
       <c r="P15" t="n">
         <v>82</v>
       </c>
+      <c r="Q15" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -35347,6 +35979,9 @@
       <c r="P16" t="n">
         <v>71</v>
       </c>
+      <c r="Q16" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -35401,6 +36036,9 @@
       <c r="P17" t="n">
         <v>68</v>
       </c>
+      <c r="Q17" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -35455,6 +36093,9 @@
       <c r="P18" t="n">
         <v>59</v>
       </c>
+      <c r="Q18" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -35508,6 +36149,9 @@
       </c>
       <c r="P19" t="n">
         <v>84</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -35521,7 +36165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD19"/>
+  <dimension ref="A1:BE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35580,6 +36224,7 @@
     <col width="10" customWidth="1" min="54" max="54"/>
     <col width="10" customWidth="1" min="55" max="55"/>
     <col width="10" customWidth="1" min="56" max="56"/>
+    <col width="10" customWidth="1" min="57" max="57"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35755,6 +36400,9 @@
       <c r="BD1" s="1" t="n">
         <v>20251216</v>
       </c>
+      <c r="BE1" s="1" t="n">
+        <v>20251217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35929,6 +36577,9 @@
       <c r="BD2" t="n">
         <v>-61</v>
       </c>
+      <c r="BE2" t="n">
+        <v>-101</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36103,6 +36754,9 @@
       <c r="BD3" t="n">
         <v>-53</v>
       </c>
+      <c r="BE3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -36277,6 +36931,9 @@
       <c r="BD4" t="n">
         <v>-60</v>
       </c>
+      <c r="BE4" t="n">
+        <v>-89</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -36451,6 +37108,9 @@
       <c r="BD5" t="n">
         <v>-119</v>
       </c>
+      <c r="BE5" t="n">
+        <v>-38</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -36625,6 +37285,9 @@
       <c r="BD6" t="n">
         <v>-59</v>
       </c>
+      <c r="BE6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -36799,6 +37462,9 @@
       <c r="BD7" t="n">
         <v>-25</v>
       </c>
+      <c r="BE7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -36973,6 +37639,9 @@
       <c r="BD8" t="n">
         <v>-49</v>
       </c>
+      <c r="BE8" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -37147,6 +37816,9 @@
       <c r="BD9" t="n">
         <v>-47</v>
       </c>
+      <c r="BE9" t="n">
+        <v>-32</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -37321,6 +37993,9 @@
       <c r="BD10" t="n">
         <v>-103</v>
       </c>
+      <c r="BE10" t="n">
+        <v>-52</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -37495,6 +38170,9 @@
       <c r="BD11" t="n">
         <v>4</v>
       </c>
+      <c r="BE11" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -37669,6 +38347,9 @@
       <c r="BD12" t="n">
         <v>6</v>
       </c>
+      <c r="BE12" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -37843,6 +38524,9 @@
       <c r="BD13" t="n">
         <v>11</v>
       </c>
+      <c r="BE13" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -38017,6 +38701,9 @@
       <c r="BD14" t="n">
         <v>-24</v>
       </c>
+      <c r="BE14" t="n">
+        <v>-20</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -38191,6 +38878,9 @@
       <c r="BD15" t="n">
         <v>-12</v>
       </c>
+      <c r="BE15" t="n">
+        <v>-72</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -38365,6 +39055,9 @@
       <c r="BD16" t="n">
         <v>-3</v>
       </c>
+      <c r="BE16" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -38539,6 +39232,9 @@
       <c r="BD17" t="n">
         <v>-5</v>
       </c>
+      <c r="BE17" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -38713,6 +39409,9 @@
       <c r="BD18" t="n">
         <v>-113</v>
       </c>
+      <c r="BE18" t="n">
+        <v>-63</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -38886,6 +39585,9 @@
       </c>
       <c r="BD19" t="n">
         <v>1</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>-38</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -729,6 +729,7 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -787,6 +788,9 @@
       <c r="Q1" s="1" t="n">
         <v>20251217</v>
       </c>
+      <c r="R1" s="1" t="n">
+        <v>20251218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -844,6 +848,9 @@
       <c r="Q2" t="n">
         <v>11</v>
       </c>
+      <c r="R2" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -901,6 +908,9 @@
       <c r="Q3" t="n">
         <v>19</v>
       </c>
+      <c r="R3" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -958,6 +968,9 @@
       <c r="Q4" t="n">
         <v>2</v>
       </c>
+      <c r="R4" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1015,6 +1028,9 @@
       <c r="Q5" t="n">
         <v>-11</v>
       </c>
+      <c r="R5" t="n">
+        <v>-27</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1072,6 +1088,9 @@
       <c r="Q6" t="n">
         <v>29</v>
       </c>
+      <c r="R6" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1129,6 +1148,9 @@
       <c r="Q7" t="n">
         <v>38</v>
       </c>
+      <c r="R7" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1186,6 +1208,9 @@
       <c r="Q8" t="n">
         <v>25</v>
       </c>
+      <c r="R8" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1243,6 +1268,9 @@
       <c r="Q9" t="n">
         <v>-1</v>
       </c>
+      <c r="R9" t="n">
+        <v>-34</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1300,6 +1328,9 @@
       <c r="Q10" t="n">
         <v>-7</v>
       </c>
+      <c r="R10" t="n">
+        <v>-33</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1357,6 +1388,9 @@
       <c r="Q11" t="n">
         <v>34</v>
       </c>
+      <c r="R11" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1414,6 +1448,9 @@
       <c r="Q12" t="n">
         <v>33</v>
       </c>
+      <c r="R12" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1471,6 +1508,9 @@
       <c r="Q13" t="n">
         <v>40</v>
       </c>
+      <c r="R13" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1528,6 +1568,9 @@
       <c r="Q14" t="n">
         <v>8</v>
       </c>
+      <c r="R14" t="n">
+        <v>-24</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1585,6 +1628,9 @@
       <c r="Q15" t="n">
         <v>38</v>
       </c>
+      <c r="R15" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1642,6 +1688,9 @@
       <c r="Q16" t="n">
         <v>24</v>
       </c>
+      <c r="R16" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1699,6 +1748,9 @@
       <c r="Q17" t="n">
         <v>20</v>
       </c>
+      <c r="R17" t="n">
+        <v>-6</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1756,6 +1808,9 @@
       <c r="Q18" t="n">
         <v>15</v>
       </c>
+      <c r="R18" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1812,6 +1867,9 @@
       </c>
       <c r="Q19" t="n">
         <v>45</v>
+      </c>
+      <c r="R19" t="n">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1825,7 +1883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE19"/>
+  <dimension ref="A1:BF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1885,6 +1943,7 @@
     <col width="12" customWidth="1" min="55" max="55"/>
     <col width="12" customWidth="1" min="56" max="56"/>
     <col width="12" customWidth="1" min="57" max="57"/>
+    <col width="12" customWidth="1" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2173,6 +2232,11 @@
           <t>20251217</t>
         </is>
       </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>20251218</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2350,6 +2414,9 @@
       <c r="BE2" t="n">
         <v>94</v>
       </c>
+      <c r="BF2" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2527,6 +2594,9 @@
       <c r="BE3" t="n">
         <v>100</v>
       </c>
+      <c r="BF3" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2704,6 +2774,9 @@
       <c r="BE4" t="n">
         <v>94</v>
       </c>
+      <c r="BF4" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2881,6 +2954,9 @@
       <c r="BE5" t="n">
         <v>98</v>
       </c>
+      <c r="BF5" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3058,6 +3134,9 @@
       <c r="BE6" t="n">
         <v>100</v>
       </c>
+      <c r="BF6" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3235,6 +3314,9 @@
       <c r="BE7" t="n">
         <v>101</v>
       </c>
+      <c r="BF7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3412,6 +3494,9 @@
       <c r="BE8" t="n">
         <v>101</v>
       </c>
+      <c r="BF8" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3589,6 +3674,9 @@
       <c r="BE9" t="n">
         <v>97</v>
       </c>
+      <c r="BF9" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3766,6 +3854,9 @@
       <c r="BE10" t="n">
         <v>97</v>
       </c>
+      <c r="BF10" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3943,6 +4034,9 @@
       <c r="BE11" t="n">
         <v>101</v>
       </c>
+      <c r="BF11" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4120,6 +4214,9 @@
       <c r="BE12" t="n">
         <v>101</v>
       </c>
+      <c r="BF12" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4297,6 +4394,9 @@
       <c r="BE13" t="n">
         <v>103</v>
       </c>
+      <c r="BF13" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4474,6 +4574,9 @@
       <c r="BE14" t="n">
         <v>97</v>
       </c>
+      <c r="BF14" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4651,6 +4754,9 @@
       <c r="BE15" t="n">
         <v>96</v>
       </c>
+      <c r="BF15" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4828,6 +4934,9 @@
       <c r="BE16" t="n">
         <v>100</v>
       </c>
+      <c r="BF16" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5005,6 +5114,9 @@
       <c r="BE17" t="n">
         <v>100</v>
       </c>
+      <c r="BF17" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5182,6 +5294,9 @@
       <c r="BE18" t="n">
         <v>96</v>
       </c>
+      <c r="BF18" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5357,6 +5472,9 @@
         <v>100</v>
       </c>
       <c r="BE19" t="n">
+        <v>98</v>
+      </c>
+      <c r="BF19" t="n">
         <v>98</v>
       </c>
     </row>
@@ -5371,7 +5489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL19"/>
+  <dimension ref="A1:AM19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5412,6 +5530,7 @@
     <col width="12" customWidth="1" min="36" max="36"/>
     <col width="12" customWidth="1" min="37" max="37"/>
     <col width="12" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5605,6 +5724,11 @@
           <t>20251217</t>
         </is>
       </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>20251218</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5725,6 +5849,9 @@
       <c r="AL2" t="n">
         <v>-24</v>
       </c>
+      <c r="AM2" t="n">
+        <v>-16.57</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5845,6 +5972,9 @@
       <c r="AL3" t="n">
         <v>-18.63</v>
       </c>
+      <c r="AM3" t="n">
+        <v>-18.71</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5965,6 +6095,9 @@
       <c r="AL4" t="n">
         <v>-15.2</v>
       </c>
+      <c r="AM4" t="n">
+        <v>-11.07</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6085,6 +6218,9 @@
       <c r="AL5" t="n">
         <v>-12.34</v>
       </c>
+      <c r="AM5" t="n">
+        <v>-10.3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6205,6 +6341,9 @@
       <c r="AL6" t="n">
         <v>-6.34</v>
       </c>
+      <c r="AM6" t="n">
+        <v>-5.76</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6325,6 +6464,9 @@
       <c r="AL7" t="n">
         <v>-1.04</v>
       </c>
+      <c r="AM7" t="n">
+        <v>-2.99</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6445,6 +6587,9 @@
       <c r="AL8" t="n">
         <v>-15.5</v>
       </c>
+      <c r="AM8" t="n">
+        <v>-15.76</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6565,6 +6710,9 @@
       <c r="AL9" t="n">
         <v>-30.97</v>
       </c>
+      <c r="AM9" t="n">
+        <v>-19.15</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6685,6 +6833,9 @@
       <c r="AL10" t="n">
         <v>4.84</v>
       </c>
+      <c r="AM10" t="n">
+        <v>12.35</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6805,6 +6956,9 @@
       <c r="AL11" t="n">
         <v>22.19</v>
       </c>
+      <c r="AM11" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6925,6 +7079,9 @@
       <c r="AL12" t="n">
         <v>23.35</v>
       </c>
+      <c r="AM12" t="n">
+        <v>21.96</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7045,6 +7202,9 @@
       <c r="AL13" t="n">
         <v>32.74</v>
       </c>
+      <c r="AM13" t="n">
+        <v>28.33</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7165,6 +7325,9 @@
       <c r="AL14" t="n">
         <v>-18.93</v>
       </c>
+      <c r="AM14" t="n">
+        <v>-9.83</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7285,6 +7448,9 @@
       <c r="AL15" t="n">
         <v>-45.64</v>
       </c>
+      <c r="AM15" t="n">
+        <v>-40.66</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7405,6 +7571,9 @@
       <c r="AL16" t="n">
         <v>4.11</v>
       </c>
+      <c r="AM16" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7525,6 +7694,9 @@
       <c r="AL17" t="n">
         <v>-0.86</v>
       </c>
+      <c r="AM17" t="n">
+        <v>2.33</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7645,6 +7817,9 @@
       <c r="AL18" t="n">
         <v>11.73</v>
       </c>
+      <c r="AM18" t="n">
+        <v>18.07</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7764,6 +7939,9 @@
       </c>
       <c r="AL19" t="n">
         <v>-43.26</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-39.89</v>
       </c>
     </row>
   </sheetData>
@@ -7777,7 +7955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7797,6 +7975,7 @@
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7885,6 +8064,11 @@
           <t>20251217</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>20251218</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7942,6 +8126,9 @@
       <c r="Q2" t="n">
         <v>52</v>
       </c>
+      <c r="R2" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7999,6 +8186,9 @@
       <c r="Q3" t="n">
         <v>29</v>
       </c>
+      <c r="R3" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8056,6 +8246,9 @@
       <c r="Q4" t="n">
         <v>35</v>
       </c>
+      <c r="R4" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8113,6 +8306,9 @@
       <c r="Q5" t="n">
         <v>5</v>
       </c>
+      <c r="R5" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8170,6 +8366,9 @@
       <c r="Q6" t="n">
         <v>24</v>
       </c>
+      <c r="R6" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8227,6 +8426,9 @@
       <c r="Q7" t="n">
         <v>10</v>
       </c>
+      <c r="R7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8284,6 +8486,9 @@
       <c r="Q8" t="n">
         <v>21</v>
       </c>
+      <c r="R8" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8341,6 +8546,9 @@
       <c r="Q9" t="n">
         <v>22</v>
       </c>
+      <c r="R9" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8398,6 +8606,9 @@
       <c r="Q10" t="n">
         <v>19</v>
       </c>
+      <c r="R10" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8455,6 +8666,9 @@
       <c r="Q11" t="n">
         <v>20</v>
       </c>
+      <c r="R11" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8512,6 +8726,9 @@
       <c r="Q12" t="n">
         <v>36</v>
       </c>
+      <c r="R12" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8569,6 +8786,9 @@
       <c r="Q13" t="n">
         <v>43</v>
       </c>
+      <c r="R13" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8626,6 +8846,9 @@
       <c r="Q14" t="n">
         <v>23</v>
       </c>
+      <c r="R14" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8683,6 +8906,9 @@
       <c r="Q15" t="n">
         <v>29</v>
       </c>
+      <c r="R15" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8740,6 +8966,9 @@
       <c r="Q16" t="n">
         <v>18</v>
       </c>
+      <c r="R16" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8797,6 +9026,9 @@
       <c r="Q17" t="n">
         <v>6</v>
       </c>
+      <c r="R17" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8854,6 +9086,9 @@
       <c r="Q18" t="n">
         <v>12</v>
       </c>
+      <c r="R18" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8910,6 +9145,9 @@
       </c>
       <c r="Q19" t="n">
         <v>34</v>
+      </c>
+      <c r="R19" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -8923,7 +9161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX19"/>
+  <dimension ref="A1:BY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9002,6 +9240,7 @@
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
+    <col width="12" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9237,6 +9476,9 @@
       <c r="BX1" s="1" t="n">
         <v>20251217</v>
       </c>
+      <c r="BY1" s="1" t="n">
+        <v>20251218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9471,6 +9713,9 @@
       <c r="BX2" t="n">
         <v>15360</v>
       </c>
+      <c r="BY2" t="n">
+        <v>14620</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9705,6 +9950,9 @@
       <c r="BX3" t="n">
         <v>54500</v>
       </c>
+      <c r="BY3" t="n">
+        <v>54910</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9939,6 +10187,9 @@
       <c r="BX4" t="n">
         <v>17980</v>
       </c>
+      <c r="BY4" t="n">
+        <v>17300</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10173,6 +10424,9 @@
       <c r="BX5" t="n">
         <v>14910</v>
       </c>
+      <c r="BY5" t="n">
+        <v>15055</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10407,6 +10661,9 @@
       <c r="BX6" t="n">
         <v>16105</v>
       </c>
+      <c r="BY6" t="n">
+        <v>16185</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10641,6 +10898,9 @@
       <c r="BX7" t="n">
         <v>18775</v>
       </c>
+      <c r="BY7" t="n">
+        <v>18945</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10875,6 +11135,9 @@
       <c r="BX8" t="n">
         <v>17615</v>
       </c>
+      <c r="BY8" t="n">
+        <v>17865</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11109,6 +11372,9 @@
       <c r="BX9" t="n">
         <v>1469</v>
       </c>
+      <c r="BY9" t="n">
+        <v>1398</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11343,6 +11609,9 @@
       <c r="BX10" t="n">
         <v>16015</v>
       </c>
+      <c r="BY10" t="n">
+        <v>16060</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11577,6 +11846,9 @@
       <c r="BX11" t="n">
         <v>5360</v>
       </c>
+      <c r="BY11" t="n">
+        <v>5180</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11811,6 +12083,9 @@
       <c r="BX12" t="n">
         <v>5840</v>
       </c>
+      <c r="BY12" t="n">
+        <v>5580</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12045,6 +12320,9 @@
       <c r="BX13" t="n">
         <v>5880</v>
       </c>
+      <c r="BY13" t="n">
+        <v>5640</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12279,6 +12557,9 @@
       <c r="BX14" t="n">
         <v>1606</v>
       </c>
+      <c r="BY14" t="n">
+        <v>1479</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12513,6 +12794,9 @@
       <c r="BX15" t="n">
         <v>19330</v>
       </c>
+      <c r="BY15" t="n">
+        <v>18400</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12747,6 +13031,9 @@
       <c r="BX16" t="n">
         <v>10880</v>
       </c>
+      <c r="BY16" t="n">
+        <v>10445</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12981,6 +13268,9 @@
       <c r="BX17" t="n">
         <v>6430</v>
       </c>
+      <c r="BY17" t="n">
+        <v>6165</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13215,6 +13505,9 @@
       <c r="BX18" t="n">
         <v>16770</v>
       </c>
+      <c r="BY18" t="n">
+        <v>16700</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13448,6 +13741,9 @@
       </c>
       <c r="BX19" t="n">
         <v>16140</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>15545</v>
       </c>
     </row>
   </sheetData>
@@ -13461,7 +13757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX19"/>
+  <dimension ref="A1:BY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13540,6 +13836,7 @@
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
+    <col width="12" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13775,6 +14072,9 @@
       <c r="BX1" s="1" t="n">
         <v>20251217</v>
       </c>
+      <c r="BY1" s="1" t="n">
+        <v>20251218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14009,6 +14309,9 @@
       <c r="BX2" t="n">
         <v>15360</v>
       </c>
+      <c r="BY2" t="n">
+        <v>15095</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14243,6 +14546,9 @@
       <c r="BX3" t="n">
         <v>56225</v>
       </c>
+      <c r="BY3" t="n">
+        <v>56200</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14477,6 +14783,9 @@
       <c r="BX4" t="n">
         <v>18005</v>
       </c>
+      <c r="BY4" t="n">
+        <v>17470</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14711,6 +15020,9 @@
       <c r="BX5" t="n">
         <v>15465</v>
       </c>
+      <c r="BY5" t="n">
+        <v>15445</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14945,6 +15257,9 @@
       <c r="BX6" t="n">
         <v>16640</v>
       </c>
+      <c r="BY6" t="n">
+        <v>16530</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15179,6 +15494,9 @@
       <c r="BX7" t="n">
         <v>19330</v>
       </c>
+      <c r="BY7" t="n">
+        <v>19260</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15413,6 +15731,9 @@
       <c r="BX8" t="n">
         <v>18235</v>
       </c>
+      <c r="BY8" t="n">
+        <v>18210</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15647,6 +15968,9 @@
       <c r="BX9" t="n">
         <v>1498</v>
       </c>
+      <c r="BY9" t="n">
+        <v>1398</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15881,6 +16205,9 @@
       <c r="BX10" t="n">
         <v>16470</v>
       </c>
+      <c r="BY10" t="n">
+        <v>16305</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16115,6 +16442,9 @@
       <c r="BX11" t="n">
         <v>5480</v>
       </c>
+      <c r="BY11" t="n">
+        <v>5215</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16349,6 +16679,9 @@
       <c r="BX12" t="n">
         <v>5935</v>
       </c>
+      <c r="BY12" t="n">
+        <v>5630</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16583,6 +16916,9 @@
       <c r="BX13" t="n">
         <v>6000</v>
       </c>
+      <c r="BY13" t="n">
+        <v>5680</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16817,6 +17153,9 @@
       <c r="BX14" t="n">
         <v>1639</v>
       </c>
+      <c r="BY14" t="n">
+        <v>1484</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17051,6 +17390,9 @@
       <c r="BX15" t="n">
         <v>19345</v>
       </c>
+      <c r="BY15" t="n">
+        <v>18932</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -17285,6 +17627,9 @@
       <c r="BX16" t="n">
         <v>11025</v>
       </c>
+      <c r="BY16" t="n">
+        <v>10520</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17519,6 +17864,9 @@
       <c r="BX17" t="n">
         <v>6525</v>
       </c>
+      <c r="BY17" t="n">
+        <v>6185</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17753,6 +18101,9 @@
       <c r="BX18" t="n">
         <v>17292</v>
       </c>
+      <c r="BY18" t="n">
+        <v>17210</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17986,6 +18337,9 @@
       </c>
       <c r="BX19" t="n">
         <v>16140</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>15900</v>
       </c>
     </row>
   </sheetData>
@@ -17999,7 +18353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX19"/>
+  <dimension ref="A1:BY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18078,6 +18432,7 @@
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
+    <col width="12" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18313,6 +18668,9 @@
       <c r="BX1" s="1" t="n">
         <v>20251217</v>
       </c>
+      <c r="BY1" s="1" t="n">
+        <v>20251218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18547,6 +18905,9 @@
       <c r="BX2" t="n">
         <v>14780</v>
       </c>
+      <c r="BY2" t="n">
+        <v>14600</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18781,6 +19142,9 @@
       <c r="BX3" t="n">
         <v>54260</v>
       </c>
+      <c r="BY3" t="n">
+        <v>54910</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19015,6 +19379,9 @@
       <c r="BX4" t="n">
         <v>17355</v>
       </c>
+      <c r="BY4" t="n">
+        <v>17110</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19249,6 +19616,9 @@
       <c r="BX5" t="n">
         <v>14825</v>
       </c>
+      <c r="BY5" t="n">
+        <v>15055</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19483,6 +19853,9 @@
       <c r="BX6" t="n">
         <v>15985</v>
       </c>
+      <c r="BY6" t="n">
+        <v>16170</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19717,6 +20090,9 @@
       <c r="BX7" t="n">
         <v>18655</v>
       </c>
+      <c r="BY7" t="n">
+        <v>18880</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19951,6 +20327,9 @@
       <c r="BX8" t="n">
         <v>17520</v>
       </c>
+      <c r="BY8" t="n">
+        <v>17820</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20185,6 +20564,9 @@
       <c r="BX9" t="n">
         <v>1416</v>
       </c>
+      <c r="BY9" t="n">
+        <v>1291</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20419,6 +20801,9 @@
       <c r="BX10" t="n">
         <v>15825</v>
       </c>
+      <c r="BY10" t="n">
+        <v>15870</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -20653,6 +21038,9 @@
       <c r="BX11" t="n">
         <v>5295</v>
       </c>
+      <c r="BY11" t="n">
+        <v>5070</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -20887,6 +21275,9 @@
       <c r="BX12" t="n">
         <v>5695</v>
       </c>
+      <c r="BY12" t="n">
+        <v>5455</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -21121,6 +21512,9 @@
       <c r="BX13" t="n">
         <v>5750</v>
       </c>
+      <c r="BY13" t="n">
+        <v>5515</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -21355,6 +21749,9 @@
       <c r="BX14" t="n">
         <v>1555</v>
       </c>
+      <c r="BY14" t="n">
+        <v>1393</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -21589,6 +21986,9 @@
       <c r="BX15" t="n">
         <v>18590</v>
       </c>
+      <c r="BY15" t="n">
+        <v>18350</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -21823,6 +22223,9 @@
       <c r="BX16" t="n">
         <v>10700</v>
       </c>
+      <c r="BY16" t="n">
+        <v>10225</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -22057,6 +22460,9 @@
       <c r="BX17" t="n">
         <v>6345</v>
       </c>
+      <c r="BY17" t="n">
+        <v>6025</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -22291,6 +22697,9 @@
       <c r="BX18" t="n">
         <v>16610</v>
       </c>
+      <c r="BY18" t="n">
+        <v>16700</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -22524,6 +22933,9 @@
       </c>
       <c r="BX19" t="n">
         <v>15750</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>15545</v>
       </c>
     </row>
   </sheetData>
@@ -22537,7 +22949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX19"/>
+  <dimension ref="A1:BY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22616,6 +23028,7 @@
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
+    <col width="12" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22851,6 +23264,9 @@
       <c r="BX1" s="1" t="n">
         <v>20251217</v>
       </c>
+      <c r="BY1" s="1" t="n">
+        <v>20251218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23085,6 +23501,9 @@
       <c r="BX2" t="n">
         <v>14800</v>
       </c>
+      <c r="BY2" t="n">
+        <v>14810</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23319,6 +23738,9 @@
       <c r="BX3" t="n">
         <v>56205</v>
       </c>
+      <c r="BY3" t="n">
+        <v>55590</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23553,6 +23975,9 @@
       <c r="BX4" t="n">
         <v>17395</v>
       </c>
+      <c r="BY4" t="n">
+        <v>17335</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23787,6 +24212,9 @@
       <c r="BX5" t="n">
         <v>15465</v>
       </c>
+      <c r="BY5" t="n">
+        <v>15200</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24021,6 +24449,9 @@
       <c r="BX6" t="n">
         <v>16640</v>
       </c>
+      <c r="BY6" t="n">
+        <v>16305</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24255,6 +24686,9 @@
       <c r="BX7" t="n">
         <v>19330</v>
       </c>
+      <c r="BY7" t="n">
+        <v>19040</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24489,6 +24923,9 @@
       <c r="BX8" t="n">
         <v>18220</v>
       </c>
+      <c r="BY8" t="n">
+        <v>17960</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24723,6 +25160,9 @@
       <c r="BX9" t="n">
         <v>1470</v>
       </c>
+      <c r="BY9" t="n">
+        <v>1299</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24957,6 +25397,9 @@
       <c r="BX10" t="n">
         <v>16430</v>
       </c>
+      <c r="BY10" t="n">
+        <v>15955</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25191,6 +25634,9 @@
       <c r="BX11" t="n">
         <v>5410</v>
       </c>
+      <c r="BY11" t="n">
+        <v>5075</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25425,6 +25871,9 @@
       <c r="BX12" t="n">
         <v>5830</v>
       </c>
+      <c r="BY12" t="n">
+        <v>5460</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -25659,6 +26108,9 @@
       <c r="BX13" t="n">
         <v>5915</v>
       </c>
+      <c r="BY13" t="n">
+        <v>5515</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -25893,6 +26345,9 @@
       <c r="BX14" t="n">
         <v>1598</v>
       </c>
+      <c r="BY14" t="n">
+        <v>1394</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -26127,6 +26582,9 @@
       <c r="BX15" t="n">
         <v>18625</v>
       </c>
+      <c r="BY15" t="n">
+        <v>18685</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -26361,6 +26819,9 @@
       <c r="BX16" t="n">
         <v>10870</v>
       </c>
+      <c r="BY16" t="n">
+        <v>10225</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -26595,6 +27056,9 @@
       <c r="BX17" t="n">
         <v>6430</v>
       </c>
+      <c r="BY17" t="n">
+        <v>6025</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -26829,6 +27293,9 @@
       <c r="BX18" t="n">
         <v>17200</v>
       </c>
+      <c r="BY18" t="n">
+        <v>16875</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -27062,6 +27529,9 @@
       </c>
       <c r="BX19" t="n">
         <v>15780</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>15770</v>
       </c>
     </row>
   </sheetData>
@@ -27075,7 +27545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX19"/>
+  <dimension ref="A1:BY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27154,6 +27624,7 @@
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
+    <col width="12" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27389,6 +27860,9 @@
       <c r="BX1" s="1" t="n">
         <v>20251217</v>
       </c>
+      <c r="BY1" s="1" t="n">
+        <v>20251218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27623,6 +28097,9 @@
       <c r="BX2" t="n">
         <v>118248</v>
       </c>
+      <c r="BY2" t="n">
+        <v>102650</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27857,6 +28334,9 @@
       <c r="BX3" t="n">
         <v>1344452</v>
       </c>
+      <c r="BY3" t="n">
+        <v>1134435</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28091,6 +28571,9 @@
       <c r="BX4" t="n">
         <v>113502</v>
       </c>
+      <c r="BY4" t="n">
+        <v>61587</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28325,6 +28808,9 @@
       <c r="BX5" t="n">
         <v>88928</v>
       </c>
+      <c r="BY5" t="n">
+        <v>99086</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28559,6 +29045,9 @@
       <c r="BX6" t="n">
         <v>971002</v>
       </c>
+      <c r="BY6" t="n">
+        <v>919719</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28793,6 +29282,9 @@
       <c r="BX7" t="n">
         <v>801272</v>
       </c>
+      <c r="BY7" t="n">
+        <v>1081599</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29027,6 +29519,9 @@
       <c r="BX8" t="n">
         <v>2944778</v>
       </c>
+      <c r="BY8" t="n">
+        <v>3108631</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29261,6 +29756,9 @@
       <c r="BX9" t="n">
         <v>3250103</v>
       </c>
+      <c r="BY9" t="n">
+        <v>10726158</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -29495,6 +29993,9 @@
       <c r="BX10" t="n">
         <v>554937</v>
       </c>
+      <c r="BY10" t="n">
+        <v>491691</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29729,6 +30230,9 @@
       <c r="BX11" t="n">
         <v>512870</v>
       </c>
+      <c r="BY11" t="n">
+        <v>1505105</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29963,6 +30467,9 @@
       <c r="BX12" t="n">
         <v>2078371</v>
       </c>
+      <c r="BY12" t="n">
+        <v>3033949</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30197,6 +30704,9 @@
       <c r="BX13" t="n">
         <v>5887251</v>
       </c>
+      <c r="BY13" t="n">
+        <v>6034141</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30431,6 +30941,9 @@
       <c r="BX14" t="n">
         <v>23418740</v>
       </c>
+      <c r="BY14" t="n">
+        <v>67159384</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -30665,6 +31178,9 @@
       <c r="BX15" t="n">
         <v>981425</v>
       </c>
+      <c r="BY15" t="n">
+        <v>698687</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -30899,6 +31415,9 @@
       <c r="BX16" t="n">
         <v>216740</v>
       </c>
+      <c r="BY16" t="n">
+        <v>684199</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -31133,6 +31652,9 @@
       <c r="BX17" t="n">
         <v>30056</v>
       </c>
+      <c r="BY17" t="n">
+        <v>62914</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -31367,6 +31889,9 @@
       <c r="BX18" t="n">
         <v>44689</v>
       </c>
+      <c r="BY18" t="n">
+        <v>43150</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -31600,6 +32125,9 @@
       </c>
       <c r="BX19" t="n">
         <v>31690</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>11550</v>
       </c>
     </row>
   </sheetData>
@@ -31613,7 +32141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE19"/>
+  <dimension ref="A1:BF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31673,6 +32201,7 @@
     <col width="10" customWidth="1" min="55" max="55"/>
     <col width="10" customWidth="1" min="56" max="56"/>
     <col width="10" customWidth="1" min="57" max="57"/>
+    <col width="10" customWidth="1" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31851,6 +32380,9 @@
       <c r="BE1" s="1" t="n">
         <v>20251217</v>
       </c>
+      <c r="BF1" s="1" t="n">
+        <v>20251218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32028,6 +32560,9 @@
       <c r="BE2" t="n">
         <v>0</v>
       </c>
+      <c r="BF2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32205,6 +32740,9 @@
       <c r="BE3" t="n">
         <v>65</v>
       </c>
+      <c r="BF3" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -32382,6 +32920,9 @@
       <c r="BE4" t="n">
         <v>0</v>
       </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32559,6 +33100,9 @@
       <c r="BE5" t="n">
         <v>45</v>
       </c>
+      <c r="BF5" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32736,6 +33280,9 @@
       <c r="BE6" t="n">
         <v>64</v>
       </c>
+      <c r="BF6" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -32913,6 +33460,9 @@
       <c r="BE7" t="n">
         <v>76</v>
       </c>
+      <c r="BF7" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -33090,6 +33640,9 @@
       <c r="BE8" t="n">
         <v>71</v>
       </c>
+      <c r="BF8" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33267,6 +33820,9 @@
       <c r="BE9" t="n">
         <v>34</v>
       </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -33444,6 +34000,9 @@
       <c r="BE10" t="n">
         <v>30</v>
       </c>
+      <c r="BF10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -33621,6 +34180,9 @@
       <c r="BE11" t="n">
         <v>63</v>
       </c>
+      <c r="BF11" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33798,6 +34360,9 @@
       <c r="BE12" t="n">
         <v>62</v>
       </c>
+      <c r="BF12" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33975,6 +34540,9 @@
       <c r="BE13" t="n">
         <v>68</v>
       </c>
+      <c r="BF13" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34152,6 +34720,9 @@
       <c r="BE14" t="n">
         <v>45</v>
       </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -34329,6 +34900,9 @@
       <c r="BE15" t="n">
         <v>7</v>
       </c>
+      <c r="BF15" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -34506,6 +35080,9 @@
       <c r="BE16" t="n">
         <v>56</v>
       </c>
+      <c r="BF16" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -34683,6 +35260,9 @@
       <c r="BE17" t="n">
         <v>55</v>
       </c>
+      <c r="BF17" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -34860,6 +35440,9 @@
       <c r="BE18" t="n">
         <v>27</v>
       </c>
+      <c r="BF18" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -35035,6 +35618,9 @@
         <v>59</v>
       </c>
       <c r="BE19" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF19" t="n">
         <v>38</v>
       </c>
     </row>
@@ -35049,7 +35635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35069,6 +35655,7 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35127,6 +35714,9 @@
       <c r="Q1" s="1" t="n">
         <v>20251217</v>
       </c>
+      <c r="R1" s="1" t="n">
+        <v>20251218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35184,6 +35774,9 @@
       <c r="Q2" t="n">
         <v>54</v>
       </c>
+      <c r="R2" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -35241,6 +35834,9 @@
       <c r="Q3" t="n">
         <v>70</v>
       </c>
+      <c r="R3" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -35298,6 +35894,9 @@
       <c r="Q4" t="n">
         <v>50</v>
       </c>
+      <c r="R4" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -35355,6 +35954,9 @@
       <c r="Q5" t="n">
         <v>54</v>
       </c>
+      <c r="R5" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -35412,6 +36014,9 @@
       <c r="Q6" t="n">
         <v>78</v>
       </c>
+      <c r="R6" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35469,6 +36074,9 @@
       <c r="Q7" t="n">
         <v>84</v>
       </c>
+      <c r="R7" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -35526,6 +36134,9 @@
       <c r="Q8" t="n">
         <v>77</v>
       </c>
+      <c r="R8" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35583,6 +36194,9 @@
       <c r="Q9" t="n">
         <v>47</v>
       </c>
+      <c r="R9" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35640,6 +36254,9 @@
       <c r="Q10" t="n">
         <v>56</v>
       </c>
+      <c r="R10" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -35697,6 +36314,9 @@
       <c r="Q11" t="n">
         <v>82</v>
       </c>
+      <c r="R11" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -35754,6 +36374,9 @@
       <c r="Q12" t="n">
         <v>81</v>
       </c>
+      <c r="R12" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35811,6 +36434,9 @@
       <c r="Q13" t="n">
         <v>82</v>
       </c>
+      <c r="R13" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35868,6 +36494,9 @@
       <c r="Q14" t="n">
         <v>55</v>
       </c>
+      <c r="R14" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35925,6 +36554,9 @@
       <c r="Q15" t="n">
         <v>71</v>
       </c>
+      <c r="R15" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -35982,6 +36614,9 @@
       <c r="Q16" t="n">
         <v>72</v>
       </c>
+      <c r="R16" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36039,6 +36674,9 @@
       <c r="Q17" t="n">
         <v>69</v>
       </c>
+      <c r="R17" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36096,6 +36734,9 @@
       <c r="Q18" t="n">
         <v>70</v>
       </c>
+      <c r="R18" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -36152,6 +36793,9 @@
       </c>
       <c r="Q19" t="n">
         <v>77</v>
+      </c>
+      <c r="R19" t="n">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -36165,7 +36809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE19"/>
+  <dimension ref="A1:BF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -36225,6 +36869,7 @@
     <col width="10" customWidth="1" min="55" max="55"/>
     <col width="10" customWidth="1" min="56" max="56"/>
     <col width="10" customWidth="1" min="57" max="57"/>
+    <col width="10" customWidth="1" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36403,6 +37048,9 @@
       <c r="BE1" s="1" t="n">
         <v>20251217</v>
       </c>
+      <c r="BF1" s="1" t="n">
+        <v>20251218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -36580,6 +37228,9 @@
       <c r="BE2" t="n">
         <v>-101</v>
       </c>
+      <c r="BF2" t="n">
+        <v>-87</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36757,6 +37408,9 @@
       <c r="BE3" t="n">
         <v>4</v>
       </c>
+      <c r="BF3" t="n">
+        <v>-13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -36934,6 +37588,9 @@
       <c r="BE4" t="n">
         <v>-89</v>
       </c>
+      <c r="BF4" t="n">
+        <v>-84</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -37111,6 +37768,9 @@
       <c r="BE5" t="n">
         <v>-38</v>
       </c>
+      <c r="BF5" t="n">
+        <v>-61</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -37288,6 +37948,9 @@
       <c r="BE6" t="n">
         <v>2</v>
       </c>
+      <c r="BF6" t="n">
+        <v>-30</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -37465,6 +38128,9 @@
       <c r="BE7" t="n">
         <v>18</v>
       </c>
+      <c r="BF7" t="n">
+        <v>-6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -37642,6 +38308,9 @@
       <c r="BE8" t="n">
         <v>14</v>
       </c>
+      <c r="BF8" t="n">
+        <v>-9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -37819,6 +38488,9 @@
       <c r="BE9" t="n">
         <v>-32</v>
       </c>
+      <c r="BF9" t="n">
+        <v>-111</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -37996,6 +38668,9 @@
       <c r="BE10" t="n">
         <v>-52</v>
       </c>
+      <c r="BF10" t="n">
+        <v>-85</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -38173,6 +38848,9 @@
       <c r="BE11" t="n">
         <v>13</v>
       </c>
+      <c r="BF11" t="n">
+        <v>-43</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -38350,6 +39028,9 @@
       <c r="BE12" t="n">
         <v>12</v>
       </c>
+      <c r="BF12" t="n">
+        <v>-39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -38527,6 +39208,9 @@
       <c r="BE13" t="n">
         <v>21</v>
       </c>
+      <c r="BF13" t="n">
+        <v>-26</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -38704,6 +39388,9 @@
       <c r="BE14" t="n">
         <v>-20</v>
       </c>
+      <c r="BF14" t="n">
+        <v>-92</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -38881,6 +39568,9 @@
       <c r="BE15" t="n">
         <v>-72</v>
       </c>
+      <c r="BF15" t="n">
+        <v>-61</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -39058,6 +39748,9 @@
       <c r="BE16" t="n">
         <v>2</v>
       </c>
+      <c r="BF16" t="n">
+        <v>-57</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -39235,6 +39928,9 @@
       <c r="BE17" t="n">
         <v>-1</v>
       </c>
+      <c r="BF17" t="n">
+        <v>-59</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -39412,6 +40108,9 @@
       <c r="BE18" t="n">
         <v>-63</v>
       </c>
+      <c r="BF18" t="n">
+        <v>-77</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -39587,6 +40286,9 @@
         <v>1</v>
       </c>
       <c r="BE19" t="n">
+        <v>-38</v>
+      </c>
+      <c r="BF19" t="n">
         <v>-38</v>
       </c>
     </row>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -730,6 +730,7 @@
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -791,6 +792,9 @@
       <c r="R1" s="1" t="n">
         <v>20251218</v>
       </c>
+      <c r="S1" s="1" t="n">
+        <v>20251219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -851,6 +855,9 @@
       <c r="R2" t="n">
         <v>10</v>
       </c>
+      <c r="S2" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -911,6 +918,9 @@
       <c r="R3" t="n">
         <v>10</v>
       </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -971,6 +981,9 @@
       <c r="R4" t="n">
         <v>-2</v>
       </c>
+      <c r="S4" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1031,6 +1044,9 @@
       <c r="R5" t="n">
         <v>-27</v>
       </c>
+      <c r="S5" t="n">
+        <v>-37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1091,6 +1107,9 @@
       <c r="R6" t="n">
         <v>16</v>
       </c>
+      <c r="S6" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1151,6 +1170,9 @@
       <c r="R7" t="n">
         <v>28</v>
       </c>
+      <c r="S7" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1211,6 +1233,9 @@
       <c r="R8" t="n">
         <v>16</v>
       </c>
+      <c r="S8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1271,6 +1296,9 @@
       <c r="R9" t="n">
         <v>-34</v>
       </c>
+      <c r="S9" t="n">
+        <v>-37</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1331,6 +1359,9 @@
       <c r="R10" t="n">
         <v>-33</v>
       </c>
+      <c r="S10" t="n">
+        <v>-37</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1391,6 +1422,9 @@
       <c r="R11" t="n">
         <v>7</v>
       </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1451,6 +1485,9 @@
       <c r="R12" t="n">
         <v>8</v>
       </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1511,6 +1548,9 @@
       <c r="R13" t="n">
         <v>14</v>
       </c>
+      <c r="S13" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1571,6 +1611,9 @@
       <c r="R14" t="n">
         <v>-24</v>
       </c>
+      <c r="S14" t="n">
+        <v>-26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1631,6 +1674,9 @@
       <c r="R15" t="n">
         <v>38</v>
       </c>
+      <c r="S15" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1691,6 +1737,9 @@
       <c r="R16" t="n">
         <v>-2</v>
       </c>
+      <c r="S16" t="n">
+        <v>-6</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1751,6 +1800,9 @@
       <c r="R17" t="n">
         <v>-6</v>
       </c>
+      <c r="S17" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1811,6 +1863,9 @@
       <c r="R18" t="n">
         <v>3</v>
       </c>
+      <c r="S18" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1870,6 +1925,9 @@
       </c>
       <c r="R19" t="n">
         <v>43</v>
+      </c>
+      <c r="S19" t="n">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1883,7 +1941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF19"/>
+  <dimension ref="A1:BG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1944,6 +2002,7 @@
     <col width="12" customWidth="1" min="56" max="56"/>
     <col width="12" customWidth="1" min="57" max="57"/>
     <col width="12" customWidth="1" min="58" max="58"/>
+    <col width="12" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2237,6 +2296,11 @@
           <t>20251218</t>
         </is>
       </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>20251219</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2417,6 +2481,9 @@
       <c r="BF2" t="n">
         <v>94</v>
       </c>
+      <c r="BG2" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2597,6 +2664,9 @@
       <c r="BF3" t="n">
         <v>99</v>
       </c>
+      <c r="BG3" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2777,6 +2847,9 @@
       <c r="BF4" t="n">
         <v>94</v>
       </c>
+      <c r="BG4" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2957,6 +3030,9 @@
       <c r="BF5" t="n">
         <v>97</v>
       </c>
+      <c r="BG5" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3137,6 +3213,9 @@
       <c r="BF6" t="n">
         <v>98</v>
       </c>
+      <c r="BG6" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3317,6 +3396,9 @@
       <c r="BF7" t="n">
         <v>100</v>
       </c>
+      <c r="BG7" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3497,6 +3579,9 @@
       <c r="BF8" t="n">
         <v>99</v>
       </c>
+      <c r="BG8" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3677,6 +3762,9 @@
       <c r="BF9" t="n">
         <v>86</v>
       </c>
+      <c r="BG9" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3857,6 +3945,9 @@
       <c r="BF10" t="n">
         <v>94</v>
       </c>
+      <c r="BG10" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4037,6 +4128,9 @@
       <c r="BF11" t="n">
         <v>95</v>
       </c>
+      <c r="BG11" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4217,6 +4311,9 @@
       <c r="BF12" t="n">
         <v>95</v>
       </c>
+      <c r="BG12" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4397,6 +4494,9 @@
       <c r="BF13" t="n">
         <v>96</v>
       </c>
+      <c r="BG13" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4577,6 +4677,9 @@
       <c r="BF14" t="n">
         <v>85</v>
       </c>
+      <c r="BG14" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4757,6 +4860,9 @@
       <c r="BF15" t="n">
         <v>96</v>
       </c>
+      <c r="BG15" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4937,6 +5043,9 @@
       <c r="BF16" t="n">
         <v>94</v>
       </c>
+      <c r="BG16" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5117,6 +5226,9 @@
       <c r="BF17" t="n">
         <v>94</v>
       </c>
+      <c r="BG17" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5297,6 +5409,9 @@
       <c r="BF18" t="n">
         <v>94</v>
       </c>
+      <c r="BG18" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5476,6 +5591,9 @@
       </c>
       <c r="BF19" t="n">
         <v>98</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -5489,7 +5607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM19"/>
+  <dimension ref="A1:AN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5531,6 +5649,7 @@
     <col width="12" customWidth="1" min="37" max="37"/>
     <col width="12" customWidth="1" min="38" max="38"/>
     <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="12" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5729,6 +5848,11 @@
           <t>20251218</t>
         </is>
       </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>20251219</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5852,6 +5976,9 @@
       <c r="AM2" t="n">
         <v>-16.57</v>
       </c>
+      <c r="AN2" t="n">
+        <v>-13.29</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5975,6 +6102,9 @@
       <c r="AM3" t="n">
         <v>-18.71</v>
       </c>
+      <c r="AN3" t="n">
+        <v>-28.38</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6098,6 +6228,9 @@
       <c r="AM4" t="n">
         <v>-11.07</v>
       </c>
+      <c r="AN4" t="n">
+        <v>-9.17</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6221,6 +6354,9 @@
       <c r="AM5" t="n">
         <v>-10.3</v>
       </c>
+      <c r="AN5" t="n">
+        <v>-10.18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6344,6 +6480,9 @@
       <c r="AM6" t="n">
         <v>-5.76</v>
       </c>
+      <c r="AN6" t="n">
+        <v>-17.16</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6467,6 +6606,9 @@
       <c r="AM7" t="n">
         <v>-2.99</v>
       </c>
+      <c r="AN7" t="n">
+        <v>-19.55</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6590,6 +6732,9 @@
       <c r="AM8" t="n">
         <v>-15.76</v>
       </c>
+      <c r="AN8" t="n">
+        <v>-26</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6713,6 +6858,9 @@
       <c r="AM9" t="n">
         <v>-19.15</v>
       </c>
+      <c r="AN9" t="n">
+        <v>-8.42</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6836,6 +6984,9 @@
       <c r="AM10" t="n">
         <v>12.35</v>
       </c>
+      <c r="AN10" t="n">
+        <v>11.98</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6959,6 +7110,9 @@
       <c r="AM11" t="n">
         <v>21.29</v>
       </c>
+      <c r="AN11" t="n">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7082,6 +7236,9 @@
       <c r="AM12" t="n">
         <v>21.96</v>
       </c>
+      <c r="AN12" t="n">
+        <v>17.24</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7205,6 +7362,9 @@
       <c r="AM13" t="n">
         <v>28.33</v>
       </c>
+      <c r="AN13" t="n">
+        <v>20.64</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7328,6 +7488,9 @@
       <c r="AM14" t="n">
         <v>-9.83</v>
       </c>
+      <c r="AN14" t="n">
+        <v>-3.69</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7451,6 +7614,9 @@
       <c r="AM15" t="n">
         <v>-40.66</v>
       </c>
+      <c r="AN15" t="n">
+        <v>-37.77</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7574,6 +7740,9 @@
       <c r="AM16" t="n">
         <v>6.5</v>
       </c>
+      <c r="AN16" t="n">
+        <v>5.96</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7697,6 +7866,9 @@
       <c r="AM17" t="n">
         <v>2.33</v>
       </c>
+      <c r="AN17" t="n">
+        <v>2.35</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7820,6 +7992,9 @@
       <c r="AM18" t="n">
         <v>18.07</v>
       </c>
+      <c r="AN18" t="n">
+        <v>16.28</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7942,6 +8117,9 @@
       </c>
       <c r="AM19" t="n">
         <v>-39.89</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-38.07</v>
       </c>
     </row>
   </sheetData>
@@ -7955,7 +8133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7976,6 +8154,7 @@
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8069,6 +8248,11 @@
           <t>20251218</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>20251219</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8129,6 +8313,9 @@
       <c r="R2" t="n">
         <v>45</v>
       </c>
+      <c r="S2" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8189,6 +8376,9 @@
       <c r="R3" t="n">
         <v>24</v>
       </c>
+      <c r="S3" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8249,6 +8439,9 @@
       <c r="R4" t="n">
         <v>19</v>
       </c>
+      <c r="S4" t="n">
+        <v>205</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8309,6 +8502,9 @@
       <c r="R5" t="n">
         <v>6</v>
       </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8369,6 +8565,9 @@
       <c r="R6" t="n">
         <v>23</v>
       </c>
+      <c r="S6" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8429,6 +8628,9 @@
       <c r="R7" t="n">
         <v>14</v>
       </c>
+      <c r="S7" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8489,6 +8691,9 @@
       <c r="R8" t="n">
         <v>22</v>
       </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8549,6 +8754,9 @@
       <c r="R9" t="n">
         <v>72</v>
       </c>
+      <c r="S9" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8609,6 +8817,9 @@
       <c r="R10" t="n">
         <v>17</v>
       </c>
+      <c r="S10" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8669,6 +8880,9 @@
       <c r="R11" t="n">
         <v>58</v>
       </c>
+      <c r="S11" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8729,6 +8943,9 @@
       <c r="R12" t="n">
         <v>53</v>
       </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8789,6 +9006,9 @@
       <c r="R13" t="n">
         <v>44</v>
       </c>
+      <c r="S13" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8849,6 +9069,9 @@
       <c r="R14" t="n">
         <v>65</v>
       </c>
+      <c r="S14" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8909,6 +9132,9 @@
       <c r="R15" t="n">
         <v>21</v>
       </c>
+      <c r="S15" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8969,6 +9195,9 @@
       <c r="R16" t="n">
         <v>55</v>
       </c>
+      <c r="S16" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9029,6 +9258,9 @@
       <c r="R17" t="n">
         <v>13</v>
       </c>
+      <c r="S17" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9089,6 +9321,9 @@
       <c r="R18" t="n">
         <v>12</v>
       </c>
+      <c r="S18" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9148,6 +9383,9 @@
       </c>
       <c r="R19" t="n">
         <v>12</v>
+      </c>
+      <c r="S19" t="n">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -9161,7 +9399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY19"/>
+  <dimension ref="A1:BZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9241,6 +9479,7 @@
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
+    <col width="12" customWidth="1" min="78" max="78"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9479,6 +9718,9 @@
       <c r="BY1" s="1" t="n">
         <v>20251218</v>
       </c>
+      <c r="BZ1" s="1" t="n">
+        <v>20251219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9716,6 +9958,9 @@
       <c r="BY2" t="n">
         <v>14620</v>
       </c>
+      <c r="BZ2" t="n">
+        <v>14910</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9953,6 +10198,9 @@
       <c r="BY3" t="n">
         <v>54910</v>
       </c>
+      <c r="BZ3" t="n">
+        <v>56450</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10190,6 +10438,9 @@
       <c r="BY4" t="n">
         <v>17300</v>
       </c>
+      <c r="BZ4" t="n">
+        <v>17500</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10427,6 +10678,9 @@
       <c r="BY5" t="n">
         <v>15055</v>
       </c>
+      <c r="BZ5" t="n">
+        <v>15490</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10664,6 +10918,9 @@
       <c r="BY6" t="n">
         <v>16185</v>
       </c>
+      <c r="BZ6" t="n">
+        <v>16655</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10901,6 +11158,9 @@
       <c r="BY7" t="n">
         <v>18945</v>
       </c>
+      <c r="BZ7" t="n">
+        <v>19535</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11138,6 +11398,9 @@
       <c r="BY8" t="n">
         <v>17865</v>
       </c>
+      <c r="BZ8" t="n">
+        <v>18345</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11375,6 +11638,9 @@
       <c r="BY9" t="n">
         <v>1398</v>
       </c>
+      <c r="BZ9" t="n">
+        <v>1325</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11612,6 +11878,9 @@
       <c r="BY10" t="n">
         <v>16060</v>
       </c>
+      <c r="BZ10" t="n">
+        <v>16270</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11849,6 +12118,9 @@
       <c r="BY11" t="n">
         <v>5180</v>
       </c>
+      <c r="BZ11" t="n">
+        <v>5085</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12086,6 +12358,9 @@
       <c r="BY12" t="n">
         <v>5580</v>
       </c>
+      <c r="BZ12" t="n">
+        <v>5480</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12323,6 +12598,9 @@
       <c r="BY13" t="n">
         <v>5640</v>
       </c>
+      <c r="BZ13" t="n">
+        <v>5580</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12560,6 +12838,9 @@
       <c r="BY14" t="n">
         <v>1479</v>
       </c>
+      <c r="BZ14" t="n">
+        <v>1410</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12797,6 +13078,9 @@
       <c r="BY15" t="n">
         <v>18400</v>
       </c>
+      <c r="BZ15" t="n">
+        <v>18780</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13034,6 +13318,9 @@
       <c r="BY16" t="n">
         <v>10445</v>
       </c>
+      <c r="BZ16" t="n">
+        <v>10320</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13271,6 +13558,9 @@
       <c r="BY17" t="n">
         <v>6165</v>
       </c>
+      <c r="BZ17" t="n">
+        <v>6050</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13508,6 +13798,9 @@
       <c r="BY18" t="n">
         <v>16700</v>
       </c>
+      <c r="BZ18" t="n">
+        <v>17230</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13744,6 +14037,9 @@
       </c>
       <c r="BY19" t="n">
         <v>15545</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>15935</v>
       </c>
     </row>
   </sheetData>
@@ -13757,7 +14053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY19"/>
+  <dimension ref="A1:BZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13837,6 +14133,7 @@
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
+    <col width="12" customWidth="1" min="78" max="78"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14075,6 +14372,9 @@
       <c r="BY1" s="1" t="n">
         <v>20251218</v>
       </c>
+      <c r="BZ1" s="1" t="n">
+        <v>20251219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14312,6 +14612,9 @@
       <c r="BY2" t="n">
         <v>15095</v>
       </c>
+      <c r="BZ2" t="n">
+        <v>15515</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14549,6 +14852,9 @@
       <c r="BY3" t="n">
         <v>56200</v>
       </c>
+      <c r="BZ3" t="n">
+        <v>56670</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14786,6 +15092,9 @@
       <c r="BY4" t="n">
         <v>17470</v>
       </c>
+      <c r="BZ4" t="n">
+        <v>18050</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15023,6 +15332,9 @@
       <c r="BY5" t="n">
         <v>15445</v>
       </c>
+      <c r="BZ5" t="n">
+        <v>15490</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15260,6 +15572,9 @@
       <c r="BY6" t="n">
         <v>16530</v>
       </c>
+      <c r="BZ6" t="n">
+        <v>16660</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15497,6 +15812,9 @@
       <c r="BY7" t="n">
         <v>19260</v>
       </c>
+      <c r="BZ7" t="n">
+        <v>19545</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15734,6 +16052,9 @@
       <c r="BY8" t="n">
         <v>18210</v>
       </c>
+      <c r="BZ8" t="n">
+        <v>18355</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15971,6 +16292,9 @@
       <c r="BY9" t="n">
         <v>1398</v>
       </c>
+      <c r="BZ9" t="n">
+        <v>1325</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16208,6 +16532,9 @@
       <c r="BY10" t="n">
         <v>16305</v>
       </c>
+      <c r="BZ10" t="n">
+        <v>16270</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16445,6 +16772,9 @@
       <c r="BY11" t="n">
         <v>5215</v>
       </c>
+      <c r="BZ11" t="n">
+        <v>5100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16682,6 +17012,9 @@
       <c r="BY12" t="n">
         <v>5630</v>
       </c>
+      <c r="BZ12" t="n">
+        <v>5495</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16919,6 +17252,9 @@
       <c r="BY13" t="n">
         <v>5680</v>
       </c>
+      <c r="BZ13" t="n">
+        <v>5590</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17156,6 +17492,9 @@
       <c r="BY14" t="n">
         <v>1484</v>
       </c>
+      <c r="BZ14" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17393,6 +17732,9 @@
       <c r="BY15" t="n">
         <v>18932</v>
       </c>
+      <c r="BZ15" t="n">
+        <v>19485</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -17630,6 +17972,9 @@
       <c r="BY16" t="n">
         <v>10520</v>
       </c>
+      <c r="BZ16" t="n">
+        <v>10320</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17867,6 +18212,9 @@
       <c r="BY17" t="n">
         <v>6185</v>
       </c>
+      <c r="BZ17" t="n">
+        <v>6050</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -18104,6 +18452,9 @@
       <c r="BY18" t="n">
         <v>17210</v>
       </c>
+      <c r="BZ18" t="n">
+        <v>17230</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -18340,6 +18691,9 @@
       </c>
       <c r="BY19" t="n">
         <v>15900</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>16275</v>
       </c>
     </row>
   </sheetData>
@@ -18353,7 +18707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY19"/>
+  <dimension ref="A1:BZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18433,6 +18787,7 @@
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
+    <col width="12" customWidth="1" min="78" max="78"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18671,6 +19026,9 @@
       <c r="BY1" s="1" t="n">
         <v>20251218</v>
       </c>
+      <c r="BZ1" s="1" t="n">
+        <v>20251219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18908,6 +19266,9 @@
       <c r="BY2" t="n">
         <v>14600</v>
       </c>
+      <c r="BZ2" t="n">
+        <v>14835</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19145,6 +19506,9 @@
       <c r="BY3" t="n">
         <v>54910</v>
       </c>
+      <c r="BZ3" t="n">
+        <v>55300</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19382,6 +19746,9 @@
       <c r="BY4" t="n">
         <v>17110</v>
       </c>
+      <c r="BZ4" t="n">
+        <v>17300</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19619,6 +19986,9 @@
       <c r="BY5" t="n">
         <v>15055</v>
       </c>
+      <c r="BZ5" t="n">
+        <v>15030</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19856,6 +20226,9 @@
       <c r="BY6" t="n">
         <v>16170</v>
       </c>
+      <c r="BZ6" t="n">
+        <v>16230</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20093,6 +20466,9 @@
       <c r="BY7" t="n">
         <v>18880</v>
       </c>
+      <c r="BZ7" t="n">
+        <v>19010</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20330,6 +20706,9 @@
       <c r="BY8" t="n">
         <v>17820</v>
       </c>
+      <c r="BZ8" t="n">
+        <v>17900</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20567,6 +20946,9 @@
       <c r="BY9" t="n">
         <v>1291</v>
       </c>
+      <c r="BZ9" t="n">
+        <v>1209</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20804,6 +21186,9 @@
       <c r="BY10" t="n">
         <v>15870</v>
       </c>
+      <c r="BZ10" t="n">
+        <v>15770</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -21041,6 +21426,9 @@
       <c r="BY11" t="n">
         <v>5070</v>
       </c>
+      <c r="BZ11" t="n">
+        <v>4870</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -21278,6 +21666,9 @@
       <c r="BY12" t="n">
         <v>5455</v>
       </c>
+      <c r="BZ12" t="n">
+        <v>5195</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -21515,6 +21906,9 @@
       <c r="BY13" t="n">
         <v>5515</v>
       </c>
+      <c r="BZ13" t="n">
+        <v>5255</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -21752,6 +22146,9 @@
       <c r="BY14" t="n">
         <v>1393</v>
       </c>
+      <c r="BZ14" t="n">
+        <v>1289</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -21989,6 +22386,9 @@
       <c r="BY15" t="n">
         <v>18350</v>
       </c>
+      <c r="BZ15" t="n">
+        <v>18690</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -22226,6 +22626,9 @@
       <c r="BY16" t="n">
         <v>10225</v>
       </c>
+      <c r="BZ16" t="n">
+        <v>9805</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -22463,6 +22866,9 @@
       <c r="BY17" t="n">
         <v>6025</v>
       </c>
+      <c r="BZ17" t="n">
+        <v>5790</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -22700,6 +23106,9 @@
       <c r="BY18" t="n">
         <v>16700</v>
       </c>
+      <c r="BZ18" t="n">
+        <v>16650</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -22936,6 +23345,9 @@
       </c>
       <c r="BY19" t="n">
         <v>15545</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>15770</v>
       </c>
     </row>
   </sheetData>
@@ -22949,7 +23361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY19"/>
+  <dimension ref="A1:BZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23029,6 +23441,7 @@
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
+    <col width="12" customWidth="1" min="78" max="78"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23267,6 +23680,9 @@
       <c r="BY1" s="1" t="n">
         <v>20251218</v>
       </c>
+      <c r="BZ1" s="1" t="n">
+        <v>20251219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23504,6 +23920,9 @@
       <c r="BY2" t="n">
         <v>14810</v>
       </c>
+      <c r="BZ2" t="n">
+        <v>15225</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23741,6 +24160,9 @@
       <c r="BY3" t="n">
         <v>55590</v>
       </c>
+      <c r="BZ3" t="n">
+        <v>55300</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23978,6 +24400,9 @@
       <c r="BY4" t="n">
         <v>17335</v>
       </c>
+      <c r="BZ4" t="n">
+        <v>17800</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24215,6 +24640,9 @@
       <c r="BY5" t="n">
         <v>15200</v>
       </c>
+      <c r="BZ5" t="n">
+        <v>15060</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24452,6 +24880,9 @@
       <c r="BY6" t="n">
         <v>16305</v>
       </c>
+      <c r="BZ6" t="n">
+        <v>16275</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24689,6 +25120,9 @@
       <c r="BY7" t="n">
         <v>19040</v>
       </c>
+      <c r="BZ7" t="n">
+        <v>19010</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24926,6 +25360,9 @@
       <c r="BY8" t="n">
         <v>17960</v>
       </c>
+      <c r="BZ8" t="n">
+        <v>17900</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25163,6 +25600,9 @@
       <c r="BY9" t="n">
         <v>1299</v>
       </c>
+      <c r="BZ9" t="n">
+        <v>1289</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25400,6 +25840,9 @@
       <c r="BY10" t="n">
         <v>15955</v>
       </c>
+      <c r="BZ10" t="n">
+        <v>15915</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25637,6 +26080,9 @@
       <c r="BY11" t="n">
         <v>5075</v>
       </c>
+      <c r="BZ11" t="n">
+        <v>5065</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25874,6 +26320,9 @@
       <c r="BY12" t="n">
         <v>5460</v>
       </c>
+      <c r="BZ12" t="n">
+        <v>5425</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -26111,6 +26560,9 @@
       <c r="BY13" t="n">
         <v>5515</v>
       </c>
+      <c r="BZ13" t="n">
+        <v>5480</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -26348,6 +26800,9 @@
       <c r="BY14" t="n">
         <v>1394</v>
       </c>
+      <c r="BZ14" t="n">
+        <v>1390</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -26585,6 +27040,9 @@
       <c r="BY15" t="n">
         <v>18685</v>
       </c>
+      <c r="BZ15" t="n">
+        <v>19100</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -26822,6 +27280,9 @@
       <c r="BY16" t="n">
         <v>10225</v>
       </c>
+      <c r="BZ16" t="n">
+        <v>10160</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -27059,6 +27520,9 @@
       <c r="BY17" t="n">
         <v>6025</v>
       </c>
+      <c r="BZ17" t="n">
+        <v>6005</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -27296,6 +27760,9 @@
       <c r="BY18" t="n">
         <v>16875</v>
       </c>
+      <c r="BZ18" t="n">
+        <v>16790</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -27532,6 +27999,9 @@
       </c>
       <c r="BY19" t="n">
         <v>15770</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>16030</v>
       </c>
     </row>
   </sheetData>
@@ -27545,7 +28015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY19"/>
+  <dimension ref="A1:BZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27625,6 +28095,7 @@
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
+    <col width="12" customWidth="1" min="78" max="78"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27863,6 +28334,9 @@
       <c r="BY1" s="1" t="n">
         <v>20251218</v>
       </c>
+      <c r="BZ1" s="1" t="n">
+        <v>20251219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28100,6 +28574,9 @@
       <c r="BY2" t="n">
         <v>102650</v>
       </c>
+      <c r="BZ2" t="n">
+        <v>167919</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28337,6 +28814,9 @@
       <c r="BY3" t="n">
         <v>1134435</v>
       </c>
+      <c r="BZ3" t="n">
+        <v>888197</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28574,6 +29054,9 @@
       <c r="BY4" t="n">
         <v>61587</v>
       </c>
+      <c r="BZ4" t="n">
+        <v>698837</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28811,6 +29294,9 @@
       <c r="BY5" t="n">
         <v>99086</v>
       </c>
+      <c r="BZ5" t="n">
+        <v>84090</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29048,6 +29534,9 @@
       <c r="BY6" t="n">
         <v>919719</v>
       </c>
+      <c r="BZ6" t="n">
+        <v>959098</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29285,6 +29774,9 @@
       <c r="BY7" t="n">
         <v>1081599</v>
       </c>
+      <c r="BZ7" t="n">
+        <v>686870</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29522,6 +30014,9 @@
       <c r="BY8" t="n">
         <v>3108631</v>
       </c>
+      <c r="BZ8" t="n">
+        <v>2765289</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29759,6 +30254,9 @@
       <c r="BY9" t="n">
         <v>10726158</v>
       </c>
+      <c r="BZ9" t="n">
+        <v>8041115</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -29996,6 +30494,9 @@
       <c r="BY10" t="n">
         <v>491691</v>
       </c>
+      <c r="BZ10" t="n">
+        <v>398291</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30233,6 +30734,9 @@
       <c r="BY11" t="n">
         <v>1505105</v>
       </c>
+      <c r="BZ11" t="n">
+        <v>769356</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30470,6 +30974,9 @@
       <c r="BY12" t="n">
         <v>3033949</v>
       </c>
+      <c r="BZ12" t="n">
+        <v>2942623</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30707,6 +31214,9 @@
       <c r="BY13" t="n">
         <v>6034141</v>
       </c>
+      <c r="BZ13" t="n">
+        <v>6692585</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30944,6 +31454,9 @@
       <c r="BY14" t="n">
         <v>67159384</v>
       </c>
+      <c r="BZ14" t="n">
+        <v>57758090</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -31181,6 +31694,9 @@
       <c r="BY15" t="n">
         <v>698687</v>
       </c>
+      <c r="BZ15" t="n">
+        <v>1144177</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -31418,6 +31934,9 @@
       <c r="BY16" t="n">
         <v>684199</v>
       </c>
+      <c r="BZ16" t="n">
+        <v>588888</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -31655,6 +32174,9 @@
       <c r="BY17" t="n">
         <v>62914</v>
       </c>
+      <c r="BZ17" t="n">
+        <v>67864</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -31892,6 +32414,9 @@
       <c r="BY18" t="n">
         <v>43150</v>
       </c>
+      <c r="BZ18" t="n">
+        <v>42831</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -32128,6 +32653,9 @@
       </c>
       <c r="BY19" t="n">
         <v>11550</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>32593</v>
       </c>
     </row>
   </sheetData>
@@ -32141,7 +32669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF19"/>
+  <dimension ref="A1:BG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -32202,6 +32730,7 @@
     <col width="10" customWidth="1" min="56" max="56"/>
     <col width="10" customWidth="1" min="57" max="57"/>
     <col width="10" customWidth="1" min="58" max="58"/>
+    <col width="10" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32383,6 +32912,9 @@
       <c r="BF1" s="1" t="n">
         <v>20251218</v>
       </c>
+      <c r="BG1" s="1" t="n">
+        <v>20251219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32563,6 +33095,9 @@
       <c r="BF2" t="n">
         <v>1</v>
       </c>
+      <c r="BG2" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32743,6 +33278,9 @@
       <c r="BF3" t="n">
         <v>54</v>
       </c>
+      <c r="BG3" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -32923,6 +33461,9 @@
       <c r="BF4" t="n">
         <v>0</v>
       </c>
+      <c r="BG4" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -33103,6 +33644,9 @@
       <c r="BF5" t="n">
         <v>27</v>
       </c>
+      <c r="BG5" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -33283,6 +33827,9 @@
       <c r="BF6" t="n">
         <v>45</v>
       </c>
+      <c r="BG6" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -33463,6 +34010,9 @@
       <c r="BF7" t="n">
         <v>63</v>
       </c>
+      <c r="BG7" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -33643,6 +34193,9 @@
       <c r="BF8" t="n">
         <v>57</v>
       </c>
+      <c r="BG8" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33823,6 +34376,9 @@
       <c r="BF9" t="n">
         <v>0</v>
       </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34003,6 +34559,9 @@
       <c r="BF10" t="n">
         <v>1</v>
       </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -34183,6 +34742,9 @@
       <c r="BF11" t="n">
         <v>29</v>
       </c>
+      <c r="BG11" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -34363,6 +34925,9 @@
       <c r="BF12" t="n">
         <v>31</v>
       </c>
+      <c r="BG12" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34543,6 +35108,9 @@
       <c r="BF13" t="n">
         <v>38</v>
       </c>
+      <c r="BG13" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34723,6 +35291,9 @@
       <c r="BF14" t="n">
         <v>0</v>
       </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -34903,6 +35474,9 @@
       <c r="BF15" t="n">
         <v>10</v>
       </c>
+      <c r="BG15" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -35083,6 +35657,9 @@
       <c r="BF16" t="n">
         <v>19</v>
       </c>
+      <c r="BG16" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -35263,6 +35840,9 @@
       <c r="BF17" t="n">
         <v>19</v>
       </c>
+      <c r="BG17" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -35443,6 +36023,9 @@
       <c r="BF18" t="n">
         <v>12</v>
       </c>
+      <c r="BG18" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -35622,6 +36205,9 @@
       </c>
       <c r="BF19" t="n">
         <v>38</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -35635,7 +36221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35656,6 +36242,7 @@
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35717,6 +36304,9 @@
       <c r="R1" s="1" t="n">
         <v>20251218</v>
       </c>
+      <c r="S1" s="1" t="n">
+        <v>20251219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35777,6 +36367,9 @@
       <c r="R2" t="n">
         <v>55</v>
       </c>
+      <c r="S2" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -35837,6 +36430,9 @@
       <c r="R3" t="n">
         <v>66</v>
       </c>
+      <c r="S3" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -35897,6 +36493,9 @@
       <c r="R4" t="n">
         <v>49</v>
       </c>
+      <c r="S4" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -35957,6 +36556,9 @@
       <c r="R5" t="n">
         <v>46</v>
       </c>
+      <c r="S5" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -36017,6 +36619,9 @@
       <c r="R6" t="n">
         <v>72</v>
       </c>
+      <c r="S6" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -36077,6 +36682,9 @@
       <c r="R7" t="n">
         <v>79</v>
       </c>
+      <c r="S7" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -36137,6 +36745,9 @@
       <c r="R8" t="n">
         <v>72</v>
       </c>
+      <c r="S8" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -36197,6 +36808,9 @@
       <c r="R9" t="n">
         <v>29</v>
       </c>
+      <c r="S9" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -36257,6 +36871,9 @@
       <c r="R10" t="n">
         <v>43</v>
       </c>
+      <c r="S10" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -36317,6 +36934,9 @@
       <c r="R11" t="n">
         <v>65</v>
       </c>
+      <c r="S11" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -36377,6 +36997,9 @@
       <c r="R12" t="n">
         <v>65</v>
       </c>
+      <c r="S12" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36437,6 +37060,9 @@
       <c r="R13" t="n">
         <v>66</v>
       </c>
+      <c r="S13" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36497,6 +37123,9 @@
       <c r="R14" t="n">
         <v>37</v>
       </c>
+      <c r="S14" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36557,6 +37186,9 @@
       <c r="R15" t="n">
         <v>72</v>
       </c>
+      <c r="S15" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -36617,6 +37249,9 @@
       <c r="R16" t="n">
         <v>56</v>
       </c>
+      <c r="S16" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36677,6 +37312,9 @@
       <c r="R17" t="n">
         <v>54</v>
       </c>
+      <c r="S17" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36737,6 +37375,9 @@
       <c r="R18" t="n">
         <v>64</v>
       </c>
+      <c r="S18" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -36796,6 +37437,9 @@
       </c>
       <c r="R19" t="n">
         <v>76</v>
+      </c>
+      <c r="S19" t="n">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -36809,7 +37453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF19"/>
+  <dimension ref="A1:BG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -36870,6 +37514,7 @@
     <col width="10" customWidth="1" min="56" max="56"/>
     <col width="10" customWidth="1" min="57" max="57"/>
     <col width="10" customWidth="1" min="58" max="58"/>
+    <col width="10" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37051,6 +37696,9 @@
       <c r="BF1" s="1" t="n">
         <v>20251218</v>
       </c>
+      <c r="BG1" s="1" t="n">
+        <v>20251219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37231,6 +37879,9 @@
       <c r="BF2" t="n">
         <v>-87</v>
       </c>
+      <c r="BG2" t="n">
+        <v>-41</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37411,6 +38062,9 @@
       <c r="BF3" t="n">
         <v>-13</v>
       </c>
+      <c r="BG3" t="n">
+        <v>-29</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -37591,6 +38245,9 @@
       <c r="BF4" t="n">
         <v>-84</v>
       </c>
+      <c r="BG4" t="n">
+        <v>-41</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -37771,6 +38428,9 @@
       <c r="BF5" t="n">
         <v>-61</v>
       </c>
+      <c r="BG5" t="n">
+        <v>-78</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -37951,6 +38611,9 @@
       <c r="BF6" t="n">
         <v>-30</v>
       </c>
+      <c r="BG6" t="n">
+        <v>-42</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -38131,6 +38794,9 @@
       <c r="BF7" t="n">
         <v>-6</v>
       </c>
+      <c r="BG7" t="n">
+        <v>-17</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -38311,6 +38977,9 @@
       <c r="BF8" t="n">
         <v>-9</v>
       </c>
+      <c r="BG8" t="n">
+        <v>-22</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -38491,6 +39160,9 @@
       <c r="BF9" t="n">
         <v>-111</v>
       </c>
+      <c r="BG9" t="n">
+        <v>-101</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -38671,6 +39343,9 @@
       <c r="BF10" t="n">
         <v>-85</v>
       </c>
+      <c r="BG10" t="n">
+        <v>-88</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -38851,6 +39526,9 @@
       <c r="BF11" t="n">
         <v>-43</v>
       </c>
+      <c r="BG11" t="n">
+        <v>-47</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -39031,6 +39709,9 @@
       <c r="BF12" t="n">
         <v>-39</v>
       </c>
+      <c r="BG12" t="n">
+        <v>-46</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -39211,6 +39892,9 @@
       <c r="BF13" t="n">
         <v>-26</v>
       </c>
+      <c r="BG13" t="n">
+        <v>-34</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39391,6 +40075,9 @@
       <c r="BF14" t="n">
         <v>-92</v>
       </c>
+      <c r="BG14" t="n">
+        <v>-86</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39571,6 +40258,9 @@
       <c r="BF15" t="n">
         <v>-61</v>
       </c>
+      <c r="BG15" t="n">
+        <v>-26</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -39751,6 +40441,9 @@
       <c r="BF16" t="n">
         <v>-57</v>
       </c>
+      <c r="BG16" t="n">
+        <v>-63</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -39931,6 +40624,9 @@
       <c r="BF17" t="n">
         <v>-59</v>
       </c>
+      <c r="BG17" t="n">
+        <v>-62</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -40111,6 +40807,9 @@
       <c r="BF18" t="n">
         <v>-77</v>
       </c>
+      <c r="BG18" t="n">
+        <v>-84</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -40290,6 +40989,9 @@
       </c>
       <c r="BF19" t="n">
         <v>-38</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>-9</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -28575,7 +28575,7 @@
         <v>102650</v>
       </c>
       <c r="BZ2" t="n">
-        <v>167919</v>
+        <v>167920</v>
       </c>
     </row>
     <row r="3">
@@ -28815,7 +28815,7 @@
         <v>1134435</v>
       </c>
       <c r="BZ3" t="n">
-        <v>888197</v>
+        <v>1284363</v>
       </c>
     </row>
     <row r="4">
@@ -29055,7 +29055,7 @@
         <v>61587</v>
       </c>
       <c r="BZ4" t="n">
-        <v>698837</v>
+        <v>698859</v>
       </c>
     </row>
     <row r="5">
@@ -29295,7 +29295,7 @@
         <v>99086</v>
       </c>
       <c r="BZ5" t="n">
-        <v>84090</v>
+        <v>92142</v>
       </c>
     </row>
     <row r="6">
@@ -29535,7 +29535,7 @@
         <v>919719</v>
       </c>
       <c r="BZ6" t="n">
-        <v>959098</v>
+        <v>959126</v>
       </c>
     </row>
     <row r="7">
@@ -29775,7 +29775,7 @@
         <v>1081599</v>
       </c>
       <c r="BZ7" t="n">
-        <v>686870</v>
+        <v>688516</v>
       </c>
     </row>
     <row r="8">
@@ -30015,7 +30015,7 @@
         <v>3108631</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2765289</v>
+        <v>3001654</v>
       </c>
     </row>
     <row r="9">
@@ -30255,7 +30255,7 @@
         <v>10726158</v>
       </c>
       <c r="BZ9" t="n">
-        <v>8041115</v>
+        <v>8046754</v>
       </c>
     </row>
     <row r="10">
@@ -30495,7 +30495,7 @@
         <v>491691</v>
       </c>
       <c r="BZ10" t="n">
-        <v>398291</v>
+        <v>398341</v>
       </c>
     </row>
     <row r="11">
@@ -30735,7 +30735,7 @@
         <v>1505105</v>
       </c>
       <c r="BZ11" t="n">
-        <v>769356</v>
+        <v>769611</v>
       </c>
     </row>
     <row r="12">
@@ -30975,7 +30975,7 @@
         <v>3033949</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2942623</v>
+        <v>2944642</v>
       </c>
     </row>
     <row r="13">
@@ -31215,7 +31215,7 @@
         <v>6034141</v>
       </c>
       <c r="BZ13" t="n">
-        <v>6692585</v>
+        <v>6693620</v>
       </c>
     </row>
     <row r="14">
@@ -31455,7 +31455,7 @@
         <v>67159384</v>
       </c>
       <c r="BZ14" t="n">
-        <v>57758090</v>
+        <v>57842448</v>
       </c>
     </row>
     <row r="15">
@@ -31695,7 +31695,7 @@
         <v>698687</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1144177</v>
+        <v>1144650</v>
       </c>
     </row>
     <row r="16">
@@ -32415,7 +32415,7 @@
         <v>43150</v>
       </c>
       <c r="BZ18" t="n">
-        <v>42831</v>
+        <v>42833</v>
       </c>
     </row>
     <row r="19">

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -731,6 +731,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -795,6 +796,9 @@
       <c r="S1" s="1" t="n">
         <v>20251219</v>
       </c>
+      <c r="T1" s="1" t="n">
+        <v>20251222</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -858,6 +862,9 @@
       <c r="S2" t="n">
         <v>26</v>
       </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -921,6 +928,9 @@
       <c r="S3" t="n">
         <v>5</v>
       </c>
+      <c r="T3" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -984,6 +994,9 @@
       <c r="S4" t="n">
         <v>18</v>
       </c>
+      <c r="T4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1047,6 +1060,9 @@
       <c r="S5" t="n">
         <v>-37</v>
       </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1110,6 +1126,9 @@
       <c r="S6" t="n">
         <v>13</v>
       </c>
+      <c r="T6" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1173,6 +1192,9 @@
       <c r="S7" t="n">
         <v>26</v>
       </c>
+      <c r="T7" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1236,6 +1258,9 @@
       <c r="S8" t="n">
         <v>12</v>
       </c>
+      <c r="T8" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1299,6 +1324,9 @@
       <c r="S9" t="n">
         <v>-37</v>
       </c>
+      <c r="T9" t="n">
+        <v>-29</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1362,6 +1390,9 @@
       <c r="S10" t="n">
         <v>-37</v>
       </c>
+      <c r="T10" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1425,6 +1456,9 @@
       <c r="S11" t="n">
         <v>5</v>
       </c>
+      <c r="T11" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1488,6 +1522,9 @@
       <c r="S12" t="n">
         <v>4</v>
       </c>
+      <c r="T12" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1551,6 +1588,9 @@
       <c r="S13" t="n">
         <v>11</v>
       </c>
+      <c r="T13" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1614,6 +1654,9 @@
       <c r="S14" t="n">
         <v>-26</v>
       </c>
+      <c r="T14" t="n">
+        <v>-19</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1677,6 +1720,9 @@
       <c r="S15" t="n">
         <v>46</v>
       </c>
+      <c r="T15" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1740,6 +1786,9 @@
       <c r="S16" t="n">
         <v>-6</v>
       </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1803,6 +1852,9 @@
       <c r="S17" t="n">
         <v>-8</v>
       </c>
+      <c r="T17" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1866,6 +1918,9 @@
       <c r="S18" t="n">
         <v>-2</v>
       </c>
+      <c r="T18" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1928,6 +1983,9 @@
       </c>
       <c r="S19" t="n">
         <v>51</v>
+      </c>
+      <c r="T19" t="n">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1941,7 +1999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG19"/>
+  <dimension ref="A1:BH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2003,6 +2061,7 @@
     <col width="12" customWidth="1" min="57" max="57"/>
     <col width="12" customWidth="1" min="58" max="58"/>
     <col width="12" customWidth="1" min="59" max="59"/>
+    <col width="12" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2301,6 +2360,11 @@
           <t>20251219</t>
         </is>
       </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>20251222</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2484,6 +2548,9 @@
       <c r="BG2" t="n">
         <v>97</v>
       </c>
+      <c r="BH2" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2667,6 +2734,9 @@
       <c r="BG3" t="n">
         <v>98</v>
       </c>
+      <c r="BH3" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2850,6 +2920,9 @@
       <c r="BG4" t="n">
         <v>97</v>
       </c>
+      <c r="BH4" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3033,6 +3106,9 @@
       <c r="BG5" t="n">
         <v>96</v>
       </c>
+      <c r="BH5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3216,6 +3292,9 @@
       <c r="BG6" t="n">
         <v>98</v>
       </c>
+      <c r="BH6" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3399,6 +3478,9 @@
       <c r="BG7" t="n">
         <v>99</v>
       </c>
+      <c r="BH7" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3582,6 +3664,9 @@
       <c r="BG8" t="n">
         <v>99</v>
       </c>
+      <c r="BH8" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3765,6 +3850,9 @@
       <c r="BG9" t="n">
         <v>86</v>
       </c>
+      <c r="BH9" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3948,6 +4036,9 @@
       <c r="BG10" t="n">
         <v>94</v>
       </c>
+      <c r="BH10" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4131,6 +4222,9 @@
       <c r="BG11" t="n">
         <v>95</v>
       </c>
+      <c r="BH11" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4314,6 +4408,9 @@
       <c r="BG12" t="n">
         <v>94</v>
       </c>
+      <c r="BH12" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4497,6 +4594,9 @@
       <c r="BG13" t="n">
         <v>95</v>
       </c>
+      <c r="BH13" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4680,6 +4780,9 @@
       <c r="BG14" t="n">
         <v>85</v>
       </c>
+      <c r="BH14" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4863,6 +4966,9 @@
       <c r="BG15" t="n">
         <v>98</v>
       </c>
+      <c r="BH15" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5046,6 +5152,9 @@
       <c r="BG16" t="n">
         <v>94</v>
       </c>
+      <c r="BH16" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5229,6 +5338,9 @@
       <c r="BG17" t="n">
         <v>94</v>
       </c>
+      <c r="BH17" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5412,6 +5524,9 @@
       <c r="BG18" t="n">
         <v>94</v>
       </c>
+      <c r="BH18" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5594,6 +5709,9 @@
       </c>
       <c r="BG19" t="n">
         <v>100</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -5607,7 +5725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN19"/>
+  <dimension ref="A1:AO19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5650,6 +5768,7 @@
     <col width="12" customWidth="1" min="38" max="38"/>
     <col width="12" customWidth="1" min="39" max="39"/>
     <col width="12" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5853,6 +5972,11 @@
           <t>20251219</t>
         </is>
       </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>20251222</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5979,6 +6103,9 @@
       <c r="AN2" t="n">
         <v>-13.29</v>
       </c>
+      <c r="AO2" t="n">
+        <v>-4.54</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6105,6 +6232,9 @@
       <c r="AN3" t="n">
         <v>-28.38</v>
       </c>
+      <c r="AO3" t="n">
+        <v>-34.91</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6231,6 +6361,9 @@
       <c r="AN4" t="n">
         <v>-9.17</v>
       </c>
+      <c r="AO4" t="n">
+        <v>-3.83</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6357,6 +6490,9 @@
       <c r="AN5" t="n">
         <v>-10.18</v>
       </c>
+      <c r="AO5" t="n">
+        <v>-13.27</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6483,6 +6619,9 @@
       <c r="AN6" t="n">
         <v>-17.16</v>
       </c>
+      <c r="AO6" t="n">
+        <v>-28.29</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6609,6 +6748,9 @@
       <c r="AN7" t="n">
         <v>-19.55</v>
       </c>
+      <c r="AO7" t="n">
+        <v>-32.44</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6735,6 +6877,9 @@
       <c r="AN8" t="n">
         <v>-26</v>
       </c>
+      <c r="AO8" t="n">
+        <v>-34.24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6861,6 +7006,9 @@
       <c r="AN9" t="n">
         <v>-8.42</v>
       </c>
+      <c r="AO9" t="n">
+        <v>-3.96</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6987,6 +7135,9 @@
       <c r="AN10" t="n">
         <v>11.98</v>
       </c>
+      <c r="AO10" t="n">
+        <v>6.01</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7113,6 +7264,9 @@
       <c r="AN11" t="n">
         <v>15.9</v>
       </c>
+      <c r="AO11" t="n">
+        <v>4.37</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7239,6 +7393,9 @@
       <c r="AN12" t="n">
         <v>17.24</v>
       </c>
+      <c r="AO12" t="n">
+        <v>6.8</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7365,6 +7522,9 @@
       <c r="AN13" t="n">
         <v>20.64</v>
       </c>
+      <c r="AO13" t="n">
+        <v>7.99</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7491,6 +7651,9 @@
       <c r="AN14" t="n">
         <v>-3.69</v>
       </c>
+      <c r="AO14" t="n">
+        <v>-3.93</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7617,6 +7780,9 @@
       <c r="AN15" t="n">
         <v>-37.77</v>
       </c>
+      <c r="AO15" t="n">
+        <v>-34.57</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7743,6 +7909,9 @@
       <c r="AN16" t="n">
         <v>5.96</v>
       </c>
+      <c r="AO16" t="n">
+        <v>-0.33</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7869,6 +8038,9 @@
       <c r="AN17" t="n">
         <v>2.35</v>
       </c>
+      <c r="AO17" t="n">
+        <v>-3.93</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7995,6 +8167,9 @@
       <c r="AN18" t="n">
         <v>16.28</v>
       </c>
+      <c r="AO18" t="n">
+        <v>9.76</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8120,6 +8295,9 @@
       </c>
       <c r="AN19" t="n">
         <v>-38.07</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-38.15</v>
       </c>
     </row>
   </sheetData>
@@ -8133,7 +8311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8155,6 +8333,7 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8253,6 +8432,11 @@
           <t>20251219</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>20251222</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8316,6 +8500,9 @@
       <c r="S2" t="n">
         <v>72</v>
       </c>
+      <c r="T2" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8379,6 +8566,9 @@
       <c r="S3" t="n">
         <v>19</v>
       </c>
+      <c r="T3" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8442,6 +8632,9 @@
       <c r="S4" t="n">
         <v>205</v>
       </c>
+      <c r="T4" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8505,6 +8698,9 @@
       <c r="S5" t="n">
         <v>5</v>
       </c>
+      <c r="T5" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8568,6 +8764,9 @@
       <c r="S6" t="n">
         <v>24</v>
       </c>
+      <c r="T6" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8631,6 +8830,9 @@
       <c r="S7" t="n">
         <v>9</v>
       </c>
+      <c r="T7" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8694,6 +8896,9 @@
       <c r="S8" t="n">
         <v>20</v>
       </c>
+      <c r="T8" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8757,6 +8962,9 @@
       <c r="S9" t="n">
         <v>53</v>
       </c>
+      <c r="T9" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8820,6 +9028,9 @@
       <c r="S10" t="n">
         <v>14</v>
       </c>
+      <c r="T10" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8883,6 +9094,9 @@
       <c r="S11" t="n">
         <v>29</v>
       </c>
+      <c r="T11" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8946,6 +9160,9 @@
       <c r="S12" t="n">
         <v>50</v>
       </c>
+      <c r="T12" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9009,6 +9226,9 @@
       <c r="S13" t="n">
         <v>48</v>
       </c>
+      <c r="T13" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9072,6 +9292,9 @@
       <c r="S14" t="n">
         <v>55</v>
       </c>
+      <c r="T14" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9135,6 +9358,9 @@
       <c r="S15" t="n">
         <v>34</v>
       </c>
+      <c r="T15" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9198,6 +9424,9 @@
       <c r="S16" t="n">
         <v>47</v>
       </c>
+      <c r="T16" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9261,6 +9490,9 @@
       <c r="S17" t="n">
         <v>14</v>
       </c>
+      <c r="T17" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9324,6 +9556,9 @@
       <c r="S18" t="n">
         <v>12</v>
       </c>
+      <c r="T18" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9386,6 +9621,9 @@
       </c>
       <c r="S19" t="n">
         <v>34</v>
+      </c>
+      <c r="T19" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -9399,7 +9637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ19"/>
+  <dimension ref="A1:CA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9480,6 +9718,7 @@
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
+    <col width="12" customWidth="1" min="79" max="79"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9721,6 +9960,9 @@
       <c r="BZ1" s="1" t="n">
         <v>20251219</v>
       </c>
+      <c r="CA1" s="1" t="n">
+        <v>20251222</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9961,6 +10203,9 @@
       <c r="BZ2" t="n">
         <v>14910</v>
       </c>
+      <c r="CA2" t="n">
+        <v>15390</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10201,6 +10446,9 @@
       <c r="BZ3" t="n">
         <v>56450</v>
       </c>
+      <c r="CA3" t="n">
+        <v>56950</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10441,6 +10689,9 @@
       <c r="BZ4" t="n">
         <v>17500</v>
       </c>
+      <c r="CA4" t="n">
+        <v>17975</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10681,6 +10932,9 @@
       <c r="BZ5" t="n">
         <v>15490</v>
       </c>
+      <c r="CA5" t="n">
+        <v>15515</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10921,6 +11175,9 @@
       <c r="BZ6" t="n">
         <v>16655</v>
       </c>
+      <c r="CA6" t="n">
+        <v>16710</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11161,6 +11418,9 @@
       <c r="BZ7" t="n">
         <v>19535</v>
       </c>
+      <c r="CA7" t="n">
+        <v>19600</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11401,6 +11661,9 @@
       <c r="BZ8" t="n">
         <v>18345</v>
       </c>
+      <c r="CA8" t="n">
+        <v>18455</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11641,6 +11904,9 @@
       <c r="BZ9" t="n">
         <v>1325</v>
       </c>
+      <c r="CA9" t="n">
+        <v>1310</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11881,6 +12147,9 @@
       <c r="BZ10" t="n">
         <v>16270</v>
       </c>
+      <c r="CA10" t="n">
+        <v>16380</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12121,6 +12390,9 @@
       <c r="BZ11" t="n">
         <v>5085</v>
       </c>
+      <c r="CA11" t="n">
+        <v>5100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12361,6 +12633,9 @@
       <c r="BZ12" t="n">
         <v>5480</v>
       </c>
+      <c r="CA12" t="n">
+        <v>5470</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12601,6 +12876,9 @@
       <c r="BZ13" t="n">
         <v>5580</v>
       </c>
+      <c r="CA13" t="n">
+        <v>5540</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12841,6 +13119,9 @@
       <c r="BZ14" t="n">
         <v>1410</v>
       </c>
+      <c r="CA14" t="n">
+        <v>1422</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13081,6 +13362,9 @@
       <c r="BZ15" t="n">
         <v>18780</v>
       </c>
+      <c r="CA15" t="n">
+        <v>19310</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13321,6 +13605,9 @@
       <c r="BZ16" t="n">
         <v>10320</v>
       </c>
+      <c r="CA16" t="n">
+        <v>10250</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13561,6 +13848,9 @@
       <c r="BZ17" t="n">
         <v>6050</v>
       </c>
+      <c r="CA17" t="n">
+        <v>6060</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13801,6 +14091,9 @@
       <c r="BZ18" t="n">
         <v>17230</v>
       </c>
+      <c r="CA18" t="n">
+        <v>17315</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14040,6 +14333,9 @@
       </c>
       <c r="BZ19" t="n">
         <v>15935</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>16175</v>
       </c>
     </row>
   </sheetData>
@@ -14053,7 +14349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ19"/>
+  <dimension ref="A1:CA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14134,6 +14430,7 @@
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
+    <col width="12" customWidth="1" min="79" max="79"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14375,6 +14672,9 @@
       <c r="BZ1" s="1" t="n">
         <v>20251219</v>
       </c>
+      <c r="CA1" s="1" t="n">
+        <v>20251222</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14615,6 +14915,9 @@
       <c r="BZ2" t="n">
         <v>15515</v>
       </c>
+      <c r="CA2" t="n">
+        <v>15390</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14855,6 +15158,9 @@
       <c r="BZ3" t="n">
         <v>56670</v>
       </c>
+      <c r="CA3" t="n">
+        <v>57990</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15095,6 +15401,9 @@
       <c r="BZ4" t="n">
         <v>18050</v>
       </c>
+      <c r="CA4" t="n">
+        <v>17975</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15335,6 +15644,9 @@
       <c r="BZ5" t="n">
         <v>15490</v>
       </c>
+      <c r="CA5" t="n">
+        <v>15775</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15575,6 +15887,9 @@
       <c r="BZ6" t="n">
         <v>16660</v>
       </c>
+      <c r="CA6" t="n">
+        <v>17045</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15815,6 +16130,9 @@
       <c r="BZ7" t="n">
         <v>19545</v>
       </c>
+      <c r="CA7" t="n">
+        <v>19780</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16055,6 +16373,9 @@
       <c r="BZ8" t="n">
         <v>18355</v>
       </c>
+      <c r="CA8" t="n">
+        <v>18820</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16295,6 +16616,9 @@
       <c r="BZ9" t="n">
         <v>1325</v>
       </c>
+      <c r="CA9" t="n">
+        <v>1345</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16535,6 +16859,9 @@
       <c r="BZ10" t="n">
         <v>16270</v>
       </c>
+      <c r="CA10" t="n">
+        <v>16635</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16775,6 +17102,9 @@
       <c r="BZ11" t="n">
         <v>5100</v>
       </c>
+      <c r="CA11" t="n">
+        <v>5180</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17015,6 +17345,9 @@
       <c r="BZ12" t="n">
         <v>5495</v>
       </c>
+      <c r="CA12" t="n">
+        <v>5545</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17255,6 +17588,9 @@
       <c r="BZ13" t="n">
         <v>5590</v>
       </c>
+      <c r="CA13" t="n">
+        <v>5635</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17495,6 +17831,9 @@
       <c r="BZ14" t="n">
         <v>1415</v>
       </c>
+      <c r="CA14" t="n">
+        <v>1456</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17735,6 +18074,9 @@
       <c r="BZ15" t="n">
         <v>19485</v>
       </c>
+      <c r="CA15" t="n">
+        <v>19310</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -17975,6 +18317,9 @@
       <c r="BZ16" t="n">
         <v>10320</v>
       </c>
+      <c r="CA16" t="n">
+        <v>10405</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -18215,6 +18560,9 @@
       <c r="BZ17" t="n">
         <v>6050</v>
       </c>
+      <c r="CA17" t="n">
+        <v>6130</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -18455,6 +18803,9 @@
       <c r="BZ18" t="n">
         <v>17230</v>
       </c>
+      <c r="CA18" t="n">
+        <v>17650</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -18694,6 +19045,9 @@
       </c>
       <c r="BZ19" t="n">
         <v>16275</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>16210</v>
       </c>
     </row>
   </sheetData>
@@ -18707,7 +19061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ19"/>
+  <dimension ref="A1:CA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18788,6 +19142,7 @@
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
+    <col width="12" customWidth="1" min="79" max="79"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19029,6 +19384,9 @@
       <c r="BZ1" s="1" t="n">
         <v>20251219</v>
       </c>
+      <c r="CA1" s="1" t="n">
+        <v>20251222</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19269,6 +19627,9 @@
       <c r="BZ2" t="n">
         <v>14835</v>
       </c>
+      <c r="CA2" t="n">
+        <v>14550</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19509,6 +19870,9 @@
       <c r="BZ3" t="n">
         <v>55300</v>
       </c>
+      <c r="CA3" t="n">
+        <v>56720</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19749,6 +20113,9 @@
       <c r="BZ4" t="n">
         <v>17300</v>
       </c>
+      <c r="CA4" t="n">
+        <v>17515</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19989,6 +20356,9 @@
       <c r="BZ5" t="n">
         <v>15030</v>
       </c>
+      <c r="CA5" t="n">
+        <v>15515</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20229,6 +20599,9 @@
       <c r="BZ6" t="n">
         <v>16230</v>
       </c>
+      <c r="CA6" t="n">
+        <v>16710</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20469,6 +20842,9 @@
       <c r="BZ7" t="n">
         <v>19010</v>
       </c>
+      <c r="CA7" t="n">
+        <v>19475</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20709,6 +21085,9 @@
       <c r="BZ8" t="n">
         <v>17900</v>
       </c>
+      <c r="CA8" t="n">
+        <v>18435</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20949,6 +21328,9 @@
       <c r="BZ9" t="n">
         <v>1209</v>
       </c>
+      <c r="CA9" t="n">
+        <v>1293</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21189,6 +21571,9 @@
       <c r="BZ10" t="n">
         <v>15770</v>
       </c>
+      <c r="CA10" t="n">
+        <v>16330</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -21429,6 +21814,9 @@
       <c r="BZ11" t="n">
         <v>4870</v>
       </c>
+      <c r="CA11" t="n">
+        <v>5035</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -21669,6 +22057,9 @@
       <c r="BZ12" t="n">
         <v>5195</v>
       </c>
+      <c r="CA12" t="n">
+        <v>5380</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -21909,6 +22300,9 @@
       <c r="BZ13" t="n">
         <v>5255</v>
       </c>
+      <c r="CA13" t="n">
+        <v>5460</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -22149,6 +22543,9 @@
       <c r="BZ14" t="n">
         <v>1289</v>
       </c>
+      <c r="CA14" t="n">
+        <v>1386</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -22389,6 +22786,9 @@
       <c r="BZ15" t="n">
         <v>18690</v>
       </c>
+      <c r="CA15" t="n">
+        <v>18555</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -22629,6 +23029,9 @@
       <c r="BZ16" t="n">
         <v>9805</v>
       </c>
+      <c r="CA16" t="n">
+        <v>10145</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -22869,6 +23272,9 @@
       <c r="BZ17" t="n">
         <v>5790</v>
       </c>
+      <c r="CA17" t="n">
+        <v>6000</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -23109,6 +23515,9 @@
       <c r="BZ18" t="n">
         <v>16650</v>
       </c>
+      <c r="CA18" t="n">
+        <v>17300</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -23348,6 +23757,9 @@
       </c>
       <c r="BZ19" t="n">
         <v>15770</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>15755</v>
       </c>
     </row>
   </sheetData>
@@ -23361,7 +23773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ19"/>
+  <dimension ref="A1:CA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23442,6 +23854,7 @@
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
+    <col width="12" customWidth="1" min="79" max="79"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23683,6 +24096,9 @@
       <c r="BZ1" s="1" t="n">
         <v>20251219</v>
       </c>
+      <c r="CA1" s="1" t="n">
+        <v>20251222</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23923,6 +24339,9 @@
       <c r="BZ2" t="n">
         <v>15225</v>
       </c>
+      <c r="CA2" t="n">
+        <v>14735</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24163,6 +24582,9 @@
       <c r="BZ3" t="n">
         <v>55300</v>
       </c>
+      <c r="CA3" t="n">
+        <v>57990</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24403,6 +24825,9 @@
       <c r="BZ4" t="n">
         <v>17800</v>
       </c>
+      <c r="CA4" t="n">
+        <v>17570</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24643,6 +25068,9 @@
       <c r="BZ5" t="n">
         <v>15060</v>
       </c>
+      <c r="CA5" t="n">
+        <v>15775</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24883,6 +25311,9 @@
       <c r="BZ6" t="n">
         <v>16275</v>
       </c>
+      <c r="CA6" t="n">
+        <v>17045</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25123,6 +25554,9 @@
       <c r="BZ7" t="n">
         <v>19010</v>
       </c>
+      <c r="CA7" t="n">
+        <v>19780</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25363,6 +25797,9 @@
       <c r="BZ8" t="n">
         <v>17900</v>
       </c>
+      <c r="CA8" t="n">
+        <v>18820</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25603,6 +26040,9 @@
       <c r="BZ9" t="n">
         <v>1289</v>
       </c>
+      <c r="CA9" t="n">
+        <v>1334</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25843,6 +26283,9 @@
       <c r="BZ10" t="n">
         <v>15915</v>
       </c>
+      <c r="CA10" t="n">
+        <v>16630</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26083,6 +26526,9 @@
       <c r="BZ11" t="n">
         <v>5065</v>
       </c>
+      <c r="CA11" t="n">
+        <v>5155</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26323,6 +26769,9 @@
       <c r="BZ12" t="n">
         <v>5425</v>
       </c>
+      <c r="CA12" t="n">
+        <v>5505</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -26563,6 +27012,9 @@
       <c r="BZ13" t="n">
         <v>5480</v>
       </c>
+      <c r="CA13" t="n">
+        <v>5585</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -26803,6 +27255,9 @@
       <c r="BZ14" t="n">
         <v>1390</v>
       </c>
+      <c r="CA14" t="n">
+        <v>1444</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -27043,6 +27498,9 @@
       <c r="BZ15" t="n">
         <v>19100</v>
       </c>
+      <c r="CA15" t="n">
+        <v>18785</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -27283,6 +27741,9 @@
       <c r="BZ16" t="n">
         <v>10160</v>
       </c>
+      <c r="CA16" t="n">
+        <v>10355</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -27523,6 +27984,9 @@
       <c r="BZ17" t="n">
         <v>6005</v>
       </c>
+      <c r="CA17" t="n">
+        <v>6100</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -27763,6 +28227,9 @@
       <c r="BZ18" t="n">
         <v>16790</v>
       </c>
+      <c r="CA18" t="n">
+        <v>17630</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -28002,6 +28469,9 @@
       </c>
       <c r="BZ19" t="n">
         <v>16030</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>15875</v>
       </c>
     </row>
   </sheetData>
@@ -28015,7 +28485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ19"/>
+  <dimension ref="A1:CA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -28096,6 +28566,7 @@
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
+    <col width="12" customWidth="1" min="79" max="79"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28337,6 +28808,9 @@
       <c r="BZ1" s="1" t="n">
         <v>20251219</v>
       </c>
+      <c r="CA1" s="1" t="n">
+        <v>20251222</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28577,6 +29051,9 @@
       <c r="BZ2" t="n">
         <v>167920</v>
       </c>
+      <c r="CA2" t="n">
+        <v>335238</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28817,6 +29294,9 @@
       <c r="BZ3" t="n">
         <v>1284363</v>
       </c>
+      <c r="CA3" t="n">
+        <v>1681670</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -29057,6 +29537,9 @@
       <c r="BZ4" t="n">
         <v>698859</v>
       </c>
+      <c r="CA4" t="n">
+        <v>125428</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29297,6 +29780,9 @@
       <c r="BZ5" t="n">
         <v>92142</v>
       </c>
+      <c r="CA5" t="n">
+        <v>169071</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29537,6 +30023,9 @@
       <c r="BZ6" t="n">
         <v>959126</v>
       </c>
+      <c r="CA6" t="n">
+        <v>1138525</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29777,6 +30266,9 @@
       <c r="BZ7" t="n">
         <v>688516</v>
       </c>
+      <c r="CA7" t="n">
+        <v>1193229</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30017,6 +30509,9 @@
       <c r="BZ8" t="n">
         <v>3001654</v>
       </c>
+      <c r="CA8" t="n">
+        <v>3756171</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30257,6 +30752,9 @@
       <c r="BZ9" t="n">
         <v>8046754</v>
       </c>
+      <c r="CA9" t="n">
+        <v>3945948</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30497,6 +30995,9 @@
       <c r="BZ10" t="n">
         <v>398341</v>
       </c>
+      <c r="CA10" t="n">
+        <v>621962</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30737,6 +31238,9 @@
       <c r="BZ11" t="n">
         <v>769611</v>
       </c>
+      <c r="CA11" t="n">
+        <v>630382</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30977,6 +31481,9 @@
       <c r="BZ12" t="n">
         <v>2944642</v>
       </c>
+      <c r="CA12" t="n">
+        <v>1971410</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31217,6 +31724,9 @@
       <c r="BZ13" t="n">
         <v>6693620</v>
       </c>
+      <c r="CA13" t="n">
+        <v>4743832</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31457,6 +31967,9 @@
       <c r="BZ14" t="n">
         <v>57842448</v>
       </c>
+      <c r="CA14" t="n">
+        <v>33729375</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -31697,6 +32210,9 @@
       <c r="BZ15" t="n">
         <v>1144650</v>
       </c>
+      <c r="CA15" t="n">
+        <v>1420221</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -31937,6 +32453,9 @@
       <c r="BZ16" t="n">
         <v>588888</v>
       </c>
+      <c r="CA16" t="n">
+        <v>301647</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -32177,6 +32696,9 @@
       <c r="BZ17" t="n">
         <v>67864</v>
       </c>
+      <c r="CA17" t="n">
+        <v>58411</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -32417,6 +32939,9 @@
       <c r="BZ18" t="n">
         <v>42833</v>
       </c>
+      <c r="CA18" t="n">
+        <v>55007</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -32656,6 +33181,9 @@
       </c>
       <c r="BZ19" t="n">
         <v>32593</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>27473</v>
       </c>
     </row>
   </sheetData>
@@ -32669,7 +33197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG19"/>
+  <dimension ref="A1:BH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -32731,6 +33259,7 @@
     <col width="10" customWidth="1" min="57" max="57"/>
     <col width="10" customWidth="1" min="58" max="58"/>
     <col width="10" customWidth="1" min="59" max="59"/>
+    <col width="10" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32915,6 +33444,9 @@
       <c r="BG1" s="1" t="n">
         <v>20251219</v>
       </c>
+      <c r="BH1" s="1" t="n">
+        <v>20251222</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33098,6 +33630,9 @@
       <c r="BG2" t="n">
         <v>24</v>
       </c>
+      <c r="BH2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -33281,6 +33816,9 @@
       <c r="BG3" t="n">
         <v>45</v>
       </c>
+      <c r="BH3" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -33464,6 +34002,9 @@
       <c r="BG4" t="n">
         <v>23</v>
       </c>
+      <c r="BH4" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -33647,6 +34188,9 @@
       <c r="BG5" t="n">
         <v>18</v>
       </c>
+      <c r="BH5" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -33830,6 +34374,9 @@
       <c r="BG6" t="n">
         <v>40</v>
       </c>
+      <c r="BH6" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -34013,6 +34560,9 @@
       <c r="BG7" t="n">
         <v>57</v>
       </c>
+      <c r="BH7" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -34196,6 +34746,9 @@
       <c r="BG8" t="n">
         <v>53</v>
       </c>
+      <c r="BH8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -34379,6 +34932,9 @@
       <c r="BG9" t="n">
         <v>0</v>
       </c>
+      <c r="BH9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34562,6 +35118,9 @@
       <c r="BG10" t="n">
         <v>0</v>
       </c>
+      <c r="BH10" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -34745,6 +35304,9 @@
       <c r="BG11" t="n">
         <v>28</v>
       </c>
+      <c r="BH11" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -34928,6 +35490,9 @@
       <c r="BG12" t="n">
         <v>28</v>
       </c>
+      <c r="BH12" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35111,6 +35676,9 @@
       <c r="BG13" t="n">
         <v>36</v>
       </c>
+      <c r="BH13" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35294,6 +35862,9 @@
       <c r="BG14" t="n">
         <v>0</v>
       </c>
+      <c r="BH14" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35477,6 +36048,9 @@
       <c r="BG15" t="n">
         <v>31</v>
       </c>
+      <c r="BH15" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -35660,6 +36234,9 @@
       <c r="BG16" t="n">
         <v>15</v>
       </c>
+      <c r="BH16" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -35843,6 +36420,9 @@
       <c r="BG17" t="n">
         <v>18</v>
       </c>
+      <c r="BH17" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36026,6 +36606,9 @@
       <c r="BG18" t="n">
         <v>8</v>
       </c>
+      <c r="BH18" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -36208,6 +36791,9 @@
       </c>
       <c r="BG19" t="n">
         <v>54</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -36221,7 +36807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -36243,6 +36829,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36307,6 +36894,9 @@
       <c r="S1" s="1" t="n">
         <v>20251219</v>
       </c>
+      <c r="T1" s="1" t="n">
+        <v>20251222</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -36370,6 +36960,9 @@
       <c r="S2" t="n">
         <v>65</v>
       </c>
+      <c r="T2" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36433,6 +37026,9 @@
       <c r="S3" t="n">
         <v>64</v>
       </c>
+      <c r="T3" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -36496,6 +37092,9 @@
       <c r="S4" t="n">
         <v>60</v>
       </c>
+      <c r="T4" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -36559,6 +37158,9 @@
       <c r="S5" t="n">
         <v>42</v>
       </c>
+      <c r="T5" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -36622,6 +37224,9 @@
       <c r="S6" t="n">
         <v>71</v>
       </c>
+      <c r="T6" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -36685,6 +37290,9 @@
       <c r="S7" t="n">
         <v>78</v>
       </c>
+      <c r="T7" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -36748,6 +37356,9 @@
       <c r="S8" t="n">
         <v>71</v>
       </c>
+      <c r="T8" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -36811,6 +37422,9 @@
       <c r="S9" t="n">
         <v>28</v>
       </c>
+      <c r="T9" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -36874,6 +37488,9 @@
       <c r="S10" t="n">
         <v>42</v>
       </c>
+      <c r="T10" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -36937,6 +37554,9 @@
       <c r="S11" t="n">
         <v>65</v>
       </c>
+      <c r="T11" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -37000,6 +37620,9 @@
       <c r="S12" t="n">
         <v>64</v>
       </c>
+      <c r="T12" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -37063,6 +37686,9 @@
       <c r="S13" t="n">
         <v>65</v>
       </c>
+      <c r="T13" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37126,6 +37752,9 @@
       <c r="S14" t="n">
         <v>36</v>
       </c>
+      <c r="T14" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37189,6 +37818,9 @@
       <c r="S15" t="n">
         <v>78</v>
       </c>
+      <c r="T15" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -37252,6 +37884,9 @@
       <c r="S16" t="n">
         <v>55</v>
       </c>
+      <c r="T16" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37315,6 +37950,9 @@
       <c r="S17" t="n">
         <v>53</v>
       </c>
+      <c r="T17" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -37378,6 +38016,9 @@
       <c r="S18" t="n">
         <v>62</v>
       </c>
+      <c r="T18" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -37440,6 +38081,9 @@
       </c>
       <c r="S19" t="n">
         <v>83</v>
+      </c>
+      <c r="T19" t="n">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -37453,7 +38097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG19"/>
+  <dimension ref="A1:BH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37515,6 +38159,7 @@
     <col width="10" customWidth="1" min="57" max="57"/>
     <col width="10" customWidth="1" min="58" max="58"/>
     <col width="10" customWidth="1" min="59" max="59"/>
+    <col width="10" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37699,6 +38344,9 @@
       <c r="BG1" s="1" t="n">
         <v>20251219</v>
       </c>
+      <c r="BH1" s="1" t="n">
+        <v>20251222</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37882,6 +38530,9 @@
       <c r="BG2" t="n">
         <v>-41</v>
       </c>
+      <c r="BH2" t="n">
+        <v>-79</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38065,6 +38716,9 @@
       <c r="BG3" t="n">
         <v>-29</v>
       </c>
+      <c r="BH3" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -38248,6 +38902,9 @@
       <c r="BG4" t="n">
         <v>-41</v>
       </c>
+      <c r="BH4" t="n">
+        <v>-56</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -38431,6 +39088,9 @@
       <c r="BG5" t="n">
         <v>-78</v>
       </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -38614,6 +39274,9 @@
       <c r="BG6" t="n">
         <v>-42</v>
       </c>
+      <c r="BH6" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -38797,6 +39460,9 @@
       <c r="BG7" t="n">
         <v>-17</v>
       </c>
+      <c r="BH7" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -38980,6 +39646,9 @@
       <c r="BG8" t="n">
         <v>-22</v>
       </c>
+      <c r="BH8" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -39163,6 +39832,9 @@
       <c r="BG9" t="n">
         <v>-101</v>
       </c>
+      <c r="BH9" t="n">
+        <v>-76</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -39346,6 +40018,9 @@
       <c r="BG10" t="n">
         <v>-88</v>
       </c>
+      <c r="BH10" t="n">
+        <v>-29</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -39529,6 +40204,9 @@
       <c r="BG11" t="n">
         <v>-47</v>
       </c>
+      <c r="BH11" t="n">
+        <v>-38</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -39712,6 +40390,9 @@
       <c r="BG12" t="n">
         <v>-46</v>
       </c>
+      <c r="BH12" t="n">
+        <v>-41</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -39895,6 +40576,9 @@
       <c r="BG13" t="n">
         <v>-34</v>
       </c>
+      <c r="BH13" t="n">
+        <v>-27</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -40078,6 +40762,9 @@
       <c r="BG14" t="n">
         <v>-86</v>
       </c>
+      <c r="BH14" t="n">
+        <v>-68</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -40261,6 +40948,9 @@
       <c r="BG15" t="n">
         <v>-26</v>
       </c>
+      <c r="BH15" t="n">
+        <v>-52</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -40444,6 +41134,9 @@
       <c r="BG16" t="n">
         <v>-63</v>
       </c>
+      <c r="BH16" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -40627,6 +41320,9 @@
       <c r="BG17" t="n">
         <v>-62</v>
       </c>
+      <c r="BH17" t="n">
+        <v>-54</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -40810,6 +41506,9 @@
       <c r="BG18" t="n">
         <v>-84</v>
       </c>
+      <c r="BH18" t="n">
+        <v>-26</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -40992,6 +41691,9 @@
       </c>
       <c r="BG19" t="n">
         <v>-9</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>-31</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -732,6 +732,7 @@
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="10" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -799,6 +800,9 @@
       <c r="T1" s="1" t="n">
         <v>20251222</v>
       </c>
+      <c r="U1" s="1" t="n">
+        <v>20251223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -865,6 +869,9 @@
       <c r="T2" t="n">
         <v>5</v>
       </c>
+      <c r="U2" t="n">
+        <v>-7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -931,6 +938,9 @@
       <c r="T3" t="n">
         <v>37</v>
       </c>
+      <c r="U3" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -997,6 +1007,9 @@
       <c r="T4" t="n">
         <v>8</v>
       </c>
+      <c r="U4" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1063,6 +1076,9 @@
       <c r="T5" t="n">
         <v>0</v>
       </c>
+      <c r="U5" t="n">
+        <v>-14</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1129,6 +1145,9 @@
       <c r="T6" t="n">
         <v>40</v>
       </c>
+      <c r="U6" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1195,6 +1214,9 @@
       <c r="T7" t="n">
         <v>49</v>
       </c>
+      <c r="U7" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1261,6 +1283,9 @@
       <c r="T8" t="n">
         <v>43</v>
       </c>
+      <c r="U8" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1327,6 +1352,9 @@
       <c r="T9" t="n">
         <v>-29</v>
       </c>
+      <c r="U9" t="n">
+        <v>-32</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1393,6 +1421,9 @@
       <c r="T10" t="n">
         <v>-1</v>
       </c>
+      <c r="U10" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1459,6 +1490,9 @@
       <c r="T11" t="n">
         <v>11</v>
       </c>
+      <c r="U11" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1525,6 +1559,9 @@
       <c r="T12" t="n">
         <v>8</v>
       </c>
+      <c r="U12" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1591,6 +1628,9 @@
       <c r="T13" t="n">
         <v>16</v>
       </c>
+      <c r="U13" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1657,6 +1697,9 @@
       <c r="T14" t="n">
         <v>-19</v>
       </c>
+      <c r="U14" t="n">
+        <v>-23</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1723,6 +1766,9 @@
       <c r="T15" t="n">
         <v>37</v>
       </c>
+      <c r="U15" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1789,6 +1835,9 @@
       <c r="T16" t="n">
         <v>0</v>
       </c>
+      <c r="U16" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1855,6 +1904,9 @@
       <c r="T17" t="n">
         <v>-4</v>
       </c>
+      <c r="U17" t="n">
+        <v>-6</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1921,6 +1973,9 @@
       <c r="T18" t="n">
         <v>26</v>
       </c>
+      <c r="U18" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1986,6 +2041,9 @@
       </c>
       <c r="T19" t="n">
         <v>44</v>
+      </c>
+      <c r="U19" t="n">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1999,7 +2057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2062,6 +2120,7 @@
     <col width="12" customWidth="1" min="58" max="58"/>
     <col width="12" customWidth="1" min="59" max="59"/>
     <col width="12" customWidth="1" min="60" max="60"/>
+    <col width="12" customWidth="1" min="61" max="61"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2365,6 +2424,11 @@
           <t>20251222</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>20251223</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2551,6 +2615,9 @@
       <c r="BH2" t="n">
         <v>95</v>
       </c>
+      <c r="BI2" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2737,6 +2804,9 @@
       <c r="BH3" t="n">
         <v>103</v>
       </c>
+      <c r="BI3" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2923,6 +2993,9 @@
       <c r="BH4" t="n">
         <v>96</v>
       </c>
+      <c r="BI4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3109,6 +3182,9 @@
       <c r="BH5" t="n">
         <v>100</v>
       </c>
+      <c r="BI5" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3295,6 +3371,9 @@
       <c r="BH6" t="n">
         <v>102</v>
       </c>
+      <c r="BI6" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3481,6 +3560,9 @@
       <c r="BH7" t="n">
         <v>103</v>
       </c>
+      <c r="BI7" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3667,6 +3749,9 @@
       <c r="BH8" t="n">
         <v>103</v>
       </c>
+      <c r="BI8" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3853,6 +3938,9 @@
       <c r="BH9" t="n">
         <v>89</v>
       </c>
+      <c r="BI9" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4039,6 +4127,9 @@
       <c r="BH10" t="n">
         <v>98</v>
       </c>
+      <c r="BI10" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4225,6 +4316,9 @@
       <c r="BH11" t="n">
         <v>96</v>
       </c>
+      <c r="BI11" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4411,6 +4505,9 @@
       <c r="BH12" t="n">
         <v>95</v>
       </c>
+      <c r="BI12" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4597,6 +4694,9 @@
       <c r="BH13" t="n">
         <v>97</v>
       </c>
+      <c r="BI13" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4783,6 +4883,9 @@
       <c r="BH14" t="n">
         <v>89</v>
       </c>
+      <c r="BI14" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4969,6 +5072,9 @@
       <c r="BH15" t="n">
         <v>97</v>
       </c>
+      <c r="BI15" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5155,6 +5261,9 @@
       <c r="BH16" t="n">
         <v>95</v>
       </c>
+      <c r="BI16" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5341,6 +5450,9 @@
       <c r="BH17" t="n">
         <v>95</v>
       </c>
+      <c r="BI17" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5527,6 +5639,9 @@
       <c r="BH18" t="n">
         <v>98</v>
       </c>
+      <c r="BI18" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5712,6 +5827,9 @@
       </c>
       <c r="BH19" t="n">
         <v>98</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -5725,7 +5843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO19"/>
+  <dimension ref="A1:AP19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5769,6 +5887,7 @@
     <col width="12" customWidth="1" min="39" max="39"/>
     <col width="12" customWidth="1" min="40" max="40"/>
     <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5977,6 +6096,11 @@
           <t>20251222</t>
         </is>
       </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>20251223</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6106,6 +6230,9 @@
       <c r="AO2" t="n">
         <v>-4.54</v>
       </c>
+      <c r="AP2" t="n">
+        <v>8.25</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6235,6 +6362,9 @@
       <c r="AO3" t="n">
         <v>-34.91</v>
       </c>
+      <c r="AP3" t="n">
+        <v>-37.91</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6364,6 +6494,9 @@
       <c r="AO4" t="n">
         <v>-3.83</v>
       </c>
+      <c r="AP4" t="n">
+        <v>3.01</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6493,6 +6626,9 @@
       <c r="AO5" t="n">
         <v>-13.27</v>
       </c>
+      <c r="AP5" t="n">
+        <v>-10.89</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6622,6 +6758,9 @@
       <c r="AO6" t="n">
         <v>-28.29</v>
       </c>
+      <c r="AP6" t="n">
+        <v>-30.63</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6751,6 +6890,9 @@
       <c r="AO7" t="n">
         <v>-32.44</v>
       </c>
+      <c r="AP7" t="n">
+        <v>-39.7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6880,6 +7022,9 @@
       <c r="AO8" t="n">
         <v>-34.24</v>
       </c>
+      <c r="AP8" t="n">
+        <v>-36.3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7009,6 +7154,9 @@
       <c r="AO9" t="n">
         <v>-3.96</v>
       </c>
+      <c r="AP9" t="n">
+        <v>1.29</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7138,6 +7286,9 @@
       <c r="AO10" t="n">
         <v>6.01</v>
       </c>
+      <c r="AP10" t="n">
+        <v>7.4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7267,6 +7418,9 @@
       <c r="AO11" t="n">
         <v>4.37</v>
       </c>
+      <c r="AP11" t="n">
+        <v>-5.18</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7396,6 +7550,9 @@
       <c r="AO12" t="n">
         <v>6.8</v>
       </c>
+      <c r="AP12" t="n">
+        <v>-3.18</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7525,6 +7682,9 @@
       <c r="AO13" t="n">
         <v>7.99</v>
       </c>
+      <c r="AP13" t="n">
+        <v>-4.19</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7654,6 +7814,9 @@
       <c r="AO14" t="n">
         <v>-3.93</v>
       </c>
+      <c r="AP14" t="n">
+        <v>-2.3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7783,6 +7946,9 @@
       <c r="AO15" t="n">
         <v>-34.57</v>
       </c>
+      <c r="AP15" t="n">
+        <v>-32.27</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7912,6 +8078,9 @@
       <c r="AO16" t="n">
         <v>-0.33</v>
       </c>
+      <c r="AP16" t="n">
+        <v>-4.65</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8041,6 +8210,9 @@
       <c r="AO17" t="n">
         <v>-3.93</v>
       </c>
+      <c r="AP17" t="n">
+        <v>-9.23</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8170,6 +8342,9 @@
       <c r="AO18" t="n">
         <v>9.76</v>
       </c>
+      <c r="AP18" t="n">
+        <v>9.41</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8298,6 +8473,9 @@
       </c>
       <c r="AO19" t="n">
         <v>-38.15</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-43.21</v>
       </c>
     </row>
   </sheetData>
@@ -8311,7 +8489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8334,6 +8512,7 @@
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8437,6 +8616,11 @@
           <t>20251222</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>20251223</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8503,6 +8687,9 @@
       <c r="T2" t="n">
         <v>140</v>
       </c>
+      <c r="U2" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8569,6 +8756,9 @@
       <c r="T3" t="n">
         <v>36</v>
       </c>
+      <c r="U3" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8635,6 +8825,9 @@
       <c r="T4" t="n">
         <v>37</v>
       </c>
+      <c r="U4" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8701,6 +8894,9 @@
       <c r="T5" t="n">
         <v>11</v>
       </c>
+      <c r="U5" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8767,6 +8963,9 @@
       <c r="T6" t="n">
         <v>29</v>
       </c>
+      <c r="U6" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8833,6 +9032,9 @@
       <c r="T7" t="n">
         <v>16</v>
       </c>
+      <c r="U7" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8899,6 +9101,9 @@
       <c r="T8" t="n">
         <v>27</v>
       </c>
+      <c r="U8" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8965,6 +9170,9 @@
       <c r="T9" t="n">
         <v>26</v>
       </c>
+      <c r="U9" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9031,6 +9239,9 @@
       <c r="T10" t="n">
         <v>22</v>
       </c>
+      <c r="U10" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9097,6 +9308,9 @@
       <c r="T11" t="n">
         <v>24</v>
       </c>
+      <c r="U11" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9163,6 +9377,9 @@
       <c r="T12" t="n">
         <v>34</v>
       </c>
+      <c r="U12" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9229,6 +9446,9 @@
       <c r="T13" t="n">
         <v>34</v>
       </c>
+      <c r="U13" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9295,6 +9515,9 @@
       <c r="T14" t="n">
         <v>32</v>
       </c>
+      <c r="U14" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9361,6 +9584,9 @@
       <c r="T15" t="n">
         <v>42</v>
       </c>
+      <c r="U15" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9427,6 +9653,9 @@
       <c r="T16" t="n">
         <v>24</v>
       </c>
+      <c r="U16" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9493,6 +9722,9 @@
       <c r="T17" t="n">
         <v>12</v>
       </c>
+      <c r="U17" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9559,6 +9791,9 @@
       <c r="T18" t="n">
         <v>16</v>
       </c>
+      <c r="U18" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9624,6 +9859,9 @@
       </c>
       <c r="T19" t="n">
         <v>29</v>
+      </c>
+      <c r="U19" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -9637,7 +9875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA19"/>
+  <dimension ref="A1:CB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9719,6 +9957,7 @@
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
+    <col width="12" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9963,6 +10202,9 @@
       <c r="CA1" s="1" t="n">
         <v>20251222</v>
       </c>
+      <c r="CB1" s="1" t="n">
+        <v>20251223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10206,6 +10448,9 @@
       <c r="CA2" t="n">
         <v>15390</v>
       </c>
+      <c r="CB2" t="n">
+        <v>14740</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10449,6 +10694,9 @@
       <c r="CA3" t="n">
         <v>56950</v>
       </c>
+      <c r="CB3" t="n">
+        <v>58280</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10692,6 +10940,9 @@
       <c r="CA4" t="n">
         <v>17975</v>
       </c>
+      <c r="CB4" t="n">
+        <v>17600</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10935,6 +11186,9 @@
       <c r="CA5" t="n">
         <v>15515</v>
       </c>
+      <c r="CB5" t="n">
+        <v>15775</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11178,6 +11432,9 @@
       <c r="CA6" t="n">
         <v>16710</v>
       </c>
+      <c r="CB6" t="n">
+        <v>17050</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11421,6 +11678,9 @@
       <c r="CA7" t="n">
         <v>19600</v>
       </c>
+      <c r="CB7" t="n">
+        <v>19840</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11664,6 +11924,9 @@
       <c r="CA8" t="n">
         <v>18455</v>
       </c>
+      <c r="CB8" t="n">
+        <v>18875</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11907,6 +12170,9 @@
       <c r="CA9" t="n">
         <v>1310</v>
       </c>
+      <c r="CB9" t="n">
+        <v>1339</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12150,6 +12416,9 @@
       <c r="CA10" t="n">
         <v>16380</v>
       </c>
+      <c r="CB10" t="n">
+        <v>16705</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12393,6 +12662,9 @@
       <c r="CA11" t="n">
         <v>5100</v>
       </c>
+      <c r="CB11" t="n">
+        <v>5155</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12636,6 +12908,9 @@
       <c r="CA12" t="n">
         <v>5470</v>
       </c>
+      <c r="CB12" t="n">
+        <v>5515</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12879,6 +13154,9 @@
       <c r="CA13" t="n">
         <v>5540</v>
       </c>
+      <c r="CB13" t="n">
+        <v>5600</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13122,6 +13400,9 @@
       <c r="CA14" t="n">
         <v>1422</v>
       </c>
+      <c r="CB14" t="n">
+        <v>1453</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13365,6 +13646,9 @@
       <c r="CA15" t="n">
         <v>19310</v>
       </c>
+      <c r="CB15" t="n">
+        <v>18790</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13608,6 +13892,9 @@
       <c r="CA16" t="n">
         <v>10250</v>
       </c>
+      <c r="CB16" t="n">
+        <v>10400</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13851,6 +14138,9 @@
       <c r="CA17" t="n">
         <v>6060</v>
       </c>
+      <c r="CB17" t="n">
+        <v>6120</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14094,6 +14384,9 @@
       <c r="CA18" t="n">
         <v>17315</v>
       </c>
+      <c r="CB18" t="n">
+        <v>17690</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14336,6 +14629,9 @@
       </c>
       <c r="CA19" t="n">
         <v>16175</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>15960</v>
       </c>
     </row>
   </sheetData>
@@ -14349,7 +14645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA19"/>
+  <dimension ref="A1:CB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14431,6 +14727,7 @@
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
+    <col width="12" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14675,6 +14972,9 @@
       <c r="CA1" s="1" t="n">
         <v>20251222</v>
       </c>
+      <c r="CB1" s="1" t="n">
+        <v>20251223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14918,6 +15218,9 @@
       <c r="CA2" t="n">
         <v>15390</v>
       </c>
+      <c r="CB2" t="n">
+        <v>14790</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15161,6 +15464,9 @@
       <c r="CA3" t="n">
         <v>57990</v>
       </c>
+      <c r="CB3" t="n">
+        <v>58685</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15404,6 +15710,9 @@
       <c r="CA4" t="n">
         <v>17975</v>
       </c>
+      <c r="CB4" t="n">
+        <v>17610</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15647,6 +15956,9 @@
       <c r="CA5" t="n">
         <v>15775</v>
       </c>
+      <c r="CB5" t="n">
+        <v>15815</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15890,6 +16202,9 @@
       <c r="CA6" t="n">
         <v>17045</v>
       </c>
+      <c r="CB6" t="n">
+        <v>17225</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16133,6 +16448,9 @@
       <c r="CA7" t="n">
         <v>19780</v>
       </c>
+      <c r="CB7" t="n">
+        <v>20010</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16376,6 +16694,9 @@
       <c r="CA8" t="n">
         <v>18820</v>
       </c>
+      <c r="CB8" t="n">
+        <v>19090</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16619,6 +16940,9 @@
       <c r="CA9" t="n">
         <v>1345</v>
       </c>
+      <c r="CB9" t="n">
+        <v>1344</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16862,6 +17186,9 @@
       <c r="CA10" t="n">
         <v>16635</v>
       </c>
+      <c r="CB10" t="n">
+        <v>16780</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17105,6 +17432,9 @@
       <c r="CA11" t="n">
         <v>5180</v>
       </c>
+      <c r="CB11" t="n">
+        <v>5170</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17348,6 +17678,9 @@
       <c r="CA12" t="n">
         <v>5545</v>
       </c>
+      <c r="CB12" t="n">
+        <v>5545</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17591,6 +17924,9 @@
       <c r="CA13" t="n">
         <v>5635</v>
       </c>
+      <c r="CB13" t="n">
+        <v>5630</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17834,6 +18170,9 @@
       <c r="CA14" t="n">
         <v>1456</v>
       </c>
+      <c r="CB14" t="n">
+        <v>1453</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18077,6 +18416,9 @@
       <c r="CA15" t="n">
         <v>19310</v>
       </c>
+      <c r="CB15" t="n">
+        <v>18875</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -18320,6 +18662,9 @@
       <c r="CA16" t="n">
         <v>10405</v>
       </c>
+      <c r="CB16" t="n">
+        <v>10400</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -18563,6 +18908,9 @@
       <c r="CA17" t="n">
         <v>6130</v>
       </c>
+      <c r="CB17" t="n">
+        <v>6135</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -18806,6 +19154,9 @@
       <c r="CA18" t="n">
         <v>17650</v>
       </c>
+      <c r="CB18" t="n">
+        <v>17835</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -19048,6 +19399,9 @@
       </c>
       <c r="CA19" t="n">
         <v>16210</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>15960</v>
       </c>
     </row>
   </sheetData>
@@ -19061,7 +19415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA19"/>
+  <dimension ref="A1:CB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19143,6 +19497,7 @@
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
+    <col width="12" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19387,6 +19742,9 @@
       <c r="CA1" s="1" t="n">
         <v>20251222</v>
       </c>
+      <c r="CB1" s="1" t="n">
+        <v>20251223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19630,6 +19988,9 @@
       <c r="CA2" t="n">
         <v>14550</v>
       </c>
+      <c r="CB2" t="n">
+        <v>14425</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19873,6 +20234,9 @@
       <c r="CA3" t="n">
         <v>56720</v>
       </c>
+      <c r="CB3" t="n">
+        <v>57975</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20116,6 +20480,9 @@
       <c r="CA4" t="n">
         <v>17515</v>
       </c>
+      <c r="CB4" t="n">
+        <v>17310</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20359,6 +20726,9 @@
       <c r="CA5" t="n">
         <v>15515</v>
       </c>
+      <c r="CB5" t="n">
+        <v>15540</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20602,6 +20972,9 @@
       <c r="CA6" t="n">
         <v>16710</v>
       </c>
+      <c r="CB6" t="n">
+        <v>17005</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20845,6 +21218,9 @@
       <c r="CA7" t="n">
         <v>19475</v>
       </c>
+      <c r="CB7" t="n">
+        <v>19765</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21088,6 +21464,9 @@
       <c r="CA8" t="n">
         <v>18435</v>
       </c>
+      <c r="CB8" t="n">
+        <v>18820</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21331,6 +21710,9 @@
       <c r="CA9" t="n">
         <v>1293</v>
       </c>
+      <c r="CB9" t="n">
+        <v>1311</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21574,6 +21956,9 @@
       <c r="CA10" t="n">
         <v>16330</v>
       </c>
+      <c r="CB10" t="n">
+        <v>16475</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -21817,6 +22202,9 @@
       <c r="CA11" t="n">
         <v>5035</v>
       </c>
+      <c r="CB11" t="n">
+        <v>5100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -22060,6 +22448,9 @@
       <c r="CA12" t="n">
         <v>5380</v>
       </c>
+      <c r="CB12" t="n">
+        <v>5450</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -22303,6 +22694,9 @@
       <c r="CA13" t="n">
         <v>5460</v>
       </c>
+      <c r="CB13" t="n">
+        <v>5525</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -22546,6 +22940,9 @@
       <c r="CA14" t="n">
         <v>1386</v>
       </c>
+      <c r="CB14" t="n">
+        <v>1413</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -22789,6 +23186,9 @@
       <c r="CA15" t="n">
         <v>18555</v>
       </c>
+      <c r="CB15" t="n">
+        <v>18510</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -23032,6 +23432,9 @@
       <c r="CA16" t="n">
         <v>10145</v>
       </c>
+      <c r="CB16" t="n">
+        <v>10260</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -23275,6 +23678,9 @@
       <c r="CA17" t="n">
         <v>6000</v>
       </c>
+      <c r="CB17" t="n">
+        <v>6050</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -23518,6 +23924,9 @@
       <c r="CA18" t="n">
         <v>17300</v>
       </c>
+      <c r="CB18" t="n">
+        <v>17480</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -23760,6 +24169,9 @@
       </c>
       <c r="CA19" t="n">
         <v>15755</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>15645</v>
       </c>
     </row>
   </sheetData>
@@ -23773,7 +24185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA19"/>
+  <dimension ref="A1:CB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23855,6 +24267,7 @@
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
+    <col width="12" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24099,6 +24512,9 @@
       <c r="CA1" s="1" t="n">
         <v>20251222</v>
       </c>
+      <c r="CB1" s="1" t="n">
+        <v>20251223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24342,6 +24758,9 @@
       <c r="CA2" t="n">
         <v>14735</v>
       </c>
+      <c r="CB2" t="n">
+        <v>14445</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24585,6 +25004,9 @@
       <c r="CA3" t="n">
         <v>57990</v>
       </c>
+      <c r="CB3" t="n">
+        <v>58295</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24828,6 +25250,9 @@
       <c r="CA4" t="n">
         <v>17570</v>
       </c>
+      <c r="CB4" t="n">
+        <v>17320</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25071,6 +25496,9 @@
       <c r="CA5" t="n">
         <v>15775</v>
       </c>
+      <c r="CB5" t="n">
+        <v>15570</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25314,6 +25742,9 @@
       <c r="CA6" t="n">
         <v>17045</v>
       </c>
+      <c r="CB6" t="n">
+        <v>17055</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25557,6 +25988,9 @@
       <c r="CA7" t="n">
         <v>19780</v>
       </c>
+      <c r="CB7" t="n">
+        <v>19805</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25800,6 +26234,9 @@
       <c r="CA8" t="n">
         <v>18820</v>
       </c>
+      <c r="CB8" t="n">
+        <v>18915</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26043,6 +26480,9 @@
       <c r="CA9" t="n">
         <v>1334</v>
       </c>
+      <c r="CB9" t="n">
+        <v>1326</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26286,6 +26726,9 @@
       <c r="CA10" t="n">
         <v>16630</v>
       </c>
+      <c r="CB10" t="n">
+        <v>16580</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26529,6 +26972,9 @@
       <c r="CA11" t="n">
         <v>5155</v>
       </c>
+      <c r="CB11" t="n">
+        <v>5130</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26772,6 +27218,9 @@
       <c r="CA12" t="n">
         <v>5505</v>
       </c>
+      <c r="CB12" t="n">
+        <v>5465</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27015,6 +27464,9 @@
       <c r="CA13" t="n">
         <v>5585</v>
       </c>
+      <c r="CB13" t="n">
+        <v>5545</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -27258,6 +27710,9 @@
       <c r="CA14" t="n">
         <v>1444</v>
       </c>
+      <c r="CB14" t="n">
+        <v>1427</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -27501,6 +27956,9 @@
       <c r="CA15" t="n">
         <v>18785</v>
       </c>
+      <c r="CB15" t="n">
+        <v>18565</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -27744,6 +28202,9 @@
       <c r="CA16" t="n">
         <v>10355</v>
       </c>
+      <c r="CB16" t="n">
+        <v>10295</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -27987,6 +28448,9 @@
       <c r="CA17" t="n">
         <v>6100</v>
       </c>
+      <c r="CB17" t="n">
+        <v>6080</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -28230,6 +28694,9 @@
       <c r="CA18" t="n">
         <v>17630</v>
       </c>
+      <c r="CB18" t="n">
+        <v>17510</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -28472,6 +28939,9 @@
       </c>
       <c r="CA19" t="n">
         <v>15875</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>15690</v>
       </c>
     </row>
   </sheetData>
@@ -28485,7 +28955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA19"/>
+  <dimension ref="A1:CB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -28567,6 +29037,7 @@
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
+    <col width="12" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28811,6 +29282,9 @@
       <c r="CA1" s="1" t="n">
         <v>20251222</v>
       </c>
+      <c r="CB1" s="1" t="n">
+        <v>20251223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29054,6 +29528,9 @@
       <c r="CA2" t="n">
         <v>335238</v>
       </c>
+      <c r="CB2" t="n">
+        <v>207562</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29297,6 +29774,9 @@
       <c r="CA3" t="n">
         <v>1681670</v>
       </c>
+      <c r="CB3" t="n">
+        <v>1658116</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -29540,6 +30020,9 @@
       <c r="CA4" t="n">
         <v>125428</v>
       </c>
+      <c r="CB4" t="n">
+        <v>129753</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29783,6 +30266,9 @@
       <c r="CA5" t="n">
         <v>169071</v>
       </c>
+      <c r="CB5" t="n">
+        <v>195913</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -30026,6 +30512,9 @@
       <c r="CA6" t="n">
         <v>1138525</v>
       </c>
+      <c r="CB6" t="n">
+        <v>1232906</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -30269,6 +30758,9 @@
       <c r="CA7" t="n">
         <v>1193229</v>
       </c>
+      <c r="CB7" t="n">
+        <v>1526214</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30512,6 +31004,9 @@
       <c r="CA8" t="n">
         <v>3756171</v>
       </c>
+      <c r="CB8" t="n">
+        <v>7465502</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30755,6 +31250,9 @@
       <c r="CA9" t="n">
         <v>3945948</v>
       </c>
+      <c r="CB9" t="n">
+        <v>3138424</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30998,6 +31496,9 @@
       <c r="CA10" t="n">
         <v>621962</v>
       </c>
+      <c r="CB10" t="n">
+        <v>700538</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -31241,6 +31742,9 @@
       <c r="CA11" t="n">
         <v>630382</v>
       </c>
+      <c r="CB11" t="n">
+        <v>229707</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31484,6 +31988,9 @@
       <c r="CA12" t="n">
         <v>1971410</v>
       </c>
+      <c r="CB12" t="n">
+        <v>1296276</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31727,6 +32234,9 @@
       <c r="CA13" t="n">
         <v>4743832</v>
       </c>
+      <c r="CB13" t="n">
+        <v>3182119</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31970,6 +32480,9 @@
       <c r="CA14" t="n">
         <v>33729375</v>
       </c>
+      <c r="CB14" t="n">
+        <v>18574208</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32213,6 +32726,9 @@
       <c r="CA15" t="n">
         <v>1420221</v>
       </c>
+      <c r="CB15" t="n">
+        <v>797819</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -32456,6 +32972,9 @@
       <c r="CA16" t="n">
         <v>301647</v>
       </c>
+      <c r="CB16" t="n">
+        <v>171212</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -32699,6 +33218,9 @@
       <c r="CA17" t="n">
         <v>58411</v>
       </c>
+      <c r="CB17" t="n">
+        <v>15232</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -32942,6 +33464,9 @@
       <c r="CA18" t="n">
         <v>55007</v>
       </c>
+      <c r="CB18" t="n">
+        <v>66888</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -33184,6 +33709,9 @@
       </c>
       <c r="CA19" t="n">
         <v>27473</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>25083</v>
       </c>
     </row>
   </sheetData>
@@ -33197,7 +33725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33260,6 +33788,7 @@
     <col width="10" customWidth="1" min="58" max="58"/>
     <col width="10" customWidth="1" min="59" max="59"/>
     <col width="10" customWidth="1" min="60" max="60"/>
+    <col width="10" customWidth="1" min="61" max="61"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33447,6 +33976,9 @@
       <c r="BH1" s="1" t="n">
         <v>20251222</v>
       </c>
+      <c r="BI1" s="1" t="n">
+        <v>20251223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33633,6 +34165,9 @@
       <c r="BH2" t="n">
         <v>0</v>
       </c>
+      <c r="BI2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -33819,6 +34354,9 @@
       <c r="BH3" t="n">
         <v>93</v>
       </c>
+      <c r="BI3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34005,6 +34543,9 @@
       <c r="BH4" t="n">
         <v>12</v>
       </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34191,6 +34732,9 @@
       <c r="BH5" t="n">
         <v>66</v>
       </c>
+      <c r="BI5" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34377,6 +34921,9 @@
       <c r="BH6" t="n">
         <v>80</v>
       </c>
+      <c r="BI6" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -34563,6 +35110,9 @@
       <c r="BH7" t="n">
         <v>92</v>
       </c>
+      <c r="BI7" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -34749,6 +35299,9 @@
       <c r="BH8" t="n">
         <v>100</v>
       </c>
+      <c r="BI8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -34935,6 +35488,9 @@
       <c r="BH9" t="n">
         <v>12</v>
       </c>
+      <c r="BI9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35121,6 +35677,9 @@
       <c r="BH10" t="n">
         <v>43</v>
       </c>
+      <c r="BI10" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -35307,6 +35866,9 @@
       <c r="BH11" t="n">
         <v>34</v>
       </c>
+      <c r="BI11" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -35493,6 +36055,9 @@
       <c r="BH12" t="n">
         <v>33</v>
       </c>
+      <c r="BI12" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35679,6 +36244,9 @@
       <c r="BH13" t="n">
         <v>42</v>
       </c>
+      <c r="BI13" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35865,6 +36433,9 @@
       <c r="BH14" t="n">
         <v>13</v>
       </c>
+      <c r="BI14" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36051,6 +36622,9 @@
       <c r="BH15" t="n">
         <v>15</v>
       </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -36237,6 +36811,9 @@
       <c r="BH16" t="n">
         <v>23</v>
       </c>
+      <c r="BI16" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36423,6 +37000,9 @@
       <c r="BH17" t="n">
         <v>24</v>
       </c>
+      <c r="BI17" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36609,6 +37189,9 @@
       <c r="BH18" t="n">
         <v>48</v>
       </c>
+      <c r="BI18" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -36794,6 +37377,9 @@
       </c>
       <c r="BH19" t="n">
         <v>44</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -36807,7 +37393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -36830,6 +37416,7 @@
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="10" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36897,6 +37484,9 @@
       <c r="T1" s="1" t="n">
         <v>20251222</v>
       </c>
+      <c r="U1" s="1" t="n">
+        <v>20251223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -36963,6 +37553,9 @@
       <c r="T2" t="n">
         <v>53</v>
       </c>
+      <c r="U2" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37029,6 +37622,9 @@
       <c r="T3" t="n">
         <v>81</v>
       </c>
+      <c r="U3" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -37095,6 +37691,9 @@
       <c r="T4" t="n">
         <v>55</v>
       </c>
+      <c r="U4" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -37161,6 +37760,9 @@
       <c r="T5" t="n">
         <v>61</v>
       </c>
+      <c r="U5" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -37227,6 +37829,9 @@
       <c r="T6" t="n">
         <v>86</v>
       </c>
+      <c r="U6" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -37293,6 +37898,9 @@
       <c r="T7" t="n">
         <v>92</v>
       </c>
+      <c r="U7" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -37359,6 +37967,9 @@
       <c r="T8" t="n">
         <v>88</v>
       </c>
+      <c r="U8" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -37425,6 +38036,9 @@
       <c r="T9" t="n">
         <v>33</v>
       </c>
+      <c r="U9" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -37491,6 +38105,9 @@
       <c r="T10" t="n">
         <v>61</v>
       </c>
+      <c r="U10" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -37557,6 +38174,9 @@
       <c r="T11" t="n">
         <v>69</v>
       </c>
+      <c r="U11" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -37623,6 +38243,9 @@
       <c r="T12" t="n">
         <v>67</v>
       </c>
+      <c r="U12" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -37689,6 +38312,9 @@
       <c r="T13" t="n">
         <v>69</v>
       </c>
+      <c r="U13" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37755,6 +38381,9 @@
       <c r="T14" t="n">
         <v>41</v>
       </c>
+      <c r="U14" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37821,6 +38450,9 @@
       <c r="T15" t="n">
         <v>73</v>
       </c>
+      <c r="U15" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -37887,6 +38519,9 @@
       <c r="T16" t="n">
         <v>59</v>
       </c>
+      <c r="U16" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37953,6 +38588,9 @@
       <c r="T17" t="n">
         <v>57</v>
       </c>
+      <c r="U17" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -38019,6 +38657,9 @@
       <c r="T18" t="n">
         <v>78</v>
       </c>
+      <c r="U18" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -38084,6 +38725,9 @@
       </c>
       <c r="T19" t="n">
         <v>79</v>
+      </c>
+      <c r="U19" t="n">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -38097,7 +38741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -38160,6 +38804,7 @@
     <col width="10" customWidth="1" min="58" max="58"/>
     <col width="10" customWidth="1" min="59" max="59"/>
     <col width="10" customWidth="1" min="60" max="60"/>
+    <col width="10" customWidth="1" min="61" max="61"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38347,6 +38992,9 @@
       <c r="BH1" s="1" t="n">
         <v>20251222</v>
       </c>
+      <c r="BI1" s="1" t="n">
+        <v>20251223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -38533,6 +39181,9 @@
       <c r="BH2" t="n">
         <v>-79</v>
       </c>
+      <c r="BI2" t="n">
+        <v>-91</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38719,6 +39370,9 @@
       <c r="BH3" t="n">
         <v>60</v>
       </c>
+      <c r="BI3" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -38905,6 +39559,9 @@
       <c r="BH4" t="n">
         <v>-56</v>
       </c>
+      <c r="BI4" t="n">
+        <v>-70</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -39091,6 +39748,9 @@
       <c r="BH5" t="n">
         <v>0</v>
       </c>
+      <c r="BI5" t="n">
+        <v>-24</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -39277,6 +39937,9 @@
       <c r="BH6" t="n">
         <v>44</v>
       </c>
+      <c r="BI6" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -39463,6 +40126,9 @@
       <c r="BH7" t="n">
         <v>56</v>
       </c>
+      <c r="BI7" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -39649,6 +40315,9 @@
       <c r="BH8" t="n">
         <v>74</v>
       </c>
+      <c r="BI8" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -39835,6 +40504,9 @@
       <c r="BH9" t="n">
         <v>-76</v>
       </c>
+      <c r="BI9" t="n">
+        <v>-76</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -40021,6 +40693,9 @@
       <c r="BH10" t="n">
         <v>-29</v>
       </c>
+      <c r="BI10" t="n">
+        <v>-32</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -40207,6 +40882,9 @@
       <c r="BH11" t="n">
         <v>-38</v>
       </c>
+      <c r="BI11" t="n">
+        <v>-51</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -40393,6 +41071,9 @@
       <c r="BH12" t="n">
         <v>-41</v>
       </c>
+      <c r="BI12" t="n">
+        <v>-56</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -40579,6 +41260,9 @@
       <c r="BH13" t="n">
         <v>-27</v>
       </c>
+      <c r="BI13" t="n">
+        <v>-40</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -40765,6 +41449,9 @@
       <c r="BH14" t="n">
         <v>-68</v>
       </c>
+      <c r="BI14" t="n">
+        <v>-75</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -40951,6 +41638,9 @@
       <c r="BH15" t="n">
         <v>-52</v>
       </c>
+      <c r="BI15" t="n">
+        <v>-71</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -41137,6 +41827,9 @@
       <c r="BH16" t="n">
         <v>-50</v>
       </c>
+      <c r="BI16" t="n">
+        <v>-61</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41323,6 +42016,9 @@
       <c r="BH17" t="n">
         <v>-54</v>
       </c>
+      <c r="BI17" t="n">
+        <v>-63</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41509,6 +42205,9 @@
       <c r="BH18" t="n">
         <v>-26</v>
       </c>
+      <c r="BI18" t="n">
+        <v>-33</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -41694,6 +42393,9 @@
       </c>
       <c r="BH19" t="n">
         <v>-31</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>-65</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -733,6 +733,7 @@
     <col width="10" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -803,6 +804,9 @@
       <c r="U1" s="1" t="n">
         <v>20251223</v>
       </c>
+      <c r="V1" s="1" t="n">
+        <v>20251224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -872,6 +876,9 @@
       <c r="U2" t="n">
         <v>-7</v>
       </c>
+      <c r="V2" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -941,6 +948,9 @@
       <c r="U3" t="n">
         <v>40</v>
       </c>
+      <c r="V3" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1010,6 +1020,9 @@
       <c r="U4" t="n">
         <v>-3</v>
       </c>
+      <c r="V4" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1079,6 +1092,9 @@
       <c r="U5" t="n">
         <v>-14</v>
       </c>
+      <c r="V5" t="n">
+        <v>-17</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1148,6 +1164,9 @@
       <c r="U6" t="n">
         <v>39</v>
       </c>
+      <c r="V6" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1217,6 +1236,9 @@
       <c r="U7" t="n">
         <v>48</v>
       </c>
+      <c r="V7" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1286,6 +1308,9 @@
       <c r="U8" t="n">
         <v>45</v>
       </c>
+      <c r="V8" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1355,6 +1380,9 @@
       <c r="U9" t="n">
         <v>-32</v>
       </c>
+      <c r="V9" t="n">
+        <v>-31</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1424,6 +1452,9 @@
       <c r="U10" t="n">
         <v>-5</v>
       </c>
+      <c r="V10" t="n">
+        <v>-21</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1493,6 +1524,9 @@
       <c r="U11" t="n">
         <v>7</v>
       </c>
+      <c r="V11" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1562,6 +1596,9 @@
       <c r="U12" t="n">
         <v>4</v>
       </c>
+      <c r="V12" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1631,6 +1668,9 @@
       <c r="U13" t="n">
         <v>12</v>
       </c>
+      <c r="V13" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1700,6 +1740,9 @@
       <c r="U14" t="n">
         <v>-23</v>
       </c>
+      <c r="V14" t="n">
+        <v>-22</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1769,6 +1812,9 @@
       <c r="U15" t="n">
         <v>31</v>
       </c>
+      <c r="V15" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1838,6 +1884,9 @@
       <c r="U16" t="n">
         <v>-4</v>
       </c>
+      <c r="V16" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1907,6 +1956,9 @@
       <c r="U17" t="n">
         <v>-6</v>
       </c>
+      <c r="V17" t="n">
+        <v>-7</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1976,6 +2028,9 @@
       <c r="U18" t="n">
         <v>20</v>
       </c>
+      <c r="V18" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2043,6 +2098,9 @@
         <v>44</v>
       </c>
       <c r="U19" t="n">
+        <v>37</v>
+      </c>
+      <c r="V19" t="n">
         <v>37</v>
       </c>
     </row>
@@ -2057,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI19"/>
+  <dimension ref="A1:BJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2121,6 +2179,7 @@
     <col width="12" customWidth="1" min="59" max="59"/>
     <col width="12" customWidth="1" min="60" max="60"/>
     <col width="12" customWidth="1" min="61" max="61"/>
+    <col width="12" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2429,6 +2488,11 @@
           <t>20251223</t>
         </is>
       </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>20251224</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2618,6 +2682,9 @@
       <c r="BI2" t="n">
         <v>93</v>
       </c>
+      <c r="BJ2" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2807,6 +2874,9 @@
       <c r="BI3" t="n">
         <v>103</v>
       </c>
+      <c r="BJ3" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2996,6 +3066,9 @@
       <c r="BI4" t="n">
         <v>95</v>
       </c>
+      <c r="BJ4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3185,6 +3258,9 @@
       <c r="BI5" t="n">
         <v>99</v>
       </c>
+      <c r="BJ5" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3374,6 +3450,9 @@
       <c r="BI6" t="n">
         <v>102</v>
       </c>
+      <c r="BJ6" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3563,6 +3642,9 @@
       <c r="BI7" t="n">
         <v>102</v>
       </c>
+      <c r="BJ7" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3752,6 +3834,9 @@
       <c r="BI8" t="n">
         <v>103</v>
       </c>
+      <c r="BJ8" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3941,6 +4026,9 @@
       <c r="BI9" t="n">
         <v>89</v>
       </c>
+      <c r="BJ9" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4130,6 +4218,9 @@
       <c r="BI10" t="n">
         <v>98</v>
       </c>
+      <c r="BJ10" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4319,6 +4410,9 @@
       <c r="BI11" t="n">
         <v>96</v>
       </c>
+      <c r="BJ11" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4508,6 +4602,9 @@
       <c r="BI12" t="n">
         <v>94</v>
       </c>
+      <c r="BJ12" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4697,6 +4794,9 @@
       <c r="BI13" t="n">
         <v>95</v>
       </c>
+      <c r="BJ13" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4886,6 +4986,9 @@
       <c r="BI14" t="n">
         <v>88</v>
       </c>
+      <c r="BJ14" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5075,6 +5178,9 @@
       <c r="BI15" t="n">
         <v>96</v>
       </c>
+      <c r="BJ15" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5264,6 +5370,9 @@
       <c r="BI16" t="n">
         <v>95</v>
       </c>
+      <c r="BJ16" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5453,6 +5562,9 @@
       <c r="BI17" t="n">
         <v>94</v>
       </c>
+      <c r="BJ17" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5642,6 +5754,9 @@
       <c r="BI18" t="n">
         <v>98</v>
       </c>
+      <c r="BJ18" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5829,6 +5944,9 @@
         <v>98</v>
       </c>
       <c r="BI19" t="n">
+        <v>97</v>
+      </c>
+      <c r="BJ19" t="n">
         <v>97</v>
       </c>
     </row>
@@ -5843,7 +5961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP19"/>
+  <dimension ref="A1:AQ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5888,6 +6006,7 @@
     <col width="12" customWidth="1" min="40" max="40"/>
     <col width="12" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6101,6 +6220,11 @@
           <t>20251223</t>
         </is>
       </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>20251224</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6233,6 +6357,9 @@
       <c r="AP2" t="n">
         <v>8.25</v>
       </c>
+      <c r="AQ2" t="n">
+        <v>13.94</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6365,6 +6492,9 @@
       <c r="AP3" t="n">
         <v>-37.91</v>
       </c>
+      <c r="AQ3" t="n">
+        <v>-38.81</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6497,6 +6627,9 @@
       <c r="AP4" t="n">
         <v>3.01</v>
       </c>
+      <c r="AQ4" t="n">
+        <v>10.09</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6629,6 +6762,9 @@
       <c r="AP5" t="n">
         <v>-10.89</v>
       </c>
+      <c r="AQ5" t="n">
+        <v>-8.33</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6761,6 +6897,9 @@
       <c r="AP6" t="n">
         <v>-30.63</v>
       </c>
+      <c r="AQ6" t="n">
+        <v>-29.97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6893,6 +7032,9 @@
       <c r="AP7" t="n">
         <v>-39.7</v>
       </c>
+      <c r="AQ7" t="n">
+        <v>-39.15</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7025,6 +7167,9 @@
       <c r="AP8" t="n">
         <v>-36.3</v>
       </c>
+      <c r="AQ8" t="n">
+        <v>-33.31</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7157,6 +7302,9 @@
       <c r="AP9" t="n">
         <v>1.29</v>
       </c>
+      <c r="AQ9" t="n">
+        <v>5.98</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7289,6 +7437,9 @@
       <c r="AP10" t="n">
         <v>7.4</v>
       </c>
+      <c r="AQ10" t="n">
+        <v>9.92</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7421,6 +7572,9 @@
       <c r="AP11" t="n">
         <v>-5.18</v>
       </c>
+      <c r="AQ11" t="n">
+        <v>-4.22</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7553,6 +7707,9 @@
       <c r="AP12" t="n">
         <v>-3.18</v>
       </c>
+      <c r="AQ12" t="n">
+        <v>-2.69</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7685,6 +7842,9 @@
       <c r="AP13" t="n">
         <v>-4.19</v>
       </c>
+      <c r="AQ13" t="n">
+        <v>-6.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7817,6 +7977,9 @@
       <c r="AP14" t="n">
         <v>-2.3</v>
       </c>
+      <c r="AQ14" t="n">
+        <v>2.87</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7949,6 +8112,9 @@
       <c r="AP15" t="n">
         <v>-32.27</v>
       </c>
+      <c r="AQ15" t="n">
+        <v>-26.73</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8081,6 +8247,9 @@
       <c r="AP16" t="n">
         <v>-4.65</v>
       </c>
+      <c r="AQ16" t="n">
+        <v>-1.86</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8213,6 +8382,9 @@
       <c r="AP17" t="n">
         <v>-9.23</v>
       </c>
+      <c r="AQ17" t="n">
+        <v>-5.71</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8345,6 +8517,9 @@
       <c r="AP18" t="n">
         <v>9.41</v>
       </c>
+      <c r="AQ18" t="n">
+        <v>7.47</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8476,6 +8651,9 @@
       </c>
       <c r="AP19" t="n">
         <v>-43.21</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>-40.5</v>
       </c>
     </row>
   </sheetData>
@@ -8489,7 +8667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8513,6 +8691,7 @@
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8621,6 +8800,11 @@
           <t>20251223</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>20251224</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8690,6 +8874,9 @@
       <c r="U2" t="n">
         <v>85</v>
       </c>
+      <c r="V2" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8759,6 +8946,9 @@
       <c r="U3" t="n">
         <v>36</v>
       </c>
+      <c r="V3" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8828,6 +9018,9 @@
       <c r="U4" t="n">
         <v>38</v>
       </c>
+      <c r="V4" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8897,6 +9090,9 @@
       <c r="U5" t="n">
         <v>13</v>
       </c>
+      <c r="V5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8966,6 +9162,9 @@
       <c r="U6" t="n">
         <v>31</v>
       </c>
+      <c r="V6" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9035,6 +9234,9 @@
       <c r="U7" t="n">
         <v>20</v>
       </c>
+      <c r="V7" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9104,6 +9306,9 @@
       <c r="U8" t="n">
         <v>54</v>
       </c>
+      <c r="V8" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9173,6 +9378,9 @@
       <c r="U9" t="n">
         <v>21</v>
       </c>
+      <c r="V9" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9242,6 +9450,9 @@
       <c r="U10" t="n">
         <v>26</v>
       </c>
+      <c r="V10" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9311,6 +9522,9 @@
       <c r="U11" t="n">
         <v>9</v>
       </c>
+      <c r="V11" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9380,6 +9594,9 @@
       <c r="U12" t="n">
         <v>22</v>
       </c>
+      <c r="V12" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9449,6 +9666,9 @@
       <c r="U13" t="n">
         <v>23</v>
       </c>
+      <c r="V13" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9518,6 +9738,9 @@
       <c r="U14" t="n">
         <v>18</v>
       </c>
+      <c r="V14" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9587,6 +9810,9 @@
       <c r="U15" t="n">
         <v>24</v>
       </c>
+      <c r="V15" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9656,6 +9882,9 @@
       <c r="U16" t="n">
         <v>14</v>
       </c>
+      <c r="V16" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9725,6 +9954,9 @@
       <c r="U17" t="n">
         <v>3</v>
       </c>
+      <c r="V17" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9794,6 +10026,9 @@
       <c r="U18" t="n">
         <v>19</v>
       </c>
+      <c r="V18" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9862,6 +10097,9 @@
       </c>
       <c r="U19" t="n">
         <v>27</v>
+      </c>
+      <c r="V19" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -9875,7 +10113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB19"/>
+  <dimension ref="A1:CC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9958,6 +10196,7 @@
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
+    <col width="12" customWidth="1" min="81" max="81"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10205,6 +10444,9 @@
       <c r="CB1" s="1" t="n">
         <v>20251223</v>
       </c>
+      <c r="CC1" s="1" t="n">
+        <v>20251224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10451,6 +10693,9 @@
       <c r="CB2" t="n">
         <v>14740</v>
       </c>
+      <c r="CC2" t="n">
+        <v>14445</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10697,6 +10942,9 @@
       <c r="CB3" t="n">
         <v>58280</v>
       </c>
+      <c r="CC3" t="n">
+        <v>58685</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10943,6 +11191,9 @@
       <c r="CB4" t="n">
         <v>17600</v>
       </c>
+      <c r="CC4" t="n">
+        <v>17385</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11189,6 +11440,9 @@
       <c r="CB5" t="n">
         <v>15775</v>
       </c>
+      <c r="CC5" t="n">
+        <v>15800</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11435,6 +11689,9 @@
       <c r="CB6" t="n">
         <v>17050</v>
       </c>
+      <c r="CC6" t="n">
+        <v>17070</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11681,6 +11938,9 @@
       <c r="CB7" t="n">
         <v>19840</v>
       </c>
+      <c r="CC7" t="n">
+        <v>19880</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11927,6 +12187,9 @@
       <c r="CB8" t="n">
         <v>18875</v>
       </c>
+      <c r="CC8" t="n">
+        <v>19030</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12173,6 +12436,9 @@
       <c r="CB9" t="n">
         <v>1339</v>
       </c>
+      <c r="CC9" t="n">
+        <v>1335</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12419,6 +12685,9 @@
       <c r="CB10" t="n">
         <v>16705</v>
       </c>
+      <c r="CC10" t="n">
+        <v>16685</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12665,6 +12934,9 @@
       <c r="CB11" t="n">
         <v>5155</v>
       </c>
+      <c r="CC11" t="n">
+        <v>5145</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12911,6 +13183,9 @@
       <c r="CB12" t="n">
         <v>5515</v>
       </c>
+      <c r="CC12" t="n">
+        <v>5495</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13157,6 +13432,9 @@
       <c r="CB13" t="n">
         <v>5600</v>
       </c>
+      <c r="CC13" t="n">
+        <v>5585</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13403,6 +13681,9 @@
       <c r="CB14" t="n">
         <v>1453</v>
       </c>
+      <c r="CC14" t="n">
+        <v>1437</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13649,6 +13930,9 @@
       <c r="CB15" t="n">
         <v>18790</v>
       </c>
+      <c r="CC15" t="n">
+        <v>18565</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13895,6 +14179,9 @@
       <c r="CB16" t="n">
         <v>10400</v>
       </c>
+      <c r="CC16" t="n">
+        <v>10315</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14141,6 +14428,9 @@
       <c r="CB17" t="n">
         <v>6120</v>
       </c>
+      <c r="CC17" t="n">
+        <v>6085</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14387,6 +14677,9 @@
       <c r="CB18" t="n">
         <v>17690</v>
       </c>
+      <c r="CC18" t="n">
+        <v>17690</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14632,6 +14925,9 @@
       </c>
       <c r="CB19" t="n">
         <v>15960</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>15680</v>
       </c>
     </row>
   </sheetData>
@@ -14645,7 +14941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB19"/>
+  <dimension ref="A1:CC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14728,6 +15024,7 @@
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
+    <col width="12" customWidth="1" min="81" max="81"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14975,6 +15272,9 @@
       <c r="CB1" s="1" t="n">
         <v>20251223</v>
       </c>
+      <c r="CC1" s="1" t="n">
+        <v>20251224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15221,6 +15521,9 @@
       <c r="CB2" t="n">
         <v>14790</v>
       </c>
+      <c r="CC2" t="n">
+        <v>14620</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15467,6 +15770,9 @@
       <c r="CB3" t="n">
         <v>58685</v>
       </c>
+      <c r="CC3" t="n">
+        <v>58685</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15713,6 +16019,9 @@
       <c r="CB4" t="n">
         <v>17610</v>
       </c>
+      <c r="CC4" t="n">
+        <v>17385</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15959,6 +16268,9 @@
       <c r="CB5" t="n">
         <v>15815</v>
       </c>
+      <c r="CC5" t="n">
+        <v>15840</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16205,6 +16517,9 @@
       <c r="CB6" t="n">
         <v>17225</v>
       </c>
+      <c r="CC6" t="n">
+        <v>17175</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16451,6 +16766,9 @@
       <c r="CB7" t="n">
         <v>20010</v>
       </c>
+      <c r="CC7" t="n">
+        <v>20000</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16697,6 +17015,9 @@
       <c r="CB8" t="n">
         <v>19090</v>
       </c>
+      <c r="CC8" t="n">
+        <v>19090</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16943,6 +17264,9 @@
       <c r="CB9" t="n">
         <v>1344</v>
       </c>
+      <c r="CC9" t="n">
+        <v>1377</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17189,6 +17513,9 @@
       <c r="CB10" t="n">
         <v>16780</v>
       </c>
+      <c r="CC10" t="n">
+        <v>16685</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17435,6 +17762,9 @@
       <c r="CB11" t="n">
         <v>5170</v>
       </c>
+      <c r="CC11" t="n">
+        <v>5235</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17681,6 +18011,9 @@
       <c r="CB12" t="n">
         <v>5545</v>
       </c>
+      <c r="CC12" t="n">
+        <v>5600</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17927,6 +18260,9 @@
       <c r="CB13" t="n">
         <v>5630</v>
       </c>
+      <c r="CC13" t="n">
+        <v>5705</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18173,6 +18509,9 @@
       <c r="CB14" t="n">
         <v>1453</v>
       </c>
+      <c r="CC14" t="n">
+        <v>1485</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18419,6 +18758,9 @@
       <c r="CB15" t="n">
         <v>18875</v>
       </c>
+      <c r="CC15" t="n">
+        <v>18780</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -18665,6 +19007,9 @@
       <c r="CB16" t="n">
         <v>10400</v>
       </c>
+      <c r="CC16" t="n">
+        <v>10500</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -18911,6 +19256,9 @@
       <c r="CB17" t="n">
         <v>6135</v>
       </c>
+      <c r="CC17" t="n">
+        <v>6165</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -19157,6 +19505,9 @@
       <c r="CB18" t="n">
         <v>17835</v>
       </c>
+      <c r="CC18" t="n">
+        <v>17750</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -19402,6 +19753,9 @@
       </c>
       <c r="CB19" t="n">
         <v>15960</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>15790</v>
       </c>
     </row>
   </sheetData>
@@ -19415,7 +19769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB19"/>
+  <dimension ref="A1:CC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19498,6 +19852,7 @@
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
+    <col width="12" customWidth="1" min="81" max="81"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19745,6 +20100,9 @@
       <c r="CB1" s="1" t="n">
         <v>20251223</v>
       </c>
+      <c r="CC1" s="1" t="n">
+        <v>20251224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19991,6 +20349,9 @@
       <c r="CB2" t="n">
         <v>14425</v>
       </c>
+      <c r="CC2" t="n">
+        <v>14280</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20237,6 +20598,9 @@
       <c r="CB3" t="n">
         <v>57975</v>
       </c>
+      <c r="CC3" t="n">
+        <v>57800</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20483,6 +20847,9 @@
       <c r="CB4" t="n">
         <v>17310</v>
       </c>
+      <c r="CC4" t="n">
+        <v>17145</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20729,6 +21096,9 @@
       <c r="CB5" t="n">
         <v>15540</v>
       </c>
+      <c r="CC5" t="n">
+        <v>15535</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20975,6 +21345,9 @@
       <c r="CB6" t="n">
         <v>17005</v>
       </c>
+      <c r="CC6" t="n">
+        <v>16930</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21221,6 +21594,9 @@
       <c r="CB7" t="n">
         <v>19765</v>
       </c>
+      <c r="CC7" t="n">
+        <v>19770</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21467,6 +21843,9 @@
       <c r="CB8" t="n">
         <v>18820</v>
       </c>
+      <c r="CC8" t="n">
+        <v>18855</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21713,6 +22092,9 @@
       <c r="CB9" t="n">
         <v>1311</v>
       </c>
+      <c r="CC9" t="n">
+        <v>1325</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21959,6 +22341,9 @@
       <c r="CB10" t="n">
         <v>16475</v>
       </c>
+      <c r="CC10" t="n">
+        <v>16270</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22205,6 +22590,9 @@
       <c r="CB11" t="n">
         <v>5100</v>
       </c>
+      <c r="CC11" t="n">
+        <v>5125</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -22451,6 +22839,9 @@
       <c r="CB12" t="n">
         <v>5450</v>
       </c>
+      <c r="CC12" t="n">
+        <v>5480</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -22697,6 +23088,9 @@
       <c r="CB13" t="n">
         <v>5525</v>
       </c>
+      <c r="CC13" t="n">
+        <v>5575</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -22943,6 +23337,9 @@
       <c r="CB14" t="n">
         <v>1413</v>
       </c>
+      <c r="CC14" t="n">
+        <v>1436</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -23189,6 +23586,9 @@
       <c r="CB15" t="n">
         <v>18510</v>
       </c>
+      <c r="CC15" t="n">
+        <v>18410</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -23435,6 +23835,9 @@
       <c r="CB16" t="n">
         <v>10260</v>
       </c>
+      <c r="CC16" t="n">
+        <v>10305</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -23681,6 +24084,9 @@
       <c r="CB17" t="n">
         <v>6050</v>
       </c>
+      <c r="CC17" t="n">
+        <v>6070</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -23927,6 +24333,9 @@
       <c r="CB18" t="n">
         <v>17480</v>
       </c>
+      <c r="CC18" t="n">
+        <v>17415</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -24172,6 +24581,9 @@
       </c>
       <c r="CB19" t="n">
         <v>15645</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>15615</v>
       </c>
     </row>
   </sheetData>
@@ -24185,7 +24597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB19"/>
+  <dimension ref="A1:CC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24268,6 +24680,7 @@
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
+    <col width="12" customWidth="1" min="81" max="81"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24515,6 +24928,9 @@
       <c r="CB1" s="1" t="n">
         <v>20251223</v>
       </c>
+      <c r="CC1" s="1" t="n">
+        <v>20251224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24761,6 +25177,9 @@
       <c r="CB2" t="n">
         <v>14445</v>
       </c>
+      <c r="CC2" t="n">
+        <v>14590</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25007,6 +25426,9 @@
       <c r="CB3" t="n">
         <v>58295</v>
       </c>
+      <c r="CC3" t="n">
+        <v>57800</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25253,6 +25675,9 @@
       <c r="CB4" t="n">
         <v>17320</v>
       </c>
+      <c r="CC4" t="n">
+        <v>17225</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25499,6 +25924,9 @@
       <c r="CB5" t="n">
         <v>15570</v>
       </c>
+      <c r="CC5" t="n">
+        <v>15545</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25745,6 +26173,9 @@
       <c r="CB6" t="n">
         <v>17055</v>
       </c>
+      <c r="CC6" t="n">
+        <v>16965</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25991,6 +26422,9 @@
       <c r="CB7" t="n">
         <v>19805</v>
       </c>
+      <c r="CC7" t="n">
+        <v>19800</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26237,6 +26671,9 @@
       <c r="CB8" t="n">
         <v>18915</v>
       </c>
+      <c r="CC8" t="n">
+        <v>18885</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26483,6 +26920,9 @@
       <c r="CB9" t="n">
         <v>1326</v>
       </c>
+      <c r="CC9" t="n">
+        <v>1343</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26729,6 +27169,9 @@
       <c r="CB10" t="n">
         <v>16580</v>
       </c>
+      <c r="CC10" t="n">
+        <v>16340</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26975,6 +27418,9 @@
       <c r="CB11" t="n">
         <v>5130</v>
       </c>
+      <c r="CC11" t="n">
+        <v>5140</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27221,6 +27667,9 @@
       <c r="CB12" t="n">
         <v>5465</v>
       </c>
+      <c r="CC12" t="n">
+        <v>5510</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27467,6 +27916,9 @@
       <c r="CB13" t="n">
         <v>5545</v>
       </c>
+      <c r="CC13" t="n">
+        <v>5590</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -27713,6 +28165,9 @@
       <c r="CB14" t="n">
         <v>1427</v>
       </c>
+      <c r="CC14" t="n">
+        <v>1445</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -27959,6 +28414,9 @@
       <c r="CB15" t="n">
         <v>18565</v>
       </c>
+      <c r="CC15" t="n">
+        <v>18680</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -28205,6 +28663,9 @@
       <c r="CB16" t="n">
         <v>10295</v>
       </c>
+      <c r="CC16" t="n">
+        <v>10350</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -28451,6 +28912,9 @@
       <c r="CB17" t="n">
         <v>6080</v>
       </c>
+      <c r="CC17" t="n">
+        <v>6095</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -28697,6 +29161,9 @@
       <c r="CB18" t="n">
         <v>17510</v>
       </c>
+      <c r="CC18" t="n">
+        <v>17520</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -28942,6 +29409,9 @@
       </c>
       <c r="CB19" t="n">
         <v>15690</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>15730</v>
       </c>
     </row>
   </sheetData>
@@ -28955,7 +29425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB19"/>
+  <dimension ref="A1:CC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29038,6 +29508,7 @@
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
+    <col width="12" customWidth="1" min="81" max="81"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29285,6 +29756,9 @@
       <c r="CB1" s="1" t="n">
         <v>20251223</v>
       </c>
+      <c r="CC1" s="1" t="n">
+        <v>20251224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29531,6 +30005,9 @@
       <c r="CB2" t="n">
         <v>207562</v>
       </c>
+      <c r="CC2" t="n">
+        <v>126282</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29777,6 +30254,9 @@
       <c r="CB3" t="n">
         <v>1658116</v>
       </c>
+      <c r="CC3" t="n">
+        <v>977090</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -30023,6 +30503,9 @@
       <c r="CB4" t="n">
         <v>129753</v>
       </c>
+      <c r="CC4" t="n">
+        <v>77928</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -30269,6 +30752,9 @@
       <c r="CB5" t="n">
         <v>195913</v>
       </c>
+      <c r="CC5" t="n">
+        <v>114982</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -30515,6 +31001,9 @@
       <c r="CB6" t="n">
         <v>1232906</v>
       </c>
+      <c r="CC6" t="n">
+        <v>866013</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -30761,6 +31250,9 @@
       <c r="CB7" t="n">
         <v>1526214</v>
       </c>
+      <c r="CC7" t="n">
+        <v>894554</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -31007,6 +31499,9 @@
       <c r="CB8" t="n">
         <v>7465502</v>
       </c>
+      <c r="CC8" t="n">
+        <v>3337592</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -31253,6 +31748,9 @@
       <c r="CB9" t="n">
         <v>3138424</v>
       </c>
+      <c r="CC9" t="n">
+        <v>2568328</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31499,6 +31997,9 @@
       <c r="CB10" t="n">
         <v>700538</v>
       </c>
+      <c r="CC10" t="n">
+        <v>429184</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -31745,6 +32246,9 @@
       <c r="CB11" t="n">
         <v>229707</v>
       </c>
+      <c r="CC11" t="n">
+        <v>329991</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31991,6 +32495,9 @@
       <c r="CB12" t="n">
         <v>1296276</v>
       </c>
+      <c r="CC12" t="n">
+        <v>1502016</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32237,6 +32744,9 @@
       <c r="CB13" t="n">
         <v>3182119</v>
       </c>
+      <c r="CC13" t="n">
+        <v>4595127</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32483,6 +32993,9 @@
       <c r="CB14" t="n">
         <v>18574208</v>
       </c>
+      <c r="CC14" t="n">
+        <v>22942261</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32729,6 +33242,9 @@
       <c r="CB15" t="n">
         <v>797819</v>
       </c>
+      <c r="CC15" t="n">
+        <v>788091</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -32975,6 +33491,9 @@
       <c r="CB16" t="n">
         <v>171212</v>
       </c>
+      <c r="CC16" t="n">
+        <v>252246</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -33221,6 +33740,9 @@
       <c r="CB17" t="n">
         <v>15232</v>
       </c>
+      <c r="CC17" t="n">
+        <v>23810</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -33467,6 +33989,9 @@
       <c r="CB18" t="n">
         <v>66888</v>
       </c>
+      <c r="CC18" t="n">
+        <v>25350</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -33712,6 +34237,9 @@
       </c>
       <c r="CB19" t="n">
         <v>25083</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>13592</v>
       </c>
     </row>
   </sheetData>
@@ -33725,7 +34253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI19"/>
+  <dimension ref="A1:BJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33789,6 +34317,7 @@
     <col width="10" customWidth="1" min="59" max="59"/>
     <col width="10" customWidth="1" min="60" max="60"/>
     <col width="10" customWidth="1" min="61" max="61"/>
+    <col width="10" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33979,6 +34508,9 @@
       <c r="BI1" s="1" t="n">
         <v>20251223</v>
       </c>
+      <c r="BJ1" s="1" t="n">
+        <v>20251224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34168,6 +34700,9 @@
       <c r="BI2" t="n">
         <v>0</v>
       </c>
+      <c r="BJ2" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34357,6 +34892,9 @@
       <c r="BI3" t="n">
         <v>100</v>
       </c>
+      <c r="BJ3" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34546,6 +35084,9 @@
       <c r="BI4" t="n">
         <v>0</v>
       </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34735,6 +35276,9 @@
       <c r="BI5" t="n">
         <v>52</v>
       </c>
+      <c r="BJ5" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34924,6 +35468,9 @@
       <c r="BI6" t="n">
         <v>81</v>
       </c>
+      <c r="BJ6" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35113,6 +35660,9 @@
       <c r="BI7" t="n">
         <v>92</v>
       </c>
+      <c r="BJ7" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -35302,6 +35852,9 @@
       <c r="BI8" t="n">
         <v>100</v>
       </c>
+      <c r="BJ8" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35491,6 +36044,9 @@
       <c r="BI9" t="n">
         <v>10</v>
       </c>
+      <c r="BJ9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35680,6 +36236,9 @@
       <c r="BI10" t="n">
         <v>40</v>
       </c>
+      <c r="BJ10" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -35869,6 +36428,9 @@
       <c r="BI11" t="n">
         <v>9</v>
       </c>
+      <c r="BJ11" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -36058,6 +36620,9 @@
       <c r="BI12" t="n">
         <v>5</v>
       </c>
+      <c r="BJ12" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36247,6 +36812,9 @@
       <c r="BI13" t="n">
         <v>11</v>
       </c>
+      <c r="BJ13" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36436,6 +37004,9 @@
       <c r="BI14" t="n">
         <v>9</v>
       </c>
+      <c r="BJ14" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36625,6 +37196,9 @@
       <c r="BI15" t="n">
         <v>0</v>
       </c>
+      <c r="BJ15" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -36814,6 +37388,9 @@
       <c r="BI16" t="n">
         <v>9</v>
       </c>
+      <c r="BJ16" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37003,6 +37580,9 @@
       <c r="BI17" t="n">
         <v>8</v>
       </c>
+      <c r="BJ17" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -37192,6 +37772,9 @@
       <c r="BI18" t="n">
         <v>42</v>
       </c>
+      <c r="BJ18" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -37380,6 +37963,9 @@
       </c>
       <c r="BI19" t="n">
         <v>0</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -37393,7 +37979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37417,6 +38003,7 @@
     <col width="10" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37487,6 +38074,9 @@
       <c r="U1" s="1" t="n">
         <v>20251223</v>
       </c>
+      <c r="V1" s="1" t="n">
+        <v>20251224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37556,6 +38146,9 @@
       <c r="U2" t="n">
         <v>45</v>
       </c>
+      <c r="V2" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37625,6 +38218,9 @@
       <c r="U3" t="n">
         <v>83</v>
       </c>
+      <c r="V3" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -37694,6 +38290,9 @@
       <c r="U4" t="n">
         <v>48</v>
       </c>
+      <c r="V4" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -37763,6 +38362,9 @@
       <c r="U5" t="n">
         <v>56</v>
       </c>
+      <c r="V5" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -37832,6 +38434,9 @@
       <c r="U6" t="n">
         <v>87</v>
       </c>
+      <c r="V6" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -37901,6 +38506,9 @@
       <c r="U7" t="n">
         <v>92</v>
       </c>
+      <c r="V7" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -37970,6 +38578,9 @@
       <c r="U8" t="n">
         <v>90</v>
       </c>
+      <c r="V8" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -38039,6 +38650,9 @@
       <c r="U9" t="n">
         <v>32</v>
       </c>
+      <c r="V9" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -38108,6 +38722,9 @@
       <c r="U10" t="n">
         <v>60</v>
       </c>
+      <c r="V10" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -38177,6 +38794,9 @@
       <c r="U11" t="n">
         <v>68</v>
       </c>
+      <c r="V11" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -38246,6 +38866,9 @@
       <c r="U12" t="n">
         <v>65</v>
       </c>
+      <c r="V12" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -38315,6 +38938,9 @@
       <c r="U13" t="n">
         <v>67</v>
       </c>
+      <c r="V13" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -38384,6 +39010,9 @@
       <c r="U14" t="n">
         <v>40</v>
       </c>
+      <c r="V14" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -38453,6 +39082,9 @@
       <c r="U15" t="n">
         <v>70</v>
       </c>
+      <c r="V15" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -38522,6 +39154,9 @@
       <c r="U16" t="n">
         <v>58</v>
       </c>
+      <c r="V16" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -38591,6 +39226,9 @@
       <c r="U17" t="n">
         <v>56</v>
       </c>
+      <c r="V17" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -38660,6 +39298,9 @@
       <c r="U18" t="n">
         <v>76</v>
       </c>
+      <c r="V18" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -38728,6 +39369,9 @@
       </c>
       <c r="U19" t="n">
         <v>74</v>
+      </c>
+      <c r="V19" t="n">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -38741,7 +39385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI19"/>
+  <dimension ref="A1:BJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -38805,6 +39449,7 @@
     <col width="10" customWidth="1" min="59" max="59"/>
     <col width="10" customWidth="1" min="60" max="60"/>
     <col width="10" customWidth="1" min="61" max="61"/>
+    <col width="10" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38995,6 +39640,9 @@
       <c r="BI1" s="1" t="n">
         <v>20251223</v>
       </c>
+      <c r="BJ1" s="1" t="n">
+        <v>20251224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -39184,6 +39832,9 @@
       <c r="BI2" t="n">
         <v>-91</v>
       </c>
+      <c r="BJ2" t="n">
+        <v>-70</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -39373,6 +40024,9 @@
       <c r="BI3" t="n">
         <v>68</v>
       </c>
+      <c r="BJ3" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -39562,6 +40216,9 @@
       <c r="BI4" t="n">
         <v>-70</v>
       </c>
+      <c r="BJ4" t="n">
+        <v>-69</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -39751,6 +40408,9 @@
       <c r="BI5" t="n">
         <v>-24</v>
       </c>
+      <c r="BJ5" t="n">
+        <v>-25</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -39940,6 +40600,9 @@
       <c r="BI6" t="n">
         <v>42</v>
       </c>
+      <c r="BJ6" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -40129,6 +40792,9 @@
       <c r="BI7" t="n">
         <v>58</v>
       </c>
+      <c r="BJ7" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40318,6 +40984,9 @@
       <c r="BI8" t="n">
         <v>81</v>
       </c>
+      <c r="BJ8" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -40507,6 +41176,9 @@
       <c r="BI9" t="n">
         <v>-76</v>
       </c>
+      <c r="BJ9" t="n">
+        <v>-61</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -40696,6 +41368,9 @@
       <c r="BI10" t="n">
         <v>-32</v>
       </c>
+      <c r="BJ10" t="n">
+        <v>-49</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -40885,6 +41560,9 @@
       <c r="BI11" t="n">
         <v>-51</v>
       </c>
+      <c r="BJ11" t="n">
+        <v>-47</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -41074,6 +41752,9 @@
       <c r="BI12" t="n">
         <v>-56</v>
       </c>
+      <c r="BJ12" t="n">
+        <v>-47</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -41263,6 +41944,9 @@
       <c r="BI13" t="n">
         <v>-40</v>
       </c>
+      <c r="BJ13" t="n">
+        <v>-35</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -41452,6 +42136,9 @@
       <c r="BI14" t="n">
         <v>-75</v>
       </c>
+      <c r="BJ14" t="n">
+        <v>-61</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41641,6 +42328,9 @@
       <c r="BI15" t="n">
         <v>-71</v>
       </c>
+      <c r="BJ15" t="n">
+        <v>-57</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -41830,6 +42520,9 @@
       <c r="BI16" t="n">
         <v>-61</v>
       </c>
+      <c r="BJ16" t="n">
+        <v>-52</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42019,6 +42712,9 @@
       <c r="BI17" t="n">
         <v>-63</v>
       </c>
+      <c r="BJ17" t="n">
+        <v>-57</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42208,6 +42904,9 @@
       <c r="BI18" t="n">
         <v>-33</v>
       </c>
+      <c r="BJ18" t="n">
+        <v>-28</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42396,6 +43095,9 @@
       </c>
       <c r="BI19" t="n">
         <v>-65</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>-59</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -30006,7 +30006,7 @@
         <v>207562</v>
       </c>
       <c r="CC2" t="n">
-        <v>126282</v>
+        <v>126292</v>
       </c>
     </row>
     <row r="3">
@@ -30255,7 +30255,7 @@
         <v>1658116</v>
       </c>
       <c r="CC3" t="n">
-        <v>977090</v>
+        <v>2084301</v>
       </c>
     </row>
     <row r="4">
@@ -30504,7 +30504,7 @@
         <v>129753</v>
       </c>
       <c r="CC4" t="n">
-        <v>77928</v>
+        <v>77932</v>
       </c>
     </row>
     <row r="5">
@@ -30753,7 +30753,7 @@
         <v>195913</v>
       </c>
       <c r="CC5" t="n">
-        <v>114982</v>
+        <v>123716</v>
       </c>
     </row>
     <row r="6">
@@ -31002,7 +31002,7 @@
         <v>1232906</v>
       </c>
       <c r="CC6" t="n">
-        <v>866013</v>
+        <v>866443</v>
       </c>
     </row>
     <row r="7">
@@ -31251,7 +31251,7 @@
         <v>1526214</v>
       </c>
       <c r="CC7" t="n">
-        <v>894554</v>
+        <v>898105</v>
       </c>
     </row>
     <row r="8">
@@ -31500,7 +31500,7 @@
         <v>7465502</v>
       </c>
       <c r="CC8" t="n">
-        <v>3337592</v>
+        <v>3337808</v>
       </c>
     </row>
     <row r="9">
@@ -31749,7 +31749,7 @@
         <v>3138424</v>
       </c>
       <c r="CC9" t="n">
-        <v>2568328</v>
+        <v>2568484</v>
       </c>
     </row>
     <row r="10">
@@ -31998,7 +31998,7 @@
         <v>700538</v>
       </c>
       <c r="CC10" t="n">
-        <v>429184</v>
+        <v>429426</v>
       </c>
     </row>
     <row r="11">
@@ -32247,7 +32247,7 @@
         <v>229707</v>
       </c>
       <c r="CC11" t="n">
-        <v>329991</v>
+        <v>330207</v>
       </c>
     </row>
     <row r="12">
@@ -32496,7 +32496,7 @@
         <v>1296276</v>
       </c>
       <c r="CC12" t="n">
-        <v>1502016</v>
+        <v>1502282</v>
       </c>
     </row>
     <row r="13">
@@ -32745,7 +32745,7 @@
         <v>3182119</v>
       </c>
       <c r="CC13" t="n">
-        <v>4595127</v>
+        <v>4596690</v>
       </c>
     </row>
     <row r="14">
@@ -32994,7 +32994,7 @@
         <v>18574208</v>
       </c>
       <c r="CC14" t="n">
-        <v>22942261</v>
+        <v>22967977</v>
       </c>
     </row>
     <row r="15">
@@ -33243,7 +33243,7 @@
         <v>797819</v>
       </c>
       <c r="CC15" t="n">
-        <v>788091</v>
+        <v>788179</v>
       </c>
     </row>
     <row r="16">
@@ -33990,7 +33990,7 @@
         <v>66888</v>
       </c>
       <c r="CC18" t="n">
-        <v>25350</v>
+        <v>25360</v>
       </c>
     </row>
     <row r="19">

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -734,6 +734,7 @@
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -807,6 +808,9 @@
       <c r="V1" s="1" t="n">
         <v>20251224</v>
       </c>
+      <c r="W1" s="1" t="n">
+        <v>20251226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -879,6 +883,9 @@
       <c r="V2" t="n">
         <v>-2</v>
       </c>
+      <c r="W2" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -951,6 +958,9 @@
       <c r="V3" t="n">
         <v>32</v>
       </c>
+      <c r="W3" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1023,6 +1033,9 @@
       <c r="V4" t="n">
         <v>-8</v>
       </c>
+      <c r="W4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1095,6 +1108,9 @@
       <c r="V5" t="n">
         <v>-17</v>
       </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1167,6 +1183,9 @@
       <c r="V6" t="n">
         <v>35</v>
       </c>
+      <c r="W6" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1239,6 +1258,9 @@
       <c r="V7" t="n">
         <v>47</v>
       </c>
+      <c r="W7" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1311,6 +1333,9 @@
       <c r="V8" t="n">
         <v>43</v>
       </c>
+      <c r="W8" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1383,6 +1408,9 @@
       <c r="V9" t="n">
         <v>-31</v>
       </c>
+      <c r="W9" t="n">
+        <v>-41</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1455,6 +1483,9 @@
       <c r="V10" t="n">
         <v>-21</v>
       </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1527,6 +1558,9 @@
       <c r="V11" t="n">
         <v>7</v>
       </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1599,6 +1633,9 @@
       <c r="V12" t="n">
         <v>6</v>
       </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1671,6 +1708,9 @@
       <c r="V13" t="n">
         <v>14</v>
       </c>
+      <c r="W13" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1743,6 +1783,9 @@
       <c r="V14" t="n">
         <v>-22</v>
       </c>
+      <c r="W14" t="n">
+        <v>-32</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1815,6 +1858,9 @@
       <c r="V15" t="n">
         <v>32</v>
       </c>
+      <c r="W15" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1887,6 +1933,9 @@
       <c r="V16" t="n">
         <v>-3</v>
       </c>
+      <c r="W16" t="n">
+        <v>-11</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1959,6 +2008,9 @@
       <c r="V17" t="n">
         <v>-7</v>
       </c>
+      <c r="W17" t="n">
+        <v>-16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2031,6 +2083,9 @@
       <c r="V18" t="n">
         <v>19</v>
       </c>
+      <c r="W18" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2102,6 +2157,9 @@
       </c>
       <c r="V19" t="n">
         <v>37</v>
+      </c>
+      <c r="W19" t="n">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2115,7 +2173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ19"/>
+  <dimension ref="A1:BK19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2180,6 +2238,7 @@
     <col width="12" customWidth="1" min="60" max="60"/>
     <col width="12" customWidth="1" min="61" max="61"/>
     <col width="12" customWidth="1" min="62" max="62"/>
+    <col width="12" customWidth="1" min="63" max="63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2493,6 +2552,11 @@
           <t>20251224</t>
         </is>
       </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>20251226</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2685,6 +2749,9 @@
       <c r="BJ2" t="n">
         <v>94</v>
       </c>
+      <c r="BK2" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2877,6 +2944,9 @@
       <c r="BJ3" t="n">
         <v>102</v>
       </c>
+      <c r="BK3" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3069,6 +3139,9 @@
       <c r="BJ4" t="n">
         <v>95</v>
       </c>
+      <c r="BK4" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3261,6 +3334,9 @@
       <c r="BJ5" t="n">
         <v>99</v>
       </c>
+      <c r="BK5" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3453,6 +3529,9 @@
       <c r="BJ6" t="n">
         <v>101</v>
       </c>
+      <c r="BK6" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3645,6 +3724,9 @@
       <c r="BJ7" t="n">
         <v>102</v>
       </c>
+      <c r="BK7" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3837,6 +3919,9 @@
       <c r="BJ8" t="n">
         <v>103</v>
       </c>
+      <c r="BK8" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4029,6 +4114,9 @@
       <c r="BJ9" t="n">
         <v>90</v>
       </c>
+      <c r="BK9" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4221,6 +4309,9 @@
       <c r="BJ10" t="n">
         <v>97</v>
       </c>
+      <c r="BK10" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4413,6 +4504,9 @@
       <c r="BJ11" t="n">
         <v>96</v>
       </c>
+      <c r="BK11" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4605,6 +4699,9 @@
       <c r="BJ12" t="n">
         <v>95</v>
       </c>
+      <c r="BK12" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4797,6 +4894,9 @@
       <c r="BJ13" t="n">
         <v>96</v>
       </c>
+      <c r="BK13" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4989,6 +5089,9 @@
       <c r="BJ14" t="n">
         <v>89</v>
       </c>
+      <c r="BK14" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5181,6 +5284,9 @@
       <c r="BJ15" t="n">
         <v>96</v>
       </c>
+      <c r="BK15" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5373,6 +5479,9 @@
       <c r="BJ16" t="n">
         <v>95</v>
       </c>
+      <c r="BK16" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5565,6 +5674,9 @@
       <c r="BJ17" t="n">
         <v>95</v>
       </c>
+      <c r="BK17" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5757,6 +5869,9 @@
       <c r="BJ18" t="n">
         <v>98</v>
       </c>
+      <c r="BK18" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5948,6 +6063,9 @@
       </c>
       <c r="BJ19" t="n">
         <v>97</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -5961,7 +6079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ19"/>
+  <dimension ref="A1:AR19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6007,6 +6125,7 @@
     <col width="12" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="12" customWidth="1" min="43" max="43"/>
+    <col width="12" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6225,6 +6344,11 @@
           <t>20251224</t>
         </is>
       </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>20251226</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6360,6 +6484,9 @@
       <c r="AQ2" t="n">
         <v>13.94</v>
       </c>
+      <c r="AR2" t="n">
+        <v>15.38</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6495,6 +6622,9 @@
       <c r="AQ3" t="n">
         <v>-38.81</v>
       </c>
+      <c r="AR3" t="n">
+        <v>-30.02</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6630,6 +6760,9 @@
       <c r="AQ4" t="n">
         <v>10.09</v>
       </c>
+      <c r="AR4" t="n">
+        <v>12.89</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6765,6 +6898,9 @@
       <c r="AQ5" t="n">
         <v>-8.33</v>
       </c>
+      <c r="AR5" t="n">
+        <v>-7.01</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6900,6 +7036,9 @@
       <c r="AQ6" t="n">
         <v>-29.97</v>
       </c>
+      <c r="AR6" t="n">
+        <v>-22.11</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7035,6 +7174,9 @@
       <c r="AQ7" t="n">
         <v>-39.15</v>
       </c>
+      <c r="AR7" t="n">
+        <v>-29.72</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7170,6 +7312,9 @@
       <c r="AQ8" t="n">
         <v>-33.31</v>
       </c>
+      <c r="AR8" t="n">
+        <v>-21.24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7305,6 +7450,9 @@
       <c r="AQ9" t="n">
         <v>5.98</v>
       </c>
+      <c r="AR9" t="n">
+        <v>12.29</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7440,6 +7588,9 @@
       <c r="AQ10" t="n">
         <v>9.92</v>
       </c>
+      <c r="AR10" t="n">
+        <v>8.720000000000001</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7575,6 +7726,9 @@
       <c r="AQ11" t="n">
         <v>-4.22</v>
       </c>
+      <c r="AR11" t="n">
+        <v>-3.13</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7710,6 +7864,9 @@
       <c r="AQ12" t="n">
         <v>-2.69</v>
       </c>
+      <c r="AR12" t="n">
+        <v>-1.83</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7845,6 +8002,9 @@
       <c r="AQ13" t="n">
         <v>-6.2</v>
       </c>
+      <c r="AR13" t="n">
+        <v>-8.07</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7980,6 +8140,9 @@
       <c r="AQ14" t="n">
         <v>2.87</v>
       </c>
+      <c r="AR14" t="n">
+        <v>9.380000000000001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8115,6 +8278,9 @@
       <c r="AQ15" t="n">
         <v>-26.73</v>
       </c>
+      <c r="AR15" t="n">
+        <v>-24</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8250,6 +8416,9 @@
       <c r="AQ16" t="n">
         <v>-1.86</v>
       </c>
+      <c r="AR16" t="n">
+        <v>1.94</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8385,6 +8554,9 @@
       <c r="AQ17" t="n">
         <v>-5.71</v>
       </c>
+      <c r="AR17" t="n">
+        <v>-0.84</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8520,6 +8692,9 @@
       <c r="AQ18" t="n">
         <v>7.47</v>
       </c>
+      <c r="AR18" t="n">
+        <v>3.33</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8654,6 +8829,9 @@
       </c>
       <c r="AQ19" t="n">
         <v>-40.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-39.13</v>
       </c>
     </row>
   </sheetData>
@@ -8667,7 +8845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8692,6 +8870,7 @@
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8805,6 +8984,11 @@
           <t>20251224</t>
         </is>
       </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>20251226</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8877,6 +9061,9 @@
       <c r="V2" t="n">
         <v>51</v>
       </c>
+      <c r="W2" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8949,6 +9136,9 @@
       <c r="V3" t="n">
         <v>21</v>
       </c>
+      <c r="W3" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9021,6 +9211,9 @@
       <c r="V4" t="n">
         <v>23</v>
       </c>
+      <c r="W4" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9093,6 +9286,9 @@
       <c r="V5" t="n">
         <v>8</v>
       </c>
+      <c r="W5" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9165,6 +9361,9 @@
       <c r="V6" t="n">
         <v>22</v>
       </c>
+      <c r="W6" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9237,6 +9436,9 @@
       <c r="V7" t="n">
         <v>12</v>
       </c>
+      <c r="W7" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9309,6 +9511,9 @@
       <c r="V8" t="n">
         <v>24</v>
       </c>
+      <c r="W8" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9381,6 +9586,9 @@
       <c r="V9" t="n">
         <v>17</v>
       </c>
+      <c r="W9" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9453,6 +9661,9 @@
       <c r="V10" t="n">
         <v>16</v>
       </c>
+      <c r="W10" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9525,6 +9736,9 @@
       <c r="V11" t="n">
         <v>13</v>
       </c>
+      <c r="W11" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9597,6 +9811,9 @@
       <c r="V12" t="n">
         <v>25</v>
       </c>
+      <c r="W12" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9669,6 +9886,9 @@
       <c r="V13" t="n">
         <v>32</v>
       </c>
+      <c r="W13" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9741,6 +9961,9 @@
       <c r="V14" t="n">
         <v>22</v>
       </c>
+      <c r="W14" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9813,6 +10036,9 @@
       <c r="V15" t="n">
         <v>24</v>
       </c>
+      <c r="W15" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9885,6 +10111,9 @@
       <c r="V16" t="n">
         <v>20</v>
       </c>
+      <c r="W16" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9957,6 +10186,9 @@
       <c r="V17" t="n">
         <v>5</v>
       </c>
+      <c r="W17" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10029,6 +10261,9 @@
       <c r="V18" t="n">
         <v>7</v>
       </c>
+      <c r="W18" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10100,6 +10335,9 @@
       </c>
       <c r="V19" t="n">
         <v>15</v>
+      </c>
+      <c r="W19" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -10113,7 +10351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC19"/>
+  <dimension ref="A1:CD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10197,6 +10435,7 @@
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
+    <col width="12" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10447,6 +10686,9 @@
       <c r="CC1" s="1" t="n">
         <v>20251224</v>
       </c>
+      <c r="CD1" s="1" t="n">
+        <v>20251226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10696,6 +10938,9 @@
       <c r="CC2" t="n">
         <v>14445</v>
       </c>
+      <c r="CD2" t="n">
+        <v>14785</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10945,6 +11190,9 @@
       <c r="CC3" t="n">
         <v>58685</v>
       </c>
+      <c r="CD3" t="n">
+        <v>58250</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11194,6 +11442,9 @@
       <c r="CC4" t="n">
         <v>17385</v>
       </c>
+      <c r="CD4" t="n">
+        <v>17340</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11443,6 +11694,9 @@
       <c r="CC5" t="n">
         <v>15800</v>
       </c>
+      <c r="CD5" t="n">
+        <v>15650</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11692,6 +11946,9 @@
       <c r="CC6" t="n">
         <v>17070</v>
       </c>
+      <c r="CD6" t="n">
+        <v>17055</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11941,6 +12198,9 @@
       <c r="CC7" t="n">
         <v>19880</v>
       </c>
+      <c r="CD7" t="n">
+        <v>19990</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12190,6 +12450,9 @@
       <c r="CC8" t="n">
         <v>19030</v>
       </c>
+      <c r="CD8" t="n">
+        <v>19035</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12439,6 +12702,9 @@
       <c r="CC9" t="n">
         <v>1335</v>
       </c>
+      <c r="CD9" t="n">
+        <v>1345</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12688,6 +12954,9 @@
       <c r="CC10" t="n">
         <v>16685</v>
       </c>
+      <c r="CD10" t="n">
+        <v>16375</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12937,6 +13206,9 @@
       <c r="CC11" t="n">
         <v>5145</v>
       </c>
+      <c r="CD11" t="n">
+        <v>5145</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13186,6 +13458,9 @@
       <c r="CC12" t="n">
         <v>5495</v>
       </c>
+      <c r="CD12" t="n">
+        <v>5540</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13435,6 +13710,9 @@
       <c r="CC13" t="n">
         <v>5585</v>
       </c>
+      <c r="CD13" t="n">
+        <v>5635</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13684,6 +13962,9 @@
       <c r="CC14" t="n">
         <v>1437</v>
       </c>
+      <c r="CD14" t="n">
+        <v>1444</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13933,6 +14214,9 @@
       <c r="CC15" t="n">
         <v>18565</v>
       </c>
+      <c r="CD15" t="n">
+        <v>18775</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14182,6 +14466,9 @@
       <c r="CC16" t="n">
         <v>10315</v>
       </c>
+      <c r="CD16" t="n">
+        <v>10335</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14431,6 +14718,9 @@
       <c r="CC17" t="n">
         <v>6085</v>
       </c>
+      <c r="CD17" t="n">
+        <v>6070</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14680,6 +14970,9 @@
       <c r="CC18" t="n">
         <v>17690</v>
       </c>
+      <c r="CD18" t="n">
+        <v>17605</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14928,6 +15221,9 @@
       </c>
       <c r="CC19" t="n">
         <v>15680</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>15755</v>
       </c>
     </row>
   </sheetData>
@@ -14941,7 +15237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC19"/>
+  <dimension ref="A1:CD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15025,6 +15321,7 @@
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
+    <col width="12" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15275,6 +15572,9 @@
       <c r="CC1" s="1" t="n">
         <v>20251224</v>
       </c>
+      <c r="CD1" s="1" t="n">
+        <v>20251226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15524,6 +15824,9 @@
       <c r="CC2" t="n">
         <v>14620</v>
       </c>
+      <c r="CD2" t="n">
+        <v>15162</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15773,6 +16076,9 @@
       <c r="CC3" t="n">
         <v>58685</v>
       </c>
+      <c r="CD3" t="n">
+        <v>59650</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16022,6 +16328,9 @@
       <c r="CC4" t="n">
         <v>17385</v>
       </c>
+      <c r="CD4" t="n">
+        <v>17610</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16271,6 +16580,9 @@
       <c r="CC5" t="n">
         <v>15840</v>
       </c>
+      <c r="CD5" t="n">
+        <v>15980</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16520,6 +16832,9 @@
       <c r="CC6" t="n">
         <v>17175</v>
       </c>
+      <c r="CD6" t="n">
+        <v>17500</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16769,6 +17084,9 @@
       <c r="CC7" t="n">
         <v>20000</v>
       </c>
+      <c r="CD7" t="n">
+        <v>20475</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17018,6 +17336,9 @@
       <c r="CC8" t="n">
         <v>19090</v>
       </c>
+      <c r="CD8" t="n">
+        <v>19570</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17267,6 +17588,9 @@
       <c r="CC9" t="n">
         <v>1377</v>
       </c>
+      <c r="CD9" t="n">
+        <v>1355</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17516,6 +17840,9 @@
       <c r="CC10" t="n">
         <v>16685</v>
       </c>
+      <c r="CD10" t="n">
+        <v>16840</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17765,6 +18092,9 @@
       <c r="CC11" t="n">
         <v>5235</v>
       </c>
+      <c r="CD11" t="n">
+        <v>5220</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -18014,6 +18344,9 @@
       <c r="CC12" t="n">
         <v>5600</v>
       </c>
+      <c r="CD12" t="n">
+        <v>5595</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -18263,6 +18596,9 @@
       <c r="CC13" t="n">
         <v>5705</v>
       </c>
+      <c r="CD13" t="n">
+        <v>5695</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18512,6 +18848,9 @@
       <c r="CC14" t="n">
         <v>1485</v>
       </c>
+      <c r="CD14" t="n">
+        <v>1467</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18761,6 +19100,9 @@
       <c r="CC15" t="n">
         <v>18780</v>
       </c>
+      <c r="CD15" t="n">
+        <v>19250</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -19010,6 +19352,9 @@
       <c r="CC16" t="n">
         <v>10500</v>
       </c>
+      <c r="CD16" t="n">
+        <v>10465</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -19259,6 +19604,9 @@
       <c r="CC17" t="n">
         <v>6165</v>
       </c>
+      <c r="CD17" t="n">
+        <v>6135</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -19508,6 +19856,9 @@
       <c r="CC18" t="n">
         <v>17750</v>
       </c>
+      <c r="CD18" t="n">
+        <v>17985</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -19756,6 +20107,9 @@
       </c>
       <c r="CC19" t="n">
         <v>15790</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>15945</v>
       </c>
     </row>
   </sheetData>
@@ -19769,7 +20123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC19"/>
+  <dimension ref="A1:CD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19853,6 +20207,7 @@
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
+    <col width="12" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20103,6 +20458,9 @@
       <c r="CC1" s="1" t="n">
         <v>20251224</v>
       </c>
+      <c r="CD1" s="1" t="n">
+        <v>20251226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20352,6 +20710,9 @@
       <c r="CC2" t="n">
         <v>14280</v>
       </c>
+      <c r="CD2" t="n">
+        <v>14480</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20601,6 +20962,9 @@
       <c r="CC3" t="n">
         <v>57800</v>
       </c>
+      <c r="CD3" t="n">
+        <v>58240</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20850,6 +21214,9 @@
       <c r="CC4" t="n">
         <v>17145</v>
       </c>
+      <c r="CD4" t="n">
+        <v>17205</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21099,6 +21466,9 @@
       <c r="CC5" t="n">
         <v>15535</v>
       </c>
+      <c r="CD5" t="n">
+        <v>15600</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21348,6 +21718,9 @@
       <c r="CC6" t="n">
         <v>16930</v>
       </c>
+      <c r="CD6" t="n">
+        <v>17035</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21597,6 +21970,9 @@
       <c r="CC7" t="n">
         <v>19770</v>
       </c>
+      <c r="CD7" t="n">
+        <v>19975</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21846,6 +22222,9 @@
       <c r="CC8" t="n">
         <v>18855</v>
       </c>
+      <c r="CD8" t="n">
+        <v>19010</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22095,6 +22474,9 @@
       <c r="CC9" t="n">
         <v>1325</v>
       </c>
+      <c r="CD9" t="n">
+        <v>1295</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22344,6 +22726,9 @@
       <c r="CC10" t="n">
         <v>16270</v>
       </c>
+      <c r="CD10" t="n">
+        <v>16340</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22593,6 +22978,9 @@
       <c r="CC11" t="n">
         <v>5125</v>
       </c>
+      <c r="CD11" t="n">
+        <v>5060</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -22842,6 +23230,9 @@
       <c r="CC12" t="n">
         <v>5480</v>
       </c>
+      <c r="CD12" t="n">
+        <v>5190</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -23091,6 +23482,9 @@
       <c r="CC13" t="n">
         <v>5575</v>
       </c>
+      <c r="CD13" t="n">
+        <v>5490</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -23340,6 +23734,9 @@
       <c r="CC14" t="n">
         <v>1436</v>
       </c>
+      <c r="CD14" t="n">
+        <v>1386</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -23589,6 +23986,9 @@
       <c r="CC15" t="n">
         <v>18410</v>
       </c>
+      <c r="CD15" t="n">
+        <v>18570</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -23838,6 +24238,9 @@
       <c r="CC16" t="n">
         <v>10305</v>
       </c>
+      <c r="CD16" t="n">
+        <v>10165</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24087,6 +24490,9 @@
       <c r="CC17" t="n">
         <v>6070</v>
       </c>
+      <c r="CD17" t="n">
+        <v>5960</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24336,6 +24742,9 @@
       <c r="CC18" t="n">
         <v>17415</v>
       </c>
+      <c r="CD18" t="n">
+        <v>17520</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -24584,6 +24993,9 @@
       </c>
       <c r="CC19" t="n">
         <v>15615</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>15630</v>
       </c>
     </row>
   </sheetData>
@@ -24597,7 +25009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC19"/>
+  <dimension ref="A1:CD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24681,6 +25093,7 @@
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
+    <col width="12" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24931,6 +25344,9 @@
       <c r="CC1" s="1" t="n">
         <v>20251224</v>
       </c>
+      <c r="CD1" s="1" t="n">
+        <v>20251226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25180,6 +25596,9 @@
       <c r="CC2" t="n">
         <v>14590</v>
       </c>
+      <c r="CD2" t="n">
+        <v>15130</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25429,6 +25848,9 @@
       <c r="CC3" t="n">
         <v>57800</v>
       </c>
+      <c r="CD3" t="n">
+        <v>59525</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25678,6 +26100,9 @@
       <c r="CC4" t="n">
         <v>17225</v>
       </c>
+      <c r="CD4" t="n">
+        <v>17530</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25927,6 +26352,9 @@
       <c r="CC5" t="n">
         <v>15545</v>
       </c>
+      <c r="CD5" t="n">
+        <v>15860</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26176,6 +26604,9 @@
       <c r="CC6" t="n">
         <v>16965</v>
       </c>
+      <c r="CD6" t="n">
+        <v>17465</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26425,6 +26856,9 @@
       <c r="CC7" t="n">
         <v>19800</v>
       </c>
+      <c r="CD7" t="n">
+        <v>20375</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26674,6 +27108,9 @@
       <c r="CC8" t="n">
         <v>18885</v>
       </c>
+      <c r="CD8" t="n">
+        <v>19420</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26923,6 +27360,9 @@
       <c r="CC9" t="n">
         <v>1343</v>
       </c>
+      <c r="CD9" t="n">
+        <v>1297</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27172,6 +27612,9 @@
       <c r="CC10" t="n">
         <v>16340</v>
       </c>
+      <c r="CD10" t="n">
+        <v>16750</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27421,6 +27864,9 @@
       <c r="CC11" t="n">
         <v>5140</v>
       </c>
+      <c r="CD11" t="n">
+        <v>5095</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27670,6 +28116,9 @@
       <c r="CC12" t="n">
         <v>5510</v>
       </c>
+      <c r="CD12" t="n">
+        <v>5450</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27919,6 +28368,9 @@
       <c r="CC13" t="n">
         <v>5590</v>
       </c>
+      <c r="CD13" t="n">
+        <v>5535</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -28168,6 +28620,9 @@
       <c r="CC14" t="n">
         <v>1445</v>
       </c>
+      <c r="CD14" t="n">
+        <v>1397</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -28417,6 +28872,9 @@
       <c r="CC15" t="n">
         <v>18680</v>
       </c>
+      <c r="CD15" t="n">
+        <v>19245</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -28666,6 +29124,9 @@
       <c r="CC16" t="n">
         <v>10350</v>
       </c>
+      <c r="CD16" t="n">
+        <v>10225</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -28915,6 +29376,9 @@
       <c r="CC17" t="n">
         <v>6095</v>
       </c>
+      <c r="CD17" t="n">
+        <v>5995</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -29164,6 +29628,9 @@
       <c r="CC18" t="n">
         <v>17520</v>
       </c>
+      <c r="CD18" t="n">
+        <v>17805</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -29412,6 +29879,9 @@
       </c>
       <c r="CC19" t="n">
         <v>15730</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>15900</v>
       </c>
     </row>
   </sheetData>
@@ -29425,7 +29895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC19"/>
+  <dimension ref="A1:CD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29509,6 +29979,7 @@
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
+    <col width="12" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29759,6 +30230,9 @@
       <c r="CC1" s="1" t="n">
         <v>20251224</v>
       </c>
+      <c r="CD1" s="1" t="n">
+        <v>20251226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30008,6 +30482,9 @@
       <c r="CC2" t="n">
         <v>126292</v>
       </c>
+      <c r="CD2" t="n">
+        <v>188645</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -30257,6 +30734,9 @@
       <c r="CC3" t="n">
         <v>2084301</v>
       </c>
+      <c r="CD3" t="n">
+        <v>2375994</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -30506,6 +30986,9 @@
       <c r="CC4" t="n">
         <v>77932</v>
       </c>
+      <c r="CD4" t="n">
+        <v>308802</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -30755,6 +31238,9 @@
       <c r="CC5" t="n">
         <v>123716</v>
       </c>
+      <c r="CD5" t="n">
+        <v>254042</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -31004,6 +31490,9 @@
       <c r="CC6" t="n">
         <v>866443</v>
       </c>
+      <c r="CD6" t="n">
+        <v>2016126</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -31253,6 +31742,9 @@
       <c r="CC7" t="n">
         <v>898105</v>
       </c>
+      <c r="CD7" t="n">
+        <v>6537875</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -31502,6 +31994,9 @@
       <c r="CC8" t="n">
         <v>3337808</v>
       </c>
+      <c r="CD8" t="n">
+        <v>10854985</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -31751,6 +32246,9 @@
       <c r="CC9" t="n">
         <v>2568484</v>
       </c>
+      <c r="CD9" t="n">
+        <v>2818252</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -32000,6 +32498,9 @@
       <c r="CC10" t="n">
         <v>429426</v>
       </c>
+      <c r="CD10" t="n">
+        <v>1039481</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -32249,6 +32750,9 @@
       <c r="CC11" t="n">
         <v>330207</v>
       </c>
+      <c r="CD11" t="n">
+        <v>471874</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32498,6 +33002,9 @@
       <c r="CC12" t="n">
         <v>1502282</v>
       </c>
+      <c r="CD12" t="n">
+        <v>1265309</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32747,6 +33254,9 @@
       <c r="CC13" t="n">
         <v>4596690</v>
       </c>
+      <c r="CD13" t="n">
+        <v>3771450</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32996,6 +33506,9 @@
       <c r="CC14" t="n">
         <v>22967977</v>
       </c>
+      <c r="CD14" t="n">
+        <v>22679446</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -33245,6 +33758,9 @@
       <c r="CC15" t="n">
         <v>788179</v>
       </c>
+      <c r="CD15" t="n">
+        <v>2682529</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -33494,6 +34010,9 @@
       <c r="CC16" t="n">
         <v>252246</v>
       </c>
+      <c r="CD16" t="n">
+        <v>326492</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -33743,6 +34262,9 @@
       <c r="CC17" t="n">
         <v>23810</v>
       </c>
+      <c r="CD17" t="n">
+        <v>40292</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -33992,6 +34514,9 @@
       <c r="CC18" t="n">
         <v>25360</v>
       </c>
+      <c r="CD18" t="n">
+        <v>54426</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -34240,6 +34765,9 @@
       </c>
       <c r="CC19" t="n">
         <v>13592</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>27530</v>
       </c>
     </row>
   </sheetData>
@@ -34253,7 +34781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ19"/>
+  <dimension ref="A1:BK19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34318,6 +34846,7 @@
     <col width="10" customWidth="1" min="60" max="60"/>
     <col width="10" customWidth="1" min="61" max="61"/>
     <col width="10" customWidth="1" min="62" max="62"/>
+    <col width="10" customWidth="1" min="63" max="63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34511,6 +35040,9 @@
       <c r="BJ1" s="1" t="n">
         <v>20251224</v>
       </c>
+      <c r="BK1" s="1" t="n">
+        <v>20251226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34703,6 +35235,9 @@
       <c r="BJ2" t="n">
         <v>7</v>
       </c>
+      <c r="BK2" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34895,6 +35430,9 @@
       <c r="BJ3" t="n">
         <v>88</v>
       </c>
+      <c r="BK3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -35087,6 +35625,9 @@
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
+      <c r="BK4" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -35279,6 +35820,9 @@
       <c r="BJ5" t="n">
         <v>51</v>
       </c>
+      <c r="BK5" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -35471,6 +36015,9 @@
       <c r="BJ6" t="n">
         <v>74</v>
       </c>
+      <c r="BK6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35663,6 +36210,9 @@
       <c r="BJ7" t="n">
         <v>91</v>
       </c>
+      <c r="BK7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -35855,6 +36405,9 @@
       <c r="BJ8" t="n">
         <v>98</v>
       </c>
+      <c r="BK8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -36047,6 +36600,9 @@
       <c r="BJ9" t="n">
         <v>15</v>
       </c>
+      <c r="BK9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -36239,6 +36795,9 @@
       <c r="BJ10" t="n">
         <v>25</v>
       </c>
+      <c r="BK10" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -36431,6 +36990,9 @@
       <c r="BJ11" t="n">
         <v>10</v>
       </c>
+      <c r="BK11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -36623,6 +37185,9 @@
       <c r="BJ12" t="n">
         <v>10</v>
       </c>
+      <c r="BK12" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36815,6 +37380,9 @@
       <c r="BJ13" t="n">
         <v>16</v>
       </c>
+      <c r="BK13" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37007,6 +37575,9 @@
       <c r="BJ14" t="n">
         <v>13</v>
       </c>
+      <c r="BK14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37199,6 +37770,9 @@
       <c r="BJ15" t="n">
         <v>6</v>
       </c>
+      <c r="BK15" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -37391,6 +37965,9 @@
       <c r="BJ16" t="n">
         <v>13</v>
       </c>
+      <c r="BK16" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37583,6 +38160,9 @@
       <c r="BJ17" t="n">
         <v>10</v>
       </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -37775,6 +38355,9 @@
       <c r="BJ18" t="n">
         <v>43</v>
       </c>
+      <c r="BK18" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -37966,6 +38549,9 @@
       </c>
       <c r="BJ19" t="n">
         <v>4</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -37979,7 +38565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -38004,6 +38590,7 @@
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38077,6 +38664,9 @@
       <c r="V1" s="1" t="n">
         <v>20251224</v>
       </c>
+      <c r="W1" s="1" t="n">
+        <v>20251226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -38149,6 +38739,9 @@
       <c r="V2" t="n">
         <v>49</v>
       </c>
+      <c r="W2" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38221,6 +38814,9 @@
       <c r="V3" t="n">
         <v>80</v>
       </c>
+      <c r="W3" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -38293,6 +38889,9 @@
       <c r="V4" t="n">
         <v>46</v>
       </c>
+      <c r="W4" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -38365,6 +38964,9 @@
       <c r="V5" t="n">
         <v>55</v>
       </c>
+      <c r="W5" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -38437,6 +39039,9 @@
       <c r="V6" t="n">
         <v>85</v>
       </c>
+      <c r="W6" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -38509,6 +39114,9 @@
       <c r="V7" t="n">
         <v>92</v>
       </c>
+      <c r="W7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -38581,6 +39189,9 @@
       <c r="V8" t="n">
         <v>89</v>
       </c>
+      <c r="W8" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -38653,6 +39264,9 @@
       <c r="V9" t="n">
         <v>34</v>
       </c>
+      <c r="W9" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -38725,6 +39339,9 @@
       <c r="V10" t="n">
         <v>53</v>
       </c>
+      <c r="W10" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -38797,6 +39414,9 @@
       <c r="V11" t="n">
         <v>68</v>
       </c>
+      <c r="W11" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -38869,6 +39489,9 @@
       <c r="V12" t="n">
         <v>67</v>
       </c>
+      <c r="W12" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -38941,6 +39564,9 @@
       <c r="V13" t="n">
         <v>69</v>
       </c>
+      <c r="W13" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39013,6 +39639,9 @@
       <c r="V14" t="n">
         <v>41</v>
       </c>
+      <c r="W14" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39085,6 +39714,9 @@
       <c r="V15" t="n">
         <v>72</v>
       </c>
+      <c r="W15" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -39157,6 +39789,9 @@
       <c r="V16" t="n">
         <v>59</v>
       </c>
+      <c r="W16" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -39229,6 +39864,9 @@
       <c r="V17" t="n">
         <v>57</v>
       </c>
+      <c r="W17" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -39301,6 +39939,9 @@
       <c r="V18" t="n">
         <v>76</v>
       </c>
+      <c r="W18" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -39372,6 +40013,9 @@
       </c>
       <c r="V19" t="n">
         <v>75</v>
+      </c>
+      <c r="W19" t="n">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -39385,7 +40029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ19"/>
+  <dimension ref="A1:BK19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -39450,6 +40094,7 @@
     <col width="10" customWidth="1" min="60" max="60"/>
     <col width="10" customWidth="1" min="61" max="61"/>
     <col width="10" customWidth="1" min="62" max="62"/>
+    <col width="10" customWidth="1" min="63" max="63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39643,6 +40288,9 @@
       <c r="BJ1" s="1" t="n">
         <v>20251224</v>
       </c>
+      <c r="BK1" s="1" t="n">
+        <v>20251226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -39835,6 +40483,9 @@
       <c r="BJ2" t="n">
         <v>-70</v>
       </c>
+      <c r="BK2" t="n">
+        <v>-24</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40027,6 +40678,9 @@
       <c r="BJ3" t="n">
         <v>44</v>
       </c>
+      <c r="BK3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -40219,6 +40873,9 @@
       <c r="BJ4" t="n">
         <v>-69</v>
       </c>
+      <c r="BK4" t="n">
+        <v>-43</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -40411,6 +41068,9 @@
       <c r="BJ5" t="n">
         <v>-25</v>
       </c>
+      <c r="BK5" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -40603,6 +41263,9 @@
       <c r="BJ6" t="n">
         <v>25</v>
       </c>
+      <c r="BK6" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -40795,6 +41458,9 @@
       <c r="BJ7" t="n">
         <v>52</v>
       </c>
+      <c r="BK7" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40987,6 +41653,9 @@
       <c r="BJ8" t="n">
         <v>70</v>
       </c>
+      <c r="BK8" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -41179,6 +41848,9 @@
       <c r="BJ9" t="n">
         <v>-61</v>
       </c>
+      <c r="BK9" t="n">
+        <v>-72</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -41371,6 +42043,9 @@
       <c r="BJ10" t="n">
         <v>-49</v>
       </c>
+      <c r="BK10" t="n">
+        <v>-11</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -41563,6 +42238,9 @@
       <c r="BJ11" t="n">
         <v>-47</v>
       </c>
+      <c r="BK11" t="n">
+        <v>-55</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -41755,6 +42433,9 @@
       <c r="BJ12" t="n">
         <v>-47</v>
       </c>
+      <c r="BK12" t="n">
+        <v>-55</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -41947,6 +42628,9 @@
       <c r="BJ13" t="n">
         <v>-35</v>
       </c>
+      <c r="BK13" t="n">
+        <v>-45</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -42139,6 +42823,9 @@
       <c r="BJ14" t="n">
         <v>-61</v>
       </c>
+      <c r="BK14" t="n">
+        <v>-70</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42331,6 +43018,9 @@
       <c r="BJ15" t="n">
         <v>-57</v>
       </c>
+      <c r="BK15" t="n">
+        <v>-11</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -42523,6 +43213,9 @@
       <c r="BJ16" t="n">
         <v>-52</v>
       </c>
+      <c r="BK16" t="n">
+        <v>-61</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42715,6 +43408,9 @@
       <c r="BJ17" t="n">
         <v>-57</v>
       </c>
+      <c r="BK17" t="n">
+        <v>-68</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42907,6 +43603,9 @@
       <c r="BJ18" t="n">
         <v>-28</v>
       </c>
+      <c r="BK18" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43098,6 +43797,9 @@
       </c>
       <c r="BJ19" t="n">
         <v>-59</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>-37</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -30483,7 +30483,7 @@
         <v>126292</v>
       </c>
       <c r="CD2" t="n">
-        <v>188645</v>
+        <v>188646</v>
       </c>
     </row>
     <row r="3">
@@ -30735,7 +30735,7 @@
         <v>2084301</v>
       </c>
       <c r="CD3" t="n">
-        <v>2375994</v>
+        <v>2378510</v>
       </c>
     </row>
     <row r="4">
@@ -30987,7 +30987,7 @@
         <v>77932</v>
       </c>
       <c r="CD4" t="n">
-        <v>308802</v>
+        <v>308837</v>
       </c>
     </row>
     <row r="5">
@@ -31239,7 +31239,7 @@
         <v>123716</v>
       </c>
       <c r="CD5" t="n">
-        <v>254042</v>
+        <v>265621</v>
       </c>
     </row>
     <row r="6">
@@ -31491,7 +31491,7 @@
         <v>866443</v>
       </c>
       <c r="CD6" t="n">
-        <v>2016126</v>
+        <v>2018380</v>
       </c>
     </row>
     <row r="7">
@@ -31743,7 +31743,7 @@
         <v>898105</v>
       </c>
       <c r="CD7" t="n">
-        <v>6537875</v>
+        <v>6551344</v>
       </c>
     </row>
     <row r="8">
@@ -31995,7 +31995,7 @@
         <v>3337808</v>
       </c>
       <c r="CD8" t="n">
-        <v>10854985</v>
+        <v>12365615</v>
       </c>
     </row>
     <row r="9">
@@ -32247,7 +32247,7 @@
         <v>2568484</v>
       </c>
       <c r="CD9" t="n">
-        <v>2818252</v>
+        <v>2853428</v>
       </c>
     </row>
     <row r="10">
@@ -32499,7 +32499,7 @@
         <v>429426</v>
       </c>
       <c r="CD10" t="n">
-        <v>1039481</v>
+        <v>1039601</v>
       </c>
     </row>
     <row r="11">
@@ -32751,7 +32751,7 @@
         <v>330207</v>
       </c>
       <c r="CD11" t="n">
-        <v>471874</v>
+        <v>473169</v>
       </c>
     </row>
     <row r="12">
@@ -33003,7 +33003,7 @@
         <v>1502282</v>
       </c>
       <c r="CD12" t="n">
-        <v>1265309</v>
+        <v>1267511</v>
       </c>
     </row>
     <row r="13">
@@ -33255,7 +33255,7 @@
         <v>4596690</v>
       </c>
       <c r="CD13" t="n">
-        <v>3771450</v>
+        <v>3773432</v>
       </c>
     </row>
     <row r="14">
@@ -33507,7 +33507,7 @@
         <v>22967977</v>
       </c>
       <c r="CD14" t="n">
-        <v>22679446</v>
+        <v>23109672</v>
       </c>
     </row>
     <row r="15">
@@ -33759,7 +33759,7 @@
         <v>788179</v>
       </c>
       <c r="CD15" t="n">
-        <v>2682529</v>
+        <v>2684380</v>
       </c>
     </row>
     <row r="16">
@@ -34011,7 +34011,7 @@
         <v>252246</v>
       </c>
       <c r="CD16" t="n">
-        <v>326492</v>
+        <v>326604</v>
       </c>
     </row>
     <row r="17">
@@ -34263,7 +34263,7 @@
         <v>23810</v>
       </c>
       <c r="CD17" t="n">
-        <v>40292</v>
+        <v>40307</v>
       </c>
     </row>
     <row r="18">
@@ -34767,7 +34767,7 @@
         <v>13592</v>
       </c>
       <c r="CD19" t="n">
-        <v>27530</v>
+        <v>27549</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -735,6 +735,7 @@
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -811,6 +812,9 @@
       <c r="W1" s="1" t="n">
         <v>20251226</v>
       </c>
+      <c r="X1" s="1" t="n">
+        <v>20251229</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -886,6 +890,9 @@
       <c r="W2" t="n">
         <v>19</v>
       </c>
+      <c r="X2" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -961,6 +968,9 @@
       <c r="W3" t="n">
         <v>55</v>
       </c>
+      <c r="X3" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1036,6 +1046,9 @@
       <c r="W4" t="n">
         <v>5</v>
       </c>
+      <c r="X4" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1111,6 +1124,9 @@
       <c r="W5" t="n">
         <v>0</v>
       </c>
+      <c r="X5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1186,6 +1202,9 @@
       <c r="W6" t="n">
         <v>54</v>
       </c>
+      <c r="X6" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1261,6 +1280,9 @@
       <c r="W7" t="n">
         <v>66</v>
       </c>
+      <c r="X7" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1336,6 +1358,9 @@
       <c r="W8" t="n">
         <v>63</v>
       </c>
+      <c r="X8" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1411,6 +1436,9 @@
       <c r="W9" t="n">
         <v>-41</v>
       </c>
+      <c r="X9" t="n">
+        <v>-45</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1486,6 +1514,9 @@
       <c r="W10" t="n">
         <v>1</v>
       </c>
+      <c r="X10" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1561,6 +1592,9 @@
       <c r="W11" t="n">
         <v>1</v>
       </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1636,6 +1670,9 @@
       <c r="W12" t="n">
         <v>0</v>
       </c>
+      <c r="X12" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1711,6 +1748,9 @@
       <c r="W13" t="n">
         <v>9</v>
       </c>
+      <c r="X13" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1786,6 +1826,9 @@
       <c r="W14" t="n">
         <v>-32</v>
       </c>
+      <c r="X14" t="n">
+        <v>-35</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1861,6 +1904,9 @@
       <c r="W15" t="n">
         <v>44</v>
       </c>
+      <c r="X15" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1936,6 +1982,9 @@
       <c r="W16" t="n">
         <v>-11</v>
       </c>
+      <c r="X16" t="n">
+        <v>-13</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2011,6 +2060,9 @@
       <c r="W17" t="n">
         <v>-16</v>
       </c>
+      <c r="X17" t="n">
+        <v>-19</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2086,6 +2138,9 @@
       <c r="W18" t="n">
         <v>29</v>
       </c>
+      <c r="X18" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2160,6 +2215,9 @@
       </c>
       <c r="W19" t="n">
         <v>41</v>
+      </c>
+      <c r="X19" t="n">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2173,7 +2231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK19"/>
+  <dimension ref="A1:BL19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2297,7 @@
     <col width="12" customWidth="1" min="61" max="61"/>
     <col width="12" customWidth="1" min="62" max="62"/>
     <col width="12" customWidth="1" min="63" max="63"/>
+    <col width="12" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2557,6 +2616,11 @@
           <t>20251226</t>
         </is>
       </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>20251229</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2752,6 +2816,9 @@
       <c r="BK2" t="n">
         <v>98</v>
       </c>
+      <c r="BL2" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2947,6 +3014,9 @@
       <c r="BK3" t="n">
         <v>104</v>
       </c>
+      <c r="BL3" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3142,6 +3212,9 @@
       <c r="BK4" t="n">
         <v>97</v>
       </c>
+      <c r="BL4" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3337,6 +3410,9 @@
       <c r="BK5" t="n">
         <v>101</v>
       </c>
+      <c r="BL5" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3532,6 +3608,9 @@
       <c r="BK6" t="n">
         <v>104</v>
       </c>
+      <c r="BL6" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3727,6 +3806,9 @@
       <c r="BK7" t="n">
         <v>105</v>
       </c>
+      <c r="BL7" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3922,6 +4004,9 @@
       <c r="BK8" t="n">
         <v>105</v>
       </c>
+      <c r="BL8" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4117,6 +4202,9 @@
       <c r="BK9" t="n">
         <v>88</v>
       </c>
+      <c r="BL9" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4312,6 +4400,9 @@
       <c r="BK10" t="n">
         <v>99</v>
       </c>
+      <c r="BL10" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4507,6 +4598,9 @@
       <c r="BK11" t="n">
         <v>95</v>
       </c>
+      <c r="BL11" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4702,6 +4796,9 @@
       <c r="BK12" t="n">
         <v>94</v>
       </c>
+      <c r="BL12" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4897,6 +4994,9 @@
       <c r="BK13" t="n">
         <v>95</v>
       </c>
+      <c r="BL13" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5092,6 +5192,9 @@
       <c r="BK14" t="n">
         <v>87</v>
       </c>
+      <c r="BL14" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5287,6 +5390,9 @@
       <c r="BK15" t="n">
         <v>99</v>
       </c>
+      <c r="BL15" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5482,6 +5588,9 @@
       <c r="BK16" t="n">
         <v>94</v>
       </c>
+      <c r="BL16" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5677,6 +5786,9 @@
       <c r="BK17" t="n">
         <v>93</v>
       </c>
+      <c r="BL17" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5872,6 +5984,9 @@
       <c r="BK18" t="n">
         <v>100</v>
       </c>
+      <c r="BL18" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6066,6 +6181,9 @@
       </c>
       <c r="BK19" t="n">
         <v>98</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -6079,7 +6197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR19"/>
+  <dimension ref="A1:BL19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6126,6 +6244,26 @@
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="12" customWidth="1" min="43" max="43"/>
     <col width="12" customWidth="1" min="44" max="44"/>
+    <col width="12" customWidth="1" min="45" max="45"/>
+    <col width="12" customWidth="1" min="46" max="46"/>
+    <col width="12" customWidth="1" min="47" max="47"/>
+    <col width="12" customWidth="1" min="48" max="48"/>
+    <col width="12" customWidth="1" min="49" max="49"/>
+    <col width="12" customWidth="1" min="50" max="50"/>
+    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="12" customWidth="1" min="52" max="52"/>
+    <col width="12" customWidth="1" min="53" max="53"/>
+    <col width="12" customWidth="1" min="54" max="54"/>
+    <col width="12" customWidth="1" min="55" max="55"/>
+    <col width="12" customWidth="1" min="56" max="56"/>
+    <col width="12" customWidth="1" min="57" max="57"/>
+    <col width="12" customWidth="1" min="58" max="58"/>
+    <col width="12" customWidth="1" min="59" max="59"/>
+    <col width="12" customWidth="1" min="60" max="60"/>
+    <col width="12" customWidth="1" min="61" max="61"/>
+    <col width="12" customWidth="1" min="62" max="62"/>
+    <col width="12" customWidth="1" min="63" max="63"/>
+    <col width="12" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6349,6 +6487,106 @@
           <t>20251226</t>
         </is>
       </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>20251201</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>20251202</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>20251203</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>20251204</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>20251205</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>20251208</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>20251209</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>20251210</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>20251211</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>20251212</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>20251215</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>20251216</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>20251217</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>20251218</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>20251219</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>20251222</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>20251223</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>20251224</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>20251226</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>20251229</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6487,6 +6725,66 @@
       <c r="AR2" t="n">
         <v>15.38</v>
       </c>
+      <c r="AS2" t="n">
+        <v>645.79</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>645.46</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>626.3099999999999</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>605.24</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>529.66</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>485.39</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>399.28</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>393.37</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>400.51</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>409.79</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>396.06</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>405.58</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>459.55</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>485.11</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>486.59</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>518.64</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>574.16</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>593.91</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>595.36</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>577.78</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6625,6 +6923,66 @@
       <c r="AR3" t="n">
         <v>-30.02</v>
       </c>
+      <c r="AS3" t="n">
+        <v>2299.56</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2173.53</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2155.48</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2090.2</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>2089.1</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>2063.38</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1938.42</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1824.92</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1685.63</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1706.19</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1609.14</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1661</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1650.25</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1652.07</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1436.26</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1273.33</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1176.69</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1118.28</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1235.59</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1442.86</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6763,6 +7121,66 @@
       <c r="AR4" t="n">
         <v>12.89</v>
       </c>
+      <c r="AS4" t="n">
+        <v>741.65</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>765.83</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>753.1900000000001</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>720.38</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>648.59</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>582.86</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>449.84</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>449.02</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>454.9</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>487.83</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>504.11</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>524.1799999999999</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>576.85</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>587.75</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>584.8099999999999</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>605.08</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>636.66</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>672.98</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>687.22</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>629.62</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6901,6 +7319,66 @@
       <c r="AR5" t="n">
         <v>-7.01</v>
       </c>
+      <c r="AS5" t="n">
+        <v>538.55</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>492.53</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>487.68</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>473.21</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>474.24</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>467.85</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>443.88</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>406.61</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>369.26</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>368.71</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>347.38</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>414.77</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>420.64</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>432.51</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>429.24</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>406.53</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>408.7</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>411.25</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>408.22</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>416</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7039,6 +7517,66 @@
       <c r="AR6" t="n">
         <v>-22.11</v>
       </c>
+      <c r="AS6" t="n">
+        <v>522.97</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>502.98</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>506.77</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>504.42</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>503.05</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>514.16</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>505.93</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>503.9</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>496.69</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>496.61</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>477.43</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>494.38</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>486.78</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>491.45</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>428.16</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>362.93</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>342.84</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>337.45</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>366.92</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>418.45</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7177,6 +7715,66 @@
       <c r="AR7" t="n">
         <v>-29.72</v>
       </c>
+      <c r="AS7" t="n">
+        <v>613.1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>584.49</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>599.25</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>599.4299999999999</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>612.26</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>639.23</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>643.13</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>662.4400000000001</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>667.24</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>679.04</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>679.89</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>664.88</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>640.21</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>631.26</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>518.92</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>427.02</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>371.28</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>364.46</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>410.92</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>484.03</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7315,6 +7913,66 @@
       <c r="AR8" t="n">
         <v>-21.24</v>
       </c>
+      <c r="AS8" t="n">
+        <v>695.97</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>660.11</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>658.1</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>651.63</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>652.0599999999999</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>649.63</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>616.5599999999999</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>588.03</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>541.03</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>553.79</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>524.87</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>538.9</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>534.54</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>534.58</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>464.25</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>402.72</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>378.65</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>384.23</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>441.75</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>539.3200000000001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7453,6 +8111,66 @@
       <c r="AR9" t="n">
         <v>12.29</v>
       </c>
+      <c r="AS9" t="n">
+        <v>125.35</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>120.99</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>120.58</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>120.22</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>120.47</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>120.32</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>118.18</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>109.82</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>76.67</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>78.52</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>79.45</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>91.86</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>105.63</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>109.27</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>113.27</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>119.62</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>126.26</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7591,6 +8309,66 @@
       <c r="AR10" t="n">
         <v>8.720000000000001</v>
       </c>
+      <c r="AS10" t="n">
+        <v>516.12</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>467.23</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>480.23</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>474.84</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>464.08</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>464.08</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>463.43</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>459.17</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>448.36</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>442.01</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>438.69</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>497.54</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>510.01</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>555.96</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>558.1799999999999</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>527.25</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>533.13</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>545.4299999999999</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>539.1900000000001</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>522.64</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7729,6 +8507,66 @@
       <c r="AR11" t="n">
         <v>-3.13</v>
       </c>
+      <c r="AS11" t="n">
+        <v>202.62</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>197.34</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>198.21</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>197.43</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>199.08</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>227.13</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>255.36</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>272</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>270.08</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>281.11</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>291.58</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>287.96</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>283.89</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>287.89</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>279.21</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>252.58</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>229.35</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>232.75</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>236.83</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>239.07</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7867,6 +8705,66 @@
       <c r="AR12" t="n">
         <v>-1.83</v>
       </c>
+      <c r="AS12" t="n">
+        <v>242.38</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>234.69</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>233.74</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>229.75</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>232.36</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>271.02</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>306.45</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>327.33</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>328.87</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>343.38</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>358.04</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>353.7</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>347.62</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>350.42</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>341.49</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>312.62</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>283.31</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>286.28</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>290.77</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>295.19</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8005,6 +8903,66 @@
       <c r="AR13" t="n">
         <v>-8.07</v>
       </c>
+      <c r="AS13" t="n">
+        <v>260.33</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>250.73</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>250.25</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>246.23</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>251.08</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>302.57</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>348.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>379.25</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>391.93</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>411.32</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>430.25</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>424.14</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>415.82</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>413.12</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>396.3</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>358.39</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>319.15</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>314.34</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>309.93</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>305</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8143,6 +9101,66 @@
       <c r="AR14" t="n">
         <v>9.380000000000001</v>
       </c>
+      <c r="AS14" t="n">
+        <v>150.35</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>143.29</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>141.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>138.61</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>138.52</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>140.39</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>140.12</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>135.9</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>115.86</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>112.21</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>112.87</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>113.02</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>125.49</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>133.31</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>131.14</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>131.22</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>137.06</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>152.5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8281,6 +9299,66 @@
       <c r="AR15" t="n">
         <v>-24</v>
       </c>
+      <c r="AS15" t="n">
+        <v>1228.63</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1259.82</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1256.74</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1234.86</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1107.2</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>943.66</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>650.0599999999999</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>598.54</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>571.54</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>560.66</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>561.76</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>556.28</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>559.16</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>582.75</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>584.22</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>586.79</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>580.71</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>602.4400000000001</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>601.85</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>585.6799999999999</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8419,6 +9497,66 @@
       <c r="AR16" t="n">
         <v>1.94</v>
       </c>
+      <c r="AS16" t="n">
+        <v>473.01</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>444.08</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>434.67</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>422.92</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>423.8</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>458.44</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>489.93</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>501.78</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>477.47</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>494.73</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>511.45</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>508.1</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>500.44</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>517.54</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>517.54</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>484.28</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>458.77</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>470.28</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>488.01</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>502.23</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8557,6 +9695,66 @@
       <c r="AR17" t="n">
         <v>-0.84</v>
       </c>
+      <c r="AS17" t="n">
+        <v>310.75</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>300.76</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>296.58</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>291.51</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>291.53</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>309.76</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>326.92</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>332.96</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>305.22</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>310.05</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>317.75</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>316.64</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>312.4</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>324.58</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>325.21</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>302.89</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>282.64</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>291.92</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>306.24</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>320.15</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8695,6 +9893,66 @@
       <c r="AR18" t="n">
         <v>3.33</v>
       </c>
+      <c r="AS18" t="n">
+        <v>626.28</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>636.1900000000001</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>630.64</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>621.76</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>550.73</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>553.5599999999999</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>558.8</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>566.0700000000001</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>568.14</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>507.01</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>528.0599999999999</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>605.0599999999999</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>627.87</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>674.0700000000001</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>674.5</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>645.4400000000001</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>652.11</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>647.17</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>625.4400000000001</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>594.71</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8832,6 +10090,66 @@
       </c>
       <c r="AR19" t="n">
         <v>-39.13</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>868</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>893.52</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>887.01</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>864.12</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>775.66</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>649.9400000000001</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>441.38</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>424.12</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>418.55</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>417.46</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>419.76</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>416.94</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>409.53</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>415.35</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>410.12</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>391.44</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>342.28</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>341.66</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>333.84</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>331.58</v>
       </c>
     </row>
   </sheetData>
@@ -8845,7 +10163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8871,6 +10189,7 @@
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8989,6 +10308,11 @@
           <t>20251226</t>
         </is>
       </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>20251229</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9064,6 +10388,9 @@
       <c r="W2" t="n">
         <v>75</v>
       </c>
+      <c r="X2" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9139,6 +10466,9 @@
       <c r="W3" t="n">
         <v>52</v>
       </c>
+      <c r="X3" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9214,6 +10544,9 @@
       <c r="W4" t="n">
         <v>89</v>
       </c>
+      <c r="X4" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9289,6 +10622,9 @@
       <c r="W5" t="n">
         <v>17</v>
       </c>
+      <c r="X5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9364,6 +10700,9 @@
       <c r="W6" t="n">
         <v>51</v>
       </c>
+      <c r="X6" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9439,6 +10778,9 @@
       <c r="W7" t="n">
         <v>85</v>
       </c>
+      <c r="X7" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9514,6 +10856,9 @@
       <c r="W8" t="n">
         <v>77</v>
       </c>
+      <c r="X8" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9589,6 +10934,9 @@
       <c r="W9" t="n">
         <v>19</v>
       </c>
+      <c r="X9" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9664,6 +11012,9 @@
       <c r="W10" t="n">
         <v>39</v>
       </c>
+      <c r="X10" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9739,6 +11090,9 @@
       <c r="W11" t="n">
         <v>18</v>
       </c>
+      <c r="X11" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9814,6 +11168,9 @@
       <c r="W12" t="n">
         <v>21</v>
       </c>
+      <c r="X12" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9889,6 +11246,9 @@
       <c r="W13" t="n">
         <v>27</v>
       </c>
+      <c r="X13" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9964,6 +11324,9 @@
       <c r="W14" t="n">
         <v>22</v>
       </c>
+      <c r="X14" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10039,6 +11402,9 @@
       <c r="W15" t="n">
         <v>79</v>
       </c>
+      <c r="X15" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10114,6 +11480,9 @@
       <c r="W16" t="n">
         <v>26</v>
       </c>
+      <c r="X16" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10189,6 +11558,9 @@
       <c r="W17" t="n">
         <v>8</v>
       </c>
+      <c r="X17" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10264,6 +11636,9 @@
       <c r="W18" t="n">
         <v>16</v>
       </c>
+      <c r="X18" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10338,6 +11713,9 @@
       </c>
       <c r="W19" t="n">
         <v>29</v>
+      </c>
+      <c r="X19" t="n">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -10351,7 +11729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD19"/>
+  <dimension ref="A1:CE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10436,6 +11814,7 @@
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
+    <col width="12" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10689,6 +12068,9 @@
       <c r="CD1" s="1" t="n">
         <v>20251226</v>
       </c>
+      <c r="CE1" s="1" t="n">
+        <v>20251229</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10941,6 +12323,9 @@
       <c r="CD2" t="n">
         <v>14785</v>
       </c>
+      <c r="CE2" t="n">
+        <v>15250</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11193,6 +12578,9 @@
       <c r="CD3" t="n">
         <v>58250</v>
       </c>
+      <c r="CE3" t="n">
+        <v>60690</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11445,6 +12833,9 @@
       <c r="CD4" t="n">
         <v>17340</v>
       </c>
+      <c r="CE4" t="n">
+        <v>17940</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11697,6 +13088,9 @@
       <c r="CD5" t="n">
         <v>15650</v>
       </c>
+      <c r="CE5" t="n">
+        <v>16070</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11949,6 +13343,9 @@
       <c r="CD6" t="n">
         <v>17055</v>
       </c>
+      <c r="CE6" t="n">
+        <v>17910</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12201,6 +13598,9 @@
       <c r="CD7" t="n">
         <v>19990</v>
       </c>
+      <c r="CE7" t="n">
+        <v>20775</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12453,6 +13853,9 @@
       <c r="CD8" t="n">
         <v>19035</v>
       </c>
+      <c r="CE8" t="n">
+        <v>19920</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12705,6 +14108,9 @@
       <c r="CD9" t="n">
         <v>1345</v>
       </c>
+      <c r="CE9" t="n">
+        <v>1255</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12957,6 +14363,9 @@
       <c r="CD10" t="n">
         <v>16375</v>
       </c>
+      <c r="CE10" t="n">
+        <v>17000</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13209,6 +14618,9 @@
       <c r="CD11" t="n">
         <v>5145</v>
       </c>
+      <c r="CE11" t="n">
+        <v>4985</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13461,6 +14873,9 @@
       <c r="CD12" t="n">
         <v>5540</v>
       </c>
+      <c r="CE12" t="n">
+        <v>5290</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13713,6 +15128,9 @@
       <c r="CD13" t="n">
         <v>5635</v>
       </c>
+      <c r="CE13" t="n">
+        <v>5370</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13965,6 +15383,9 @@
       <c r="CD14" t="n">
         <v>1444</v>
       </c>
+      <c r="CE14" t="n">
+        <v>1311</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14217,6 +15638,9 @@
       <c r="CD15" t="n">
         <v>18775</v>
       </c>
+      <c r="CE15" t="n">
+        <v>19500</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14469,6 +15893,9 @@
       <c r="CD16" t="n">
         <v>10335</v>
       </c>
+      <c r="CE16" t="n">
+        <v>9975</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14721,6 +16148,9 @@
       <c r="CD17" t="n">
         <v>6070</v>
       </c>
+      <c r="CE17" t="n">
+        <v>5845</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14973,6 +16403,9 @@
       <c r="CD18" t="n">
         <v>17605</v>
       </c>
+      <c r="CE18" t="n">
+        <v>18125</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -15224,6 +16657,9 @@
       </c>
       <c r="CD19" t="n">
         <v>15755</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>16115</v>
       </c>
     </row>
   </sheetData>
@@ -15237,7 +16673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD19"/>
+  <dimension ref="A1:CE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15322,6 +16758,7 @@
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
+    <col width="12" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15575,6 +17012,9 @@
       <c r="CD1" s="1" t="n">
         <v>20251226</v>
       </c>
+      <c r="CE1" s="1" t="n">
+        <v>20251229</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15827,6 +17267,9 @@
       <c r="CD2" t="n">
         <v>15162</v>
       </c>
+      <c r="CE2" t="n">
+        <v>15500</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16079,6 +17522,9 @@
       <c r="CD3" t="n">
         <v>59650</v>
       </c>
+      <c r="CE3" t="n">
+        <v>60960</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16331,6 +17777,9 @@
       <c r="CD4" t="n">
         <v>17610</v>
       </c>
+      <c r="CE4" t="n">
+        <v>18015</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16583,6 +18032,9 @@
       <c r="CD5" t="n">
         <v>15980</v>
       </c>
+      <c r="CE5" t="n">
+        <v>16255</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16835,6 +18287,9 @@
       <c r="CD6" t="n">
         <v>17500</v>
       </c>
+      <c r="CE6" t="n">
+        <v>17920</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17087,6 +18542,9 @@
       <c r="CD7" t="n">
         <v>20475</v>
       </c>
+      <c r="CE7" t="n">
+        <v>20830</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17339,6 +18797,9 @@
       <c r="CD8" t="n">
         <v>19570</v>
       </c>
+      <c r="CE8" t="n">
+        <v>19945</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17591,6 +19052,9 @@
       <c r="CD9" t="n">
         <v>1355</v>
       </c>
+      <c r="CE9" t="n">
+        <v>1305</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17843,6 +19307,9 @@
       <c r="CD10" t="n">
         <v>16840</v>
       </c>
+      <c r="CE10" t="n">
+        <v>17020</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -18095,6 +19562,9 @@
       <c r="CD11" t="n">
         <v>5220</v>
       </c>
+      <c r="CE11" t="n">
+        <v>5150</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -18347,6 +19817,9 @@
       <c r="CD12" t="n">
         <v>5595</v>
       </c>
+      <c r="CE12" t="n">
+        <v>5520</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -18599,6 +20072,9 @@
       <c r="CD13" t="n">
         <v>5695</v>
       </c>
+      <c r="CE13" t="n">
+        <v>5620</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18851,6 +20327,9 @@
       <c r="CD14" t="n">
         <v>1467</v>
       </c>
+      <c r="CE14" t="n">
+        <v>1414</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19103,6 +20582,9 @@
       <c r="CD15" t="n">
         <v>19250</v>
       </c>
+      <c r="CE15" t="n">
+        <v>19635</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -19355,6 +20837,9 @@
       <c r="CD16" t="n">
         <v>10465</v>
       </c>
+      <c r="CE16" t="n">
+        <v>10290</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -19607,6 +21092,9 @@
       <c r="CD17" t="n">
         <v>6135</v>
       </c>
+      <c r="CE17" t="n">
+        <v>6020</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -19859,6 +21347,9 @@
       <c r="CD18" t="n">
         <v>17985</v>
       </c>
+      <c r="CE18" t="n">
+        <v>18195</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -20110,6 +21601,9 @@
       </c>
       <c r="CD19" t="n">
         <v>15945</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>16115</v>
       </c>
     </row>
   </sheetData>
@@ -20123,7 +21617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD19"/>
+  <dimension ref="A1:CE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20208,6 +21702,7 @@
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
+    <col width="12" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20461,6 +21956,9 @@
       <c r="CD1" s="1" t="n">
         <v>20251226</v>
       </c>
+      <c r="CE1" s="1" t="n">
+        <v>20251229</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20713,6 +22211,9 @@
       <c r="CD2" t="n">
         <v>14480</v>
       </c>
+      <c r="CE2" t="n">
+        <v>15135</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20965,6 +22466,9 @@
       <c r="CD3" t="n">
         <v>58240</v>
       </c>
+      <c r="CE3" t="n">
+        <v>60140</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21217,6 +22721,9 @@
       <c r="CD4" t="n">
         <v>17205</v>
       </c>
+      <c r="CE4" t="n">
+        <v>17695</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21469,6 +22976,9 @@
       <c r="CD5" t="n">
         <v>15600</v>
       </c>
+      <c r="CE5" t="n">
+        <v>16015</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21721,6 +23231,9 @@
       <c r="CD6" t="n">
         <v>17035</v>
       </c>
+      <c r="CE6" t="n">
+        <v>17610</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21973,6 +23486,9 @@
       <c r="CD7" t="n">
         <v>19975</v>
       </c>
+      <c r="CE7" t="n">
+        <v>20595</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22225,6 +23741,9 @@
       <c r="CD8" t="n">
         <v>19010</v>
       </c>
+      <c r="CE8" t="n">
+        <v>19700</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22477,6 +23996,9 @@
       <c r="CD9" t="n">
         <v>1295</v>
       </c>
+      <c r="CE9" t="n">
+        <v>1235</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22729,6 +24251,9 @@
       <c r="CD10" t="n">
         <v>16340</v>
       </c>
+      <c r="CE10" t="n">
+        <v>16695</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22981,6 +24506,9 @@
       <c r="CD11" t="n">
         <v>5060</v>
       </c>
+      <c r="CE11" t="n">
+        <v>4930</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -23233,6 +24761,9 @@
       <c r="CD12" t="n">
         <v>5190</v>
       </c>
+      <c r="CE12" t="n">
+        <v>5255</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -23485,6 +25016,9 @@
       <c r="CD13" t="n">
         <v>5490</v>
       </c>
+      <c r="CE13" t="n">
+        <v>5350</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -23737,6 +25271,9 @@
       <c r="CD14" t="n">
         <v>1386</v>
       </c>
+      <c r="CE14" t="n">
+        <v>1308</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -23989,6 +25526,9 @@
       <c r="CD15" t="n">
         <v>18570</v>
       </c>
+      <c r="CE15" t="n">
+        <v>19225</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24241,6 +25781,9 @@
       <c r="CD16" t="n">
         <v>10165</v>
       </c>
+      <c r="CE16" t="n">
+        <v>9905</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24493,6 +26036,9 @@
       <c r="CD17" t="n">
         <v>5960</v>
       </c>
+      <c r="CE17" t="n">
+        <v>5815</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24745,6 +26291,9 @@
       <c r="CD18" t="n">
         <v>17520</v>
       </c>
+      <c r="CE18" t="n">
+        <v>17870</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -24996,6 +26545,9 @@
       </c>
       <c r="CD19" t="n">
         <v>15630</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>15830</v>
       </c>
     </row>
   </sheetData>
@@ -25009,7 +26561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD19"/>
+  <dimension ref="A1:CE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25094,6 +26646,7 @@
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
+    <col width="12" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25347,6 +26900,9 @@
       <c r="CD1" s="1" t="n">
         <v>20251226</v>
       </c>
+      <c r="CE1" s="1" t="n">
+        <v>20251229</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25599,6 +27155,9 @@
       <c r="CD2" t="n">
         <v>15130</v>
       </c>
+      <c r="CE2" t="n">
+        <v>15475</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25851,6 +27410,9 @@
       <c r="CD3" t="n">
         <v>59525</v>
       </c>
+      <c r="CE3" t="n">
+        <v>60755</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26103,6 +27665,9 @@
       <c r="CD4" t="n">
         <v>17530</v>
       </c>
+      <c r="CE4" t="n">
+        <v>17980</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26355,6 +27920,9 @@
       <c r="CD5" t="n">
         <v>15860</v>
       </c>
+      <c r="CE5" t="n">
+        <v>16200</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26607,6 +28175,9 @@
       <c r="CD6" t="n">
         <v>17465</v>
       </c>
+      <c r="CE6" t="n">
+        <v>17795</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26859,6 +28430,9 @@
       <c r="CD7" t="n">
         <v>20375</v>
       </c>
+      <c r="CE7" t="n">
+        <v>20830</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27111,6 +28685,9 @@
       <c r="CD8" t="n">
         <v>19420</v>
       </c>
+      <c r="CE8" t="n">
+        <v>19940</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27363,6 +28940,9 @@
       <c r="CD9" t="n">
         <v>1297</v>
       </c>
+      <c r="CE9" t="n">
+        <v>1288</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27615,6 +29195,9 @@
       <c r="CD10" t="n">
         <v>16750</v>
       </c>
+      <c r="CE10" t="n">
+        <v>16815</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27867,6 +29450,9 @@
       <c r="CD11" t="n">
         <v>5095</v>
       </c>
+      <c r="CE11" t="n">
+        <v>5100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28119,6 +29705,9 @@
       <c r="CD12" t="n">
         <v>5450</v>
       </c>
+      <c r="CE12" t="n">
+        <v>5445</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28371,6 +29960,9 @@
       <c r="CD13" t="n">
         <v>5535</v>
       </c>
+      <c r="CE13" t="n">
+        <v>5530</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -28623,6 +30215,9 @@
       <c r="CD14" t="n">
         <v>1397</v>
       </c>
+      <c r="CE14" t="n">
+        <v>1392</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -28875,6 +30470,9 @@
       <c r="CD15" t="n">
         <v>19245</v>
       </c>
+      <c r="CE15" t="n">
+        <v>19595</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -29127,6 +30725,9 @@
       <c r="CD16" t="n">
         <v>10225</v>
       </c>
+      <c r="CE16" t="n">
+        <v>10215</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -29379,6 +30980,9 @@
       <c r="CD17" t="n">
         <v>5995</v>
       </c>
+      <c r="CE17" t="n">
+        <v>5975</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -29631,6 +31235,9 @@
       <c r="CD18" t="n">
         <v>17805</v>
       </c>
+      <c r="CE18" t="n">
+        <v>18045</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -29882,6 +31489,9 @@
       </c>
       <c r="CD19" t="n">
         <v>15900</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>16040</v>
       </c>
     </row>
   </sheetData>
@@ -29895,7 +31505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD19"/>
+  <dimension ref="A1:CE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29980,6 +31590,7 @@
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
+    <col width="12" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30233,6 +31844,9 @@
       <c r="CD1" s="1" t="n">
         <v>20251226</v>
       </c>
+      <c r="CE1" s="1" t="n">
+        <v>20251229</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30485,6 +32099,9 @@
       <c r="CD2" t="n">
         <v>188646</v>
       </c>
+      <c r="CE2" t="n">
+        <v>118489</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -30737,6 +32354,9 @@
       <c r="CD3" t="n">
         <v>2378510</v>
       </c>
+      <c r="CE3" t="n">
+        <v>1993001</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -30989,6 +32609,9 @@
       <c r="CD4" t="n">
         <v>308837</v>
       </c>
+      <c r="CE4" t="n">
+        <v>80785</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -31241,6 +32864,9 @@
       <c r="CD5" t="n">
         <v>265621</v>
       </c>
+      <c r="CE5" t="n">
+        <v>298036</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -31493,6 +33119,9 @@
       <c r="CD6" t="n">
         <v>2018380</v>
       </c>
+      <c r="CE6" t="n">
+        <v>1475159</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -31745,6 +33374,9 @@
       <c r="CD7" t="n">
         <v>6551344</v>
       </c>
+      <c r="CE7" t="n">
+        <v>6920233</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -31997,6 +33629,9 @@
       <c r="CD8" t="n">
         <v>12365615</v>
       </c>
+      <c r="CE8" t="n">
+        <v>13069790</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -32249,6 +33884,9 @@
       <c r="CD9" t="n">
         <v>2853428</v>
       </c>
+      <c r="CE9" t="n">
+        <v>3167394</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -32501,6 +34139,9 @@
       <c r="CD10" t="n">
         <v>1039601</v>
       </c>
+      <c r="CE10" t="n">
+        <v>417900</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -32753,6 +34394,9 @@
       <c r="CD11" t="n">
         <v>473169</v>
       </c>
+      <c r="CE11" t="n">
+        <v>609382</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33005,6 +34649,9 @@
       <c r="CD12" t="n">
         <v>1267511</v>
       </c>
+      <c r="CE12" t="n">
+        <v>1814306</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33257,6 +34904,9 @@
       <c r="CD13" t="n">
         <v>3773432</v>
       </c>
+      <c r="CE13" t="n">
+        <v>4403569</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33509,6 +35159,9 @@
       <c r="CD14" t="n">
         <v>23109672</v>
       </c>
+      <c r="CE14" t="n">
+        <v>28148290</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -33761,6 +35414,9 @@
       <c r="CD15" t="n">
         <v>2684380</v>
       </c>
+      <c r="CE15" t="n">
+        <v>2016413</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -34013,6 +35669,9 @@
       <c r="CD16" t="n">
         <v>326604</v>
       </c>
+      <c r="CE16" t="n">
+        <v>180376</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -34265,6 +35924,9 @@
       <c r="CD17" t="n">
         <v>40307</v>
       </c>
+      <c r="CE17" t="n">
+        <v>48810</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -34517,6 +36179,9 @@
       <c r="CD18" t="n">
         <v>54426</v>
       </c>
+      <c r="CE18" t="n">
+        <v>38763</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -34768,6 +36433,9 @@
       </c>
       <c r="CD19" t="n">
         <v>27549</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>30235</v>
       </c>
     </row>
   </sheetData>
@@ -34781,7 +36449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK19"/>
+  <dimension ref="A1:BL19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34847,6 +36515,7 @@
     <col width="10" customWidth="1" min="61" max="61"/>
     <col width="10" customWidth="1" min="62" max="62"/>
     <col width="10" customWidth="1" min="63" max="63"/>
+    <col width="10" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35043,6 +36712,9 @@
       <c r="BK1" s="1" t="n">
         <v>20251226</v>
       </c>
+      <c r="BL1" s="1" t="n">
+        <v>20251229</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35238,6 +36910,9 @@
       <c r="BK2" t="n">
         <v>32</v>
       </c>
+      <c r="BL2" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -35433,6 +37108,9 @@
       <c r="BK3" t="n">
         <v>100</v>
       </c>
+      <c r="BL3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -35628,6 +37306,9 @@
       <c r="BK4" t="n">
         <v>14</v>
       </c>
+      <c r="BL4" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -35823,6 +37504,9 @@
       <c r="BK5" t="n">
         <v>72</v>
       </c>
+      <c r="BL5" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -36018,6 +37702,9 @@
       <c r="BK6" t="n">
         <v>100</v>
       </c>
+      <c r="BL6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -36213,6 +37900,9 @@
       <c r="BK7" t="n">
         <v>100</v>
       </c>
+      <c r="BL7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -36408,6 +38098,9 @@
       <c r="BK8" t="n">
         <v>100</v>
       </c>
+      <c r="BL8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -36603,6 +38296,9 @@
       <c r="BK9" t="n">
         <v>2</v>
       </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -36798,6 +38494,9 @@
       <c r="BK10" t="n">
         <v>50</v>
       </c>
+      <c r="BL10" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -36993,6 +38692,9 @@
       <c r="BK11" t="n">
         <v>4</v>
       </c>
+      <c r="BL11" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -37188,6 +38890,9 @@
       <c r="BK12" t="n">
         <v>3</v>
       </c>
+      <c r="BL12" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -37383,6 +39088,9 @@
       <c r="BK13" t="n">
         <v>10</v>
       </c>
+      <c r="BL13" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37578,6 +39286,9 @@
       <c r="BK14" t="n">
         <v>2</v>
       </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37773,6 +39484,9 @@
       <c r="BK15" t="n">
         <v>36</v>
       </c>
+      <c r="BL15" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -37968,6 +39682,9 @@
       <c r="BK16" t="n">
         <v>4</v>
       </c>
+      <c r="BL16" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -38163,6 +39880,9 @@
       <c r="BK17" t="n">
         <v>0</v>
       </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -38358,6 +40078,9 @@
       <c r="BK18" t="n">
         <v>56</v>
       </c>
+      <c r="BL18" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -38552,6 +40275,9 @@
       </c>
       <c r="BK19" t="n">
         <v>20</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -38565,7 +40291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -38591,6 +40317,7 @@
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38667,6 +40394,9 @@
       <c r="W1" s="1" t="n">
         <v>20251226</v>
       </c>
+      <c r="X1" s="1" t="n">
+        <v>20251229</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -38742,6 +40472,9 @@
       <c r="W2" t="n">
         <v>63</v>
       </c>
+      <c r="X2" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38817,6 +40550,9 @@
       <c r="W3" t="n">
         <v>90</v>
       </c>
+      <c r="X3" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -38892,6 +40628,9 @@
       <c r="W4" t="n">
         <v>54</v>
       </c>
+      <c r="X4" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -38967,6 +40706,9 @@
       <c r="W5" t="n">
         <v>64</v>
       </c>
+      <c r="X5" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -39042,6 +40784,9 @@
       <c r="W6" t="n">
         <v>95</v>
       </c>
+      <c r="X6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -39117,6 +40862,9 @@
       <c r="W7" t="n">
         <v>100</v>
       </c>
+      <c r="X7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -39192,6 +40940,9 @@
       <c r="W8" t="n">
         <v>99</v>
       </c>
+      <c r="X8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -39267,6 +41018,9 @@
       <c r="W9" t="n">
         <v>29</v>
       </c>
+      <c r="X9" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -39342,6 +41096,9 @@
       <c r="W10" t="n">
         <v>64</v>
       </c>
+      <c r="X10" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -39417,6 +41174,9 @@
       <c r="W11" t="n">
         <v>66</v>
       </c>
+      <c r="X11" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -39492,6 +41252,9 @@
       <c r="W12" t="n">
         <v>65</v>
       </c>
+      <c r="X12" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -39567,6 +41330,9 @@
       <c r="W13" t="n">
         <v>67</v>
       </c>
+      <c r="X13" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39642,6 +41408,9 @@
       <c r="W14" t="n">
         <v>37</v>
       </c>
+      <c r="X14" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39717,6 +41486,9 @@
       <c r="W15" t="n">
         <v>81</v>
       </c>
+      <c r="X15" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -39792,6 +41564,9 @@
       <c r="W16" t="n">
         <v>56</v>
       </c>
+      <c r="X16" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -39867,6 +41642,9 @@
       <c r="W17" t="n">
         <v>53</v>
       </c>
+      <c r="X17" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -39942,6 +41720,9 @@
       <c r="W18" t="n">
         <v>82</v>
       </c>
+      <c r="X18" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -40016,6 +41797,9 @@
       </c>
       <c r="W19" t="n">
         <v>79</v>
+      </c>
+      <c r="X19" t="n">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -40029,7 +41813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK19"/>
+  <dimension ref="A1:BL19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -40095,6 +41879,7 @@
     <col width="10" customWidth="1" min="61" max="61"/>
     <col width="10" customWidth="1" min="62" max="62"/>
     <col width="10" customWidth="1" min="63" max="63"/>
+    <col width="10" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40291,6 +42076,9 @@
       <c r="BK1" s="1" t="n">
         <v>20251226</v>
       </c>
+      <c r="BL1" s="1" t="n">
+        <v>20251229</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40486,6 +42274,9 @@
       <c r="BK2" t="n">
         <v>-24</v>
       </c>
+      <c r="BL2" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40681,6 +42472,9 @@
       <c r="BK3" t="n">
         <v>100</v>
       </c>
+      <c r="BL3" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -40876,6 +42670,9 @@
       <c r="BK4" t="n">
         <v>-43</v>
       </c>
+      <c r="BL4" t="n">
+        <v>-7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -41071,6 +42868,9 @@
       <c r="BK5" t="n">
         <v>13</v>
       </c>
+      <c r="BL5" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -41266,6 +43066,9 @@
       <c r="BK6" t="n">
         <v>85</v>
       </c>
+      <c r="BL6" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -41461,6 +43264,9 @@
       <c r="BK7" t="n">
         <v>106</v>
       </c>
+      <c r="BL7" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -41656,6 +43462,9 @@
       <c r="BK8" t="n">
         <v>112</v>
       </c>
+      <c r="BL8" t="n">
+        <v>129</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -41851,6 +43660,9 @@
       <c r="BK9" t="n">
         <v>-72</v>
       </c>
+      <c r="BL9" t="n">
+        <v>-68</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -42046,6 +43858,9 @@
       <c r="BK10" t="n">
         <v>-11</v>
       </c>
+      <c r="BL10" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -42241,6 +44056,9 @@
       <c r="BK11" t="n">
         <v>-55</v>
       </c>
+      <c r="BL11" t="n">
+        <v>-53</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -42436,6 +44254,9 @@
       <c r="BK12" t="n">
         <v>-55</v>
       </c>
+      <c r="BL12" t="n">
+        <v>-55</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -42631,6 +44452,9 @@
       <c r="BK13" t="n">
         <v>-45</v>
       </c>
+      <c r="BL13" t="n">
+        <v>-47</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -42826,6 +44650,9 @@
       <c r="BK14" t="n">
         <v>-70</v>
       </c>
+      <c r="BL14" t="n">
+        <v>-65</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -43021,6 +44848,9 @@
       <c r="BK15" t="n">
         <v>-11</v>
       </c>
+      <c r="BL15" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -43216,6 +45046,9 @@
       <c r="BK16" t="n">
         <v>-61</v>
       </c>
+      <c r="BL16" t="n">
+        <v>-58</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -43411,6 +45244,9 @@
       <c r="BK17" t="n">
         <v>-68</v>
       </c>
+      <c r="BL17" t="n">
+        <v>-66</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -43606,6 +45442,9 @@
       <c r="BK18" t="n">
         <v>-4</v>
       </c>
+      <c r="BL18" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43800,6 +45639,9 @@
       </c>
       <c r="BK19" t="n">
         <v>-37</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>-15</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:Y19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -736,6 +736,7 @@
     <col width="10" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
     <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -815,6 +816,9 @@
       <c r="X1" s="1" t="n">
         <v>20251229</v>
       </c>
+      <c r="Y1" s="1" t="n">
+        <v>20251230</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -893,6 +897,9 @@
       <c r="X2" t="n">
         <v>32</v>
       </c>
+      <c r="Y2" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -971,6 +978,9 @@
       <c r="X3" t="n">
         <v>74</v>
       </c>
+      <c r="Y3" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1049,6 +1059,9 @@
       <c r="X4" t="n">
         <v>23</v>
       </c>
+      <c r="Y4" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1127,6 +1140,9 @@
       <c r="X5" t="n">
         <v>20</v>
       </c>
+      <c r="Y5" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1205,6 +1221,9 @@
       <c r="X6" t="n">
         <v>69</v>
       </c>
+      <c r="Y6" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1283,6 +1302,9 @@
       <c r="X7" t="n">
         <v>83</v>
       </c>
+      <c r="Y7" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1361,6 +1383,9 @@
       <c r="X8" t="n">
         <v>86</v>
       </c>
+      <c r="Y8" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1439,6 +1464,9 @@
       <c r="X9" t="n">
         <v>-45</v>
       </c>
+      <c r="Y9" t="n">
+        <v>-62</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1517,6 +1545,9 @@
       <c r="X10" t="n">
         <v>3</v>
       </c>
+      <c r="Y10" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1595,6 +1626,9 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="n">
+        <v>-21</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1673,6 +1707,9 @@
       <c r="X12" t="n">
         <v>-3</v>
       </c>
+      <c r="Y12" t="n">
+        <v>-26</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1751,6 +1788,9 @@
       <c r="X13" t="n">
         <v>7</v>
       </c>
+      <c r="Y13" t="n">
+        <v>-15</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1829,6 +1869,9 @@
       <c r="X14" t="n">
         <v>-35</v>
       </c>
+      <c r="Y14" t="n">
+        <v>-54</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1907,6 +1950,9 @@
       <c r="X15" t="n">
         <v>51</v>
       </c>
+      <c r="Y15" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1985,6 +2031,9 @@
       <c r="X16" t="n">
         <v>-13</v>
       </c>
+      <c r="Y16" t="n">
+        <v>-35</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2063,6 +2112,9 @@
       <c r="X17" t="n">
         <v>-19</v>
       </c>
+      <c r="Y17" t="n">
+        <v>-41</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2141,6 +2193,9 @@
       <c r="X18" t="n">
         <v>37</v>
       </c>
+      <c r="Y18" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2218,6 +2273,9 @@
       </c>
       <c r="X19" t="n">
         <v>44</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2231,7 +2289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL19"/>
+  <dimension ref="A1:BM19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2298,6 +2356,7 @@
     <col width="12" customWidth="1" min="62" max="62"/>
     <col width="12" customWidth="1" min="63" max="63"/>
     <col width="12" customWidth="1" min="64" max="64"/>
+    <col width="12" customWidth="1" min="65" max="65"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2621,6 +2680,11 @@
           <t>20251229</t>
         </is>
       </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>20251230</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2819,6 +2883,9 @@
       <c r="BL2" t="n">
         <v>101</v>
       </c>
+      <c r="BM2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3017,6 +3084,9 @@
       <c r="BL3" t="n">
         <v>106</v>
       </c>
+      <c r="BM3" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3215,6 +3285,9 @@
       <c r="BL4" t="n">
         <v>99</v>
       </c>
+      <c r="BM4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3413,6 +3486,9 @@
       <c r="BL5" t="n">
         <v>103</v>
       </c>
+      <c r="BM5" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3611,6 +3687,9 @@
       <c r="BL6" t="n">
         <v>105</v>
       </c>
+      <c r="BM6" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3809,6 +3888,9 @@
       <c r="BL7" t="n">
         <v>106</v>
       </c>
+      <c r="BM7" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4007,6 +4089,9 @@
       <c r="BL8" t="n">
         <v>108</v>
       </c>
+      <c r="BM8" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4205,6 +4290,9 @@
       <c r="BL9" t="n">
         <v>88</v>
       </c>
+      <c r="BM9" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4403,6 +4491,9 @@
       <c r="BL10" t="n">
         <v>100</v>
       </c>
+      <c r="BM10" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4601,6 +4692,9 @@
       <c r="BL11" t="n">
         <v>95</v>
       </c>
+      <c r="BM11" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4799,6 +4893,9 @@
       <c r="BL12" t="n">
         <v>94</v>
       </c>
+      <c r="BM12" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4997,6 +5094,9 @@
       <c r="BL13" t="n">
         <v>95</v>
       </c>
+      <c r="BM13" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5195,6 +5295,9 @@
       <c r="BL14" t="n">
         <v>87</v>
       </c>
+      <c r="BM14" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5393,6 +5496,9 @@
       <c r="BL15" t="n">
         <v>101</v>
       </c>
+      <c r="BM15" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5591,6 +5697,9 @@
       <c r="BL16" t="n">
         <v>94</v>
       </c>
+      <c r="BM16" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5789,6 +5898,9 @@
       <c r="BL17" t="n">
         <v>93</v>
       </c>
+      <c r="BM17" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5987,6 +6099,9 @@
       <c r="BL18" t="n">
         <v>101</v>
       </c>
+      <c r="BM18" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6184,6 +6299,9 @@
       </c>
       <c r="BL19" t="n">
         <v>99</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -6197,7 +6315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL19"/>
+  <dimension ref="A1:BM19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6264,6 +6382,7 @@
     <col width="12" customWidth="1" min="62" max="62"/>
     <col width="12" customWidth="1" min="63" max="63"/>
     <col width="12" customWidth="1" min="64" max="64"/>
+    <col width="12" customWidth="1" min="65" max="65"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6587,6 +6706,11 @@
           <t>20251229</t>
         </is>
       </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>20251230</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6785,6 +6909,9 @@
       <c r="BL2" t="n">
         <v>577.78</v>
       </c>
+      <c r="BM2" t="n">
+        <v>547.09</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6983,6 +7110,9 @@
       <c r="BL3" t="n">
         <v>1442.86</v>
       </c>
+      <c r="BM3" t="n">
+        <v>1666.41</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7181,6 +7311,9 @@
       <c r="BL4" t="n">
         <v>629.62</v>
       </c>
+      <c r="BM4" t="n">
+        <v>561.4400000000001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7379,6 +7512,9 @@
       <c r="BL5" t="n">
         <v>416</v>
       </c>
+      <c r="BM5" t="n">
+        <v>429.46</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7577,6 +7713,9 @@
       <c r="BL6" t="n">
         <v>418.45</v>
       </c>
+      <c r="BM6" t="n">
+        <v>471.64</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7775,6 +7914,9 @@
       <c r="BL7" t="n">
         <v>484.03</v>
       </c>
+      <c r="BM7" t="n">
+        <v>555.38</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7973,6 +8115,9 @@
       <c r="BL8" t="n">
         <v>539.3200000000001</v>
       </c>
+      <c r="BM8" t="n">
+        <v>632.08</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8171,6 +8316,9 @@
       <c r="BL9" t="n">
         <v>126.26</v>
       </c>
+      <c r="BM9" t="n">
+        <v>136.94</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8369,6 +8517,9 @@
       <c r="BL10" t="n">
         <v>522.64</v>
       </c>
+      <c r="BM10" t="n">
+        <v>503.14</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8567,6 +8718,9 @@
       <c r="BL11" t="n">
         <v>239.07</v>
       </c>
+      <c r="BM11" t="n">
+        <v>258.52</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8765,6 +8919,9 @@
       <c r="BL12" t="n">
         <v>295.19</v>
       </c>
+      <c r="BM12" t="n">
+        <v>322.46</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8963,6 +9120,9 @@
       <c r="BL13" t="n">
         <v>305</v>
       </c>
+      <c r="BM13" t="n">
+        <v>326.23</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9161,6 +9321,9 @@
       <c r="BL14" t="n">
         <v>152.5</v>
       </c>
+      <c r="BM14" t="n">
+        <v>165.68</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9359,6 +9522,9 @@
       <c r="BL15" t="n">
         <v>585.6799999999999</v>
       </c>
+      <c r="BM15" t="n">
+        <v>543.92</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9557,6 +9723,9 @@
       <c r="BL16" t="n">
         <v>502.23</v>
       </c>
+      <c r="BM16" t="n">
+        <v>548.13</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9755,6 +9924,9 @@
       <c r="BL17" t="n">
         <v>320.15</v>
       </c>
+      <c r="BM17" t="n">
+        <v>353.21</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9953,6 +10125,9 @@
       <c r="BL18" t="n">
         <v>594.71</v>
       </c>
+      <c r="BM18" t="n">
+        <v>579.6900000000001</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10150,6 +10325,9 @@
       </c>
       <c r="BL19" t="n">
         <v>331.58</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>300.88</v>
       </c>
     </row>
   </sheetData>
@@ -10163,7 +10341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:Y19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10190,6 +10368,7 @@
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10313,6 +10492,11 @@
           <t>20251229</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>20251230</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10391,6 +10575,9 @@
       <c r="X2" t="n">
         <v>47</v>
       </c>
+      <c r="Y2" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10469,6 +10656,9 @@
       <c r="X3" t="n">
         <v>43</v>
       </c>
+      <c r="Y3" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10547,6 +10737,9 @@
       <c r="X4" t="n">
         <v>23</v>
       </c>
+      <c r="Y4" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10625,6 +10818,9 @@
       <c r="X5" t="n">
         <v>20</v>
       </c>
+      <c r="Y5" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10703,6 +10899,9 @@
       <c r="X6" t="n">
         <v>37</v>
       </c>
+      <c r="Y6" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10781,6 +10980,9 @@
       <c r="X7" t="n">
         <v>88</v>
       </c>
+      <c r="Y7" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10859,6 +11061,9 @@
       <c r="X8" t="n">
         <v>92</v>
       </c>
+      <c r="Y8" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10937,6 +11142,9 @@
       <c r="X9" t="n">
         <v>21</v>
       </c>
+      <c r="Y9" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11015,6 +11223,9 @@
       <c r="X10" t="n">
         <v>16</v>
       </c>
+      <c r="Y10" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11093,6 +11304,9 @@
       <c r="X11" t="n">
         <v>23</v>
       </c>
+      <c r="Y11" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11171,6 +11385,9 @@
       <c r="X12" t="n">
         <v>31</v>
       </c>
+      <c r="Y12" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11249,6 +11466,9 @@
       <c r="X13" t="n">
         <v>31</v>
       </c>
+      <c r="Y13" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11327,6 +11547,9 @@
       <c r="X14" t="n">
         <v>27</v>
       </c>
+      <c r="Y14" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11405,6 +11628,9 @@
       <c r="X15" t="n">
         <v>59</v>
       </c>
+      <c r="Y15" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11483,6 +11709,9 @@
       <c r="X16" t="n">
         <v>14</v>
       </c>
+      <c r="Y16" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11561,6 +11790,9 @@
       <c r="X17" t="n">
         <v>10</v>
       </c>
+      <c r="Y17" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11639,6 +11871,9 @@
       <c r="X18" t="n">
         <v>11</v>
       </c>
+      <c r="Y18" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11716,6 +11951,9 @@
       </c>
       <c r="X19" t="n">
         <v>32</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -11729,7 +11967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE19"/>
+  <dimension ref="A1:CF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11815,6 +12053,7 @@
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
+    <col width="12" customWidth="1" min="84" max="84"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12071,6 +12310,9 @@
       <c r="CE1" s="1" t="n">
         <v>20251229</v>
       </c>
+      <c r="CF1" s="1" t="n">
+        <v>20251230</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12326,6 +12568,9 @@
       <c r="CE2" t="n">
         <v>15250</v>
       </c>
+      <c r="CF2" t="n">
+        <v>15540</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12581,6 +12826,9 @@
       <c r="CE3" t="n">
         <v>60690</v>
       </c>
+      <c r="CF3" t="n">
+        <v>60735</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12836,6 +13084,9 @@
       <c r="CE4" t="n">
         <v>17940</v>
       </c>
+      <c r="CF4" t="n">
+        <v>17980</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13091,6 +13342,9 @@
       <c r="CE5" t="n">
         <v>16070</v>
       </c>
+      <c r="CF5" t="n">
+        <v>16150</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13346,6 +13600,9 @@
       <c r="CE6" t="n">
         <v>17910</v>
       </c>
+      <c r="CF6" t="n">
+        <v>17750</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13601,6 +13858,9 @@
       <c r="CE7" t="n">
         <v>20775</v>
       </c>
+      <c r="CF7" t="n">
+        <v>20800</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13856,6 +14116,9 @@
       <c r="CE8" t="n">
         <v>19920</v>
       </c>
+      <c r="CF8" t="n">
+        <v>19945</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14111,6 +14374,9 @@
       <c r="CE9" t="n">
         <v>1255</v>
       </c>
+      <c r="CF9" t="n">
+        <v>1276</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14366,6 +14632,9 @@
       <c r="CE10" t="n">
         <v>17000</v>
       </c>
+      <c r="CF10" t="n">
+        <v>16755</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14621,6 +14890,9 @@
       <c r="CE11" t="n">
         <v>4985</v>
       </c>
+      <c r="CF11" t="n">
+        <v>5025</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14876,6 +15148,9 @@
       <c r="CE12" t="n">
         <v>5290</v>
       </c>
+      <c r="CF12" t="n">
+        <v>5340</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15131,6 +15406,9 @@
       <c r="CE13" t="n">
         <v>5370</v>
       </c>
+      <c r="CF13" t="n">
+        <v>5455</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -15386,6 +15664,9 @@
       <c r="CE14" t="n">
         <v>1311</v>
       </c>
+      <c r="CF14" t="n">
+        <v>1361</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15641,6 +15922,9 @@
       <c r="CE15" t="n">
         <v>19500</v>
       </c>
+      <c r="CF15" t="n">
+        <v>19580</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15896,6 +16180,9 @@
       <c r="CE16" t="n">
         <v>9975</v>
       </c>
+      <c r="CF16" t="n">
+        <v>10110</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16151,6 +16438,9 @@
       <c r="CE17" t="n">
         <v>5845</v>
       </c>
+      <c r="CF17" t="n">
+        <v>5890</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16406,6 +16696,9 @@
       <c r="CE18" t="n">
         <v>18125</v>
       </c>
+      <c r="CF18" t="n">
+        <v>17890</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -16660,6 +16953,9 @@
       </c>
       <c r="CE19" t="n">
         <v>16115</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>16105</v>
       </c>
     </row>
   </sheetData>
@@ -16673,7 +16969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE19"/>
+  <dimension ref="A1:CF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16759,6 +17055,7 @@
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
+    <col width="12" customWidth="1" min="84" max="84"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17015,6 +17312,9 @@
       <c r="CE1" s="1" t="n">
         <v>20251229</v>
       </c>
+      <c r="CF1" s="1" t="n">
+        <v>20251230</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17270,6 +17570,9 @@
       <c r="CE2" t="n">
         <v>15500</v>
       </c>
+      <c r="CF2" t="n">
+        <v>15545</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17525,6 +17828,9 @@
       <c r="CE3" t="n">
         <v>60960</v>
       </c>
+      <c r="CF3" t="n">
+        <v>61700</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17780,6 +18086,9 @@
       <c r="CE4" t="n">
         <v>18015</v>
       </c>
+      <c r="CF4" t="n">
+        <v>18130</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18035,6 +18344,9 @@
       <c r="CE5" t="n">
         <v>16255</v>
       </c>
+      <c r="CF5" t="n">
+        <v>16480</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18290,6 +18602,9 @@
       <c r="CE6" t="n">
         <v>17920</v>
       </c>
+      <c r="CF6" t="n">
+        <v>17980</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18545,6 +18860,9 @@
       <c r="CE7" t="n">
         <v>20830</v>
       </c>
+      <c r="CF7" t="n">
+        <v>21075</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18800,6 +19118,9 @@
       <c r="CE8" t="n">
         <v>19945</v>
       </c>
+      <c r="CF8" t="n">
+        <v>20260</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19055,6 +19376,9 @@
       <c r="CE9" t="n">
         <v>1305</v>
       </c>
+      <c r="CF9" t="n">
+        <v>1279</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19310,6 +19634,9 @@
       <c r="CE10" t="n">
         <v>17020</v>
       </c>
+      <c r="CF10" t="n">
+        <v>16895</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -19565,6 +19892,9 @@
       <c r="CE11" t="n">
         <v>5150</v>
       </c>
+      <c r="CF11" t="n">
+        <v>5025</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -19820,6 +20150,9 @@
       <c r="CE12" t="n">
         <v>5520</v>
       </c>
+      <c r="CF12" t="n">
+        <v>5340</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -20075,6 +20408,9 @@
       <c r="CE13" t="n">
         <v>5620</v>
       </c>
+      <c r="CF13" t="n">
+        <v>5460</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -20330,6 +20666,9 @@
       <c r="CE14" t="n">
         <v>1414</v>
       </c>
+      <c r="CF14" t="n">
+        <v>1370</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -20585,6 +20924,9 @@
       <c r="CE15" t="n">
         <v>19635</v>
       </c>
+      <c r="CF15" t="n">
+        <v>19655</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -20840,6 +21182,9 @@
       <c r="CE16" t="n">
         <v>10290</v>
       </c>
+      <c r="CF16" t="n">
+        <v>10110</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -21095,6 +21440,9 @@
       <c r="CE17" t="n">
         <v>6020</v>
       </c>
+      <c r="CF17" t="n">
+        <v>5970</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -21350,6 +21698,9 @@
       <c r="CE18" t="n">
         <v>18195</v>
       </c>
+      <c r="CF18" t="n">
+        <v>18035</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -21603,6 +21954,9 @@
         <v>15945</v>
       </c>
       <c r="CE19" t="n">
+        <v>16115</v>
+      </c>
+      <c r="CF19" t="n">
         <v>16115</v>
       </c>
     </row>
@@ -21617,7 +21971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE19"/>
+  <dimension ref="A1:CF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21703,6 +22057,7 @@
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
+    <col width="12" customWidth="1" min="84" max="84"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21959,6 +22314,9 @@
       <c r="CE1" s="1" t="n">
         <v>20251229</v>
       </c>
+      <c r="CF1" s="1" t="n">
+        <v>20251230</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22214,6 +22572,9 @@
       <c r="CE2" t="n">
         <v>15135</v>
       </c>
+      <c r="CF2" t="n">
+        <v>15150</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22469,6 +22830,9 @@
       <c r="CE3" t="n">
         <v>60140</v>
       </c>
+      <c r="CF3" t="n">
+        <v>60245</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22724,6 +23088,9 @@
       <c r="CE4" t="n">
         <v>17695</v>
       </c>
+      <c r="CF4" t="n">
+        <v>17770</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22979,6 +23346,9 @@
       <c r="CE5" t="n">
         <v>16015</v>
       </c>
+      <c r="CF5" t="n">
+        <v>16060</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23234,6 +23604,9 @@
       <c r="CE6" t="n">
         <v>17610</v>
       </c>
+      <c r="CF6" t="n">
+        <v>17600</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23489,6 +23862,9 @@
       <c r="CE7" t="n">
         <v>20595</v>
       </c>
+      <c r="CF7" t="n">
+        <v>20695</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23744,6 +24120,9 @@
       <c r="CE8" t="n">
         <v>19700</v>
       </c>
+      <c r="CF8" t="n">
+        <v>19800</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23999,6 +24378,9 @@
       <c r="CE9" t="n">
         <v>1235</v>
       </c>
+      <c r="CF9" t="n">
+        <v>1212</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24254,6 +24636,9 @@
       <c r="CE10" t="n">
         <v>16695</v>
       </c>
+      <c r="CF10" t="n">
+        <v>16625</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24509,6 +24894,9 @@
       <c r="CE11" t="n">
         <v>4930</v>
       </c>
+      <c r="CF11" t="n">
+        <v>4865</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24764,6 +25152,9 @@
       <c r="CE12" t="n">
         <v>5255</v>
       </c>
+      <c r="CF12" t="n">
+        <v>5140</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -25019,6 +25410,9 @@
       <c r="CE13" t="n">
         <v>5350</v>
       </c>
+      <c r="CF13" t="n">
+        <v>5245</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -25274,6 +25668,9 @@
       <c r="CE14" t="n">
         <v>1308</v>
       </c>
+      <c r="CF14" t="n">
+        <v>1286</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -25529,6 +25926,9 @@
       <c r="CE15" t="n">
         <v>19225</v>
       </c>
+      <c r="CF15" t="n">
+        <v>19190</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25784,6 +26184,9 @@
       <c r="CE16" t="n">
         <v>9905</v>
       </c>
+      <c r="CF16" t="n">
+        <v>9770</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -26039,6 +26442,9 @@
       <c r="CE17" t="n">
         <v>5815</v>
       </c>
+      <c r="CF17" t="n">
+        <v>5690</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -26294,6 +26700,9 @@
       <c r="CE18" t="n">
         <v>17870</v>
       </c>
+      <c r="CF18" t="n">
+        <v>17745</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -26548,6 +26957,9 @@
       </c>
       <c r="CE19" t="n">
         <v>15830</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>15760</v>
       </c>
     </row>
   </sheetData>
@@ -26561,7 +26973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE19"/>
+  <dimension ref="A1:CF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26647,6 +27059,7 @@
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
+    <col width="12" customWidth="1" min="84" max="84"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26903,6 +27316,9 @@
       <c r="CE1" s="1" t="n">
         <v>20251229</v>
       </c>
+      <c r="CF1" s="1" t="n">
+        <v>20251230</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27158,6 +27574,9 @@
       <c r="CE2" t="n">
         <v>15475</v>
       </c>
+      <c r="CF2" t="n">
+        <v>15380</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27413,6 +27832,9 @@
       <c r="CE3" t="n">
         <v>60755</v>
       </c>
+      <c r="CF3" t="n">
+        <v>61300</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -27668,6 +28090,9 @@
       <c r="CE4" t="n">
         <v>17980</v>
       </c>
+      <c r="CF4" t="n">
+        <v>17990</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27923,6 +28348,9 @@
       <c r="CE5" t="n">
         <v>16200</v>
       </c>
+      <c r="CF5" t="n">
+        <v>16250</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28178,6 +28606,9 @@
       <c r="CE6" t="n">
         <v>17795</v>
       </c>
+      <c r="CF6" t="n">
+        <v>17925</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28433,6 +28864,9 @@
       <c r="CE7" t="n">
         <v>20830</v>
       </c>
+      <c r="CF7" t="n">
+        <v>20980</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28688,6 +29122,9 @@
       <c r="CE8" t="n">
         <v>19940</v>
       </c>
+      <c r="CF8" t="n">
+        <v>20110</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28943,6 +29380,9 @@
       <c r="CE9" t="n">
         <v>1288</v>
       </c>
+      <c r="CF9" t="n">
+        <v>1219</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -29198,6 +29638,9 @@
       <c r="CE10" t="n">
         <v>16815</v>
       </c>
+      <c r="CF10" t="n">
+        <v>16735</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29453,6 +29896,9 @@
       <c r="CE11" t="n">
         <v>5100</v>
       </c>
+      <c r="CF11" t="n">
+        <v>4905</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29708,6 +30154,9 @@
       <c r="CE12" t="n">
         <v>5445</v>
       </c>
+      <c r="CF12" t="n">
+        <v>5180</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29963,6 +30412,9 @@
       <c r="CE13" t="n">
         <v>5530</v>
       </c>
+      <c r="CF13" t="n">
+        <v>5280</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30218,6 +30670,9 @@
       <c r="CE14" t="n">
         <v>1392</v>
       </c>
+      <c r="CF14" t="n">
+        <v>1298</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -30473,6 +30928,9 @@
       <c r="CE15" t="n">
         <v>19595</v>
       </c>
+      <c r="CF15" t="n">
+        <v>19575</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -30728,6 +31186,9 @@
       <c r="CE16" t="n">
         <v>10215</v>
       </c>
+      <c r="CF16" t="n">
+        <v>9810</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -30983,6 +31444,9 @@
       <c r="CE17" t="n">
         <v>5975</v>
       </c>
+      <c r="CF17" t="n">
+        <v>5720</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -31238,6 +31702,9 @@
       <c r="CE18" t="n">
         <v>18045</v>
       </c>
+      <c r="CF18" t="n">
+        <v>17965</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -31492,6 +31959,9 @@
       </c>
       <c r="CE19" t="n">
         <v>16040</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>16035</v>
       </c>
     </row>
   </sheetData>
@@ -31505,7 +31975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE19"/>
+  <dimension ref="A1:CF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31591,6 +32061,7 @@
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
+    <col width="12" customWidth="1" min="84" max="84"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31847,6 +32318,9 @@
       <c r="CE1" s="1" t="n">
         <v>20251229</v>
       </c>
+      <c r="CF1" s="1" t="n">
+        <v>20251230</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32102,6 +32576,9 @@
       <c r="CE2" t="n">
         <v>118489</v>
       </c>
+      <c r="CF2" t="n">
+        <v>79050</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32357,6 +32834,9 @@
       <c r="CE3" t="n">
         <v>1993001</v>
       </c>
+      <c r="CF3" t="n">
+        <v>1987755</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -32612,6 +33092,9 @@
       <c r="CE4" t="n">
         <v>80785</v>
       </c>
+      <c r="CF4" t="n">
+        <v>111403</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32867,6 +33350,9 @@
       <c r="CE5" t="n">
         <v>298036</v>
       </c>
+      <c r="CF5" t="n">
+        <v>402298</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -33122,6 +33608,9 @@
       <c r="CE6" t="n">
         <v>1475159</v>
       </c>
+      <c r="CF6" t="n">
+        <v>1535549</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -33377,6 +33866,9 @@
       <c r="CE7" t="n">
         <v>6920233</v>
       </c>
+      <c r="CF7" t="n">
+        <v>4510138</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -33632,6 +34124,9 @@
       <c r="CE8" t="n">
         <v>13069790</v>
       </c>
+      <c r="CF8" t="n">
+        <v>6991744</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33887,6 +34382,9 @@
       <c r="CE9" t="n">
         <v>3167394</v>
       </c>
+      <c r="CF9" t="n">
+        <v>4548590</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34142,6 +34640,9 @@
       <c r="CE10" t="n">
         <v>417900</v>
       </c>
+      <c r="CF10" t="n">
+        <v>465247</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -34397,6 +34898,9 @@
       <c r="CE11" t="n">
         <v>609382</v>
       </c>
+      <c r="CF11" t="n">
+        <v>375227</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -34652,6 +35156,9 @@
       <c r="CE12" t="n">
         <v>1814306</v>
       </c>
+      <c r="CF12" t="n">
+        <v>1937868</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34907,6 +35414,9 @@
       <c r="CE13" t="n">
         <v>4403569</v>
       </c>
+      <c r="CF13" t="n">
+        <v>3686700</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35162,6 +35672,9 @@
       <c r="CE14" t="n">
         <v>28148290</v>
       </c>
+      <c r="CF14" t="n">
+        <v>34322840</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35417,6 +35930,9 @@
       <c r="CE15" t="n">
         <v>2016413</v>
       </c>
+      <c r="CF15" t="n">
+        <v>709512</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -35672,6 +36188,9 @@
       <c r="CE16" t="n">
         <v>180376</v>
       </c>
+      <c r="CF16" t="n">
+        <v>290819</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -35927,6 +36446,9 @@
       <c r="CE17" t="n">
         <v>48810</v>
       </c>
+      <c r="CF17" t="n">
+        <v>68711</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36182,6 +36704,9 @@
       <c r="CE18" t="n">
         <v>38763</v>
       </c>
+      <c r="CF18" t="n">
+        <v>38778</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -36436,6 +36961,9 @@
       </c>
       <c r="CE19" t="n">
         <v>30235</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>11434</v>
       </c>
     </row>
   </sheetData>
@@ -36449,7 +36977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL19"/>
+  <dimension ref="A1:BM19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -36516,6 +37044,7 @@
     <col width="10" customWidth="1" min="62" max="62"/>
     <col width="10" customWidth="1" min="63" max="63"/>
     <col width="10" customWidth="1" min="64" max="64"/>
+    <col width="10" customWidth="1" min="65" max="65"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36715,6 +37244,9 @@
       <c r="BL1" s="1" t="n">
         <v>20251229</v>
       </c>
+      <c r="BM1" s="1" t="n">
+        <v>20251230</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -36913,6 +37445,9 @@
       <c r="BL2" t="n">
         <v>49</v>
       </c>
+      <c r="BM2" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37111,6 +37646,9 @@
       <c r="BL3" t="n">
         <v>100</v>
       </c>
+      <c r="BM3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -37309,6 +37847,9 @@
       <c r="BL4" t="n">
         <v>36</v>
       </c>
+      <c r="BM4" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -37507,6 +38048,9 @@
       <c r="BL5" t="n">
         <v>95</v>
       </c>
+      <c r="BM5" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -37705,6 +38249,9 @@
       <c r="BL6" t="n">
         <v>100</v>
       </c>
+      <c r="BM6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -37903,6 +38450,9 @@
       <c r="BL7" t="n">
         <v>100</v>
       </c>
+      <c r="BM7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -38101,6 +38651,9 @@
       <c r="BL8" t="n">
         <v>100</v>
       </c>
+      <c r="BM8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -38299,6 +38852,9 @@
       <c r="BL9" t="n">
         <v>0</v>
       </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -38497,6 +39053,9 @@
       <c r="BL10" t="n">
         <v>54</v>
       </c>
+      <c r="BM10" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -38695,6 +39254,9 @@
       <c r="BL11" t="n">
         <v>5</v>
       </c>
+      <c r="BM11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -38893,6 +39455,9 @@
       <c r="BL12" t="n">
         <v>2</v>
       </c>
+      <c r="BM12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -39091,6 +39656,9 @@
       <c r="BL13" t="n">
         <v>6</v>
       </c>
+      <c r="BM13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39289,6 +39857,9 @@
       <c r="BL14" t="n">
         <v>0</v>
       </c>
+      <c r="BM14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39487,6 +40058,9 @@
       <c r="BL15" t="n">
         <v>55</v>
       </c>
+      <c r="BM15" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -39685,6 +40259,9 @@
       <c r="BL16" t="n">
         <v>4</v>
       </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -39883,6 +40460,9 @@
       <c r="BL17" t="n">
         <v>0</v>
       </c>
+      <c r="BM17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -40081,6 +40661,9 @@
       <c r="BL18" t="n">
         <v>75</v>
       </c>
+      <c r="BM18" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -40278,6 +40861,9 @@
       </c>
       <c r="BL19" t="n">
         <v>33</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -40291,7 +40877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:Y19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -40318,6 +40904,7 @@
     <col width="10" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
     <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40397,6 +40984,9 @@
       <c r="X1" s="1" t="n">
         <v>20251229</v>
       </c>
+      <c r="Y1" s="1" t="n">
+        <v>20251230</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40475,6 +41065,9 @@
       <c r="X2" t="n">
         <v>70</v>
       </c>
+      <c r="Y2" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40553,6 +41146,9 @@
       <c r="X3" t="n">
         <v>98</v>
       </c>
+      <c r="Y3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -40631,6 +41227,9 @@
       <c r="X4" t="n">
         <v>65</v>
       </c>
+      <c r="Y4" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -40709,6 +41308,9 @@
       <c r="X5" t="n">
         <v>71</v>
       </c>
+      <c r="Y5" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -40787,6 +41389,9 @@
       <c r="X6" t="n">
         <v>100</v>
       </c>
+      <c r="Y6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -40865,6 +41470,9 @@
       <c r="X7" t="n">
         <v>100</v>
       </c>
+      <c r="Y7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40943,6 +41551,9 @@
       <c r="X8" t="n">
         <v>100</v>
       </c>
+      <c r="Y8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -41021,6 +41632,9 @@
       <c r="X9" t="n">
         <v>28</v>
       </c>
+      <c r="Y9" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -41099,6 +41713,9 @@
       <c r="X10" t="n">
         <v>63</v>
       </c>
+      <c r="Y10" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -41177,6 +41794,9 @@
       <c r="X11" t="n">
         <v>66</v>
       </c>
+      <c r="Y11" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -41255,6 +41875,9 @@
       <c r="X12" t="n">
         <v>64</v>
       </c>
+      <c r="Y12" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -41333,6 +41956,9 @@
       <c r="X13" t="n">
         <v>67</v>
       </c>
+      <c r="Y13" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -41411,6 +42037,9 @@
       <c r="X14" t="n">
         <v>37</v>
       </c>
+      <c r="Y14" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41489,6 +42118,9 @@
       <c r="X15" t="n">
         <v>86</v>
       </c>
+      <c r="Y15" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -41567,6 +42199,9 @@
       <c r="X16" t="n">
         <v>56</v>
       </c>
+      <c r="Y16" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41645,6 +42280,9 @@
       <c r="X17" t="n">
         <v>52</v>
       </c>
+      <c r="Y17" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41723,6 +42361,9 @@
       <c r="X18" t="n">
         <v>86</v>
       </c>
+      <c r="Y18" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -41799,6 +42440,9 @@
         <v>79</v>
       </c>
       <c r="X19" t="n">
+        <v>83</v>
+      </c>
+      <c r="Y19" t="n">
         <v>83</v>
       </c>
     </row>
@@ -41813,7 +42457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL19"/>
+  <dimension ref="A1:BM19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -41880,6 +42524,7 @@
     <col width="10" customWidth="1" min="62" max="62"/>
     <col width="10" customWidth="1" min="63" max="63"/>
     <col width="10" customWidth="1" min="64" max="64"/>
+    <col width="10" customWidth="1" min="65" max="65"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -42079,6 +42724,9 @@
       <c r="BL1" s="1" t="n">
         <v>20251229</v>
       </c>
+      <c r="BM1" s="1" t="n">
+        <v>20251230</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -42277,6 +42925,9 @@
       <c r="BL2" t="n">
         <v>7</v>
       </c>
+      <c r="BM2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -42475,6 +43126,9 @@
       <c r="BL3" t="n">
         <v>119</v>
       </c>
+      <c r="BM3" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -42673,6 +43327,9 @@
       <c r="BL4" t="n">
         <v>-7</v>
       </c>
+      <c r="BM4" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -42871,6 +43528,9 @@
       <c r="BL5" t="n">
         <v>52</v>
       </c>
+      <c r="BM5" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -43069,6 +43729,9 @@
       <c r="BL6" t="n">
         <v>106</v>
       </c>
+      <c r="BM6" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -43267,6 +43930,9 @@
       <c r="BL7" t="n">
         <v>126</v>
       </c>
+      <c r="BM7" t="n">
+        <v>115</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -43465,6 +44131,9 @@
       <c r="BL8" t="n">
         <v>129</v>
       </c>
+      <c r="BM8" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -43663,6 +44332,9 @@
       <c r="BL9" t="n">
         <v>-68</v>
       </c>
+      <c r="BM9" t="n">
+        <v>-83</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -43861,6 +44533,9 @@
       <c r="BL10" t="n">
         <v>-2</v>
       </c>
+      <c r="BM10" t="n">
+        <v>-6</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -44059,6 +44734,9 @@
       <c r="BL11" t="n">
         <v>-53</v>
       </c>
+      <c r="BM11" t="n">
+        <v>-82</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -44257,6 +44935,9 @@
       <c r="BL12" t="n">
         <v>-55</v>
       </c>
+      <c r="BM12" t="n">
+        <v>-86</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -44455,6 +45136,9 @@
       <c r="BL13" t="n">
         <v>-47</v>
       </c>
+      <c r="BM13" t="n">
+        <v>-78</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -44653,6 +45337,9 @@
       <c r="BL14" t="n">
         <v>-65</v>
       </c>
+      <c r="BM14" t="n">
+        <v>-83</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -44851,6 +45538,9 @@
       <c r="BL15" t="n">
         <v>20</v>
       </c>
+      <c r="BM15" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -45049,6 +45739,9 @@
       <c r="BL16" t="n">
         <v>-58</v>
       </c>
+      <c r="BM16" t="n">
+        <v>-85</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -45247,6 +45940,9 @@
       <c r="BL17" t="n">
         <v>-66</v>
       </c>
+      <c r="BM17" t="n">
+        <v>-90</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -45445,6 +46141,9 @@
       <c r="BL18" t="n">
         <v>18</v>
       </c>
+      <c r="BM18" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -45642,6 +46341,9 @@
       </c>
       <c r="BL19" t="n">
         <v>-15</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>-11</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -32577,7 +32577,7 @@
         <v>118489</v>
       </c>
       <c r="CF2" t="n">
-        <v>79050</v>
+        <v>79055</v>
       </c>
     </row>
     <row r="3">
@@ -32835,7 +32835,7 @@
         <v>1993001</v>
       </c>
       <c r="CF3" t="n">
-        <v>1987755</v>
+        <v>1989357</v>
       </c>
     </row>
     <row r="4">
@@ -33093,7 +33093,7 @@
         <v>80785</v>
       </c>
       <c r="CF4" t="n">
-        <v>111403</v>
+        <v>111473</v>
       </c>
     </row>
     <row r="5">
@@ -33351,7 +33351,7 @@
         <v>298036</v>
       </c>
       <c r="CF5" t="n">
-        <v>402298</v>
+        <v>405157</v>
       </c>
     </row>
     <row r="6">
@@ -33609,7 +33609,7 @@
         <v>1475159</v>
       </c>
       <c r="CF6" t="n">
-        <v>1535549</v>
+        <v>1537147</v>
       </c>
     </row>
     <row r="7">
@@ -33867,7 +33867,7 @@
         <v>6920233</v>
       </c>
       <c r="CF7" t="n">
-        <v>4510138</v>
+        <v>4511027</v>
       </c>
     </row>
     <row r="8">
@@ -34125,7 +34125,7 @@
         <v>13069790</v>
       </c>
       <c r="CF8" t="n">
-        <v>6991744</v>
+        <v>7257620</v>
       </c>
     </row>
     <row r="9">
@@ -34383,7 +34383,7 @@
         <v>3167394</v>
       </c>
       <c r="CF9" t="n">
-        <v>4548590</v>
+        <v>4550477</v>
       </c>
     </row>
     <row r="10">
@@ -34641,7 +34641,7 @@
         <v>417900</v>
       </c>
       <c r="CF10" t="n">
-        <v>465247</v>
+        <v>466016</v>
       </c>
     </row>
     <row r="11">
@@ -34899,7 +34899,7 @@
         <v>609382</v>
       </c>
       <c r="CF11" t="n">
-        <v>375227</v>
+        <v>375300</v>
       </c>
     </row>
     <row r="12">
@@ -35157,7 +35157,7 @@
         <v>1814306</v>
       </c>
       <c r="CF12" t="n">
-        <v>1937868</v>
+        <v>1938194</v>
       </c>
     </row>
     <row r="13">
@@ -35415,7 +35415,7 @@
         <v>4403569</v>
       </c>
       <c r="CF13" t="n">
-        <v>3686700</v>
+        <v>3693011</v>
       </c>
     </row>
     <row r="14">
@@ -35673,7 +35673,7 @@
         <v>28148290</v>
       </c>
       <c r="CF14" t="n">
-        <v>34322840</v>
+        <v>34437364</v>
       </c>
     </row>
     <row r="15">
@@ -35931,7 +35931,7 @@
         <v>2016413</v>
       </c>
       <c r="CF15" t="n">
-        <v>709512</v>
+        <v>709730</v>
       </c>
     </row>
     <row r="16">
@@ -36189,7 +36189,7 @@
         <v>180376</v>
       </c>
       <c r="CF16" t="n">
-        <v>290819</v>
+        <v>290953</v>
       </c>
     </row>
     <row r="17">
@@ -36447,7 +36447,7 @@
         <v>48810</v>
       </c>
       <c r="CF17" t="n">
-        <v>68711</v>
+        <v>68740</v>
       </c>
     </row>
     <row r="18">

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y19"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -737,6 +737,7 @@
     <col width="10" customWidth="1" min="23" max="23"/>
     <col width="10" customWidth="1" min="24" max="24"/>
     <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -819,6 +820,9 @@
       <c r="Y1" s="1" t="n">
         <v>20251230</v>
       </c>
+      <c r="Z1" s="1" t="n">
+        <v>20260102</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -900,6 +904,9 @@
       <c r="Y2" t="n">
         <v>27</v>
       </c>
+      <c r="Z2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -981,6 +988,9 @@
       <c r="Y3" t="n">
         <v>83</v>
       </c>
+      <c r="Z3" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1062,6 +1072,9 @@
       <c r="Y4" t="n">
         <v>23</v>
       </c>
+      <c r="Z4" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1143,6 +1156,9 @@
       <c r="Y5" t="n">
         <v>22</v>
       </c>
+      <c r="Z5" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1224,6 +1240,9 @@
       <c r="Y6" t="n">
         <v>75</v>
       </c>
+      <c r="Z6" t="n">
+        <v>130</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1305,6 +1324,9 @@
       <c r="Y7" t="n">
         <v>89</v>
       </c>
+      <c r="Z7" t="n">
+        <v>141</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1386,6 +1408,9 @@
       <c r="Y8" t="n">
         <v>94</v>
       </c>
+      <c r="Z8" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1467,6 +1492,9 @@
       <c r="Y9" t="n">
         <v>-62</v>
       </c>
+      <c r="Z9" t="n">
+        <v>-75</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1548,6 +1576,9 @@
       <c r="Y10" t="n">
         <v>-5</v>
       </c>
+      <c r="Z10" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1629,6 +1660,9 @@
       <c r="Y11" t="n">
         <v>-21</v>
       </c>
+      <c r="Z11" t="n">
+        <v>-38</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1710,6 +1744,9 @@
       <c r="Y12" t="n">
         <v>-26</v>
       </c>
+      <c r="Z12" t="n">
+        <v>-42</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1791,6 +1828,9 @@
       <c r="Y13" t="n">
         <v>-15</v>
       </c>
+      <c r="Z13" t="n">
+        <v>-33</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1872,6 +1912,9 @@
       <c r="Y14" t="n">
         <v>-54</v>
       </c>
+      <c r="Z14" t="n">
+        <v>-68</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1953,6 +1996,9 @@
       <c r="Y15" t="n">
         <v>49</v>
       </c>
+      <c r="Z15" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2034,6 +2080,9 @@
       <c r="Y16" t="n">
         <v>-35</v>
       </c>
+      <c r="Z16" t="n">
+        <v>-51</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2115,6 +2164,9 @@
       <c r="Y17" t="n">
         <v>-41</v>
       </c>
+      <c r="Z17" t="n">
+        <v>-57</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2196,6 +2248,9 @@
       <c r="Y18" t="n">
         <v>33</v>
       </c>
+      <c r="Z18" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2276,6 +2331,9 @@
       </c>
       <c r="Y19" t="n">
         <v>43</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2289,7 +2347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM19"/>
+  <dimension ref="A1:BN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2357,6 +2415,7 @@
     <col width="12" customWidth="1" min="63" max="63"/>
     <col width="12" customWidth="1" min="64" max="64"/>
     <col width="12" customWidth="1" min="65" max="65"/>
+    <col width="12" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2685,6 +2744,11 @@
           <t>20251230</t>
         </is>
       </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>20260102</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2886,6 +2950,9 @@
       <c r="BM2" t="n">
         <v>100</v>
       </c>
+      <c r="BN2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3087,6 +3154,9 @@
       <c r="BM3" t="n">
         <v>107</v>
       </c>
+      <c r="BN3" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3288,6 +3358,9 @@
       <c r="BM4" t="n">
         <v>100</v>
       </c>
+      <c r="BN4" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3489,6 +3562,9 @@
       <c r="BM5" t="n">
         <v>103</v>
       </c>
+      <c r="BN5" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3690,6 +3766,9 @@
       <c r="BM6" t="n">
         <v>106</v>
       </c>
+      <c r="BN6" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3891,6 +3970,9 @@
       <c r="BM7" t="n">
         <v>107</v>
       </c>
+      <c r="BN7" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4092,6 +4174,9 @@
       <c r="BM8" t="n">
         <v>108</v>
       </c>
+      <c r="BN8" t="n">
+        <v>115</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4293,6 +4378,9 @@
       <c r="BM9" t="n">
         <v>84</v>
       </c>
+      <c r="BN9" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4494,6 +4582,9 @@
       <c r="BM10" t="n">
         <v>100</v>
       </c>
+      <c r="BN10" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4695,6 +4786,9 @@
       <c r="BM11" t="n">
         <v>92</v>
       </c>
+      <c r="BN11" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4896,6 +4990,9 @@
       <c r="BM12" t="n">
         <v>90</v>
       </c>
+      <c r="BN12" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5097,6 +5194,9 @@
       <c r="BM13" t="n">
         <v>91</v>
       </c>
+      <c r="BN13" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5298,6 +5398,9 @@
       <c r="BM14" t="n">
         <v>82</v>
       </c>
+      <c r="BN14" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5499,6 +5602,9 @@
       <c r="BM15" t="n">
         <v>101</v>
       </c>
+      <c r="BN15" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5700,6 +5806,9 @@
       <c r="BM16" t="n">
         <v>91</v>
       </c>
+      <c r="BN16" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5901,6 +6010,9 @@
       <c r="BM17" t="n">
         <v>90</v>
       </c>
+      <c r="BN17" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6102,6 +6214,9 @@
       <c r="BM18" t="n">
         <v>101</v>
       </c>
+      <c r="BN18" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6302,6 +6417,9 @@
       </c>
       <c r="BM19" t="n">
         <v>100</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -10341,7 +10459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y19"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10369,6 +10487,7 @@
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10497,6 +10616,11 @@
           <t>20251230</t>
         </is>
       </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>20260102</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10578,6 +10702,9 @@
       <c r="Y2" t="n">
         <v>31</v>
       </c>
+      <c r="Z2" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10659,6 +10786,9 @@
       <c r="Y3" t="n">
         <v>43</v>
       </c>
+      <c r="Z3" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10740,6 +10870,9 @@
       <c r="Y4" t="n">
         <v>32</v>
       </c>
+      <c r="Z4" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10821,6 +10954,9 @@
       <c r="Y5" t="n">
         <v>27</v>
       </c>
+      <c r="Z5" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10902,6 +11038,9 @@
       <c r="Y6" t="n">
         <v>38</v>
       </c>
+      <c r="Z6" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10983,6 +11122,9 @@
       <c r="Y7" t="n">
         <v>57</v>
       </c>
+      <c r="Z7" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11064,6 +11206,9 @@
       <c r="Y8" t="n">
         <v>48</v>
       </c>
+      <c r="Z8" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11145,6 +11290,9 @@
       <c r="Y9" t="n">
         <v>30</v>
       </c>
+      <c r="Z9" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11226,6 +11374,9 @@
       <c r="Y10" t="n">
         <v>18</v>
       </c>
+      <c r="Z10" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11307,6 +11458,9 @@
       <c r="Y11" t="n">
         <v>14</v>
       </c>
+      <c r="Z11" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11388,6 +11542,9 @@
       <c r="Y12" t="n">
         <v>32</v>
       </c>
+      <c r="Z12" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11469,6 +11626,9 @@
       <c r="Y13" t="n">
         <v>26</v>
       </c>
+      <c r="Z13" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11550,6 +11710,9 @@
       <c r="Y14" t="n">
         <v>33</v>
       </c>
+      <c r="Z14" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11631,6 +11794,9 @@
       <c r="Y15" t="n">
         <v>21</v>
       </c>
+      <c r="Z15" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11712,6 +11878,9 @@
       <c r="Y16" t="n">
         <v>23</v>
       </c>
+      <c r="Z16" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11793,6 +11962,9 @@
       <c r="Y17" t="n">
         <v>14</v>
       </c>
+      <c r="Z17" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11874,6 +12046,9 @@
       <c r="Y18" t="n">
         <v>11</v>
       </c>
+      <c r="Z18" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11954,6 +12129,9 @@
       </c>
       <c r="Y19" t="n">
         <v>12</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -11967,7 +12145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF19"/>
+  <dimension ref="A1:CG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12054,6 +12232,7 @@
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
+    <col width="12" customWidth="1" min="85" max="85"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12313,6 +12492,9 @@
       <c r="CF1" s="1" t="n">
         <v>20251230</v>
       </c>
+      <c r="CG1" s="1" t="n">
+        <v>20260102</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12571,6 +12753,9 @@
       <c r="CF2" t="n">
         <v>15540</v>
       </c>
+      <c r="CG2" t="n">
+        <v>15390</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12829,6 +13014,9 @@
       <c r="CF3" t="n">
         <v>60735</v>
       </c>
+      <c r="CG3" t="n">
+        <v>61355</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13087,6 +13275,9 @@
       <c r="CF4" t="n">
         <v>17980</v>
       </c>
+      <c r="CG4" t="n">
+        <v>18055</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13345,6 +13536,9 @@
       <c r="CF5" t="n">
         <v>16150</v>
       </c>
+      <c r="CG5" t="n">
+        <v>16375</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13603,6 +13797,9 @@
       <c r="CF6" t="n">
         <v>17750</v>
       </c>
+      <c r="CG6" t="n">
+        <v>17925</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13861,6 +14058,9 @@
       <c r="CF7" t="n">
         <v>20800</v>
       </c>
+      <c r="CG7" t="n">
+        <v>20990</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14119,6 +14319,9 @@
       <c r="CF8" t="n">
         <v>19945</v>
       </c>
+      <c r="CG8" t="n">
+        <v>20140</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14377,6 +14580,9 @@
       <c r="CF9" t="n">
         <v>1276</v>
       </c>
+      <c r="CG9" t="n">
+        <v>1206</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14635,6 +14841,9 @@
       <c r="CF10" t="n">
         <v>16755</v>
       </c>
+      <c r="CG10" t="n">
+        <v>16820</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14893,6 +15102,9 @@
       <c r="CF11" t="n">
         <v>5025</v>
       </c>
+      <c r="CG11" t="n">
+        <v>4865</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15151,6 +15363,9 @@
       <c r="CF12" t="n">
         <v>5340</v>
       </c>
+      <c r="CG12" t="n">
+        <v>5110</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15409,6 +15624,9 @@
       <c r="CF13" t="n">
         <v>5455</v>
       </c>
+      <c r="CG13" t="n">
+        <v>5225</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -15667,6 +15885,9 @@
       <c r="CF14" t="n">
         <v>1361</v>
       </c>
+      <c r="CG14" t="n">
+        <v>1290</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15925,6 +16146,9 @@
       <c r="CF15" t="n">
         <v>19580</v>
       </c>
+      <c r="CG15" t="n">
+        <v>19570</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -16183,6 +16407,9 @@
       <c r="CF16" t="n">
         <v>10110</v>
       </c>
+      <c r="CG16" t="n">
+        <v>9750</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16441,6 +16668,9 @@
       <c r="CF17" t="n">
         <v>5890</v>
       </c>
+      <c r="CG17" t="n">
+        <v>5660</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16699,6 +16929,9 @@
       <c r="CF18" t="n">
         <v>17890</v>
       </c>
+      <c r="CG18" t="n">
+        <v>17925</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -16956,6 +17189,9 @@
       </c>
       <c r="CF19" t="n">
         <v>16105</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>16075</v>
       </c>
     </row>
   </sheetData>
@@ -16969,7 +17205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF19"/>
+  <dimension ref="A1:CG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17056,6 +17292,7 @@
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
+    <col width="12" customWidth="1" min="85" max="85"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17315,6 +17552,9 @@
       <c r="CF1" s="1" t="n">
         <v>20251230</v>
       </c>
+      <c r="CG1" s="1" t="n">
+        <v>20260102</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17573,6 +17813,9 @@
       <c r="CF2" t="n">
         <v>15545</v>
       </c>
+      <c r="CG2" t="n">
+        <v>15600</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17831,6 +18074,9 @@
       <c r="CF3" t="n">
         <v>61700</v>
       </c>
+      <c r="CG3" t="n">
+        <v>65520</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18089,6 +18335,9 @@
       <c r="CF4" t="n">
         <v>18130</v>
       </c>
+      <c r="CG4" t="n">
+        <v>18390</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18347,6 +18596,9 @@
       <c r="CF5" t="n">
         <v>16480</v>
       </c>
+      <c r="CG5" t="n">
+        <v>17170</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18605,6 +18857,9 @@
       <c r="CF6" t="n">
         <v>17980</v>
       </c>
+      <c r="CG6" t="n">
+        <v>19060</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18863,6 +19118,9 @@
       <c r="CF7" t="n">
         <v>21075</v>
       </c>
+      <c r="CG7" t="n">
+        <v>22385</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19121,6 +19379,9 @@
       <c r="CF8" t="n">
         <v>20260</v>
       </c>
+      <c r="CG8" t="n">
+        <v>21645</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19379,6 +19640,9 @@
       <c r="CF9" t="n">
         <v>1279</v>
       </c>
+      <c r="CG9" t="n">
+        <v>1215</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19637,6 +19901,9 @@
       <c r="CF10" t="n">
         <v>16895</v>
       </c>
+      <c r="CG10" t="n">
+        <v>17965</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -19895,6 +20162,9 @@
       <c r="CF11" t="n">
         <v>5025</v>
       </c>
+      <c r="CG11" t="n">
+        <v>4865</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -20153,6 +20423,9 @@
       <c r="CF12" t="n">
         <v>5340</v>
       </c>
+      <c r="CG12" t="n">
+        <v>5140</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -20411,6 +20684,9 @@
       <c r="CF13" t="n">
         <v>5460</v>
       </c>
+      <c r="CG13" t="n">
+        <v>5230</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -20669,6 +20945,9 @@
       <c r="CF14" t="n">
         <v>1370</v>
       </c>
+      <c r="CG14" t="n">
+        <v>1290</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -20927,6 +21206,9 @@
       <c r="CF15" t="n">
         <v>19655</v>
       </c>
+      <c r="CG15" t="n">
+        <v>19685</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -21185,6 +21467,9 @@
       <c r="CF16" t="n">
         <v>10110</v>
       </c>
+      <c r="CG16" t="n">
+        <v>9780</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -21443,6 +21728,9 @@
       <c r="CF17" t="n">
         <v>5970</v>
       </c>
+      <c r="CG17" t="n">
+        <v>5665</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -21701,6 +21989,9 @@
       <c r="CF18" t="n">
         <v>18035</v>
       </c>
+      <c r="CG18" t="n">
+        <v>19130</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -21958,6 +22249,9 @@
       </c>
       <c r="CF19" t="n">
         <v>16115</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>16185</v>
       </c>
     </row>
   </sheetData>
@@ -21971,7 +22265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF19"/>
+  <dimension ref="A1:CG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22058,6 +22352,7 @@
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
+    <col width="12" customWidth="1" min="85" max="85"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22317,6 +22612,9 @@
       <c r="CF1" s="1" t="n">
         <v>20251230</v>
       </c>
+      <c r="CG1" s="1" t="n">
+        <v>20260102</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22575,6 +22873,9 @@
       <c r="CF2" t="n">
         <v>15150</v>
       </c>
+      <c r="CG2" t="n">
+        <v>15100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22833,6 +23134,9 @@
       <c r="CF3" t="n">
         <v>60245</v>
       </c>
+      <c r="CG3" t="n">
+        <v>61355</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23091,6 +23395,9 @@
       <c r="CF4" t="n">
         <v>17770</v>
       </c>
+      <c r="CG4" t="n">
+        <v>18050</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23349,6 +23656,9 @@
       <c r="CF5" t="n">
         <v>16060</v>
       </c>
+      <c r="CG5" t="n">
+        <v>16275</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23607,6 +23917,9 @@
       <c r="CF6" t="n">
         <v>17600</v>
       </c>
+      <c r="CG6" t="n">
+        <v>17885</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23865,6 +24178,9 @@
       <c r="CF7" t="n">
         <v>20695</v>
       </c>
+      <c r="CG7" t="n">
+        <v>20990</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24123,6 +24439,9 @@
       <c r="CF8" t="n">
         <v>19800</v>
       </c>
+      <c r="CG8" t="n">
+        <v>20140</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24381,6 +24700,9 @@
       <c r="CF9" t="n">
         <v>1212</v>
       </c>
+      <c r="CG9" t="n">
+        <v>1160</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24639,6 +24961,9 @@
       <c r="CF10" t="n">
         <v>16625</v>
       </c>
+      <c r="CG10" t="n">
+        <v>16745</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24897,6 +25222,9 @@
       <c r="CF11" t="n">
         <v>4865</v>
       </c>
+      <c r="CG11" t="n">
+        <v>4730</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25155,6 +25483,9 @@
       <c r="CF12" t="n">
         <v>5140</v>
       </c>
+      <c r="CG12" t="n">
+        <v>5005</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -25413,6 +25744,9 @@
       <c r="CF13" t="n">
         <v>5245</v>
       </c>
+      <c r="CG13" t="n">
+        <v>5085</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -25671,6 +26005,9 @@
       <c r="CF14" t="n">
         <v>1286</v>
       </c>
+      <c r="CG14" t="n">
+        <v>1218</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -25929,6 +26266,9 @@
       <c r="CF15" t="n">
         <v>19190</v>
       </c>
+      <c r="CG15" t="n">
+        <v>19080</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -26187,6 +26527,9 @@
       <c r="CF16" t="n">
         <v>9770</v>
       </c>
+      <c r="CG16" t="n">
+        <v>9535</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -26445,6 +26788,9 @@
       <c r="CF17" t="n">
         <v>5690</v>
       </c>
+      <c r="CG17" t="n">
+        <v>5540</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -26703,6 +27049,9 @@
       <c r="CF18" t="n">
         <v>17745</v>
       </c>
+      <c r="CG18" t="n">
+        <v>17920</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -26960,6 +27309,9 @@
       </c>
       <c r="CF19" t="n">
         <v>15760</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>15875</v>
       </c>
     </row>
   </sheetData>
@@ -26973,7 +27325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF19"/>
+  <dimension ref="A1:CG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27060,6 +27412,7 @@
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
+    <col width="12" customWidth="1" min="85" max="85"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27319,6 +27672,9 @@
       <c r="CF1" s="1" t="n">
         <v>20251230</v>
       </c>
+      <c r="CG1" s="1" t="n">
+        <v>20260102</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27577,6 +27933,9 @@
       <c r="CF2" t="n">
         <v>15380</v>
       </c>
+      <c r="CG2" t="n">
+        <v>15205</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27835,6 +28194,9 @@
       <c r="CF3" t="n">
         <v>61300</v>
       </c>
+      <c r="CG3" t="n">
+        <v>65480</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28093,6 +28455,9 @@
       <c r="CF4" t="n">
         <v>17990</v>
       </c>
+      <c r="CG4" t="n">
+        <v>18150</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28351,6 +28716,9 @@
       <c r="CF5" t="n">
         <v>16250</v>
       </c>
+      <c r="CG5" t="n">
+        <v>17140</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28609,6 +28977,9 @@
       <c r="CF6" t="n">
         <v>17925</v>
       </c>
+      <c r="CG6" t="n">
+        <v>19060</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28867,6 +29238,9 @@
       <c r="CF7" t="n">
         <v>20980</v>
       </c>
+      <c r="CG7" t="n">
+        <v>22385</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29125,6 +29499,9 @@
       <c r="CF8" t="n">
         <v>20110</v>
       </c>
+      <c r="CG8" t="n">
+        <v>21645</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29383,6 +29760,9 @@
       <c r="CF9" t="n">
         <v>1219</v>
       </c>
+      <c r="CG9" t="n">
+        <v>1167</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -29641,6 +30021,9 @@
       <c r="CF10" t="n">
         <v>16735</v>
       </c>
+      <c r="CG10" t="n">
+        <v>17965</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29899,6 +30282,9 @@
       <c r="CF11" t="n">
         <v>4905</v>
       </c>
+      <c r="CG11" t="n">
+        <v>4755</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30157,6 +30543,9 @@
       <c r="CF12" t="n">
         <v>5180</v>
       </c>
+      <c r="CG12" t="n">
+        <v>5020</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30415,6 +30804,9 @@
       <c r="CF13" t="n">
         <v>5280</v>
       </c>
+      <c r="CG13" t="n">
+        <v>5090</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30673,6 +31065,9 @@
       <c r="CF14" t="n">
         <v>1298</v>
       </c>
+      <c r="CG14" t="n">
+        <v>1232</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -30931,6 +31326,9 @@
       <c r="CF15" t="n">
         <v>19575</v>
       </c>
+      <c r="CG15" t="n">
+        <v>19185</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -31189,6 +31587,9 @@
       <c r="CF16" t="n">
         <v>9810</v>
       </c>
+      <c r="CG16" t="n">
+        <v>9565</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -31447,6 +31848,9 @@
       <c r="CF17" t="n">
         <v>5720</v>
       </c>
+      <c r="CG17" t="n">
+        <v>5565</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -31705,6 +32109,9 @@
       <c r="CF18" t="n">
         <v>17965</v>
       </c>
+      <c r="CG18" t="n">
+        <v>19130</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -31962,6 +32369,9 @@
       </c>
       <c r="CF19" t="n">
         <v>16035</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>15975</v>
       </c>
     </row>
   </sheetData>
@@ -31975,7 +32385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF19"/>
+  <dimension ref="A1:CG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -32062,6 +32472,7 @@
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
+    <col width="12" customWidth="1" min="85" max="85"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32321,6 +32732,9 @@
       <c r="CF1" s="1" t="n">
         <v>20251230</v>
       </c>
+      <c r="CG1" s="1" t="n">
+        <v>20260102</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32579,6 +32993,9 @@
       <c r="CF2" t="n">
         <v>79055</v>
       </c>
+      <c r="CG2" t="n">
+        <v>113541</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32837,6 +33254,9 @@
       <c r="CF3" t="n">
         <v>1989357</v>
       </c>
+      <c r="CG3" t="n">
+        <v>3119559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -33095,6 +33515,9 @@
       <c r="CF4" t="n">
         <v>111473</v>
       </c>
+      <c r="CG4" t="n">
+        <v>121182</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -33353,6 +33776,9 @@
       <c r="CF5" t="n">
         <v>405157</v>
       </c>
+      <c r="CG5" t="n">
+        <v>1333840</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -33611,6 +34037,9 @@
       <c r="CF6" t="n">
         <v>1537147</v>
       </c>
+      <c r="CG6" t="n">
+        <v>4343698</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -33869,6 +34298,9 @@
       <c r="CF7" t="n">
         <v>4511027</v>
       </c>
+      <c r="CG7" t="n">
+        <v>7404354</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -34127,6 +34559,9 @@
       <c r="CF8" t="n">
         <v>7257620</v>
       </c>
+      <c r="CG8" t="n">
+        <v>12239343</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -34385,6 +34820,9 @@
       <c r="CF9" t="n">
         <v>4550477</v>
       </c>
+      <c r="CG9" t="n">
+        <v>4443741</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34643,6 +35081,9 @@
       <c r="CF10" t="n">
         <v>466016</v>
       </c>
+      <c r="CG10" t="n">
+        <v>2074169</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -34901,6 +35342,9 @@
       <c r="CF11" t="n">
         <v>375300</v>
       </c>
+      <c r="CG11" t="n">
+        <v>677293</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -35159,6 +35603,9 @@
       <c r="CF12" t="n">
         <v>1938194</v>
       </c>
+      <c r="CG12" t="n">
+        <v>1971626</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35417,6 +35864,9 @@
       <c r="CF13" t="n">
         <v>3693011</v>
       </c>
+      <c r="CG13" t="n">
+        <v>5229924</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35675,6 +36125,9 @@
       <c r="CF14" t="n">
         <v>34437364</v>
       </c>
+      <c r="CG14" t="n">
+        <v>35153489</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35933,6 +36386,9 @@
       <c r="CF15" t="n">
         <v>709730</v>
       </c>
+      <c r="CG15" t="n">
+        <v>1219236</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -36191,6 +36647,9 @@
       <c r="CF16" t="n">
         <v>290953</v>
       </c>
+      <c r="CG16" t="n">
+        <v>315686</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36449,6 +36908,9 @@
       <c r="CF17" t="n">
         <v>68740</v>
       </c>
+      <c r="CG17" t="n">
+        <v>95990</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36707,6 +37169,9 @@
       <c r="CF18" t="n">
         <v>38778</v>
       </c>
+      <c r="CG18" t="n">
+        <v>103462</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -36964,6 +37429,9 @@
       </c>
       <c r="CF19" t="n">
         <v>11434</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>22784</v>
       </c>
     </row>
   </sheetData>
@@ -36977,7 +37445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM19"/>
+  <dimension ref="A1:BN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37045,6 +37513,7 @@
     <col width="10" customWidth="1" min="63" max="63"/>
     <col width="10" customWidth="1" min="64" max="64"/>
     <col width="10" customWidth="1" min="65" max="65"/>
+    <col width="10" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37247,6 +37716,9 @@
       <c r="BM1" s="1" t="n">
         <v>20251230</v>
       </c>
+      <c r="BN1" s="1" t="n">
+        <v>20260102</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37448,6 +37920,9 @@
       <c r="BM2" t="n">
         <v>44</v>
       </c>
+      <c r="BN2" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37649,6 +38124,9 @@
       <c r="BM3" t="n">
         <v>100</v>
       </c>
+      <c r="BN3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -37850,6 +38328,9 @@
       <c r="BM4" t="n">
         <v>38</v>
       </c>
+      <c r="BN4" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -38051,6 +38532,9 @@
       <c r="BM5" t="n">
         <v>98</v>
       </c>
+      <c r="BN5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -38252,6 +38736,9 @@
       <c r="BM6" t="n">
         <v>100</v>
       </c>
+      <c r="BN6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -38453,6 +38940,9 @@
       <c r="BM7" t="n">
         <v>100</v>
       </c>
+      <c r="BN7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -38654,6 +39144,9 @@
       <c r="BM8" t="n">
         <v>100</v>
       </c>
+      <c r="BN8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -38855,6 +39348,9 @@
       <c r="BM9" t="n">
         <v>0</v>
       </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -39056,6 +39552,9 @@
       <c r="BM10" t="n">
         <v>49</v>
       </c>
+      <c r="BN10" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -39257,6 +39756,9 @@
       <c r="BM11" t="n">
         <v>0</v>
       </c>
+      <c r="BN11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -39458,6 +39960,9 @@
       <c r="BM12" t="n">
         <v>0</v>
       </c>
+      <c r="BN12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -39659,6 +40164,9 @@
       <c r="BM13" t="n">
         <v>0</v>
       </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39860,6 +40368,9 @@
       <c r="BM14" t="n">
         <v>0</v>
       </c>
+      <c r="BN14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -40061,6 +40572,9 @@
       <c r="BM15" t="n">
         <v>54</v>
       </c>
+      <c r="BN15" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -40262,6 +40776,9 @@
       <c r="BM16" t="n">
         <v>0</v>
       </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -40463,6 +40980,9 @@
       <c r="BM17" t="n">
         <v>0</v>
       </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -40664,6 +41184,9 @@
       <c r="BM18" t="n">
         <v>71</v>
       </c>
+      <c r="BN18" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -40864,6 +41387,9 @@
       </c>
       <c r="BM19" t="n">
         <v>36</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -40877,7 +41403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y19"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -40905,6 +41431,7 @@
     <col width="10" customWidth="1" min="23" max="23"/>
     <col width="10" customWidth="1" min="24" max="24"/>
     <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40987,6 +41514,9 @@
       <c r="Y1" s="1" t="n">
         <v>20251230</v>
       </c>
+      <c r="Z1" s="1" t="n">
+        <v>20260102</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -41068,6 +41598,9 @@
       <c r="Y2" t="n">
         <v>68</v>
       </c>
+      <c r="Z2" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -41149,6 +41682,9 @@
       <c r="Y3" t="n">
         <v>100</v>
       </c>
+      <c r="Z3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -41230,6 +41766,9 @@
       <c r="Y4" t="n">
         <v>65</v>
       </c>
+      <c r="Z4" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -41311,6 +41850,9 @@
       <c r="Y5" t="n">
         <v>72</v>
       </c>
+      <c r="Z5" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -41392,6 +41934,9 @@
       <c r="Y6" t="n">
         <v>100</v>
       </c>
+      <c r="Z6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -41473,6 +42018,9 @@
       <c r="Y7" t="n">
         <v>100</v>
       </c>
+      <c r="Z7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -41554,6 +42102,9 @@
       <c r="Y8" t="n">
         <v>100</v>
       </c>
+      <c r="Z8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -41635,6 +42186,9 @@
       <c r="Y9" t="n">
         <v>21</v>
       </c>
+      <c r="Z9" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -41716,6 +42270,9 @@
       <c r="Y10" t="n">
         <v>61</v>
       </c>
+      <c r="Z10" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -41797,6 +42354,9 @@
       <c r="Y11" t="n">
         <v>57</v>
       </c>
+      <c r="Z11" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -41878,6 +42438,9 @@
       <c r="Y12" t="n">
         <v>53</v>
       </c>
+      <c r="Z12" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -41959,6 +42522,9 @@
       <c r="Y13" t="n">
         <v>57</v>
       </c>
+      <c r="Z13" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -42040,6 +42606,9 @@
       <c r="Y14" t="n">
         <v>28</v>
       </c>
+      <c r="Z14" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42121,6 +42690,9 @@
       <c r="Y15" t="n">
         <v>86</v>
       </c>
+      <c r="Z15" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -42202,6 +42774,9 @@
       <c r="Y16" t="n">
         <v>46</v>
       </c>
+      <c r="Z16" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42283,6 +42858,9 @@
       <c r="Y17" t="n">
         <v>42</v>
       </c>
+      <c r="Z17" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42364,6 +42942,9 @@
       <c r="Y18" t="n">
         <v>85</v>
       </c>
+      <c r="Z18" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42444,6 +43025,9 @@
       </c>
       <c r="Y19" t="n">
         <v>83</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -42457,7 +43041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM19"/>
+  <dimension ref="A1:BN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -42525,6 +43109,7 @@
     <col width="10" customWidth="1" min="63" max="63"/>
     <col width="10" customWidth="1" min="64" max="64"/>
     <col width="10" customWidth="1" min="65" max="65"/>
+    <col width="10" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -42727,6 +43312,9 @@
       <c r="BM1" s="1" t="n">
         <v>20251230</v>
       </c>
+      <c r="BN1" s="1" t="n">
+        <v>20260102</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -42928,6 +43516,9 @@
       <c r="BM2" t="n">
         <v>3</v>
       </c>
+      <c r="BN2" t="n">
+        <v>-9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -43129,6 +43720,9 @@
       <c r="BM3" t="n">
         <v>111</v>
       </c>
+      <c r="BN3" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -43330,6 +43924,9 @@
       <c r="BM4" t="n">
         <v>-1</v>
       </c>
+      <c r="BN4" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -43531,6 +44128,9 @@
       <c r="BM5" t="n">
         <v>53</v>
       </c>
+      <c r="BN5" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -43732,6 +44332,9 @@
       <c r="BM6" t="n">
         <v>101</v>
       </c>
+      <c r="BN6" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -43933,6 +44536,9 @@
       <c r="BM7" t="n">
         <v>115</v>
       </c>
+      <c r="BN7" t="n">
+        <v>155</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -44134,6 +44740,9 @@
       <c r="BM8" t="n">
         <v>116</v>
       </c>
+      <c r="BN8" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -44335,6 +44944,9 @@
       <c r="BM9" t="n">
         <v>-83</v>
       </c>
+      <c r="BN9" t="n">
+        <v>-87</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -44536,6 +45148,9 @@
       <c r="BM10" t="n">
         <v>-6</v>
       </c>
+      <c r="BN10" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -44737,6 +45352,9 @@
       <c r="BM11" t="n">
         <v>-82</v>
       </c>
+      <c r="BN11" t="n">
+        <v>-94</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -44938,6 +45556,9 @@
       <c r="BM12" t="n">
         <v>-86</v>
       </c>
+      <c r="BN12" t="n">
+        <v>-94</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -45139,6 +45760,9 @@
       <c r="BM13" t="n">
         <v>-78</v>
       </c>
+      <c r="BN13" t="n">
+        <v>-92</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -45340,6 +45964,9 @@
       <c r="BM14" t="n">
         <v>-83</v>
       </c>
+      <c r="BN14" t="n">
+        <v>-88</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -45541,6 +46168,9 @@
       <c r="BM15" t="n">
         <v>23</v>
       </c>
+      <c r="BN15" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -45742,6 +46372,9 @@
       <c r="BM16" t="n">
         <v>-85</v>
       </c>
+      <c r="BN16" t="n">
+        <v>-92</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -45943,6 +46576,9 @@
       <c r="BM17" t="n">
         <v>-90</v>
       </c>
+      <c r="BN17" t="n">
+        <v>-94</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -46144,6 +46780,9 @@
       <c r="BM18" t="n">
         <v>14</v>
       </c>
+      <c r="BN18" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -46344,6 +46983,9 @@
       </c>
       <c r="BM19" t="n">
         <v>-11</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>-17</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -33255,7 +33255,7 @@
         <v>1989357</v>
       </c>
       <c r="CG3" t="n">
-        <v>3119559</v>
+        <v>3121543</v>
       </c>
     </row>
     <row r="4">
@@ -33516,7 +33516,7 @@
         <v>111473</v>
       </c>
       <c r="CG4" t="n">
-        <v>121182</v>
+        <v>121310</v>
       </c>
     </row>
     <row r="5">
@@ -33777,7 +33777,7 @@
         <v>405157</v>
       </c>
       <c r="CG5" t="n">
-        <v>1333840</v>
+        <v>1343881</v>
       </c>
     </row>
     <row r="6">
@@ -34038,7 +34038,7 @@
         <v>1537147</v>
       </c>
       <c r="CG6" t="n">
-        <v>4343698</v>
+        <v>4399112</v>
       </c>
     </row>
     <row r="7">
@@ -34299,7 +34299,7 @@
         <v>4511027</v>
       </c>
       <c r="CG7" t="n">
-        <v>7404354</v>
+        <v>7425175</v>
       </c>
     </row>
     <row r="8">
@@ -34560,7 +34560,7 @@
         <v>7257620</v>
       </c>
       <c r="CG8" t="n">
-        <v>12239343</v>
+        <v>12775404</v>
       </c>
     </row>
     <row r="9">
@@ -34821,7 +34821,7 @@
         <v>4550477</v>
       </c>
       <c r="CG9" t="n">
-        <v>4443741</v>
+        <v>4449073</v>
       </c>
     </row>
     <row r="10">
@@ -35082,7 +35082,7 @@
         <v>466016</v>
       </c>
       <c r="CG10" t="n">
-        <v>2074169</v>
+        <v>2076513</v>
       </c>
     </row>
     <row r="11">
@@ -35343,7 +35343,7 @@
         <v>375300</v>
       </c>
       <c r="CG11" t="n">
-        <v>677293</v>
+        <v>677354</v>
       </c>
     </row>
     <row r="12">
@@ -35604,7 +35604,7 @@
         <v>1938194</v>
       </c>
       <c r="CG12" t="n">
-        <v>1971626</v>
+        <v>1979322</v>
       </c>
     </row>
     <row r="13">
@@ -35865,7 +35865,7 @@
         <v>3693011</v>
       </c>
       <c r="CG13" t="n">
-        <v>5229924</v>
+        <v>5231368</v>
       </c>
     </row>
     <row r="14">
@@ -36126,7 +36126,7 @@
         <v>34437364</v>
       </c>
       <c r="CG14" t="n">
-        <v>35153489</v>
+        <v>35209324</v>
       </c>
     </row>
     <row r="15">
@@ -36387,7 +36387,7 @@
         <v>709730</v>
       </c>
       <c r="CG15" t="n">
-        <v>1219236</v>
+        <v>1219729</v>
       </c>
     </row>
     <row r="16">
@@ -36648,7 +36648,7 @@
         <v>290953</v>
       </c>
       <c r="CG16" t="n">
-        <v>315686</v>
+        <v>315748</v>
       </c>
     </row>
     <row r="17">
@@ -37170,7 +37170,7 @@
         <v>38778</v>
       </c>
       <c r="CG18" t="n">
-        <v>103462</v>
+        <v>103482</v>
       </c>
     </row>
     <row r="19">
@@ -37431,7 +37431,7 @@
         <v>11434</v>
       </c>
       <c r="CG19" t="n">
-        <v>22784</v>
+        <v>22809</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -738,6 +738,7 @@
     <col width="10" customWidth="1" min="24" max="24"/>
     <col width="10" customWidth="1" min="25" max="25"/>
     <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -823,6 +824,9 @@
       <c r="Z1" s="1" t="n">
         <v>20260102</v>
       </c>
+      <c r="AA1" s="1" t="n">
+        <v>20260105</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -907,6 +911,9 @@
       <c r="Z2" t="n">
         <v>18</v>
       </c>
+      <c r="AA2" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -991,6 +998,9 @@
       <c r="Z3" t="n">
         <v>148</v>
       </c>
+      <c r="AA3" t="n">
+        <v>185</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1075,6 +1085,9 @@
       <c r="Z4" t="n">
         <v>29</v>
       </c>
+      <c r="AA4" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1159,6 +1172,9 @@
       <c r="Z5" t="n">
         <v>88</v>
       </c>
+      <c r="AA5" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1243,6 +1259,9 @@
       <c r="Z6" t="n">
         <v>130</v>
       </c>
+      <c r="AA6" t="n">
+        <v>163</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1327,6 +1346,9 @@
       <c r="Z7" t="n">
         <v>141</v>
       </c>
+      <c r="AA7" t="n">
+        <v>169</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1411,6 +1433,9 @@
       <c r="Z8" t="n">
         <v>159</v>
       </c>
+      <c r="AA8" t="n">
+        <v>197</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1495,6 +1520,9 @@
       <c r="Z9" t="n">
         <v>-75</v>
       </c>
+      <c r="AA9" t="n">
+        <v>-65</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1579,6 +1607,9 @@
       <c r="Z10" t="n">
         <v>84</v>
       </c>
+      <c r="AA10" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1663,6 +1694,9 @@
       <c r="Z11" t="n">
         <v>-38</v>
       </c>
+      <c r="AA11" t="n">
+        <v>-33</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1747,6 +1781,9 @@
       <c r="Z12" t="n">
         <v>-42</v>
       </c>
+      <c r="AA12" t="n">
+        <v>-37</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1831,6 +1868,9 @@
       <c r="Z13" t="n">
         <v>-33</v>
       </c>
+      <c r="AA13" t="n">
+        <v>-25</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1915,6 +1955,9 @@
       <c r="Z14" t="n">
         <v>-68</v>
       </c>
+      <c r="AA14" t="n">
+        <v>-59</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1999,6 +2042,9 @@
       <c r="Z15" t="n">
         <v>38</v>
       </c>
+      <c r="AA15" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2083,6 +2129,9 @@
       <c r="Z16" t="n">
         <v>-51</v>
       </c>
+      <c r="AA16" t="n">
+        <v>-41</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2167,6 +2216,9 @@
       <c r="Z17" t="n">
         <v>-57</v>
       </c>
+      <c r="AA17" t="n">
+        <v>-49</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2251,6 +2303,9 @@
       <c r="Z18" t="n">
         <v>85</v>
       </c>
+      <c r="AA18" t="n">
+        <v>122</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2334,6 +2389,9 @@
       </c>
       <c r="Z19" t="n">
         <v>39</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -2347,7 +2405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN19"/>
+  <dimension ref="A1:BO19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2416,6 +2474,7 @@
     <col width="12" customWidth="1" min="64" max="64"/>
     <col width="12" customWidth="1" min="65" max="65"/>
     <col width="12" customWidth="1" min="66" max="66"/>
+    <col width="12" customWidth="1" min="67" max="67"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2749,6 +2808,11 @@
           <t>20260102</t>
         </is>
       </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>20260105</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2953,6 +3017,9 @@
       <c r="BN2" t="n">
         <v>99</v>
       </c>
+      <c r="BO2" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3157,6 +3224,9 @@
       <c r="BN3" t="n">
         <v>113</v>
       </c>
+      <c r="BO3" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3361,6 +3431,9 @@
       <c r="BN4" t="n">
         <v>101</v>
       </c>
+      <c r="BO4" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3565,6 +3638,9 @@
       <c r="BN5" t="n">
         <v>108</v>
       </c>
+      <c r="BO5" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3769,6 +3845,9 @@
       <c r="BN6" t="n">
         <v>112</v>
       </c>
+      <c r="BO6" t="n">
+        <v>115</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3973,6 +4052,9 @@
       <c r="BN7" t="n">
         <v>113</v>
       </c>
+      <c r="BO7" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4177,6 +4259,9 @@
       <c r="BN8" t="n">
         <v>115</v>
       </c>
+      <c r="BO8" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4381,6 +4466,9 @@
       <c r="BN9" t="n">
         <v>81</v>
       </c>
+      <c r="BO9" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4585,6 +4673,9 @@
       <c r="BN10" t="n">
         <v>107</v>
       </c>
+      <c r="BO10" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4789,6 +4880,9 @@
       <c r="BN11" t="n">
         <v>90</v>
       </c>
+      <c r="BO11" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4993,6 +5087,9 @@
       <c r="BN12" t="n">
         <v>88</v>
       </c>
+      <c r="BO12" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5197,6 +5294,9 @@
       <c r="BN13" t="n">
         <v>88</v>
       </c>
+      <c r="BO13" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5401,6 +5501,9 @@
       <c r="BN14" t="n">
         <v>79</v>
       </c>
+      <c r="BO14" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5605,6 +5708,9 @@
       <c r="BN15" t="n">
         <v>100</v>
       </c>
+      <c r="BO15" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5809,6 +5915,9 @@
       <c r="BN16" t="n">
         <v>89</v>
       </c>
+      <c r="BO16" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6013,6 +6122,9 @@
       <c r="BN17" t="n">
         <v>88</v>
       </c>
+      <c r="BO17" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6217,6 +6329,9 @@
       <c r="BN18" t="n">
         <v>107</v>
       </c>
+      <c r="BO18" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6420,6 +6535,9 @@
       </c>
       <c r="BN19" t="n">
         <v>99</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -10459,7 +10577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10488,6 +10606,7 @@
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10621,6 +10740,11 @@
           <t>20260102</t>
         </is>
       </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>20260105</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10705,6 +10829,9 @@
       <c r="Z2" t="n">
         <v>44</v>
       </c>
+      <c r="AA2" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10789,6 +10916,9 @@
       <c r="Z3" t="n">
         <v>66</v>
       </c>
+      <c r="AA3" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10873,6 +11003,9 @@
       <c r="Z4" t="n">
         <v>34</v>
       </c>
+      <c r="AA4" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10957,6 +11090,9 @@
       <c r="Z5" t="n">
         <v>88</v>
       </c>
+      <c r="AA5" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11041,6 +11177,9 @@
       <c r="Z6" t="n">
         <v>106</v>
       </c>
+      <c r="AA6" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11125,6 +11264,9 @@
       <c r="Z7" t="n">
         <v>91</v>
       </c>
+      <c r="AA7" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11209,6 +11351,9 @@
       <c r="Z8" t="n">
         <v>83</v>
       </c>
+      <c r="AA8" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11293,6 +11438,9 @@
       <c r="Z9" t="n">
         <v>29</v>
       </c>
+      <c r="AA9" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11377,6 +11525,9 @@
       <c r="Z10" t="n">
         <v>79</v>
       </c>
+      <c r="AA10" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11461,6 +11612,9 @@
       <c r="Z11" t="n">
         <v>25</v>
       </c>
+      <c r="AA11" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11545,6 +11699,9 @@
       <c r="Z12" t="n">
         <v>33</v>
       </c>
+      <c r="AA12" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11629,6 +11786,9 @@
       <c r="Z13" t="n">
         <v>36</v>
       </c>
+      <c r="AA13" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11713,6 +11873,9 @@
       <c r="Z14" t="n">
         <v>33</v>
       </c>
+      <c r="AA14" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11797,6 +11960,9 @@
       <c r="Z15" t="n">
         <v>35</v>
       </c>
+      <c r="AA15" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11881,6 +12047,9 @@
       <c r="Z16" t="n">
         <v>25</v>
       </c>
+      <c r="AA16" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11965,6 +12134,9 @@
       <c r="Z17" t="n">
         <v>20</v>
       </c>
+      <c r="AA17" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12049,6 +12221,9 @@
       <c r="Z18" t="n">
         <v>29</v>
       </c>
+      <c r="AA18" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12132,6 +12307,9 @@
       </c>
       <c r="Z19" t="n">
         <v>24</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -12145,7 +12323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG19"/>
+  <dimension ref="A1:CH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12233,6 +12411,7 @@
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
+    <col width="12" customWidth="1" min="86" max="86"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12495,6 +12674,9 @@
       <c r="CG1" s="1" t="n">
         <v>20260102</v>
       </c>
+      <c r="CH1" s="1" t="n">
+        <v>20260105</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12756,6 +12938,9 @@
       <c r="CG2" t="n">
         <v>15390</v>
       </c>
+      <c r="CH2" t="n">
+        <v>14805</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13017,6 +13202,9 @@
       <c r="CG3" t="n">
         <v>61355</v>
       </c>
+      <c r="CH3" t="n">
+        <v>67660</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13278,6 +13466,9 @@
       <c r="CG4" t="n">
         <v>18055</v>
       </c>
+      <c r="CH4" t="n">
+        <v>18100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13539,6 +13730,9 @@
       <c r="CG5" t="n">
         <v>16375</v>
       </c>
+      <c r="CH5" t="n">
+        <v>17675</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13800,6 +13994,9 @@
       <c r="CG6" t="n">
         <v>17925</v>
       </c>
+      <c r="CH6" t="n">
+        <v>19620</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14061,6 +14258,9 @@
       <c r="CG7" t="n">
         <v>20990</v>
       </c>
+      <c r="CH7" t="n">
+        <v>23080</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14322,6 +14522,9 @@
       <c r="CG8" t="n">
         <v>20140</v>
       </c>
+      <c r="CH8" t="n">
+        <v>22375</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14583,6 +14786,9 @@
       <c r="CG9" t="n">
         <v>1206</v>
       </c>
+      <c r="CH9" t="n">
+        <v>1153</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14844,6 +15050,9 @@
       <c r="CG10" t="n">
         <v>16820</v>
       </c>
+      <c r="CH10" t="n">
+        <v>18590</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15105,6 +15314,9 @@
       <c r="CG11" t="n">
         <v>4865</v>
       </c>
+      <c r="CH11" t="n">
+        <v>4725</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15366,6 +15578,9 @@
       <c r="CG12" t="n">
         <v>5110</v>
       </c>
+      <c r="CH12" t="n">
+        <v>4910</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15627,6 +15842,9 @@
       <c r="CG13" t="n">
         <v>5225</v>
       </c>
+      <c r="CH13" t="n">
+        <v>5010</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -15888,6 +16106,9 @@
       <c r="CG14" t="n">
         <v>1290</v>
       </c>
+      <c r="CH14" t="n">
+        <v>1217</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -16149,6 +16370,9 @@
       <c r="CG15" t="n">
         <v>19570</v>
       </c>
+      <c r="CH15" t="n">
+        <v>19010</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -16410,6 +16634,9 @@
       <c r="CG16" t="n">
         <v>9750</v>
       </c>
+      <c r="CH16" t="n">
+        <v>9490</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16671,6 +16898,9 @@
       <c r="CG17" t="n">
         <v>5660</v>
       </c>
+      <c r="CH17" t="n">
+        <v>5515</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16932,6 +17162,9 @@
       <c r="CG18" t="n">
         <v>17925</v>
       </c>
+      <c r="CH18" t="n">
+        <v>19945</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17192,6 +17425,9 @@
       </c>
       <c r="CG19" t="n">
         <v>16075</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>15875</v>
       </c>
     </row>
   </sheetData>
@@ -17205,7 +17441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG19"/>
+  <dimension ref="A1:CH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17293,6 +17529,7 @@
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
+    <col width="12" customWidth="1" min="86" max="86"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17555,6 +17792,9 @@
       <c r="CG1" s="1" t="n">
         <v>20260102</v>
       </c>
+      <c r="CH1" s="1" t="n">
+        <v>20260105</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17816,6 +18056,9 @@
       <c r="CG2" t="n">
         <v>15600</v>
       </c>
+      <c r="CH2" t="n">
+        <v>15755</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18077,6 +18320,9 @@
       <c r="CG3" t="n">
         <v>65520</v>
       </c>
+      <c r="CH3" t="n">
+        <v>68750</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18338,6 +18584,9 @@
       <c r="CG4" t="n">
         <v>18390</v>
       </c>
+      <c r="CH4" t="n">
+        <v>18670</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18599,6 +18848,9 @@
       <c r="CG5" t="n">
         <v>17170</v>
       </c>
+      <c r="CH5" t="n">
+        <v>17855</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18860,6 +19112,9 @@
       <c r="CG6" t="n">
         <v>19060</v>
       </c>
+      <c r="CH6" t="n">
+        <v>19925</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19121,6 +19376,9 @@
       <c r="CG7" t="n">
         <v>22385</v>
       </c>
+      <c r="CH7" t="n">
+        <v>23335</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19382,6 +19640,9 @@
       <c r="CG8" t="n">
         <v>21645</v>
       </c>
+      <c r="CH8" t="n">
+        <v>22850</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19643,6 +19904,9 @@
       <c r="CG9" t="n">
         <v>1215</v>
       </c>
+      <c r="CH9" t="n">
+        <v>1235</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19904,6 +20168,9 @@
       <c r="CG10" t="n">
         <v>17965</v>
       </c>
+      <c r="CH10" t="n">
+        <v>18925</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -20165,6 +20432,9 @@
       <c r="CG11" t="n">
         <v>4865</v>
       </c>
+      <c r="CH11" t="n">
+        <v>4905</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -20426,6 +20696,9 @@
       <c r="CG12" t="n">
         <v>5140</v>
       </c>
+      <c r="CH12" t="n">
+        <v>5180</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -20687,6 +20960,9 @@
       <c r="CG13" t="n">
         <v>5230</v>
       </c>
+      <c r="CH13" t="n">
+        <v>5270</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -20948,6 +21224,9 @@
       <c r="CG14" t="n">
         <v>1290</v>
       </c>
+      <c r="CH14" t="n">
+        <v>1322</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -21209,6 +21488,9 @@
       <c r="CG15" t="n">
         <v>19685</v>
       </c>
+      <c r="CH15" t="n">
+        <v>19945</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -21470,6 +21752,9 @@
       <c r="CG16" t="n">
         <v>9780</v>
       </c>
+      <c r="CH16" t="n">
+        <v>9920</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -21731,6 +22016,9 @@
       <c r="CG17" t="n">
         <v>5665</v>
       </c>
+      <c r="CH17" t="n">
+        <v>5765</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -21992,6 +22280,9 @@
       <c r="CG18" t="n">
         <v>19130</v>
       </c>
+      <c r="CH18" t="n">
+        <v>20090</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -22252,6 +22543,9 @@
       </c>
       <c r="CG19" t="n">
         <v>16185</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>16450</v>
       </c>
     </row>
   </sheetData>
@@ -22265,7 +22559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG19"/>
+  <dimension ref="A1:CH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22353,6 +22647,7 @@
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
+    <col width="12" customWidth="1" min="86" max="86"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22615,6 +22910,9 @@
       <c r="CG1" s="1" t="n">
         <v>20260102</v>
       </c>
+      <c r="CH1" s="1" t="n">
+        <v>20260105</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22876,6 +23174,9 @@
       <c r="CG2" t="n">
         <v>15100</v>
       </c>
+      <c r="CH2" t="n">
+        <v>14680</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23137,6 +23438,9 @@
       <c r="CG3" t="n">
         <v>61355</v>
       </c>
+      <c r="CH3" t="n">
+        <v>67005</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23398,6 +23702,9 @@
       <c r="CG4" t="n">
         <v>18050</v>
       </c>
+      <c r="CH4" t="n">
+        <v>17780</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23659,6 +23966,9 @@
       <c r="CG5" t="n">
         <v>16275</v>
       </c>
+      <c r="CH5" t="n">
+        <v>17310</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23920,6 +24230,9 @@
       <c r="CG6" t="n">
         <v>17885</v>
       </c>
+      <c r="CH6" t="n">
+        <v>19410</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24181,6 +24494,9 @@
       <c r="CG7" t="n">
         <v>20990</v>
       </c>
+      <c r="CH7" t="n">
+        <v>22775</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24442,6 +24758,9 @@
       <c r="CG8" t="n">
         <v>20140</v>
       </c>
+      <c r="CH8" t="n">
+        <v>22200</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24703,6 +25022,9 @@
       <c r="CG9" t="n">
         <v>1160</v>
       </c>
+      <c r="CH9" t="n">
+        <v>1153</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24964,6 +25286,9 @@
       <c r="CG10" t="n">
         <v>16745</v>
       </c>
+      <c r="CH10" t="n">
+        <v>18265</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25225,6 +25550,9 @@
       <c r="CG11" t="n">
         <v>4730</v>
       </c>
+      <c r="CH11" t="n">
+        <v>4720</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25486,6 +25814,9 @@
       <c r="CG12" t="n">
         <v>5005</v>
       </c>
+      <c r="CH12" t="n">
+        <v>4910</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -25747,6 +26078,9 @@
       <c r="CG13" t="n">
         <v>5085</v>
       </c>
+      <c r="CH13" t="n">
+        <v>5010</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -26008,6 +26342,9 @@
       <c r="CG14" t="n">
         <v>1218</v>
       </c>
+      <c r="CH14" t="n">
+        <v>1212</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -26269,6 +26606,9 @@
       <c r="CG15" t="n">
         <v>19080</v>
       </c>
+      <c r="CH15" t="n">
+        <v>18645</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -26530,6 +26870,9 @@
       <c r="CG16" t="n">
         <v>9535</v>
       </c>
+      <c r="CH16" t="n">
+        <v>9490</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -26791,6 +27134,9 @@
       <c r="CG17" t="n">
         <v>5540</v>
       </c>
+      <c r="CH17" t="n">
+        <v>5515</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -27052,6 +27398,9 @@
       <c r="CG18" t="n">
         <v>17920</v>
       </c>
+      <c r="CH18" t="n">
+        <v>19440</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -27312,6 +27661,9 @@
       </c>
       <c r="CG19" t="n">
         <v>15875</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>15635</v>
       </c>
     </row>
   </sheetData>
@@ -27325,7 +27677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG19"/>
+  <dimension ref="A1:CH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27413,6 +27765,7 @@
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
+    <col width="12" customWidth="1" min="86" max="86"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27675,6 +28028,9 @@
       <c r="CG1" s="1" t="n">
         <v>20260102</v>
       </c>
+      <c r="CH1" s="1" t="n">
+        <v>20260105</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27936,6 +28292,9 @@
       <c r="CG2" t="n">
         <v>15205</v>
       </c>
+      <c r="CH2" t="n">
+        <v>15740</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28197,6 +28556,9 @@
       <c r="CG3" t="n">
         <v>65480</v>
       </c>
+      <c r="CH3" t="n">
+        <v>68600</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28458,6 +28820,9 @@
       <c r="CG4" t="n">
         <v>18150</v>
       </c>
+      <c r="CH4" t="n">
+        <v>18640</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28719,6 +29084,9 @@
       <c r="CG5" t="n">
         <v>17140</v>
       </c>
+      <c r="CH5" t="n">
+        <v>17515</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28980,6 +29348,9 @@
       <c r="CG6" t="n">
         <v>19060</v>
       </c>
+      <c r="CH6" t="n">
+        <v>19870</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29241,6 +29612,9 @@
       <c r="CG7" t="n">
         <v>22385</v>
       </c>
+      <c r="CH7" t="n">
+        <v>23325</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29502,6 +29876,9 @@
       <c r="CG8" t="n">
         <v>21645</v>
       </c>
+      <c r="CH8" t="n">
+        <v>22850</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29763,6 +30140,9 @@
       <c r="CG9" t="n">
         <v>1167</v>
       </c>
+      <c r="CH9" t="n">
+        <v>1223</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30024,6 +30404,9 @@
       <c r="CG10" t="n">
         <v>17965</v>
       </c>
+      <c r="CH10" t="n">
+        <v>18635</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30285,6 +30668,9 @@
       <c r="CG11" t="n">
         <v>4755</v>
       </c>
+      <c r="CH11" t="n">
+        <v>4850</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30546,6 +30932,9 @@
       <c r="CG12" t="n">
         <v>5020</v>
       </c>
+      <c r="CH12" t="n">
+        <v>5125</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30807,6 +31196,9 @@
       <c r="CG13" t="n">
         <v>5090</v>
       </c>
+      <c r="CH13" t="n">
+        <v>5220</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31068,6 +31460,9 @@
       <c r="CG14" t="n">
         <v>1232</v>
       </c>
+      <c r="CH14" t="n">
+        <v>1299</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -31329,6 +31724,9 @@
       <c r="CG15" t="n">
         <v>19185</v>
       </c>
+      <c r="CH15" t="n">
+        <v>19925</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -31590,6 +31988,9 @@
       <c r="CG16" t="n">
         <v>9565</v>
       </c>
+      <c r="CH16" t="n">
+        <v>9845</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -31851,6 +32252,9 @@
       <c r="CG17" t="n">
         <v>5565</v>
       </c>
+      <c r="CH17" t="n">
+        <v>5710</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -32112,6 +32516,9 @@
       <c r="CG18" t="n">
         <v>19130</v>
       </c>
+      <c r="CH18" t="n">
+        <v>19950</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -32372,6 +32779,9 @@
       </c>
       <c r="CG19" t="n">
         <v>15975</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>16435</v>
       </c>
     </row>
   </sheetData>
@@ -32385,7 +32795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG19"/>
+  <dimension ref="A1:CH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -32473,6 +32883,7 @@
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
+    <col width="12" customWidth="1" min="86" max="86"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32735,6 +33146,9 @@
       <c r="CG1" s="1" t="n">
         <v>20260102</v>
       </c>
+      <c r="CH1" s="1" t="n">
+        <v>20260105</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32996,6 +33410,9 @@
       <c r="CG2" t="n">
         <v>113541</v>
       </c>
+      <c r="CH2" t="n">
+        <v>176986</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -33257,6 +33674,9 @@
       <c r="CG3" t="n">
         <v>3121543</v>
       </c>
+      <c r="CH3" t="n">
+        <v>4394575</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -33518,6 +33938,9 @@
       <c r="CG4" t="n">
         <v>121310</v>
       </c>
+      <c r="CH4" t="n">
+        <v>172768</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -33779,6 +34202,9 @@
       <c r="CG5" t="n">
         <v>1343881</v>
       </c>
+      <c r="CH5" t="n">
+        <v>1983862</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34040,6 +34466,9 @@
       <c r="CG6" t="n">
         <v>4399112</v>
       </c>
+      <c r="CH6" t="n">
+        <v>5158465</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -34301,6 +34730,9 @@
       <c r="CG7" t="n">
         <v>7425175</v>
       </c>
+      <c r="CH7" t="n">
+        <v>4694499</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -34562,6 +34994,9 @@
       <c r="CG8" t="n">
         <v>12775404</v>
       </c>
+      <c r="CH8" t="n">
+        <v>15893026</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -34823,6 +35258,9 @@
       <c r="CG9" t="n">
         <v>4449073</v>
       </c>
+      <c r="CH9" t="n">
+        <v>7210172</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35084,6 +35522,9 @@
       <c r="CG10" t="n">
         <v>2076513</v>
       </c>
+      <c r="CH10" t="n">
+        <v>4027529</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -35345,6 +35786,9 @@
       <c r="CG11" t="n">
         <v>677354</v>
       </c>
+      <c r="CH11" t="n">
+        <v>430956</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -35606,6 +36050,9 @@
       <c r="CG12" t="n">
         <v>1979322</v>
       </c>
+      <c r="CH12" t="n">
+        <v>2012209</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35867,6 +36314,9 @@
       <c r="CG13" t="n">
         <v>5231368</v>
       </c>
+      <c r="CH13" t="n">
+        <v>4550210</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36128,6 +36578,9 @@
       <c r="CG14" t="n">
         <v>35209324</v>
       </c>
+      <c r="CH14" t="n">
+        <v>32400440</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36389,6 +36842,9 @@
       <c r="CG15" t="n">
         <v>1219729</v>
       </c>
+      <c r="CH15" t="n">
+        <v>1889109</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -36650,6 +37106,9 @@
       <c r="CG16" t="n">
         <v>315748</v>
       </c>
+      <c r="CH16" t="n">
+        <v>350519</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36911,6 +37370,9 @@
       <c r="CG17" t="n">
         <v>95990</v>
       </c>
+      <c r="CH17" t="n">
+        <v>84958</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -37172,6 +37634,9 @@
       <c r="CG18" t="n">
         <v>103482</v>
       </c>
+      <c r="CH18" t="n">
+        <v>85902</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -37432,6 +37897,9 @@
       </c>
       <c r="CG19" t="n">
         <v>22809</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>35964</v>
       </c>
     </row>
   </sheetData>
@@ -37445,7 +37913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN19"/>
+  <dimension ref="A1:BO19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37514,6 +37982,7 @@
     <col width="10" customWidth="1" min="64" max="64"/>
     <col width="10" customWidth="1" min="65" max="65"/>
     <col width="10" customWidth="1" min="66" max="66"/>
+    <col width="10" customWidth="1" min="67" max="67"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37719,6 +38188,9 @@
       <c r="BN1" s="1" t="n">
         <v>20260102</v>
       </c>
+      <c r="BO1" s="1" t="n">
+        <v>20260105</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37923,6 +38395,9 @@
       <c r="BN2" t="n">
         <v>36</v>
       </c>
+      <c r="BO2" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38127,6 +38602,9 @@
       <c r="BN3" t="n">
         <v>100</v>
       </c>
+      <c r="BO3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -38331,6 +38809,9 @@
       <c r="BN4" t="n">
         <v>52</v>
       </c>
+      <c r="BO4" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -38535,6 +39016,9 @@
       <c r="BN5" t="n">
         <v>100</v>
       </c>
+      <c r="BO5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -38739,6 +39223,9 @@
       <c r="BN6" t="n">
         <v>100</v>
       </c>
+      <c r="BO6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -38943,6 +39430,9 @@
       <c r="BN7" t="n">
         <v>100</v>
       </c>
+      <c r="BO7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -39147,6 +39637,9 @@
       <c r="BN8" t="n">
         <v>100</v>
       </c>
+      <c r="BO8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -39351,6 +39844,9 @@
       <c r="BN9" t="n">
         <v>0</v>
       </c>
+      <c r="BO9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -39555,6 +40051,9 @@
       <c r="BN10" t="n">
         <v>100</v>
       </c>
+      <c r="BO10" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -39759,6 +40258,9 @@
       <c r="BN11" t="n">
         <v>0</v>
       </c>
+      <c r="BO11" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -39963,6 +40465,9 @@
       <c r="BN12" t="n">
         <v>0</v>
       </c>
+      <c r="BO12" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -40167,6 +40672,9 @@
       <c r="BN13" t="n">
         <v>0</v>
       </c>
+      <c r="BO13" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -40371,6 +40879,9 @@
       <c r="BN14" t="n">
         <v>0</v>
       </c>
+      <c r="BO14" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -40575,6 +41086,9 @@
       <c r="BN15" t="n">
         <v>33</v>
       </c>
+      <c r="BO15" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -40779,6 +41293,9 @@
       <c r="BN16" t="n">
         <v>0</v>
       </c>
+      <c r="BO16" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -40983,6 +41500,9 @@
       <c r="BN17" t="n">
         <v>0</v>
       </c>
+      <c r="BO17" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41187,6 +41707,9 @@
       <c r="BN18" t="n">
         <v>100</v>
       </c>
+      <c r="BO18" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -41390,6 +41913,9 @@
       </c>
       <c r="BN19" t="n">
         <v>30</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -41403,7 +41929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -41432,6 +41958,7 @@
     <col width="10" customWidth="1" min="24" max="24"/>
     <col width="10" customWidth="1" min="25" max="25"/>
     <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -41517,6 +42044,9 @@
       <c r="Z1" s="1" t="n">
         <v>20260102</v>
       </c>
+      <c r="AA1" s="1" t="n">
+        <v>20260105</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -41601,6 +42131,9 @@
       <c r="Z2" t="n">
         <v>63</v>
       </c>
+      <c r="AA2" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -41685,6 +42218,9 @@
       <c r="Z3" t="n">
         <v>100</v>
       </c>
+      <c r="AA3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -41769,6 +42305,9 @@
       <c r="Z4" t="n">
         <v>69</v>
       </c>
+      <c r="AA4" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -41853,6 +42392,9 @@
       <c r="Z5" t="n">
         <v>98</v>
       </c>
+      <c r="AA5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -41937,6 +42479,9 @@
       <c r="Z6" t="n">
         <v>100</v>
       </c>
+      <c r="AA6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -42021,6 +42566,9 @@
       <c r="Z7" t="n">
         <v>100</v>
       </c>
+      <c r="AA7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -42105,6 +42653,9 @@
       <c r="Z8" t="n">
         <v>100</v>
       </c>
+      <c r="AA8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -42189,6 +42740,9 @@
       <c r="Z9" t="n">
         <v>16</v>
       </c>
+      <c r="AA9" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -42273,6 +42827,9 @@
       <c r="Z10" t="n">
         <v>95</v>
       </c>
+      <c r="AA10" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -42357,6 +42914,9 @@
       <c r="Z11" t="n">
         <v>49</v>
       </c>
+      <c r="AA11" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -42441,6 +43001,9 @@
       <c r="Z12" t="n">
         <v>47</v>
       </c>
+      <c r="AA12" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -42525,6 +43088,9 @@
       <c r="Z13" t="n">
         <v>49</v>
       </c>
+      <c r="AA13" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -42609,6 +43175,9 @@
       <c r="Z14" t="n">
         <v>22</v>
       </c>
+      <c r="AA14" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42693,6 +43262,9 @@
       <c r="Z15" t="n">
         <v>80</v>
       </c>
+      <c r="AA15" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -42777,6 +43349,9 @@
       <c r="Z16" t="n">
         <v>40</v>
       </c>
+      <c r="AA16" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42861,6 +43436,9 @@
       <c r="Z17" t="n">
         <v>36</v>
       </c>
+      <c r="AA17" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42945,6 +43523,9 @@
       <c r="Z18" t="n">
         <v>100</v>
       </c>
+      <c r="AA18" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43028,6 +43609,9 @@
       </c>
       <c r="Z19" t="n">
         <v>81</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -43041,7 +43625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN19"/>
+  <dimension ref="A1:BO19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -43110,6 +43694,7 @@
     <col width="10" customWidth="1" min="64" max="64"/>
     <col width="10" customWidth="1" min="65" max="65"/>
     <col width="10" customWidth="1" min="66" max="66"/>
+    <col width="10" customWidth="1" min="67" max="67"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43315,6 +43900,9 @@
       <c r="BN1" s="1" t="n">
         <v>20260102</v>
       </c>
+      <c r="BO1" s="1" t="n">
+        <v>20260105</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -43519,6 +44107,9 @@
       <c r="BN2" t="n">
         <v>-9</v>
       </c>
+      <c r="BO2" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -43723,6 +44314,9 @@
       <c r="BN3" t="n">
         <v>153</v>
       </c>
+      <c r="BO3" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -43927,6 +44521,9 @@
       <c r="BN4" t="n">
         <v>20</v>
       </c>
+      <c r="BO4" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -44131,6 +44728,9 @@
       <c r="BN5" t="n">
         <v>121</v>
       </c>
+      <c r="BO5" t="n">
+        <v>124</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -44335,6 +44935,9 @@
       <c r="BN6" t="n">
         <v>148</v>
       </c>
+      <c r="BO6" t="n">
+        <v>145</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -44539,6 +45142,9 @@
       <c r="BN7" t="n">
         <v>155</v>
       </c>
+      <c r="BO7" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -44743,6 +45349,9 @@
       <c r="BN8" t="n">
         <v>154</v>
       </c>
+      <c r="BO8" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -44947,6 +45556,9 @@
       <c r="BN9" t="n">
         <v>-87</v>
       </c>
+      <c r="BO9" t="n">
+        <v>-62</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -45151,6 +45763,9 @@
       <c r="BN10" t="n">
         <v>101</v>
       </c>
+      <c r="BO10" t="n">
+        <v>130</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -45355,6 +45970,9 @@
       <c r="BN11" t="n">
         <v>-94</v>
       </c>
+      <c r="BO11" t="n">
+        <v>-70</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -45559,6 +46177,9 @@
       <c r="BN12" t="n">
         <v>-94</v>
       </c>
+      <c r="BO12" t="n">
+        <v>-71</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -45763,6 +46384,9 @@
       <c r="BN13" t="n">
         <v>-92</v>
       </c>
+      <c r="BO13" t="n">
+        <v>-68</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -45967,6 +46591,9 @@
       <c r="BN14" t="n">
         <v>-88</v>
       </c>
+      <c r="BO14" t="n">
+        <v>-63</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -46171,6 +46798,9 @@
       <c r="BN15" t="n">
         <v>-8</v>
       </c>
+      <c r="BO15" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -46375,6 +47005,9 @@
       <c r="BN16" t="n">
         <v>-92</v>
       </c>
+      <c r="BO16" t="n">
+        <v>-62</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -46579,6 +47212,9 @@
       <c r="BN17" t="n">
         <v>-94</v>
       </c>
+      <c r="BO17" t="n">
+        <v>-68</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -46783,6 +47419,9 @@
       <c r="BN18" t="n">
         <v>99</v>
       </c>
+      <c r="BO18" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -46986,6 +47625,9 @@
       </c>
       <c r="BN19" t="n">
         <v>-17</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -33411,7 +33411,7 @@
         <v>113541</v>
       </c>
       <c r="CH2" t="n">
-        <v>176986</v>
+        <v>177035</v>
       </c>
     </row>
     <row r="3">
@@ -33675,7 +33675,7 @@
         <v>3121543</v>
       </c>
       <c r="CH3" t="n">
-        <v>4394575</v>
+        <v>4395229</v>
       </c>
     </row>
     <row r="4">
@@ -33939,7 +33939,7 @@
         <v>121310</v>
       </c>
       <c r="CH4" t="n">
-        <v>172768</v>
+        <v>172792</v>
       </c>
     </row>
     <row r="5">
@@ -34203,7 +34203,7 @@
         <v>1343881</v>
       </c>
       <c r="CH5" t="n">
-        <v>1983862</v>
+        <v>1995377</v>
       </c>
     </row>
     <row r="6">
@@ -34467,7 +34467,7 @@
         <v>4399112</v>
       </c>
       <c r="CH6" t="n">
-        <v>5158465</v>
+        <v>5160628</v>
       </c>
     </row>
     <row r="7">
@@ -34731,7 +34731,7 @@
         <v>7425175</v>
       </c>
       <c r="CH7" t="n">
-        <v>4694499</v>
+        <v>4786647</v>
       </c>
     </row>
     <row r="8">
@@ -34995,7 +34995,7 @@
         <v>12775404</v>
       </c>
       <c r="CH8" t="n">
-        <v>15893026</v>
+        <v>15898595</v>
       </c>
     </row>
     <row r="9">
@@ -35259,7 +35259,7 @@
         <v>4449073</v>
       </c>
       <c r="CH9" t="n">
-        <v>7210172</v>
+        <v>7211412</v>
       </c>
     </row>
     <row r="10">
@@ -35523,7 +35523,7 @@
         <v>2076513</v>
       </c>
       <c r="CH10" t="n">
-        <v>4027529</v>
+        <v>4052041</v>
       </c>
     </row>
     <row r="11">
@@ -35787,7 +35787,7 @@
         <v>677354</v>
       </c>
       <c r="CH11" t="n">
-        <v>430956</v>
+        <v>431618</v>
       </c>
     </row>
     <row r="12">
@@ -36051,7 +36051,7 @@
         <v>1979322</v>
       </c>
       <c r="CH12" t="n">
-        <v>2012209</v>
+        <v>2012540</v>
       </c>
     </row>
     <row r="13">
@@ -36315,7 +36315,7 @@
         <v>5231368</v>
       </c>
       <c r="CH13" t="n">
-        <v>4550210</v>
+        <v>4552736</v>
       </c>
     </row>
     <row r="14">
@@ -36579,7 +36579,7 @@
         <v>35209324</v>
       </c>
       <c r="CH14" t="n">
-        <v>32400440</v>
+        <v>32466922</v>
       </c>
     </row>
     <row r="15">
@@ -36843,7 +36843,7 @@
         <v>1219729</v>
       </c>
       <c r="CH15" t="n">
-        <v>1889109</v>
+        <v>1889416</v>
       </c>
     </row>
     <row r="16">
@@ -37107,7 +37107,7 @@
         <v>315748</v>
       </c>
       <c r="CH16" t="n">
-        <v>350519</v>
+        <v>351012</v>
       </c>
     </row>
     <row r="17">
@@ -37635,7 +37635,7 @@
         <v>103482</v>
       </c>
       <c r="CH18" t="n">
-        <v>85902</v>
+        <v>85995</v>
       </c>
     </row>
     <row r="19">

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -739,6 +739,7 @@
     <col width="10" customWidth="1" min="25" max="25"/>
     <col width="10" customWidth="1" min="26" max="26"/>
     <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,6 +828,9 @@
       <c r="AA1" s="1" t="n">
         <v>20260105</v>
       </c>
+      <c r="AB1" s="1" t="n">
+        <v>20260106</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -914,6 +918,9 @@
       <c r="AA2" t="n">
         <v>40</v>
       </c>
+      <c r="AB2" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1001,6 +1008,9 @@
       <c r="AA3" t="n">
         <v>185</v>
       </c>
+      <c r="AB3" t="n">
+        <v>194</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1088,6 +1098,9 @@
       <c r="AA4" t="n">
         <v>49</v>
       </c>
+      <c r="AB4" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1175,6 +1188,9 @@
       <c r="AA5" t="n">
         <v>116</v>
       </c>
+      <c r="AB5" t="n">
+        <v>125</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1262,6 +1278,9 @@
       <c r="AA6" t="n">
         <v>163</v>
       </c>
+      <c r="AB6" t="n">
+        <v>172</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1349,6 +1368,9 @@
       <c r="AA7" t="n">
         <v>169</v>
       </c>
+      <c r="AB7" t="n">
+        <v>174</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1436,6 +1458,9 @@
       <c r="AA8" t="n">
         <v>197</v>
       </c>
+      <c r="AB8" t="n">
+        <v>202</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1523,6 +1548,9 @@
       <c r="AA9" t="n">
         <v>-65</v>
       </c>
+      <c r="AB9" t="n">
+        <v>-60</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1610,6 +1638,9 @@
       <c r="AA10" t="n">
         <v>134</v>
       </c>
+      <c r="AB10" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1697,6 +1728,9 @@
       <c r="AA11" t="n">
         <v>-33</v>
       </c>
+      <c r="AB11" t="n">
+        <v>-30</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1784,6 +1818,9 @@
       <c r="AA12" t="n">
         <v>-37</v>
       </c>
+      <c r="AB12" t="n">
+        <v>-33</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1871,6 +1908,9 @@
       <c r="AA13" t="n">
         <v>-25</v>
       </c>
+      <c r="AB13" t="n">
+        <v>-22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1958,6 +1998,9 @@
       <c r="AA14" t="n">
         <v>-59</v>
       </c>
+      <c r="AB14" t="n">
+        <v>-56</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2045,6 +2088,9 @@
       <c r="AA15" t="n">
         <v>54</v>
       </c>
+      <c r="AB15" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2132,6 +2178,9 @@
       <c r="AA16" t="n">
         <v>-41</v>
       </c>
+      <c r="AB16" t="n">
+        <v>-35</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2219,6 +2268,9 @@
       <c r="AA17" t="n">
         <v>-49</v>
       </c>
+      <c r="AB17" t="n">
+        <v>-45</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2306,6 +2358,9 @@
       <c r="AA18" t="n">
         <v>122</v>
       </c>
+      <c r="AB18" t="n">
+        <v>145</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2392,6 +2447,9 @@
       </c>
       <c r="AA19" t="n">
         <v>54</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2405,7 +2463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO19"/>
+  <dimension ref="A1:BP19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2475,6 +2533,7 @@
     <col width="12" customWidth="1" min="65" max="65"/>
     <col width="12" customWidth="1" min="66" max="66"/>
     <col width="12" customWidth="1" min="67" max="67"/>
+    <col width="12" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2813,6 +2872,11 @@
           <t>20260105</t>
         </is>
       </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>20260106</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3020,6 +3084,9 @@
       <c r="BO2" t="n">
         <v>103</v>
       </c>
+      <c r="BP2" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3227,6 +3294,9 @@
       <c r="BO3" t="n">
         <v>117</v>
       </c>
+      <c r="BP3" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3434,6 +3504,9 @@
       <c r="BO4" t="n">
         <v>104</v>
       </c>
+      <c r="BP4" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3641,6 +3714,9 @@
       <c r="BO5" t="n">
         <v>110</v>
       </c>
+      <c r="BP5" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3848,6 +3924,9 @@
       <c r="BO6" t="n">
         <v>115</v>
       </c>
+      <c r="BP6" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4055,6 +4134,9 @@
       <c r="BO7" t="n">
         <v>117</v>
       </c>
+      <c r="BP7" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4262,6 +4344,9 @@
       <c r="BO8" t="n">
         <v>120</v>
       </c>
+      <c r="BP8" t="n">
+        <v>123</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4469,6 +4554,9 @@
       <c r="BO9" t="n">
         <v>86</v>
       </c>
+      <c r="BP9" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4676,6 +4764,9 @@
       <c r="BO10" t="n">
         <v>110</v>
       </c>
+      <c r="BP10" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4883,6 +4974,9 @@
       <c r="BO11" t="n">
         <v>92</v>
       </c>
+      <c r="BP11" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5090,6 +5184,9 @@
       <c r="BO12" t="n">
         <v>90</v>
       </c>
+      <c r="BP12" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5297,6 +5394,9 @@
       <c r="BO13" t="n">
         <v>91</v>
       </c>
+      <c r="BP13" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5504,6 +5604,9 @@
       <c r="BO14" t="n">
         <v>84</v>
       </c>
+      <c r="BP14" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5711,6 +5814,9 @@
       <c r="BO15" t="n">
         <v>103</v>
       </c>
+      <c r="BP15" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5918,6 +6024,9 @@
       <c r="BO16" t="n">
         <v>92</v>
       </c>
+      <c r="BP16" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6125,6 +6234,9 @@
       <c r="BO17" t="n">
         <v>91</v>
       </c>
+      <c r="BP17" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6332,6 +6444,9 @@
       <c r="BO18" t="n">
         <v>111</v>
       </c>
+      <c r="BP18" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6538,6 +6653,9 @@
       </c>
       <c r="BO19" t="n">
         <v>102</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -10577,7 +10695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10607,6 +10725,7 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
     <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10745,6 +10864,11 @@
           <t>20260105</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>20260106</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10832,6 +10956,9 @@
       <c r="AA2" t="n">
         <v>68</v>
       </c>
+      <c r="AB2" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10919,6 +11046,9 @@
       <c r="AA3" t="n">
         <v>92</v>
       </c>
+      <c r="AB3" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11006,6 +11136,9 @@
       <c r="AA4" t="n">
         <v>49</v>
       </c>
+      <c r="AB4" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11093,6 +11226,9 @@
       <c r="AA5" t="n">
         <v>127</v>
       </c>
+      <c r="AB5" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11180,6 +11316,9 @@
       <c r="AA6" t="n">
         <v>121</v>
       </c>
+      <c r="AB6" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11267,6 +11406,9 @@
       <c r="AA7" t="n">
         <v>57</v>
       </c>
+      <c r="AB7" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11354,6 +11496,9 @@
       <c r="AA8" t="n">
         <v>105</v>
       </c>
+      <c r="AB8" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11441,6 +11586,9 @@
       <c r="AA9" t="n">
         <v>47</v>
       </c>
+      <c r="AB9" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11528,6 +11676,9 @@
       <c r="AA10" t="n">
         <v>148</v>
       </c>
+      <c r="AB10" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11615,6 +11766,9 @@
       <c r="AA11" t="n">
         <v>16</v>
       </c>
+      <c r="AB11" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11702,6 +11856,9 @@
       <c r="AA12" t="n">
         <v>33</v>
       </c>
+      <c r="AB12" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11789,6 +11946,9 @@
       <c r="AA13" t="n">
         <v>31</v>
       </c>
+      <c r="AB13" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11876,6 +12036,9 @@
       <c r="AA14" t="n">
         <v>31</v>
       </c>
+      <c r="AB14" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11963,6 +12126,9 @@
       <c r="AA15" t="n">
         <v>54</v>
       </c>
+      <c r="AB15" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12050,6 +12216,9 @@
       <c r="AA16" t="n">
         <v>28</v>
       </c>
+      <c r="AB16" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12137,6 +12306,9 @@
       <c r="AA17" t="n">
         <v>17</v>
       </c>
+      <c r="AB17" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12224,6 +12396,9 @@
       <c r="AA18" t="n">
         <v>24</v>
       </c>
+      <c r="AB18" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12310,6 +12485,9 @@
       </c>
       <c r="AA19" t="n">
         <v>38</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -12323,7 +12501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH19"/>
+  <dimension ref="A1:CI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12412,6 +12590,7 @@
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
+    <col width="12" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12677,6 +12856,9 @@
       <c r="CH1" s="1" t="n">
         <v>20260105</v>
       </c>
+      <c r="CI1" s="1" t="n">
+        <v>20260106</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12941,6 +13123,9 @@
       <c r="CH2" t="n">
         <v>14805</v>
       </c>
+      <c r="CI2" t="n">
+        <v>15780</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13205,6 +13390,9 @@
       <c r="CH3" t="n">
         <v>67660</v>
       </c>
+      <c r="CI3" t="n">
+        <v>67735</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13469,6 +13657,9 @@
       <c r="CH4" t="n">
         <v>18100</v>
       </c>
+      <c r="CI4" t="n">
+        <v>18690</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13733,6 +13924,9 @@
       <c r="CH5" t="n">
         <v>17675</v>
       </c>
+      <c r="CI5" t="n">
+        <v>17385</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13997,6 +14191,9 @@
       <c r="CH6" t="n">
         <v>19620</v>
       </c>
+      <c r="CI6" t="n">
+        <v>19675</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14261,6 +14458,9 @@
       <c r="CH7" t="n">
         <v>23080</v>
       </c>
+      <c r="CI7" t="n">
+        <v>23165</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14525,6 +14725,9 @@
       <c r="CH8" t="n">
         <v>22375</v>
       </c>
+      <c r="CI8" t="n">
+        <v>22585</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14789,6 +14992,9 @@
       <c r="CH9" t="n">
         <v>1153</v>
       </c>
+      <c r="CI9" t="n">
+        <v>1269</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15053,6 +15259,9 @@
       <c r="CH10" t="n">
         <v>18590</v>
       </c>
+      <c r="CI10" t="n">
+        <v>18525</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15317,6 +15526,9 @@
       <c r="CH11" t="n">
         <v>4725</v>
       </c>
+      <c r="CI11" t="n">
+        <v>4970</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15581,6 +15793,9 @@
       <c r="CH12" t="n">
         <v>4910</v>
       </c>
+      <c r="CI12" t="n">
+        <v>5265</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15845,6 +16060,9 @@
       <c r="CH13" t="n">
         <v>5010</v>
       </c>
+      <c r="CI13" t="n">
+        <v>5385</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16109,6 +16327,9 @@
       <c r="CH14" t="n">
         <v>1217</v>
       </c>
+      <c r="CI14" t="n">
+        <v>1349</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -16373,6 +16594,9 @@
       <c r="CH15" t="n">
         <v>19010</v>
       </c>
+      <c r="CI15" t="n">
+        <v>19930</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -16637,6 +16861,9 @@
       <c r="CH16" t="n">
         <v>9490</v>
       </c>
+      <c r="CI16" t="n">
+        <v>10085</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16901,6 +17128,9 @@
       <c r="CH17" t="n">
         <v>5515</v>
       </c>
+      <c r="CI17" t="n">
+        <v>5850</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17165,6 +17395,9 @@
       <c r="CH18" t="n">
         <v>19945</v>
       </c>
+      <c r="CI18" t="n">
+        <v>19890</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17428,6 +17661,9 @@
       </c>
       <c r="CH19" t="n">
         <v>15875</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>16435</v>
       </c>
     </row>
   </sheetData>
@@ -17441,7 +17677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH19"/>
+  <dimension ref="A1:CI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17530,6 +17766,7 @@
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
+    <col width="12" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17795,6 +18032,9 @@
       <c r="CH1" s="1" t="n">
         <v>20260105</v>
       </c>
+      <c r="CI1" s="1" t="n">
+        <v>20260106</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18059,6 +18299,9 @@
       <c r="CH2" t="n">
         <v>15755</v>
       </c>
+      <c r="CI2" t="n">
+        <v>15905</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18323,6 +18566,9 @@
       <c r="CH3" t="n">
         <v>68750</v>
       </c>
+      <c r="CI3" t="n">
+        <v>70785</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18587,6 +18833,9 @@
       <c r="CH4" t="n">
         <v>18670</v>
       </c>
+      <c r="CI4" t="n">
+        <v>18850</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18851,6 +19100,9 @@
       <c r="CH5" t="n">
         <v>17855</v>
       </c>
+      <c r="CI5" t="n">
+        <v>17710</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19115,6 +19367,9 @@
       <c r="CH6" t="n">
         <v>19925</v>
       </c>
+      <c r="CI6" t="n">
+        <v>20335</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19379,6 +19634,9 @@
       <c r="CH7" t="n">
         <v>23335</v>
       </c>
+      <c r="CI7" t="n">
+        <v>23900</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19643,6 +19901,9 @@
       <c r="CH8" t="n">
         <v>22850</v>
       </c>
+      <c r="CI8" t="n">
+        <v>23640</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19907,6 +20168,9 @@
       <c r="CH9" t="n">
         <v>1235</v>
       </c>
+      <c r="CI9" t="n">
+        <v>1276</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20171,6 +20435,9 @@
       <c r="CH10" t="n">
         <v>18925</v>
       </c>
+      <c r="CI10" t="n">
+        <v>19100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -20435,6 +20702,9 @@
       <c r="CH11" t="n">
         <v>4905</v>
       </c>
+      <c r="CI11" t="n">
+        <v>4995</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -20699,6 +20969,9 @@
       <c r="CH12" t="n">
         <v>5180</v>
       </c>
+      <c r="CI12" t="n">
+        <v>5305</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -20963,6 +21236,9 @@
       <c r="CH13" t="n">
         <v>5270</v>
       </c>
+      <c r="CI13" t="n">
+        <v>5390</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -21227,6 +21503,9 @@
       <c r="CH14" t="n">
         <v>1322</v>
       </c>
+      <c r="CI14" t="n">
+        <v>1365</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -21491,6 +21770,9 @@
       <c r="CH15" t="n">
         <v>19945</v>
       </c>
+      <c r="CI15" t="n">
+        <v>20090</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -21755,6 +22037,9 @@
       <c r="CH16" t="n">
         <v>9920</v>
       </c>
+      <c r="CI16" t="n">
+        <v>10125</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -22019,6 +22304,9 @@
       <c r="CH17" t="n">
         <v>5765</v>
       </c>
+      <c r="CI17" t="n">
+        <v>5880</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -22283,6 +22571,9 @@
       <c r="CH18" t="n">
         <v>20090</v>
       </c>
+      <c r="CI18" t="n">
+        <v>20545</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -22546,6 +22837,9 @@
       </c>
       <c r="CH19" t="n">
         <v>16450</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>16555</v>
       </c>
     </row>
   </sheetData>
@@ -22559,7 +22853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH19"/>
+  <dimension ref="A1:CI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22648,6 +22942,7 @@
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
+    <col width="12" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22913,6 +23208,9 @@
       <c r="CH1" s="1" t="n">
         <v>20260105</v>
       </c>
+      <c r="CI1" s="1" t="n">
+        <v>20260106</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23177,6 +23475,9 @@
       <c r="CH2" t="n">
         <v>14680</v>
       </c>
+      <c r="CI2" t="n">
+        <v>15525</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23441,6 +23742,9 @@
       <c r="CH3" t="n">
         <v>67005</v>
       </c>
+      <c r="CI3" t="n">
+        <v>66435</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23705,6 +24009,9 @@
       <c r="CH4" t="n">
         <v>17780</v>
       </c>
+      <c r="CI4" t="n">
+        <v>18430</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23969,6 +24276,9 @@
       <c r="CH5" t="n">
         <v>17310</v>
       </c>
+      <c r="CI5" t="n">
+        <v>16940</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24233,6 +24543,9 @@
       <c r="CH6" t="n">
         <v>19410</v>
       </c>
+      <c r="CI6" t="n">
+        <v>19290</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24497,6 +24810,9 @@
       <c r="CH7" t="n">
         <v>22775</v>
       </c>
+      <c r="CI7" t="n">
+        <v>22615</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24761,6 +25077,9 @@
       <c r="CH8" t="n">
         <v>22200</v>
       </c>
+      <c r="CI8" t="n">
+        <v>22130</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25025,6 +25344,9 @@
       <c r="CH9" t="n">
         <v>1153</v>
       </c>
+      <c r="CI9" t="n">
+        <v>1231</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25289,6 +25611,9 @@
       <c r="CH10" t="n">
         <v>18265</v>
       </c>
+      <c r="CI10" t="n">
+        <v>18210</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25553,6 +25878,9 @@
       <c r="CH11" t="n">
         <v>4720</v>
       </c>
+      <c r="CI11" t="n">
+        <v>4880</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25817,6 +26145,9 @@
       <c r="CH12" t="n">
         <v>4910</v>
       </c>
+      <c r="CI12" t="n">
+        <v>5190</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -26081,6 +26412,9 @@
       <c r="CH13" t="n">
         <v>5010</v>
       </c>
+      <c r="CI13" t="n">
+        <v>5255</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -26345,6 +26679,9 @@
       <c r="CH14" t="n">
         <v>1212</v>
       </c>
+      <c r="CI14" t="n">
+        <v>1315</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -26609,6 +26946,9 @@
       <c r="CH15" t="n">
         <v>18645</v>
       </c>
+      <c r="CI15" t="n">
+        <v>19615</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -26873,6 +27213,9 @@
       <c r="CH16" t="n">
         <v>9490</v>
       </c>
+      <c r="CI16" t="n">
+        <v>9920</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -27137,6 +27480,9 @@
       <c r="CH17" t="n">
         <v>5515</v>
       </c>
+      <c r="CI17" t="n">
+        <v>5785</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -27401,6 +27747,9 @@
       <c r="CH18" t="n">
         <v>19440</v>
       </c>
+      <c r="CI18" t="n">
+        <v>19515</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -27664,6 +28013,9 @@
       </c>
       <c r="CH19" t="n">
         <v>15635</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>16170</v>
       </c>
     </row>
   </sheetData>
@@ -27677,7 +28029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH19"/>
+  <dimension ref="A1:CI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27766,6 +28118,7 @@
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
+    <col width="12" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28031,6 +28384,9 @@
       <c r="CH1" s="1" t="n">
         <v>20260105</v>
       </c>
+      <c r="CI1" s="1" t="n">
+        <v>20260106</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28295,6 +28651,9 @@
       <c r="CH2" t="n">
         <v>15740</v>
       </c>
+      <c r="CI2" t="n">
+        <v>15665</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28559,6 +28918,9 @@
       <c r="CH3" t="n">
         <v>68600</v>
       </c>
+      <c r="CI3" t="n">
+        <v>70785</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28823,6 +29185,9 @@
       <c r="CH4" t="n">
         <v>18640</v>
       </c>
+      <c r="CI4" t="n">
+        <v>18555</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29087,6 +29452,9 @@
       <c r="CH5" t="n">
         <v>17515</v>
       </c>
+      <c r="CI5" t="n">
+        <v>17685</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29351,6 +29719,9 @@
       <c r="CH6" t="n">
         <v>19870</v>
       </c>
+      <c r="CI6" t="n">
+        <v>20335</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29615,6 +29986,9 @@
       <c r="CH7" t="n">
         <v>23325</v>
       </c>
+      <c r="CI7" t="n">
+        <v>23855</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29879,6 +30253,9 @@
       <c r="CH8" t="n">
         <v>22850</v>
       </c>
+      <c r="CI8" t="n">
+        <v>23640</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30143,6 +30520,9 @@
       <c r="CH9" t="n">
         <v>1223</v>
       </c>
+      <c r="CI9" t="n">
+        <v>1257</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30407,6 +30787,9 @@
       <c r="CH10" t="n">
         <v>18635</v>
       </c>
+      <c r="CI10" t="n">
+        <v>19100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30671,6 +31054,9 @@
       <c r="CH11" t="n">
         <v>4850</v>
       </c>
+      <c r="CI11" t="n">
+        <v>4915</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30935,6 +31321,9 @@
       <c r="CH12" t="n">
         <v>5125</v>
       </c>
+      <c r="CI12" t="n">
+        <v>5220</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31199,6 +31588,9 @@
       <c r="CH13" t="n">
         <v>5220</v>
       </c>
+      <c r="CI13" t="n">
+        <v>5295</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31463,6 +31855,9 @@
       <c r="CH14" t="n">
         <v>1299</v>
       </c>
+      <c r="CI14" t="n">
+        <v>1329</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -31727,6 +32122,9 @@
       <c r="CH15" t="n">
         <v>19925</v>
       </c>
+      <c r="CI15" t="n">
+        <v>19770</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -31991,6 +32389,9 @@
       <c r="CH16" t="n">
         <v>9845</v>
       </c>
+      <c r="CI16" t="n">
+        <v>10010</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -32255,6 +32656,9 @@
       <c r="CH17" t="n">
         <v>5710</v>
       </c>
+      <c r="CI17" t="n">
+        <v>5810</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -32519,6 +32923,9 @@
       <c r="CH18" t="n">
         <v>19950</v>
       </c>
+      <c r="CI18" t="n">
+        <v>20545</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -32782,6 +33189,9 @@
       </c>
       <c r="CH19" t="n">
         <v>16435</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>16275</v>
       </c>
     </row>
   </sheetData>
@@ -32795,7 +33205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH19"/>
+  <dimension ref="A1:CI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -32884,6 +33294,7 @@
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
+    <col width="12" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33149,6 +33560,9 @@
       <c r="CH1" s="1" t="n">
         <v>20260105</v>
       </c>
+      <c r="CI1" s="1" t="n">
+        <v>20260106</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33413,6 +33827,9 @@
       <c r="CH2" t="n">
         <v>177035</v>
       </c>
+      <c r="CI2" t="n">
+        <v>145136</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -33677,6 +34094,9 @@
       <c r="CH3" t="n">
         <v>4395229</v>
       </c>
+      <c r="CI3" t="n">
+        <v>5061353</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -33941,6 +34361,9 @@
       <c r="CH4" t="n">
         <v>172792</v>
       </c>
+      <c r="CI4" t="n">
+        <v>130988</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34205,6 +34628,9 @@
       <c r="CH5" t="n">
         <v>1995377</v>
       </c>
+      <c r="CI5" t="n">
+        <v>463326</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34469,6 +34895,9 @@
       <c r="CH6" t="n">
         <v>5160628</v>
       </c>
+      <c r="CI6" t="n">
+        <v>6514528</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -34733,6 +35162,9 @@
       <c r="CH7" t="n">
         <v>4786647</v>
       </c>
+      <c r="CI7" t="n">
+        <v>3933169</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -34997,6 +35429,9 @@
       <c r="CH8" t="n">
         <v>15898595</v>
       </c>
+      <c r="CI8" t="n">
+        <v>16983095</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35261,6 +35696,9 @@
       <c r="CH9" t="n">
         <v>7211412</v>
       </c>
+      <c r="CI9" t="n">
+        <v>3375106</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35525,6 +35963,9 @@
       <c r="CH10" t="n">
         <v>4052041</v>
       </c>
+      <c r="CI10" t="n">
+        <v>2296845</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -35789,6 +36230,9 @@
       <c r="CH11" t="n">
         <v>431618</v>
       </c>
+      <c r="CI11" t="n">
+        <v>673223</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -36053,6 +36497,9 @@
       <c r="CH12" t="n">
         <v>2012540</v>
       </c>
+      <c r="CI12" t="n">
+        <v>1384731</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36317,6 +36764,9 @@
       <c r="CH13" t="n">
         <v>4552736</v>
       </c>
+      <c r="CI13" t="n">
+        <v>4979516</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36581,6 +37031,9 @@
       <c r="CH14" t="n">
         <v>32466922</v>
       </c>
+      <c r="CI14" t="n">
+        <v>27316934</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36845,6 +37298,9 @@
       <c r="CH15" t="n">
         <v>1889416</v>
       </c>
+      <c r="CI15" t="n">
+        <v>1324727</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -37109,6 +37565,9 @@
       <c r="CH16" t="n">
         <v>351012</v>
       </c>
+      <c r="CI16" t="n">
+        <v>236919</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37373,6 +37832,9 @@
       <c r="CH17" t="n">
         <v>84958</v>
       </c>
+      <c r="CI17" t="n">
+        <v>87430</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -37637,6 +38099,9 @@
       <c r="CH18" t="n">
         <v>85995</v>
       </c>
+      <c r="CI18" t="n">
+        <v>121853</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -37900,6 +38365,9 @@
       </c>
       <c r="CH19" t="n">
         <v>35964</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>22124</v>
       </c>
     </row>
   </sheetData>
@@ -37913,7 +38381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO19"/>
+  <dimension ref="A1:BP19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37983,6 +38451,7 @@
     <col width="10" customWidth="1" min="65" max="65"/>
     <col width="10" customWidth="1" min="66" max="66"/>
     <col width="10" customWidth="1" min="67" max="67"/>
+    <col width="10" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38191,6 +38660,9 @@
       <c r="BO1" s="1" t="n">
         <v>20260105</v>
       </c>
+      <c r="BP1" s="1" t="n">
+        <v>20260106</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -38398,6 +38870,9 @@
       <c r="BO2" t="n">
         <v>61</v>
       </c>
+      <c r="BP2" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38605,6 +39080,9 @@
       <c r="BO3" t="n">
         <v>100</v>
       </c>
+      <c r="BP3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -38812,6 +39290,9 @@
       <c r="BO4" t="n">
         <v>81</v>
       </c>
+      <c r="BP4" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -39019,6 +39500,9 @@
       <c r="BO5" t="n">
         <v>100</v>
       </c>
+      <c r="BP5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -39226,6 +39710,9 @@
       <c r="BO6" t="n">
         <v>100</v>
       </c>
+      <c r="BP6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -39433,6 +39920,9 @@
       <c r="BO7" t="n">
         <v>100</v>
       </c>
+      <c r="BP7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -39640,6 +40130,9 @@
       <c r="BO8" t="n">
         <v>100</v>
       </c>
+      <c r="BP8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -39847,6 +40340,9 @@
       <c r="BO9" t="n">
         <v>12</v>
       </c>
+      <c r="BP9" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -40054,6 +40550,9 @@
       <c r="BO10" t="n">
         <v>100</v>
       </c>
+      <c r="BP10" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -40261,6 +40760,9 @@
       <c r="BO11" t="n">
         <v>9</v>
       </c>
+      <c r="BP11" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -40468,6 +40970,9 @@
       <c r="BO12" t="n">
         <v>8</v>
       </c>
+      <c r="BP12" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -40675,6 +41180,9 @@
       <c r="BO13" t="n">
         <v>10</v>
       </c>
+      <c r="BP13" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -40882,6 +41390,9 @@
       <c r="BO14" t="n">
         <v>11</v>
       </c>
+      <c r="BP14" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41089,6 +41600,9 @@
       <c r="BO15" t="n">
         <v>72</v>
       </c>
+      <c r="BP15" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -41296,6 +41810,9 @@
       <c r="BO16" t="n">
         <v>13</v>
       </c>
+      <c r="BP16" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41503,6 +42020,9 @@
       <c r="BO17" t="n">
         <v>11</v>
       </c>
+      <c r="BP17" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41710,6 +42230,9 @@
       <c r="BO18" t="n">
         <v>100</v>
       </c>
+      <c r="BP18" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -41916,6 +42439,9 @@
       </c>
       <c r="BO19" t="n">
         <v>77</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -41929,7 +42455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -41959,6 +42485,7 @@
     <col width="10" customWidth="1" min="25" max="25"/>
     <col width="10" customWidth="1" min="26" max="26"/>
     <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -42047,6 +42574,9 @@
       <c r="AA1" s="1" t="n">
         <v>20260105</v>
       </c>
+      <c r="AB1" s="1" t="n">
+        <v>20260106</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -42134,6 +42664,9 @@
       <c r="AA2" t="n">
         <v>77</v>
       </c>
+      <c r="AB2" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -42221,6 +42754,9 @@
       <c r="AA3" t="n">
         <v>100</v>
       </c>
+      <c r="AB3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -42308,6 +42844,9 @@
       <c r="AA4" t="n">
         <v>82</v>
       </c>
+      <c r="AB4" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -42395,6 +42934,9 @@
       <c r="AA5" t="n">
         <v>100</v>
       </c>
+      <c r="AB5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -42482,6 +43024,9 @@
       <c r="AA6" t="n">
         <v>100</v>
       </c>
+      <c r="AB6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -42569,6 +43114,9 @@
       <c r="AA7" t="n">
         <v>100</v>
       </c>
+      <c r="AB7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -42656,6 +43204,9 @@
       <c r="AA8" t="n">
         <v>100</v>
       </c>
+      <c r="AB8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -42743,6 +43294,9 @@
       <c r="AA9" t="n">
         <v>21</v>
       </c>
+      <c r="AB9" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -42830,6 +43384,9 @@
       <c r="AA10" t="n">
         <v>100</v>
       </c>
+      <c r="AB10" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -42917,6 +43474,9 @@
       <c r="AA11" t="n">
         <v>54</v>
       </c>
+      <c r="AB11" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -43004,6 +43564,9 @@
       <c r="AA12" t="n">
         <v>51</v>
       </c>
+      <c r="AB12" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -43091,6 +43654,9 @@
       <c r="AA13" t="n">
         <v>54</v>
       </c>
+      <c r="AB13" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -43178,6 +43744,9 @@
       <c r="AA14" t="n">
         <v>28</v>
       </c>
+      <c r="AB14" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -43265,6 +43834,9 @@
       <c r="AA15" t="n">
         <v>92</v>
       </c>
+      <c r="AB15" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -43352,6 +43924,9 @@
       <c r="AA16" t="n">
         <v>46</v>
       </c>
+      <c r="AB16" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -43439,6 +44014,9 @@
       <c r="AA17" t="n">
         <v>42</v>
       </c>
+      <c r="AB17" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -43526,6 +44104,9 @@
       <c r="AA18" t="n">
         <v>100</v>
       </c>
+      <c r="AB18" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43612,6 +44193,9 @@
       </c>
       <c r="AA19" t="n">
         <v>92</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -43625,7 +44209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO19"/>
+  <dimension ref="A1:BP19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -43695,6 +44279,7 @@
     <col width="10" customWidth="1" min="65" max="65"/>
     <col width="10" customWidth="1" min="66" max="66"/>
     <col width="10" customWidth="1" min="67" max="67"/>
+    <col width="10" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43903,6 +44488,9 @@
       <c r="BO1" s="1" t="n">
         <v>20260105</v>
       </c>
+      <c r="BP1" s="1" t="n">
+        <v>20260106</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -44110,6 +44698,9 @@
       <c r="BO2" t="n">
         <v>48</v>
       </c>
+      <c r="BP2" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -44317,6 +44908,9 @@
       <c r="BO3" t="n">
         <v>148</v>
       </c>
+      <c r="BP3" t="n">
+        <v>133</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -44524,6 +45118,9 @@
       <c r="BO4" t="n">
         <v>76</v>
       </c>
+      <c r="BP4" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -44731,6 +45328,9 @@
       <c r="BO5" t="n">
         <v>124</v>
       </c>
+      <c r="BP5" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -44938,6 +45538,9 @@
       <c r="BO6" t="n">
         <v>145</v>
       </c>
+      <c r="BP6" t="n">
+        <v>129</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -45145,6 +45748,9 @@
       <c r="BO7" t="n">
         <v>146</v>
       </c>
+      <c r="BP7" t="n">
+        <v>129</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -45352,6 +45958,9 @@
       <c r="BO8" t="n">
         <v>148</v>
       </c>
+      <c r="BP8" t="n">
+        <v>133</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -45559,6 +46168,9 @@
       <c r="BO9" t="n">
         <v>-62</v>
       </c>
+      <c r="BP9" t="n">
+        <v>-47</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -45766,6 +46378,9 @@
       <c r="BO10" t="n">
         <v>130</v>
       </c>
+      <c r="BP10" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -45973,6 +46588,9 @@
       <c r="BO11" t="n">
         <v>-70</v>
       </c>
+      <c r="BP11" t="n">
+        <v>-55</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -46180,6 +46798,9 @@
       <c r="BO12" t="n">
         <v>-71</v>
       </c>
+      <c r="BP12" t="n">
+        <v>-55</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -46387,6 +47008,9 @@
       <c r="BO13" t="n">
         <v>-68</v>
       </c>
+      <c r="BP13" t="n">
+        <v>-55</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -46594,6 +47218,9 @@
       <c r="BO14" t="n">
         <v>-63</v>
       </c>
+      <c r="BP14" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -46801,6 +47428,9 @@
       <c r="BO15" t="n">
         <v>69</v>
       </c>
+      <c r="BP15" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -47008,6 +47638,9 @@
       <c r="BO16" t="n">
         <v>-62</v>
       </c>
+      <c r="BP16" t="n">
+        <v>-46</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -47215,6 +47848,9 @@
       <c r="BO17" t="n">
         <v>-68</v>
       </c>
+      <c r="BP17" t="n">
+        <v>-52</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -47422,6 +48058,9 @@
       <c r="BO18" t="n">
         <v>128</v>
       </c>
+      <c r="BP18" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -47628,6 +48267,9 @@
       </c>
       <c r="BO19" t="n">
         <v>71</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -740,6 +740,7 @@
     <col width="10" customWidth="1" min="26" max="26"/>
     <col width="10" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -831,6 +832,9 @@
       <c r="AB1" s="1" t="n">
         <v>20260106</v>
       </c>
+      <c r="AC1" s="1" t="n">
+        <v>20260107</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -921,6 +925,9 @@
       <c r="AB2" t="n">
         <v>35</v>
       </c>
+      <c r="AC2" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1011,6 +1018,9 @@
       <c r="AB3" t="n">
         <v>194</v>
       </c>
+      <c r="AC3" t="n">
+        <v>167</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1101,6 +1111,9 @@
       <c r="AB4" t="n">
         <v>44</v>
       </c>
+      <c r="AC4" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1191,6 +1204,9 @@
       <c r="AB5" t="n">
         <v>125</v>
       </c>
+      <c r="AC5" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1281,6 +1297,9 @@
       <c r="AB6" t="n">
         <v>172</v>
       </c>
+      <c r="AC6" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1371,6 +1390,9 @@
       <c r="AB7" t="n">
         <v>174</v>
       </c>
+      <c r="AC7" t="n">
+        <v>161</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1461,6 +1483,9 @@
       <c r="AB8" t="n">
         <v>202</v>
       </c>
+      <c r="AC8" t="n">
+        <v>179</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1551,6 +1576,9 @@
       <c r="AB9" t="n">
         <v>-60</v>
       </c>
+      <c r="AC9" t="n">
+        <v>-69</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1641,6 +1669,9 @@
       <c r="AB10" t="n">
         <v>159</v>
       </c>
+      <c r="AC10" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1731,6 +1762,9 @@
       <c r="AB11" t="n">
         <v>-30</v>
       </c>
+      <c r="AC11" t="n">
+        <v>-44</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1821,6 +1855,9 @@
       <c r="AB12" t="n">
         <v>-33</v>
       </c>
+      <c r="AC12" t="n">
+        <v>-42</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1911,6 +1948,9 @@
       <c r="AB13" t="n">
         <v>-22</v>
       </c>
+      <c r="AC13" t="n">
+        <v>-33</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2001,6 +2041,9 @@
       <c r="AB14" t="n">
         <v>-56</v>
       </c>
+      <c r="AC14" t="n">
+        <v>-69</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2091,6 +2134,9 @@
       <c r="AB15" t="n">
         <v>49</v>
       </c>
+      <c r="AC15" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2181,6 +2227,9 @@
       <c r="AB16" t="n">
         <v>-35</v>
       </c>
+      <c r="AC16" t="n">
+        <v>-47</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2271,6 +2320,9 @@
       <c r="AB17" t="n">
         <v>-45</v>
       </c>
+      <c r="AC17" t="n">
+        <v>-57</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2361,6 +2413,9 @@
       <c r="AB18" t="n">
         <v>145</v>
       </c>
+      <c r="AC18" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2450,6 +2505,9 @@
       </c>
       <c r="AB19" t="n">
         <v>47</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -2463,7 +2521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP19"/>
+  <dimension ref="A1:BQ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2534,6 +2592,7 @@
     <col width="12" customWidth="1" min="66" max="66"/>
     <col width="12" customWidth="1" min="67" max="67"/>
     <col width="12" customWidth="1" min="68" max="68"/>
+    <col width="12" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2877,6 +2936,11 @@
           <t>20260106</t>
         </is>
       </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>20260107</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3087,6 +3151,9 @@
       <c r="BP2" t="n">
         <v>103</v>
       </c>
+      <c r="BQ2" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3297,6 +3364,9 @@
       <c r="BP3" t="n">
         <v>120</v>
       </c>
+      <c r="BQ3" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3507,6 +3577,9 @@
       <c r="BP4" t="n">
         <v>104</v>
       </c>
+      <c r="BQ4" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3717,6 +3790,9 @@
       <c r="BP5" t="n">
         <v>111</v>
       </c>
+      <c r="BQ5" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3927,6 +4003,9 @@
       <c r="BP6" t="n">
         <v>117</v>
       </c>
+      <c r="BQ6" t="n">
+        <v>115</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4137,6 +4216,9 @@
       <c r="BP7" t="n">
         <v>118</v>
       </c>
+      <c r="BQ7" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4347,6 +4429,9 @@
       <c r="BP8" t="n">
         <v>123</v>
       </c>
+      <c r="BQ8" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4557,6 +4642,9 @@
       <c r="BP9" t="n">
         <v>89</v>
       </c>
+      <c r="BQ9" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4767,6 +4855,9 @@
       <c r="BP10" t="n">
         <v>112</v>
       </c>
+      <c r="BQ10" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4977,6 +5068,9 @@
       <c r="BP11" t="n">
         <v>93</v>
       </c>
+      <c r="BQ11" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5187,6 +5281,9 @@
       <c r="BP12" t="n">
         <v>92</v>
       </c>
+      <c r="BQ12" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5397,6 +5494,9 @@
       <c r="BP13" t="n">
         <v>92</v>
       </c>
+      <c r="BQ13" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5607,6 +5707,9 @@
       <c r="BP14" t="n">
         <v>87</v>
       </c>
+      <c r="BQ14" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5817,6 +5920,9 @@
       <c r="BP15" t="n">
         <v>103</v>
       </c>
+      <c r="BQ15" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6027,6 +6133,9 @@
       <c r="BP16" t="n">
         <v>94</v>
       </c>
+      <c r="BQ16" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6237,6 +6346,9 @@
       <c r="BP17" t="n">
         <v>93</v>
       </c>
+      <c r="BQ17" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6447,6 +6559,9 @@
       <c r="BP18" t="n">
         <v>114</v>
       </c>
+      <c r="BQ18" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6656,6 +6771,9 @@
       </c>
       <c r="BP19" t="n">
         <v>101</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -10695,7 +10813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10726,6 +10844,7 @@
     <col width="12" customWidth="1" min="26" max="26"/>
     <col width="12" customWidth="1" min="27" max="27"/>
     <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10869,6 +10988,11 @@
           <t>20260106</t>
         </is>
       </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>20260107</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10959,6 +11083,9 @@
       <c r="AB2" t="n">
         <v>55</v>
       </c>
+      <c r="AC2" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11049,6 +11176,9 @@
       <c r="AB3" t="n">
         <v>104</v>
       </c>
+      <c r="AC3" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11139,6 +11269,9 @@
       <c r="AB4" t="n">
         <v>37</v>
       </c>
+      <c r="AC4" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11229,6 +11362,9 @@
       <c r="AB5" t="n">
         <v>32</v>
       </c>
+      <c r="AC5" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11319,6 +11455,9 @@
       <c r="AB6" t="n">
         <v>148</v>
       </c>
+      <c r="AC6" t="n">
+        <v>185</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11409,6 +11548,9 @@
       <c r="AB7" t="n">
         <v>49</v>
       </c>
+      <c r="AC7" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11499,6 +11641,9 @@
       <c r="AB8" t="n">
         <v>111</v>
       </c>
+      <c r="AC8" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11589,6 +11734,9 @@
       <c r="AB9" t="n">
         <v>22</v>
       </c>
+      <c r="AC9" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11679,6 +11827,9 @@
       <c r="AB10" t="n">
         <v>85</v>
       </c>
+      <c r="AC10" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11769,6 +11920,9 @@
       <c r="AB11" t="n">
         <v>25</v>
       </c>
+      <c r="AC11" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11859,6 +12013,9 @@
       <c r="AB12" t="n">
         <v>23</v>
       </c>
+      <c r="AC12" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11949,6 +12106,9 @@
       <c r="AB13" t="n">
         <v>34</v>
       </c>
+      <c r="AC13" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12039,6 +12199,9 @@
       <c r="AB14" t="n">
         <v>26</v>
       </c>
+      <c r="AC14" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12129,6 +12292,9 @@
       <c r="AB15" t="n">
         <v>37</v>
       </c>
+      <c r="AC15" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12219,6 +12385,9 @@
       <c r="AB16" t="n">
         <v>19</v>
       </c>
+      <c r="AC16" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12309,6 +12478,9 @@
       <c r="AB17" t="n">
         <v>18</v>
       </c>
+      <c r="AC17" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12399,6 +12571,9 @@
       <c r="AB18" t="n">
         <v>35</v>
       </c>
+      <c r="AC18" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12488,6 +12663,9 @@
       </c>
       <c r="AB19" t="n">
         <v>23</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -12501,7 +12679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI19"/>
+  <dimension ref="A1:CJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12591,6 +12769,7 @@
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
+    <col width="12" customWidth="1" min="88" max="88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12859,6 +13038,9 @@
       <c r="CI1" s="1" t="n">
         <v>20260106</v>
       </c>
+      <c r="CJ1" s="1" t="n">
+        <v>20260107</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13126,6 +13308,9 @@
       <c r="CI2" t="n">
         <v>15780</v>
       </c>
+      <c r="CJ2" t="n">
+        <v>15780</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13393,6 +13578,9 @@
       <c r="CI3" t="n">
         <v>67735</v>
       </c>
+      <c r="CJ3" t="n">
+        <v>72440</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13660,6 +13848,9 @@
       <c r="CI4" t="n">
         <v>18690</v>
       </c>
+      <c r="CJ4" t="n">
+        <v>18535</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13927,6 +14118,9 @@
       <c r="CI5" t="n">
         <v>17385</v>
       </c>
+      <c r="CJ5" t="n">
+        <v>18080</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14194,6 +14388,9 @@
       <c r="CI6" t="n">
         <v>19675</v>
       </c>
+      <c r="CJ6" t="n">
+        <v>20775</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14461,6 +14658,9 @@
       <c r="CI7" t="n">
         <v>23165</v>
       </c>
+      <c r="CJ7" t="n">
+        <v>24475</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14728,6 +14928,9 @@
       <c r="CI8" t="n">
         <v>22585</v>
       </c>
+      <c r="CJ8" t="n">
+        <v>24250</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14995,6 +15198,9 @@
       <c r="CI9" t="n">
         <v>1269</v>
       </c>
+      <c r="CJ9" t="n">
+        <v>1260</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15262,6 +15468,9 @@
       <c r="CI10" t="n">
         <v>18525</v>
       </c>
+      <c r="CJ10" t="n">
+        <v>19330</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15529,6 +15738,9 @@
       <c r="CI11" t="n">
         <v>4970</v>
       </c>
+      <c r="CJ11" t="n">
+        <v>4905</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15796,6 +16008,9 @@
       <c r="CI12" t="n">
         <v>5265</v>
       </c>
+      <c r="CJ12" t="n">
+        <v>5235</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16063,6 +16278,9 @@
       <c r="CI13" t="n">
         <v>5385</v>
       </c>
+      <c r="CJ13" t="n">
+        <v>5300</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16330,6 +16548,9 @@
       <c r="CI14" t="n">
         <v>1349</v>
       </c>
+      <c r="CJ14" t="n">
+        <v>1336</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -16597,6 +16818,9 @@
       <c r="CI15" t="n">
         <v>19930</v>
       </c>
+      <c r="CJ15" t="n">
+        <v>19865</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -16864,6 +17088,9 @@
       <c r="CI16" t="n">
         <v>10085</v>
       </c>
+      <c r="CJ16" t="n">
+        <v>10020</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17131,6 +17358,9 @@
       <c r="CI17" t="n">
         <v>5850</v>
       </c>
+      <c r="CJ17" t="n">
+        <v>5835</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17398,6 +17628,9 @@
       <c r="CI18" t="n">
         <v>19890</v>
       </c>
+      <c r="CJ18" t="n">
+        <v>20980</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17664,6 +17897,9 @@
       </c>
       <c r="CI19" t="n">
         <v>16435</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>16365</v>
       </c>
     </row>
   </sheetData>
@@ -17677,7 +17913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI19"/>
+  <dimension ref="A1:CJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17767,6 +18003,7 @@
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
+    <col width="12" customWidth="1" min="88" max="88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18035,6 +18272,9 @@
       <c r="CI1" s="1" t="n">
         <v>20260106</v>
       </c>
+      <c r="CJ1" s="1" t="n">
+        <v>20260107</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18302,6 +18542,9 @@
       <c r="CI2" t="n">
         <v>15905</v>
       </c>
+      <c r="CJ2" t="n">
+        <v>16030</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18569,6 +18812,9 @@
       <c r="CI3" t="n">
         <v>70785</v>
       </c>
+      <c r="CJ3" t="n">
+        <v>72750</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18836,6 +19082,9 @@
       <c r="CI4" t="n">
         <v>18850</v>
       </c>
+      <c r="CJ4" t="n">
+        <v>18700</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19103,6 +19352,9 @@
       <c r="CI5" t="n">
         <v>17710</v>
       </c>
+      <c r="CJ5" t="n">
+        <v>18130</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19370,6 +19622,9 @@
       <c r="CI6" t="n">
         <v>20335</v>
       </c>
+      <c r="CJ6" t="n">
+        <v>20865</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19637,6 +19892,9 @@
       <c r="CI7" t="n">
         <v>23900</v>
       </c>
+      <c r="CJ7" t="n">
+        <v>24630</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19904,6 +20162,9 @@
       <c r="CI8" t="n">
         <v>23640</v>
       </c>
+      <c r="CJ8" t="n">
+        <v>24380</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20171,6 +20432,9 @@
       <c r="CI9" t="n">
         <v>1276</v>
       </c>
+      <c r="CJ9" t="n">
+        <v>1295</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20438,6 +20702,9 @@
       <c r="CI10" t="n">
         <v>19100</v>
       </c>
+      <c r="CJ10" t="n">
+        <v>19410</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -20705,6 +20972,9 @@
       <c r="CI11" t="n">
         <v>4995</v>
       </c>
+      <c r="CJ11" t="n">
+        <v>5010</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -20972,6 +21242,9 @@
       <c r="CI12" t="n">
         <v>5305</v>
       </c>
+      <c r="CJ12" t="n">
+        <v>5340</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -21239,6 +21512,9 @@
       <c r="CI13" t="n">
         <v>5390</v>
       </c>
+      <c r="CJ13" t="n">
+        <v>5430</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -21506,6 +21782,9 @@
       <c r="CI14" t="n">
         <v>1365</v>
       </c>
+      <c r="CJ14" t="n">
+        <v>1375</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -21773,6 +22052,9 @@
       <c r="CI15" t="n">
         <v>20090</v>
       </c>
+      <c r="CJ15" t="n">
+        <v>20120</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -22040,6 +22322,9 @@
       <c r="CI16" t="n">
         <v>10125</v>
       </c>
+      <c r="CJ16" t="n">
+        <v>10195</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -22307,6 +22592,9 @@
       <c r="CI17" t="n">
         <v>5880</v>
       </c>
+      <c r="CJ17" t="n">
+        <v>5910</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -22574,6 +22862,9 @@
       <c r="CI18" t="n">
         <v>20545</v>
       </c>
+      <c r="CJ18" t="n">
+        <v>21075</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -22840,6 +23131,9 @@
       </c>
       <c r="CI19" t="n">
         <v>16555</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>16665</v>
       </c>
     </row>
   </sheetData>
@@ -22853,7 +23147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI19"/>
+  <dimension ref="A1:CJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22943,6 +23237,7 @@
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
+    <col width="12" customWidth="1" min="88" max="88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23211,6 +23506,9 @@
       <c r="CI1" s="1" t="n">
         <v>20260106</v>
       </c>
+      <c r="CJ1" s="1" t="n">
+        <v>20260107</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23478,6 +23776,9 @@
       <c r="CI2" t="n">
         <v>15525</v>
       </c>
+      <c r="CJ2" t="n">
+        <v>15560</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23745,6 +24046,9 @@
       <c r="CI3" t="n">
         <v>66435</v>
       </c>
+      <c r="CJ3" t="n">
+        <v>69020</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24012,6 +24316,9 @@
       <c r="CI4" t="n">
         <v>18430</v>
       </c>
+      <c r="CJ4" t="n">
+        <v>18225</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24279,6 +24586,9 @@
       <c r="CI5" t="n">
         <v>16940</v>
       </c>
+      <c r="CJ5" t="n">
+        <v>17070</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24546,6 +24856,9 @@
       <c r="CI6" t="n">
         <v>19290</v>
       </c>
+      <c r="CJ6" t="n">
+        <v>19860</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24813,6 +25126,9 @@
       <c r="CI7" t="n">
         <v>22615</v>
       </c>
+      <c r="CJ7" t="n">
+        <v>23495</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25080,6 +25396,9 @@
       <c r="CI8" t="n">
         <v>22130</v>
       </c>
+      <c r="CJ8" t="n">
+        <v>23160</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25347,6 +25666,9 @@
       <c r="CI9" t="n">
         <v>1231</v>
       </c>
+      <c r="CJ9" t="n">
+        <v>1210</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25614,6 +25936,9 @@
       <c r="CI10" t="n">
         <v>18210</v>
       </c>
+      <c r="CJ10" t="n">
+        <v>18275</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25881,6 +26206,9 @@
       <c r="CI11" t="n">
         <v>4880</v>
       </c>
+      <c r="CJ11" t="n">
+        <v>4810</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26148,6 +26476,9 @@
       <c r="CI12" t="n">
         <v>5190</v>
       </c>
+      <c r="CJ12" t="n">
+        <v>5110</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -26415,6 +26746,9 @@
       <c r="CI13" t="n">
         <v>5255</v>
       </c>
+      <c r="CJ13" t="n">
+        <v>5190</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -26682,6 +27016,9 @@
       <c r="CI14" t="n">
         <v>1315</v>
       </c>
+      <c r="CJ14" t="n">
+        <v>1264</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -26949,6 +27286,9 @@
       <c r="CI15" t="n">
         <v>19615</v>
       </c>
+      <c r="CJ15" t="n">
+        <v>19500</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -27216,6 +27556,9 @@
       <c r="CI16" t="n">
         <v>9920</v>
       </c>
+      <c r="CJ16" t="n">
+        <v>9795</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -27483,6 +27826,9 @@
       <c r="CI17" t="n">
         <v>5785</v>
       </c>
+      <c r="CJ17" t="n">
+        <v>5675</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -27750,6 +28096,9 @@
       <c r="CI18" t="n">
         <v>19515</v>
       </c>
+      <c r="CJ18" t="n">
+        <v>19665</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -28016,6 +28365,9 @@
       </c>
       <c r="CI19" t="n">
         <v>16170</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>16195</v>
       </c>
     </row>
   </sheetData>
@@ -28029,7 +28381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI19"/>
+  <dimension ref="A1:CJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -28119,6 +28471,7 @@
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
+    <col width="12" customWidth="1" min="88" max="88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28387,6 +28740,9 @@
       <c r="CI1" s="1" t="n">
         <v>20260106</v>
       </c>
+      <c r="CJ1" s="1" t="n">
+        <v>20260107</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28654,6 +29010,9 @@
       <c r="CI2" t="n">
         <v>15665</v>
       </c>
+      <c r="CJ2" t="n">
+        <v>15870</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28921,6 +29280,9 @@
       <c r="CI3" t="n">
         <v>70785</v>
       </c>
+      <c r="CJ3" t="n">
+        <v>70300</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -29188,6 +29550,9 @@
       <c r="CI4" t="n">
         <v>18555</v>
       </c>
+      <c r="CJ4" t="n">
+        <v>18580</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29455,6 +29820,9 @@
       <c r="CI5" t="n">
         <v>17685</v>
       </c>
+      <c r="CJ5" t="n">
+        <v>17420</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29722,6 +30090,9 @@
       <c r="CI6" t="n">
         <v>20335</v>
       </c>
+      <c r="CJ6" t="n">
+        <v>20230</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29989,6 +30360,9 @@
       <c r="CI7" t="n">
         <v>23855</v>
       </c>
+      <c r="CJ7" t="n">
+        <v>23960</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30256,6 +30630,9 @@
       <c r="CI8" t="n">
         <v>23640</v>
       </c>
+      <c r="CJ8" t="n">
+        <v>23650</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30523,6 +30900,9 @@
       <c r="CI9" t="n">
         <v>1257</v>
       </c>
+      <c r="CJ9" t="n">
+        <v>1228</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30790,6 +31170,9 @@
       <c r="CI10" t="n">
         <v>19100</v>
       </c>
+      <c r="CJ10" t="n">
+        <v>18605</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -31057,6 +31440,9 @@
       <c r="CI11" t="n">
         <v>4915</v>
       </c>
+      <c r="CJ11" t="n">
+        <v>4845</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31324,6 +31710,9 @@
       <c r="CI12" t="n">
         <v>5220</v>
       </c>
+      <c r="CJ12" t="n">
+        <v>5180</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31591,6 +31980,9 @@
       <c r="CI13" t="n">
         <v>5295</v>
       </c>
+      <c r="CJ13" t="n">
+        <v>5235</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31858,6 +32250,9 @@
       <c r="CI14" t="n">
         <v>1329</v>
       </c>
+      <c r="CJ14" t="n">
+        <v>1285</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32125,6 +32520,9 @@
       <c r="CI15" t="n">
         <v>19770</v>
       </c>
+      <c r="CJ15" t="n">
+        <v>20050</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -32392,6 +32790,9 @@
       <c r="CI16" t="n">
         <v>10010</v>
       </c>
+      <c r="CJ16" t="n">
+        <v>9900</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -32659,6 +33060,9 @@
       <c r="CI17" t="n">
         <v>5810</v>
       </c>
+      <c r="CJ17" t="n">
+        <v>5740</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -32926,6 +33330,9 @@
       <c r="CI18" t="n">
         <v>20545</v>
       </c>
+      <c r="CJ18" t="n">
+        <v>20105</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -33192,6 +33599,9 @@
       </c>
       <c r="CI19" t="n">
         <v>16275</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>16575</v>
       </c>
     </row>
   </sheetData>
@@ -33205,7 +33615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI19"/>
+  <dimension ref="A1:CJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33295,6 +33705,7 @@
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
+    <col width="12" customWidth="1" min="88" max="88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33563,6 +33974,9 @@
       <c r="CI1" s="1" t="n">
         <v>20260106</v>
       </c>
+      <c r="CJ1" s="1" t="n">
+        <v>20260107</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33830,6 +34244,9 @@
       <c r="CI2" t="n">
         <v>145136</v>
       </c>
+      <c r="CJ2" t="n">
+        <v>172908</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34097,6 +34514,9 @@
       <c r="CI3" t="n">
         <v>5061353</v>
       </c>
+      <c r="CJ3" t="n">
+        <v>4570118</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34364,6 +34784,9 @@
       <c r="CI4" t="n">
         <v>130988</v>
       </c>
+      <c r="CJ4" t="n">
+        <v>265911</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34631,6 +35054,9 @@
       <c r="CI5" t="n">
         <v>463326</v>
       </c>
+      <c r="CJ5" t="n">
+        <v>656507</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34898,6 +35324,9 @@
       <c r="CI6" t="n">
         <v>6514528</v>
       </c>
+      <c r="CJ6" t="n">
+        <v>8520436</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35165,6 +35594,9 @@
       <c r="CI7" t="n">
         <v>3933169</v>
       </c>
+      <c r="CJ7" t="n">
+        <v>5318613</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -35432,6 +35864,9 @@
       <c r="CI8" t="n">
         <v>16983095</v>
       </c>
+      <c r="CJ8" t="n">
+        <v>18273223</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35699,6 +36134,9 @@
       <c r="CI9" t="n">
         <v>3375106</v>
       </c>
+      <c r="CJ9" t="n">
+        <v>4861845</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35966,6 +36404,9 @@
       <c r="CI10" t="n">
         <v>2296845</v>
       </c>
+      <c r="CJ10" t="n">
+        <v>2931119</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -36233,6 +36674,9 @@
       <c r="CI11" t="n">
         <v>673223</v>
       </c>
+      <c r="CJ11" t="n">
+        <v>589349</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -36500,6 +36944,9 @@
       <c r="CI12" t="n">
         <v>1384731</v>
       </c>
+      <c r="CJ12" t="n">
+        <v>1737633</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36767,6 +37214,9 @@
       <c r="CI13" t="n">
         <v>4979516</v>
       </c>
+      <c r="CJ13" t="n">
+        <v>3989351</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37034,6 +37484,9 @@
       <c r="CI14" t="n">
         <v>27316934</v>
       </c>
+      <c r="CJ14" t="n">
+        <v>39020502</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37301,6 +37754,9 @@
       <c r="CI15" t="n">
         <v>1324727</v>
       </c>
+      <c r="CJ15" t="n">
+        <v>1524651</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -37568,6 +38024,9 @@
       <c r="CI16" t="n">
         <v>236919</v>
       </c>
+      <c r="CJ16" t="n">
+        <v>372949</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37835,6 +38294,9 @@
       <c r="CI17" t="n">
         <v>87430</v>
       </c>
+      <c r="CJ17" t="n">
+        <v>56417</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -38102,6 +38564,9 @@
       <c r="CI18" t="n">
         <v>121853</v>
       </c>
+      <c r="CJ18" t="n">
+        <v>163725</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -38368,6 +38833,9 @@
       </c>
       <c r="CI19" t="n">
         <v>22124</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>36865</v>
       </c>
     </row>
   </sheetData>
@@ -38381,7 +38849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP19"/>
+  <dimension ref="A1:BQ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -38452,6 +38920,7 @@
     <col width="10" customWidth="1" min="66" max="66"/>
     <col width="10" customWidth="1" min="67" max="67"/>
     <col width="10" customWidth="1" min="68" max="68"/>
+    <col width="10" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38663,6 +39132,9 @@
       <c r="BP1" s="1" t="n">
         <v>20260106</v>
       </c>
+      <c r="BQ1" s="1" t="n">
+        <v>20260107</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -38873,6 +39345,9 @@
       <c r="BP2" t="n">
         <v>92</v>
       </c>
+      <c r="BQ2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -39083,6 +39558,9 @@
       <c r="BP3" t="n">
         <v>100</v>
       </c>
+      <c r="BQ3" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -39293,6 +39771,9 @@
       <c r="BP4" t="n">
         <v>94</v>
       </c>
+      <c r="BQ4" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -39503,6 +39984,9 @@
       <c r="BP5" t="n">
         <v>100</v>
       </c>
+      <c r="BQ5" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -39713,6 +40197,9 @@
       <c r="BP6" t="n">
         <v>100</v>
       </c>
+      <c r="BQ6" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -39923,6 +40410,9 @@
       <c r="BP7" t="n">
         <v>100</v>
       </c>
+      <c r="BQ7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40133,6 +40623,9 @@
       <c r="BP8" t="n">
         <v>100</v>
       </c>
+      <c r="BQ8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -40343,6 +40836,9 @@
       <c r="BP9" t="n">
         <v>19</v>
       </c>
+      <c r="BQ9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -40553,6 +41049,9 @@
       <c r="BP10" t="n">
         <v>100</v>
       </c>
+      <c r="BQ10" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -40763,6 +41262,9 @@
       <c r="BP11" t="n">
         <v>16</v>
       </c>
+      <c r="BQ11" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -40973,6 +41475,9 @@
       <c r="BP12" t="n">
         <v>16</v>
       </c>
+      <c r="BQ12" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -41183,6 +41688,9 @@
       <c r="BP13" t="n">
         <v>16</v>
       </c>
+      <c r="BQ13" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -41393,6 +41901,9 @@
       <c r="BP14" t="n">
         <v>17</v>
       </c>
+      <c r="BQ14" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41603,6 +42114,9 @@
       <c r="BP15" t="n">
         <v>89</v>
       </c>
+      <c r="BQ15" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -41813,6 +42327,9 @@
       <c r="BP16" t="n">
         <v>21</v>
       </c>
+      <c r="BQ16" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42023,6 +42540,9 @@
       <c r="BP17" t="n">
         <v>18</v>
       </c>
+      <c r="BQ17" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42233,6 +42753,9 @@
       <c r="BP18" t="n">
         <v>100</v>
       </c>
+      <c r="BQ18" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42442,6 +42965,9 @@
       </c>
       <c r="BP19" t="n">
         <v>78</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -42455,7 +42981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -42486,6 +43012,7 @@
     <col width="10" customWidth="1" min="26" max="26"/>
     <col width="10" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -42577,6 +43104,9 @@
       <c r="AB1" s="1" t="n">
         <v>20260106</v>
       </c>
+      <c r="AC1" s="1" t="n">
+        <v>20260107</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -42667,6 +43197,9 @@
       <c r="AB2" t="n">
         <v>75</v>
       </c>
+      <c r="AC2" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -42757,6 +43290,9 @@
       <c r="AB3" t="n">
         <v>100</v>
       </c>
+      <c r="AC3" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -42847,6 +43383,9 @@
       <c r="AB4" t="n">
         <v>80</v>
       </c>
+      <c r="AC4" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -42937,6 +43476,9 @@
       <c r="AB5" t="n">
         <v>100</v>
       </c>
+      <c r="AC5" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -43027,6 +43569,9 @@
       <c r="AB6" t="n">
         <v>100</v>
       </c>
+      <c r="AC6" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -43117,6 +43662,9 @@
       <c r="AB7" t="n">
         <v>100</v>
       </c>
+      <c r="AC7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -43207,6 +43755,9 @@
       <c r="AB8" t="n">
         <v>100</v>
       </c>
+      <c r="AC8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -43297,6 +43848,9 @@
       <c r="AB9" t="n">
         <v>24</v>
       </c>
+      <c r="AC9" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -43387,6 +43941,9 @@
       <c r="AB10" t="n">
         <v>100</v>
       </c>
+      <c r="AC10" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -43477,6 +44034,9 @@
       <c r="AB11" t="n">
         <v>57</v>
       </c>
+      <c r="AC11" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -43567,6 +44127,9 @@
       <c r="AB12" t="n">
         <v>55</v>
       </c>
+      <c r="AC12" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -43657,6 +44220,9 @@
       <c r="AB13" t="n">
         <v>57</v>
       </c>
+      <c r="AC13" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -43747,6 +44313,9 @@
       <c r="AB14" t="n">
         <v>31</v>
       </c>
+      <c r="AC14" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -43837,6 +44406,9 @@
       <c r="AB15" t="n">
         <v>89</v>
       </c>
+      <c r="AC15" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -43927,6 +44499,9 @@
       <c r="AB16" t="n">
         <v>50</v>
       </c>
+      <c r="AC16" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -44017,6 +44592,9 @@
       <c r="AB17" t="n">
         <v>45</v>
       </c>
+      <c r="AC17" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -44107,6 +44685,9 @@
       <c r="AB18" t="n">
         <v>100</v>
       </c>
+      <c r="AC18" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -44196,6 +44777,9 @@
       </c>
       <c r="AB19" t="n">
         <v>89</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -44209,7 +44793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP19"/>
+  <dimension ref="A1:BQ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -44280,6 +44864,7 @@
     <col width="10" customWidth="1" min="66" max="66"/>
     <col width="10" customWidth="1" min="67" max="67"/>
     <col width="10" customWidth="1" min="68" max="68"/>
+    <col width="10" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -44491,6 +45076,9 @@
       <c r="BP1" s="1" t="n">
         <v>20260106</v>
       </c>
+      <c r="BQ1" s="1" t="n">
+        <v>20260107</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -44701,6 +45289,9 @@
       <c r="BP2" t="n">
         <v>56</v>
       </c>
+      <c r="BQ2" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -44911,6 +45502,9 @@
       <c r="BP3" t="n">
         <v>133</v>
       </c>
+      <c r="BQ3" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -45121,6 +45715,9 @@
       <c r="BP4" t="n">
         <v>76</v>
       </c>
+      <c r="BQ4" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -45331,6 +45928,9 @@
       <c r="BP5" t="n">
         <v>111</v>
       </c>
+      <c r="BQ5" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -45541,6 +46141,9 @@
       <c r="BP6" t="n">
         <v>129</v>
       </c>
+      <c r="BQ6" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -45751,6 +46354,9 @@
       <c r="BP7" t="n">
         <v>129</v>
       </c>
+      <c r="BQ7" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -45961,6 +46567,9 @@
       <c r="BP8" t="n">
         <v>133</v>
       </c>
+      <c r="BQ8" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -46171,6 +46780,9 @@
       <c r="BP9" t="n">
         <v>-47</v>
       </c>
+      <c r="BQ9" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -46381,6 +46993,9 @@
       <c r="BP10" t="n">
         <v>126</v>
       </c>
+      <c r="BQ10" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -46591,6 +47206,9 @@
       <c r="BP11" t="n">
         <v>-55</v>
       </c>
+      <c r="BQ11" t="n">
+        <v>-59</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -46801,6 +47419,9 @@
       <c r="BP12" t="n">
         <v>-55</v>
       </c>
+      <c r="BQ12" t="n">
+        <v>-54</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -47011,6 +47632,9 @@
       <c r="BP13" t="n">
         <v>-55</v>
       </c>
+      <c r="BQ13" t="n">
+        <v>-57</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -47221,6 +47845,9 @@
       <c r="BP14" t="n">
         <v>-50</v>
       </c>
+      <c r="BQ14" t="n">
+        <v>-55</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -47431,6 +48058,9 @@
       <c r="BP15" t="n">
         <v>66</v>
       </c>
+      <c r="BQ15" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -47641,6 +48271,9 @@
       <c r="BP16" t="n">
         <v>-46</v>
       </c>
+      <c r="BQ16" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -47851,6 +48484,9 @@
       <c r="BP17" t="n">
         <v>-52</v>
       </c>
+      <c r="BQ17" t="n">
+        <v>-54</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -48061,6 +48697,9 @@
       <c r="BP18" t="n">
         <v>127</v>
       </c>
+      <c r="BQ18" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -48270,6 +48909,9 @@
       </c>
       <c r="BP19" t="n">
         <v>50</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -741,6 +741,7 @@
     <col width="10" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
     <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -835,6 +836,9 @@
       <c r="AC1" s="1" t="n">
         <v>20260107</v>
       </c>
+      <c r="AD1" s="1" t="n">
+        <v>20260108</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -928,6 +932,9 @@
       <c r="AC2" t="n">
         <v>43</v>
       </c>
+      <c r="AD2" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1021,6 +1028,9 @@
       <c r="AC3" t="n">
         <v>167</v>
       </c>
+      <c r="AD3" t="n">
+        <v>151</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1114,6 +1124,9 @@
       <c r="AC4" t="n">
         <v>43</v>
       </c>
+      <c r="AD4" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1207,6 +1220,9 @@
       <c r="AC5" t="n">
         <v>99</v>
       </c>
+      <c r="AD5" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1300,6 +1316,9 @@
       <c r="AC6" t="n">
         <v>153</v>
       </c>
+      <c r="AD6" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1393,6 +1412,9 @@
       <c r="AC7" t="n">
         <v>161</v>
       </c>
+      <c r="AD7" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1486,6 +1508,9 @@
       <c r="AC8" t="n">
         <v>179</v>
       </c>
+      <c r="AD8" t="n">
+        <v>161</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1579,6 +1604,9 @@
       <c r="AC9" t="n">
         <v>-69</v>
       </c>
+      <c r="AD9" t="n">
+        <v>-78</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1672,6 +1700,9 @@
       <c r="AC10" t="n">
         <v>116</v>
       </c>
+      <c r="AD10" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1765,6 +1796,9 @@
       <c r="AC11" t="n">
         <v>-44</v>
       </c>
+      <c r="AD11" t="n">
+        <v>-57</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1858,6 +1892,9 @@
       <c r="AC12" t="n">
         <v>-42</v>
       </c>
+      <c r="AD12" t="n">
+        <v>-54</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1951,6 +1988,9 @@
       <c r="AC13" t="n">
         <v>-33</v>
       </c>
+      <c r="AD13" t="n">
+        <v>-42</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2044,6 +2084,9 @@
       <c r="AC14" t="n">
         <v>-69</v>
       </c>
+      <c r="AD14" t="n">
+        <v>-77</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2137,6 +2180,9 @@
       <c r="AC15" t="n">
         <v>54</v>
       </c>
+      <c r="AD15" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2230,6 +2276,9 @@
       <c r="AC16" t="n">
         <v>-47</v>
       </c>
+      <c r="AD16" t="n">
+        <v>-60</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2323,6 +2372,9 @@
       <c r="AC17" t="n">
         <v>-57</v>
       </c>
+      <c r="AD17" t="n">
+        <v>-69</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2416,6 +2468,9 @@
       <c r="AC18" t="n">
         <v>119</v>
       </c>
+      <c r="AD18" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2508,6 +2563,9 @@
       </c>
       <c r="AC19" t="n">
         <v>56</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -2521,7 +2579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ19"/>
+  <dimension ref="A1:BR19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2593,6 +2651,7 @@
     <col width="12" customWidth="1" min="67" max="67"/>
     <col width="12" customWidth="1" min="68" max="68"/>
     <col width="12" customWidth="1" min="69" max="69"/>
+    <col width="12" customWidth="1" min="70" max="70"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2941,6 +3000,11 @@
           <t>20260107</t>
         </is>
       </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>20260108</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3154,6 +3218,9 @@
       <c r="BQ2" t="n">
         <v>104</v>
       </c>
+      <c r="BR2" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3367,6 +3434,9 @@
       <c r="BQ3" t="n">
         <v>117</v>
       </c>
+      <c r="BR3" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3580,6 +3650,9 @@
       <c r="BQ4" t="n">
         <v>104</v>
       </c>
+      <c r="BR4" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3793,6 +3866,9 @@
       <c r="BQ5" t="n">
         <v>108</v>
       </c>
+      <c r="BR5" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4006,6 +4082,9 @@
       <c r="BQ6" t="n">
         <v>115</v>
       </c>
+      <c r="BR6" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4219,6 +4298,9 @@
       <c r="BQ7" t="n">
         <v>117</v>
       </c>
+      <c r="BR7" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4432,6 +4514,9 @@
       <c r="BQ8" t="n">
         <v>121</v>
       </c>
+      <c r="BR8" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4645,6 +4730,9 @@
       <c r="BQ9" t="n">
         <v>88</v>
       </c>
+      <c r="BR9" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4858,6 +4946,9 @@
       <c r="BQ10" t="n">
         <v>109</v>
       </c>
+      <c r="BR10" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5071,6 +5162,9 @@
       <c r="BQ11" t="n">
         <v>92</v>
       </c>
+      <c r="BR11" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5284,6 +5378,9 @@
       <c r="BQ12" t="n">
         <v>92</v>
       </c>
+      <c r="BR12" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5497,6 +5594,9 @@
       <c r="BQ13" t="n">
         <v>92</v>
       </c>
+      <c r="BR13" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5710,6 +5810,9 @@
       <c r="BQ14" t="n">
         <v>85</v>
       </c>
+      <c r="BR14" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5923,6 +6026,9 @@
       <c r="BQ15" t="n">
         <v>104</v>
       </c>
+      <c r="BR15" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6136,6 +6242,9 @@
       <c r="BQ16" t="n">
         <v>94</v>
       </c>
+      <c r="BR16" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6349,6 +6458,9 @@
       <c r="BQ17" t="n">
         <v>92</v>
       </c>
+      <c r="BR17" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6562,6 +6674,9 @@
       <c r="BQ18" t="n">
         <v>111</v>
       </c>
+      <c r="BR18" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6774,6 +6889,9 @@
       </c>
       <c r="BQ19" t="n">
         <v>103</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -10813,7 +10931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10845,6 +10963,7 @@
     <col width="12" customWidth="1" min="27" max="27"/>
     <col width="12" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10993,6 +11112,11 @@
           <t>20260107</t>
         </is>
       </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>20260108</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11086,6 +11210,9 @@
       <c r="AC2" t="n">
         <v>65</v>
       </c>
+      <c r="AD2" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11179,6 +11306,9 @@
       <c r="AC3" t="n">
         <v>94</v>
       </c>
+      <c r="AD3" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11272,6 +11402,9 @@
       <c r="AC4" t="n">
         <v>73</v>
       </c>
+      <c r="AD4" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11365,6 +11498,9 @@
       <c r="AC5" t="n">
         <v>53</v>
       </c>
+      <c r="AD5" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11458,6 +11594,9 @@
       <c r="AC6" t="n">
         <v>185</v>
       </c>
+      <c r="AD6" t="n">
+        <v>135</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11551,6 +11690,9 @@
       <c r="AC7" t="n">
         <v>66</v>
       </c>
+      <c r="AD7" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11644,6 +11786,9 @@
       <c r="AC8" t="n">
         <v>117</v>
       </c>
+      <c r="AD8" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11737,6 +11882,9 @@
       <c r="AC9" t="n">
         <v>31</v>
       </c>
+      <c r="AD9" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11830,6 +11978,9 @@
       <c r="AC10" t="n">
         <v>107</v>
       </c>
+      <c r="AD10" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11923,6 +12074,9 @@
       <c r="AC11" t="n">
         <v>22</v>
       </c>
+      <c r="AD11" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12016,6 +12170,9 @@
       <c r="AC12" t="n">
         <v>28</v>
       </c>
+      <c r="AD12" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12109,6 +12266,9 @@
       <c r="AC13" t="n">
         <v>27</v>
       </c>
+      <c r="AD13" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12202,6 +12362,9 @@
       <c r="AC14" t="n">
         <v>37</v>
       </c>
+      <c r="AD14" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12295,6 +12458,9 @@
       <c r="AC15" t="n">
         <v>42</v>
       </c>
+      <c r="AD15" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12388,6 +12554,9 @@
       <c r="AC16" t="n">
         <v>29</v>
       </c>
+      <c r="AD16" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12481,6 +12650,9 @@
       <c r="AC17" t="n">
         <v>12</v>
       </c>
+      <c r="AD17" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12574,6 +12746,9 @@
       <c r="AC18" t="n">
         <v>47</v>
       </c>
+      <c r="AD18" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12666,6 +12841,9 @@
       </c>
       <c r="AC19" t="n">
         <v>39</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -12679,7 +12857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ19"/>
+  <dimension ref="A1:CK19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12770,6 +12948,7 @@
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
+    <col width="12" customWidth="1" min="89" max="89"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13041,6 +13220,9 @@
       <c r="CJ1" s="1" t="n">
         <v>20260107</v>
       </c>
+      <c r="CK1" s="1" t="n">
+        <v>20260108</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13311,6 +13493,9 @@
       <c r="CJ2" t="n">
         <v>15780</v>
       </c>
+      <c r="CK2" t="n">
+        <v>16285</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13581,6 +13766,9 @@
       <c r="CJ3" t="n">
         <v>72440</v>
       </c>
+      <c r="CK3" t="n">
+        <v>69690</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13851,6 +14039,9 @@
       <c r="CJ4" t="n">
         <v>18535</v>
       </c>
+      <c r="CK4" t="n">
+        <v>18750</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14121,6 +14312,9 @@
       <c r="CJ5" t="n">
         <v>18080</v>
       </c>
+      <c r="CK5" t="n">
+        <v>17135</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14391,6 +14585,9 @@
       <c r="CJ6" t="n">
         <v>20775</v>
       </c>
+      <c r="CK6" t="n">
+        <v>19995</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14661,6 +14858,9 @@
       <c r="CJ7" t="n">
         <v>24475</v>
       </c>
+      <c r="CK7" t="n">
+        <v>23715</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14931,6 +15131,9 @@
       <c r="CJ8" t="n">
         <v>24250</v>
       </c>
+      <c r="CK8" t="n">
+        <v>23290</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15201,6 +15404,9 @@
       <c r="CJ9" t="n">
         <v>1260</v>
       </c>
+      <c r="CK9" t="n">
+        <v>1228</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15471,6 +15677,9 @@
       <c r="CJ10" t="n">
         <v>19330</v>
       </c>
+      <c r="CK10" t="n">
+        <v>18410</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15741,6 +15950,9 @@
       <c r="CJ11" t="n">
         <v>4905</v>
       </c>
+      <c r="CK11" t="n">
+        <v>4850</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16011,6 +16223,9 @@
       <c r="CJ12" t="n">
         <v>5235</v>
       </c>
+      <c r="CK12" t="n">
+        <v>5170</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16281,6 +16496,9 @@
       <c r="CJ13" t="n">
         <v>5300</v>
       </c>
+      <c r="CK13" t="n">
+        <v>5240</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16551,6 +16769,9 @@
       <c r="CJ14" t="n">
         <v>1336</v>
       </c>
+      <c r="CK14" t="n">
+        <v>1276</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -16821,6 +17042,9 @@
       <c r="CJ15" t="n">
         <v>19865</v>
       </c>
+      <c r="CK15" t="n">
+        <v>20345</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -17091,6 +17315,9 @@
       <c r="CJ16" t="n">
         <v>10020</v>
       </c>
+      <c r="CK16" t="n">
+        <v>9895</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17361,6 +17588,9 @@
       <c r="CJ17" t="n">
         <v>5835</v>
       </c>
+      <c r="CK17" t="n">
+        <v>5695</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17631,6 +17861,9 @@
       <c r="CJ18" t="n">
         <v>20980</v>
       </c>
+      <c r="CK18" t="n">
+        <v>19915</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17900,6 +18133,9 @@
       </c>
       <c r="CJ19" t="n">
         <v>16365</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>16845</v>
       </c>
     </row>
   </sheetData>
@@ -17913,7 +18149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ19"/>
+  <dimension ref="A1:CK19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18004,6 +18240,7 @@
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
+    <col width="12" customWidth="1" min="89" max="89"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18275,6 +18512,9 @@
       <c r="CJ1" s="1" t="n">
         <v>20260107</v>
       </c>
+      <c r="CK1" s="1" t="n">
+        <v>20260108</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18545,6 +18785,9 @@
       <c r="CJ2" t="n">
         <v>16030</v>
       </c>
+      <c r="CK2" t="n">
+        <v>16395</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18815,6 +19058,9 @@
       <c r="CJ3" t="n">
         <v>72750</v>
       </c>
+      <c r="CK3" t="n">
+        <v>72965</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19085,6 +19331,9 @@
       <c r="CJ4" t="n">
         <v>18700</v>
       </c>
+      <c r="CK4" t="n">
+        <v>18945</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19355,6 +19604,9 @@
       <c r="CJ5" t="n">
         <v>18130</v>
       </c>
+      <c r="CK5" t="n">
+        <v>17800</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19625,6 +19877,9 @@
       <c r="CJ6" t="n">
         <v>20865</v>
       </c>
+      <c r="CK6" t="n">
+        <v>20880</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19895,6 +20150,9 @@
       <c r="CJ7" t="n">
         <v>24630</v>
       </c>
+      <c r="CK7" t="n">
+        <v>24955</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20165,6 +20423,9 @@
       <c r="CJ8" t="n">
         <v>24380</v>
       </c>
+      <c r="CK8" t="n">
+        <v>24575</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20435,6 +20696,9 @@
       <c r="CJ9" t="n">
         <v>1295</v>
       </c>
+      <c r="CK9" t="n">
+        <v>1249</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20705,6 +20969,9 @@
       <c r="CJ10" t="n">
         <v>19410</v>
       </c>
+      <c r="CK10" t="n">
+        <v>19185</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -20975,6 +21242,9 @@
       <c r="CJ11" t="n">
         <v>5010</v>
       </c>
+      <c r="CK11" t="n">
+        <v>4910</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -21245,6 +21515,9 @@
       <c r="CJ12" t="n">
         <v>5340</v>
       </c>
+      <c r="CK12" t="n">
+        <v>5255</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -21515,6 +21788,9 @@
       <c r="CJ13" t="n">
         <v>5430</v>
       </c>
+      <c r="CK13" t="n">
+        <v>5335</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -21785,6 +22061,9 @@
       <c r="CJ14" t="n">
         <v>1375</v>
       </c>
+      <c r="CK14" t="n">
+        <v>1310</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -22055,6 +22334,9 @@
       <c r="CJ15" t="n">
         <v>20120</v>
       </c>
+      <c r="CK15" t="n">
+        <v>20595</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -22325,6 +22607,9 @@
       <c r="CJ16" t="n">
         <v>10195</v>
       </c>
+      <c r="CK16" t="n">
+        <v>9970</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -22595,6 +22880,9 @@
       <c r="CJ17" t="n">
         <v>5910</v>
       </c>
+      <c r="CK17" t="n">
+        <v>5750</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -22865,6 +23153,9 @@
       <c r="CJ18" t="n">
         <v>21075</v>
       </c>
+      <c r="CK18" t="n">
+        <v>20865</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -23134,6 +23425,9 @@
       </c>
       <c r="CJ19" t="n">
         <v>16665</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>16920</v>
       </c>
     </row>
   </sheetData>
@@ -23147,7 +23441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ19"/>
+  <dimension ref="A1:CK19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23238,6 +23532,7 @@
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
+    <col width="12" customWidth="1" min="89" max="89"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23509,6 +23804,9 @@
       <c r="CJ1" s="1" t="n">
         <v>20260107</v>
       </c>
+      <c r="CK1" s="1" t="n">
+        <v>20260108</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23779,6 +24077,9 @@
       <c r="CJ2" t="n">
         <v>15560</v>
       </c>
+      <c r="CK2" t="n">
+        <v>16020</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24049,6 +24350,9 @@
       <c r="CJ3" t="n">
         <v>69020</v>
       </c>
+      <c r="CK3" t="n">
+        <v>69220</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24319,6 +24623,9 @@
       <c r="CJ4" t="n">
         <v>18225</v>
       </c>
+      <c r="CK4" t="n">
+        <v>18595</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24589,6 +24896,9 @@
       <c r="CJ5" t="n">
         <v>17070</v>
       </c>
+      <c r="CK5" t="n">
+        <v>17115</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24859,6 +25169,9 @@
       <c r="CJ6" t="n">
         <v>19860</v>
       </c>
+      <c r="CK6" t="n">
+        <v>19945</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25129,6 +25442,9 @@
       <c r="CJ7" t="n">
         <v>23495</v>
       </c>
+      <c r="CK7" t="n">
+        <v>23655</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25399,6 +25715,9 @@
       <c r="CJ8" t="n">
         <v>23160</v>
       </c>
+      <c r="CK8" t="n">
+        <v>23285</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25669,6 +25988,9 @@
       <c r="CJ9" t="n">
         <v>1210</v>
       </c>
+      <c r="CK9" t="n">
+        <v>1171</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25939,6 +26261,9 @@
       <c r="CJ10" t="n">
         <v>18275</v>
       </c>
+      <c r="CK10" t="n">
+        <v>18345</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26209,6 +26534,9 @@
       <c r="CJ11" t="n">
         <v>4810</v>
       </c>
+      <c r="CK11" t="n">
+        <v>4785</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26479,6 +26807,9 @@
       <c r="CJ12" t="n">
         <v>5110</v>
       </c>
+      <c r="CK12" t="n">
+        <v>5110</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -26749,6 +27080,9 @@
       <c r="CJ13" t="n">
         <v>5190</v>
       </c>
+      <c r="CK13" t="n">
+        <v>5170</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -27019,6 +27353,9 @@
       <c r="CJ14" t="n">
         <v>1264</v>
       </c>
+      <c r="CK14" t="n">
+        <v>1248</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -27289,6 +27626,9 @@
       <c r="CJ15" t="n">
         <v>19500</v>
       </c>
+      <c r="CK15" t="n">
+        <v>20060</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -27559,6 +27899,9 @@
       <c r="CJ16" t="n">
         <v>9795</v>
       </c>
+      <c r="CK16" t="n">
+        <v>9750</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -27829,6 +28172,9 @@
       <c r="CJ17" t="n">
         <v>5675</v>
       </c>
+      <c r="CK17" t="n">
+        <v>5635</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -28099,6 +28445,9 @@
       <c r="CJ18" t="n">
         <v>19665</v>
       </c>
+      <c r="CK18" t="n">
+        <v>19825</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -28368,6 +28717,9 @@
       </c>
       <c r="CJ19" t="n">
         <v>16195</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>16570</v>
       </c>
     </row>
   </sheetData>
@@ -28381,7 +28733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ19"/>
+  <dimension ref="A1:CK19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -28472,6 +28824,7 @@
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
+    <col width="12" customWidth="1" min="89" max="89"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28743,6 +29096,9 @@
       <c r="CJ1" s="1" t="n">
         <v>20260107</v>
       </c>
+      <c r="CK1" s="1" t="n">
+        <v>20260108</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29013,6 +29369,9 @@
       <c r="CJ2" t="n">
         <v>15870</v>
       </c>
+      <c r="CK2" t="n">
+        <v>16270</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29283,6 +29642,9 @@
       <c r="CJ3" t="n">
         <v>70300</v>
       </c>
+      <c r="CK3" t="n">
+        <v>70160</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -29553,6 +29915,9 @@
       <c r="CJ4" t="n">
         <v>18580</v>
       </c>
+      <c r="CK4" t="n">
+        <v>18860</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29823,6 +30188,9 @@
       <c r="CJ5" t="n">
         <v>17420</v>
       </c>
+      <c r="CK5" t="n">
+        <v>17115</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -30093,6 +30461,9 @@
       <c r="CJ6" t="n">
         <v>20230</v>
       </c>
+      <c r="CK6" t="n">
+        <v>20150</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -30363,6 +30734,9 @@
       <c r="CJ7" t="n">
         <v>23960</v>
       </c>
+      <c r="CK7" t="n">
+        <v>24030</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30633,6 +31007,9 @@
       <c r="CJ8" t="n">
         <v>23650</v>
       </c>
+      <c r="CK8" t="n">
+        <v>23670</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30903,6 +31280,9 @@
       <c r="CJ9" t="n">
         <v>1228</v>
       </c>
+      <c r="CK9" t="n">
+        <v>1202</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31173,6 +31553,9 @@
       <c r="CJ10" t="n">
         <v>18605</v>
       </c>
+      <c r="CK10" t="n">
+        <v>18450</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -31443,6 +31826,9 @@
       <c r="CJ11" t="n">
         <v>4845</v>
       </c>
+      <c r="CK11" t="n">
+        <v>4795</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31713,6 +32099,9 @@
       <c r="CJ12" t="n">
         <v>5180</v>
       </c>
+      <c r="CK12" t="n">
+        <v>5130</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31983,6 +32372,9 @@
       <c r="CJ13" t="n">
         <v>5235</v>
       </c>
+      <c r="CK13" t="n">
+        <v>5205</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32253,6 +32645,9 @@
       <c r="CJ14" t="n">
         <v>1285</v>
       </c>
+      <c r="CK14" t="n">
+        <v>1260</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32523,6 +32918,9 @@
       <c r="CJ15" t="n">
         <v>20050</v>
       </c>
+      <c r="CK15" t="n">
+        <v>20470</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -32793,6 +33191,9 @@
       <c r="CJ16" t="n">
         <v>9900</v>
       </c>
+      <c r="CK16" t="n">
+        <v>9795</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -33063,6 +33464,9 @@
       <c r="CJ17" t="n">
         <v>5740</v>
       </c>
+      <c r="CK17" t="n">
+        <v>5675</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -33333,6 +33737,9 @@
       <c r="CJ18" t="n">
         <v>20105</v>
       </c>
+      <c r="CK18" t="n">
+        <v>19890</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -33602,6 +34009,9 @@
       </c>
       <c r="CJ19" t="n">
         <v>16575</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>16780</v>
       </c>
     </row>
   </sheetData>
@@ -33615,7 +34025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ19"/>
+  <dimension ref="A1:CK19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33706,6 +34116,7 @@
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
+    <col width="12" customWidth="1" min="89" max="89"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33977,6 +34388,9 @@
       <c r="CJ1" s="1" t="n">
         <v>20260107</v>
       </c>
+      <c r="CK1" s="1" t="n">
+        <v>20260108</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34247,6 +34661,9 @@
       <c r="CJ2" t="n">
         <v>172908</v>
       </c>
+      <c r="CK2" t="n">
+        <v>204622</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34517,6 +34934,9 @@
       <c r="CJ3" t="n">
         <v>4570118</v>
       </c>
+      <c r="CK3" t="n">
+        <v>3860480</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34787,6 +35207,9 @@
       <c r="CJ4" t="n">
         <v>265911</v>
       </c>
+      <c r="CK4" t="n">
+        <v>137034</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -35057,6 +35480,9 @@
       <c r="CJ5" t="n">
         <v>656507</v>
       </c>
+      <c r="CK5" t="n">
+        <v>294110</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -35327,6 +35753,9 @@
       <c r="CJ6" t="n">
         <v>8520436</v>
       </c>
+      <c r="CK6" t="n">
+        <v>6346827</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35597,6 +36026,9 @@
       <c r="CJ7" t="n">
         <v>5318613</v>
       </c>
+      <c r="CK7" t="n">
+        <v>5095519</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -35867,6 +36299,9 @@
       <c r="CJ8" t="n">
         <v>18273223</v>
       </c>
+      <c r="CK8" t="n">
+        <v>17910007</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -36137,6 +36572,9 @@
       <c r="CJ9" t="n">
         <v>4861845</v>
       </c>
+      <c r="CK9" t="n">
+        <v>3606225</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -36407,6 +36845,9 @@
       <c r="CJ10" t="n">
         <v>2931119</v>
       </c>
+      <c r="CK10" t="n">
+        <v>2021510</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -36677,6 +37118,9 @@
       <c r="CJ11" t="n">
         <v>589349</v>
       </c>
+      <c r="CK11" t="n">
+        <v>353004</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -36947,6 +37391,9 @@
       <c r="CJ12" t="n">
         <v>1737633</v>
       </c>
+      <c r="CK12" t="n">
+        <v>1005697</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -37217,6 +37664,9 @@
       <c r="CJ13" t="n">
         <v>3989351</v>
       </c>
+      <c r="CK13" t="n">
+        <v>2788144</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37487,6 +37937,9 @@
       <c r="CJ14" t="n">
         <v>39020502</v>
       </c>
+      <c r="CK14" t="n">
+        <v>22944248</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37757,6 +38210,9 @@
       <c r="CJ15" t="n">
         <v>1524651</v>
       </c>
+      <c r="CK15" t="n">
+        <v>1754364</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -38027,6 +38483,9 @@
       <c r="CJ16" t="n">
         <v>372949</v>
       </c>
+      <c r="CK16" t="n">
+        <v>234753</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -38297,6 +38756,9 @@
       <c r="CJ17" t="n">
         <v>56417</v>
       </c>
+      <c r="CK17" t="n">
+        <v>26884</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -38567,6 +39029,9 @@
       <c r="CJ18" t="n">
         <v>163725</v>
       </c>
+      <c r="CK18" t="n">
+        <v>117365</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -38836,6 +39301,9 @@
       </c>
       <c r="CJ19" t="n">
         <v>36865</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>35618</v>
       </c>
     </row>
   </sheetData>
@@ -38849,7 +39317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ19"/>
+  <dimension ref="A1:BR19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -38921,6 +39389,7 @@
     <col width="10" customWidth="1" min="67" max="67"/>
     <col width="10" customWidth="1" min="68" max="68"/>
     <col width="10" customWidth="1" min="69" max="69"/>
+    <col width="10" customWidth="1" min="70" max="70"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39135,6 +39604,9 @@
       <c r="BQ1" s="1" t="n">
         <v>20260107</v>
       </c>
+      <c r="BR1" s="1" t="n">
+        <v>20260108</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -39348,6 +39820,9 @@
       <c r="BQ2" t="n">
         <v>100</v>
       </c>
+      <c r="BR2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -39561,6 +40036,9 @@
       <c r="BQ3" t="n">
         <v>97</v>
       </c>
+      <c r="BR3" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -39774,6 +40252,9 @@
       <c r="BQ4" t="n">
         <v>96</v>
       </c>
+      <c r="BR4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -39987,6 +40468,9 @@
       <c r="BQ5" t="n">
         <v>91</v>
       </c>
+      <c r="BR5" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -40200,6 +40684,9 @@
       <c r="BQ6" t="n">
         <v>98</v>
       </c>
+      <c r="BR6" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -40413,6 +40900,9 @@
       <c r="BQ7" t="n">
         <v>100</v>
       </c>
+      <c r="BR7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40626,6 +41116,9 @@
       <c r="BQ8" t="n">
         <v>100</v>
       </c>
+      <c r="BR8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -40839,6 +41332,9 @@
       <c r="BQ9" t="n">
         <v>13</v>
       </c>
+      <c r="BR9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -41052,6 +41548,9 @@
       <c r="BQ10" t="n">
         <v>84</v>
       </c>
+      <c r="BR10" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -41265,6 +41764,9 @@
       <c r="BQ11" t="n">
         <v>9</v>
       </c>
+      <c r="BR11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -41478,6 +41980,9 @@
       <c r="BQ12" t="n">
         <v>13</v>
       </c>
+      <c r="BR12" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -41691,6 +42196,9 @@
       <c r="BQ13" t="n">
         <v>11</v>
       </c>
+      <c r="BR13" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -41904,6 +42412,9 @@
       <c r="BQ14" t="n">
         <v>9</v>
       </c>
+      <c r="BR14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42117,6 +42628,9 @@
       <c r="BQ15" t="n">
         <v>100</v>
       </c>
+      <c r="BR15" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -42330,6 +42844,9 @@
       <c r="BQ16" t="n">
         <v>16</v>
       </c>
+      <c r="BR16" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42543,6 +43060,9 @@
       <c r="BQ17" t="n">
         <v>13</v>
       </c>
+      <c r="BR17" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42756,6 +43276,9 @@
       <c r="BQ18" t="n">
         <v>89</v>
       </c>
+      <c r="BR18" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42967,6 +43490,9 @@
         <v>78</v>
       </c>
       <c r="BQ19" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR19" t="n">
         <v>100</v>
       </c>
     </row>
@@ -42981,7 +43507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -43013,6 +43539,7 @@
     <col width="10" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
     <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43107,6 +43634,9 @@
       <c r="AC1" s="1" t="n">
         <v>20260107</v>
       </c>
+      <c r="AD1" s="1" t="n">
+        <v>20260108</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -43200,6 +43730,9 @@
       <c r="AC2" t="n">
         <v>81</v>
       </c>
+      <c r="AD2" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -43293,6 +43826,9 @@
       <c r="AC3" t="n">
         <v>98</v>
       </c>
+      <c r="AD3" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -43386,6 +43922,9 @@
       <c r="AC4" t="n">
         <v>80</v>
       </c>
+      <c r="AD4" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -43479,6 +44018,9 @@
       <c r="AC5" t="n">
         <v>91</v>
       </c>
+      <c r="AD5" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -43572,6 +44114,9 @@
       <c r="AC6" t="n">
         <v>98</v>
       </c>
+      <c r="AD6" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -43665,6 +44210,9 @@
       <c r="AC7" t="n">
         <v>100</v>
       </c>
+      <c r="AD7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -43758,6 +44306,9 @@
       <c r="AC8" t="n">
         <v>100</v>
       </c>
+      <c r="AD8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -43851,6 +44402,9 @@
       <c r="AC9" t="n">
         <v>18</v>
       </c>
+      <c r="AD9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -43944,6 +44498,9 @@
       <c r="AC10" t="n">
         <v>85</v>
       </c>
+      <c r="AD10" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -44037,6 +44594,9 @@
       <c r="AC11" t="n">
         <v>50</v>
       </c>
+      <c r="AD11" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -44130,6 +44690,9 @@
       <c r="AC12" t="n">
         <v>50</v>
       </c>
+      <c r="AD12" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -44223,6 +44786,9 @@
       <c r="AC13" t="n">
         <v>52</v>
       </c>
+      <c r="AD13" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -44316,6 +44882,9 @@
       <c r="AC14" t="n">
         <v>24</v>
       </c>
+      <c r="AD14" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -44409,6 +44978,9 @@
       <c r="AC15" t="n">
         <v>94</v>
       </c>
+      <c r="AD15" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -44502,6 +45074,9 @@
       <c r="AC16" t="n">
         <v>45</v>
       </c>
+      <c r="AD16" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -44595,6 +45170,9 @@
       <c r="AC17" t="n">
         <v>39</v>
       </c>
+      <c r="AD17" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -44688,6 +45266,9 @@
       <c r="AC18" t="n">
         <v>92</v>
       </c>
+      <c r="AD18" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -44780,6 +45361,9 @@
       </c>
       <c r="AC19" t="n">
         <v>96</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -44793,7 +45377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ19"/>
+  <dimension ref="A1:BR19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -44865,6 +45449,7 @@
     <col width="10" customWidth="1" min="67" max="67"/>
     <col width="10" customWidth="1" min="68" max="68"/>
     <col width="10" customWidth="1" min="69" max="69"/>
+    <col width="10" customWidth="1" min="70" max="70"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -45079,6 +45664,9 @@
       <c r="BQ1" s="1" t="n">
         <v>20260107</v>
       </c>
+      <c r="BR1" s="1" t="n">
+        <v>20260108</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -45292,6 +45880,9 @@
       <c r="BQ2" t="n">
         <v>76</v>
       </c>
+      <c r="BR2" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -45505,6 +46096,9 @@
       <c r="BQ3" t="n">
         <v>105</v>
       </c>
+      <c r="BR3" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -45718,6 +46312,9 @@
       <c r="BQ4" t="n">
         <v>75</v>
       </c>
+      <c r="BR4" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -45931,6 +46528,9 @@
       <c r="BQ5" t="n">
         <v>83</v>
       </c>
+      <c r="BR5" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -46144,6 +46744,9 @@
       <c r="BQ6" t="n">
         <v>103</v>
       </c>
+      <c r="BR6" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -46357,6 +46960,9 @@
       <c r="BQ7" t="n">
         <v>108</v>
       </c>
+      <c r="BR7" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -46570,6 +47176,9 @@
       <c r="BQ8" t="n">
         <v>109</v>
       </c>
+      <c r="BR8" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -46783,6 +47392,9 @@
       <c r="BQ9" t="n">
         <v>-50</v>
       </c>
+      <c r="BR9" t="n">
+        <v>-53</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -46996,6 +47608,9 @@
       <c r="BQ10" t="n">
         <v>85</v>
       </c>
+      <c r="BR10" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -47209,6 +47824,9 @@
       <c r="BQ11" t="n">
         <v>-59</v>
       </c>
+      <c r="BR11" t="n">
+        <v>-61</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -47422,6 +48040,9 @@
       <c r="BQ12" t="n">
         <v>-54</v>
       </c>
+      <c r="BR12" t="n">
+        <v>-55</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -47635,6 +48256,9 @@
       <c r="BQ13" t="n">
         <v>-57</v>
       </c>
+      <c r="BR13" t="n">
+        <v>-55</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -47848,6 +48472,9 @@
       <c r="BQ14" t="n">
         <v>-55</v>
       </c>
+      <c r="BR14" t="n">
+        <v>-56</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -48061,6 +48688,9 @@
       <c r="BQ15" t="n">
         <v>88</v>
       </c>
+      <c r="BR15" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -48274,6 +48904,9 @@
       <c r="BQ16" t="n">
         <v>-50</v>
       </c>
+      <c r="BR16" t="n">
+        <v>-52</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -48487,6 +49120,9 @@
       <c r="BQ17" t="n">
         <v>-54</v>
       </c>
+      <c r="BR17" t="n">
+        <v>-56</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -48700,6 +49336,9 @@
       <c r="BQ18" t="n">
         <v>90</v>
       </c>
+      <c r="BR18" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -48912,6 +49551,9 @@
       </c>
       <c r="BQ19" t="n">
         <v>98</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -6905,7 +6905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM19"/>
+  <dimension ref="A1:AR19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7196,111 +7196,6 @@
           <t>20251226</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>20251201</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>20251202</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>20251203</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>20251204</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>20251205</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>20251208</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>20251209</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>20251210</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>20251211</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>20251212</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>20251215</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>20251216</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>20251217</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>20251218</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>20251219</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>20251222</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>20251223</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>20251224</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>20251226</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>20251229</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>20251230</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7439,69 +7334,6 @@
       <c r="AR2" t="n">
         <v>15.38</v>
       </c>
-      <c r="AS2" t="n">
-        <v>645.79</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>645.46</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>626.3099999999999</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>605.24</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>529.66</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>485.39</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>399.28</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>393.37</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>400.51</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>409.79</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>396.06</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>405.58</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>459.55</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>485.11</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>486.59</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>518.64</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>574.16</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>593.91</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>595.36</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>577.78</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>547.09</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7640,69 +7472,6 @@
       <c r="AR3" t="n">
         <v>-30.02</v>
       </c>
-      <c r="AS3" t="n">
-        <v>2299.56</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2173.53</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>2155.48</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2090.2</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>2089.1</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>2063.38</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1938.42</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1824.92</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1685.63</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1706.19</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1609.14</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1661</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1650.25</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1652.07</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>1436.26</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>1273.33</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>1176.69</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1118.28</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>1235.59</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1442.86</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1666.41</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7841,69 +7610,6 @@
       <c r="AR4" t="n">
         <v>12.89</v>
       </c>
-      <c r="AS4" t="n">
-        <v>741.65</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>765.83</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>753.1900000000001</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>720.38</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>648.59</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>582.86</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>449.84</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>449.02</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>454.9</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>487.83</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>504.11</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>524.1799999999999</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>576.85</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>587.75</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>584.8099999999999</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>605.08</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>636.66</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>672.98</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>687.22</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>629.62</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>561.4400000000001</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8042,69 +7748,6 @@
       <c r="AR5" t="n">
         <v>-7.01</v>
       </c>
-      <c r="AS5" t="n">
-        <v>538.55</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>492.53</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>487.68</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>473.21</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>474.24</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>467.85</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>443.88</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>406.61</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>369.26</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>368.71</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>347.38</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>414.77</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>420.64</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>432.51</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>429.24</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>406.53</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>408.7</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>411.25</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>408.22</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>416</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>429.46</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8243,69 +7886,6 @@
       <c r="AR6" t="n">
         <v>-22.11</v>
       </c>
-      <c r="AS6" t="n">
-        <v>522.97</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>502.98</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>506.77</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>504.42</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>503.05</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>514.16</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>505.93</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>503.9</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>496.69</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>496.61</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>477.43</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>494.38</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>486.78</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>491.45</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>428.16</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>362.93</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>342.84</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>337.45</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>366.92</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>418.45</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>471.64</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8444,69 +8024,6 @@
       <c r="AR7" t="n">
         <v>-29.72</v>
       </c>
-      <c r="AS7" t="n">
-        <v>613.1</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>584.49</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>599.25</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>599.4299999999999</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>612.26</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>639.23</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>643.13</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>662.4400000000001</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>667.24</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>679.04</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>679.89</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>664.88</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>640.21</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>631.26</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>518.92</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>427.02</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>371.28</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>364.46</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>410.92</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>484.03</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>555.38</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8645,69 +8162,6 @@
       <c r="AR8" t="n">
         <v>-21.24</v>
       </c>
-      <c r="AS8" t="n">
-        <v>695.97</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>660.11</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>658.1</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>651.63</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>652.0599999999999</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>649.63</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>616.5599999999999</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>588.03</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>541.03</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>553.79</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>524.87</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>538.9</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>534.54</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>534.58</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>464.25</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>402.72</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>378.65</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>384.23</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>441.75</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>539.3200000000001</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>632.08</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8846,69 +8300,6 @@
       <c r="AR9" t="n">
         <v>12.29</v>
       </c>
-      <c r="AS9" t="n">
-        <v>125.35</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>120.99</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>120.58</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>120.22</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>120.47</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>120.32</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>118.18</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>109.82</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>82.48</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>76.67</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>78.52</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>79.45</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>91.86</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>102.65</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>105.63</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>109.27</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>113.27</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>119.62</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>126.26</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>136.94</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9047,69 +8438,6 @@
       <c r="AR10" t="n">
         <v>8.720000000000001</v>
       </c>
-      <c r="AS10" t="n">
-        <v>516.12</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>467.23</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>480.23</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>474.84</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>464.08</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>464.08</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>463.43</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>459.17</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>448.36</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>442.01</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>438.69</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>497.54</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>510.01</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>555.96</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>558.1799999999999</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>527.25</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>533.13</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>545.4299999999999</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>539.1900000000001</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>522.64</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>503.14</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9248,69 +8576,6 @@
       <c r="AR11" t="n">
         <v>-3.13</v>
       </c>
-      <c r="AS11" t="n">
-        <v>202.62</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>197.34</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>198.21</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>197.43</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>199.08</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>227.13</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>255.36</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>272</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>270.08</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>281.11</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>291.58</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>287.96</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>283.89</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>287.89</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>279.21</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>252.58</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>229.35</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>232.75</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>236.83</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>239.07</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>258.52</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9449,69 +8714,6 @@
       <c r="AR12" t="n">
         <v>-1.83</v>
       </c>
-      <c r="AS12" t="n">
-        <v>242.38</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>234.69</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>233.74</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>229.75</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>232.36</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>271.02</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>306.45</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>327.33</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>328.87</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>343.38</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>358.04</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>353.7</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>347.62</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>350.42</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>341.49</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>312.62</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>283.31</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>286.28</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>290.77</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>295.19</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>322.46</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9650,69 +8852,6 @@
       <c r="AR13" t="n">
         <v>-8.07</v>
       </c>
-      <c r="AS13" t="n">
-        <v>260.33</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>250.73</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>250.25</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>246.23</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>251.08</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>302.57</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>348.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>379.25</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>391.93</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>411.32</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>430.25</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>424.14</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>415.82</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>413.12</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>396.3</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>358.39</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>319.15</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>314.34</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>309.93</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>305</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>326.23</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9851,69 +8990,6 @@
       <c r="AR14" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="AS14" t="n">
-        <v>150.35</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>143.29</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>141.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>138.61</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>138.52</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>140.39</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>140.12</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>135.9</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>115.86</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>113.8</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>112.21</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>112.87</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>113.02</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>125.49</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>133.31</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>131.14</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>131.22</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>137.06</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>145.2</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>152.5</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>165.68</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10052,69 +9128,6 @@
       <c r="AR15" t="n">
         <v>-24</v>
       </c>
-      <c r="AS15" t="n">
-        <v>1228.63</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1259.82</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1256.74</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>1234.86</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1107.2</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>943.66</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>650.0599999999999</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>598.54</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>571.54</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>560.66</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>561.76</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>556.28</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>559.16</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>582.75</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>584.22</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>586.79</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>580.71</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>602.4400000000001</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>601.85</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>585.6799999999999</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>543.92</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10253,69 +9266,6 @@
       <c r="AR16" t="n">
         <v>1.94</v>
       </c>
-      <c r="AS16" t="n">
-        <v>473.01</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>444.08</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>434.67</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>422.92</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>423.8</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>458.44</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>489.93</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>501.78</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>477.47</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>494.73</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>511.45</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>508.1</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>500.44</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>517.54</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>517.54</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>484.28</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>458.77</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>470.28</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>488.01</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>502.23</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>548.13</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10454,69 +9404,6 @@
       <c r="AR17" t="n">
         <v>-0.84</v>
       </c>
-      <c r="AS17" t="n">
-        <v>310.75</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>300.76</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>296.58</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>291.51</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>291.53</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>309.76</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>326.92</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>332.96</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>305.22</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>310.05</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>317.75</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>316.64</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>312.4</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>324.58</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>325.21</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>302.89</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>282.64</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>291.92</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>306.24</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>320.15</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>353.21</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10655,69 +9542,6 @@
       <c r="AR18" t="n">
         <v>3.33</v>
       </c>
-      <c r="AS18" t="n">
-        <v>626.28</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>636.1900000000001</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>630.64</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>621.76</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>550.73</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>553.5599999999999</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>558.8</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>566.0700000000001</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>568.14</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>507.01</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>528.0599999999999</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>605.0599999999999</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>627.87</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>674.0700000000001</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>674.5</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>645.4400000000001</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>652.11</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>647.17</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>625.4400000000001</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>594.71</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>579.6900000000001</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10855,69 +9679,6 @@
       </c>
       <c r="AR19" t="n">
         <v>-39.13</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>868</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>893.52</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>887.01</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>864.12</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>775.66</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>649.9400000000001</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>441.38</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>424.12</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>418.55</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>417.46</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>419.76</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>416.94</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>409.53</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>415.35</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>410.12</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>391.44</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>342.28</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>341.66</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>333.84</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>331.58</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>300.88</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -6907,294 +6907,143 @@
   </sheetPr>
   <dimension ref="A1:AR19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="12" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
-    <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
-    <col width="12" customWidth="1" min="36" max="36"/>
-    <col width="12" customWidth="1" min="37" max="37"/>
-    <col width="12" customWidth="1" min="38" max="38"/>
-    <col width="12" customWidth="1" min="39" max="39"/>
-    <col width="12" customWidth="1" min="40" max="40"/>
-    <col width="12" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
-    <col width="12" customWidth="1" min="43" max="43"/>
-    <col width="12" customWidth="1" min="44" max="44"/>
-    <col width="12" customWidth="1" min="45" max="45"/>
-    <col width="12" customWidth="1" min="46" max="46"/>
-    <col width="12" customWidth="1" min="47" max="47"/>
-    <col width="12" customWidth="1" min="48" max="48"/>
-    <col width="12" customWidth="1" min="49" max="49"/>
-    <col width="12" customWidth="1" min="50" max="50"/>
-    <col width="12" customWidth="1" min="51" max="51"/>
-    <col width="12" customWidth="1" min="52" max="52"/>
-    <col width="12" customWidth="1" min="53" max="53"/>
-    <col width="12" customWidth="1" min="54" max="54"/>
-    <col width="12" customWidth="1" min="55" max="55"/>
-    <col width="12" customWidth="1" min="56" max="56"/>
-    <col width="12" customWidth="1" min="57" max="57"/>
-    <col width="12" customWidth="1" min="58" max="58"/>
-    <col width="12" customWidth="1" min="59" max="59"/>
-    <col width="12" customWidth="1" min="60" max="60"/>
-    <col width="12" customWidth="1" min="61" max="61"/>
-    <col width="12" customWidth="1" min="62" max="62"/>
-    <col width="12" customWidth="1" min="63" max="63"/>
-    <col width="12" customWidth="1" min="64" max="64"/>
-    <col width="12" customWidth="1" min="65" max="65"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>종목코드</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>20251029</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>20251030</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>20251031</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>20251103</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>20251104</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>20251105</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>20251106</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>20251107</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>20251110</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>20251111</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>20251112</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>20251113</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>20251114</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>20251117</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>20251118</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>20251119</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>20251120</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>20251121</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>20251124</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>20251125</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>20251126</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>20251127</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>20251128</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>20251201</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>20251202</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>20251203</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>20251204</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>20251205</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>20251208</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>20251209</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>20251210</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>20251211</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>20251212</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>20251215</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>20251216</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>20251217</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>20251218</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>20251219</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>20251222</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>20251223</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>20251224</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>20251226</t>
-        </is>
+      <c r="C1" t="n">
+        <v>20251029</v>
+      </c>
+      <c r="D1" t="n">
+        <v>20251030</v>
+      </c>
+      <c r="E1" t="n">
+        <v>20251031</v>
+      </c>
+      <c r="F1" t="n">
+        <v>20251103</v>
+      </c>
+      <c r="G1" t="n">
+        <v>20251104</v>
+      </c>
+      <c r="H1" t="n">
+        <v>20251105</v>
+      </c>
+      <c r="I1" t="n">
+        <v>20251106</v>
+      </c>
+      <c r="J1" t="n">
+        <v>20251107</v>
+      </c>
+      <c r="K1" t="n">
+        <v>20251110</v>
+      </c>
+      <c r="L1" t="n">
+        <v>20251111</v>
+      </c>
+      <c r="M1" t="n">
+        <v>20251112</v>
+      </c>
+      <c r="N1" t="n">
+        <v>20251113</v>
+      </c>
+      <c r="O1" t="n">
+        <v>20251114</v>
+      </c>
+      <c r="P1" t="n">
+        <v>20251117</v>
+      </c>
+      <c r="Q1" t="n">
+        <v>20251118</v>
+      </c>
+      <c r="R1" t="n">
+        <v>20251119</v>
+      </c>
+      <c r="S1" t="n">
+        <v>20251120</v>
+      </c>
+      <c r="T1" t="n">
+        <v>20251121</v>
+      </c>
+      <c r="U1" t="n">
+        <v>20251124</v>
+      </c>
+      <c r="V1" t="n">
+        <v>20251125</v>
+      </c>
+      <c r="W1" t="n">
+        <v>20251126</v>
+      </c>
+      <c r="X1" t="n">
+        <v>20251127</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>20251128</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>20251201</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>20251202</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>20251203</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>20251204</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>20251205</v>
+      </c>
+      <c r="AE1" t="n">
+        <v>20251208</v>
+      </c>
+      <c r="AF1" t="n">
+        <v>20251209</v>
+      </c>
+      <c r="AG1" t="n">
+        <v>20251210</v>
+      </c>
+      <c r="AH1" t="n">
+        <v>20251211</v>
+      </c>
+      <c r="AI1" t="n">
+        <v>20251212</v>
+      </c>
+      <c r="AJ1" t="n">
+        <v>20251215</v>
+      </c>
+      <c r="AK1" t="n">
+        <v>20251216</v>
+      </c>
+      <c r="AL1" t="n">
+        <v>20251217</v>
+      </c>
+      <c r="AM1" t="n">
+        <v>20251218</v>
+      </c>
+      <c r="AN1" t="n">
+        <v>20251219</v>
+      </c>
+      <c r="AO1" t="n">
+        <v>20251222</v>
+      </c>
+      <c r="AP1" t="n">
+        <v>20251223</v>
+      </c>
+      <c r="AQ1" t="n">
+        <v>20251224</v>
+      </c>
+      <c r="AR1" t="n">
+        <v>20251226</v>
       </c>
     </row>
     <row r="2">
@@ -7205,7 +7054,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0000Z0</t>
+          <t>000000</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -9510,7 +9359,7 @@
         <v>-1.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI18" t="n">
         <v>-9.880000000000001</v>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -6905,7 +6905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR19"/>
+  <dimension ref="A1:CK19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6920,130 +6920,265 @@
         </is>
       </c>
       <c r="C1" t="n">
+        <v>20250829</v>
+      </c>
+      <c r="D1" t="n">
+        <v>20250901</v>
+      </c>
+      <c r="E1" t="n">
+        <v>20250902</v>
+      </c>
+      <c r="F1" t="n">
+        <v>20250903</v>
+      </c>
+      <c r="G1" t="n">
+        <v>20250904</v>
+      </c>
+      <c r="H1" t="n">
+        <v>20250905</v>
+      </c>
+      <c r="I1" t="n">
+        <v>20250908</v>
+      </c>
+      <c r="J1" t="n">
+        <v>20250909</v>
+      </c>
+      <c r="K1" t="n">
+        <v>20250910</v>
+      </c>
+      <c r="L1" t="n">
+        <v>20250911</v>
+      </c>
+      <c r="M1" t="n">
+        <v>20250912</v>
+      </c>
+      <c r="N1" t="n">
+        <v>20250915</v>
+      </c>
+      <c r="O1" t="n">
+        <v>20250916</v>
+      </c>
+      <c r="P1" t="n">
+        <v>20250917</v>
+      </c>
+      <c r="Q1" t="n">
+        <v>20250918</v>
+      </c>
+      <c r="R1" t="n">
+        <v>20250919</v>
+      </c>
+      <c r="S1" t="n">
+        <v>20250922</v>
+      </c>
+      <c r="T1" t="n">
+        <v>20250923</v>
+      </c>
+      <c r="U1" t="n">
+        <v>20250924</v>
+      </c>
+      <c r="V1" t="n">
+        <v>20250925</v>
+      </c>
+      <c r="W1" t="n">
+        <v>20250926</v>
+      </c>
+      <c r="X1" t="n">
+        <v>20250929</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>20250930</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>20251001</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>20251002</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>20251010</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>20251013</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>20251014</v>
+      </c>
+      <c r="AE1" t="n">
+        <v>20251015</v>
+      </c>
+      <c r="AF1" t="n">
+        <v>20251016</v>
+      </c>
+      <c r="AG1" t="n">
+        <v>20251017</v>
+      </c>
+      <c r="AH1" t="n">
+        <v>20251020</v>
+      </c>
+      <c r="AI1" t="n">
+        <v>20251021</v>
+      </c>
+      <c r="AJ1" t="n">
+        <v>20251022</v>
+      </c>
+      <c r="AK1" t="n">
+        <v>20251023</v>
+      </c>
+      <c r="AL1" t="n">
+        <v>20251024</v>
+      </c>
+      <c r="AM1" t="n">
+        <v>20251027</v>
+      </c>
+      <c r="AN1" t="n">
+        <v>20251028</v>
+      </c>
+      <c r="AO1" t="n">
         <v>20251029</v>
       </c>
-      <c r="D1" t="n">
+      <c r="AP1" t="n">
         <v>20251030</v>
       </c>
-      <c r="E1" t="n">
+      <c r="AQ1" t="n">
         <v>20251031</v>
       </c>
-      <c r="F1" t="n">
+      <c r="AR1" t="n">
         <v>20251103</v>
       </c>
-      <c r="G1" t="n">
+      <c r="AS1" t="n">
         <v>20251104</v>
       </c>
-      <c r="H1" t="n">
+      <c r="AT1" t="n">
         <v>20251105</v>
       </c>
-      <c r="I1" t="n">
+      <c r="AU1" t="n">
         <v>20251106</v>
       </c>
-      <c r="J1" t="n">
+      <c r="AV1" t="n">
         <v>20251107</v>
       </c>
-      <c r="K1" t="n">
+      <c r="AW1" t="n">
         <v>20251110</v>
       </c>
-      <c r="L1" t="n">
+      <c r="AX1" t="n">
         <v>20251111</v>
       </c>
-      <c r="M1" t="n">
+      <c r="AY1" t="n">
         <v>20251112</v>
       </c>
-      <c r="N1" t="n">
+      <c r="AZ1" t="n">
         <v>20251113</v>
       </c>
-      <c r="O1" t="n">
+      <c r="BA1" t="n">
         <v>20251114</v>
       </c>
-      <c r="P1" t="n">
+      <c r="BB1" t="n">
         <v>20251117</v>
       </c>
-      <c r="Q1" t="n">
+      <c r="BC1" t="n">
         <v>20251118</v>
       </c>
-      <c r="R1" t="n">
+      <c r="BD1" t="n">
         <v>20251119</v>
       </c>
-      <c r="S1" t="n">
+      <c r="BE1" t="n">
         <v>20251120</v>
       </c>
-      <c r="T1" t="n">
+      <c r="BF1" t="n">
         <v>20251121</v>
       </c>
-      <c r="U1" t="n">
+      <c r="BG1" t="n">
         <v>20251124</v>
       </c>
-      <c r="V1" t="n">
+      <c r="BH1" t="n">
         <v>20251125</v>
       </c>
-      <c r="W1" t="n">
+      <c r="BI1" t="n">
         <v>20251126</v>
       </c>
-      <c r="X1" t="n">
+      <c r="BJ1" t="n">
         <v>20251127</v>
       </c>
-      <c r="Y1" t="n">
+      <c r="BK1" t="n">
         <v>20251128</v>
       </c>
-      <c r="Z1" t="n">
+      <c r="BL1" t="n">
         <v>20251201</v>
       </c>
-      <c r="AA1" t="n">
+      <c r="BM1" t="n">
         <v>20251202</v>
       </c>
-      <c r="AB1" t="n">
+      <c r="BN1" t="n">
         <v>20251203</v>
       </c>
-      <c r="AC1" t="n">
+      <c r="BO1" t="n">
         <v>20251204</v>
       </c>
-      <c r="AD1" t="n">
+      <c r="BP1" t="n">
         <v>20251205</v>
       </c>
-      <c r="AE1" t="n">
+      <c r="BQ1" t="n">
         <v>20251208</v>
       </c>
-      <c r="AF1" t="n">
+      <c r="BR1" t="n">
         <v>20251209</v>
       </c>
-      <c r="AG1" t="n">
+      <c r="BS1" t="n">
         <v>20251210</v>
       </c>
-      <c r="AH1" t="n">
+      <c r="BT1" t="n">
         <v>20251211</v>
       </c>
-      <c r="AI1" t="n">
+      <c r="BU1" t="n">
         <v>20251212</v>
       </c>
-      <c r="AJ1" t="n">
+      <c r="BV1" t="n">
         <v>20251215</v>
       </c>
-      <c r="AK1" t="n">
+      <c r="BW1" t="n">
         <v>20251216</v>
       </c>
-      <c r="AL1" t="n">
+      <c r="BX1" t="n">
         <v>20251217</v>
       </c>
-      <c r="AM1" t="n">
+      <c r="BY1" t="n">
         <v>20251218</v>
       </c>
-      <c r="AN1" t="n">
+      <c r="BZ1" t="n">
         <v>20251219</v>
       </c>
-      <c r="AO1" t="n">
+      <c r="CA1" t="n">
         <v>20251222</v>
       </c>
-      <c r="AP1" t="n">
+      <c r="CB1" t="n">
         <v>20251223</v>
       </c>
-      <c r="AQ1" t="n">
+      <c r="CC1" t="n">
         <v>20251224</v>
       </c>
-      <c r="AR1" t="n">
+      <c r="CD1" t="n">
         <v>20251226</v>
+      </c>
+      <c r="CE1" t="n">
+        <v>20251229</v>
+      </c>
+      <c r="CF1" t="n">
+        <v>20251230</v>
+      </c>
+      <c r="CG1" t="n">
+        <v>20260102</v>
+      </c>
+      <c r="CH1" t="n">
+        <v>20260105</v>
+      </c>
+      <c r="CI1" t="n">
+        <v>20260106</v>
+      </c>
+      <c r="CJ1" t="n">
+        <v>20260107</v>
+      </c>
+      <c r="CK1" t="n">
+        <v>20260108</v>
       </c>
     </row>
     <row r="2">
@@ -7058,130 +7193,265 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v/>
+      </c>
+      <c r="D2" t="n">
+        <v/>
+      </c>
+      <c r="E2" t="n">
+        <v/>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v/>
+      </c>
+      <c r="K2" t="n">
+        <v/>
+      </c>
+      <c r="L2" t="n">
+        <v/>
+      </c>
+      <c r="M2" t="n">
+        <v/>
+      </c>
+      <c r="N2" t="n">
+        <v/>
+      </c>
+      <c r="O2" t="n">
+        <v/>
+      </c>
+      <c r="P2" t="n">
+        <v/>
+      </c>
+      <c r="Q2" t="n">
+        <v/>
+      </c>
+      <c r="R2" t="n">
+        <v/>
+      </c>
+      <c r="S2" t="n">
+        <v/>
+      </c>
+      <c r="T2" t="n">
+        <v/>
+      </c>
+      <c r="U2" t="n">
+        <v/>
+      </c>
+      <c r="V2" t="n">
+        <v/>
+      </c>
+      <c r="W2" t="n">
+        <v/>
+      </c>
+      <c r="X2" t="n">
+        <v/>
+      </c>
+      <c r="Y2" t="n">
+        <v/>
+      </c>
+      <c r="Z2" t="n">
+        <v/>
+      </c>
+      <c r="AA2" t="n">
+        <v/>
+      </c>
+      <c r="AB2" t="n">
+        <v/>
+      </c>
+      <c r="AC2" t="n">
+        <v/>
+      </c>
+      <c r="AD2" t="n">
+        <v/>
+      </c>
+      <c r="AE2" t="n">
+        <v/>
+      </c>
+      <c r="AF2" t="n">
+        <v/>
+      </c>
+      <c r="AG2" t="n">
+        <v/>
+      </c>
+      <c r="AH2" t="n">
+        <v/>
+      </c>
+      <c r="AI2" t="n">
+        <v/>
+      </c>
+      <c r="AJ2" t="n">
+        <v/>
+      </c>
+      <c r="AK2" t="n">
+        <v/>
+      </c>
+      <c r="AL2" t="n">
+        <v/>
+      </c>
+      <c r="AM2" t="n">
+        <v/>
+      </c>
+      <c r="AN2" t="n">
+        <v/>
+      </c>
+      <c r="AO2" t="n">
         <v>19.02</v>
       </c>
-      <c r="D2" t="n">
+      <c r="AP2" t="n">
         <v>29.44</v>
       </c>
-      <c r="E2" t="n">
+      <c r="AQ2" t="n">
         <v>49.8</v>
       </c>
-      <c r="F2" t="n">
+      <c r="AR2" t="n">
         <v>76.39</v>
       </c>
-      <c r="G2" t="n">
+      <c r="AS2" t="n">
         <v>103.88</v>
       </c>
-      <c r="H2" t="n">
+      <c r="AT2" t="n">
         <v>110.94</v>
       </c>
-      <c r="I2" t="n">
+      <c r="AU2" t="n">
         <v>108.63</v>
       </c>
-      <c r="J2" t="n">
+      <c r="AV2" t="n">
         <v>101.37</v>
       </c>
-      <c r="K2" t="n">
+      <c r="AW2" t="n">
         <v>91.86</v>
       </c>
-      <c r="L2" t="n">
+      <c r="AX2" t="n">
         <v>78.51000000000001</v>
       </c>
-      <c r="M2" t="n">
+      <c r="AY2" t="n">
         <v>82.69</v>
       </c>
-      <c r="N2" t="n">
+      <c r="AZ2" t="n">
         <v>85.18000000000001</v>
       </c>
-      <c r="O2" t="n">
+      <c r="BA2" t="n">
         <v>84.73</v>
       </c>
-      <c r="P2" t="n">
+      <c r="BB2" t="n">
         <v>85.33</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="BC2" t="n">
         <v>76.92</v>
       </c>
-      <c r="R2" t="n">
+      <c r="BD2" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="S2" t="n">
+      <c r="BE2" t="n">
         <v>52.56</v>
       </c>
-      <c r="T2" t="n">
+      <c r="BF2" t="n">
         <v>35.7</v>
       </c>
-      <c r="U2" t="n">
+      <c r="BG2" t="n">
         <v>26.99</v>
       </c>
-      <c r="V2" t="n">
+      <c r="BH2" t="n">
         <v>16.1</v>
       </c>
-      <c r="W2" t="n">
+      <c r="BI2" t="n">
         <v>5.08</v>
       </c>
-      <c r="X2" t="n">
+      <c r="BJ2" t="n">
         <v>-7.58</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="BK2" t="n">
         <v>-13.96</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="BL2" t="n">
         <v>-17.27</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="BM2" t="n">
         <v>-17.7</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="BN2" t="n">
         <v>-20.12</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="BO2" t="n">
         <v>-22.5</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="BP2" t="n">
         <v>-31.48</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="BQ2" t="n">
         <v>-36.33</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="BR2" t="n">
         <v>-46.6</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="BS2" t="n">
         <v>-46.09</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="BT2" t="n">
         <v>-43.49</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="BU2" t="n">
         <v>-40.21</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="BV2" t="n">
         <v>-39.8</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="BW2" t="n">
         <v>-35.6</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="BX2" t="n">
         <v>-24</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="BY2" t="n">
         <v>-16.57</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="BZ2" t="n">
         <v>-13.29</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="CA2" t="n">
         <v>-4.54</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="CB2" t="n">
         <v>8.25</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="CC2" t="n">
         <v>13.94</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="CD2" t="n">
         <v>15.38</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>-20.76</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>-15.66</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>-4.14</v>
       </c>
     </row>
     <row r="3">
@@ -7196,130 +7466,265 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v/>
+      </c>
+      <c r="D3" t="n">
+        <v/>
+      </c>
+      <c r="E3" t="n">
+        <v/>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v/>
+      </c>
+      <c r="K3" t="n">
+        <v/>
+      </c>
+      <c r="L3" t="n">
+        <v/>
+      </c>
+      <c r="M3" t="n">
+        <v/>
+      </c>
+      <c r="N3" t="n">
+        <v/>
+      </c>
+      <c r="O3" t="n">
+        <v/>
+      </c>
+      <c r="P3" t="n">
+        <v/>
+      </c>
+      <c r="Q3" t="n">
+        <v/>
+      </c>
+      <c r="R3" t="n">
+        <v/>
+      </c>
+      <c r="S3" t="n">
+        <v/>
+      </c>
+      <c r="T3" t="n">
+        <v/>
+      </c>
+      <c r="U3" t="n">
+        <v/>
+      </c>
+      <c r="V3" t="n">
+        <v/>
+      </c>
+      <c r="W3" t="n">
+        <v/>
+      </c>
+      <c r="X3" t="n">
+        <v/>
+      </c>
+      <c r="Y3" t="n">
+        <v/>
+      </c>
+      <c r="Z3" t="n">
+        <v/>
+      </c>
+      <c r="AA3" t="n">
+        <v/>
+      </c>
+      <c r="AB3" t="n">
+        <v/>
+      </c>
+      <c r="AC3" t="n">
+        <v/>
+      </c>
+      <c r="AD3" t="n">
+        <v/>
+      </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="n">
+        <v/>
+      </c>
+      <c r="AI3" t="n">
+        <v/>
+      </c>
+      <c r="AJ3" t="n">
+        <v/>
+      </c>
+      <c r="AK3" t="n">
+        <v/>
+      </c>
+      <c r="AL3" t="n">
+        <v/>
+      </c>
+      <c r="AM3" t="n">
+        <v/>
+      </c>
+      <c r="AN3" t="n">
+        <v/>
+      </c>
+      <c r="AO3" t="n">
         <v>12.54</v>
       </c>
-      <c r="D3" t="n">
+      <c r="AP3" t="n">
         <v>12.33</v>
       </c>
-      <c r="E3" t="n">
+      <c r="AQ3" t="n">
         <v>6.36</v>
       </c>
-      <c r="F3" t="n">
+      <c r="AR3" t="n">
         <v>4.42</v>
       </c>
-      <c r="G3" t="n">
+      <c r="AS3" t="n">
         <v>-3.97</v>
       </c>
-      <c r="H3" t="n">
+      <c r="AT3" t="n">
         <v>-15.64</v>
       </c>
-      <c r="I3" t="n">
+      <c r="AU3" t="n">
         <v>-22.29</v>
       </c>
-      <c r="J3" t="n">
+      <c r="AV3" t="n">
         <v>-25.49</v>
       </c>
-      <c r="K3" t="n">
+      <c r="AW3" t="n">
         <v>-27.73</v>
       </c>
-      <c r="L3" t="n">
+      <c r="AX3" t="n">
         <v>-34.44</v>
       </c>
-      <c r="M3" t="n">
+      <c r="AY3" t="n">
         <v>-37.09</v>
       </c>
-      <c r="N3" t="n">
+      <c r="AZ3" t="n">
         <v>-38.43</v>
       </c>
-      <c r="O3" t="n">
+      <c r="BA3" t="n">
         <v>-41.51</v>
       </c>
-      <c r="P3" t="n">
+      <c r="BB3" t="n">
         <v>-42.5</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="BC3" t="n">
         <v>-44.24</v>
       </c>
-      <c r="R3" t="n">
+      <c r="BD3" t="n">
         <v>-42.68</v>
       </c>
-      <c r="S3" t="n">
+      <c r="BE3" t="n">
         <v>-44.94</v>
       </c>
-      <c r="T3" t="n">
+      <c r="BF3" t="n">
         <v>-28.38</v>
       </c>
-      <c r="U3" t="n">
+      <c r="BG3" t="n">
         <v>-15.66</v>
       </c>
-      <c r="V3" t="n">
+      <c r="BH3" t="n">
         <v>-7.66</v>
       </c>
-      <c r="W3" t="n">
+      <c r="BI3" t="n">
         <v>-2.01</v>
       </c>
-      <c r="X3" t="n">
+      <c r="BJ3" t="n">
         <v>1.52</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="BK3" t="n">
         <v>4.23</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="BL3" t="n">
         <v>0.06</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="BM3" t="n">
         <v>-2.67</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="BN3" t="n">
         <v>-1.53</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="BO3" t="n">
         <v>-2.97</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="BP3" t="n">
         <v>-1.76</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="BQ3" t="n">
         <v>-1.88</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="BR3" t="n">
         <v>-7.09</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="BS3" t="n">
         <v>-11.87</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="BT3" t="n">
         <v>-17.88</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="BU3" t="n">
         <v>-16.48</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="BV3" t="n">
         <v>-20.83</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="BW3" t="n">
         <v>-18.19</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="BX3" t="n">
         <v>-18.63</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="BY3" t="n">
         <v>-18.71</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="BZ3" t="n">
         <v>-28.38</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="CA3" t="n">
         <v>-34.91</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="CB3" t="n">
         <v>-37.91</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="CC3" t="n">
         <v>-38.81</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="CD3" t="n">
         <v>-30.02</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>-15.82</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>41.82</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>90.51000000000001</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>127.96</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>142.78</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>146.46</v>
       </c>
     </row>
     <row r="4">
@@ -7334,130 +7739,265 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v/>
+      </c>
+      <c r="D4" t="n">
+        <v/>
+      </c>
+      <c r="E4" t="n">
+        <v/>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v/>
+      </c>
+      <c r="K4" t="n">
+        <v/>
+      </c>
+      <c r="L4" t="n">
+        <v/>
+      </c>
+      <c r="M4" t="n">
+        <v/>
+      </c>
+      <c r="N4" t="n">
+        <v/>
+      </c>
+      <c r="O4" t="n">
+        <v/>
+      </c>
+      <c r="P4" t="n">
+        <v/>
+      </c>
+      <c r="Q4" t="n">
+        <v/>
+      </c>
+      <c r="R4" t="n">
+        <v/>
+      </c>
+      <c r="S4" t="n">
+        <v/>
+      </c>
+      <c r="T4" t="n">
+        <v/>
+      </c>
+      <c r="U4" t="n">
+        <v/>
+      </c>
+      <c r="V4" t="n">
+        <v/>
+      </c>
+      <c r="W4" t="n">
+        <v/>
+      </c>
+      <c r="X4" t="n">
+        <v/>
+      </c>
+      <c r="Y4" t="n">
+        <v/>
+      </c>
+      <c r="Z4" t="n">
+        <v/>
+      </c>
+      <c r="AA4" t="n">
+        <v/>
+      </c>
+      <c r="AB4" t="n">
+        <v/>
+      </c>
+      <c r="AC4" t="n">
+        <v/>
+      </c>
+      <c r="AD4" t="n">
+        <v/>
+      </c>
+      <c r="AE4" t="n">
+        <v/>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
+      <c r="AI4" t="n">
+        <v/>
+      </c>
+      <c r="AJ4" t="n">
+        <v/>
+      </c>
+      <c r="AK4" t="n">
+        <v/>
+      </c>
+      <c r="AL4" t="n">
+        <v/>
+      </c>
+      <c r="AM4" t="n">
+        <v/>
+      </c>
+      <c r="AN4" t="n">
+        <v/>
+      </c>
+      <c r="AO4" t="n">
         <v>-22.69</v>
       </c>
-      <c r="D4" t="n">
+      <c r="AP4" t="n">
         <v>-19.19</v>
       </c>
-      <c r="E4" t="n">
+      <c r="AQ4" t="n">
         <v>-9.529999999999999</v>
       </c>
-      <c r="F4" t="n">
+      <c r="AR4" t="n">
         <v>2.4</v>
       </c>
-      <c r="G4" t="n">
+      <c r="AS4" t="n">
         <v>32.42</v>
       </c>
-      <c r="H4" t="n">
+      <c r="AT4" t="n">
         <v>40.77</v>
       </c>
-      <c r="I4" t="n">
+      <c r="AU4" t="n">
         <v>43.76</v>
       </c>
-      <c r="J4" t="n">
+      <c r="AV4" t="n">
         <v>42.59</v>
       </c>
-      <c r="K4" t="n">
+      <c r="AW4" t="n">
         <v>40.42</v>
       </c>
-      <c r="L4" t="n">
+      <c r="AX4" t="n">
         <v>34.22</v>
       </c>
-      <c r="M4" t="n">
+      <c r="AY4" t="n">
         <v>45.83</v>
       </c>
-      <c r="N4" t="n">
+      <c r="AZ4" t="n">
         <v>54.72</v>
       </c>
-      <c r="O4" t="n">
+      <c r="BA4" t="n">
         <v>56.7</v>
       </c>
-      <c r="P4" t="n">
+      <c r="BB4" t="n">
         <v>61.21</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="BC4" t="n">
         <v>58.28</v>
       </c>
-      <c r="R4" t="n">
+      <c r="BD4" t="n">
         <v>49.77</v>
       </c>
-      <c r="S4" t="n">
+      <c r="BE4" t="n">
         <v>46.67</v>
       </c>
-      <c r="T4" t="n">
+      <c r="BF4" t="n">
         <v>34.81</v>
       </c>
-      <c r="U4" t="n">
+      <c r="BG4" t="n">
         <v>26.36</v>
       </c>
-      <c r="V4" t="n">
+      <c r="BH4" t="n">
         <v>16.79</v>
       </c>
-      <c r="W4" t="n">
+      <c r="BI4" t="n">
         <v>6.38</v>
       </c>
-      <c r="X4" t="n">
+      <c r="BJ4" t="n">
         <v>-5.19</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="BK4" t="n">
         <v>-6.86</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="BL4" t="n">
         <v>-8.48</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="BM4" t="n">
         <v>-6.47</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="BN4" t="n">
         <v>-8.57</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="BO4" t="n">
         <v>-12.71</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="BP4" t="n">
         <v>-21.12</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="BQ4" t="n">
         <v>-28.52</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="BR4" t="n">
         <v>-43.96</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="BS4" t="n">
         <v>-42.86</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="BT4" t="n">
         <v>-40.58</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="BU4" t="n">
         <v>-34.52</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="BV4" t="n">
         <v>-30.2</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="BW4" t="n">
         <v>-25.06</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="BX4" t="n">
         <v>-15.2</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="BY4" t="n">
         <v>-11.07</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="BZ4" t="n">
         <v>-9.17</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="CA4" t="n">
         <v>-3.83</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="CB4" t="n">
         <v>3.01</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="CC4" t="n">
         <v>10.09</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="CD4" t="n">
         <v>12.89</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>-5.51</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>-15.74</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>-19.72</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>-25.01</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>-20.78</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>-11.27</v>
       </c>
     </row>
     <row r="5">
@@ -7472,130 +8012,265 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v/>
+      </c>
+      <c r="D5" t="n">
+        <v/>
+      </c>
+      <c r="E5" t="n">
+        <v/>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v/>
+      </c>
+      <c r="K5" t="n">
+        <v/>
+      </c>
+      <c r="L5" t="n">
+        <v/>
+      </c>
+      <c r="M5" t="n">
+        <v/>
+      </c>
+      <c r="N5" t="n">
+        <v/>
+      </c>
+      <c r="O5" t="n">
+        <v/>
+      </c>
+      <c r="P5" t="n">
+        <v/>
+      </c>
+      <c r="Q5" t="n">
+        <v/>
+      </c>
+      <c r="R5" t="n">
+        <v/>
+      </c>
+      <c r="S5" t="n">
+        <v/>
+      </c>
+      <c r="T5" t="n">
+        <v/>
+      </c>
+      <c r="U5" t="n">
+        <v/>
+      </c>
+      <c r="V5" t="n">
+        <v/>
+      </c>
+      <c r="W5" t="n">
+        <v/>
+      </c>
+      <c r="X5" t="n">
+        <v/>
+      </c>
+      <c r="Y5" t="n">
+        <v/>
+      </c>
+      <c r="Z5" t="n">
+        <v/>
+      </c>
+      <c r="AA5" t="n">
+        <v/>
+      </c>
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
+        <v/>
+      </c>
+      <c r="AJ5" t="n">
+        <v/>
+      </c>
+      <c r="AK5" t="n">
+        <v/>
+      </c>
+      <c r="AL5" t="n">
+        <v/>
+      </c>
+      <c r="AM5" t="n">
+        <v/>
+      </c>
+      <c r="AN5" t="n">
+        <v/>
+      </c>
+      <c r="AO5" t="n">
         <v>6.36</v>
       </c>
-      <c r="D5" t="n">
+      <c r="AP5" t="n">
         <v>5.42</v>
       </c>
-      <c r="E5" t="n">
+      <c r="AQ5" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="F5" t="n">
+      <c r="AR5" t="n">
         <v>-5.87</v>
       </c>
-      <c r="G5" t="n">
+      <c r="AS5" t="n">
         <v>-15.54</v>
       </c>
-      <c r="H5" t="n">
+      <c r="AT5" t="n">
         <v>-28.05</v>
       </c>
-      <c r="I5" t="n">
+      <c r="AU5" t="n">
         <v>-37.83</v>
       </c>
-      <c r="J5" t="n">
+      <c r="AV5" t="n">
         <v>-41.25</v>
       </c>
-      <c r="K5" t="n">
+      <c r="AW5" t="n">
         <v>-42.96</v>
       </c>
-      <c r="L5" t="n">
+      <c r="AX5" t="n">
         <v>-50.72</v>
       </c>
-      <c r="M5" t="n">
+      <c r="AY5" t="n">
         <v>-51.56</v>
       </c>
-      <c r="N5" t="n">
+      <c r="AZ5" t="n">
         <v>-51.2</v>
       </c>
-      <c r="O5" t="n">
+      <c r="BA5" t="n">
         <v>-49.64</v>
       </c>
-      <c r="P5" t="n">
+      <c r="BB5" t="n">
         <v>-48.43</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="BC5" t="n">
         <v>-48.13</v>
       </c>
-      <c r="R5" t="n">
+      <c r="BD5" t="n">
         <v>-44.93</v>
       </c>
-      <c r="S5" t="n">
+      <c r="BE5" t="n">
         <v>-42.46</v>
       </c>
-      <c r="T5" t="n">
+      <c r="BF5" t="n">
         <v>-20.58</v>
       </c>
-      <c r="U5" t="n">
+      <c r="BG5" t="n">
         <v>-5.57</v>
       </c>
-      <c r="V5" t="n">
+      <c r="BH5" t="n">
         <v>1.2</v>
       </c>
-      <c r="W5" t="n">
+      <c r="BI5" t="n">
         <v>5.26</v>
       </c>
-      <c r="X5" t="n">
+      <c r="BJ5" t="n">
         <v>7.36</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="BK5" t="n">
         <v>7.34</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="BL5" t="n">
         <v>3.63</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="BM5" t="n">
         <v>-2.13</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="BN5" t="n">
         <v>-1.1</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="BO5" t="n">
         <v>-2.92</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="BP5" t="n">
         <v>-2.02</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="BQ5" t="n">
         <v>-2.87</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="BR5" t="n">
         <v>-7.96</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="BS5" t="n">
         <v>-15.64</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="BT5" t="n">
         <v>-23.13</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="BU5" t="n">
         <v>-22.99</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="BV5" t="n">
         <v>-27.09</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="BW5" t="n">
         <v>-13.26</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="BX5" t="n">
         <v>-12.34</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="BY5" t="n">
         <v>-10.3</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="BZ5" t="n">
         <v>-10.18</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="CA5" t="n">
         <v>-13.27</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="CB5" t="n">
         <v>-10.89</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="CC5" t="n">
         <v>-8.33</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="CD5" t="n">
         <v>-7.01</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>45.64</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>65.53</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>72.98999999999999</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>72.95999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -7610,130 +8285,265 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v/>
+      </c>
+      <c r="D6" t="n">
+        <v/>
+      </c>
+      <c r="E6" t="n">
+        <v/>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v/>
+      </c>
+      <c r="K6" t="n">
+        <v/>
+      </c>
+      <c r="L6" t="n">
+        <v/>
+      </c>
+      <c r="M6" t="n">
+        <v/>
+      </c>
+      <c r="N6" t="n">
+        <v/>
+      </c>
+      <c r="O6" t="n">
+        <v/>
+      </c>
+      <c r="P6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" t="n">
+        <v/>
+      </c>
+      <c r="R6" t="n">
+        <v/>
+      </c>
+      <c r="S6" t="n">
+        <v/>
+      </c>
+      <c r="T6" t="n">
+        <v/>
+      </c>
+      <c r="U6" t="n">
+        <v/>
+      </c>
+      <c r="V6" t="n">
+        <v/>
+      </c>
+      <c r="W6" t="n">
+        <v/>
+      </c>
+      <c r="X6" t="n">
+        <v/>
+      </c>
+      <c r="Y6" t="n">
+        <v/>
+      </c>
+      <c r="Z6" t="n">
+        <v/>
+      </c>
+      <c r="AA6" t="n">
+        <v/>
+      </c>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
+      </c>
+      <c r="AJ6" t="n">
+        <v/>
+      </c>
+      <c r="AK6" t="n">
+        <v/>
+      </c>
+      <c r="AL6" t="n">
+        <v/>
+      </c>
+      <c r="AM6" t="n">
+        <v/>
+      </c>
+      <c r="AN6" t="n">
+        <v/>
+      </c>
+      <c r="AO6" t="n">
         <v>22.88</v>
       </c>
-      <c r="D6" t="n">
+      <c r="AP6" t="n">
         <v>23.33</v>
       </c>
-      <c r="E6" t="n">
+      <c r="AQ6" t="n">
         <v>18.19</v>
       </c>
-      <c r="F6" t="n">
+      <c r="AR6" t="n">
         <v>16.9</v>
       </c>
-      <c r="G6" t="n">
+      <c r="AS6" t="n">
         <v>7.93</v>
       </c>
-      <c r="H6" t="n">
+      <c r="AT6" t="n">
         <v>-4.84</v>
       </c>
-      <c r="I6" t="n">
+      <c r="AU6" t="n">
         <v>-12.88</v>
       </c>
-      <c r="J6" t="n">
+      <c r="AV6" t="n">
         <v>-17.12</v>
       </c>
-      <c r="K6" t="n">
+      <c r="AW6" t="n">
         <v>-20.39</v>
       </c>
-      <c r="L6" t="n">
+      <c r="AX6" t="n">
         <v>-27.1</v>
       </c>
-      <c r="M6" t="n">
+      <c r="AY6" t="n">
         <v>-30.38</v>
       </c>
-      <c r="N6" t="n">
+      <c r="AZ6" t="n">
         <v>-32.15</v>
       </c>
-      <c r="O6" t="n">
+      <c r="BA6" t="n">
         <v>-35.9</v>
       </c>
-      <c r="P6" t="n">
+      <c r="BB6" t="n">
         <v>-36.58</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="BC6" t="n">
         <v>-40.83</v>
       </c>
-      <c r="R6" t="n">
+      <c r="BD6" t="n">
         <v>-43.52</v>
       </c>
-      <c r="S6" t="n">
+      <c r="BE6" t="n">
         <v>-50.45</v>
       </c>
-      <c r="T6" t="n">
+      <c r="BF6" t="n">
         <v>-41.58</v>
       </c>
-      <c r="U6" t="n">
+      <c r="BG6" t="n">
         <v>-32.82</v>
       </c>
-      <c r="V6" t="n">
+      <c r="BH6" t="n">
         <v>-29.85</v>
       </c>
-      <c r="W6" t="n">
+      <c r="BI6" t="n">
         <v>-26.52</v>
       </c>
-      <c r="X6" t="n">
+      <c r="BJ6" t="n">
         <v>-23.5</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="BK6" t="n">
         <v>-20.9</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="BL6" t="n">
         <v>-24.55</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="BM6" t="n">
         <v>-23.91</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="BN6" t="n">
         <v>-20.26</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="BO6" t="n">
         <v>-17.86</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="BP6" t="n">
         <v>-15.44</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="BQ6" t="n">
         <v>-11.06</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="BR6" t="n">
         <v>-10.4</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="BS6" t="n">
         <v>-8.91</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="BT6" t="n">
         <v>-8.470000000000001</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="BU6" t="n">
         <v>-7.11</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="BV6" t="n">
         <v>-9.34</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="BW6" t="n">
         <v>-5.34</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="BX6" t="n">
         <v>-6.34</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="BY6" t="n">
         <v>-5.76</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="BZ6" t="n">
         <v>-17.16</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="CA6" t="n">
         <v>-28.29</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="CB6" t="n">
         <v>-30.63</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="CC6" t="n">
         <v>-29.97</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="CD6" t="n">
         <v>-22.11</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>-9.66</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>40.41</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>83.72</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>114.74</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>127.29</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>130.33</v>
       </c>
     </row>
     <row r="7">
@@ -7748,130 +8558,265 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v/>
+      </c>
+      <c r="D7" t="n">
+        <v/>
+      </c>
+      <c r="E7" t="n">
+        <v/>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v/>
+      </c>
+      <c r="L7" t="n">
+        <v/>
+      </c>
+      <c r="M7" t="n">
+        <v/>
+      </c>
+      <c r="N7" t="n">
+        <v/>
+      </c>
+      <c r="O7" t="n">
+        <v/>
+      </c>
+      <c r="P7" t="n">
+        <v/>
+      </c>
+      <c r="Q7" t="n">
+        <v/>
+      </c>
+      <c r="R7" t="n">
+        <v/>
+      </c>
+      <c r="S7" t="n">
+        <v/>
+      </c>
+      <c r="T7" t="n">
+        <v/>
+      </c>
+      <c r="U7" t="n">
+        <v/>
+      </c>
+      <c r="V7" t="n">
+        <v/>
+      </c>
+      <c r="W7" t="n">
+        <v/>
+      </c>
+      <c r="X7" t="n">
+        <v/>
+      </c>
+      <c r="Y7" t="n">
+        <v/>
+      </c>
+      <c r="Z7" t="n">
+        <v/>
+      </c>
+      <c r="AA7" t="n">
+        <v/>
+      </c>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
+      </c>
+      <c r="AJ7" t="n">
+        <v/>
+      </c>
+      <c r="AK7" t="n">
+        <v/>
+      </c>
+      <c r="AL7" t="n">
+        <v/>
+      </c>
+      <c r="AM7" t="n">
+        <v/>
+      </c>
+      <c r="AN7" t="n">
+        <v/>
+      </c>
+      <c r="AO7" t="n">
         <v>21.85</v>
       </c>
-      <c r="D7" t="n">
+      <c r="AP7" t="n">
         <v>21.69</v>
       </c>
-      <c r="E7" t="n">
+      <c r="AQ7" t="n">
         <v>16.72</v>
       </c>
-      <c r="F7" t="n">
+      <c r="AR7" t="n">
         <v>16.21</v>
       </c>
-      <c r="G7" t="n">
+      <c r="AS7" t="n">
         <v>7.89</v>
       </c>
-      <c r="H7" t="n">
+      <c r="AT7" t="n">
         <v>-4.65</v>
       </c>
-      <c r="I7" t="n">
+      <c r="AU7" t="n">
         <v>-12.9</v>
       </c>
-      <c r="J7" t="n">
+      <c r="AV7" t="n">
         <v>-16.66</v>
       </c>
-      <c r="K7" t="n">
+      <c r="AW7" t="n">
         <v>-20.47</v>
       </c>
-      <c r="L7" t="n">
+      <c r="AX7" t="n">
         <v>-27.13</v>
       </c>
-      <c r="M7" t="n">
+      <c r="AY7" t="n">
         <v>-32.33</v>
       </c>
-      <c r="N7" t="n">
+      <c r="AZ7" t="n">
         <v>-35.07</v>
       </c>
-      <c r="O7" t="n">
+      <c r="BA7" t="n">
         <v>-38.81</v>
       </c>
-      <c r="P7" t="n">
+      <c r="BB7" t="n">
         <v>-40.96</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="BC7" t="n">
         <v>-42.68</v>
       </c>
-      <c r="R7" t="n">
+      <c r="BD7" t="n">
         <v>-43.74</v>
       </c>
-      <c r="S7" t="n">
+      <c r="BE7" t="n">
         <v>-47.12</v>
       </c>
-      <c r="T7" t="n">
+      <c r="BF7" t="n">
         <v>-37.6</v>
       </c>
-      <c r="U7" t="n">
+      <c r="BG7" t="n">
         <v>-30</v>
       </c>
-      <c r="V7" t="n">
+      <c r="BH7" t="n">
         <v>-26.22</v>
       </c>
-      <c r="W7" t="n">
+      <c r="BI7" t="n">
         <v>-23.23</v>
       </c>
-      <c r="X7" t="n">
+      <c r="BJ7" t="n">
         <v>-20.18</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="BK7" t="n">
         <v>-18.12</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="BL7" t="n">
         <v>-23.13</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="BM7" t="n">
         <v>-23.19</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="BN7" t="n">
         <v>-18.18</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="BO7" t="n">
         <v>-15.42</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="BP7" t="n">
         <v>-11.02</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="BQ7" t="n">
         <v>-4.77</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="BR7" t="n">
         <v>-2.41</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="BS7" t="n">
         <v>1.72</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="BT7" t="n">
         <v>3.3</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="BU7" t="n">
         <v>5.44</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="BV7" t="n">
         <v>5.55</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="BW7" t="n">
         <v>3.02</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="BX7" t="n">
         <v>-1.04</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="BY7" t="n">
         <v>-2.99</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="BZ7" t="n">
         <v>-19.55</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="CA7" t="n">
         <v>-32.44</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="CB7" t="n">
         <v>-39.7</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="CC7" t="n">
         <v>-39.15</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="CD7" t="n">
         <v>-29.72</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-15.77</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>81.38</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>111.74</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>126.85</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>132.93</v>
       </c>
     </row>
     <row r="8">
@@ -7886,130 +8831,265 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v/>
+      </c>
+      <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
+        <v/>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
+        <v/>
+      </c>
+      <c r="R8" t="n">
+        <v/>
+      </c>
+      <c r="S8" t="n">
+        <v/>
+      </c>
+      <c r="T8" t="n">
+        <v/>
+      </c>
+      <c r="U8" t="n">
+        <v/>
+      </c>
+      <c r="V8" t="n">
+        <v/>
+      </c>
+      <c r="W8" t="n">
+        <v/>
+      </c>
+      <c r="X8" t="n">
+        <v/>
+      </c>
+      <c r="Y8" t="n">
+        <v/>
+      </c>
+      <c r="Z8" t="n">
+        <v/>
+      </c>
+      <c r="AA8" t="n">
+        <v/>
+      </c>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
+      </c>
+      <c r="AJ8" t="n">
+        <v/>
+      </c>
+      <c r="AK8" t="n">
+        <v/>
+      </c>
+      <c r="AL8" t="n">
+        <v/>
+      </c>
+      <c r="AM8" t="n">
+        <v/>
+      </c>
+      <c r="AN8" t="n">
+        <v/>
+      </c>
+      <c r="AO8" t="n">
         <v>17.93</v>
       </c>
-      <c r="D8" t="n">
+      <c r="AP8" t="n">
         <v>16.83</v>
       </c>
-      <c r="E8" t="n">
+      <c r="AQ8" t="n">
         <v>9.75</v>
       </c>
-      <c r="F8" t="n">
+      <c r="AR8" t="n">
         <v>5.54</v>
       </c>
-      <c r="G8" t="n">
+      <c r="AS8" t="n">
         <v>-3.84</v>
       </c>
-      <c r="H8" t="n">
+      <c r="AT8" t="n">
         <v>-18.19</v>
       </c>
-      <c r="I8" t="n">
+      <c r="AU8" t="n">
         <v>-28.94</v>
       </c>
-      <c r="J8" t="n">
+      <c r="AV8" t="n">
         <v>-33.29</v>
       </c>
-      <c r="K8" t="n">
+      <c r="AW8" t="n">
         <v>-36.34</v>
       </c>
-      <c r="L8" t="n">
+      <c r="AX8" t="n">
         <v>-42.37</v>
       </c>
-      <c r="M8" t="n">
+      <c r="AY8" t="n">
         <v>-44.78</v>
       </c>
-      <c r="N8" t="n">
+      <c r="AZ8" t="n">
         <v>-44.77</v>
       </c>
-      <c r="O8" t="n">
+      <c r="BA8" t="n">
         <v>-47.2</v>
       </c>
-      <c r="P8" t="n">
+      <c r="BB8" t="n">
         <v>-47.39</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="BC8" t="n">
         <v>-48.46</v>
       </c>
-      <c r="R8" t="n">
+      <c r="BD8" t="n">
         <v>-46.83</v>
       </c>
-      <c r="S8" t="n">
+      <c r="BE8" t="n">
         <v>-48.91</v>
       </c>
-      <c r="T8" t="n">
+      <c r="BF8" t="n">
         <v>-34.53</v>
       </c>
-      <c r="U8" t="n">
+      <c r="BG8" t="n">
         <v>-21.49</v>
       </c>
-      <c r="V8" t="n">
+      <c r="BH8" t="n">
         <v>-13.9</v>
       </c>
-      <c r="W8" t="n">
+      <c r="BI8" t="n">
         <v>-8.869999999999999</v>
       </c>
-      <c r="X8" t="n">
+      <c r="BJ8" t="n">
         <v>-4.95</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="BK8" t="n">
         <v>-1.35</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="BL8" t="n">
         <v>-3.89</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="BM8" t="n">
         <v>-5.19</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="BN8" t="n">
         <v>-2.86</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="BO8" t="n">
         <v>-2.07</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="BP8" t="n">
         <v>-0.68</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="BQ8" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="BR8" t="n">
         <v>-4.54</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="BS8" t="n">
         <v>-8.48</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="BT8" t="n">
         <v>-15.14</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="BU8" t="n">
         <v>-12.85</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="BV8" t="n">
         <v>-17.08</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="BW8" t="n">
         <v>-14.84</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="BX8" t="n">
         <v>-15.5</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="BY8" t="n">
         <v>-15.76</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="BZ8" t="n">
         <v>-26</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="CA8" t="n">
         <v>-34.24</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="CB8" t="n">
         <v>-36.3</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="CC8" t="n">
         <v>-33.31</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="CD8" t="n">
         <v>-21.24</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>62.65</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>114.46</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>151.15</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>164.61</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>166.2</v>
       </c>
     </row>
     <row r="9">
@@ -8024,130 +9104,265 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v/>
+      </c>
+      <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
+        <v/>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v/>
+      </c>
+      <c r="K9" t="n">
+        <v/>
+      </c>
+      <c r="L9" t="n">
+        <v/>
+      </c>
+      <c r="M9" t="n">
+        <v/>
+      </c>
+      <c r="N9" t="n">
+        <v/>
+      </c>
+      <c r="O9" t="n">
+        <v/>
+      </c>
+      <c r="P9" t="n">
+        <v/>
+      </c>
+      <c r="Q9" t="n">
+        <v/>
+      </c>
+      <c r="R9" t="n">
+        <v/>
+      </c>
+      <c r="S9" t="n">
+        <v/>
+      </c>
+      <c r="T9" t="n">
+        <v/>
+      </c>
+      <c r="U9" t="n">
+        <v/>
+      </c>
+      <c r="V9" t="n">
+        <v/>
+      </c>
+      <c r="W9" t="n">
+        <v/>
+      </c>
+      <c r="X9" t="n">
+        <v/>
+      </c>
+      <c r="Y9" t="n">
+        <v/>
+      </c>
+      <c r="Z9" t="n">
+        <v/>
+      </c>
+      <c r="AA9" t="n">
+        <v/>
+      </c>
+      <c r="AB9" t="n">
+        <v/>
+      </c>
+      <c r="AC9" t="n">
+        <v/>
+      </c>
+      <c r="AD9" t="n">
+        <v/>
+      </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
+      <c r="AI9" t="n">
+        <v/>
+      </c>
+      <c r="AJ9" t="n">
+        <v/>
+      </c>
+      <c r="AK9" t="n">
+        <v/>
+      </c>
+      <c r="AL9" t="n">
+        <v/>
+      </c>
+      <c r="AM9" t="n">
+        <v/>
+      </c>
+      <c r="AN9" t="n">
+        <v/>
+      </c>
+      <c r="AO9" t="n">
         <v>193.55</v>
       </c>
-      <c r="D9" t="n">
+      <c r="AP9" t="n">
         <v>163.86</v>
       </c>
-      <c r="E9" t="n">
+      <c r="AQ9" t="n">
         <v>132.58</v>
       </c>
-      <c r="F9" t="n">
+      <c r="AR9" t="n">
         <v>106.56</v>
       </c>
-      <c r="G9" t="n">
+      <c r="AS9" t="n">
         <v>82.78</v>
       </c>
-      <c r="H9" t="n">
+      <c r="AT9" t="n">
         <v>59.41</v>
       </c>
-      <c r="I9" t="n">
+      <c r="AU9" t="n">
         <v>40.06</v>
       </c>
-      <c r="J9" t="n">
+      <c r="AV9" t="n">
         <v>19.26</v>
       </c>
-      <c r="K9" t="n">
+      <c r="AW9" t="n">
         <v>0.01</v>
       </c>
-      <c r="L9" t="n">
+      <c r="AX9" t="n">
         <v>-15.64</v>
       </c>
-      <c r="M9" t="n">
+      <c r="AY9" t="n">
         <v>-32.24</v>
       </c>
-      <c r="N9" t="n">
+      <c r="AZ9" t="n">
         <v>-41.13</v>
       </c>
-      <c r="O9" t="n">
+      <c r="BA9" t="n">
         <v>-46.93</v>
       </c>
-      <c r="P9" t="n">
+      <c r="BB9" t="n">
         <v>-51.98</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="BC9" t="n">
         <v>-52.85</v>
       </c>
-      <c r="R9" t="n">
+      <c r="BD9" t="n">
         <v>-49.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="BE9" t="n">
         <v>-48.17</v>
       </c>
-      <c r="T9" t="n">
+      <c r="BF9" t="n">
         <v>-41.62</v>
       </c>
-      <c r="U9" t="n">
+      <c r="BG9" t="n">
         <v>-33.41</v>
       </c>
-      <c r="V9" t="n">
+      <c r="BH9" t="n">
         <v>-29.18</v>
       </c>
-      <c r="W9" t="n">
+      <c r="BI9" t="n">
         <v>-34.67</v>
       </c>
-      <c r="X9" t="n">
+      <c r="BJ9" t="n">
         <v>-34.5</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="BK9" t="n">
         <v>-30.15</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="BL9" t="n">
         <v>-27.17</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="BM9" t="n">
         <v>-25.33</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="BN9" t="n">
         <v>-21.13</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="BO9" t="n">
         <v>-16.89</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="BP9" t="n">
         <v>-12.61</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="BQ9" t="n">
         <v>-9.279999999999999</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="BR9" t="n">
         <v>-8.18</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="BS9" t="n">
         <v>-12.9</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="BT9" t="n">
         <v>-28.81</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="BU9" t="n">
         <v>-31.82</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="BV9" t="n">
         <v>-35.54</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="BW9" t="n">
         <v>-32.98</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="BX9" t="n">
         <v>-30.97</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="BY9" t="n">
         <v>-19.15</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="BZ9" t="n">
         <v>-8.42</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="CA9" t="n">
         <v>-3.96</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="CB9" t="n">
         <v>1.29</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="CC9" t="n">
         <v>5.98</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="CD9" t="n">
         <v>12.29</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>27.92</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>37.95</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>41.62</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>33.61</v>
       </c>
     </row>
     <row r="10">
@@ -8162,130 +9377,265 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v/>
+      </c>
+      <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
+        <v/>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v/>
+      </c>
+      <c r="K10" t="n">
+        <v/>
+      </c>
+      <c r="L10" t="n">
+        <v/>
+      </c>
+      <c r="M10" t="n">
+        <v/>
+      </c>
+      <c r="N10" t="n">
+        <v/>
+      </c>
+      <c r="O10" t="n">
+        <v/>
+      </c>
+      <c r="P10" t="n">
+        <v/>
+      </c>
+      <c r="Q10" t="n">
+        <v/>
+      </c>
+      <c r="R10" t="n">
+        <v/>
+      </c>
+      <c r="S10" t="n">
+        <v/>
+      </c>
+      <c r="T10" t="n">
+        <v/>
+      </c>
+      <c r="U10" t="n">
+        <v/>
+      </c>
+      <c r="V10" t="n">
+        <v/>
+      </c>
+      <c r="W10" t="n">
+        <v/>
+      </c>
+      <c r="X10" t="n">
+        <v/>
+      </c>
+      <c r="Y10" t="n">
+        <v/>
+      </c>
+      <c r="Z10" t="n">
+        <v/>
+      </c>
+      <c r="AA10" t="n">
+        <v/>
+      </c>
+      <c r="AB10" t="n">
+        <v/>
+      </c>
+      <c r="AC10" t="n">
+        <v/>
+      </c>
+      <c r="AD10" t="n">
+        <v/>
+      </c>
+      <c r="AE10" t="n">
+        <v/>
+      </c>
+      <c r="AF10" t="n">
+        <v/>
+      </c>
+      <c r="AG10" t="n">
+        <v/>
+      </c>
+      <c r="AH10" t="n">
+        <v/>
+      </c>
+      <c r="AI10" t="n">
+        <v/>
+      </c>
+      <c r="AJ10" t="n">
+        <v/>
+      </c>
+      <c r="AK10" t="n">
+        <v/>
+      </c>
+      <c r="AL10" t="n">
+        <v/>
+      </c>
+      <c r="AM10" t="n">
+        <v/>
+      </c>
+      <c r="AN10" t="n">
+        <v/>
+      </c>
+      <c r="AO10" t="n">
         <v>8.58</v>
       </c>
-      <c r="D10" t="n">
+      <c r="AP10" t="n">
         <v>8.92</v>
       </c>
-      <c r="E10" t="n">
+      <c r="AQ10" t="n">
         <v>4.18</v>
       </c>
-      <c r="F10" t="n">
+      <c r="AR10" t="n">
         <v>-0.33</v>
       </c>
-      <c r="G10" t="n">
+      <c r="AS10" t="n">
         <v>-5.51</v>
       </c>
-      <c r="H10" t="n">
+      <c r="AT10" t="n">
         <v>-18.08</v>
       </c>
-      <c r="I10" t="n">
+      <c r="AU10" t="n">
         <v>-26.24</v>
       </c>
-      <c r="J10" t="n">
+      <c r="AV10" t="n">
         <v>-29.59</v>
       </c>
-      <c r="K10" t="n">
+      <c r="AW10" t="n">
         <v>-31.13</v>
       </c>
-      <c r="L10" t="n">
+      <c r="AX10" t="n">
         <v>-38.22</v>
       </c>
-      <c r="M10" t="n">
+      <c r="AY10" t="n">
         <v>-39.23</v>
       </c>
-      <c r="N10" t="n">
+      <c r="AZ10" t="n">
         <v>-38.6</v>
       </c>
-      <c r="O10" t="n">
+      <c r="BA10" t="n">
         <v>-39.22</v>
       </c>
-      <c r="P10" t="n">
+      <c r="BB10" t="n">
         <v>-38.39</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="BC10" t="n">
         <v>-40.03</v>
       </c>
-      <c r="R10" t="n">
+      <c r="BD10" t="n">
         <v>-39.18</v>
       </c>
-      <c r="S10" t="n">
+      <c r="BE10" t="n">
         <v>-41.35</v>
       </c>
-      <c r="T10" t="n">
+      <c r="BF10" t="n">
         <v>-24.42</v>
       </c>
-      <c r="U10" t="n">
+      <c r="BG10" t="n">
         <v>-12.08</v>
       </c>
-      <c r="V10" t="n">
+      <c r="BH10" t="n">
         <v>-8.720000000000001</v>
       </c>
-      <c r="W10" t="n">
+      <c r="BI10" t="n">
         <v>-6.21</v>
       </c>
-      <c r="X10" t="n">
+      <c r="BJ10" t="n">
         <v>-3.62</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="BK10" t="n">
         <v>-2.21</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="BL10" t="n">
         <v>-2.4</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="BM10" t="n">
         <v>-8.68</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="BN10" t="n">
         <v>-4.12</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="BO10" t="n">
         <v>-3.81</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="BP10" t="n">
         <v>-4.84</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="BQ10" t="n">
         <v>-3.89</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="BR10" t="n">
         <v>-3.71</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="BS10" t="n">
         <v>-4.42</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="BT10" t="n">
         <v>-6.46</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="BU10" t="n">
         <v>-7.66</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="BV10" t="n">
         <v>-8.25</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="BW10" t="n">
         <v>3.26</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="BX10" t="n">
         <v>4.84</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="BY10" t="n">
         <v>12.35</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="BZ10" t="n">
         <v>11.98</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="CA10" t="n">
         <v>6.01</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="CB10" t="n">
         <v>7.4</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="CC10" t="n">
         <v>9.92</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="CD10" t="n">
         <v>8.720000000000001</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>29.74</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>55.72</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>63.05</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>64.95</v>
       </c>
     </row>
     <row r="11">
@@ -8300,130 +9650,265 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v/>
+      </c>
+      <c r="D11" t="n">
+        <v/>
+      </c>
+      <c r="E11" t="n">
+        <v/>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v/>
+      </c>
+      <c r="J11" t="n">
+        <v/>
+      </c>
+      <c r="K11" t="n">
+        <v/>
+      </c>
+      <c r="L11" t="n">
+        <v/>
+      </c>
+      <c r="M11" t="n">
+        <v/>
+      </c>
+      <c r="N11" t="n">
+        <v/>
+      </c>
+      <c r="O11" t="n">
+        <v/>
+      </c>
+      <c r="P11" t="n">
+        <v/>
+      </c>
+      <c r="Q11" t="n">
+        <v/>
+      </c>
+      <c r="R11" t="n">
+        <v/>
+      </c>
+      <c r="S11" t="n">
+        <v/>
+      </c>
+      <c r="T11" t="n">
+        <v/>
+      </c>
+      <c r="U11" t="n">
+        <v/>
+      </c>
+      <c r="V11" t="n">
+        <v/>
+      </c>
+      <c r="W11" t="n">
+        <v/>
+      </c>
+      <c r="X11" t="n">
+        <v/>
+      </c>
+      <c r="Y11" t="n">
+        <v/>
+      </c>
+      <c r="Z11" t="n">
+        <v/>
+      </c>
+      <c r="AA11" t="n">
+        <v/>
+      </c>
+      <c r="AB11" t="n">
+        <v/>
+      </c>
+      <c r="AC11" t="n">
+        <v/>
+      </c>
+      <c r="AD11" t="n">
+        <v/>
+      </c>
+      <c r="AE11" t="n">
+        <v/>
+      </c>
+      <c r="AF11" t="n">
+        <v/>
+      </c>
+      <c r="AG11" t="n">
+        <v/>
+      </c>
+      <c r="AH11" t="n">
+        <v/>
+      </c>
+      <c r="AI11" t="n">
+        <v/>
+      </c>
+      <c r="AJ11" t="n">
+        <v/>
+      </c>
+      <c r="AK11" t="n">
+        <v/>
+      </c>
+      <c r="AL11" t="n">
+        <v/>
+      </c>
+      <c r="AM11" t="n">
+        <v/>
+      </c>
+      <c r="AN11" t="n">
+        <v/>
+      </c>
+      <c r="AO11" t="n">
         <v>170.77</v>
       </c>
-      <c r="D11" t="n">
+      <c r="AP11" t="n">
         <v>143.35</v>
       </c>
-      <c r="E11" t="n">
+      <c r="AQ11" t="n">
         <v>116.39</v>
       </c>
-      <c r="F11" t="n">
+      <c r="AR11" t="n">
         <v>93.78</v>
       </c>
-      <c r="G11" t="n">
+      <c r="AS11" t="n">
         <v>72.73999999999999</v>
       </c>
-      <c r="H11" t="n">
+      <c r="AT11" t="n">
         <v>51.54</v>
       </c>
-      <c r="I11" t="n">
+      <c r="AU11" t="n">
         <v>32.01</v>
       </c>
-      <c r="J11" t="n">
+      <c r="AV11" t="n">
         <v>10.45</v>
       </c>
-      <c r="K11" t="n">
+      <c r="AW11" t="n">
         <v>-8.75</v>
       </c>
-      <c r="L11" t="n">
+      <c r="AX11" t="n">
         <v>-25.16</v>
       </c>
-      <c r="M11" t="n">
+      <c r="AY11" t="n">
         <v>-44.26</v>
       </c>
-      <c r="N11" t="n">
+      <c r="AZ11" t="n">
         <v>-55.39</v>
       </c>
-      <c r="O11" t="n">
+      <c r="BA11" t="n">
         <v>-60.1</v>
       </c>
-      <c r="P11" t="n">
+      <c r="BB11" t="n">
         <v>-64.08</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="BC11" t="n">
         <v>-65.73</v>
       </c>
-      <c r="R11" t="n">
+      <c r="BD11" t="n">
         <v>-62.56</v>
       </c>
-      <c r="S11" t="n">
+      <c r="BE11" t="n">
         <v>-61.43</v>
       </c>
-      <c r="T11" t="n">
+      <c r="BF11" t="n">
         <v>-55.51</v>
       </c>
-      <c r="U11" t="n">
+      <c r="BG11" t="n">
         <v>-48.37</v>
       </c>
-      <c r="V11" t="n">
+      <c r="BH11" t="n">
         <v>-45.22</v>
       </c>
-      <c r="W11" t="n">
+      <c r="BI11" t="n">
         <v>-46.97</v>
       </c>
-      <c r="X11" t="n">
+      <c r="BJ11" t="n">
         <v>-43.96</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="BK11" t="n">
         <v>-39.69</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="BL11" t="n">
         <v>-36.14</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="BM11" t="n">
         <v>-32.45</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="BN11" t="n">
         <v>-26.34</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="BO11" t="n">
         <v>-20.53</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="BP11" t="n">
         <v>-14.02</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="BQ11" t="n">
         <v>3.31</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="BR11" t="n">
         <v>19.82</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="BS11" t="n">
         <v>28.35</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="BT11" t="n">
         <v>26.52</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="BU11" t="n">
         <v>29.61</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="BV11" t="n">
         <v>31.34</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="BW11" t="n">
         <v>26.54</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="BX11" t="n">
         <v>22.19</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="BY11" t="n">
         <v>21.29</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="BZ11" t="n">
         <v>15.9</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="CA11" t="n">
         <v>4.37</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="CB11" t="n">
         <v>-5.18</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="CC11" t="n">
         <v>-4.22</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="CD11" t="n">
         <v>-3.13</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>17.15</v>
       </c>
     </row>
     <row r="12">
@@ -8438,130 +9923,265 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v/>
+      </c>
+      <c r="D12" t="n">
+        <v/>
+      </c>
+      <c r="E12" t="n">
+        <v/>
+      </c>
+      <c r="F12" t="n">
+        <v/>
+      </c>
+      <c r="G12" t="n">
+        <v/>
+      </c>
+      <c r="H12" t="n">
+        <v/>
+      </c>
+      <c r="I12" t="n">
+        <v/>
+      </c>
+      <c r="J12" t="n">
+        <v/>
+      </c>
+      <c r="K12" t="n">
+        <v/>
+      </c>
+      <c r="L12" t="n">
+        <v/>
+      </c>
+      <c r="M12" t="n">
+        <v/>
+      </c>
+      <c r="N12" t="n">
+        <v/>
+      </c>
+      <c r="O12" t="n">
+        <v/>
+      </c>
+      <c r="P12" t="n">
+        <v/>
+      </c>
+      <c r="Q12" t="n">
+        <v/>
+      </c>
+      <c r="R12" t="n">
+        <v/>
+      </c>
+      <c r="S12" t="n">
+        <v/>
+      </c>
+      <c r="T12" t="n">
+        <v/>
+      </c>
+      <c r="U12" t="n">
+        <v/>
+      </c>
+      <c r="V12" t="n">
+        <v/>
+      </c>
+      <c r="W12" t="n">
+        <v/>
+      </c>
+      <c r="X12" t="n">
+        <v/>
+      </c>
+      <c r="Y12" t="n">
+        <v/>
+      </c>
+      <c r="Z12" t="n">
+        <v/>
+      </c>
+      <c r="AA12" t="n">
+        <v/>
+      </c>
+      <c r="AB12" t="n">
+        <v/>
+      </c>
+      <c r="AC12" t="n">
+        <v/>
+      </c>
+      <c r="AD12" t="n">
+        <v/>
+      </c>
+      <c r="AE12" t="n">
+        <v/>
+      </c>
+      <c r="AF12" t="n">
+        <v/>
+      </c>
+      <c r="AG12" t="n">
+        <v/>
+      </c>
+      <c r="AH12" t="n">
+        <v/>
+      </c>
+      <c r="AI12" t="n">
+        <v/>
+      </c>
+      <c r="AJ12" t="n">
+        <v/>
+      </c>
+      <c r="AK12" t="n">
+        <v/>
+      </c>
+      <c r="AL12" t="n">
+        <v/>
+      </c>
+      <c r="AM12" t="n">
+        <v/>
+      </c>
+      <c r="AN12" t="n">
+        <v/>
+      </c>
+      <c r="AO12" t="n">
         <v>177.13</v>
       </c>
-      <c r="D12" t="n">
+      <c r="AP12" t="n">
         <v>147.55</v>
       </c>
-      <c r="E12" t="n">
+      <c r="AQ12" t="n">
         <v>119.23</v>
       </c>
-      <c r="F12" t="n">
+      <c r="AR12" t="n">
         <v>95.90000000000001</v>
       </c>
-      <c r="G12" t="n">
+      <c r="AS12" t="n">
         <v>74.06</v>
       </c>
-      <c r="H12" t="n">
+      <c r="AT12" t="n">
         <v>53.04</v>
       </c>
-      <c r="I12" t="n">
+      <c r="AU12" t="n">
         <v>33.42</v>
       </c>
-      <c r="J12" t="n">
+      <c r="AV12" t="n">
         <v>11.98</v>
       </c>
-      <c r="K12" t="n">
+      <c r="AW12" t="n">
         <v>-7.45</v>
       </c>
-      <c r="L12" t="n">
+      <c r="AX12" t="n">
         <v>-24.57</v>
       </c>
-      <c r="M12" t="n">
+      <c r="AY12" t="n">
         <v>-43.73</v>
       </c>
-      <c r="N12" t="n">
+      <c r="AZ12" t="n">
         <v>-55.16</v>
       </c>
-      <c r="O12" t="n">
+      <c r="BA12" t="n">
         <v>-59.68</v>
       </c>
-      <c r="P12" t="n">
+      <c r="BB12" t="n">
         <v>-63.32</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="BC12" t="n">
         <v>-64.14</v>
       </c>
-      <c r="R12" t="n">
+      <c r="BD12" t="n">
         <v>-60.57</v>
       </c>
-      <c r="S12" t="n">
+      <c r="BE12" t="n">
         <v>-59.05</v>
       </c>
-      <c r="T12" t="n">
+      <c r="BF12" t="n">
         <v>-53.56</v>
       </c>
-      <c r="U12" t="n">
+      <c r="BG12" t="n">
         <v>-47.45</v>
       </c>
-      <c r="V12" t="n">
+      <c r="BH12" t="n">
         <v>-44.33</v>
       </c>
-      <c r="W12" t="n">
+      <c r="BI12" t="n">
         <v>-47.02</v>
       </c>
-      <c r="X12" t="n">
+      <c r="BJ12" t="n">
         <v>-44.12</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="BK12" t="n">
         <v>-40.15</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="BL12" t="n">
         <v>-37.16</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="BM12" t="n">
         <v>-34</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="BN12" t="n">
         <v>-28.66</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="BO12" t="n">
         <v>-24.01</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="BP12" t="n">
         <v>-17.45</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="BQ12" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="BR12" t="n">
         <v>18.41</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="BS12" t="n">
         <v>27.25</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="BT12" t="n">
         <v>26.85</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="BU12" t="n">
         <v>30.31</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="BV12" t="n">
         <v>32.7</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="BW12" t="n">
         <v>27.98</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="BX12" t="n">
         <v>23.35</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="BY12" t="n">
         <v>21.96</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="BZ12" t="n">
         <v>17.24</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="CA12" t="n">
         <v>6.8</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="CB12" t="n">
         <v>-3.18</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="CC12" t="n">
         <v>-2.69</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="CD12" t="n">
         <v>-1.83</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>20.77</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>17.01</v>
       </c>
     </row>
     <row r="13">
@@ -8576,130 +10196,265 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v/>
+      </c>
+      <c r="D13" t="n">
+        <v/>
+      </c>
+      <c r="E13" t="n">
+        <v/>
+      </c>
+      <c r="F13" t="n">
+        <v/>
+      </c>
+      <c r="G13" t="n">
+        <v/>
+      </c>
+      <c r="H13" t="n">
+        <v/>
+      </c>
+      <c r="I13" t="n">
+        <v/>
+      </c>
+      <c r="J13" t="n">
+        <v/>
+      </c>
+      <c r="K13" t="n">
+        <v/>
+      </c>
+      <c r="L13" t="n">
+        <v/>
+      </c>
+      <c r="M13" t="n">
+        <v/>
+      </c>
+      <c r="N13" t="n">
+        <v/>
+      </c>
+      <c r="O13" t="n">
+        <v/>
+      </c>
+      <c r="P13" t="n">
+        <v/>
+      </c>
+      <c r="Q13" t="n">
+        <v/>
+      </c>
+      <c r="R13" t="n">
+        <v/>
+      </c>
+      <c r="S13" t="n">
+        <v/>
+      </c>
+      <c r="T13" t="n">
+        <v/>
+      </c>
+      <c r="U13" t="n">
+        <v/>
+      </c>
+      <c r="V13" t="n">
+        <v/>
+      </c>
+      <c r="W13" t="n">
+        <v/>
+      </c>
+      <c r="X13" t="n">
+        <v/>
+      </c>
+      <c r="Y13" t="n">
+        <v/>
+      </c>
+      <c r="Z13" t="n">
+        <v/>
+      </c>
+      <c r="AA13" t="n">
+        <v/>
+      </c>
+      <c r="AB13" t="n">
+        <v/>
+      </c>
+      <c r="AC13" t="n">
+        <v/>
+      </c>
+      <c r="AD13" t="n">
+        <v/>
+      </c>
+      <c r="AE13" t="n">
+        <v/>
+      </c>
+      <c r="AF13" t="n">
+        <v/>
+      </c>
+      <c r="AG13" t="n">
+        <v/>
+      </c>
+      <c r="AH13" t="n">
+        <v/>
+      </c>
+      <c r="AI13" t="n">
+        <v/>
+      </c>
+      <c r="AJ13" t="n">
+        <v/>
+      </c>
+      <c r="AK13" t="n">
+        <v/>
+      </c>
+      <c r="AL13" t="n">
+        <v/>
+      </c>
+      <c r="AM13" t="n">
+        <v/>
+      </c>
+      <c r="AN13" t="n">
+        <v/>
+      </c>
+      <c r="AO13" t="n">
         <v>174.73</v>
       </c>
-      <c r="D13" t="n">
+      <c r="AP13" t="n">
         <v>145.48</v>
       </c>
-      <c r="E13" t="n">
+      <c r="AQ13" t="n">
         <v>117.59</v>
       </c>
-      <c r="F13" t="n">
+      <c r="AR13" t="n">
         <v>94.97</v>
       </c>
-      <c r="G13" t="n">
+      <c r="AS13" t="n">
         <v>73.62</v>
       </c>
-      <c r="H13" t="n">
+      <c r="AT13" t="n">
         <v>52.41</v>
       </c>
-      <c r="I13" t="n">
+      <c r="AU13" t="n">
         <v>32.85</v>
       </c>
-      <c r="J13" t="n">
+      <c r="AV13" t="n">
         <v>11.2</v>
       </c>
-      <c r="K13" t="n">
+      <c r="AW13" t="n">
         <v>-7.82</v>
       </c>
-      <c r="L13" t="n">
+      <c r="AX13" t="n">
         <v>-24.67</v>
       </c>
-      <c r="M13" t="n">
+      <c r="AY13" t="n">
         <v>-43.7</v>
       </c>
-      <c r="N13" t="n">
+      <c r="AZ13" t="n">
         <v>-56.1</v>
       </c>
-      <c r="O13" t="n">
+      <c r="BA13" t="n">
         <v>-60.6</v>
       </c>
-      <c r="P13" t="n">
+      <c r="BB13" t="n">
         <v>-64.18000000000001</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="BC13" t="n">
         <v>-64.93000000000001</v>
       </c>
-      <c r="R13" t="n">
+      <c r="BD13" t="n">
         <v>-60.23</v>
       </c>
-      <c r="S13" t="n">
+      <c r="BE13" t="n">
         <v>-58.38</v>
       </c>
-      <c r="T13" t="n">
+      <c r="BF13" t="n">
         <v>-52.22</v>
       </c>
-      <c r="U13" t="n">
+      <c r="BG13" t="n">
         <v>-45.08</v>
       </c>
-      <c r="V13" t="n">
+      <c r="BH13" t="n">
         <v>-41.49</v>
       </c>
-      <c r="W13" t="n">
+      <c r="BI13" t="n">
         <v>-42.28</v>
       </c>
-      <c r="X13" t="n">
+      <c r="BJ13" t="n">
         <v>-39.1</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="BK13" t="n">
         <v>-35.02</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="BL13" t="n">
         <v>-32.27</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="BM13" t="n">
         <v>-29.51</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="BN13" t="n">
         <v>-24.02</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="BO13" t="n">
         <v>-19.42</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="BP13" t="n">
         <v>-12.31</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="BQ13" t="n">
         <v>10.44</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="BR13" t="n">
         <v>29.93</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="BS13" t="n">
         <v>40.71</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="BT13" t="n">
         <v>42.4</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="BU13" t="n">
         <v>45.15</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="BV13" t="n">
         <v>46.47</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="BW13" t="n">
         <v>39.39</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="BX13" t="n">
         <v>32.74</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="BY13" t="n">
         <v>28.33</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="BZ13" t="n">
         <v>20.64</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="CA13" t="n">
         <v>7.99</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="CB13" t="n">
         <v>-4.19</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="CC13" t="n">
         <v>-6.2</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="CD13" t="n">
         <v>-8.07</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>-10.01</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>-4.67</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>6.24</v>
       </c>
     </row>
     <row r="14">
@@ -8714,130 +10469,265 @@
         </is>
       </c>
       <c r="C14" t="n">
+        <v/>
+      </c>
+      <c r="D14" t="n">
+        <v/>
+      </c>
+      <c r="E14" t="n">
+        <v/>
+      </c>
+      <c r="F14" t="n">
+        <v/>
+      </c>
+      <c r="G14" t="n">
+        <v/>
+      </c>
+      <c r="H14" t="n">
+        <v/>
+      </c>
+      <c r="I14" t="n">
+        <v/>
+      </c>
+      <c r="J14" t="n">
+        <v/>
+      </c>
+      <c r="K14" t="n">
+        <v/>
+      </c>
+      <c r="L14" t="n">
+        <v/>
+      </c>
+      <c r="M14" t="n">
+        <v/>
+      </c>
+      <c r="N14" t="n">
+        <v/>
+      </c>
+      <c r="O14" t="n">
+        <v/>
+      </c>
+      <c r="P14" t="n">
+        <v/>
+      </c>
+      <c r="Q14" t="n">
+        <v/>
+      </c>
+      <c r="R14" t="n">
+        <v/>
+      </c>
+      <c r="S14" t="n">
+        <v/>
+      </c>
+      <c r="T14" t="n">
+        <v/>
+      </c>
+      <c r="U14" t="n">
+        <v/>
+      </c>
+      <c r="V14" t="n">
+        <v/>
+      </c>
+      <c r="W14" t="n">
+        <v/>
+      </c>
+      <c r="X14" t="n">
+        <v/>
+      </c>
+      <c r="Y14" t="n">
+        <v/>
+      </c>
+      <c r="Z14" t="n">
+        <v/>
+      </c>
+      <c r="AA14" t="n">
+        <v/>
+      </c>
+      <c r="AB14" t="n">
+        <v/>
+      </c>
+      <c r="AC14" t="n">
+        <v/>
+      </c>
+      <c r="AD14" t="n">
+        <v/>
+      </c>
+      <c r="AE14" t="n">
+        <v/>
+      </c>
+      <c r="AF14" t="n">
+        <v/>
+      </c>
+      <c r="AG14" t="n">
+        <v/>
+      </c>
+      <c r="AH14" t="n">
+        <v/>
+      </c>
+      <c r="AI14" t="n">
+        <v/>
+      </c>
+      <c r="AJ14" t="n">
+        <v/>
+      </c>
+      <c r="AK14" t="n">
+        <v/>
+      </c>
+      <c r="AL14" t="n">
+        <v/>
+      </c>
+      <c r="AM14" t="n">
+        <v/>
+      </c>
+      <c r="AN14" t="n">
+        <v/>
+      </c>
+      <c r="AO14" t="n">
         <v>194.76</v>
       </c>
-      <c r="D14" t="n">
+      <c r="AP14" t="n">
         <v>164.49</v>
       </c>
-      <c r="E14" t="n">
+      <c r="AQ14" t="n">
         <v>134.07</v>
       </c>
-      <c r="F14" t="n">
+      <c r="AR14" t="n">
         <v>109.22</v>
       </c>
-      <c r="G14" t="n">
+      <c r="AS14" t="n">
         <v>86.16</v>
       </c>
-      <c r="H14" t="n">
+      <c r="AT14" t="n">
         <v>63.23</v>
       </c>
-      <c r="I14" t="n">
+      <c r="AU14" t="n">
         <v>42.66</v>
       </c>
-      <c r="J14" t="n">
+      <c r="AV14" t="n">
         <v>21.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="AW14" t="n">
         <v>1.81</v>
       </c>
-      <c r="L14" t="n">
+      <c r="AX14" t="n">
         <v>-14.31</v>
       </c>
-      <c r="M14" t="n">
+      <c r="AY14" t="n">
         <v>-31.89</v>
       </c>
-      <c r="N14" t="n">
+      <c r="AZ14" t="n">
         <v>-42.03</v>
       </c>
-      <c r="O14" t="n">
+      <c r="BA14" t="n">
         <v>-48.2</v>
       </c>
-      <c r="P14" t="n">
+      <c r="BB14" t="n">
         <v>-53.67</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="BC14" t="n">
         <v>-56.27</v>
       </c>
-      <c r="R14" t="n">
+      <c r="BD14" t="n">
         <v>-53.18</v>
       </c>
-      <c r="S14" t="n">
+      <c r="BE14" t="n">
         <v>-52.56</v>
       </c>
-      <c r="T14" t="n">
+      <c r="BF14" t="n">
         <v>-44.68</v>
       </c>
-      <c r="U14" t="n">
+      <c r="BG14" t="n">
         <v>-35.1</v>
       </c>
-      <c r="V14" t="n">
+      <c r="BH14" t="n">
         <v>-30.27</v>
       </c>
-      <c r="W14" t="n">
+      <c r="BI14" t="n">
         <v>-33.76</v>
       </c>
-      <c r="X14" t="n">
+      <c r="BJ14" t="n">
         <v>-31.77</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="BK14" t="n">
         <v>-27.64</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="BL14" t="n">
         <v>-25.76</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="BM14" t="n">
         <v>-24.74</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="BN14" t="n">
         <v>-21.19</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="BO14" t="n">
         <v>-17.98</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="BP14" t="n">
         <v>-13.71</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="BQ14" t="n">
         <v>-8.85</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="BR14" t="n">
         <v>-6.09</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="BS14" t="n">
         <v>-7.15</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="BT14" t="n">
         <v>-19.44</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="BU14" t="n">
         <v>-19.86</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="BV14" t="n">
         <v>-20.39</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="BW14" t="n">
         <v>-19.58</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="BX14" t="n">
         <v>-18.93</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="BY14" t="n">
         <v>-9.83</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="BZ14" t="n">
         <v>-3.69</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="CA14" t="n">
         <v>-3.93</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="CB14" t="n">
         <v>-2.3</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="CC14" t="n">
         <v>2.87</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="CD14" t="n">
         <v>9.380000000000001</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>24.23</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>34.21</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>38.27</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>32.14</v>
       </c>
     </row>
     <row r="15">
@@ -8852,130 +10742,265 @@
         </is>
       </c>
       <c r="C15" t="n">
+        <v/>
+      </c>
+      <c r="D15" t="n">
+        <v/>
+      </c>
+      <c r="E15" t="n">
+        <v/>
+      </c>
+      <c r="F15" t="n">
+        <v/>
+      </c>
+      <c r="G15" t="n">
+        <v/>
+      </c>
+      <c r="H15" t="n">
+        <v/>
+      </c>
+      <c r="I15" t="n">
+        <v/>
+      </c>
+      <c r="J15" t="n">
+        <v/>
+      </c>
+      <c r="K15" t="n">
+        <v/>
+      </c>
+      <c r="L15" t="n">
+        <v/>
+      </c>
+      <c r="M15" t="n">
+        <v/>
+      </c>
+      <c r="N15" t="n">
+        <v/>
+      </c>
+      <c r="O15" t="n">
+        <v/>
+      </c>
+      <c r="P15" t="n">
+        <v/>
+      </c>
+      <c r="Q15" t="n">
+        <v/>
+      </c>
+      <c r="R15" t="n">
+        <v/>
+      </c>
+      <c r="S15" t="n">
+        <v/>
+      </c>
+      <c r="T15" t="n">
+        <v/>
+      </c>
+      <c r="U15" t="n">
+        <v/>
+      </c>
+      <c r="V15" t="n">
+        <v/>
+      </c>
+      <c r="W15" t="n">
+        <v/>
+      </c>
+      <c r="X15" t="n">
+        <v/>
+      </c>
+      <c r="Y15" t="n">
+        <v/>
+      </c>
+      <c r="Z15" t="n">
+        <v/>
+      </c>
+      <c r="AA15" t="n">
+        <v/>
+      </c>
+      <c r="AB15" t="n">
+        <v/>
+      </c>
+      <c r="AC15" t="n">
+        <v/>
+      </c>
+      <c r="AD15" t="n">
+        <v/>
+      </c>
+      <c r="AE15" t="n">
+        <v/>
+      </c>
+      <c r="AF15" t="n">
+        <v/>
+      </c>
+      <c r="AG15" t="n">
+        <v/>
+      </c>
+      <c r="AH15" t="n">
+        <v/>
+      </c>
+      <c r="AI15" t="n">
+        <v/>
+      </c>
+      <c r="AJ15" t="n">
+        <v/>
+      </c>
+      <c r="AK15" t="n">
+        <v/>
+      </c>
+      <c r="AL15" t="n">
+        <v/>
+      </c>
+      <c r="AM15" t="n">
+        <v/>
+      </c>
+      <c r="AN15" t="n">
+        <v/>
+      </c>
+      <c r="AO15" t="n">
         <v>-3.78</v>
       </c>
-      <c r="D15" t="n">
+      <c r="AP15" t="n">
         <v>3.44</v>
       </c>
-      <c r="E15" t="n">
+      <c r="AQ15" t="n">
         <v>30.8</v>
       </c>
-      <c r="F15" t="n">
+      <c r="AR15" t="n">
         <v>57.74</v>
       </c>
-      <c r="G15" t="n">
+      <c r="AS15" t="n">
         <v>94.01000000000001</v>
       </c>
-      <c r="H15" t="n">
+      <c r="AT15" t="n">
         <v>105.04</v>
       </c>
-      <c r="I15" t="n">
+      <c r="AU15" t="n">
         <v>106.84</v>
       </c>
-      <c r="J15" t="n">
+      <c r="AV15" t="n">
         <v>99.88</v>
       </c>
-      <c r="K15" t="n">
+      <c r="AW15" t="n">
         <v>90.43000000000001</v>
       </c>
-      <c r="L15" t="n">
+      <c r="AX15" t="n">
         <v>78.37</v>
       </c>
-      <c r="M15" t="n">
+      <c r="AY15" t="n">
         <v>89.54000000000001</v>
       </c>
-      <c r="N15" t="n">
+      <c r="AZ15" t="n">
         <v>94.61</v>
       </c>
-      <c r="O15" t="n">
+      <c r="BA15" t="n">
         <v>95.91</v>
       </c>
-      <c r="P15" t="n">
+      <c r="BB15" t="n">
         <v>99.13</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="BC15" t="n">
         <v>91.05</v>
       </c>
-      <c r="R15" t="n">
+      <c r="BD15" t="n">
         <v>77.95</v>
       </c>
-      <c r="S15" t="n">
+      <c r="BE15" t="n">
         <v>66.62</v>
       </c>
-      <c r="T15" t="n">
+      <c r="BF15" t="n">
         <v>51.04</v>
       </c>
-      <c r="U15" t="n">
+      <c r="BG15" t="n">
         <v>40.96</v>
       </c>
-      <c r="V15" t="n">
+      <c r="BH15" t="n">
         <v>28.73</v>
       </c>
-      <c r="W15" t="n">
+      <c r="BI15" t="n">
         <v>17.47</v>
       </c>
-      <c r="X15" t="n">
+      <c r="BJ15" t="n">
         <v>4.76</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="BK15" t="n">
         <v>1.65</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="BL15" t="n">
         <v>0.52</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="BM15" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="BN15" t="n">
         <v>-0.79</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="BO15" t="n">
         <v>-3.66</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="BP15" t="n">
         <v>-14.07</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="BQ15" t="n">
         <v>-26.63</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="BR15" t="n">
         <v>-48.79</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="BS15" t="n">
         <v>-51.85</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="BT15" t="n">
         <v>-52.74</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="BU15" t="n">
         <v>-52.09</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="BV15" t="n">
         <v>-50.05</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="BW15" t="n">
         <v>-48.32</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="BX15" t="n">
         <v>-45.64</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="BY15" t="n">
         <v>-40.66</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="BZ15" t="n">
         <v>-37.77</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="CA15" t="n">
         <v>-34.57</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="CB15" t="n">
         <v>-32.27</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="CC15" t="n">
         <v>-26.73</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="CD15" t="n">
         <v>-24</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-23</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>-25.12</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>-26.98</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>-27.21</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>-33.39</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>-22.92</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>-8.68</v>
       </c>
     </row>
     <row r="16">
@@ -8990,130 +11015,265 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v/>
+      </c>
+      <c r="D16" t="n">
+        <v/>
+      </c>
+      <c r="E16" t="n">
+        <v/>
+      </c>
+      <c r="F16" t="n">
+        <v/>
+      </c>
+      <c r="G16" t="n">
+        <v/>
+      </c>
+      <c r="H16" t="n">
+        <v/>
+      </c>
+      <c r="I16" t="n">
+        <v/>
+      </c>
+      <c r="J16" t="n">
+        <v/>
+      </c>
+      <c r="K16" t="n">
+        <v/>
+      </c>
+      <c r="L16" t="n">
+        <v/>
+      </c>
+      <c r="M16" t="n">
+        <v/>
+      </c>
+      <c r="N16" t="n">
+        <v/>
+      </c>
+      <c r="O16" t="n">
+        <v/>
+      </c>
+      <c r="P16" t="n">
+        <v/>
+      </c>
+      <c r="Q16" t="n">
+        <v/>
+      </c>
+      <c r="R16" t="n">
+        <v/>
+      </c>
+      <c r="S16" t="n">
+        <v/>
+      </c>
+      <c r="T16" t="n">
+        <v/>
+      </c>
+      <c r="U16" t="n">
+        <v/>
+      </c>
+      <c r="V16" t="n">
+        <v/>
+      </c>
+      <c r="W16" t="n">
+        <v/>
+      </c>
+      <c r="X16" t="n">
+        <v/>
+      </c>
+      <c r="Y16" t="n">
+        <v/>
+      </c>
+      <c r="Z16" t="n">
+        <v/>
+      </c>
+      <c r="AA16" t="n">
+        <v/>
+      </c>
+      <c r="AB16" t="n">
+        <v/>
+      </c>
+      <c r="AC16" t="n">
+        <v/>
+      </c>
+      <c r="AD16" t="n">
+        <v/>
+      </c>
+      <c r="AE16" t="n">
+        <v/>
+      </c>
+      <c r="AF16" t="n">
+        <v/>
+      </c>
+      <c r="AG16" t="n">
+        <v/>
+      </c>
+      <c r="AH16" t="n">
+        <v/>
+      </c>
+      <c r="AI16" t="n">
+        <v/>
+      </c>
+      <c r="AJ16" t="n">
+        <v/>
+      </c>
+      <c r="AK16" t="n">
+        <v/>
+      </c>
+      <c r="AL16" t="n">
+        <v/>
+      </c>
+      <c r="AM16" t="n">
+        <v/>
+      </c>
+      <c r="AN16" t="n">
+        <v/>
+      </c>
+      <c r="AO16" t="n">
         <v>176.14</v>
       </c>
-      <c r="D16" t="n">
+      <c r="AP16" t="n">
         <v>149.02</v>
       </c>
-      <c r="E16" t="n">
+      <c r="AQ16" t="n">
         <v>121.12</v>
       </c>
-      <c r="F16" t="n">
+      <c r="AR16" t="n">
         <v>98.42</v>
       </c>
-      <c r="G16" t="n">
+      <c r="AS16" t="n">
         <v>76.84</v>
       </c>
-      <c r="H16" t="n">
+      <c r="AT16" t="n">
         <v>54.91</v>
       </c>
-      <c r="I16" t="n">
+      <c r="AU16" t="n">
         <v>35.96</v>
       </c>
-      <c r="J16" t="n">
+      <c r="AV16" t="n">
         <v>14.63</v>
       </c>
-      <c r="K16" t="n">
+      <c r="AW16" t="n">
         <v>-5.05</v>
       </c>
-      <c r="L16" t="n">
+      <c r="AX16" t="n">
         <v>-21.72</v>
       </c>
-      <c r="M16" t="n">
+      <c r="AY16" t="n">
         <v>-40.31</v>
       </c>
-      <c r="N16" t="n">
+      <c r="AZ16" t="n">
         <v>-50.59</v>
       </c>
-      <c r="O16" t="n">
+      <c r="BA16" t="n">
         <v>-55.5</v>
       </c>
-      <c r="P16" t="n">
+      <c r="BB16" t="n">
         <v>-59.68</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="BC16" t="n">
         <v>-61.17</v>
       </c>
-      <c r="R16" t="n">
+      <c r="BD16" t="n">
         <v>-58.16</v>
       </c>
-      <c r="S16" t="n">
+      <c r="BE16" t="n">
         <v>-58.48</v>
       </c>
-      <c r="T16" t="n">
+      <c r="BF16" t="n">
         <v>-51.21</v>
       </c>
-      <c r="U16" t="n">
+      <c r="BG16" t="n">
         <v>-41.99</v>
       </c>
-      <c r="V16" t="n">
+      <c r="BH16" t="n">
         <v>-37.21</v>
       </c>
-      <c r="W16" t="n">
+      <c r="BI16" t="n">
         <v>-38.94</v>
       </c>
-      <c r="X16" t="n">
+      <c r="BJ16" t="n">
         <v>-36.54</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="BK16" t="n">
         <v>-32.47</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="BL16" t="n">
         <v>-31.12</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="BM16" t="n">
         <v>-30.42</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="BN16" t="n">
         <v>-26.74</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="BO16" t="n">
         <v>-23.4</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="BP16" t="n">
         <v>-18.17</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="BQ16" t="n">
         <v>-6.98</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="BR16" t="n">
         <v>2.83</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="BS16" t="n">
         <v>6.83</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="BT16" t="n">
         <v>2.25</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="BU16" t="n">
         <v>5.77</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="BV16" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="BW16" t="n">
         <v>6.52</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="BX16" t="n">
         <v>4.11</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="BY16" t="n">
         <v>6.5</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="BZ16" t="n">
         <v>5.96</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="CA16" t="n">
         <v>-0.33</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="CB16" t="n">
         <v>-4.65</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="CC16" t="n">
         <v>-1.86</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="CD16" t="n">
         <v>1.94</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>21.16</v>
       </c>
     </row>
     <row r="17">
@@ -9128,130 +11288,265 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v/>
+      </c>
+      <c r="D17" t="n">
+        <v/>
+      </c>
+      <c r="E17" t="n">
+        <v/>
+      </c>
+      <c r="F17" t="n">
+        <v/>
+      </c>
+      <c r="G17" t="n">
+        <v/>
+      </c>
+      <c r="H17" t="n">
+        <v/>
+      </c>
+      <c r="I17" t="n">
+        <v/>
+      </c>
+      <c r="J17" t="n">
+        <v/>
+      </c>
+      <c r="K17" t="n">
+        <v/>
+      </c>
+      <c r="L17" t="n">
+        <v/>
+      </c>
+      <c r="M17" t="n">
+        <v/>
+      </c>
+      <c r="N17" t="n">
+        <v/>
+      </c>
+      <c r="O17" t="n">
+        <v/>
+      </c>
+      <c r="P17" t="n">
+        <v/>
+      </c>
+      <c r="Q17" t="n">
+        <v/>
+      </c>
+      <c r="R17" t="n">
+        <v/>
+      </c>
+      <c r="S17" t="n">
+        <v/>
+      </c>
+      <c r="T17" t="n">
+        <v/>
+      </c>
+      <c r="U17" t="n">
+        <v/>
+      </c>
+      <c r="V17" t="n">
+        <v/>
+      </c>
+      <c r="W17" t="n">
+        <v/>
+      </c>
+      <c r="X17" t="n">
+        <v/>
+      </c>
+      <c r="Y17" t="n">
+        <v/>
+      </c>
+      <c r="Z17" t="n">
+        <v/>
+      </c>
+      <c r="AA17" t="n">
+        <v/>
+      </c>
+      <c r="AB17" t="n">
+        <v/>
+      </c>
+      <c r="AC17" t="n">
+        <v/>
+      </c>
+      <c r="AD17" t="n">
+        <v/>
+      </c>
+      <c r="AE17" t="n">
+        <v/>
+      </c>
+      <c r="AF17" t="n">
+        <v/>
+      </c>
+      <c r="AG17" t="n">
+        <v/>
+      </c>
+      <c r="AH17" t="n">
+        <v/>
+      </c>
+      <c r="AI17" t="n">
+        <v/>
+      </c>
+      <c r="AJ17" t="n">
+        <v/>
+      </c>
+      <c r="AK17" t="n">
+        <v/>
+      </c>
+      <c r="AL17" t="n">
+        <v/>
+      </c>
+      <c r="AM17" t="n">
+        <v/>
+      </c>
+      <c r="AN17" t="n">
+        <v/>
+      </c>
+      <c r="AO17" t="n">
         <v>164.34</v>
       </c>
-      <c r="D17" t="n">
+      <c r="AP17" t="n">
         <v>139.06</v>
       </c>
-      <c r="E17" t="n">
+      <c r="AQ17" t="n">
         <v>113.37</v>
       </c>
-      <c r="F17" t="n">
+      <c r="AR17" t="n">
         <v>91.38</v>
       </c>
-      <c r="G17" t="n">
+      <c r="AS17" t="n">
         <v>70.3</v>
       </c>
-      <c r="H17" t="n">
+      <c r="AT17" t="n">
         <v>49.24</v>
       </c>
-      <c r="I17" t="n">
+      <c r="AU17" t="n">
         <v>30.19</v>
       </c>
-      <c r="J17" t="n">
+      <c r="AV17" t="n">
         <v>9.15</v>
       </c>
-      <c r="K17" t="n">
+      <c r="AW17" t="n">
         <v>-10.28</v>
       </c>
-      <c r="L17" t="n">
+      <c r="AX17" t="n">
         <v>-26.34</v>
       </c>
-      <c r="M17" t="n">
+      <c r="AY17" t="n">
         <v>-45.44</v>
       </c>
-      <c r="N17" t="n">
+      <c r="AZ17" t="n">
         <v>-54.4</v>
       </c>
-      <c r="O17" t="n">
+      <c r="BA17" t="n">
         <v>-58.48</v>
       </c>
-      <c r="P17" t="n">
+      <c r="BB17" t="n">
         <v>-61.95</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="BC17" t="n">
         <v>-61.94</v>
       </c>
-      <c r="R17" t="n">
+      <c r="BD17" t="n">
         <v>-57.45</v>
       </c>
-      <c r="S17" t="n">
+      <c r="BE17" t="n">
         <v>-55.94</v>
       </c>
-      <c r="T17" t="n">
+      <c r="BF17" t="n">
         <v>-49.25</v>
       </c>
-      <c r="U17" t="n">
+      <c r="BG17" t="n">
         <v>-40.76</v>
       </c>
-      <c r="V17" t="n">
+      <c r="BH17" t="n">
         <v>-36.43</v>
       </c>
-      <c r="W17" t="n">
+      <c r="BI17" t="n">
         <v>-38.77</v>
       </c>
-      <c r="X17" t="n">
+      <c r="BJ17" t="n">
         <v>-35.85</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="BK17" t="n">
         <v>-31.79</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="BL17" t="n">
         <v>-28.97</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="BM17" t="n">
         <v>-26.06</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="BN17" t="n">
         <v>-21.68</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="BO17" t="n">
         <v>-17.55</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="BP17" t="n">
         <v>-12.51</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="BQ17" t="n">
         <v>-2.85</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="BR17" t="n">
         <v>5.47</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="BS17" t="n">
         <v>8.24</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="BT17" t="n">
         <v>-0.53</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="BU17" t="n">
         <v>0.71</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="BV17" t="n">
         <v>2.3</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="BW17" t="n">
         <v>0.99</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="BX17" t="n">
         <v>-0.86</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="BY17" t="n">
         <v>2.33</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="BZ17" t="n">
         <v>2.35</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="CA17" t="n">
         <v>-3.93</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="CB17" t="n">
         <v>-9.23</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="CC17" t="n">
         <v>-5.71</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="CD17" t="n">
         <v>-0.84</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>28.86</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>30.08</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>25.4</v>
       </c>
     </row>
     <row r="18">
@@ -9266,130 +11561,265 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v/>
+      </c>
+      <c r="D18" t="n">
+        <v/>
+      </c>
+      <c r="E18" t="n">
+        <v/>
+      </c>
+      <c r="F18" t="n">
+        <v/>
+      </c>
+      <c r="G18" t="n">
+        <v/>
+      </c>
+      <c r="H18" t="n">
+        <v/>
+      </c>
+      <c r="I18" t="n">
+        <v/>
+      </c>
+      <c r="J18" t="n">
+        <v/>
+      </c>
+      <c r="K18" t="n">
+        <v/>
+      </c>
+      <c r="L18" t="n">
+        <v/>
+      </c>
+      <c r="M18" t="n">
+        <v/>
+      </c>
+      <c r="N18" t="n">
+        <v/>
+      </c>
+      <c r="O18" t="n">
+        <v/>
+      </c>
+      <c r="P18" t="n">
+        <v/>
+      </c>
+      <c r="Q18" t="n">
+        <v/>
+      </c>
+      <c r="R18" t="n">
+        <v/>
+      </c>
+      <c r="S18" t="n">
+        <v/>
+      </c>
+      <c r="T18" t="n">
+        <v/>
+      </c>
+      <c r="U18" t="n">
+        <v/>
+      </c>
+      <c r="V18" t="n">
+        <v/>
+      </c>
+      <c r="W18" t="n">
+        <v/>
+      </c>
+      <c r="X18" t="n">
+        <v/>
+      </c>
+      <c r="Y18" t="n">
+        <v/>
+      </c>
+      <c r="Z18" t="n">
+        <v/>
+      </c>
+      <c r="AA18" t="n">
+        <v/>
+      </c>
+      <c r="AB18" t="n">
+        <v/>
+      </c>
+      <c r="AC18" t="n">
+        <v/>
+      </c>
+      <c r="AD18" t="n">
+        <v/>
+      </c>
+      <c r="AE18" t="n">
+        <v/>
+      </c>
+      <c r="AF18" t="n">
+        <v/>
+      </c>
+      <c r="AG18" t="n">
+        <v/>
+      </c>
+      <c r="AH18" t="n">
+        <v/>
+      </c>
+      <c r="AI18" t="n">
+        <v/>
+      </c>
+      <c r="AJ18" t="n">
+        <v/>
+      </c>
+      <c r="AK18" t="n">
+        <v/>
+      </c>
+      <c r="AL18" t="n">
+        <v/>
+      </c>
+      <c r="AM18" t="n">
+        <v/>
+      </c>
+      <c r="AN18" t="n">
+        <v/>
+      </c>
+      <c r="AO18" t="n">
         <v>31.57</v>
       </c>
-      <c r="D18" t="n">
+      <c r="AP18" t="n">
         <v>31</v>
       </c>
-      <c r="E18" t="n">
+      <c r="AQ18" t="n">
         <v>25.54</v>
       </c>
-      <c r="F18" t="n">
+      <c r="AR18" t="n">
         <v>20.36</v>
       </c>
-      <c r="G18" t="n">
+      <c r="AS18" t="n">
         <v>13.97</v>
       </c>
-      <c r="H18" t="n">
+      <c r="AT18" t="n">
         <v>-2.19</v>
       </c>
-      <c r="I18" t="n">
+      <c r="AU18" t="n">
         <v>-13.61</v>
       </c>
-      <c r="J18" t="n">
+      <c r="AV18" t="n">
         <v>-20.27</v>
       </c>
-      <c r="K18" t="n">
+      <c r="AW18" t="n">
         <v>-23.14</v>
       </c>
-      <c r="L18" t="n">
+      <c r="AX18" t="n">
         <v>-30.26</v>
       </c>
-      <c r="M18" t="n">
+      <c r="AY18" t="n">
         <v>-30.46</v>
       </c>
-      <c r="N18" t="n">
+      <c r="AZ18" t="n">
         <v>-29.03</v>
       </c>
-      <c r="O18" t="n">
+      <c r="BA18" t="n">
         <v>-32.42</v>
       </c>
-      <c r="P18" t="n">
+      <c r="BB18" t="n">
         <v>-27.84</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="BC18" t="n">
         <v>-33.72</v>
       </c>
-      <c r="R18" t="n">
+      <c r="BD18" t="n">
         <v>-37.94</v>
       </c>
-      <c r="S18" t="n">
+      <c r="BE18" t="n">
         <v>-41.06</v>
       </c>
-      <c r="T18" t="n">
+      <c r="BF18" t="n">
         <v>-39.57</v>
       </c>
-      <c r="U18" t="n">
+      <c r="BG18" t="n">
         <v>-37.97</v>
       </c>
-      <c r="V18" t="n">
+      <c r="BH18" t="n">
         <v>-34.62</v>
       </c>
-      <c r="W18" t="n">
+      <c r="BI18" t="n">
         <v>-27.37</v>
       </c>
-      <c r="X18" t="n">
+      <c r="BJ18" t="n">
         <v>-18.67</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="BK18" t="n">
         <v>-8.84</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="BL18" t="n">
         <v>-2.62</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="BM18" t="n">
         <v>2.16</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="BN18" t="n">
         <v>3.54</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="BO18" t="n">
         <v>3.64</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="BP18" t="n">
         <v>-6.67</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="BQ18" t="n">
         <v>-4.83</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="BR18" t="n">
         <v>-3.13</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="BS18" t="n">
         <v>-1.15</v>
       </c>
-      <c r="AH18" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AI18" t="n">
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
         <v>-9.880000000000001</v>
       </c>
-      <c r="AJ18" t="n">
+      <c r="BV18" t="n">
         <v>-5.1</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="BW18" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="BX18" t="n">
         <v>11.73</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="BY18" t="n">
         <v>18.07</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="BZ18" t="n">
         <v>16.28</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="CA18" t="n">
         <v>9.76</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="CB18" t="n">
         <v>9.41</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="CC18" t="n">
         <v>7.47</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="CD18" t="n">
         <v>3.33</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>-1.65</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>-3.76</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>53.97</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>66.05</v>
       </c>
     </row>
     <row r="19">
@@ -9404,130 +11834,265 @@
         </is>
       </c>
       <c r="C19" t="n">
+        <v/>
+      </c>
+      <c r="D19" t="n">
+        <v/>
+      </c>
+      <c r="E19" t="n">
+        <v/>
+      </c>
+      <c r="F19" t="n">
+        <v/>
+      </c>
+      <c r="G19" t="n">
+        <v/>
+      </c>
+      <c r="H19" t="n">
+        <v/>
+      </c>
+      <c r="I19" t="n">
+        <v/>
+      </c>
+      <c r="J19" t="n">
+        <v/>
+      </c>
+      <c r="K19" t="n">
+        <v/>
+      </c>
+      <c r="L19" t="n">
+        <v/>
+      </c>
+      <c r="M19" t="n">
+        <v/>
+      </c>
+      <c r="N19" t="n">
+        <v/>
+      </c>
+      <c r="O19" t="n">
+        <v/>
+      </c>
+      <c r="P19" t="n">
+        <v/>
+      </c>
+      <c r="Q19" t="n">
+        <v/>
+      </c>
+      <c r="R19" t="n">
+        <v/>
+      </c>
+      <c r="S19" t="n">
+        <v/>
+      </c>
+      <c r="T19" t="n">
+        <v/>
+      </c>
+      <c r="U19" t="n">
+        <v/>
+      </c>
+      <c r="V19" t="n">
+        <v/>
+      </c>
+      <c r="W19" t="n">
+        <v/>
+      </c>
+      <c r="X19" t="n">
+        <v/>
+      </c>
+      <c r="Y19" t="n">
+        <v/>
+      </c>
+      <c r="Z19" t="n">
+        <v/>
+      </c>
+      <c r="AA19" t="n">
+        <v/>
+      </c>
+      <c r="AB19" t="n">
+        <v/>
+      </c>
+      <c r="AC19" t="n">
+        <v/>
+      </c>
+      <c r="AD19" t="n">
+        <v/>
+      </c>
+      <c r="AE19" t="n">
+        <v/>
+      </c>
+      <c r="AF19" t="n">
+        <v/>
+      </c>
+      <c r="AG19" t="n">
+        <v/>
+      </c>
+      <c r="AH19" t="n">
+        <v/>
+      </c>
+      <c r="AI19" t="n">
+        <v/>
+      </c>
+      <c r="AJ19" t="n">
+        <v/>
+      </c>
+      <c r="AK19" t="n">
+        <v/>
+      </c>
+      <c r="AL19" t="n">
+        <v/>
+      </c>
+      <c r="AM19" t="n">
+        <v/>
+      </c>
+      <c r="AN19" t="n">
+        <v/>
+      </c>
+      <c r="AO19" t="n">
         <v>-16.79</v>
       </c>
-      <c r="D19" t="n">
+      <c r="AP19" t="n">
         <v>-11.34</v>
       </c>
-      <c r="E19" t="n">
+      <c r="AQ19" t="n">
         <v>4.21</v>
       </c>
-      <c r="F19" t="n">
+      <c r="AR19" t="n">
         <v>20.98</v>
       </c>
-      <c r="G19" t="n">
+      <c r="AS19" t="n">
         <v>49.61</v>
       </c>
-      <c r="H19" t="n">
+      <c r="AT19" t="n">
         <v>58.27</v>
       </c>
-      <c r="I19" t="n">
+      <c r="AU19" t="n">
         <v>62.91</v>
       </c>
-      <c r="J19" t="n">
+      <c r="AV19" t="n">
         <v>60.32</v>
       </c>
-      <c r="K19" t="n">
+      <c r="AW19" t="n">
         <v>55.12</v>
       </c>
-      <c r="L19" t="n">
+      <c r="AX19" t="n">
         <v>47.11</v>
       </c>
-      <c r="M19" t="n">
+      <c r="AY19" t="n">
         <v>67.45</v>
       </c>
-      <c r="N19" t="n">
+      <c r="AZ19" t="n">
         <v>81.08</v>
       </c>
-      <c r="O19" t="n">
+      <c r="BA19" t="n">
         <v>91.34</v>
       </c>
-      <c r="P19" t="n">
+      <c r="BB19" t="n">
         <v>98.43000000000001</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="BC19" t="n">
         <v>92.81</v>
       </c>
-      <c r="R19" t="n">
+      <c r="BD19" t="n">
         <v>81.83</v>
       </c>
-      <c r="S19" t="n">
+      <c r="BE19" t="n">
         <v>71.27</v>
       </c>
-      <c r="T19" t="n">
+      <c r="BF19" t="n">
         <v>55.65</v>
       </c>
-      <c r="U19" t="n">
+      <c r="BG19" t="n">
         <v>46.13</v>
       </c>
-      <c r="V19" t="n">
+      <c r="BH19" t="n">
         <v>34.92</v>
       </c>
-      <c r="W19" t="n">
+      <c r="BI19" t="n">
         <v>24.07</v>
       </c>
-      <c r="X19" t="n">
+      <c r="BJ19" t="n">
         <v>11.62</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="BK19" t="n">
         <v>7.63</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="BL19" t="n">
         <v>6.93</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="BM19" t="n">
         <v>7.44</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="BN19" t="n">
         <v>4.49</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="BO19" t="n">
         <v>0.12</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="BP19" t="n">
         <v>-11.05</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="BQ19" t="n">
         <v>-25.68</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="BR19" t="n">
         <v>-49.11</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="BS19" t="n">
         <v>-50.31</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="BT19" t="n">
         <v>-49.87</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="BU19" t="n">
         <v>-48.54</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="BV19" t="n">
         <v>-46.39</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="BW19" t="n">
         <v>-44.61</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="BX19" t="n">
         <v>-43.26</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="BY19" t="n">
         <v>-39.89</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="BZ19" t="n">
         <v>-38.07</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="CA19" t="n">
         <v>-38.15</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="CB19" t="n">
         <v>-43.21</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="CC19" t="n">
         <v>-40.5</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="CD19" t="n">
         <v>-39.13</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>-36.55</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>-39.13</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>-40.36</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>-40.09</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>-43.42</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>-32.04</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>-17.16</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -6905,7 +6905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK19"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6920,264 +6920,150 @@
         </is>
       </c>
       <c r="C1" t="n">
-        <v>20250829</v>
+        <v>20251029</v>
       </c>
       <c r="D1" t="n">
-        <v>20250901</v>
+        <v>20251030</v>
       </c>
       <c r="E1" t="n">
-        <v>20250902</v>
+        <v>20251031</v>
       </c>
       <c r="F1" t="n">
-        <v>20250903</v>
+        <v>20251103</v>
       </c>
       <c r="G1" t="n">
-        <v>20250904</v>
+        <v>20251104</v>
       </c>
       <c r="H1" t="n">
-        <v>20250905</v>
+        <v>20251105</v>
       </c>
       <c r="I1" t="n">
-        <v>20250908</v>
+        <v>20251106</v>
       </c>
       <c r="J1" t="n">
-        <v>20250909</v>
+        <v>20251107</v>
       </c>
       <c r="K1" t="n">
-        <v>20250910</v>
+        <v>20251110</v>
       </c>
       <c r="L1" t="n">
-        <v>20250911</v>
+        <v>20251111</v>
       </c>
       <c r="M1" t="n">
-        <v>20250912</v>
+        <v>20251112</v>
       </c>
       <c r="N1" t="n">
-        <v>20250915</v>
+        <v>20251113</v>
       </c>
       <c r="O1" t="n">
-        <v>20250916</v>
+        <v>20251114</v>
       </c>
       <c r="P1" t="n">
-        <v>20250917</v>
+        <v>20251117</v>
       </c>
       <c r="Q1" t="n">
-        <v>20250918</v>
+        <v>20251118</v>
       </c>
       <c r="R1" t="n">
-        <v>20250919</v>
+        <v>20251119</v>
       </c>
       <c r="S1" t="n">
-        <v>20250922</v>
+        <v>20251120</v>
       </c>
       <c r="T1" t="n">
-        <v>20250923</v>
+        <v>20251121</v>
       </c>
       <c r="U1" t="n">
-        <v>20250924</v>
+        <v>20251124</v>
       </c>
       <c r="V1" t="n">
-        <v>20250925</v>
+        <v>20251125</v>
       </c>
       <c r="W1" t="n">
-        <v>20250926</v>
+        <v>20251126</v>
       </c>
       <c r="X1" t="n">
-        <v>20250929</v>
+        <v>20251127</v>
       </c>
       <c r="Y1" t="n">
-        <v>20250930</v>
+        <v>20251128</v>
       </c>
       <c r="Z1" t="n">
-        <v>20251001</v>
+        <v>20251201</v>
       </c>
       <c r="AA1" t="n">
-        <v>20251002</v>
+        <v>20251202</v>
       </c>
       <c r="AB1" t="n">
-        <v>20251010</v>
+        <v>20251203</v>
       </c>
       <c r="AC1" t="n">
-        <v>20251013</v>
+        <v>20251204</v>
       </c>
       <c r="AD1" t="n">
-        <v>20251014</v>
+        <v>20251205</v>
       </c>
       <c r="AE1" t="n">
-        <v>20251015</v>
+        <v>20251208</v>
       </c>
       <c r="AF1" t="n">
-        <v>20251016</v>
+        <v>20251209</v>
       </c>
       <c r="AG1" t="n">
-        <v>20251017</v>
+        <v>20251210</v>
       </c>
       <c r="AH1" t="n">
-        <v>20251020</v>
+        <v>20251211</v>
       </c>
       <c r="AI1" t="n">
-        <v>20251021</v>
+        <v>20251212</v>
       </c>
       <c r="AJ1" t="n">
-        <v>20251022</v>
+        <v>20251215</v>
       </c>
       <c r="AK1" t="n">
-        <v>20251023</v>
+        <v>20251216</v>
       </c>
       <c r="AL1" t="n">
-        <v>20251024</v>
+        <v>20251217</v>
       </c>
       <c r="AM1" t="n">
-        <v>20251027</v>
+        <v>20251218</v>
       </c>
       <c r="AN1" t="n">
-        <v>20251028</v>
+        <v>20251219</v>
       </c>
       <c r="AO1" t="n">
-        <v>20251029</v>
+        <v>20251222</v>
       </c>
       <c r="AP1" t="n">
-        <v>20251030</v>
+        <v>20251223</v>
       </c>
       <c r="AQ1" t="n">
-        <v>20251031</v>
+        <v>20251224</v>
       </c>
       <c r="AR1" t="n">
-        <v>20251103</v>
+        <v>20251226</v>
       </c>
       <c r="AS1" t="n">
-        <v>20251104</v>
+        <v>20251229</v>
       </c>
       <c r="AT1" t="n">
-        <v>20251105</v>
+        <v>20251230</v>
       </c>
       <c r="AU1" t="n">
-        <v>20251106</v>
+        <v>20260102</v>
       </c>
       <c r="AV1" t="n">
-        <v>20251107</v>
+        <v>20260105</v>
       </c>
       <c r="AW1" t="n">
-        <v>20251110</v>
+        <v>20260106</v>
       </c>
       <c r="AX1" t="n">
-        <v>20251111</v>
+        <v>20260107</v>
       </c>
       <c r="AY1" t="n">
-        <v>20251112</v>
-      </c>
-      <c r="AZ1" t="n">
-        <v>20251113</v>
-      </c>
-      <c r="BA1" t="n">
-        <v>20251114</v>
-      </c>
-      <c r="BB1" t="n">
-        <v>20251117</v>
-      </c>
-      <c r="BC1" t="n">
-        <v>20251118</v>
-      </c>
-      <c r="BD1" t="n">
-        <v>20251119</v>
-      </c>
-      <c r="BE1" t="n">
-        <v>20251120</v>
-      </c>
-      <c r="BF1" t="n">
-        <v>20251121</v>
-      </c>
-      <c r="BG1" t="n">
-        <v>20251124</v>
-      </c>
-      <c r="BH1" t="n">
-        <v>20251125</v>
-      </c>
-      <c r="BI1" t="n">
-        <v>20251126</v>
-      </c>
-      <c r="BJ1" t="n">
-        <v>20251127</v>
-      </c>
-      <c r="BK1" t="n">
-        <v>20251128</v>
-      </c>
-      <c r="BL1" t="n">
-        <v>20251201</v>
-      </c>
-      <c r="BM1" t="n">
-        <v>20251202</v>
-      </c>
-      <c r="BN1" t="n">
-        <v>20251203</v>
-      </c>
-      <c r="BO1" t="n">
-        <v>20251204</v>
-      </c>
-      <c r="BP1" t="n">
-        <v>20251205</v>
-      </c>
-      <c r="BQ1" t="n">
-        <v>20251208</v>
-      </c>
-      <c r="BR1" t="n">
-        <v>20251209</v>
-      </c>
-      <c r="BS1" t="n">
-        <v>20251210</v>
-      </c>
-      <c r="BT1" t="n">
-        <v>20251211</v>
-      </c>
-      <c r="BU1" t="n">
-        <v>20251212</v>
-      </c>
-      <c r="BV1" t="n">
-        <v>20251215</v>
-      </c>
-      <c r="BW1" t="n">
-        <v>20251216</v>
-      </c>
-      <c r="BX1" t="n">
-        <v>20251217</v>
-      </c>
-      <c r="BY1" t="n">
-        <v>20251218</v>
-      </c>
-      <c r="BZ1" t="n">
-        <v>20251219</v>
-      </c>
-      <c r="CA1" t="n">
-        <v>20251222</v>
-      </c>
-      <c r="CB1" t="n">
-        <v>20251223</v>
-      </c>
-      <c r="CC1" t="n">
-        <v>20251224</v>
-      </c>
-      <c r="CD1" t="n">
-        <v>20251226</v>
-      </c>
-      <c r="CE1" t="n">
-        <v>20251229</v>
-      </c>
-      <c r="CF1" t="n">
-        <v>20251230</v>
-      </c>
-      <c r="CG1" t="n">
-        <v>20260102</v>
-      </c>
-      <c r="CH1" t="n">
-        <v>20260105</v>
-      </c>
-      <c r="CI1" t="n">
-        <v>20260106</v>
-      </c>
-      <c r="CJ1" t="n">
-        <v>20260107</v>
-      </c>
-      <c r="CK1" t="n">
         <v>20260108</v>
       </c>
     </row>
@@ -7193,264 +7079,150 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v/>
+        <v>19.02</v>
       </c>
       <c r="D2" t="n">
-        <v/>
+        <v>29.44</v>
       </c>
       <c r="E2" t="n">
-        <v/>
+        <v>49.8</v>
       </c>
       <c r="F2" t="n">
-        <v/>
+        <v>76.39</v>
       </c>
       <c r="G2" t="n">
-        <v/>
+        <v>103.88</v>
       </c>
       <c r="H2" t="n">
-        <v/>
+        <v>110.94</v>
       </c>
       <c r="I2" t="n">
-        <v/>
+        <v>108.63</v>
       </c>
       <c r="J2" t="n">
-        <v/>
+        <v>101.37</v>
       </c>
       <c r="K2" t="n">
-        <v/>
+        <v>91.86</v>
       </c>
       <c r="L2" t="n">
-        <v/>
+        <v>78.51000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v/>
+        <v>82.69</v>
       </c>
       <c r="N2" t="n">
-        <v/>
+        <v>85.18000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v/>
+        <v>84.73</v>
       </c>
       <c r="P2" t="n">
-        <v/>
+        <v>85.33</v>
       </c>
       <c r="Q2" t="n">
-        <v/>
+        <v>76.92</v>
       </c>
       <c r="R2" t="n">
-        <v/>
+        <v>64.34999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v/>
+        <v>52.56</v>
       </c>
       <c r="T2" t="n">
-        <v/>
+        <v>35.7</v>
       </c>
       <c r="U2" t="n">
-        <v/>
+        <v>26.99</v>
       </c>
       <c r="V2" t="n">
-        <v/>
+        <v>16.1</v>
       </c>
       <c r="W2" t="n">
-        <v/>
+        <v>5.08</v>
       </c>
       <c r="X2" t="n">
-        <v/>
+        <v>-7.58</v>
       </c>
       <c r="Y2" t="n">
-        <v/>
+        <v>-13.96</v>
       </c>
       <c r="Z2" t="n">
-        <v/>
+        <v>-17.27</v>
       </c>
       <c r="AA2" t="n">
-        <v/>
+        <v>-17.7</v>
       </c>
       <c r="AB2" t="n">
-        <v/>
+        <v>-20.12</v>
       </c>
       <c r="AC2" t="n">
-        <v/>
+        <v>-22.5</v>
       </c>
       <c r="AD2" t="n">
-        <v/>
+        <v>-31.48</v>
       </c>
       <c r="AE2" t="n">
-        <v/>
+        <v>-36.33</v>
       </c>
       <c r="AF2" t="n">
-        <v/>
+        <v>-46.6</v>
       </c>
       <c r="AG2" t="n">
-        <v/>
+        <v>-46.09</v>
       </c>
       <c r="AH2" t="n">
-        <v/>
+        <v>-43.49</v>
       </c>
       <c r="AI2" t="n">
-        <v/>
+        <v>-40.21</v>
       </c>
       <c r="AJ2" t="n">
-        <v/>
+        <v>-39.8</v>
       </c>
       <c r="AK2" t="n">
-        <v/>
+        <v>-35.6</v>
       </c>
       <c r="AL2" t="n">
-        <v/>
+        <v>-24</v>
       </c>
       <c r="AM2" t="n">
-        <v/>
+        <v>-16.57</v>
       </c>
       <c r="AN2" t="n">
-        <v/>
+        <v>-13.29</v>
       </c>
       <c r="AO2" t="n">
-        <v>19.02</v>
+        <v>-4.54</v>
       </c>
       <c r="AP2" t="n">
-        <v>29.44</v>
+        <v>8.25</v>
       </c>
       <c r="AQ2" t="n">
-        <v>49.8</v>
+        <v>13.94</v>
       </c>
       <c r="AR2" t="n">
-        <v>76.39</v>
+        <v>15.38</v>
       </c>
       <c r="AS2" t="n">
-        <v>103.88</v>
+        <v>12.92</v>
       </c>
       <c r="AT2" t="n">
-        <v>110.94</v>
+        <v>7.96</v>
       </c>
       <c r="AU2" t="n">
-        <v>108.63</v>
+        <v>1.42</v>
       </c>
       <c r="AV2" t="n">
-        <v>101.37</v>
+        <v>-4.02</v>
       </c>
       <c r="AW2" t="n">
-        <v>91.86</v>
+        <v>-20.76</v>
       </c>
       <c r="AX2" t="n">
-        <v>78.51000000000001</v>
+        <v>-15.66</v>
       </c>
       <c r="AY2" t="n">
-        <v>82.69</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>85.18000000000001</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>84.73</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>85.33</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>76.92</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>52.56</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>26.99</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>-7.58</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>-13.96</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>-17.27</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>-17.7</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>-20.12</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>-22.5</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>-31.48</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>-36.33</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>-46.6</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>-46.09</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>-43.49</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>-40.21</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>-39.8</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>-35.6</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>-24</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>-16.57</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>-13.29</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>-4.54</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>13.94</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>15.38</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>12.92</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>7.96</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>-4.02</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>-20.76</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>-15.66</v>
-      </c>
-      <c r="CK2" t="n">
         <v>-4.14</v>
       </c>
     </row>
@@ -7466,264 +7238,150 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v/>
+        <v>12.54</v>
       </c>
       <c r="D3" t="n">
-        <v/>
+        <v>12.33</v>
       </c>
       <c r="E3" t="n">
-        <v/>
+        <v>6.36</v>
       </c>
       <c r="F3" t="n">
-        <v/>
+        <v>4.42</v>
       </c>
       <c r="G3" t="n">
-        <v/>
+        <v>-3.97</v>
       </c>
       <c r="H3" t="n">
-        <v/>
+        <v>-15.64</v>
       </c>
       <c r="I3" t="n">
-        <v/>
+        <v>-22.29</v>
       </c>
       <c r="J3" t="n">
-        <v/>
+        <v>-25.49</v>
       </c>
       <c r="K3" t="n">
-        <v/>
+        <v>-27.73</v>
       </c>
       <c r="L3" t="n">
-        <v/>
+        <v>-34.44</v>
       </c>
       <c r="M3" t="n">
-        <v/>
+        <v>-37.09</v>
       </c>
       <c r="N3" t="n">
-        <v/>
+        <v>-38.43</v>
       </c>
       <c r="O3" t="n">
-        <v/>
+        <v>-41.51</v>
       </c>
       <c r="P3" t="n">
-        <v/>
+        <v>-42.5</v>
       </c>
       <c r="Q3" t="n">
-        <v/>
+        <v>-44.24</v>
       </c>
       <c r="R3" t="n">
-        <v/>
+        <v>-42.68</v>
       </c>
       <c r="S3" t="n">
-        <v/>
+        <v>-44.94</v>
       </c>
       <c r="T3" t="n">
-        <v/>
+        <v>-28.38</v>
       </c>
       <c r="U3" t="n">
-        <v/>
+        <v>-15.66</v>
       </c>
       <c r="V3" t="n">
-        <v/>
+        <v>-7.66</v>
       </c>
       <c r="W3" t="n">
-        <v/>
+        <v>-2.01</v>
       </c>
       <c r="X3" t="n">
-        <v/>
+        <v>1.52</v>
       </c>
       <c r="Y3" t="n">
-        <v/>
+        <v>4.23</v>
       </c>
       <c r="Z3" t="n">
-        <v/>
+        <v>0.06</v>
       </c>
       <c r="AA3" t="n">
-        <v/>
+        <v>-2.67</v>
       </c>
       <c r="AB3" t="n">
-        <v/>
+        <v>-1.53</v>
       </c>
       <c r="AC3" t="n">
-        <v/>
+        <v>-2.97</v>
       </c>
       <c r="AD3" t="n">
-        <v/>
+        <v>-1.76</v>
       </c>
       <c r="AE3" t="n">
-        <v/>
+        <v>-1.88</v>
       </c>
       <c r="AF3" t="n">
-        <v/>
+        <v>-7.09</v>
       </c>
       <c r="AG3" t="n">
-        <v/>
+        <v>-11.87</v>
       </c>
       <c r="AH3" t="n">
-        <v/>
+        <v>-17.88</v>
       </c>
       <c r="AI3" t="n">
-        <v/>
+        <v>-16.48</v>
       </c>
       <c r="AJ3" t="n">
-        <v/>
+        <v>-20.83</v>
       </c>
       <c r="AK3" t="n">
-        <v/>
+        <v>-18.19</v>
       </c>
       <c r="AL3" t="n">
-        <v/>
+        <v>-18.63</v>
       </c>
       <c r="AM3" t="n">
-        <v/>
+        <v>-18.71</v>
       </c>
       <c r="AN3" t="n">
-        <v/>
+        <v>-28.38</v>
       </c>
       <c r="AO3" t="n">
-        <v>12.54</v>
+        <v>-34.91</v>
       </c>
       <c r="AP3" t="n">
-        <v>12.33</v>
+        <v>-37.91</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.36</v>
+        <v>-38.81</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.42</v>
+        <v>-30.02</v>
       </c>
       <c r="AS3" t="n">
-        <v>-3.97</v>
+        <v>-15.82</v>
       </c>
       <c r="AT3" t="n">
-        <v>-15.64</v>
+        <v>-0.95</v>
       </c>
       <c r="AU3" t="n">
-        <v>-22.29</v>
+        <v>41.82</v>
       </c>
       <c r="AV3" t="n">
-        <v>-25.49</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>-27.73</v>
+        <v>127.96</v>
       </c>
       <c r="AX3" t="n">
-        <v>-34.44</v>
+        <v>142.78</v>
       </c>
       <c r="AY3" t="n">
-        <v>-37.09</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-38.43</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>-41.51</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>-42.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>-44.24</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>-42.68</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>-44.94</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>-28.38</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>-15.66</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>-7.66</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>-2.01</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>-2.67</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>-1.53</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>-2.97</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>-1.76</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>-1.88</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>-7.09</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>-11.87</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>-17.88</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>-16.48</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>-20.83</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>-18.19</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>-18.63</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>-18.71</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>-28.38</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>-34.91</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>-37.91</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>-38.81</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>-30.02</v>
-      </c>
-      <c r="CE3" t="n">
-        <v>-15.82</v>
-      </c>
-      <c r="CF3" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="CG3" t="n">
-        <v>41.82</v>
-      </c>
-      <c r="CH3" t="n">
-        <v>90.51000000000001</v>
-      </c>
-      <c r="CI3" t="n">
-        <v>127.96</v>
-      </c>
-      <c r="CJ3" t="n">
-        <v>142.78</v>
-      </c>
-      <c r="CK3" t="n">
         <v>146.46</v>
       </c>
     </row>
@@ -7739,264 +7397,150 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v/>
+        <v>-22.69</v>
       </c>
       <c r="D4" t="n">
-        <v/>
+        <v>-19.19</v>
       </c>
       <c r="E4" t="n">
-        <v/>
+        <v>-9.529999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v/>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v/>
+        <v>32.42</v>
       </c>
       <c r="H4" t="n">
-        <v/>
+        <v>40.77</v>
       </c>
       <c r="I4" t="n">
-        <v/>
+        <v>43.76</v>
       </c>
       <c r="J4" t="n">
-        <v/>
+        <v>42.59</v>
       </c>
       <c r="K4" t="n">
-        <v/>
+        <v>40.42</v>
       </c>
       <c r="L4" t="n">
-        <v/>
+        <v>34.22</v>
       </c>
       <c r="M4" t="n">
-        <v/>
+        <v>45.83</v>
       </c>
       <c r="N4" t="n">
-        <v/>
+        <v>54.72</v>
       </c>
       <c r="O4" t="n">
-        <v/>
+        <v>56.7</v>
       </c>
       <c r="P4" t="n">
-        <v/>
+        <v>61.21</v>
       </c>
       <c r="Q4" t="n">
-        <v/>
+        <v>58.28</v>
       </c>
       <c r="R4" t="n">
-        <v/>
+        <v>49.77</v>
       </c>
       <c r="S4" t="n">
-        <v/>
+        <v>46.67</v>
       </c>
       <c r="T4" t="n">
-        <v/>
+        <v>34.81</v>
       </c>
       <c r="U4" t="n">
-        <v/>
+        <v>26.36</v>
       </c>
       <c r="V4" t="n">
-        <v/>
+        <v>16.79</v>
       </c>
       <c r="W4" t="n">
-        <v/>
+        <v>6.38</v>
       </c>
       <c r="X4" t="n">
-        <v/>
+        <v>-5.19</v>
       </c>
       <c r="Y4" t="n">
-        <v/>
+        <v>-6.86</v>
       </c>
       <c r="Z4" t="n">
-        <v/>
+        <v>-8.48</v>
       </c>
       <c r="AA4" t="n">
-        <v/>
+        <v>-6.47</v>
       </c>
       <c r="AB4" t="n">
-        <v/>
+        <v>-8.57</v>
       </c>
       <c r="AC4" t="n">
-        <v/>
+        <v>-12.71</v>
       </c>
       <c r="AD4" t="n">
-        <v/>
+        <v>-21.12</v>
       </c>
       <c r="AE4" t="n">
-        <v/>
+        <v>-28.52</v>
       </c>
       <c r="AF4" t="n">
-        <v/>
+        <v>-43.96</v>
       </c>
       <c r="AG4" t="n">
-        <v/>
+        <v>-42.86</v>
       </c>
       <c r="AH4" t="n">
-        <v/>
+        <v>-40.58</v>
       </c>
       <c r="AI4" t="n">
-        <v/>
+        <v>-34.52</v>
       </c>
       <c r="AJ4" t="n">
-        <v/>
+        <v>-30.2</v>
       </c>
       <c r="AK4" t="n">
-        <v/>
+        <v>-25.06</v>
       </c>
       <c r="AL4" t="n">
-        <v/>
+        <v>-15.2</v>
       </c>
       <c r="AM4" t="n">
-        <v/>
+        <v>-11.07</v>
       </c>
       <c r="AN4" t="n">
-        <v/>
+        <v>-9.17</v>
       </c>
       <c r="AO4" t="n">
-        <v>-22.69</v>
+        <v>-3.83</v>
       </c>
       <c r="AP4" t="n">
-        <v>-19.19</v>
+        <v>3.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-9.529999999999999</v>
+        <v>10.09</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.4</v>
+        <v>12.89</v>
       </c>
       <c r="AS4" t="n">
-        <v>32.42</v>
+        <v>4.39</v>
       </c>
       <c r="AT4" t="n">
-        <v>40.77</v>
+        <v>-5.51</v>
       </c>
       <c r="AU4" t="n">
-        <v>43.76</v>
+        <v>-15.74</v>
       </c>
       <c r="AV4" t="n">
-        <v>42.59</v>
+        <v>-19.72</v>
       </c>
       <c r="AW4" t="n">
-        <v>40.42</v>
+        <v>-25.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>34.22</v>
+        <v>-20.78</v>
       </c>
       <c r="AY4" t="n">
-        <v>45.83</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>54.72</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>61.21</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>58.28</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>49.77</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>46.67</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>34.81</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>26.36</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>16.79</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>-5.19</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>-6.86</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>-8.48</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>-6.47</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>-8.57</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>-12.71</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>-21.12</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>-28.52</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>-43.96</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>-42.86</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>-40.58</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>-34.52</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>-30.2</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>-25.06</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>-15.2</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>-11.07</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>-9.17</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>-3.83</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="CC4" t="n">
-        <v>10.09</v>
-      </c>
-      <c r="CD4" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="CE4" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="CF4" t="n">
-        <v>-5.51</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>-15.74</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>-19.72</v>
-      </c>
-      <c r="CI4" t="n">
-        <v>-25.01</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>-20.78</v>
-      </c>
-      <c r="CK4" t="n">
         <v>-11.27</v>
       </c>
     </row>
@@ -8012,264 +7556,150 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v/>
+        <v>6.36</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>5.42</v>
       </c>
       <c r="E5" t="n">
-        <v/>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v/>
+        <v>-5.87</v>
       </c>
       <c r="G5" t="n">
-        <v/>
+        <v>-15.54</v>
       </c>
       <c r="H5" t="n">
-        <v/>
+        <v>-28.05</v>
       </c>
       <c r="I5" t="n">
-        <v/>
+        <v>-37.83</v>
       </c>
       <c r="J5" t="n">
-        <v/>
+        <v>-41.25</v>
       </c>
       <c r="K5" t="n">
-        <v/>
+        <v>-42.96</v>
       </c>
       <c r="L5" t="n">
-        <v/>
+        <v>-50.72</v>
       </c>
       <c r="M5" t="n">
-        <v/>
+        <v>-51.56</v>
       </c>
       <c r="N5" t="n">
-        <v/>
+        <v>-51.2</v>
       </c>
       <c r="O5" t="n">
-        <v/>
+        <v>-49.64</v>
       </c>
       <c r="P5" t="n">
-        <v/>
+        <v>-48.43</v>
       </c>
       <c r="Q5" t="n">
-        <v/>
+        <v>-48.13</v>
       </c>
       <c r="R5" t="n">
-        <v/>
+        <v>-44.93</v>
       </c>
       <c r="S5" t="n">
-        <v/>
+        <v>-42.46</v>
       </c>
       <c r="T5" t="n">
-        <v/>
+        <v>-20.58</v>
       </c>
       <c r="U5" t="n">
-        <v/>
+        <v>-5.57</v>
       </c>
       <c r="V5" t="n">
-        <v/>
+        <v>1.2</v>
       </c>
       <c r="W5" t="n">
-        <v/>
+        <v>5.26</v>
       </c>
       <c r="X5" t="n">
-        <v/>
+        <v>7.36</v>
       </c>
       <c r="Y5" t="n">
-        <v/>
+        <v>7.34</v>
       </c>
       <c r="Z5" t="n">
-        <v/>
+        <v>3.63</v>
       </c>
       <c r="AA5" t="n">
-        <v/>
+        <v>-2.13</v>
       </c>
       <c r="AB5" t="n">
-        <v/>
+        <v>-1.1</v>
       </c>
       <c r="AC5" t="n">
-        <v/>
+        <v>-2.92</v>
       </c>
       <c r="AD5" t="n">
-        <v/>
+        <v>-2.02</v>
       </c>
       <c r="AE5" t="n">
-        <v/>
+        <v>-2.87</v>
       </c>
       <c r="AF5" t="n">
-        <v/>
+        <v>-7.96</v>
       </c>
       <c r="AG5" t="n">
-        <v/>
+        <v>-15.64</v>
       </c>
       <c r="AH5" t="n">
-        <v/>
+        <v>-23.13</v>
       </c>
       <c r="AI5" t="n">
-        <v/>
+        <v>-22.99</v>
       </c>
       <c r="AJ5" t="n">
-        <v/>
+        <v>-27.09</v>
       </c>
       <c r="AK5" t="n">
-        <v/>
+        <v>-13.26</v>
       </c>
       <c r="AL5" t="n">
-        <v/>
+        <v>-12.34</v>
       </c>
       <c r="AM5" t="n">
-        <v/>
+        <v>-10.3</v>
       </c>
       <c r="AN5" t="n">
-        <v/>
+        <v>-10.18</v>
       </c>
       <c r="AO5" t="n">
-        <v>6.36</v>
+        <v>-13.27</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.42</v>
+        <v>-10.89</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-8.33</v>
       </c>
       <c r="AR5" t="n">
-        <v>-5.87</v>
+        <v>-7.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>-15.54</v>
+        <v>-3.45</v>
       </c>
       <c r="AT5" t="n">
-        <v>-28.05</v>
+        <v>0.95</v>
       </c>
       <c r="AU5" t="n">
-        <v>-37.83</v>
+        <v>22.29</v>
       </c>
       <c r="AV5" t="n">
-        <v>-41.25</v>
+        <v>45.64</v>
       </c>
       <c r="AW5" t="n">
-        <v>-42.96</v>
+        <v>65.53</v>
       </c>
       <c r="AX5" t="n">
-        <v>-50.72</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="AY5" t="n">
-        <v>-51.56</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-51.2</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>-49.64</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>-48.43</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>-48.13</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>-44.93</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>-42.46</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>-20.58</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>-5.57</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>7.36</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>-2.92</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>-2.02</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>-2.87</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>-7.96</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>-15.64</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>-23.13</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>-22.99</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>-27.09</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>-13.26</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>-12.34</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>-10.3</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>-10.18</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>-13.27</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>-10.89</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>-8.33</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>-7.01</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>-3.45</v>
-      </c>
-      <c r="CF5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>45.64</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>65.53</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>72.98999999999999</v>
-      </c>
-      <c r="CK5" t="n">
         <v>72.95999999999999</v>
       </c>
     </row>
@@ -8285,264 +7715,150 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v/>
+        <v>22.88</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>23.33</v>
       </c>
       <c r="E6" t="n">
-        <v/>
+        <v>18.19</v>
       </c>
       <c r="F6" t="n">
-        <v/>
+        <v>16.9</v>
       </c>
       <c r="G6" t="n">
-        <v/>
+        <v>7.93</v>
       </c>
       <c r="H6" t="n">
-        <v/>
+        <v>-4.84</v>
       </c>
       <c r="I6" t="n">
-        <v/>
+        <v>-12.88</v>
       </c>
       <c r="J6" t="n">
-        <v/>
+        <v>-17.12</v>
       </c>
       <c r="K6" t="n">
-        <v/>
+        <v>-20.39</v>
       </c>
       <c r="L6" t="n">
-        <v/>
+        <v>-27.1</v>
       </c>
       <c r="M6" t="n">
-        <v/>
+        <v>-30.38</v>
       </c>
       <c r="N6" t="n">
-        <v/>
+        <v>-32.15</v>
       </c>
       <c r="O6" t="n">
-        <v/>
+        <v>-35.9</v>
       </c>
       <c r="P6" t="n">
-        <v/>
+        <v>-36.58</v>
       </c>
       <c r="Q6" t="n">
-        <v/>
+        <v>-40.83</v>
       </c>
       <c r="R6" t="n">
-        <v/>
+        <v>-43.52</v>
       </c>
       <c r="S6" t="n">
-        <v/>
+        <v>-50.45</v>
       </c>
       <c r="T6" t="n">
-        <v/>
+        <v>-41.58</v>
       </c>
       <c r="U6" t="n">
-        <v/>
+        <v>-32.82</v>
       </c>
       <c r="V6" t="n">
-        <v/>
+        <v>-29.85</v>
       </c>
       <c r="W6" t="n">
-        <v/>
+        <v>-26.52</v>
       </c>
       <c r="X6" t="n">
-        <v/>
+        <v>-23.5</v>
       </c>
       <c r="Y6" t="n">
-        <v/>
+        <v>-20.9</v>
       </c>
       <c r="Z6" t="n">
-        <v/>
+        <v>-24.55</v>
       </c>
       <c r="AA6" t="n">
-        <v/>
+        <v>-23.91</v>
       </c>
       <c r="AB6" t="n">
-        <v/>
+        <v>-20.26</v>
       </c>
       <c r="AC6" t="n">
-        <v/>
+        <v>-17.86</v>
       </c>
       <c r="AD6" t="n">
-        <v/>
+        <v>-15.44</v>
       </c>
       <c r="AE6" t="n">
-        <v/>
+        <v>-11.06</v>
       </c>
       <c r="AF6" t="n">
-        <v/>
+        <v>-10.4</v>
       </c>
       <c r="AG6" t="n">
-        <v/>
+        <v>-8.91</v>
       </c>
       <c r="AH6" t="n">
-        <v/>
+        <v>-8.470000000000001</v>
       </c>
       <c r="AI6" t="n">
-        <v/>
+        <v>-7.11</v>
       </c>
       <c r="AJ6" t="n">
-        <v/>
+        <v>-9.34</v>
       </c>
       <c r="AK6" t="n">
-        <v/>
+        <v>-5.34</v>
       </c>
       <c r="AL6" t="n">
-        <v/>
+        <v>-6.34</v>
       </c>
       <c r="AM6" t="n">
-        <v/>
+        <v>-5.76</v>
       </c>
       <c r="AN6" t="n">
-        <v/>
+        <v>-17.16</v>
       </c>
       <c r="AO6" t="n">
-        <v>22.88</v>
+        <v>-28.29</v>
       </c>
       <c r="AP6" t="n">
-        <v>23.33</v>
+        <v>-30.63</v>
       </c>
       <c r="AQ6" t="n">
-        <v>18.19</v>
+        <v>-29.97</v>
       </c>
       <c r="AR6" t="n">
-        <v>16.9</v>
+        <v>-22.11</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.93</v>
+        <v>-9.66</v>
       </c>
       <c r="AT6" t="n">
-        <v>-4.84</v>
+        <v>2.39</v>
       </c>
       <c r="AU6" t="n">
-        <v>-12.88</v>
+        <v>40.41</v>
       </c>
       <c r="AV6" t="n">
-        <v>-17.12</v>
+        <v>83.72</v>
       </c>
       <c r="AW6" t="n">
-        <v>-20.39</v>
+        <v>114.74</v>
       </c>
       <c r="AX6" t="n">
-        <v>-27.1</v>
+        <v>127.29</v>
       </c>
       <c r="AY6" t="n">
-        <v>-30.38</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-32.15</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>-35.9</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>-36.58</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>-40.83</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>-43.52</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>-50.45</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>-41.58</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>-32.82</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>-29.85</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>-26.52</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>-23.5</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>-20.9</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>-24.55</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>-23.91</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>-20.26</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>-17.86</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>-15.44</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>-11.06</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>-10.4</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>-8.91</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>-8.470000000000001</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>-7.11</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>-9.34</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>-5.34</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>-6.34</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>-5.76</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>-17.16</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>-28.29</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>-30.63</v>
-      </c>
-      <c r="CC6" t="n">
-        <v>-29.97</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>-22.11</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>-9.66</v>
-      </c>
-      <c r="CF6" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="CG6" t="n">
-        <v>40.41</v>
-      </c>
-      <c r="CH6" t="n">
-        <v>83.72</v>
-      </c>
-      <c r="CI6" t="n">
-        <v>114.74</v>
-      </c>
-      <c r="CJ6" t="n">
-        <v>127.29</v>
-      </c>
-      <c r="CK6" t="n">
         <v>130.33</v>
       </c>
     </row>
@@ -8558,264 +7874,150 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v/>
+        <v>21.85</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>21.69</v>
       </c>
       <c r="E7" t="n">
-        <v/>
+        <v>16.72</v>
       </c>
       <c r="F7" t="n">
-        <v/>
+        <v>16.21</v>
       </c>
       <c r="G7" t="n">
-        <v/>
+        <v>7.89</v>
       </c>
       <c r="H7" t="n">
-        <v/>
+        <v>-4.65</v>
       </c>
       <c r="I7" t="n">
-        <v/>
+        <v>-12.9</v>
       </c>
       <c r="J7" t="n">
-        <v/>
+        <v>-16.66</v>
       </c>
       <c r="K7" t="n">
-        <v/>
+        <v>-20.47</v>
       </c>
       <c r="L7" t="n">
-        <v/>
+        <v>-27.13</v>
       </c>
       <c r="M7" t="n">
-        <v/>
+        <v>-32.33</v>
       </c>
       <c r="N7" t="n">
-        <v/>
+        <v>-35.07</v>
       </c>
       <c r="O7" t="n">
-        <v/>
+        <v>-38.81</v>
       </c>
       <c r="P7" t="n">
-        <v/>
+        <v>-40.96</v>
       </c>
       <c r="Q7" t="n">
-        <v/>
+        <v>-42.68</v>
       </c>
       <c r="R7" t="n">
-        <v/>
+        <v>-43.74</v>
       </c>
       <c r="S7" t="n">
-        <v/>
+        <v>-47.12</v>
       </c>
       <c r="T7" t="n">
-        <v/>
+        <v>-37.6</v>
       </c>
       <c r="U7" t="n">
-        <v/>
+        <v>-30</v>
       </c>
       <c r="V7" t="n">
-        <v/>
+        <v>-26.22</v>
       </c>
       <c r="W7" t="n">
-        <v/>
+        <v>-23.23</v>
       </c>
       <c r="X7" t="n">
-        <v/>
+        <v>-20.18</v>
       </c>
       <c r="Y7" t="n">
-        <v/>
+        <v>-18.12</v>
       </c>
       <c r="Z7" t="n">
-        <v/>
+        <v>-23.13</v>
       </c>
       <c r="AA7" t="n">
-        <v/>
+        <v>-23.19</v>
       </c>
       <c r="AB7" t="n">
-        <v/>
+        <v>-18.18</v>
       </c>
       <c r="AC7" t="n">
-        <v/>
+        <v>-15.42</v>
       </c>
       <c r="AD7" t="n">
-        <v/>
+        <v>-11.02</v>
       </c>
       <c r="AE7" t="n">
-        <v/>
+        <v>-4.77</v>
       </c>
       <c r="AF7" t="n">
-        <v/>
+        <v>-2.41</v>
       </c>
       <c r="AG7" t="n">
-        <v/>
+        <v>1.72</v>
       </c>
       <c r="AH7" t="n">
-        <v/>
+        <v>3.3</v>
       </c>
       <c r="AI7" t="n">
-        <v/>
+        <v>5.44</v>
       </c>
       <c r="AJ7" t="n">
-        <v/>
+        <v>5.55</v>
       </c>
       <c r="AK7" t="n">
-        <v/>
+        <v>3.02</v>
       </c>
       <c r="AL7" t="n">
-        <v/>
+        <v>-1.04</v>
       </c>
       <c r="AM7" t="n">
-        <v/>
+        <v>-2.99</v>
       </c>
       <c r="AN7" t="n">
-        <v/>
+        <v>-19.55</v>
       </c>
       <c r="AO7" t="n">
-        <v>21.85</v>
+        <v>-32.44</v>
       </c>
       <c r="AP7" t="n">
-        <v>21.69</v>
+        <v>-39.7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16.72</v>
+        <v>-39.15</v>
       </c>
       <c r="AR7" t="n">
-        <v>16.21</v>
+        <v>-29.72</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.89</v>
+        <v>-15.77</v>
       </c>
       <c r="AT7" t="n">
-        <v>-4.65</v>
+        <v>-2.86</v>
       </c>
       <c r="AU7" t="n">
-        <v>-12.9</v>
+        <v>37.86</v>
       </c>
       <c r="AV7" t="n">
-        <v>-16.66</v>
+        <v>81.38</v>
       </c>
       <c r="AW7" t="n">
-        <v>-20.47</v>
+        <v>111.74</v>
       </c>
       <c r="AX7" t="n">
-        <v>-27.13</v>
+        <v>126.85</v>
       </c>
       <c r="AY7" t="n">
-        <v>-32.33</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-35.07</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>-38.81</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>-40.96</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>-42.68</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>-43.74</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>-47.12</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>-37.6</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>-30</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>-26.22</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>-23.23</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>-20.18</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>-18.12</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>-23.13</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>-23.19</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>-18.18</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>-15.42</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>-11.02</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>-4.77</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>-2.41</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>-2.99</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>-19.55</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>-32.44</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>-39.7</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>-39.15</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>-29.72</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>-15.77</v>
-      </c>
-      <c r="CF7" t="n">
-        <v>-2.86</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>37.86</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>81.38</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>111.74</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>126.85</v>
-      </c>
-      <c r="CK7" t="n">
         <v>132.93</v>
       </c>
     </row>
@@ -8831,264 +8033,150 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v/>
+        <v>17.93</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>16.83</v>
       </c>
       <c r="E8" t="n">
-        <v/>
+        <v>9.75</v>
       </c>
       <c r="F8" t="n">
-        <v/>
+        <v>5.54</v>
       </c>
       <c r="G8" t="n">
-        <v/>
+        <v>-3.84</v>
       </c>
       <c r="H8" t="n">
-        <v/>
+        <v>-18.19</v>
       </c>
       <c r="I8" t="n">
-        <v/>
+        <v>-28.94</v>
       </c>
       <c r="J8" t="n">
-        <v/>
+        <v>-33.29</v>
       </c>
       <c r="K8" t="n">
-        <v/>
+        <v>-36.34</v>
       </c>
       <c r="L8" t="n">
-        <v/>
+        <v>-42.37</v>
       </c>
       <c r="M8" t="n">
-        <v/>
+        <v>-44.78</v>
       </c>
       <c r="N8" t="n">
-        <v/>
+        <v>-44.77</v>
       </c>
       <c r="O8" t="n">
-        <v/>
+        <v>-47.2</v>
       </c>
       <c r="P8" t="n">
-        <v/>
+        <v>-47.39</v>
       </c>
       <c r="Q8" t="n">
-        <v/>
+        <v>-48.46</v>
       </c>
       <c r="R8" t="n">
-        <v/>
+        <v>-46.83</v>
       </c>
       <c r="S8" t="n">
-        <v/>
+        <v>-48.91</v>
       </c>
       <c r="T8" t="n">
-        <v/>
+        <v>-34.53</v>
       </c>
       <c r="U8" t="n">
-        <v/>
+        <v>-21.49</v>
       </c>
       <c r="V8" t="n">
-        <v/>
+        <v>-13.9</v>
       </c>
       <c r="W8" t="n">
-        <v/>
+        <v>-8.869999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v/>
+        <v>-4.95</v>
       </c>
       <c r="Y8" t="n">
-        <v/>
+        <v>-1.35</v>
       </c>
       <c r="Z8" t="n">
-        <v/>
+        <v>-3.89</v>
       </c>
       <c r="AA8" t="n">
-        <v/>
+        <v>-5.19</v>
       </c>
       <c r="AB8" t="n">
-        <v/>
+        <v>-2.86</v>
       </c>
       <c r="AC8" t="n">
-        <v/>
+        <v>-2.07</v>
       </c>
       <c r="AD8" t="n">
-        <v/>
+        <v>-0.68</v>
       </c>
       <c r="AE8" t="n">
-        <v/>
+        <v>-0.04</v>
       </c>
       <c r="AF8" t="n">
-        <v/>
+        <v>-4.54</v>
       </c>
       <c r="AG8" t="n">
-        <v/>
+        <v>-8.48</v>
       </c>
       <c r="AH8" t="n">
-        <v/>
+        <v>-15.14</v>
       </c>
       <c r="AI8" t="n">
-        <v/>
+        <v>-12.85</v>
       </c>
       <c r="AJ8" t="n">
-        <v/>
+        <v>-17.08</v>
       </c>
       <c r="AK8" t="n">
-        <v/>
+        <v>-14.84</v>
       </c>
       <c r="AL8" t="n">
-        <v/>
+        <v>-15.5</v>
       </c>
       <c r="AM8" t="n">
-        <v/>
+        <v>-15.76</v>
       </c>
       <c r="AN8" t="n">
-        <v/>
+        <v>-26</v>
       </c>
       <c r="AO8" t="n">
-        <v>17.93</v>
+        <v>-34.24</v>
       </c>
       <c r="AP8" t="n">
-        <v>16.83</v>
+        <v>-36.3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.75</v>
+        <v>-33.31</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.54</v>
+        <v>-21.24</v>
       </c>
       <c r="AS8" t="n">
-        <v>-3.84</v>
+        <v>-2.04</v>
       </c>
       <c r="AT8" t="n">
-        <v>-18.19</v>
+        <v>15.48</v>
       </c>
       <c r="AU8" t="n">
-        <v>-28.94</v>
+        <v>62.65</v>
       </c>
       <c r="AV8" t="n">
-        <v>-33.29</v>
+        <v>114.46</v>
       </c>
       <c r="AW8" t="n">
-        <v>-36.34</v>
+        <v>151.15</v>
       </c>
       <c r="AX8" t="n">
-        <v>-42.37</v>
+        <v>164.61</v>
       </c>
       <c r="AY8" t="n">
-        <v>-44.78</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>-44.77</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>-47.2</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>-47.39</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>-48.46</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>-46.83</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>-48.91</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>-34.53</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>-21.49</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>-13.9</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>-8.869999999999999</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>-4.95</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>-1.35</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>-3.89</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>-5.19</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>-2.86</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>-2.07</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>-0.68</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>-4.54</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>-8.48</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>-15.14</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>-12.85</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>-17.08</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>-14.84</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>-15.5</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>-15.76</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>-26</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>-34.24</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>-36.3</v>
-      </c>
-      <c r="CC8" t="n">
-        <v>-33.31</v>
-      </c>
-      <c r="CD8" t="n">
-        <v>-21.24</v>
-      </c>
-      <c r="CE8" t="n">
-        <v>-2.04</v>
-      </c>
-      <c r="CF8" t="n">
-        <v>15.48</v>
-      </c>
-      <c r="CG8" t="n">
-        <v>62.65</v>
-      </c>
-      <c r="CH8" t="n">
-        <v>114.46</v>
-      </c>
-      <c r="CI8" t="n">
-        <v>151.15</v>
-      </c>
-      <c r="CJ8" t="n">
-        <v>164.61</v>
-      </c>
-      <c r="CK8" t="n">
         <v>166.2</v>
       </c>
     </row>
@@ -9104,264 +8192,150 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v/>
+        <v>193.55</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>163.86</v>
       </c>
       <c r="E9" t="n">
-        <v/>
+        <v>132.58</v>
       </c>
       <c r="F9" t="n">
-        <v/>
+        <v>106.56</v>
       </c>
       <c r="G9" t="n">
-        <v/>
+        <v>82.78</v>
       </c>
       <c r="H9" t="n">
-        <v/>
+        <v>59.41</v>
       </c>
       <c r="I9" t="n">
-        <v/>
+        <v>40.06</v>
       </c>
       <c r="J9" t="n">
-        <v/>
+        <v>19.26</v>
       </c>
       <c r="K9" t="n">
-        <v/>
+        <v>0.01</v>
       </c>
       <c r="L9" t="n">
-        <v/>
+        <v>-15.64</v>
       </c>
       <c r="M9" t="n">
-        <v/>
+        <v>-32.24</v>
       </c>
       <c r="N9" t="n">
-        <v/>
+        <v>-41.13</v>
       </c>
       <c r="O9" t="n">
-        <v/>
+        <v>-46.93</v>
       </c>
       <c r="P9" t="n">
-        <v/>
+        <v>-51.98</v>
       </c>
       <c r="Q9" t="n">
-        <v/>
+        <v>-52.85</v>
       </c>
       <c r="R9" t="n">
-        <v/>
+        <v>-49.3</v>
       </c>
       <c r="S9" t="n">
-        <v/>
+        <v>-48.17</v>
       </c>
       <c r="T9" t="n">
-        <v/>
+        <v>-41.62</v>
       </c>
       <c r="U9" t="n">
-        <v/>
+        <v>-33.41</v>
       </c>
       <c r="V9" t="n">
-        <v/>
+        <v>-29.18</v>
       </c>
       <c r="W9" t="n">
-        <v/>
+        <v>-34.67</v>
       </c>
       <c r="X9" t="n">
-        <v/>
+        <v>-34.5</v>
       </c>
       <c r="Y9" t="n">
-        <v/>
+        <v>-30.15</v>
       </c>
       <c r="Z9" t="n">
-        <v/>
+        <v>-27.17</v>
       </c>
       <c r="AA9" t="n">
-        <v/>
+        <v>-25.33</v>
       </c>
       <c r="AB9" t="n">
-        <v/>
+        <v>-21.13</v>
       </c>
       <c r="AC9" t="n">
-        <v/>
+        <v>-16.89</v>
       </c>
       <c r="AD9" t="n">
-        <v/>
+        <v>-12.61</v>
       </c>
       <c r="AE9" t="n">
-        <v/>
+        <v>-9.279999999999999</v>
       </c>
       <c r="AF9" t="n">
-        <v/>
+        <v>-8.18</v>
       </c>
       <c r="AG9" t="n">
-        <v/>
+        <v>-12.9</v>
       </c>
       <c r="AH9" t="n">
-        <v/>
+        <v>-28.81</v>
       </c>
       <c r="AI9" t="n">
-        <v/>
+        <v>-31.82</v>
       </c>
       <c r="AJ9" t="n">
-        <v/>
+        <v>-35.54</v>
       </c>
       <c r="AK9" t="n">
-        <v/>
+        <v>-32.98</v>
       </c>
       <c r="AL9" t="n">
-        <v/>
+        <v>-30.97</v>
       </c>
       <c r="AM9" t="n">
-        <v/>
+        <v>-19.15</v>
       </c>
       <c r="AN9" t="n">
-        <v/>
+        <v>-8.42</v>
       </c>
       <c r="AO9" t="n">
-        <v>193.55</v>
+        <v>-3.96</v>
       </c>
       <c r="AP9" t="n">
-        <v>163.86</v>
+        <v>1.29</v>
       </c>
       <c r="AQ9" t="n">
-        <v>132.58</v>
+        <v>5.98</v>
       </c>
       <c r="AR9" t="n">
-        <v>106.56</v>
+        <v>12.29</v>
       </c>
       <c r="AS9" t="n">
-        <v>82.78</v>
+        <v>18.59</v>
       </c>
       <c r="AT9" t="n">
-        <v>59.41</v>
+        <v>27.92</v>
       </c>
       <c r="AU9" t="n">
-        <v>40.06</v>
+        <v>37.95</v>
       </c>
       <c r="AV9" t="n">
-        <v>19.26</v>
+        <v>40.91</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.01</v>
+        <v>41.62</v>
       </c>
       <c r="AX9" t="n">
-        <v>-15.64</v>
+        <v>41.1</v>
       </c>
       <c r="AY9" t="n">
-        <v>-32.24</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>-41.13</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>-46.93</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>-51.98</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>-52.85</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>-49.3</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>-48.17</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>-41.62</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>-33.41</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>-29.18</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>-34.67</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>-34.5</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>-30.15</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>-27.17</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>-25.33</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>-21.13</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>-16.89</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>-12.61</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>-9.279999999999999</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>-8.18</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>-12.9</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>-28.81</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>-31.82</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>-35.54</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>-32.98</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>-30.97</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>-19.15</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>-8.42</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>-3.96</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>12.29</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>18.59</v>
-      </c>
-      <c r="CF9" t="n">
-        <v>27.92</v>
-      </c>
-      <c r="CG9" t="n">
-        <v>37.95</v>
-      </c>
-      <c r="CH9" t="n">
-        <v>40.91</v>
-      </c>
-      <c r="CI9" t="n">
-        <v>41.62</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="CK9" t="n">
         <v>33.61</v>
       </c>
     </row>
@@ -9377,264 +8351,150 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v/>
+        <v>8.58</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>8.92</v>
       </c>
       <c r="E10" t="n">
-        <v/>
+        <v>4.18</v>
       </c>
       <c r="F10" t="n">
-        <v/>
+        <v>-0.33</v>
       </c>
       <c r="G10" t="n">
-        <v/>
+        <v>-5.51</v>
       </c>
       <c r="H10" t="n">
-        <v/>
+        <v>-18.08</v>
       </c>
       <c r="I10" t="n">
-        <v/>
+        <v>-26.24</v>
       </c>
       <c r="J10" t="n">
-        <v/>
+        <v>-29.59</v>
       </c>
       <c r="K10" t="n">
-        <v/>
+        <v>-31.13</v>
       </c>
       <c r="L10" t="n">
-        <v/>
+        <v>-38.22</v>
       </c>
       <c r="M10" t="n">
-        <v/>
+        <v>-39.23</v>
       </c>
       <c r="N10" t="n">
-        <v/>
+        <v>-38.6</v>
       </c>
       <c r="O10" t="n">
-        <v/>
+        <v>-39.22</v>
       </c>
       <c r="P10" t="n">
-        <v/>
+        <v>-38.39</v>
       </c>
       <c r="Q10" t="n">
-        <v/>
+        <v>-40.03</v>
       </c>
       <c r="R10" t="n">
-        <v/>
+        <v>-39.18</v>
       </c>
       <c r="S10" t="n">
-        <v/>
+        <v>-41.35</v>
       </c>
       <c r="T10" t="n">
-        <v/>
+        <v>-24.42</v>
       </c>
       <c r="U10" t="n">
-        <v/>
+        <v>-12.08</v>
       </c>
       <c r="V10" t="n">
-        <v/>
+        <v>-8.720000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v/>
+        <v>-6.21</v>
       </c>
       <c r="X10" t="n">
-        <v/>
+        <v>-3.62</v>
       </c>
       <c r="Y10" t="n">
-        <v/>
+        <v>-2.21</v>
       </c>
       <c r="Z10" t="n">
-        <v/>
+        <v>-2.4</v>
       </c>
       <c r="AA10" t="n">
-        <v/>
+        <v>-8.68</v>
       </c>
       <c r="AB10" t="n">
-        <v/>
+        <v>-4.12</v>
       </c>
       <c r="AC10" t="n">
-        <v/>
+        <v>-3.81</v>
       </c>
       <c r="AD10" t="n">
-        <v/>
+        <v>-4.84</v>
       </c>
       <c r="AE10" t="n">
-        <v/>
+        <v>-3.89</v>
       </c>
       <c r="AF10" t="n">
-        <v/>
+        <v>-3.71</v>
       </c>
       <c r="AG10" t="n">
-        <v/>
+        <v>-4.42</v>
       </c>
       <c r="AH10" t="n">
-        <v/>
+        <v>-6.46</v>
       </c>
       <c r="AI10" t="n">
-        <v/>
+        <v>-7.66</v>
       </c>
       <c r="AJ10" t="n">
-        <v/>
+        <v>-8.25</v>
       </c>
       <c r="AK10" t="n">
-        <v/>
+        <v>3.26</v>
       </c>
       <c r="AL10" t="n">
-        <v/>
+        <v>4.84</v>
       </c>
       <c r="AM10" t="n">
-        <v/>
+        <v>12.35</v>
       </c>
       <c r="AN10" t="n">
-        <v/>
+        <v>11.98</v>
       </c>
       <c r="AO10" t="n">
-        <v>8.58</v>
+        <v>6.01</v>
       </c>
       <c r="AP10" t="n">
-        <v>8.92</v>
+        <v>7.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.18</v>
+        <v>9.92</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.33</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="AS10" t="n">
-        <v>-5.51</v>
+        <v>5.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>-18.08</v>
+        <v>1.7</v>
       </c>
       <c r="AU10" t="n">
-        <v>-26.24</v>
+        <v>10.26</v>
       </c>
       <c r="AV10" t="n">
-        <v>-29.59</v>
+        <v>29.74</v>
       </c>
       <c r="AW10" t="n">
-        <v>-31.13</v>
+        <v>55.72</v>
       </c>
       <c r="AX10" t="n">
-        <v>-38.22</v>
+        <v>63.05</v>
       </c>
       <c r="AY10" t="n">
-        <v>-39.23</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>-38.6</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>-39.22</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>-38.39</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>-40.03</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>-39.18</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>-41.35</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>-24.42</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>-12.08</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>-8.720000000000001</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>-6.21</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>-3.62</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>-2.21</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>-8.68</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>-4.12</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>-3.81</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>-4.84</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>-3.89</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>-3.71</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>-4.42</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>-6.46</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>-7.66</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>-8.25</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>12.35</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>11.98</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>6.01</v>
-      </c>
-      <c r="CB10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="CC10" t="n">
-        <v>9.92</v>
-      </c>
-      <c r="CD10" t="n">
-        <v>8.720000000000001</v>
-      </c>
-      <c r="CE10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="CF10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="CG10" t="n">
-        <v>10.26</v>
-      </c>
-      <c r="CH10" t="n">
-        <v>29.74</v>
-      </c>
-      <c r="CI10" t="n">
-        <v>55.72</v>
-      </c>
-      <c r="CJ10" t="n">
-        <v>63.05</v>
-      </c>
-      <c r="CK10" t="n">
         <v>64.95</v>
       </c>
     </row>
@@ -9650,264 +8510,150 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v/>
+        <v>170.77</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>143.35</v>
       </c>
       <c r="E11" t="n">
-        <v/>
+        <v>116.39</v>
       </c>
       <c r="F11" t="n">
-        <v/>
+        <v>93.78</v>
       </c>
       <c r="G11" t="n">
-        <v/>
+        <v>72.73999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v/>
+        <v>51.54</v>
       </c>
       <c r="I11" t="n">
-        <v/>
+        <v>32.01</v>
       </c>
       <c r="J11" t="n">
-        <v/>
+        <v>10.45</v>
       </c>
       <c r="K11" t="n">
-        <v/>
+        <v>-8.75</v>
       </c>
       <c r="L11" t="n">
-        <v/>
+        <v>-25.16</v>
       </c>
       <c r="M11" t="n">
-        <v/>
+        <v>-44.26</v>
       </c>
       <c r="N11" t="n">
-        <v/>
+        <v>-55.39</v>
       </c>
       <c r="O11" t="n">
-        <v/>
+        <v>-60.1</v>
       </c>
       <c r="P11" t="n">
-        <v/>
+        <v>-64.08</v>
       </c>
       <c r="Q11" t="n">
-        <v/>
+        <v>-65.73</v>
       </c>
       <c r="R11" t="n">
-        <v/>
+        <v>-62.56</v>
       </c>
       <c r="S11" t="n">
-        <v/>
+        <v>-61.43</v>
       </c>
       <c r="T11" t="n">
-        <v/>
+        <v>-55.51</v>
       </c>
       <c r="U11" t="n">
-        <v/>
+        <v>-48.37</v>
       </c>
       <c r="V11" t="n">
-        <v/>
+        <v>-45.22</v>
       </c>
       <c r="W11" t="n">
-        <v/>
+        <v>-46.97</v>
       </c>
       <c r="X11" t="n">
-        <v/>
+        <v>-43.96</v>
       </c>
       <c r="Y11" t="n">
-        <v/>
+        <v>-39.69</v>
       </c>
       <c r="Z11" t="n">
-        <v/>
+        <v>-36.14</v>
       </c>
       <c r="AA11" t="n">
-        <v/>
+        <v>-32.45</v>
       </c>
       <c r="AB11" t="n">
-        <v/>
+        <v>-26.34</v>
       </c>
       <c r="AC11" t="n">
-        <v/>
+        <v>-20.53</v>
       </c>
       <c r="AD11" t="n">
-        <v/>
+        <v>-14.02</v>
       </c>
       <c r="AE11" t="n">
-        <v/>
+        <v>3.31</v>
       </c>
       <c r="AF11" t="n">
-        <v/>
+        <v>19.82</v>
       </c>
       <c r="AG11" t="n">
-        <v/>
+        <v>28.35</v>
       </c>
       <c r="AH11" t="n">
-        <v/>
+        <v>26.52</v>
       </c>
       <c r="AI11" t="n">
-        <v/>
+        <v>29.61</v>
       </c>
       <c r="AJ11" t="n">
-        <v/>
+        <v>31.34</v>
       </c>
       <c r="AK11" t="n">
-        <v/>
+        <v>26.54</v>
       </c>
       <c r="AL11" t="n">
-        <v/>
+        <v>22.19</v>
       </c>
       <c r="AM11" t="n">
-        <v/>
+        <v>21.29</v>
       </c>
       <c r="AN11" t="n">
-        <v/>
+        <v>15.9</v>
       </c>
       <c r="AO11" t="n">
-        <v>170.77</v>
+        <v>4.37</v>
       </c>
       <c r="AP11" t="n">
-        <v>143.35</v>
+        <v>-5.18</v>
       </c>
       <c r="AQ11" t="n">
-        <v>116.39</v>
+        <v>-4.22</v>
       </c>
       <c r="AR11" t="n">
-        <v>93.78</v>
+        <v>-3.13</v>
       </c>
       <c r="AS11" t="n">
-        <v>72.73999999999999</v>
+        <v>-2.85</v>
       </c>
       <c r="AT11" t="n">
-        <v>51.54</v>
+        <v>3.88</v>
       </c>
       <c r="AU11" t="n">
-        <v>32.01</v>
+        <v>13.74</v>
       </c>
       <c r="AV11" t="n">
-        <v>10.45</v>
+        <v>17.97</v>
       </c>
       <c r="AW11" t="n">
-        <v>-8.75</v>
+        <v>19.36</v>
       </c>
       <c r="AX11" t="n">
-        <v>-25.16</v>
+        <v>21.19</v>
       </c>
       <c r="AY11" t="n">
-        <v>-44.26</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>-55.39</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>-60.1</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>-64.08</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>-65.73</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>-62.56</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>-61.43</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>-55.51</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>-48.37</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>-45.22</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>-46.97</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>-43.96</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>-39.69</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>-36.14</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>-32.45</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>-26.34</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>-20.53</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>-14.02</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>19.82</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>28.35</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>26.52</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>29.61</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>31.34</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>26.54</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>22.19</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="CB11" t="n">
-        <v>-5.18</v>
-      </c>
-      <c r="CC11" t="n">
-        <v>-4.22</v>
-      </c>
-      <c r="CD11" t="n">
-        <v>-3.13</v>
-      </c>
-      <c r="CE11" t="n">
-        <v>-2.85</v>
-      </c>
-      <c r="CF11" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="CG11" t="n">
-        <v>13.74</v>
-      </c>
-      <c r="CH11" t="n">
-        <v>17.97</v>
-      </c>
-      <c r="CI11" t="n">
-        <v>19.36</v>
-      </c>
-      <c r="CJ11" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="CK11" t="n">
         <v>17.15</v>
       </c>
     </row>
@@ -9923,264 +8669,150 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v/>
+        <v>177.13</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>147.55</v>
       </c>
       <c r="E12" t="n">
-        <v/>
+        <v>119.23</v>
       </c>
       <c r="F12" t="n">
-        <v/>
+        <v>95.90000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v/>
+        <v>74.06</v>
       </c>
       <c r="H12" t="n">
-        <v/>
+        <v>53.04</v>
       </c>
       <c r="I12" t="n">
-        <v/>
+        <v>33.42</v>
       </c>
       <c r="J12" t="n">
-        <v/>
+        <v>11.98</v>
       </c>
       <c r="K12" t="n">
-        <v/>
+        <v>-7.45</v>
       </c>
       <c r="L12" t="n">
-        <v/>
+        <v>-24.57</v>
       </c>
       <c r="M12" t="n">
-        <v/>
+        <v>-43.73</v>
       </c>
       <c r="N12" t="n">
-        <v/>
+        <v>-55.16</v>
       </c>
       <c r="O12" t="n">
-        <v/>
+        <v>-59.68</v>
       </c>
       <c r="P12" t="n">
-        <v/>
+        <v>-63.32</v>
       </c>
       <c r="Q12" t="n">
-        <v/>
+        <v>-64.14</v>
       </c>
       <c r="R12" t="n">
-        <v/>
+        <v>-60.57</v>
       </c>
       <c r="S12" t="n">
-        <v/>
+        <v>-59.05</v>
       </c>
       <c r="T12" t="n">
-        <v/>
+        <v>-53.56</v>
       </c>
       <c r="U12" t="n">
-        <v/>
+        <v>-47.45</v>
       </c>
       <c r="V12" t="n">
-        <v/>
+        <v>-44.33</v>
       </c>
       <c r="W12" t="n">
-        <v/>
+        <v>-47.02</v>
       </c>
       <c r="X12" t="n">
-        <v/>
+        <v>-44.12</v>
       </c>
       <c r="Y12" t="n">
-        <v/>
+        <v>-40.15</v>
       </c>
       <c r="Z12" t="n">
-        <v/>
+        <v>-37.16</v>
       </c>
       <c r="AA12" t="n">
-        <v/>
+        <v>-34</v>
       </c>
       <c r="AB12" t="n">
-        <v/>
+        <v>-28.66</v>
       </c>
       <c r="AC12" t="n">
-        <v/>
+        <v>-24.01</v>
       </c>
       <c r="AD12" t="n">
-        <v/>
+        <v>-17.45</v>
       </c>
       <c r="AE12" t="n">
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="AF12" t="n">
-        <v/>
+        <v>18.41</v>
       </c>
       <c r="AG12" t="n">
-        <v/>
+        <v>27.25</v>
       </c>
       <c r="AH12" t="n">
-        <v/>
+        <v>26.85</v>
       </c>
       <c r="AI12" t="n">
-        <v/>
+        <v>30.31</v>
       </c>
       <c r="AJ12" t="n">
-        <v/>
+        <v>32.7</v>
       </c>
       <c r="AK12" t="n">
-        <v/>
+        <v>27.98</v>
       </c>
       <c r="AL12" t="n">
-        <v/>
+        <v>23.35</v>
       </c>
       <c r="AM12" t="n">
-        <v/>
+        <v>21.96</v>
       </c>
       <c r="AN12" t="n">
-        <v/>
+        <v>17.24</v>
       </c>
       <c r="AO12" t="n">
-        <v>177.13</v>
+        <v>6.8</v>
       </c>
       <c r="AP12" t="n">
-        <v>147.55</v>
+        <v>-3.18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>119.23</v>
+        <v>-2.69</v>
       </c>
       <c r="AR12" t="n">
-        <v>95.90000000000001</v>
+        <v>-1.83</v>
       </c>
       <c r="AS12" t="n">
-        <v>74.06</v>
+        <v>-1.1</v>
       </c>
       <c r="AT12" t="n">
-        <v>53.04</v>
+        <v>6.61</v>
       </c>
       <c r="AU12" t="n">
-        <v>33.42</v>
+        <v>16.48</v>
       </c>
       <c r="AV12" t="n">
-        <v>11.98</v>
+        <v>20.77</v>
       </c>
       <c r="AW12" t="n">
-        <v>-7.45</v>
+        <v>21.75</v>
       </c>
       <c r="AX12" t="n">
-        <v>-24.57</v>
+        <v>22.46</v>
       </c>
       <c r="AY12" t="n">
-        <v>-43.73</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-55.16</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>-59.68</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>-63.32</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>-64.14</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>-60.57</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>-59.05</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>-53.56</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>-47.45</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>-44.33</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>-47.02</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>-44.12</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>-40.15</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>-37.16</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>-34</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>-28.66</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>-24.01</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>-17.45</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>18.41</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>27.25</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>26.85</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>30.31</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>27.98</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>23.35</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>21.96</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>17.24</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="CB12" t="n">
-        <v>-3.18</v>
-      </c>
-      <c r="CC12" t="n">
-        <v>-2.69</v>
-      </c>
-      <c r="CD12" t="n">
-        <v>-1.83</v>
-      </c>
-      <c r="CE12" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="CF12" t="n">
-        <v>6.61</v>
-      </c>
-      <c r="CG12" t="n">
-        <v>16.48</v>
-      </c>
-      <c r="CH12" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="CI12" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="CJ12" t="n">
-        <v>22.46</v>
-      </c>
-      <c r="CK12" t="n">
         <v>17.01</v>
       </c>
     </row>
@@ -10196,264 +8828,150 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v/>
+        <v>174.73</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>145.48</v>
       </c>
       <c r="E13" t="n">
-        <v/>
+        <v>117.59</v>
       </c>
       <c r="F13" t="n">
-        <v/>
+        <v>94.97</v>
       </c>
       <c r="G13" t="n">
-        <v/>
+        <v>73.62</v>
       </c>
       <c r="H13" t="n">
-        <v/>
+        <v>52.41</v>
       </c>
       <c r="I13" t="n">
-        <v/>
+        <v>32.85</v>
       </c>
       <c r="J13" t="n">
-        <v/>
+        <v>11.2</v>
       </c>
       <c r="K13" t="n">
-        <v/>
+        <v>-7.82</v>
       </c>
       <c r="L13" t="n">
-        <v/>
+        <v>-24.67</v>
       </c>
       <c r="M13" t="n">
-        <v/>
+        <v>-43.7</v>
       </c>
       <c r="N13" t="n">
-        <v/>
+        <v>-56.1</v>
       </c>
       <c r="O13" t="n">
-        <v/>
+        <v>-60.6</v>
       </c>
       <c r="P13" t="n">
-        <v/>
+        <v>-64.18000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v/>
+        <v>-64.93000000000001</v>
       </c>
       <c r="R13" t="n">
-        <v/>
+        <v>-60.23</v>
       </c>
       <c r="S13" t="n">
-        <v/>
+        <v>-58.38</v>
       </c>
       <c r="T13" t="n">
-        <v/>
+        <v>-52.22</v>
       </c>
       <c r="U13" t="n">
-        <v/>
+        <v>-45.08</v>
       </c>
       <c r="V13" t="n">
-        <v/>
+        <v>-41.49</v>
       </c>
       <c r="W13" t="n">
-        <v/>
+        <v>-42.28</v>
       </c>
       <c r="X13" t="n">
-        <v/>
+        <v>-39.1</v>
       </c>
       <c r="Y13" t="n">
-        <v/>
+        <v>-35.02</v>
       </c>
       <c r="Z13" t="n">
-        <v/>
+        <v>-32.27</v>
       </c>
       <c r="AA13" t="n">
-        <v/>
+        <v>-29.51</v>
       </c>
       <c r="AB13" t="n">
-        <v/>
+        <v>-24.02</v>
       </c>
       <c r="AC13" t="n">
-        <v/>
+        <v>-19.42</v>
       </c>
       <c r="AD13" t="n">
-        <v/>
+        <v>-12.31</v>
       </c>
       <c r="AE13" t="n">
-        <v/>
+        <v>10.44</v>
       </c>
       <c r="AF13" t="n">
-        <v/>
+        <v>29.93</v>
       </c>
       <c r="AG13" t="n">
-        <v/>
+        <v>40.71</v>
       </c>
       <c r="AH13" t="n">
-        <v/>
+        <v>42.4</v>
       </c>
       <c r="AI13" t="n">
-        <v/>
+        <v>45.15</v>
       </c>
       <c r="AJ13" t="n">
-        <v/>
+        <v>46.47</v>
       </c>
       <c r="AK13" t="n">
-        <v/>
+        <v>39.39</v>
       </c>
       <c r="AL13" t="n">
-        <v/>
+        <v>32.74</v>
       </c>
       <c r="AM13" t="n">
-        <v/>
+        <v>28.33</v>
       </c>
       <c r="AN13" t="n">
-        <v/>
+        <v>20.64</v>
       </c>
       <c r="AO13" t="n">
-        <v>174.73</v>
+        <v>7.99</v>
       </c>
       <c r="AP13" t="n">
-        <v>145.48</v>
+        <v>-4.19</v>
       </c>
       <c r="AQ13" t="n">
-        <v>117.59</v>
+        <v>-6.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>94.97</v>
+        <v>-8.07</v>
       </c>
       <c r="AS13" t="n">
-        <v>73.62</v>
+        <v>-10.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>52.41</v>
+        <v>-4.67</v>
       </c>
       <c r="AU13" t="n">
-        <v>32.85</v>
+        <v>3.83</v>
       </c>
       <c r="AV13" t="n">
-        <v>11.2</v>
+        <v>7.35</v>
       </c>
       <c r="AW13" t="n">
-        <v>-7.82</v>
+        <v>8.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>-24.67</v>
+        <v>10.21</v>
       </c>
       <c r="AY13" t="n">
-        <v>-43.7</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>-56.1</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>-60.6</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>-64.18000000000001</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>-64.93000000000001</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>-60.23</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>-58.38</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>-52.22</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>-45.08</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>-41.49</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>-42.28</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>-39.1</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>-35.02</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>-32.27</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>-29.51</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>-24.02</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>-19.42</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>-12.31</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>10.44</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>29.93</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>40.71</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>45.15</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>46.47</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>39.39</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>32.74</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>28.33</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>20.64</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="CB13" t="n">
-        <v>-4.19</v>
-      </c>
-      <c r="CC13" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="CD13" t="n">
-        <v>-8.07</v>
-      </c>
-      <c r="CE13" t="n">
-        <v>-10.01</v>
-      </c>
-      <c r="CF13" t="n">
-        <v>-4.67</v>
-      </c>
-      <c r="CG13" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="CH13" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="CI13" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="CJ13" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="CK13" t="n">
         <v>6.24</v>
       </c>
     </row>
@@ -10469,264 +8987,150 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v/>
+        <v>194.76</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>164.49</v>
       </c>
       <c r="E14" t="n">
-        <v/>
+        <v>134.07</v>
       </c>
       <c r="F14" t="n">
-        <v/>
+        <v>109.22</v>
       </c>
       <c r="G14" t="n">
-        <v/>
+        <v>86.16</v>
       </c>
       <c r="H14" t="n">
-        <v/>
+        <v>63.23</v>
       </c>
       <c r="I14" t="n">
-        <v/>
+        <v>42.66</v>
       </c>
       <c r="J14" t="n">
-        <v/>
+        <v>21.4</v>
       </c>
       <c r="K14" t="n">
-        <v/>
+        <v>1.81</v>
       </c>
       <c r="L14" t="n">
-        <v/>
+        <v>-14.31</v>
       </c>
       <c r="M14" t="n">
-        <v/>
+        <v>-31.89</v>
       </c>
       <c r="N14" t="n">
-        <v/>
+        <v>-42.03</v>
       </c>
       <c r="O14" t="n">
-        <v/>
+        <v>-48.2</v>
       </c>
       <c r="P14" t="n">
-        <v/>
+        <v>-53.67</v>
       </c>
       <c r="Q14" t="n">
-        <v/>
+        <v>-56.27</v>
       </c>
       <c r="R14" t="n">
-        <v/>
+        <v>-53.18</v>
       </c>
       <c r="S14" t="n">
-        <v/>
+        <v>-52.56</v>
       </c>
       <c r="T14" t="n">
-        <v/>
+        <v>-44.68</v>
       </c>
       <c r="U14" t="n">
-        <v/>
+        <v>-35.1</v>
       </c>
       <c r="V14" t="n">
-        <v/>
+        <v>-30.27</v>
       </c>
       <c r="W14" t="n">
-        <v/>
+        <v>-33.76</v>
       </c>
       <c r="X14" t="n">
-        <v/>
+        <v>-31.77</v>
       </c>
       <c r="Y14" t="n">
-        <v/>
+        <v>-27.64</v>
       </c>
       <c r="Z14" t="n">
-        <v/>
+        <v>-25.76</v>
       </c>
       <c r="AA14" t="n">
-        <v/>
+        <v>-24.74</v>
       </c>
       <c r="AB14" t="n">
-        <v/>
+        <v>-21.19</v>
       </c>
       <c r="AC14" t="n">
-        <v/>
+        <v>-17.98</v>
       </c>
       <c r="AD14" t="n">
-        <v/>
+        <v>-13.71</v>
       </c>
       <c r="AE14" t="n">
-        <v/>
+        <v>-8.85</v>
       </c>
       <c r="AF14" t="n">
-        <v/>
+        <v>-6.09</v>
       </c>
       <c r="AG14" t="n">
-        <v/>
+        <v>-7.15</v>
       </c>
       <c r="AH14" t="n">
-        <v/>
+        <v>-19.44</v>
       </c>
       <c r="AI14" t="n">
-        <v/>
+        <v>-19.86</v>
       </c>
       <c r="AJ14" t="n">
-        <v/>
+        <v>-20.39</v>
       </c>
       <c r="AK14" t="n">
-        <v/>
+        <v>-19.58</v>
       </c>
       <c r="AL14" t="n">
-        <v/>
+        <v>-18.93</v>
       </c>
       <c r="AM14" t="n">
-        <v/>
+        <v>-9.83</v>
       </c>
       <c r="AN14" t="n">
-        <v/>
+        <v>-3.69</v>
       </c>
       <c r="AO14" t="n">
-        <v>194.76</v>
+        <v>-3.93</v>
       </c>
       <c r="AP14" t="n">
-        <v>164.49</v>
+        <v>-2.3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>134.07</v>
+        <v>2.87</v>
       </c>
       <c r="AR14" t="n">
-        <v>109.22</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AS14" t="n">
-        <v>86.16</v>
+        <v>15.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>63.23</v>
+        <v>24.23</v>
       </c>
       <c r="AU14" t="n">
-        <v>42.66</v>
+        <v>34.21</v>
       </c>
       <c r="AV14" t="n">
-        <v>21.4</v>
+        <v>37.35</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.81</v>
+        <v>38.27</v>
       </c>
       <c r="AX14" t="n">
-        <v>-14.31</v>
+        <v>38.68</v>
       </c>
       <c r="AY14" t="n">
-        <v>-31.89</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>-42.03</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>-48.2</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>-53.67</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>-56.27</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>-53.18</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>-52.56</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>-44.68</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>-35.1</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>-30.27</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>-33.76</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>-31.77</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>-27.64</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>-25.76</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>-24.74</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>-21.19</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>-17.98</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>-13.71</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>-8.85</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>-6.09</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>-7.15</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>-19.44</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>-19.86</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>-20.39</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>-19.58</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>-18.93</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>-9.83</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>-3.69</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>-3.93</v>
-      </c>
-      <c r="CB14" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="CC14" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="CD14" t="n">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="CE14" t="n">
-        <v>15.01</v>
-      </c>
-      <c r="CF14" t="n">
-        <v>24.23</v>
-      </c>
-      <c r="CG14" t="n">
-        <v>34.21</v>
-      </c>
-      <c r="CH14" t="n">
-        <v>37.35</v>
-      </c>
-      <c r="CI14" t="n">
-        <v>38.27</v>
-      </c>
-      <c r="CJ14" t="n">
-        <v>38.68</v>
-      </c>
-      <c r="CK14" t="n">
         <v>32.14</v>
       </c>
     </row>
@@ -10742,264 +9146,150 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v/>
+        <v>-3.78</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>3.44</v>
       </c>
       <c r="E15" t="n">
-        <v/>
+        <v>30.8</v>
       </c>
       <c r="F15" t="n">
-        <v/>
+        <v>57.74</v>
       </c>
       <c r="G15" t="n">
-        <v/>
+        <v>94.01000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v/>
+        <v>105.04</v>
       </c>
       <c r="I15" t="n">
-        <v/>
+        <v>106.84</v>
       </c>
       <c r="J15" t="n">
-        <v/>
+        <v>99.88</v>
       </c>
       <c r="K15" t="n">
-        <v/>
+        <v>90.43000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v/>
+        <v>78.37</v>
       </c>
       <c r="M15" t="n">
-        <v/>
+        <v>89.54000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v/>
+        <v>94.61</v>
       </c>
       <c r="O15" t="n">
-        <v/>
+        <v>95.91</v>
       </c>
       <c r="P15" t="n">
-        <v/>
+        <v>99.13</v>
       </c>
       <c r="Q15" t="n">
-        <v/>
+        <v>91.05</v>
       </c>
       <c r="R15" t="n">
-        <v/>
+        <v>77.95</v>
       </c>
       <c r="S15" t="n">
-        <v/>
+        <v>66.62</v>
       </c>
       <c r="T15" t="n">
-        <v/>
+        <v>51.04</v>
       </c>
       <c r="U15" t="n">
-        <v/>
+        <v>40.96</v>
       </c>
       <c r="V15" t="n">
-        <v/>
+        <v>28.73</v>
       </c>
       <c r="W15" t="n">
-        <v/>
+        <v>17.47</v>
       </c>
       <c r="X15" t="n">
-        <v/>
+        <v>4.76</v>
       </c>
       <c r="Y15" t="n">
-        <v/>
+        <v>1.65</v>
       </c>
       <c r="Z15" t="n">
-        <v/>
+        <v>0.52</v>
       </c>
       <c r="AA15" t="n">
-        <v/>
+        <v>1.02</v>
       </c>
       <c r="AB15" t="n">
-        <v/>
+        <v>-0.79</v>
       </c>
       <c r="AC15" t="n">
-        <v/>
+        <v>-3.66</v>
       </c>
       <c r="AD15" t="n">
-        <v/>
+        <v>-14.07</v>
       </c>
       <c r="AE15" t="n">
-        <v/>
+        <v>-26.63</v>
       </c>
       <c r="AF15" t="n">
-        <v/>
+        <v>-48.79</v>
       </c>
       <c r="AG15" t="n">
-        <v/>
+        <v>-51.85</v>
       </c>
       <c r="AH15" t="n">
-        <v/>
+        <v>-52.74</v>
       </c>
       <c r="AI15" t="n">
-        <v/>
+        <v>-52.09</v>
       </c>
       <c r="AJ15" t="n">
-        <v/>
+        <v>-50.05</v>
       </c>
       <c r="AK15" t="n">
-        <v/>
+        <v>-48.32</v>
       </c>
       <c r="AL15" t="n">
-        <v/>
+        <v>-45.64</v>
       </c>
       <c r="AM15" t="n">
-        <v/>
+        <v>-40.66</v>
       </c>
       <c r="AN15" t="n">
-        <v/>
+        <v>-37.77</v>
       </c>
       <c r="AO15" t="n">
-        <v>-3.78</v>
+        <v>-34.57</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.44</v>
+        <v>-32.27</v>
       </c>
       <c r="AQ15" t="n">
-        <v>30.8</v>
+        <v>-26.73</v>
       </c>
       <c r="AR15" t="n">
-        <v>57.74</v>
+        <v>-24</v>
       </c>
       <c r="AS15" t="n">
-        <v>94.01000000000001</v>
+        <v>-23</v>
       </c>
       <c r="AT15" t="n">
-        <v>105.04</v>
+        <v>-25.12</v>
       </c>
       <c r="AU15" t="n">
-        <v>106.84</v>
+        <v>-26.98</v>
       </c>
       <c r="AV15" t="n">
-        <v>99.88</v>
+        <v>-27.21</v>
       </c>
       <c r="AW15" t="n">
-        <v>90.43000000000001</v>
+        <v>-33.39</v>
       </c>
       <c r="AX15" t="n">
-        <v>78.37</v>
+        <v>-22.92</v>
       </c>
       <c r="AY15" t="n">
-        <v>89.54000000000001</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>94.61</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>95.91</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>99.13</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>91.05</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>77.95</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>66.62</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>51.04</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>40.96</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>28.73</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>17.47</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>-0.79</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>-14.07</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>-26.63</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>-48.79</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>-51.85</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>-52.74</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>-52.09</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>-50.05</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>-48.32</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>-45.64</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>-40.66</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>-37.77</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>-34.57</v>
-      </c>
-      <c r="CB15" t="n">
-        <v>-32.27</v>
-      </c>
-      <c r="CC15" t="n">
-        <v>-26.73</v>
-      </c>
-      <c r="CD15" t="n">
-        <v>-24</v>
-      </c>
-      <c r="CE15" t="n">
-        <v>-23</v>
-      </c>
-      <c r="CF15" t="n">
-        <v>-25.12</v>
-      </c>
-      <c r="CG15" t="n">
-        <v>-26.98</v>
-      </c>
-      <c r="CH15" t="n">
-        <v>-27.21</v>
-      </c>
-      <c r="CI15" t="n">
-        <v>-33.39</v>
-      </c>
-      <c r="CJ15" t="n">
-        <v>-22.92</v>
-      </c>
-      <c r="CK15" t="n">
         <v>-8.68</v>
       </c>
     </row>
@@ -11015,264 +9305,150 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v/>
+        <v>176.14</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>149.02</v>
       </c>
       <c r="E16" t="n">
-        <v/>
+        <v>121.12</v>
       </c>
       <c r="F16" t="n">
-        <v/>
+        <v>98.42</v>
       </c>
       <c r="G16" t="n">
-        <v/>
+        <v>76.84</v>
       </c>
       <c r="H16" t="n">
-        <v/>
+        <v>54.91</v>
       </c>
       <c r="I16" t="n">
-        <v/>
+        <v>35.96</v>
       </c>
       <c r="J16" t="n">
-        <v/>
+        <v>14.63</v>
       </c>
       <c r="K16" t="n">
-        <v/>
+        <v>-5.05</v>
       </c>
       <c r="L16" t="n">
-        <v/>
+        <v>-21.72</v>
       </c>
       <c r="M16" t="n">
-        <v/>
+        <v>-40.31</v>
       </c>
       <c r="N16" t="n">
-        <v/>
+        <v>-50.59</v>
       </c>
       <c r="O16" t="n">
-        <v/>
+        <v>-55.5</v>
       </c>
       <c r="P16" t="n">
-        <v/>
+        <v>-59.68</v>
       </c>
       <c r="Q16" t="n">
-        <v/>
+        <v>-61.17</v>
       </c>
       <c r="R16" t="n">
-        <v/>
+        <v>-58.16</v>
       </c>
       <c r="S16" t="n">
-        <v/>
+        <v>-58.48</v>
       </c>
       <c r="T16" t="n">
-        <v/>
+        <v>-51.21</v>
       </c>
       <c r="U16" t="n">
-        <v/>
+        <v>-41.99</v>
       </c>
       <c r="V16" t="n">
-        <v/>
+        <v>-37.21</v>
       </c>
       <c r="W16" t="n">
-        <v/>
+        <v>-38.94</v>
       </c>
       <c r="X16" t="n">
-        <v/>
+        <v>-36.54</v>
       </c>
       <c r="Y16" t="n">
-        <v/>
+        <v>-32.47</v>
       </c>
       <c r="Z16" t="n">
-        <v/>
+        <v>-31.12</v>
       </c>
       <c r="AA16" t="n">
-        <v/>
+        <v>-30.42</v>
       </c>
       <c r="AB16" t="n">
-        <v/>
+        <v>-26.74</v>
       </c>
       <c r="AC16" t="n">
-        <v/>
+        <v>-23.4</v>
       </c>
       <c r="AD16" t="n">
-        <v/>
+        <v>-18.17</v>
       </c>
       <c r="AE16" t="n">
-        <v/>
+        <v>-6.98</v>
       </c>
       <c r="AF16" t="n">
-        <v/>
+        <v>2.83</v>
       </c>
       <c r="AG16" t="n">
-        <v/>
+        <v>6.83</v>
       </c>
       <c r="AH16" t="n">
-        <v/>
+        <v>2.25</v>
       </c>
       <c r="AI16" t="n">
-        <v/>
+        <v>5.77</v>
       </c>
       <c r="AJ16" t="n">
-        <v/>
+        <v>8.380000000000001</v>
       </c>
       <c r="AK16" t="n">
-        <v/>
+        <v>6.52</v>
       </c>
       <c r="AL16" t="n">
-        <v/>
+        <v>4.11</v>
       </c>
       <c r="AM16" t="n">
-        <v/>
+        <v>6.5</v>
       </c>
       <c r="AN16" t="n">
-        <v/>
+        <v>5.96</v>
       </c>
       <c r="AO16" t="n">
-        <v>176.14</v>
+        <v>-0.33</v>
       </c>
       <c r="AP16" t="n">
-        <v>149.02</v>
+        <v>-4.65</v>
       </c>
       <c r="AQ16" t="n">
-        <v>121.12</v>
+        <v>-1.86</v>
       </c>
       <c r="AR16" t="n">
-        <v>98.42</v>
+        <v>1.94</v>
       </c>
       <c r="AS16" t="n">
-        <v>76.84</v>
+        <v>4.85</v>
       </c>
       <c r="AT16" t="n">
-        <v>54.91</v>
+        <v>13.55</v>
       </c>
       <c r="AU16" t="n">
-        <v>35.96</v>
+        <v>23.68</v>
       </c>
       <c r="AV16" t="n">
-        <v>14.63</v>
+        <v>26.77</v>
       </c>
       <c r="AW16" t="n">
-        <v>-5.05</v>
+        <v>26.99</v>
       </c>
       <c r="AX16" t="n">
-        <v>-21.72</v>
+        <v>27.15</v>
       </c>
       <c r="AY16" t="n">
-        <v>-40.31</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>-50.59</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>-55.5</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>-59.68</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>-61.17</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>-58.16</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>-58.48</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>-51.21</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>-41.99</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>-37.21</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>-38.94</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>-36.54</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>-32.47</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>-31.12</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>-30.42</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>-26.74</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>-23.4</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>-18.17</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>-6.98</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="CB16" t="n">
-        <v>-4.65</v>
-      </c>
-      <c r="CC16" t="n">
-        <v>-1.86</v>
-      </c>
-      <c r="CD16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="CE16" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="CF16" t="n">
-        <v>13.55</v>
-      </c>
-      <c r="CG16" t="n">
-        <v>23.68</v>
-      </c>
-      <c r="CH16" t="n">
-        <v>26.77</v>
-      </c>
-      <c r="CI16" t="n">
-        <v>26.99</v>
-      </c>
-      <c r="CJ16" t="n">
-        <v>27.15</v>
-      </c>
-      <c r="CK16" t="n">
         <v>21.16</v>
       </c>
     </row>
@@ -11288,264 +9464,150 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v/>
+        <v>164.34</v>
       </c>
       <c r="D17" t="n">
-        <v/>
+        <v>139.06</v>
       </c>
       <c r="E17" t="n">
-        <v/>
+        <v>113.37</v>
       </c>
       <c r="F17" t="n">
-        <v/>
+        <v>91.38</v>
       </c>
       <c r="G17" t="n">
-        <v/>
+        <v>70.3</v>
       </c>
       <c r="H17" t="n">
-        <v/>
+        <v>49.24</v>
       </c>
       <c r="I17" t="n">
-        <v/>
+        <v>30.19</v>
       </c>
       <c r="J17" t="n">
-        <v/>
+        <v>9.15</v>
       </c>
       <c r="K17" t="n">
-        <v/>
+        <v>-10.28</v>
       </c>
       <c r="L17" t="n">
-        <v/>
+        <v>-26.34</v>
       </c>
       <c r="M17" t="n">
-        <v/>
+        <v>-45.44</v>
       </c>
       <c r="N17" t="n">
-        <v/>
+        <v>-54.4</v>
       </c>
       <c r="O17" t="n">
-        <v/>
+        <v>-58.48</v>
       </c>
       <c r="P17" t="n">
-        <v/>
+        <v>-61.95</v>
       </c>
       <c r="Q17" t="n">
-        <v/>
+        <v>-61.94</v>
       </c>
       <c r="R17" t="n">
-        <v/>
+        <v>-57.45</v>
       </c>
       <c r="S17" t="n">
-        <v/>
+        <v>-55.94</v>
       </c>
       <c r="T17" t="n">
-        <v/>
+        <v>-49.25</v>
       </c>
       <c r="U17" t="n">
-        <v/>
+        <v>-40.76</v>
       </c>
       <c r="V17" t="n">
-        <v/>
+        <v>-36.43</v>
       </c>
       <c r="W17" t="n">
-        <v/>
+        <v>-38.77</v>
       </c>
       <c r="X17" t="n">
-        <v/>
+        <v>-35.85</v>
       </c>
       <c r="Y17" t="n">
-        <v/>
+        <v>-31.79</v>
       </c>
       <c r="Z17" t="n">
-        <v/>
+        <v>-28.97</v>
       </c>
       <c r="AA17" t="n">
-        <v/>
+        <v>-26.06</v>
       </c>
       <c r="AB17" t="n">
-        <v/>
+        <v>-21.68</v>
       </c>
       <c r="AC17" t="n">
-        <v/>
+        <v>-17.55</v>
       </c>
       <c r="AD17" t="n">
-        <v/>
+        <v>-12.51</v>
       </c>
       <c r="AE17" t="n">
-        <v/>
+        <v>-2.85</v>
       </c>
       <c r="AF17" t="n">
-        <v/>
+        <v>5.47</v>
       </c>
       <c r="AG17" t="n">
-        <v/>
+        <v>8.24</v>
       </c>
       <c r="AH17" t="n">
-        <v/>
+        <v>-0.53</v>
       </c>
       <c r="AI17" t="n">
-        <v/>
+        <v>0.71</v>
       </c>
       <c r="AJ17" t="n">
-        <v/>
+        <v>2.3</v>
       </c>
       <c r="AK17" t="n">
-        <v/>
+        <v>0.99</v>
       </c>
       <c r="AL17" t="n">
-        <v/>
+        <v>-0.86</v>
       </c>
       <c r="AM17" t="n">
-        <v/>
+        <v>2.33</v>
       </c>
       <c r="AN17" t="n">
-        <v/>
+        <v>2.35</v>
       </c>
       <c r="AO17" t="n">
-        <v>164.34</v>
+        <v>-3.93</v>
       </c>
       <c r="AP17" t="n">
-        <v>139.06</v>
+        <v>-9.23</v>
       </c>
       <c r="AQ17" t="n">
-        <v>113.37</v>
+        <v>-5.71</v>
       </c>
       <c r="AR17" t="n">
-        <v>91.38</v>
+        <v>-0.84</v>
       </c>
       <c r="AS17" t="n">
-        <v>70.3</v>
+        <v>3.67</v>
       </c>
       <c r="AT17" t="n">
-        <v>49.24</v>
+        <v>13.59</v>
       </c>
       <c r="AU17" t="n">
-        <v>30.19</v>
+        <v>24.62</v>
       </c>
       <c r="AV17" t="n">
-        <v>9.15</v>
+        <v>28.86</v>
       </c>
       <c r="AW17" t="n">
-        <v>-10.28</v>
+        <v>30.08</v>
       </c>
       <c r="AX17" t="n">
-        <v>-26.34</v>
+        <v>31.11</v>
       </c>
       <c r="AY17" t="n">
-        <v>-45.44</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>-54.4</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>-58.48</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>-61.95</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>-61.94</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>-57.45</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>-55.94</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>-49.25</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>-40.76</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>-36.43</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>-38.77</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>-35.85</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>-31.79</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>-28.97</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>-26.06</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>-21.68</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>-17.55</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>-12.51</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>-2.85</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>8.24</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>-3.93</v>
-      </c>
-      <c r="CB17" t="n">
-        <v>-9.23</v>
-      </c>
-      <c r="CC17" t="n">
-        <v>-5.71</v>
-      </c>
-      <c r="CD17" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="CE17" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="CF17" t="n">
-        <v>13.59</v>
-      </c>
-      <c r="CG17" t="n">
-        <v>24.62</v>
-      </c>
-      <c r="CH17" t="n">
-        <v>28.86</v>
-      </c>
-      <c r="CI17" t="n">
-        <v>30.08</v>
-      </c>
-      <c r="CJ17" t="n">
-        <v>31.11</v>
-      </c>
-      <c r="CK17" t="n">
         <v>25.4</v>
       </c>
     </row>
@@ -11561,264 +9623,150 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v/>
+        <v>31.57</v>
       </c>
       <c r="D18" t="n">
-        <v/>
+        <v>31</v>
       </c>
       <c r="E18" t="n">
-        <v/>
+        <v>25.54</v>
       </c>
       <c r="F18" t="n">
-        <v/>
+        <v>20.36</v>
       </c>
       <c r="G18" t="n">
-        <v/>
+        <v>13.97</v>
       </c>
       <c r="H18" t="n">
-        <v/>
+        <v>-2.19</v>
       </c>
       <c r="I18" t="n">
-        <v/>
+        <v>-13.61</v>
       </c>
       <c r="J18" t="n">
-        <v/>
+        <v>-20.27</v>
       </c>
       <c r="K18" t="n">
-        <v/>
+        <v>-23.14</v>
       </c>
       <c r="L18" t="n">
-        <v/>
+        <v>-30.26</v>
       </c>
       <c r="M18" t="n">
-        <v/>
+        <v>-30.46</v>
       </c>
       <c r="N18" t="n">
-        <v/>
+        <v>-29.03</v>
       </c>
       <c r="O18" t="n">
-        <v/>
+        <v>-32.42</v>
       </c>
       <c r="P18" t="n">
-        <v/>
+        <v>-27.84</v>
       </c>
       <c r="Q18" t="n">
-        <v/>
+        <v>-33.72</v>
       </c>
       <c r="R18" t="n">
-        <v/>
+        <v>-37.94</v>
       </c>
       <c r="S18" t="n">
-        <v/>
+        <v>-41.06</v>
       </c>
       <c r="T18" t="n">
-        <v/>
+        <v>-39.57</v>
       </c>
       <c r="U18" t="n">
-        <v/>
+        <v>-37.97</v>
       </c>
       <c r="V18" t="n">
-        <v/>
+        <v>-34.62</v>
       </c>
       <c r="W18" t="n">
-        <v/>
+        <v>-27.37</v>
       </c>
       <c r="X18" t="n">
-        <v/>
+        <v>-18.67</v>
       </c>
       <c r="Y18" t="n">
-        <v/>
+        <v>-8.84</v>
       </c>
       <c r="Z18" t="n">
-        <v/>
+        <v>-2.62</v>
       </c>
       <c r="AA18" t="n">
-        <v/>
+        <v>2.16</v>
       </c>
       <c r="AB18" t="n">
-        <v/>
+        <v>3.54</v>
       </c>
       <c r="AC18" t="n">
-        <v/>
+        <v>3.64</v>
       </c>
       <c r="AD18" t="n">
-        <v/>
+        <v>-6.67</v>
       </c>
       <c r="AE18" t="n">
-        <v/>
+        <v>-4.83</v>
       </c>
       <c r="AF18" t="n">
-        <v/>
+        <v>-3.13</v>
       </c>
       <c r="AG18" t="n">
-        <v/>
+        <v>-1.15</v>
       </c>
       <c r="AH18" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v/>
+        <v>-9.880000000000001</v>
       </c>
       <c r="AJ18" t="n">
-        <v/>
+        <v>-5.1</v>
       </c>
       <c r="AK18" t="n">
-        <v/>
+        <v>8.550000000000001</v>
       </c>
       <c r="AL18" t="n">
-        <v/>
+        <v>11.73</v>
       </c>
       <c r="AM18" t="n">
-        <v/>
+        <v>18.07</v>
       </c>
       <c r="AN18" t="n">
-        <v/>
+        <v>16.28</v>
       </c>
       <c r="AO18" t="n">
-        <v>31.57</v>
+        <v>9.76</v>
       </c>
       <c r="AP18" t="n">
-        <v>31</v>
+        <v>9.41</v>
       </c>
       <c r="AQ18" t="n">
-        <v>25.54</v>
+        <v>7.47</v>
       </c>
       <c r="AR18" t="n">
-        <v>20.36</v>
+        <v>3.33</v>
       </c>
       <c r="AS18" t="n">
-        <v>13.97</v>
+        <v>-1.65</v>
       </c>
       <c r="AT18" t="n">
-        <v>-2.19</v>
+        <v>-3.76</v>
       </c>
       <c r="AU18" t="n">
-        <v>-13.61</v>
+        <v>5.74</v>
       </c>
       <c r="AV18" t="n">
-        <v>-20.27</v>
+        <v>27.09</v>
       </c>
       <c r="AW18" t="n">
-        <v>-23.14</v>
+        <v>53.97</v>
       </c>
       <c r="AX18" t="n">
-        <v>-30.26</v>
+        <v>63.25</v>
       </c>
       <c r="AY18" t="n">
-        <v>-30.46</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>-29.03</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>-32.42</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>-27.84</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>-33.72</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>-37.94</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>-41.06</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>-39.57</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>-37.97</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>-34.62</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>-27.37</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>-18.67</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>-8.84</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>-2.62</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>-6.67</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>-4.83</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>-3.13</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>-1.15</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>-9.880000000000001</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>11.73</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>18.07</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>16.28</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>9.76</v>
-      </c>
-      <c r="CB18" t="n">
-        <v>9.41</v>
-      </c>
-      <c r="CC18" t="n">
-        <v>7.47</v>
-      </c>
-      <c r="CD18" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="CE18" t="n">
-        <v>-1.65</v>
-      </c>
-      <c r="CF18" t="n">
-        <v>-3.76</v>
-      </c>
-      <c r="CG18" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="CH18" t="n">
-        <v>27.09</v>
-      </c>
-      <c r="CI18" t="n">
-        <v>53.97</v>
-      </c>
-      <c r="CJ18" t="n">
-        <v>63.25</v>
-      </c>
-      <c r="CK18" t="n">
         <v>66.05</v>
       </c>
     </row>
@@ -11834,264 +9782,150 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v/>
+        <v>-16.79</v>
       </c>
       <c r="D19" t="n">
-        <v/>
+        <v>-11.34</v>
       </c>
       <c r="E19" t="n">
-        <v/>
+        <v>4.21</v>
       </c>
       <c r="F19" t="n">
-        <v/>
+        <v>20.98</v>
       </c>
       <c r="G19" t="n">
-        <v/>
+        <v>49.61</v>
       </c>
       <c r="H19" t="n">
-        <v/>
+        <v>58.27</v>
       </c>
       <c r="I19" t="n">
-        <v/>
+        <v>62.91</v>
       </c>
       <c r="J19" t="n">
-        <v/>
+        <v>60.32</v>
       </c>
       <c r="K19" t="n">
-        <v/>
+        <v>55.12</v>
       </c>
       <c r="L19" t="n">
-        <v/>
+        <v>47.11</v>
       </c>
       <c r="M19" t="n">
-        <v/>
+        <v>67.45</v>
       </c>
       <c r="N19" t="n">
-        <v/>
+        <v>81.08</v>
       </c>
       <c r="O19" t="n">
-        <v/>
+        <v>91.34</v>
       </c>
       <c r="P19" t="n">
-        <v/>
+        <v>98.43000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v/>
+        <v>92.81</v>
       </c>
       <c r="R19" t="n">
-        <v/>
+        <v>81.83</v>
       </c>
       <c r="S19" t="n">
-        <v/>
+        <v>71.27</v>
       </c>
       <c r="T19" t="n">
-        <v/>
+        <v>55.65</v>
       </c>
       <c r="U19" t="n">
-        <v/>
+        <v>46.13</v>
       </c>
       <c r="V19" t="n">
-        <v/>
+        <v>34.92</v>
       </c>
       <c r="W19" t="n">
-        <v/>
+        <v>24.07</v>
       </c>
       <c r="X19" t="n">
-        <v/>
+        <v>11.62</v>
       </c>
       <c r="Y19" t="n">
-        <v/>
+        <v>7.63</v>
       </c>
       <c r="Z19" t="n">
-        <v/>
+        <v>6.93</v>
       </c>
       <c r="AA19" t="n">
-        <v/>
+        <v>7.44</v>
       </c>
       <c r="AB19" t="n">
-        <v/>
+        <v>4.49</v>
       </c>
       <c r="AC19" t="n">
-        <v/>
+        <v>0.12</v>
       </c>
       <c r="AD19" t="n">
-        <v/>
+        <v>-11.05</v>
       </c>
       <c r="AE19" t="n">
-        <v/>
+        <v>-25.68</v>
       </c>
       <c r="AF19" t="n">
-        <v/>
+        <v>-49.11</v>
       </c>
       <c r="AG19" t="n">
-        <v/>
+        <v>-50.31</v>
       </c>
       <c r="AH19" t="n">
-        <v/>
+        <v>-49.87</v>
       </c>
       <c r="AI19" t="n">
-        <v/>
+        <v>-48.54</v>
       </c>
       <c r="AJ19" t="n">
-        <v/>
+        <v>-46.39</v>
       </c>
       <c r="AK19" t="n">
-        <v/>
+        <v>-44.61</v>
       </c>
       <c r="AL19" t="n">
-        <v/>
+        <v>-43.26</v>
       </c>
       <c r="AM19" t="n">
-        <v/>
+        <v>-39.89</v>
       </c>
       <c r="AN19" t="n">
-        <v/>
+        <v>-38.07</v>
       </c>
       <c r="AO19" t="n">
-        <v>-16.79</v>
+        <v>-38.15</v>
       </c>
       <c r="AP19" t="n">
-        <v>-11.34</v>
+        <v>-43.21</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4.21</v>
+        <v>-40.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>20.98</v>
+        <v>-39.13</v>
       </c>
       <c r="AS19" t="n">
-        <v>49.61</v>
+        <v>-36.55</v>
       </c>
       <c r="AT19" t="n">
-        <v>58.27</v>
+        <v>-39.13</v>
       </c>
       <c r="AU19" t="n">
-        <v>62.91</v>
+        <v>-40.36</v>
       </c>
       <c r="AV19" t="n">
-        <v>60.32</v>
+        <v>-40.09</v>
       </c>
       <c r="AW19" t="n">
-        <v>55.12</v>
+        <v>-43.42</v>
       </c>
       <c r="AX19" t="n">
-        <v>47.11</v>
+        <v>-32.04</v>
       </c>
       <c r="AY19" t="n">
-        <v>67.45</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>81.08</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>91.34</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>98.43000000000001</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>92.81</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>81.83</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>71.27</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>55.65</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>34.92</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>24.07</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>11.62</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>7.63</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>7.44</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>-11.05</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>-25.68</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>-49.11</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>-50.31</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>-49.87</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>-48.54</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>-46.39</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>-44.61</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>-43.26</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>-39.89</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>-38.07</v>
-      </c>
-      <c r="CA19" t="n">
-        <v>-38.15</v>
-      </c>
-      <c r="CB19" t="n">
-        <v>-43.21</v>
-      </c>
-      <c r="CC19" t="n">
-        <v>-40.5</v>
-      </c>
-      <c r="CD19" t="n">
-        <v>-39.13</v>
-      </c>
-      <c r="CE19" t="n">
-        <v>-36.55</v>
-      </c>
-      <c r="CF19" t="n">
-        <v>-39.13</v>
-      </c>
-      <c r="CG19" t="n">
-        <v>-40.36</v>
-      </c>
-      <c r="CH19" t="n">
-        <v>-40.09</v>
-      </c>
-      <c r="CI19" t="n">
-        <v>-43.42</v>
-      </c>
-      <c r="CJ19" t="n">
-        <v>-32.04</v>
-      </c>
-      <c r="CK19" t="n">
         <v>-17.16</v>
       </c>
     </row>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -7075,7 +7075,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>000000</t>
+          <t>0000Z0</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:AE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -742,6 +742,7 @@
     <col width="10" customWidth="1" min="28" max="28"/>
     <col width="10" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -839,6 +840,9 @@
       <c r="AD1" s="1" t="n">
         <v>20260108</v>
       </c>
+      <c r="AE1" s="1" t="n">
+        <v>20260109</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -935,6 +939,9 @@
       <c r="AD2" t="n">
         <v>60</v>
       </c>
+      <c r="AE2" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1031,6 +1038,9 @@
       <c r="AD3" t="n">
         <v>151</v>
       </c>
+      <c r="AE3" t="n">
+        <v>131</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1127,6 +1137,9 @@
       <c r="AD4" t="n">
         <v>54</v>
       </c>
+      <c r="AE4" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1223,6 +1236,9 @@
       <c r="AD5" t="n">
         <v>72</v>
       </c>
+      <c r="AE5" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1319,6 +1335,9 @@
       <c r="AD6" t="n">
         <v>140</v>
       </c>
+      <c r="AE6" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1415,6 +1434,9 @@
       <c r="AD7" t="n">
         <v>150</v>
       </c>
+      <c r="AE7" t="n">
+        <v>132</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1511,6 +1533,9 @@
       <c r="AD8" t="n">
         <v>161</v>
       </c>
+      <c r="AE8" t="n">
+        <v>139</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1607,6 +1632,9 @@
       <c r="AD9" t="n">
         <v>-78</v>
       </c>
+      <c r="AE9" t="n">
+        <v>-85</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1703,6 +1731,9 @@
       <c r="AD10" t="n">
         <v>99</v>
       </c>
+      <c r="AE10" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1799,6 +1830,9 @@
       <c r="AD11" t="n">
         <v>-57</v>
       </c>
+      <c r="AE11" t="n">
+        <v>-68</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1895,6 +1929,9 @@
       <c r="AD12" t="n">
         <v>-54</v>
       </c>
+      <c r="AE12" t="n">
+        <v>-66</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1991,6 +2028,9 @@
       <c r="AD13" t="n">
         <v>-42</v>
       </c>
+      <c r="AE13" t="n">
+        <v>-62</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2087,6 +2127,9 @@
       <c r="AD14" t="n">
         <v>-77</v>
       </c>
+      <c r="AE14" t="n">
+        <v>-85</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2183,6 +2226,9 @@
       <c r="AD15" t="n">
         <v>62</v>
       </c>
+      <c r="AE15" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2279,6 +2325,9 @@
       <c r="AD16" t="n">
         <v>-60</v>
       </c>
+      <c r="AE16" t="n">
+        <v>-74</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2375,6 +2424,9 @@
       <c r="AD17" t="n">
         <v>-69</v>
       </c>
+      <c r="AE17" t="n">
+        <v>-78</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2471,6 +2523,9 @@
       <c r="AD18" t="n">
         <v>105</v>
       </c>
+      <c r="AE18" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2566,6 +2621,9 @@
       </c>
       <c r="AD19" t="n">
         <v>61</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2579,7 +2637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR19"/>
+  <dimension ref="A1:BS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2652,6 +2710,7 @@
     <col width="12" customWidth="1" min="68" max="68"/>
     <col width="12" customWidth="1" min="69" max="69"/>
     <col width="12" customWidth="1" min="70" max="70"/>
+    <col width="12" customWidth="1" min="71" max="71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3005,6 +3064,11 @@
           <t>20260108</t>
         </is>
       </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>20260109</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3221,6 +3285,9 @@
       <c r="BR2" t="n">
         <v>106</v>
       </c>
+      <c r="BS2" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3437,6 +3504,9 @@
       <c r="BR3" t="n">
         <v>116</v>
       </c>
+      <c r="BS3" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3653,6 +3723,9 @@
       <c r="BR4" t="n">
         <v>105</v>
       </c>
+      <c r="BS4" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3869,6 +3942,9 @@
       <c r="BR5" t="n">
         <v>106</v>
       </c>
+      <c r="BS5" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4085,6 +4161,9 @@
       <c r="BR6" t="n">
         <v>114</v>
       </c>
+      <c r="BS6" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4301,6 +4380,9 @@
       <c r="BR7" t="n">
         <v>116</v>
       </c>
+      <c r="BS7" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4517,6 +4599,9 @@
       <c r="BR8" t="n">
         <v>120</v>
       </c>
+      <c r="BS8" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4733,6 +4818,9 @@
       <c r="BR9" t="n">
         <v>88</v>
       </c>
+      <c r="BS9" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4949,6 +5037,9 @@
       <c r="BR10" t="n">
         <v>108</v>
       </c>
+      <c r="BS10" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5165,6 +5256,9 @@
       <c r="BR11" t="n">
         <v>92</v>
       </c>
+      <c r="BS11" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5381,6 +5475,9 @@
       <c r="BR12" t="n">
         <v>92</v>
       </c>
+      <c r="BS12" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5597,6 +5694,9 @@
       <c r="BR13" t="n">
         <v>92</v>
       </c>
+      <c r="BS13" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5813,6 +5913,9 @@
       <c r="BR14" t="n">
         <v>85</v>
       </c>
+      <c r="BS14" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6029,6 +6132,9 @@
       <c r="BR15" t="n">
         <v>106</v>
       </c>
+      <c r="BS15" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6245,6 +6351,9 @@
       <c r="BR16" t="n">
         <v>93</v>
       </c>
+      <c r="BS16" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6461,6 +6570,9 @@
       <c r="BR17" t="n">
         <v>92</v>
       </c>
+      <c r="BS17" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6677,6 +6789,9 @@
       <c r="BR18" t="n">
         <v>109</v>
       </c>
+      <c r="BS18" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6892,6 +7007,9 @@
       </c>
       <c r="BR19" t="n">
         <v>104</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -6905,16 +7023,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="52" max="52"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>종목코드</t>
         </is>
@@ -7065,6 +7188,11 @@
       </c>
       <c r="AY1" t="n">
         <v>20260108</v>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>20260109</t>
+        </is>
       </c>
     </row>
     <row r="2">
@@ -7225,6 +7353,9 @@
       <c r="AY2" t="n">
         <v>-4.14</v>
       </c>
+      <c r="AZ2" t="n">
+        <v>4.15</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7384,6 +7515,9 @@
       <c r="AY3" t="n">
         <v>146.46</v>
       </c>
+      <c r="AZ3" t="n">
+        <v>139.52</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7543,6 +7677,9 @@
       <c r="AY4" t="n">
         <v>-11.27</v>
       </c>
+      <c r="AZ4" t="n">
+        <v>-2.26</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7702,6 +7839,9 @@
       <c r="AY5" t="n">
         <v>72.95999999999999</v>
       </c>
+      <c r="AZ5" t="n">
+        <v>68.81999999999999</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7861,6 +8001,9 @@
       <c r="AY6" t="n">
         <v>130.33</v>
       </c>
+      <c r="AZ6" t="n">
+        <v>124.13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8020,6 +8163,9 @@
       <c r="AY7" t="n">
         <v>132.93</v>
       </c>
+      <c r="AZ7" t="n">
+        <v>128.69</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8179,6 +8325,9 @@
       <c r="AY8" t="n">
         <v>166.2</v>
       </c>
+      <c r="AZ8" t="n">
+        <v>155.87</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8338,6 +8487,9 @@
       <c r="AY9" t="n">
         <v>33.61</v>
       </c>
+      <c r="AZ9" t="n">
+        <v>25.99</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8497,6 +8649,9 @@
       <c r="AY10" t="n">
         <v>64.95</v>
       </c>
+      <c r="AZ10" t="n">
+        <v>61.57</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8656,6 +8811,9 @@
       <c r="AY11" t="n">
         <v>17.15</v>
       </c>
+      <c r="AZ11" t="n">
+        <v>10.2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8815,6 +8973,9 @@
       <c r="AY12" t="n">
         <v>17.01</v>
       </c>
+      <c r="AZ12" t="n">
+        <v>9.539999999999999</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8974,6 +9135,9 @@
       <c r="AY13" t="n">
         <v>6.24</v>
       </c>
+      <c r="AZ13" t="n">
+        <v>1.41</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9133,6 +9297,9 @@
       <c r="AY14" t="n">
         <v>32.14</v>
       </c>
+      <c r="AZ14" t="n">
+        <v>24.47</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9292,6 +9459,9 @@
       <c r="AY15" t="n">
         <v>-8.68</v>
       </c>
+      <c r="AZ15" t="n">
+        <v>3.08</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9451,6 +9621,9 @@
       <c r="AY16" t="n">
         <v>21.16</v>
       </c>
+      <c r="AZ16" t="n">
+        <v>13.49</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9610,6 +9783,9 @@
       <c r="AY17" t="n">
         <v>25.4</v>
       </c>
+      <c r="AZ17" t="n">
+        <v>17.24</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9769,6 +9945,9 @@
       <c r="AY18" t="n">
         <v>66.05</v>
       </c>
+      <c r="AZ18" t="n">
+        <v>64.81</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9927,6 +10106,9 @@
       </c>
       <c r="AY19" t="n">
         <v>-17.16</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>-3.3</v>
       </c>
     </row>
   </sheetData>
@@ -9940,7 +10122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:AE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9973,6 +10155,7 @@
     <col width="12" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10126,6 +10309,11 @@
           <t>20260108</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>20260109</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10222,6 +10410,9 @@
       <c r="AD2" t="n">
         <v>75</v>
       </c>
+      <c r="AE2" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10318,6 +10509,9 @@
       <c r="AD3" t="n">
         <v>79</v>
       </c>
+      <c r="AE3" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10414,6 +10608,9 @@
       <c r="AD4" t="n">
         <v>38</v>
       </c>
+      <c r="AE4" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10510,6 +10707,9 @@
       <c r="AD5" t="n">
         <v>24</v>
       </c>
+      <c r="AE5" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10606,6 +10806,9 @@
       <c r="AD6" t="n">
         <v>135</v>
       </c>
+      <c r="AE6" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10702,6 +10905,9 @@
       <c r="AD7" t="n">
         <v>63</v>
       </c>
+      <c r="AE7" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10798,6 +11004,9 @@
       <c r="AD8" t="n">
         <v>113</v>
       </c>
+      <c r="AE8" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10894,6 +11103,9 @@
       <c r="AD9" t="n">
         <v>23</v>
       </c>
+      <c r="AE9" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10990,6 +11202,9 @@
       <c r="AD10" t="n">
         <v>74</v>
       </c>
+      <c r="AE10" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11086,6 +11301,9 @@
       <c r="AD11" t="n">
         <v>13</v>
       </c>
+      <c r="AE11" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11182,6 +11400,9 @@
       <c r="AD12" t="n">
         <v>17</v>
       </c>
+      <c r="AE12" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11278,6 +11499,9 @@
       <c r="AD13" t="n">
         <v>19</v>
       </c>
+      <c r="AE13" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11374,6 +11598,9 @@
       <c r="AD14" t="n">
         <v>22</v>
       </c>
+      <c r="AE14" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11470,6 +11697,9 @@
       <c r="AD15" t="n">
         <v>48</v>
       </c>
+      <c r="AE15" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11566,6 +11796,9 @@
       <c r="AD16" t="n">
         <v>19</v>
       </c>
+      <c r="AE16" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11662,6 +11895,9 @@
       <c r="AD17" t="n">
         <v>6</v>
       </c>
+      <c r="AE17" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11758,6 +11994,9 @@
       <c r="AD18" t="n">
         <v>33</v>
       </c>
+      <c r="AE18" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11853,6 +12092,9 @@
       </c>
       <c r="AD19" t="n">
         <v>37</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -11866,7 +12108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK19"/>
+  <dimension ref="A1:CL19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11958,6 +12200,7 @@
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
+    <col width="12" customWidth="1" min="90" max="90"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12232,6 +12475,9 @@
       <c r="CK1" s="1" t="n">
         <v>20260108</v>
       </c>
+      <c r="CL1" s="1" t="n">
+        <v>20260109</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12505,6 +12751,9 @@
       <c r="CK2" t="n">
         <v>16285</v>
       </c>
+      <c r="CL2" t="n">
+        <v>16320</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12778,6 +13027,9 @@
       <c r="CK3" t="n">
         <v>69690</v>
       </c>
+      <c r="CL3" t="n">
+        <v>69770</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13051,6 +13303,9 @@
       <c r="CK4" t="n">
         <v>18750</v>
       </c>
+      <c r="CL4" t="n">
+        <v>18860</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13324,6 +13579,9 @@
       <c r="CK5" t="n">
         <v>17135</v>
       </c>
+      <c r="CL5" t="n">
+        <v>16875</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13597,6 +13855,9 @@
       <c r="CK6" t="n">
         <v>19995</v>
       </c>
+      <c r="CL6" t="n">
+        <v>19935</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13870,6 +14131,9 @@
       <c r="CK7" t="n">
         <v>23715</v>
       </c>
+      <c r="CL7" t="n">
+        <v>23710</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14143,6 +14407,9 @@
       <c r="CK8" t="n">
         <v>23290</v>
       </c>
+      <c r="CL8" t="n">
+        <v>23320</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14416,6 +14683,9 @@
       <c r="CK9" t="n">
         <v>1228</v>
       </c>
+      <c r="CL9" t="n">
+        <v>1210</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14689,6 +14959,9 @@
       <c r="CK10" t="n">
         <v>18410</v>
       </c>
+      <c r="CL10" t="n">
+        <v>18255</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14962,6 +15235,9 @@
       <c r="CK11" t="n">
         <v>4850</v>
       </c>
+      <c r="CL11" t="n">
+        <v>4800</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15235,6 +15511,9 @@
       <c r="CK12" t="n">
         <v>5170</v>
       </c>
+      <c r="CL12" t="n">
+        <v>5130</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15508,6 +15787,9 @@
       <c r="CK13" t="n">
         <v>5240</v>
       </c>
+      <c r="CL13" t="n">
+        <v>5250</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -15781,6 +16063,9 @@
       <c r="CK14" t="n">
         <v>1276</v>
       </c>
+      <c r="CL14" t="n">
+        <v>1280</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -16054,6 +16339,9 @@
       <c r="CK15" t="n">
         <v>20345</v>
       </c>
+      <c r="CL15" t="n">
+        <v>20470</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -16327,6 +16615,9 @@
       <c r="CK16" t="n">
         <v>9895</v>
       </c>
+      <c r="CL16" t="n">
+        <v>9820</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16600,6 +16891,9 @@
       <c r="CK17" t="n">
         <v>5695</v>
       </c>
+      <c r="CL17" t="n">
+        <v>5655</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16873,6 +17167,9 @@
       <c r="CK18" t="n">
         <v>19915</v>
       </c>
+      <c r="CL18" t="n">
+        <v>19795</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17145,6 +17442,9 @@
       </c>
       <c r="CK19" t="n">
         <v>16845</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>16875</v>
       </c>
     </row>
   </sheetData>
@@ -17158,7 +17458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK19"/>
+  <dimension ref="A1:CL19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17250,6 +17550,7 @@
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
+    <col width="12" customWidth="1" min="90" max="90"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17524,6 +17825,9 @@
       <c r="CK1" s="1" t="n">
         <v>20260108</v>
       </c>
+      <c r="CL1" s="1" t="n">
+        <v>20260109</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17797,6 +18101,9 @@
       <c r="CK2" t="n">
         <v>16395</v>
       </c>
+      <c r="CL2" t="n">
+        <v>16345</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18070,6 +18377,9 @@
       <c r="CK3" t="n">
         <v>72965</v>
       </c>
+      <c r="CL3" t="n">
+        <v>70465</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18343,6 +18653,9 @@
       <c r="CK4" t="n">
         <v>18945</v>
       </c>
+      <c r="CL4" t="n">
+        <v>19030</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18616,6 +18929,9 @@
       <c r="CK5" t="n">
         <v>17800</v>
       </c>
+      <c r="CL5" t="n">
+        <v>17170</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18889,6 +19205,9 @@
       <c r="CK6" t="n">
         <v>20880</v>
       </c>
+      <c r="CL6" t="n">
+        <v>20150</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19162,6 +19481,9 @@
       <c r="CK7" t="n">
         <v>24955</v>
       </c>
+      <c r="CL7" t="n">
+        <v>24065</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19435,6 +19757,9 @@
       <c r="CK8" t="n">
         <v>24575</v>
       </c>
+      <c r="CL8" t="n">
+        <v>23630</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19708,6 +20033,9 @@
       <c r="CK9" t="n">
         <v>1249</v>
       </c>
+      <c r="CL9" t="n">
+        <v>1214</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19981,6 +20309,9 @@
       <c r="CK10" t="n">
         <v>19185</v>
       </c>
+      <c r="CL10" t="n">
+        <v>18365</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -20254,6 +20585,9 @@
       <c r="CK11" t="n">
         <v>4910</v>
       </c>
+      <c r="CL11" t="n">
+        <v>4850</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -20527,6 +20861,9 @@
       <c r="CK12" t="n">
         <v>5255</v>
       </c>
+      <c r="CL12" t="n">
+        <v>5185</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -20800,6 +21137,9 @@
       <c r="CK13" t="n">
         <v>5335</v>
       </c>
+      <c r="CL13" t="n">
+        <v>5255</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -21073,6 +21413,9 @@
       <c r="CK14" t="n">
         <v>1310</v>
       </c>
+      <c r="CL14" t="n">
+        <v>1282</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -21346,6 +21689,9 @@
       <c r="CK15" t="n">
         <v>20595</v>
       </c>
+      <c r="CL15" t="n">
+        <v>20555</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -21619,6 +21965,9 @@
       <c r="CK16" t="n">
         <v>9970</v>
       </c>
+      <c r="CL16" t="n">
+        <v>9875</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -21892,6 +22241,9 @@
       <c r="CK17" t="n">
         <v>5750</v>
       </c>
+      <c r="CL17" t="n">
+        <v>5695</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -22165,6 +22517,9 @@
       <c r="CK18" t="n">
         <v>20865</v>
       </c>
+      <c r="CL18" t="n">
+        <v>19950</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -22437,6 +22792,9 @@
       </c>
       <c r="CK19" t="n">
         <v>16920</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>16885</v>
       </c>
     </row>
   </sheetData>
@@ -22450,7 +22808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK19"/>
+  <dimension ref="A1:CL19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22542,6 +22900,7 @@
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
+    <col width="12" customWidth="1" min="90" max="90"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22816,6 +23175,9 @@
       <c r="CK1" s="1" t="n">
         <v>20260108</v>
       </c>
+      <c r="CL1" s="1" t="n">
+        <v>20260109</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23089,6 +23451,9 @@
       <c r="CK2" t="n">
         <v>16020</v>
       </c>
+      <c r="CL2" t="n">
+        <v>15975</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23362,6 +23727,9 @@
       <c r="CK3" t="n">
         <v>69220</v>
       </c>
+      <c r="CL3" t="n">
+        <v>68080</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23635,6 +24003,9 @@
       <c r="CK4" t="n">
         <v>18595</v>
       </c>
+      <c r="CL4" t="n">
+        <v>18580</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23908,6 +24279,9 @@
       <c r="CK5" t="n">
         <v>17115</v>
       </c>
+      <c r="CL5" t="n">
+        <v>16650</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24181,6 +24555,9 @@
       <c r="CK6" t="n">
         <v>19945</v>
       </c>
+      <c r="CL6" t="n">
+        <v>19510</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24454,6 +24831,9 @@
       <c r="CK7" t="n">
         <v>23655</v>
       </c>
+      <c r="CL7" t="n">
+        <v>23265</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24727,6 +25107,9 @@
       <c r="CK8" t="n">
         <v>23285</v>
       </c>
+      <c r="CL8" t="n">
+        <v>22825</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25000,6 +25383,9 @@
       <c r="CK9" t="n">
         <v>1171</v>
       </c>
+      <c r="CL9" t="n">
+        <v>1164</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25273,6 +25659,9 @@
       <c r="CK10" t="n">
         <v>18345</v>
       </c>
+      <c r="CL10" t="n">
+        <v>17825</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25546,6 +25935,9 @@
       <c r="CK11" t="n">
         <v>4785</v>
       </c>
+      <c r="CL11" t="n">
+        <v>4710</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25819,6 +26211,9 @@
       <c r="CK12" t="n">
         <v>5110</v>
       </c>
+      <c r="CL12" t="n">
+        <v>5025</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -26092,6 +26487,9 @@
       <c r="CK13" t="n">
         <v>5170</v>
       </c>
+      <c r="CL13" t="n">
+        <v>5055</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -26365,6 +26763,9 @@
       <c r="CK14" t="n">
         <v>1248</v>
       </c>
+      <c r="CL14" t="n">
+        <v>1220</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -26638,6 +27039,9 @@
       <c r="CK15" t="n">
         <v>20060</v>
       </c>
+      <c r="CL15" t="n">
+        <v>20050</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -26911,6 +27315,9 @@
       <c r="CK16" t="n">
         <v>9750</v>
       </c>
+      <c r="CL16" t="n">
+        <v>9605</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -27184,6 +27591,9 @@
       <c r="CK17" t="n">
         <v>5635</v>
       </c>
+      <c r="CL17" t="n">
+        <v>5560</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -27457,6 +27867,9 @@
       <c r="CK18" t="n">
         <v>19825</v>
       </c>
+      <c r="CL18" t="n">
+        <v>19265</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -27729,6 +28142,9 @@
       </c>
       <c r="CK19" t="n">
         <v>16570</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>16630</v>
       </c>
     </row>
   </sheetData>
@@ -27742,7 +28158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK19"/>
+  <dimension ref="A1:CL19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27834,6 +28250,7 @@
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
+    <col width="12" customWidth="1" min="90" max="90"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28108,6 +28525,9 @@
       <c r="CK1" s="1" t="n">
         <v>20260108</v>
       </c>
+      <c r="CL1" s="1" t="n">
+        <v>20260109</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28381,6 +28801,9 @@
       <c r="CK2" t="n">
         <v>16270</v>
       </c>
+      <c r="CL2" t="n">
+        <v>16270</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28654,6 +29077,9 @@
       <c r="CK3" t="n">
         <v>70160</v>
       </c>
+      <c r="CL3" t="n">
+        <v>69305</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28927,6 +29353,9 @@
       <c r="CK4" t="n">
         <v>18860</v>
       </c>
+      <c r="CL4" t="n">
+        <v>19015</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29200,6 +29629,9 @@
       <c r="CK5" t="n">
         <v>17115</v>
       </c>
+      <c r="CL5" t="n">
+        <v>16810</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29473,6 +29905,9 @@
       <c r="CK6" t="n">
         <v>20150</v>
       </c>
+      <c r="CL6" t="n">
+        <v>19845</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29746,6 +30181,9 @@
       <c r="CK7" t="n">
         <v>24030</v>
       </c>
+      <c r="CL7" t="n">
+        <v>23720</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30019,6 +30457,9 @@
       <c r="CK8" t="n">
         <v>23670</v>
       </c>
+      <c r="CL8" t="n">
+        <v>23310</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30292,6 +30733,9 @@
       <c r="CK9" t="n">
         <v>1202</v>
       </c>
+      <c r="CL9" t="n">
+        <v>1175</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30565,6 +31009,9 @@
       <c r="CK10" t="n">
         <v>18450</v>
       </c>
+      <c r="CL10" t="n">
+        <v>18060</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30838,6 +31285,9 @@
       <c r="CK11" t="n">
         <v>4795</v>
       </c>
+      <c r="CL11" t="n">
+        <v>4765</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31111,6 +31561,9 @@
       <c r="CK12" t="n">
         <v>5130</v>
       </c>
+      <c r="CL12" t="n">
+        <v>5085</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31384,6 +31837,9 @@
       <c r="CK13" t="n">
         <v>5205</v>
       </c>
+      <c r="CL13" t="n">
+        <v>5085</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31657,6 +32113,9 @@
       <c r="CK14" t="n">
         <v>1260</v>
       </c>
+      <c r="CL14" t="n">
+        <v>1234</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -31930,6 +32389,9 @@
       <c r="CK15" t="n">
         <v>20470</v>
       </c>
+      <c r="CL15" t="n">
+        <v>20555</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -32203,6 +32665,9 @@
       <c r="CK16" t="n">
         <v>9795</v>
       </c>
+      <c r="CL16" t="n">
+        <v>9670</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -32476,6 +32941,9 @@
       <c r="CK17" t="n">
         <v>5675</v>
       </c>
+      <c r="CL17" t="n">
+        <v>5635</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -32749,6 +33217,9 @@
       <c r="CK18" t="n">
         <v>19890</v>
       </c>
+      <c r="CL18" t="n">
+        <v>19640</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -33021,6 +33492,9 @@
       </c>
       <c r="CK19" t="n">
         <v>16780</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>16885</v>
       </c>
     </row>
   </sheetData>
@@ -33034,7 +33508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK19"/>
+  <dimension ref="A1:CL19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33126,6 +33600,7 @@
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
+    <col width="12" customWidth="1" min="90" max="90"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33400,6 +33875,9 @@
       <c r="CK1" s="1" t="n">
         <v>20260108</v>
       </c>
+      <c r="CL1" s="1" t="n">
+        <v>20260109</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33673,6 +34151,9 @@
       <c r="CK2" t="n">
         <v>204622</v>
       </c>
+      <c r="CL2" t="n">
+        <v>178544</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -33946,6 +34427,9 @@
       <c r="CK3" t="n">
         <v>3860480</v>
       </c>
+      <c r="CL3" t="n">
+        <v>3307668</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34219,6 +34703,9 @@
       <c r="CK4" t="n">
         <v>137034</v>
       </c>
+      <c r="CL4" t="n">
+        <v>138828</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34492,6 +34979,9 @@
       <c r="CK5" t="n">
         <v>294110</v>
       </c>
+      <c r="CL5" t="n">
+        <v>206474</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34765,6 +35255,9 @@
       <c r="CK6" t="n">
         <v>6346827</v>
       </c>
+      <c r="CL6" t="n">
+        <v>7490230</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35038,6 +35531,9 @@
       <c r="CK7" t="n">
         <v>5095519</v>
       </c>
+      <c r="CL7" t="n">
+        <v>5074958</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -35311,6 +35807,9 @@
       <c r="CK8" t="n">
         <v>17910007</v>
       </c>
+      <c r="CL8" t="n">
+        <v>15549015</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35584,6 +36083,9 @@
       <c r="CK9" t="n">
         <v>3606225</v>
       </c>
+      <c r="CL9" t="n">
+        <v>2943038</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35857,6 +36359,9 @@
       <c r="CK10" t="n">
         <v>2021510</v>
       </c>
+      <c r="CL10" t="n">
+        <v>1925427</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -36130,6 +36635,9 @@
       <c r="CK11" t="n">
         <v>353004</v>
       </c>
+      <c r="CL11" t="n">
+        <v>499786</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -36403,6 +36911,9 @@
       <c r="CK12" t="n">
         <v>1005697</v>
       </c>
+      <c r="CL12" t="n">
+        <v>1087673</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36676,6 +37187,9 @@
       <c r="CK13" t="n">
         <v>2788144</v>
       </c>
+      <c r="CL13" t="n">
+        <v>4394758</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36949,6 +37463,9 @@
       <c r="CK14" t="n">
         <v>22944248</v>
       </c>
+      <c r="CL14" t="n">
+        <v>24136049</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37222,6 +37739,9 @@
       <c r="CK15" t="n">
         <v>1754364</v>
       </c>
+      <c r="CL15" t="n">
+        <v>1161284</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -37495,6 +38015,9 @@
       <c r="CK16" t="n">
         <v>234753</v>
       </c>
+      <c r="CL16" t="n">
+        <v>156755</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37768,6 +38291,9 @@
       <c r="CK17" t="n">
         <v>26884</v>
       </c>
+      <c r="CL17" t="n">
+        <v>19814</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -38041,6 +38567,9 @@
       <c r="CK18" t="n">
         <v>117365</v>
       </c>
+      <c r="CL18" t="n">
+        <v>202729</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -38313,6 +38842,9 @@
       </c>
       <c r="CK19" t="n">
         <v>35618</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>33801</v>
       </c>
     </row>
   </sheetData>
@@ -38326,7 +38858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR19"/>
+  <dimension ref="A1:BS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -38399,6 +38931,7 @@
     <col width="10" customWidth="1" min="68" max="68"/>
     <col width="10" customWidth="1" min="69" max="69"/>
     <col width="10" customWidth="1" min="70" max="70"/>
+    <col width="10" customWidth="1" min="71" max="71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38616,6 +39149,9 @@
       <c r="BR1" s="1" t="n">
         <v>20260108</v>
       </c>
+      <c r="BS1" s="1" t="n">
+        <v>20260109</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -38832,6 +39368,9 @@
       <c r="BR2" t="n">
         <v>100</v>
       </c>
+      <c r="BS2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -39048,6 +39587,9 @@
       <c r="BR3" t="n">
         <v>96</v>
       </c>
+      <c r="BS3" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -39264,6 +39806,9 @@
       <c r="BR4" t="n">
         <v>100</v>
       </c>
+      <c r="BS4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -39480,6 +40025,9 @@
       <c r="BR5" t="n">
         <v>80</v>
       </c>
+      <c r="BS5" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -39696,6 +40244,9 @@
       <c r="BR6" t="n">
         <v>96</v>
       </c>
+      <c r="BS6" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -39912,6 +40463,9 @@
       <c r="BR7" t="n">
         <v>100</v>
       </c>
+      <c r="BS7" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40128,6 +40682,9 @@
       <c r="BR8" t="n">
         <v>100</v>
       </c>
+      <c r="BS8" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -40344,6 +40901,9 @@
       <c r="BR9" t="n">
         <v>7</v>
       </c>
+      <c r="BS9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -40560,6 +41120,9 @@
       <c r="BR10" t="n">
         <v>80</v>
       </c>
+      <c r="BS10" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -40776,6 +41339,9 @@
       <c r="BR11" t="n">
         <v>4</v>
       </c>
+      <c r="BS11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -40992,6 +41558,9 @@
       <c r="BR12" t="n">
         <v>9</v>
       </c>
+      <c r="BS12" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -41208,6 +41777,9 @@
       <c r="BR13" t="n">
         <v>9</v>
       </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -41424,6 +41996,9 @@
       <c r="BR14" t="n">
         <v>5</v>
       </c>
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41640,6 +42215,9 @@
       <c r="BR15" t="n">
         <v>100</v>
       </c>
+      <c r="BS15" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -41856,6 +42434,9 @@
       <c r="BR16" t="n">
         <v>11</v>
       </c>
+      <c r="BS16" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42072,6 +42653,9 @@
       <c r="BR17" t="n">
         <v>8</v>
       </c>
+      <c r="BS17" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42288,6 +42872,9 @@
       <c r="BR18" t="n">
         <v>83</v>
       </c>
+      <c r="BS18" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42502,6 +43089,9 @@
         <v>100</v>
       </c>
       <c r="BR19" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS19" t="n">
         <v>100</v>
       </c>
     </row>
@@ -42516,7 +43106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:AE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -42549,6 +43139,7 @@
     <col width="10" customWidth="1" min="28" max="28"/>
     <col width="10" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -42646,6 +43237,9 @@
       <c r="AD1" s="1" t="n">
         <v>20260108</v>
       </c>
+      <c r="AE1" s="1" t="n">
+        <v>20260109</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -42742,6 +43336,9 @@
       <c r="AD2" t="n">
         <v>92</v>
       </c>
+      <c r="AE2" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -42838,6 +43435,9 @@
       <c r="AD3" t="n">
         <v>97</v>
       </c>
+      <c r="AE3" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -42934,6 +43534,9 @@
       <c r="AD4" t="n">
         <v>88</v>
       </c>
+      <c r="AE4" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -43030,6 +43633,9 @@
       <c r="AD5" t="n">
         <v>80</v>
       </c>
+      <c r="AE5" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -43126,6 +43732,9 @@
       <c r="AD6" t="n">
         <v>97</v>
       </c>
+      <c r="AE6" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -43222,6 +43831,9 @@
       <c r="AD7" t="n">
         <v>100</v>
       </c>
+      <c r="AE7" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -43318,6 +43930,9 @@
       <c r="AD8" t="n">
         <v>100</v>
       </c>
+      <c r="AE8" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -43414,6 +44029,9 @@
       <c r="AD9" t="n">
         <v>6</v>
       </c>
+      <c r="AE9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -43510,6 +44128,9 @@
       <c r="AD10" t="n">
         <v>80</v>
       </c>
+      <c r="AE10" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -43606,6 +44227,9 @@
       <c r="AD11" t="n">
         <v>42</v>
       </c>
+      <c r="AE11" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -43702,6 +44326,9 @@
       <c r="AD12" t="n">
         <v>43</v>
       </c>
+      <c r="AE12" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -43798,6 +44425,9 @@
       <c r="AD13" t="n">
         <v>46</v>
       </c>
+      <c r="AE13" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -43894,6 +44524,9 @@
       <c r="AD14" t="n">
         <v>14</v>
       </c>
+      <c r="AE14" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -43990,6 +44623,9 @@
       <c r="AD15" t="n">
         <v>100</v>
       </c>
+      <c r="AE15" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -44086,6 +44722,9 @@
       <c r="AD16" t="n">
         <v>36</v>
       </c>
+      <c r="AE16" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -44182,6 +44821,9 @@
       <c r="AD17" t="n">
         <v>29</v>
       </c>
+      <c r="AE17" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -44278,6 +44920,9 @@
       <c r="AD18" t="n">
         <v>88</v>
       </c>
+      <c r="AE18" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -44372,6 +45017,9 @@
         <v>96</v>
       </c>
       <c r="AD19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE19" t="n">
         <v>100</v>
       </c>
     </row>
@@ -44386,7 +45034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR19"/>
+  <dimension ref="A1:BS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -44459,6 +45107,7 @@
     <col width="10" customWidth="1" min="68" max="68"/>
     <col width="10" customWidth="1" min="69" max="69"/>
     <col width="10" customWidth="1" min="70" max="70"/>
+    <col width="10" customWidth="1" min="71" max="71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -44676,6 +45325,9 @@
       <c r="BR1" s="1" t="n">
         <v>20260108</v>
       </c>
+      <c r="BS1" s="1" t="n">
+        <v>20260109</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -44892,6 +45544,9 @@
       <c r="BR2" t="n">
         <v>104</v>
       </c>
+      <c r="BS2" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -45108,6 +45763,9 @@
       <c r="BR3" t="n">
         <v>89</v>
       </c>
+      <c r="BS3" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -45324,6 +45982,9 @@
       <c r="BR4" t="n">
         <v>92</v>
       </c>
+      <c r="BS4" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -45540,6 +46201,9 @@
       <c r="BR5" t="n">
         <v>59</v>
       </c>
+      <c r="BS5" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -45756,6 +46420,9 @@
       <c r="BR6" t="n">
         <v>86</v>
       </c>
+      <c r="BS6" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -45972,6 +46639,9 @@
       <c r="BR7" t="n">
         <v>93</v>
       </c>
+      <c r="BS7" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -46188,6 +46858,9 @@
       <c r="BR8" t="n">
         <v>93</v>
       </c>
+      <c r="BS8" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -46404,6 +47077,9 @@
       <c r="BR9" t="n">
         <v>-53</v>
       </c>
+      <c r="BS9" t="n">
+        <v>-57</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -46620,6 +47296,9 @@
       <c r="BR10" t="n">
         <v>69</v>
       </c>
+      <c r="BS10" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -46836,6 +47515,9 @@
       <c r="BR11" t="n">
         <v>-61</v>
       </c>
+      <c r="BS11" t="n">
+        <v>-61</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -47052,6 +47734,9 @@
       <c r="BR12" t="n">
         <v>-55</v>
       </c>
+      <c r="BS12" t="n">
+        <v>-56</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -47268,6 +47953,9 @@
       <c r="BR13" t="n">
         <v>-55</v>
       </c>
+      <c r="BS13" t="n">
+        <v>-65</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -47484,6 +48172,9 @@
       <c r="BR14" t="n">
         <v>-56</v>
       </c>
+      <c r="BS14" t="n">
+        <v>-58</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -47700,6 +48391,9 @@
       <c r="BR15" t="n">
         <v>110</v>
       </c>
+      <c r="BS15" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -47916,6 +48610,9 @@
       <c r="BR16" t="n">
         <v>-52</v>
       </c>
+      <c r="BS16" t="n">
+        <v>-57</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -48132,6 +48829,9 @@
       <c r="BR17" t="n">
         <v>-56</v>
       </c>
+      <c r="BS17" t="n">
+        <v>-56</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -48348,6 +49048,9 @@
       <c r="BR18" t="n">
         <v>73</v>
       </c>
+      <c r="BS18" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -48563,6 +49266,9 @@
       </c>
       <c r="BR19" t="n">
         <v>111</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -34428,7 +34428,7 @@
         <v>3860480</v>
       </c>
       <c r="CL3" t="n">
-        <v>3307668</v>
+        <v>3475134</v>
       </c>
     </row>
     <row r="4">
@@ -34704,7 +34704,7 @@
         <v>137034</v>
       </c>
       <c r="CL4" t="n">
-        <v>138828</v>
+        <v>138831</v>
       </c>
     </row>
     <row r="5">
@@ -34980,7 +34980,7 @@
         <v>294110</v>
       </c>
       <c r="CL5" t="n">
-        <v>206474</v>
+        <v>211259</v>
       </c>
     </row>
     <row r="6">
@@ -35256,7 +35256,7 @@
         <v>6346827</v>
       </c>
       <c r="CL6" t="n">
-        <v>7490230</v>
+        <v>7491943</v>
       </c>
     </row>
     <row r="7">
@@ -35532,7 +35532,7 @@
         <v>5095519</v>
       </c>
       <c r="CL7" t="n">
-        <v>5074958</v>
+        <v>5106090</v>
       </c>
     </row>
     <row r="8">
@@ -35808,7 +35808,7 @@
         <v>17910007</v>
       </c>
       <c r="CL8" t="n">
-        <v>15549015</v>
+        <v>17709113</v>
       </c>
     </row>
     <row r="9">
@@ -36084,7 +36084,7 @@
         <v>3606225</v>
       </c>
       <c r="CL9" t="n">
-        <v>2943038</v>
+        <v>2948185</v>
       </c>
     </row>
     <row r="10">
@@ -36360,7 +36360,7 @@
         <v>2021510</v>
       </c>
       <c r="CL10" t="n">
-        <v>1925427</v>
+        <v>1926448</v>
       </c>
     </row>
     <row r="11">
@@ -36636,7 +36636,7 @@
         <v>353004</v>
       </c>
       <c r="CL11" t="n">
-        <v>499786</v>
+        <v>499800</v>
       </c>
     </row>
     <row r="12">
@@ -36912,7 +36912,7 @@
         <v>1005697</v>
       </c>
       <c r="CL12" t="n">
-        <v>1087673</v>
+        <v>1091306</v>
       </c>
     </row>
     <row r="13">
@@ -37188,7 +37188,7 @@
         <v>2788144</v>
       </c>
       <c r="CL13" t="n">
-        <v>4394758</v>
+        <v>4396701</v>
       </c>
     </row>
     <row r="14">
@@ -37464,7 +37464,7 @@
         <v>22944248</v>
       </c>
       <c r="CL14" t="n">
-        <v>24136049</v>
+        <v>24175445</v>
       </c>
     </row>
     <row r="15">
@@ -37740,7 +37740,7 @@
         <v>1754364</v>
       </c>
       <c r="CL15" t="n">
-        <v>1161284</v>
+        <v>1162621</v>
       </c>
     </row>
     <row r="16">
@@ -38568,7 +38568,7 @@
         <v>117365</v>
       </c>
       <c r="CL18" t="n">
-        <v>202729</v>
+        <v>202736</v>
       </c>
     </row>
     <row r="19">
@@ -38844,7 +38844,7 @@
         <v>35618</v>
       </c>
       <c r="CL19" t="n">
-        <v>33801</v>
+        <v>33805</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE19"/>
+  <dimension ref="A1:AF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -743,6 +743,7 @@
     <col width="10" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -843,6 +844,9 @@
       <c r="AE1" s="1" t="n">
         <v>20260109</v>
       </c>
+      <c r="AF1" s="1" t="n">
+        <v>20260112</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -942,6 +946,9 @@
       <c r="AE2" t="n">
         <v>59</v>
       </c>
+      <c r="AF2" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1041,6 +1048,9 @@
       <c r="AE3" t="n">
         <v>131</v>
       </c>
+      <c r="AF3" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1140,6 +1150,9 @@
       <c r="AE4" t="n">
         <v>60</v>
       </c>
+      <c r="AF4" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1239,6 +1252,9 @@
       <c r="AE5" t="n">
         <v>48</v>
       </c>
+      <c r="AF5" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1338,6 +1354,9 @@
       <c r="AE6" t="n">
         <v>121</v>
       </c>
+      <c r="AF6" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1437,6 +1456,9 @@
       <c r="AE7" t="n">
         <v>132</v>
       </c>
+      <c r="AF7" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1536,6 +1558,9 @@
       <c r="AE8" t="n">
         <v>139</v>
       </c>
+      <c r="AF8" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1635,6 +1660,9 @@
       <c r="AE9" t="n">
         <v>-85</v>
       </c>
+      <c r="AF9" t="n">
+        <v>-67</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1734,6 +1762,9 @@
       <c r="AE10" t="n">
         <v>69</v>
       </c>
+      <c r="AF10" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1833,6 +1864,9 @@
       <c r="AE11" t="n">
         <v>-68</v>
       </c>
+      <c r="AF11" t="n">
+        <v>-46</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1932,6 +1966,9 @@
       <c r="AE12" t="n">
         <v>-66</v>
       </c>
+      <c r="AF12" t="n">
+        <v>-41</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2031,6 +2068,9 @@
       <c r="AE13" t="n">
         <v>-62</v>
       </c>
+      <c r="AF13" t="n">
+        <v>-35</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2130,6 +2170,9 @@
       <c r="AE14" t="n">
         <v>-85</v>
       </c>
+      <c r="AF14" t="n">
+        <v>-64</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2229,6 +2272,9 @@
       <c r="AE15" t="n">
         <v>63</v>
       </c>
+      <c r="AF15" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2328,6 +2374,9 @@
       <c r="AE16" t="n">
         <v>-74</v>
       </c>
+      <c r="AF16" t="n">
+        <v>-48</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2427,6 +2476,9 @@
       <c r="AE17" t="n">
         <v>-78</v>
       </c>
+      <c r="AF17" t="n">
+        <v>-61</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2526,6 +2578,9 @@
       <c r="AE18" t="n">
         <v>92</v>
       </c>
+      <c r="AF18" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2624,6 +2679,9 @@
       </c>
       <c r="AE19" t="n">
         <v>64</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2637,7 +2695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS19"/>
+  <dimension ref="A1:BT19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2711,6 +2769,7 @@
     <col width="12" customWidth="1" min="69" max="69"/>
     <col width="12" customWidth="1" min="70" max="70"/>
     <col width="12" customWidth="1" min="71" max="71"/>
+    <col width="12" customWidth="1" min="72" max="72"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3069,6 +3128,11 @@
           <t>20260109</t>
         </is>
       </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>20260112</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3288,6 +3352,9 @@
       <c r="BS2" t="n">
         <v>106</v>
       </c>
+      <c r="BT2" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3507,6 +3574,9 @@
       <c r="BS3" t="n">
         <v>114</v>
       </c>
+      <c r="BT3" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3726,6 +3796,9 @@
       <c r="BS4" t="n">
         <v>106</v>
       </c>
+      <c r="BT4" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3945,6 +4018,9 @@
       <c r="BS5" t="n">
         <v>104</v>
       </c>
+      <c r="BT5" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4164,6 +4240,9 @@
       <c r="BS6" t="n">
         <v>111</v>
       </c>
+      <c r="BT6" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4383,6 +4462,9 @@
       <c r="BS7" t="n">
         <v>114</v>
       </c>
+      <c r="BT7" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4602,6 +4684,9 @@
       <c r="BS8" t="n">
         <v>116</v>
       </c>
+      <c r="BT8" t="n">
+        <v>115</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4821,6 +4906,9 @@
       <c r="BS9" t="n">
         <v>87</v>
       </c>
+      <c r="BT9" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5040,6 +5128,9 @@
       <c r="BS10" t="n">
         <v>105</v>
       </c>
+      <c r="BT10" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5259,6 +5350,9 @@
       <c r="BS11" t="n">
         <v>93</v>
       </c>
+      <c r="BT11" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5478,6 +5572,9 @@
       <c r="BS12" t="n">
         <v>92</v>
       </c>
+      <c r="BT12" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5697,6 +5794,9 @@
       <c r="BS13" t="n">
         <v>91</v>
       </c>
+      <c r="BT13" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5916,6 +6016,9 @@
       <c r="BS14" t="n">
         <v>85</v>
       </c>
+      <c r="BT14" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6135,6 +6238,9 @@
       <c r="BS15" t="n">
         <v>106</v>
       </c>
+      <c r="BT15" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6354,6 +6460,9 @@
       <c r="BS16" t="n">
         <v>93</v>
       </c>
+      <c r="BT16" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6573,6 +6682,9 @@
       <c r="BS17" t="n">
         <v>92</v>
       </c>
+      <c r="BT17" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6792,6 +6904,9 @@
       <c r="BS18" t="n">
         <v>108</v>
       </c>
+      <c r="BT18" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7010,6 +7125,9 @@
       </c>
       <c r="BS19" t="n">
         <v>105</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -7023,12 +7141,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:BA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="52" max="52"/>
+    <col width="12" customWidth="1" min="53" max="53"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7194,6 +7313,11 @@
           <t>20260109</t>
         </is>
       </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>20260112</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7356,6 +7480,9 @@
       <c r="AZ2" t="n">
         <v>4.15</v>
       </c>
+      <c r="BA2" t="n">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7518,6 +7645,9 @@
       <c r="AZ3" t="n">
         <v>139.52</v>
       </c>
+      <c r="BA3" t="n">
+        <v>129.26</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7680,6 +7810,9 @@
       <c r="AZ4" t="n">
         <v>-2.26</v>
       </c>
+      <c r="BA4" t="n">
+        <v>-1.15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7842,6 +7975,9 @@
       <c r="AZ5" t="n">
         <v>68.81999999999999</v>
       </c>
+      <c r="BA5" t="n">
+        <v>64.26000000000001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8004,6 +8140,9 @@
       <c r="AZ6" t="n">
         <v>124.13</v>
       </c>
+      <c r="BA6" t="n">
+        <v>116.06</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8166,6 +8305,9 @@
       <c r="AZ7" t="n">
         <v>128.69</v>
       </c>
+      <c r="BA7" t="n">
+        <v>122.24</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8328,6 +8470,9 @@
       <c r="AZ8" t="n">
         <v>155.87</v>
       </c>
+      <c r="BA8" t="n">
+        <v>142.01</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8490,6 +8635,9 @@
       <c r="AZ9" t="n">
         <v>25.99</v>
       </c>
+      <c r="BA9" t="n">
+        <v>13.31</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8652,6 +8800,9 @@
       <c r="AZ10" t="n">
         <v>61.57</v>
       </c>
+      <c r="BA10" t="n">
+        <v>57.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8814,6 +8965,9 @@
       <c r="AZ11" t="n">
         <v>10.2</v>
       </c>
+      <c r="BA11" t="n">
+        <v>0.32</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8976,6 +9130,9 @@
       <c r="AZ12" t="n">
         <v>9.539999999999999</v>
       </c>
+      <c r="BA12" t="n">
+        <v>-0.11</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9138,6 +9295,9 @@
       <c r="AZ13" t="n">
         <v>1.41</v>
       </c>
+      <c r="BA13" t="n">
+        <v>-7.16</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9300,6 +9460,9 @@
       <c r="AZ14" t="n">
         <v>24.47</v>
       </c>
+      <c r="BA14" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9462,6 +9625,9 @@
       <c r="AZ15" t="n">
         <v>3.08</v>
       </c>
+      <c r="BA15" t="n">
+        <v>6.07</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9624,6 +9790,9 @@
       <c r="AZ16" t="n">
         <v>13.49</v>
       </c>
+      <c r="BA16" t="n">
+        <v>2.19</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9786,6 +9955,9 @@
       <c r="AZ17" t="n">
         <v>17.24</v>
       </c>
+      <c r="BA17" t="n">
+        <v>6.49</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9948,6 +10120,9 @@
       <c r="AZ18" t="n">
         <v>64.81</v>
       </c>
+      <c r="BA18" t="n">
+        <v>61.25</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10109,6 +10284,9 @@
       </c>
       <c r="AZ19" t="n">
         <v>-3.3</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>-1.03</v>
       </c>
     </row>
   </sheetData>
@@ -10122,7 +10300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE19"/>
+  <dimension ref="A1:AF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10156,6 +10334,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10314,6 +10493,11 @@
           <t>20260109</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>20260112</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10413,6 +10597,9 @@
       <c r="AE2" t="n">
         <v>64</v>
       </c>
+      <c r="AF2" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10512,6 +10699,9 @@
       <c r="AE3" t="n">
         <v>69</v>
       </c>
+      <c r="AF3" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10611,6 +10801,9 @@
       <c r="AE4" t="n">
         <v>38</v>
       </c>
+      <c r="AF4" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10710,6 +10903,9 @@
       <c r="AE5" t="n">
         <v>18</v>
       </c>
+      <c r="AF5" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10809,6 +11005,9 @@
       <c r="AE6" t="n">
         <v>154</v>
       </c>
+      <c r="AF6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10908,6 +11107,9 @@
       <c r="AE7" t="n">
         <v>63</v>
       </c>
+      <c r="AF7" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11007,6 +11209,9 @@
       <c r="AE8" t="n">
         <v>98</v>
       </c>
+      <c r="AF8" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11106,6 +11311,9 @@
       <c r="AE9" t="n">
         <v>19</v>
       </c>
+      <c r="AF9" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11205,6 +11413,9 @@
       <c r="AE10" t="n">
         <v>74</v>
       </c>
+      <c r="AF10" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11304,6 +11515,9 @@
       <c r="AE11" t="n">
         <v>19</v>
       </c>
+      <c r="AF11" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11403,6 +11617,9 @@
       <c r="AE12" t="n">
         <v>18</v>
       </c>
+      <c r="AF12" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11502,6 +11719,9 @@
       <c r="AE13" t="n">
         <v>30</v>
       </c>
+      <c r="AF13" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11601,6 +11821,9 @@
       <c r="AE14" t="n">
         <v>23</v>
       </c>
+      <c r="AF14" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11700,6 +11923,9 @@
       <c r="AE15" t="n">
         <v>32</v>
       </c>
+      <c r="AF15" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11799,6 +12025,9 @@
       <c r="AE16" t="n">
         <v>13</v>
       </c>
+      <c r="AF16" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11898,6 +12127,9 @@
       <c r="AE17" t="n">
         <v>4</v>
       </c>
+      <c r="AF17" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11997,6 +12229,9 @@
       <c r="AE18" t="n">
         <v>58</v>
       </c>
+      <c r="AF18" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12095,6 +12330,9 @@
       </c>
       <c r="AE19" t="n">
         <v>35</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -12108,7 +12346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL19"/>
+  <dimension ref="A1:CM19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12201,6 +12439,7 @@
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
+    <col width="12" customWidth="1" min="91" max="91"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12478,6 +12717,9 @@
       <c r="CL1" s="1" t="n">
         <v>20260109</v>
       </c>
+      <c r="CM1" s="1" t="n">
+        <v>20260112</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12754,6 +12996,9 @@
       <c r="CL2" t="n">
         <v>16320</v>
       </c>
+      <c r="CM2" t="n">
+        <v>16245</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13030,6 +13275,9 @@
       <c r="CL3" t="n">
         <v>69770</v>
       </c>
+      <c r="CM3" t="n">
+        <v>70330</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13306,6 +13554,9 @@
       <c r="CL4" t="n">
         <v>18860</v>
       </c>
+      <c r="CM4" t="n">
+        <v>18955</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13582,6 +13833,9 @@
       <c r="CL5" t="n">
         <v>16875</v>
       </c>
+      <c r="CM5" t="n">
+        <v>17175</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13858,6 +14112,9 @@
       <c r="CL6" t="n">
         <v>19935</v>
       </c>
+      <c r="CM6" t="n">
+        <v>20150</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14134,6 +14391,9 @@
       <c r="CL7" t="n">
         <v>23710</v>
       </c>
+      <c r="CM7" t="n">
+        <v>24050</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14410,6 +14670,9 @@
       <c r="CL8" t="n">
         <v>23320</v>
       </c>
+      <c r="CM8" t="n">
+        <v>23650</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14686,6 +14949,9 @@
       <c r="CL9" t="n">
         <v>1210</v>
       </c>
+      <c r="CM9" t="n">
+        <v>1160</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14962,6 +15228,9 @@
       <c r="CL10" t="n">
         <v>18255</v>
       </c>
+      <c r="CM10" t="n">
+        <v>18255</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15238,6 +15507,9 @@
       <c r="CL11" t="n">
         <v>4800</v>
       </c>
+      <c r="CM11" t="n">
+        <v>4740</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15514,6 +15786,9 @@
       <c r="CL12" t="n">
         <v>5130</v>
       </c>
+      <c r="CM12" t="n">
+        <v>5020</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15790,6 +16065,9 @@
       <c r="CL13" t="n">
         <v>5250</v>
       </c>
+      <c r="CM13" t="n">
+        <v>5050</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16066,6 +16344,9 @@
       <c r="CL14" t="n">
         <v>1280</v>
       </c>
+      <c r="CM14" t="n">
+        <v>1220</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -16342,6 +16623,9 @@
       <c r="CL15" t="n">
         <v>20470</v>
       </c>
+      <c r="CM15" t="n">
+        <v>20410</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -16618,6 +16902,9 @@
       <c r="CL16" t="n">
         <v>9820</v>
       </c>
+      <c r="CM16" t="n">
+        <v>9640</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16894,6 +17181,9 @@
       <c r="CL17" t="n">
         <v>5655</v>
       </c>
+      <c r="CM17" t="n">
+        <v>5595</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17170,6 +17460,9 @@
       <c r="CL18" t="n">
         <v>19795</v>
       </c>
+      <c r="CM18" t="n">
+        <v>19855</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17445,6 +17738,9 @@
       </c>
       <c r="CL19" t="n">
         <v>16875</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>16755</v>
       </c>
     </row>
   </sheetData>
@@ -17458,7 +17754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL19"/>
+  <dimension ref="A1:CM19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17551,6 +17847,7 @@
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
+    <col width="12" customWidth="1" min="91" max="91"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17828,6 +18125,9 @@
       <c r="CL1" s="1" t="n">
         <v>20260109</v>
       </c>
+      <c r="CM1" s="1" t="n">
+        <v>20260112</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18104,6 +18404,9 @@
       <c r="CL2" t="n">
         <v>16345</v>
       </c>
+      <c r="CM2" t="n">
+        <v>16530</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18380,6 +18683,9 @@
       <c r="CL3" t="n">
         <v>70465</v>
       </c>
+      <c r="CM3" t="n">
+        <v>70450</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18656,6 +18962,9 @@
       <c r="CL4" t="n">
         <v>19030</v>
       </c>
+      <c r="CM4" t="n">
+        <v>19095</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18932,6 +19241,9 @@
       <c r="CL5" t="n">
         <v>17170</v>
       </c>
+      <c r="CM5" t="n">
+        <v>17215</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19208,6 +19520,9 @@
       <c r="CL6" t="n">
         <v>20150</v>
       </c>
+      <c r="CM6" t="n">
+        <v>20185</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19484,6 +19799,9 @@
       <c r="CL7" t="n">
         <v>24065</v>
       </c>
+      <c r="CM7" t="n">
+        <v>24140</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19760,6 +20078,9 @@
       <c r="CL8" t="n">
         <v>23630</v>
       </c>
+      <c r="CM8" t="n">
+        <v>23690</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20036,6 +20357,9 @@
       <c r="CL9" t="n">
         <v>1214</v>
       </c>
+      <c r="CM9" t="n">
+        <v>1258</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20312,6 +20636,9 @@
       <c r="CL10" t="n">
         <v>18365</v>
       </c>
+      <c r="CM10" t="n">
+        <v>18305</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -20588,6 +20915,9 @@
       <c r="CL11" t="n">
         <v>4850</v>
       </c>
+      <c r="CM11" t="n">
+        <v>4970</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -20864,6 +21194,9 @@
       <c r="CL12" t="n">
         <v>5185</v>
       </c>
+      <c r="CM12" t="n">
+        <v>5335</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -21140,6 +21473,9 @@
       <c r="CL13" t="n">
         <v>5255</v>
       </c>
+      <c r="CM13" t="n">
+        <v>5385</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -21416,6 +21752,9 @@
       <c r="CL14" t="n">
         <v>1282</v>
       </c>
+      <c r="CM14" t="n">
+        <v>1344</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -21692,6 +22031,9 @@
       <c r="CL15" t="n">
         <v>20555</v>
       </c>
+      <c r="CM15" t="n">
+        <v>20515</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -21968,6 +22310,9 @@
       <c r="CL16" t="n">
         <v>9875</v>
       </c>
+      <c r="CM16" t="n">
+        <v>10120</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -22244,6 +22589,9 @@
       <c r="CL17" t="n">
         <v>5695</v>
       </c>
+      <c r="CM17" t="n">
+        <v>5855</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -22520,6 +22868,9 @@
       <c r="CL18" t="n">
         <v>19950</v>
       </c>
+      <c r="CM18" t="n">
+        <v>19870</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -22795,6 +23146,9 @@
       </c>
       <c r="CL19" t="n">
         <v>16885</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>16825</v>
       </c>
     </row>
   </sheetData>
@@ -22808,7 +23162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL19"/>
+  <dimension ref="A1:CM19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22901,6 +23255,7 @@
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
+    <col width="12" customWidth="1" min="91" max="91"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23178,6 +23533,9 @@
       <c r="CL1" s="1" t="n">
         <v>20260109</v>
       </c>
+      <c r="CM1" s="1" t="n">
+        <v>20260112</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23454,6 +23812,9 @@
       <c r="CL2" t="n">
         <v>15975</v>
       </c>
+      <c r="CM2" t="n">
+        <v>15745</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23730,6 +24091,9 @@
       <c r="CL3" t="n">
         <v>68080</v>
       </c>
+      <c r="CM3" t="n">
+        <v>68110</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24006,6 +24370,9 @@
       <c r="CL4" t="n">
         <v>18580</v>
       </c>
+      <c r="CM4" t="n">
+        <v>18480</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24282,6 +24649,9 @@
       <c r="CL5" t="n">
         <v>16650</v>
       </c>
+      <c r="CM5" t="n">
+        <v>16630</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24558,6 +24928,9 @@
       <c r="CL6" t="n">
         <v>19510</v>
       </c>
+      <c r="CM6" t="n">
+        <v>19510</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24834,6 +25207,9 @@
       <c r="CL7" t="n">
         <v>23265</v>
       </c>
+      <c r="CM7" t="n">
+        <v>23425</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25110,6 +25486,9 @@
       <c r="CL8" t="n">
         <v>22825</v>
       </c>
+      <c r="CM8" t="n">
+        <v>22755</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25386,6 +25765,9 @@
       <c r="CL9" t="n">
         <v>1164</v>
       </c>
+      <c r="CM9" t="n">
+        <v>1160</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25662,6 +26044,9 @@
       <c r="CL10" t="n">
         <v>17825</v>
       </c>
+      <c r="CM10" t="n">
+        <v>17710</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25938,6 +26323,9 @@
       <c r="CL11" t="n">
         <v>4710</v>
       </c>
+      <c r="CM11" t="n">
+        <v>4735</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26214,6 +26602,9 @@
       <c r="CL12" t="n">
         <v>5025</v>
       </c>
+      <c r="CM12" t="n">
+        <v>5020</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -26490,6 +26881,9 @@
       <c r="CL13" t="n">
         <v>5055</v>
       </c>
+      <c r="CM13" t="n">
+        <v>5050</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -26766,6 +27160,9 @@
       <c r="CL14" t="n">
         <v>1220</v>
       </c>
+      <c r="CM14" t="n">
+        <v>1220</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -27042,6 +27439,9 @@
       <c r="CL15" t="n">
         <v>20050</v>
       </c>
+      <c r="CM15" t="n">
+        <v>19820</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -27318,6 +27718,9 @@
       <c r="CL16" t="n">
         <v>9605</v>
       </c>
+      <c r="CM16" t="n">
+        <v>9620</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -27594,6 +27997,9 @@
       <c r="CL17" t="n">
         <v>5560</v>
       </c>
+      <c r="CM17" t="n">
+        <v>5590</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -27870,6 +28276,9 @@
       <c r="CL18" t="n">
         <v>19265</v>
       </c>
+      <c r="CM18" t="n">
+        <v>19050</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -28145,6 +28554,9 @@
       </c>
       <c r="CL19" t="n">
         <v>16630</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>16350</v>
       </c>
     </row>
   </sheetData>
@@ -28158,7 +28570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL19"/>
+  <dimension ref="A1:CM19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -28251,6 +28663,7 @@
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
+    <col width="12" customWidth="1" min="91" max="91"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28528,6 +28941,9 @@
       <c r="CL1" s="1" t="n">
         <v>20260109</v>
       </c>
+      <c r="CM1" s="1" t="n">
+        <v>20260112</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28804,6 +29220,9 @@
       <c r="CL2" t="n">
         <v>16270</v>
       </c>
+      <c r="CM2" t="n">
+        <v>15880</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29080,6 +29499,9 @@
       <c r="CL3" t="n">
         <v>69305</v>
       </c>
+      <c r="CM3" t="n">
+        <v>69120</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -29356,6 +29778,9 @@
       <c r="CL4" t="n">
         <v>19015</v>
       </c>
+      <c r="CM4" t="n">
+        <v>18640</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29632,6 +30057,9 @@
       <c r="CL5" t="n">
         <v>16810</v>
       </c>
+      <c r="CM5" t="n">
+        <v>16860</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29908,6 +30336,9 @@
       <c r="CL6" t="n">
         <v>19845</v>
       </c>
+      <c r="CM6" t="n">
+        <v>19825</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -30184,6 +30615,9 @@
       <c r="CL7" t="n">
         <v>23720</v>
       </c>
+      <c r="CM7" t="n">
+        <v>23800</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30460,6 +30894,9 @@
       <c r="CL8" t="n">
         <v>23310</v>
       </c>
+      <c r="CM8" t="n">
+        <v>23180</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30736,6 +31173,9 @@
       <c r="CL9" t="n">
         <v>1175</v>
       </c>
+      <c r="CM9" t="n">
+        <v>1252</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31012,6 +31452,9 @@
       <c r="CL10" t="n">
         <v>18060</v>
       </c>
+      <c r="CM10" t="n">
+        <v>17985</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -31288,6 +31731,9 @@
       <c r="CL11" t="n">
         <v>4765</v>
       </c>
+      <c r="CM11" t="n">
+        <v>4955</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31564,6 +32010,9 @@
       <c r="CL12" t="n">
         <v>5085</v>
       </c>
+      <c r="CM12" t="n">
+        <v>5325</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31840,6 +32289,9 @@
       <c r="CL13" t="n">
         <v>5085</v>
       </c>
+      <c r="CM13" t="n">
+        <v>5350</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32116,6 +32568,9 @@
       <c r="CL14" t="n">
         <v>1234</v>
       </c>
+      <c r="CM14" t="n">
+        <v>1338</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32392,6 +32847,9 @@
       <c r="CL15" t="n">
         <v>20555</v>
       </c>
+      <c r="CM15" t="n">
+        <v>20035</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -32668,6 +33126,9 @@
       <c r="CL16" t="n">
         <v>9670</v>
       </c>
+      <c r="CM16" t="n">
+        <v>10100</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -32944,6 +33405,9 @@
       <c r="CL17" t="n">
         <v>5635</v>
       </c>
+      <c r="CM17" t="n">
+        <v>5835</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -33220,6 +33684,9 @@
       <c r="CL18" t="n">
         <v>19640</v>
       </c>
+      <c r="CM18" t="n">
+        <v>19405</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -33495,6 +33962,9 @@
       </c>
       <c r="CL19" t="n">
         <v>16885</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>16515</v>
       </c>
     </row>
   </sheetData>
@@ -33508,7 +33978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL19"/>
+  <dimension ref="A1:CM19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33601,6 +34071,7 @@
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
+    <col width="12" customWidth="1" min="91" max="91"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33878,6 +34349,9 @@
       <c r="CL1" s="1" t="n">
         <v>20260109</v>
       </c>
+      <c r="CM1" s="1" t="n">
+        <v>20260112</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34154,6 +34628,9 @@
       <c r="CL2" t="n">
         <v>178544</v>
       </c>
+      <c r="CM2" t="n">
+        <v>246040</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34430,6 +34907,9 @@
       <c r="CL3" t="n">
         <v>3475134</v>
       </c>
+      <c r="CM3" t="n">
+        <v>2369574</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34706,6 +35186,9 @@
       <c r="CL4" t="n">
         <v>138831</v>
       </c>
+      <c r="CM4" t="n">
+        <v>159491</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34982,6 +35465,9 @@
       <c r="CL5" t="n">
         <v>211259</v>
       </c>
+      <c r="CM5" t="n">
+        <v>239318</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -35258,6 +35744,9 @@
       <c r="CL6" t="n">
         <v>7491943</v>
       </c>
+      <c r="CM6" t="n">
+        <v>4965267</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35534,6 +36023,9 @@
       <c r="CL7" t="n">
         <v>5106090</v>
       </c>
+      <c r="CM7" t="n">
+        <v>4284905</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -35810,6 +36302,9 @@
       <c r="CL8" t="n">
         <v>17709113</v>
       </c>
+      <c r="CM8" t="n">
+        <v>12993461</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -36086,6 +36581,9 @@
       <c r="CL9" t="n">
         <v>2948185</v>
       </c>
+      <c r="CM9" t="n">
+        <v>4634146</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -36362,6 +36860,9 @@
       <c r="CL10" t="n">
         <v>1926448</v>
       </c>
+      <c r="CM10" t="n">
+        <v>1311431</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -36638,6 +37139,9 @@
       <c r="CL11" t="n">
         <v>499800</v>
       </c>
+      <c r="CM11" t="n">
+        <v>692858</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -36914,6 +37418,9 @@
       <c r="CL12" t="n">
         <v>1091306</v>
       </c>
+      <c r="CM12" t="n">
+        <v>2700445</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -37190,6 +37697,9 @@
       <c r="CL13" t="n">
         <v>4396701</v>
       </c>
+      <c r="CM13" t="n">
+        <v>6113760</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37466,6 +37976,9 @@
       <c r="CL14" t="n">
         <v>24175445</v>
       </c>
+      <c r="CM14" t="n">
+        <v>51206357</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37742,6 +38255,9 @@
       <c r="CL15" t="n">
         <v>1162621</v>
       </c>
+      <c r="CM15" t="n">
+        <v>1828099</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -38018,6 +38534,9 @@
       <c r="CL16" t="n">
         <v>156755</v>
       </c>
+      <c r="CM16" t="n">
+        <v>387700</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -38294,6 +38813,9 @@
       <c r="CL17" t="n">
         <v>19814</v>
       </c>
+      <c r="CM17" t="n">
+        <v>64453</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -38570,6 +39092,9 @@
       <c r="CL18" t="n">
         <v>202736</v>
       </c>
+      <c r="CM18" t="n">
+        <v>111535</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -38845,6 +39370,9 @@
       </c>
       <c r="CL19" t="n">
         <v>33805</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>72992</v>
       </c>
     </row>
   </sheetData>
@@ -38858,7 +39386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS19"/>
+  <dimension ref="A1:BT19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -38932,6 +39460,7 @@
     <col width="10" customWidth="1" min="69" max="69"/>
     <col width="10" customWidth="1" min="70" max="70"/>
     <col width="10" customWidth="1" min="71" max="71"/>
+    <col width="10" customWidth="1" min="72" max="72"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39152,6 +39681,9 @@
       <c r="BS1" s="1" t="n">
         <v>20260109</v>
       </c>
+      <c r="BT1" s="1" t="n">
+        <v>20260112</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -39371,6 +39903,9 @@
       <c r="BS2" t="n">
         <v>100</v>
       </c>
+      <c r="BT2" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -39590,6 +40125,9 @@
       <c r="BS3" t="n">
         <v>91</v>
       </c>
+      <c r="BT3" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -39809,6 +40347,9 @@
       <c r="BS4" t="n">
         <v>100</v>
       </c>
+      <c r="BT4" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -40028,6 +40569,9 @@
       <c r="BS5" t="n">
         <v>70</v>
       </c>
+      <c r="BT5" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -40247,6 +40791,9 @@
       <c r="BS6" t="n">
         <v>89</v>
       </c>
+      <c r="BT6" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -40466,6 +41013,9 @@
       <c r="BS7" t="n">
         <v>94</v>
       </c>
+      <c r="BT7" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40685,6 +41235,9 @@
       <c r="BS8" t="n">
         <v>94</v>
       </c>
+      <c r="BT8" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -40904,6 +41457,9 @@
       <c r="BS9" t="n">
         <v>2</v>
       </c>
+      <c r="BT9" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -41123,6 +41679,9 @@
       <c r="BS10" t="n">
         <v>67</v>
       </c>
+      <c r="BT10" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -41342,6 +41901,9 @@
       <c r="BS11" t="n">
         <v>1</v>
       </c>
+      <c r="BT11" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -41561,6 +42123,9 @@
       <c r="BS12" t="n">
         <v>6</v>
       </c>
+      <c r="BT12" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -41780,6 +42345,9 @@
       <c r="BS13" t="n">
         <v>0</v>
       </c>
+      <c r="BT13" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -41999,6 +42567,9 @@
       <c r="BS14" t="n">
         <v>0</v>
       </c>
+      <c r="BT14" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42218,6 +42789,9 @@
       <c r="BS15" t="n">
         <v>100</v>
       </c>
+      <c r="BT15" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -42437,6 +43011,9 @@
       <c r="BS16" t="n">
         <v>5</v>
       </c>
+      <c r="BT16" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42656,6 +43233,9 @@
       <c r="BS17" t="n">
         <v>5</v>
       </c>
+      <c r="BT17" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42875,6 +43455,9 @@
       <c r="BS18" t="n">
         <v>77</v>
       </c>
+      <c r="BT18" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43093,6 +43676,9 @@
       </c>
       <c r="BS19" t="n">
         <v>100</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -43106,7 +43692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE19"/>
+  <dimension ref="A1:AF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -43140,6 +43726,7 @@
     <col width="10" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43240,6 +43827,9 @@
       <c r="AE1" s="1" t="n">
         <v>20260109</v>
       </c>
+      <c r="AF1" s="1" t="n">
+        <v>20260112</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -43339,6 +43929,9 @@
       <c r="AE2" t="n">
         <v>92</v>
       </c>
+      <c r="AF2" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -43438,6 +44031,9 @@
       <c r="AE3" t="n">
         <v>92</v>
       </c>
+      <c r="AF3" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -43537,6 +44133,9 @@
       <c r="AE4" t="n">
         <v>92</v>
       </c>
+      <c r="AF4" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -43636,6 +44235,9 @@
       <c r="AE5" t="n">
         <v>70</v>
       </c>
+      <c r="AF5" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -43735,6 +44337,9 @@
       <c r="AE6" t="n">
         <v>91</v>
       </c>
+      <c r="AF6" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -43834,6 +44439,9 @@
       <c r="AE7" t="n">
         <v>96</v>
       </c>
+      <c r="AF7" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -43933,6 +44541,9 @@
       <c r="AE8" t="n">
         <v>95</v>
       </c>
+      <c r="AF8" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -44032,6 +44643,9 @@
       <c r="AE9" t="n">
         <v>2</v>
       </c>
+      <c r="AF9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -44131,6 +44745,9 @@
       <c r="AE10" t="n">
         <v>67</v>
       </c>
+      <c r="AF10" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -44230,6 +44847,9 @@
       <c r="AE11" t="n">
         <v>39</v>
       </c>
+      <c r="AF11" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -44329,6 +44949,9 @@
       <c r="AE12" t="n">
         <v>39</v>
       </c>
+      <c r="AF12" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -44428,6 +45051,9 @@
       <c r="AE13" t="n">
         <v>39</v>
       </c>
+      <c r="AF13" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -44527,6 +45153,9 @@
       <c r="AE14" t="n">
         <v>10</v>
       </c>
+      <c r="AF14" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -44626,6 +45255,9 @@
       <c r="AE15" t="n">
         <v>100</v>
       </c>
+      <c r="AF15" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -44725,6 +45357,9 @@
       <c r="AE16" t="n">
         <v>31</v>
       </c>
+      <c r="AF16" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -44824,6 +45459,9 @@
       <c r="AE17" t="n">
         <v>26</v>
       </c>
+      <c r="AF17" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -44923,6 +45561,9 @@
       <c r="AE18" t="n">
         <v>81</v>
       </c>
+      <c r="AF18" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -45021,6 +45662,9 @@
       </c>
       <c r="AE19" t="n">
         <v>100</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -45034,7 +45678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS19"/>
+  <dimension ref="A1:BT19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -45108,6 +45752,7 @@
     <col width="10" customWidth="1" min="69" max="69"/>
     <col width="10" customWidth="1" min="70" max="70"/>
     <col width="10" customWidth="1" min="71" max="71"/>
+    <col width="10" customWidth="1" min="72" max="72"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -45328,6 +45973,9 @@
       <c r="BS1" s="1" t="n">
         <v>20260109</v>
       </c>
+      <c r="BT1" s="1" t="n">
+        <v>20260112</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -45547,6 +46195,9 @@
       <c r="BS2" t="n">
         <v>89</v>
       </c>
+      <c r="BT2" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -45766,6 +46417,9 @@
       <c r="BS3" t="n">
         <v>72</v>
       </c>
+      <c r="BT3" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -45985,6 +46639,9 @@
       <c r="BS4" t="n">
         <v>93</v>
       </c>
+      <c r="BT4" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -46204,6 +46861,9 @@
       <c r="BS5" t="n">
         <v>39</v>
       </c>
+      <c r="BT5" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -46423,6 +47083,9 @@
       <c r="BS6" t="n">
         <v>67</v>
       </c>
+      <c r="BT6" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -46642,6 +47305,9 @@
       <c r="BS7" t="n">
         <v>75</v>
       </c>
+      <c r="BT7" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -46861,6 +47527,9 @@
       <c r="BS8" t="n">
         <v>74</v>
       </c>
+      <c r="BT8" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -47080,6 +47749,9 @@
       <c r="BS9" t="n">
         <v>-57</v>
       </c>
+      <c r="BT9" t="n">
+        <v>-28</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -47299,6 +47971,9 @@
       <c r="BS10" t="n">
         <v>47</v>
       </c>
+      <c r="BT10" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -47518,6 +48193,9 @@
       <c r="BS11" t="n">
         <v>-61</v>
       </c>
+      <c r="BT11" t="n">
+        <v>-27</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -47737,6 +48415,9 @@
       <c r="BS12" t="n">
         <v>-56</v>
       </c>
+      <c r="BT12" t="n">
+        <v>-21</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -47956,6 +48637,9 @@
       <c r="BS13" t="n">
         <v>-65</v>
       </c>
+      <c r="BT13" t="n">
+        <v>-27</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -48175,6 +48859,9 @@
       <c r="BS14" t="n">
         <v>-58</v>
       </c>
+      <c r="BT14" t="n">
+        <v>-27</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -48394,6 +49081,9 @@
       <c r="BS15" t="n">
         <v>99</v>
       </c>
+      <c r="BT15" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -48613,6 +49303,9 @@
       <c r="BS16" t="n">
         <v>-57</v>
       </c>
+      <c r="BT16" t="n">
+        <v>-19</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -48832,6 +49525,9 @@
       <c r="BS17" t="n">
         <v>-56</v>
       </c>
+      <c r="BT17" t="n">
+        <v>-29</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -49051,6 +49747,9 @@
       <c r="BS18" t="n">
         <v>57</v>
       </c>
+      <c r="BT18" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -49269,6 +49968,9 @@
       </c>
       <c r="BS19" t="n">
         <v>106</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF19"/>
+  <dimension ref="A1:AG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -744,6 +744,7 @@
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="10" customWidth="1" min="31" max="31"/>
     <col width="10" customWidth="1" min="32" max="32"/>
+    <col width="10" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -847,6 +848,9 @@
       <c r="AF1" s="1" t="n">
         <v>20260112</v>
       </c>
+      <c r="AG1" s="1" t="n">
+        <v>20260113</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -949,6 +953,9 @@
       <c r="AF2" t="n">
         <v>39</v>
       </c>
+      <c r="AG2" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1051,6 +1058,9 @@
       <c r="AF3" t="n">
         <v>121</v>
       </c>
+      <c r="AG3" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1153,6 +1163,9 @@
       <c r="AF4" t="n">
         <v>41</v>
       </c>
+      <c r="AG4" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1255,6 +1268,9 @@
       <c r="AF5" t="n">
         <v>50</v>
       </c>
+      <c r="AG5" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1357,6 +1373,9 @@
       <c r="AF6" t="n">
         <v>114</v>
       </c>
+      <c r="AG6" t="n">
+        <v>115</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1459,6 +1478,9 @@
       <c r="AF7" t="n">
         <v>126</v>
       </c>
+      <c r="AG7" t="n">
+        <v>122</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1561,6 +1583,9 @@
       <c r="AF8" t="n">
         <v>126</v>
       </c>
+      <c r="AG8" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1663,6 +1688,9 @@
       <c r="AF9" t="n">
         <v>-67</v>
       </c>
+      <c r="AG9" t="n">
+        <v>-23</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1765,6 +1793,9 @@
       <c r="AF10" t="n">
         <v>62</v>
       </c>
+      <c r="AG10" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1867,6 +1898,9 @@
       <c r="AF11" t="n">
         <v>-46</v>
       </c>
+      <c r="AG11" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1969,6 +2003,9 @@
       <c r="AF12" t="n">
         <v>-41</v>
       </c>
+      <c r="AG12" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2071,6 +2108,9 @@
       <c r="AF13" t="n">
         <v>-35</v>
       </c>
+      <c r="AG13" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2173,6 +2213,9 @@
       <c r="AF14" t="n">
         <v>-64</v>
       </c>
+      <c r="AG14" t="n">
+        <v>-29</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2275,6 +2318,9 @@
       <c r="AF15" t="n">
         <v>48</v>
       </c>
+      <c r="AG15" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2377,6 +2423,9 @@
       <c r="AF16" t="n">
         <v>-48</v>
       </c>
+      <c r="AG16" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2479,6 +2528,9 @@
       <c r="AF17" t="n">
         <v>-61</v>
       </c>
+      <c r="AG17" t="n">
+        <v>-28</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2581,6 +2633,9 @@
       <c r="AF18" t="n">
         <v>78</v>
       </c>
+      <c r="AG18" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2682,6 +2737,9 @@
       </c>
       <c r="AF19" t="n">
         <v>48</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2695,7 +2753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT19"/>
+  <dimension ref="A1:BU19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2770,6 +2828,7 @@
     <col width="12" customWidth="1" min="70" max="70"/>
     <col width="12" customWidth="1" min="71" max="71"/>
     <col width="12" customWidth="1" min="72" max="72"/>
+    <col width="12" customWidth="1" min="73" max="73"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3133,6 +3192,11 @@
           <t>20260112</t>
         </is>
       </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>20260113</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3355,6 +3419,9 @@
       <c r="BT2" t="n">
         <v>103</v>
       </c>
+      <c r="BU2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3577,6 +3644,9 @@
       <c r="BT3" t="n">
         <v>112</v>
       </c>
+      <c r="BU3" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3799,6 +3869,9 @@
       <c r="BT4" t="n">
         <v>103</v>
       </c>
+      <c r="BU4" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4021,6 +4094,9 @@
       <c r="BT5" t="n">
         <v>104</v>
       </c>
+      <c r="BU5" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4243,6 +4319,9 @@
       <c r="BT6" t="n">
         <v>110</v>
       </c>
+      <c r="BU6" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4465,6 +4544,9 @@
       <c r="BT7" t="n">
         <v>113</v>
       </c>
+      <c r="BU7" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4687,6 +4769,9 @@
       <c r="BT8" t="n">
         <v>115</v>
       </c>
+      <c r="BU8" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4909,6 +4994,9 @@
       <c r="BT9" t="n">
         <v>94</v>
       </c>
+      <c r="BU9" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5131,6 +5219,9 @@
       <c r="BT10" t="n">
         <v>105</v>
       </c>
+      <c r="BU10" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5353,6 +5444,9 @@
       <c r="BT11" t="n">
         <v>97</v>
       </c>
+      <c r="BU11" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5575,6 +5669,9 @@
       <c r="BT12" t="n">
         <v>97</v>
       </c>
+      <c r="BU12" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5797,6 +5894,9 @@
       <c r="BT13" t="n">
         <v>97</v>
       </c>
+      <c r="BU13" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6019,6 +6119,9 @@
       <c r="BT14" t="n">
         <v>93</v>
       </c>
+      <c r="BU14" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6241,6 +6344,9 @@
       <c r="BT15" t="n">
         <v>103</v>
       </c>
+      <c r="BU15" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6463,6 +6569,9 @@
       <c r="BT16" t="n">
         <v>98</v>
       </c>
+      <c r="BU16" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6685,6 +6794,9 @@
       <c r="BT17" t="n">
         <v>96</v>
       </c>
+      <c r="BU17" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6907,6 +7019,9 @@
       <c r="BT18" t="n">
         <v>106</v>
       </c>
+      <c r="BU18" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7128,6 +7243,9 @@
       </c>
       <c r="BT19" t="n">
         <v>102</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -7141,13 +7259,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA19"/>
+  <dimension ref="A1:BB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="52" max="52"/>
     <col width="12" customWidth="1" min="53" max="53"/>
+    <col width="12" customWidth="1" min="54" max="54"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7318,6 +7437,11 @@
           <t>20260112</t>
         </is>
       </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>20260113</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7483,6 +7607,9 @@
       <c r="BA2" t="n">
         <v>5.3</v>
       </c>
+      <c r="BB2" t="n">
+        <v>3.78</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7648,6 +7775,9 @@
       <c r="BA3" t="n">
         <v>129.26</v>
       </c>
+      <c r="BB3" t="n">
+        <v>117.01</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7813,6 +7943,9 @@
       <c r="BA4" t="n">
         <v>-1.15</v>
       </c>
+      <c r="BB4" t="n">
+        <v>-2.09</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7978,6 +8111,9 @@
       <c r="BA5" t="n">
         <v>64.26000000000001</v>
       </c>
+      <c r="BB5" t="n">
+        <v>59.98</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8143,6 +8279,9 @@
       <c r="BA6" t="n">
         <v>116.06</v>
       </c>
+      <c r="BB6" t="n">
+        <v>107.33</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8308,6 +8447,9 @@
       <c r="BA7" t="n">
         <v>122.24</v>
       </c>
+      <c r="BB7" t="n">
+        <v>113.65</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8473,6 +8615,9 @@
       <c r="BA8" t="n">
         <v>142.01</v>
       </c>
+      <c r="BB8" t="n">
+        <v>126.37</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8638,6 +8783,9 @@
       <c r="BA9" t="n">
         <v>13.31</v>
       </c>
+      <c r="BB9" t="n">
+        <v>3.35</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8803,6 +8951,9 @@
       <c r="BA10" t="n">
         <v>57.5</v>
       </c>
+      <c r="BB10" t="n">
+        <v>56.59</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8968,6 +9119,9 @@
       <c r="BA11" t="n">
         <v>0.32</v>
       </c>
+      <c r="BB11" t="n">
+        <v>-7.26</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9133,6 +9287,9 @@
       <c r="BA12" t="n">
         <v>-0.11</v>
       </c>
+      <c r="BB12" t="n">
+        <v>-7.72</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9298,6 +9455,9 @@
       <c r="BA13" t="n">
         <v>-7.16</v>
       </c>
+      <c r="BB13" t="n">
+        <v>-14.27</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9463,6 +9623,9 @@
       <c r="BA14" t="n">
         <v>12.26</v>
       </c>
+      <c r="BB14" t="n">
+        <v>0.21</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9628,6 +9791,9 @@
       <c r="BA15" t="n">
         <v>6.07</v>
       </c>
+      <c r="BB15" t="n">
+        <v>5.95</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9793,6 +9959,9 @@
       <c r="BA16" t="n">
         <v>2.19</v>
       </c>
+      <c r="BB16" t="n">
+        <v>-6.03</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9958,6 +10127,9 @@
       <c r="BA17" t="n">
         <v>6.49</v>
       </c>
+      <c r="BB17" t="n">
+        <v>-2.97</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10123,6 +10295,9 @@
       <c r="BA18" t="n">
         <v>61.25</v>
       </c>
+      <c r="BB18" t="n">
+        <v>59.72</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10287,6 +10462,9 @@
       </c>
       <c r="BA19" t="n">
         <v>-1.03</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>-1.69</v>
       </c>
     </row>
   </sheetData>
@@ -10300,7 +10478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF19"/>
+  <dimension ref="A1:AG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10335,6 +10513,7 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="12" customWidth="1" min="31" max="31"/>
     <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10498,6 +10677,11 @@
           <t>20260112</t>
         </is>
       </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>20260113</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10600,6 +10784,9 @@
       <c r="AF2" t="n">
         <v>86</v>
       </c>
+      <c r="AG2" t="n">
+        <v>137</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10702,6 +10889,9 @@
       <c r="AF3" t="n">
         <v>49</v>
       </c>
+      <c r="AG3" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10804,6 +10994,9 @@
       <c r="AF4" t="n">
         <v>43</v>
       </c>
+      <c r="AG4" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10906,6 +11099,9 @@
       <c r="AF5" t="n">
         <v>22</v>
       </c>
+      <c r="AG5" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11008,6 +11204,9 @@
       <c r="AF6" t="n">
         <v>100</v>
       </c>
+      <c r="AG6" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11110,6 +11309,9 @@
       <c r="AF7" t="n">
         <v>54</v>
       </c>
+      <c r="AG7" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11212,6 +11414,9 @@
       <c r="AF8" t="n">
         <v>81</v>
       </c>
+      <c r="AG8" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11314,6 +11519,9 @@
       <c r="AF9" t="n">
         <v>30</v>
       </c>
+      <c r="AG9" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11416,6 +11624,9 @@
       <c r="AF10" t="n">
         <v>51</v>
       </c>
+      <c r="AG10" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11518,6 +11729,9 @@
       <c r="AF11" t="n">
         <v>26</v>
       </c>
+      <c r="AG11" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11620,6 +11834,9 @@
       <c r="AF12" t="n">
         <v>45</v>
       </c>
+      <c r="AG12" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11722,6 +11939,9 @@
       <c r="AF13" t="n">
         <v>42</v>
       </c>
+      <c r="AG13" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11824,6 +12044,9 @@
       <c r="AF14" t="n">
         <v>49</v>
       </c>
+      <c r="AG14" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11926,6 +12149,9 @@
       <c r="AF15" t="n">
         <v>50</v>
       </c>
+      <c r="AG15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12028,6 +12254,9 @@
       <c r="AF16" t="n">
         <v>31</v>
       </c>
+      <c r="AG16" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12130,6 +12359,9 @@
       <c r="AF17" t="n">
         <v>13</v>
       </c>
+      <c r="AG17" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12232,6 +12464,9 @@
       <c r="AF18" t="n">
         <v>32</v>
       </c>
+      <c r="AG18" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12333,6 +12568,9 @@
       </c>
       <c r="AF19" t="n">
         <v>74</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -12346,7 +12584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM19"/>
+  <dimension ref="A1:CN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12440,6 +12678,7 @@
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
+    <col width="12" customWidth="1" min="92" max="92"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12720,6 +12959,9 @@
       <c r="CM1" s="1" t="n">
         <v>20260112</v>
       </c>
+      <c r="CN1" s="1" t="n">
+        <v>20260113</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12999,6 +13241,9 @@
       <c r="CM2" t="n">
         <v>16245</v>
       </c>
+      <c r="CN2" t="n">
+        <v>15890</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13278,6 +13523,9 @@
       <c r="CM3" t="n">
         <v>70330</v>
       </c>
+      <c r="CN3" t="n">
+        <v>69950</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13557,6 +13805,9 @@
       <c r="CM4" t="n">
         <v>18955</v>
       </c>
+      <c r="CN4" t="n">
+        <v>18620</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13836,6 +14087,9 @@
       <c r="CM5" t="n">
         <v>17175</v>
       </c>
+      <c r="CN5" t="n">
+        <v>17155</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14115,6 +14369,9 @@
       <c r="CM6" t="n">
         <v>20150</v>
       </c>
+      <c r="CN6" t="n">
+        <v>19990</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14394,6 +14651,9 @@
       <c r="CM7" t="n">
         <v>24050</v>
       </c>
+      <c r="CN7" t="n">
+        <v>24125</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14673,6 +14933,9 @@
       <c r="CM8" t="n">
         <v>23650</v>
       </c>
+      <c r="CN8" t="n">
+        <v>23340</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14952,6 +15215,9 @@
       <c r="CM9" t="n">
         <v>1160</v>
       </c>
+      <c r="CN9" t="n">
+        <v>1265</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15231,6 +15497,9 @@
       <c r="CM10" t="n">
         <v>18255</v>
       </c>
+      <c r="CN10" t="n">
+        <v>18250</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15510,6 +15779,9 @@
       <c r="CM11" t="n">
         <v>4740</v>
       </c>
+      <c r="CN11" t="n">
+        <v>5010</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15789,6 +16061,9 @@
       <c r="CM12" t="n">
         <v>5020</v>
       </c>
+      <c r="CN12" t="n">
+        <v>5380</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16068,6 +16343,9 @@
       <c r="CM13" t="n">
         <v>5050</v>
       </c>
+      <c r="CN13" t="n">
+        <v>5425</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16347,6 +16625,9 @@
       <c r="CM14" t="n">
         <v>1220</v>
       </c>
+      <c r="CN14" t="n">
+        <v>1374</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -16626,6 +16907,9 @@
       <c r="CM15" t="n">
         <v>20410</v>
       </c>
+      <c r="CN15" t="n">
+        <v>20055</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -16905,6 +17189,9 @@
       <c r="CM16" t="n">
         <v>9640</v>
       </c>
+      <c r="CN16" t="n">
+        <v>10205</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17184,6 +17471,9 @@
       <c r="CM17" t="n">
         <v>5595</v>
       </c>
+      <c r="CN17" t="n">
+        <v>5915</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17463,6 +17753,9 @@
       <c r="CM18" t="n">
         <v>19855</v>
       </c>
+      <c r="CN18" t="n">
+        <v>19670</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17741,6 +18034,9 @@
       </c>
       <c r="CM19" t="n">
         <v>16755</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>16580</v>
       </c>
     </row>
   </sheetData>
@@ -17754,7 +18050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM19"/>
+  <dimension ref="A1:CN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17848,6 +18144,7 @@
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
+    <col width="12" customWidth="1" min="92" max="92"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18128,6 +18425,9 @@
       <c r="CM1" s="1" t="n">
         <v>20260112</v>
       </c>
+      <c r="CN1" s="1" t="n">
+        <v>20260113</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18407,6 +18707,9 @@
       <c r="CM2" t="n">
         <v>16530</v>
       </c>
+      <c r="CN2" t="n">
+        <v>15910</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18686,6 +18989,9 @@
       <c r="CM3" t="n">
         <v>70450</v>
       </c>
+      <c r="CN3" t="n">
+        <v>70190</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18965,6 +19271,9 @@
       <c r="CM4" t="n">
         <v>19095</v>
       </c>
+      <c r="CN4" t="n">
+        <v>18640</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19244,6 +19553,9 @@
       <c r="CM5" t="n">
         <v>17215</v>
       </c>
+      <c r="CN5" t="n">
+        <v>17265</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19523,6 +19835,9 @@
       <c r="CM6" t="n">
         <v>20185</v>
       </c>
+      <c r="CN6" t="n">
+        <v>20170</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19802,6 +20117,9 @@
       <c r="CM7" t="n">
         <v>24140</v>
       </c>
+      <c r="CN7" t="n">
+        <v>24125</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20081,6 +20399,9 @@
       <c r="CM8" t="n">
         <v>23690</v>
       </c>
+      <c r="CN8" t="n">
+        <v>23410</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20360,6 +20681,9 @@
       <c r="CM9" t="n">
         <v>1258</v>
       </c>
+      <c r="CN9" t="n">
+        <v>1431</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20639,6 +20963,9 @@
       <c r="CM10" t="n">
         <v>18305</v>
       </c>
+      <c r="CN10" t="n">
+        <v>18525</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -20918,6 +21245,9 @@
       <c r="CM11" t="n">
         <v>4970</v>
       </c>
+      <c r="CN11" t="n">
+        <v>5280</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -21197,6 +21527,9 @@
       <c r="CM12" t="n">
         <v>5335</v>
       </c>
+      <c r="CN12" t="n">
+        <v>5660</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -21476,6 +21809,9 @@
       <c r="CM13" t="n">
         <v>5385</v>
       </c>
+      <c r="CN13" t="n">
+        <v>5670</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -21755,6 +22091,9 @@
       <c r="CM14" t="n">
         <v>1344</v>
       </c>
+      <c r="CN14" t="n">
+        <v>1498</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -22034,6 +22373,9 @@
       <c r="CM15" t="n">
         <v>20515</v>
       </c>
+      <c r="CN15" t="n">
+        <v>20160</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -22313,6 +22655,9 @@
       <c r="CM16" t="n">
         <v>10120</v>
       </c>
+      <c r="CN16" t="n">
+        <v>10680</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -22592,6 +22937,9 @@
       <c r="CM17" t="n">
         <v>5855</v>
       </c>
+      <c r="CN17" t="n">
+        <v>6160</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -22871,6 +23219,9 @@
       <c r="CM18" t="n">
         <v>19870</v>
       </c>
+      <c r="CN18" t="n">
+        <v>19860</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -23149,6 +23500,9 @@
       </c>
       <c r="CM19" t="n">
         <v>16825</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>16580</v>
       </c>
     </row>
   </sheetData>
@@ -23162,7 +23516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM19"/>
+  <dimension ref="A1:CN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23256,6 +23610,7 @@
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
+    <col width="12" customWidth="1" min="92" max="92"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23536,6 +23891,9 @@
       <c r="CM1" s="1" t="n">
         <v>20260112</v>
       </c>
+      <c r="CN1" s="1" t="n">
+        <v>20260113</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23815,6 +24173,9 @@
       <c r="CM2" t="n">
         <v>15745</v>
       </c>
+      <c r="CN2" t="n">
+        <v>15240</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24094,6 +24455,9 @@
       <c r="CM3" t="n">
         <v>68110</v>
       </c>
+      <c r="CN3" t="n">
+        <v>68665</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24373,6 +24737,9 @@
       <c r="CM4" t="n">
         <v>18480</v>
       </c>
+      <c r="CN4" t="n">
+        <v>18195</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24652,6 +25019,9 @@
       <c r="CM5" t="n">
         <v>16630</v>
       </c>
+      <c r="CN5" t="n">
+        <v>16865</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24931,6 +25301,9 @@
       <c r="CM6" t="n">
         <v>19510</v>
       </c>
+      <c r="CN6" t="n">
+        <v>19740</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25210,6 +25583,9 @@
       <c r="CM7" t="n">
         <v>23425</v>
       </c>
+      <c r="CN7" t="n">
+        <v>23645</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25489,6 +25865,9 @@
       <c r="CM8" t="n">
         <v>22755</v>
       </c>
+      <c r="CN8" t="n">
+        <v>22880</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25768,6 +26147,9 @@
       <c r="CM9" t="n">
         <v>1160</v>
       </c>
+      <c r="CN9" t="n">
+        <v>1257</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26047,6 +26429,9 @@
       <c r="CM10" t="n">
         <v>17710</v>
       </c>
+      <c r="CN10" t="n">
+        <v>18150</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26326,6 +26711,9 @@
       <c r="CM11" t="n">
         <v>4735</v>
       </c>
+      <c r="CN11" t="n">
+        <v>4970</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26605,6 +26993,9 @@
       <c r="CM12" t="n">
         <v>5020</v>
       </c>
+      <c r="CN12" t="n">
+        <v>5320</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -26884,6 +27275,9 @@
       <c r="CM13" t="n">
         <v>5050</v>
       </c>
+      <c r="CN13" t="n">
+        <v>5355</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -27163,6 +27557,9 @@
       <c r="CM14" t="n">
         <v>1220</v>
       </c>
+      <c r="CN14" t="n">
+        <v>1340</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -27442,6 +27839,9 @@
       <c r="CM15" t="n">
         <v>19820</v>
       </c>
+      <c r="CN15" t="n">
+        <v>19540</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -27721,6 +28121,9 @@
       <c r="CM16" t="n">
         <v>9620</v>
       </c>
+      <c r="CN16" t="n">
+        <v>10110</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -28000,6 +28403,9 @@
       <c r="CM17" t="n">
         <v>5590</v>
       </c>
+      <c r="CN17" t="n">
+        <v>5870</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -28279,6 +28685,9 @@
       <c r="CM18" t="n">
         <v>19050</v>
       </c>
+      <c r="CN18" t="n">
+        <v>19490</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -28557,6 +28966,9 @@
       </c>
       <c r="CM19" t="n">
         <v>16350</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>16060</v>
       </c>
     </row>
   </sheetData>
@@ -28570,7 +28982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM19"/>
+  <dimension ref="A1:CN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -28664,6 +29076,7 @@
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
+    <col width="12" customWidth="1" min="92" max="92"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28944,6 +29357,9 @@
       <c r="CM1" s="1" t="n">
         <v>20260112</v>
       </c>
+      <c r="CN1" s="1" t="n">
+        <v>20260113</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29223,6 +29639,9 @@
       <c r="CM2" t="n">
         <v>15880</v>
       </c>
+      <c r="CN2" t="n">
+        <v>15335</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29502,6 +29921,9 @@
       <c r="CM3" t="n">
         <v>69120</v>
       </c>
+      <c r="CN3" t="n">
+        <v>69400</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -29781,6 +30203,9 @@
       <c r="CM4" t="n">
         <v>18640</v>
       </c>
+      <c r="CN4" t="n">
+        <v>18265</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -30060,6 +30485,9 @@
       <c r="CM5" t="n">
         <v>16860</v>
       </c>
+      <c r="CN5" t="n">
+        <v>17030</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -30339,6 +30767,9 @@
       <c r="CM6" t="n">
         <v>19825</v>
       </c>
+      <c r="CN6" t="n">
+        <v>20000</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -30618,6 +31049,9 @@
       <c r="CM7" t="n">
         <v>23800</v>
       </c>
+      <c r="CN7" t="n">
+        <v>23935</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30897,6 +31331,9 @@
       <c r="CM8" t="n">
         <v>23180</v>
       </c>
+      <c r="CN8" t="n">
+        <v>23205</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -31176,6 +31613,9 @@
       <c r="CM9" t="n">
         <v>1252</v>
       </c>
+      <c r="CN9" t="n">
+        <v>1431</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31455,6 +31895,9 @@
       <c r="CM10" t="n">
         <v>17985</v>
       </c>
+      <c r="CN10" t="n">
+        <v>18450</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -31734,6 +32177,9 @@
       <c r="CM11" t="n">
         <v>4955</v>
       </c>
+      <c r="CN11" t="n">
+        <v>5260</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32013,6 +32459,9 @@
       <c r="CM12" t="n">
         <v>5325</v>
       </c>
+      <c r="CN12" t="n">
+        <v>5660</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32292,6 +32741,9 @@
       <c r="CM13" t="n">
         <v>5350</v>
       </c>
+      <c r="CN13" t="n">
+        <v>5670</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32571,6 +33023,9 @@
       <c r="CM14" t="n">
         <v>1338</v>
       </c>
+      <c r="CN14" t="n">
+        <v>1498</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32850,6 +33305,9 @@
       <c r="CM15" t="n">
         <v>20035</v>
       </c>
+      <c r="CN15" t="n">
+        <v>19625</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -33129,6 +33587,9 @@
       <c r="CM16" t="n">
         <v>10100</v>
       </c>
+      <c r="CN16" t="n">
+        <v>10675</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -33408,6 +33869,9 @@
       <c r="CM17" t="n">
         <v>5835</v>
       </c>
+      <c r="CN17" t="n">
+        <v>6135</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -33687,6 +34151,9 @@
       <c r="CM18" t="n">
         <v>19405</v>
       </c>
+      <c r="CN18" t="n">
+        <v>19785</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -33965,6 +34432,9 @@
       </c>
       <c r="CM19" t="n">
         <v>16515</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>16110</v>
       </c>
     </row>
   </sheetData>
@@ -33978,7 +34448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM19"/>
+  <dimension ref="A1:CN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34072,6 +34542,7 @@
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
+    <col width="12" customWidth="1" min="92" max="92"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34352,6 +34823,9 @@
       <c r="CM1" s="1" t="n">
         <v>20260112</v>
       </c>
+      <c r="CN1" s="1" t="n">
+        <v>20260113</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34631,6 +35105,9 @@
       <c r="CM2" t="n">
         <v>246040</v>
       </c>
+      <c r="CN2" t="n">
+        <v>406544</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34910,6 +35387,9 @@
       <c r="CM3" t="n">
         <v>2369574</v>
       </c>
+      <c r="CN3" t="n">
+        <v>1824187</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -35189,6 +35669,9 @@
       <c r="CM4" t="n">
         <v>159491</v>
       </c>
+      <c r="CN4" t="n">
+        <v>193077</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -35468,6 +35951,9 @@
       <c r="CM5" t="n">
         <v>239318</v>
       </c>
+      <c r="CN5" t="n">
+        <v>192340</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -35747,6 +36233,9 @@
       <c r="CM6" t="n">
         <v>4965267</v>
       </c>
+      <c r="CN6" t="n">
+        <v>5006118</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -36026,6 +36515,9 @@
       <c r="CM7" t="n">
         <v>4284905</v>
       </c>
+      <c r="CN7" t="n">
+        <v>4151198</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -36305,6 +36797,9 @@
       <c r="CM8" t="n">
         <v>12993461</v>
       </c>
+      <c r="CN8" t="n">
+        <v>12180981</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -36584,6 +37079,9 @@
       <c r="CM9" t="n">
         <v>4634146</v>
       </c>
+      <c r="CN9" t="n">
+        <v>11753486</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -36863,6 +37361,9 @@
       <c r="CM10" t="n">
         <v>1311431</v>
       </c>
+      <c r="CN10" t="n">
+        <v>1192883</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -37142,6 +37643,9 @@
       <c r="CM11" t="n">
         <v>692858</v>
       </c>
+      <c r="CN11" t="n">
+        <v>911249</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -37421,6 +37925,9 @@
       <c r="CM12" t="n">
         <v>2700445</v>
       </c>
+      <c r="CN12" t="n">
+        <v>2422919</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -37700,6 +38207,9 @@
       <c r="CM13" t="n">
         <v>6113760</v>
       </c>
+      <c r="CN13" t="n">
+        <v>5168204</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37979,6 +38489,9 @@
       <c r="CM14" t="n">
         <v>51206357</v>
       </c>
+      <c r="CN14" t="n">
+        <v>53194181</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -38258,6 +38771,9 @@
       <c r="CM15" t="n">
         <v>1828099</v>
       </c>
+      <c r="CN15" t="n">
+        <v>1453821</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -38537,6 +39053,9 @@
       <c r="CM16" t="n">
         <v>387700</v>
       </c>
+      <c r="CN16" t="n">
+        <v>493730</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -38816,6 +39335,9 @@
       <c r="CM17" t="n">
         <v>64453</v>
       </c>
+      <c r="CN17" t="n">
+        <v>46247</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -39095,6 +39617,9 @@
       <c r="CM18" t="n">
         <v>111535</v>
       </c>
+      <c r="CN18" t="n">
+        <v>95145</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -39373,6 +39898,9 @@
       </c>
       <c r="CM19" t="n">
         <v>72992</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>113034</v>
       </c>
     </row>
   </sheetData>
@@ -39386,7 +39914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT19"/>
+  <dimension ref="A1:BU19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -39461,6 +39989,7 @@
     <col width="10" customWidth="1" min="70" max="70"/>
     <col width="10" customWidth="1" min="71" max="71"/>
     <col width="10" customWidth="1" min="72" max="72"/>
+    <col width="10" customWidth="1" min="73" max="73"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39684,6 +40213,9 @@
       <c r="BT1" s="1" t="n">
         <v>20260112</v>
       </c>
+      <c r="BU1" s="1" t="n">
+        <v>20260113</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -39906,6 +40438,9 @@
       <c r="BT2" t="n">
         <v>79</v>
       </c>
+      <c r="BU2" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40128,6 +40663,9 @@
       <c r="BT3" t="n">
         <v>90</v>
       </c>
+      <c r="BU3" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -40350,6 +40888,9 @@
       <c r="BT4" t="n">
         <v>79</v>
       </c>
+      <c r="BU4" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -40572,6 +41113,9 @@
       <c r="BT5" t="n">
         <v>71</v>
       </c>
+      <c r="BU5" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -40794,6 +41338,9 @@
       <c r="BT6" t="n">
         <v>88</v>
       </c>
+      <c r="BU6" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -41016,6 +41563,9 @@
       <c r="BT7" t="n">
         <v>96</v>
       </c>
+      <c r="BU7" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -41238,6 +41788,9 @@
       <c r="BT8" t="n">
         <v>92</v>
       </c>
+      <c r="BU8" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -41460,6 +42013,9 @@
       <c r="BT9" t="n">
         <v>19</v>
       </c>
+      <c r="BU9" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -41682,6 +42238,9 @@
       <c r="BT10" t="n">
         <v>65</v>
       </c>
+      <c r="BU10" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -41904,6 +42463,9 @@
       <c r="BT11" t="n">
         <v>22</v>
       </c>
+      <c r="BU11" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -42126,6 +42688,9 @@
       <c r="BT12" t="n">
         <v>27</v>
       </c>
+      <c r="BU12" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -42348,6 +42913,9 @@
       <c r="BT13" t="n">
         <v>23</v>
       </c>
+      <c r="BU13" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -42570,6 +43138,9 @@
       <c r="BT14" t="n">
         <v>20</v>
       </c>
+      <c r="BU14" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42792,6 +43363,9 @@
       <c r="BT15" t="n">
         <v>74</v>
       </c>
+      <c r="BU15" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -43014,6 +43588,9 @@
       <c r="BT16" t="n">
         <v>29</v>
       </c>
+      <c r="BU16" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -43236,6 +43813,9 @@
       <c r="BT17" t="n">
         <v>22</v>
       </c>
+      <c r="BU17" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -43458,6 +44038,9 @@
       <c r="BT18" t="n">
         <v>71</v>
       </c>
+      <c r="BU18" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43679,6 +44262,9 @@
       </c>
       <c r="BT19" t="n">
         <v>69</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -43692,7 +44278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF19"/>
+  <dimension ref="A1:AG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -43727,6 +44313,7 @@
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="10" customWidth="1" min="31" max="31"/>
     <col width="10" customWidth="1" min="32" max="32"/>
+    <col width="10" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43830,6 +44417,9 @@
       <c r="AF1" s="1" t="n">
         <v>20260112</v>
       </c>
+      <c r="AG1" s="1" t="n">
+        <v>20260113</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -43932,6 +44522,9 @@
       <c r="AF2" t="n">
         <v>81</v>
       </c>
+      <c r="AG2" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -44034,6 +44627,9 @@
       <c r="AF3" t="n">
         <v>91</v>
       </c>
+      <c r="AG3" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -44136,6 +44732,9 @@
       <c r="AF4" t="n">
         <v>82</v>
       </c>
+      <c r="AG4" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -44238,6 +44837,9 @@
       <c r="AF5" t="n">
         <v>71</v>
       </c>
+      <c r="AG5" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -44340,6 +44942,9 @@
       <c r="AF6" t="n">
         <v>90</v>
       </c>
+      <c r="AG6" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -44442,6 +45047,9 @@
       <c r="AF7" t="n">
         <v>97</v>
       </c>
+      <c r="AG7" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -44544,6 +45152,9 @@
       <c r="AF8" t="n">
         <v>93</v>
       </c>
+      <c r="AG8" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -44646,6 +45257,9 @@
       <c r="AF9" t="n">
         <v>10</v>
       </c>
+      <c r="AG9" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -44748,6 +45362,9 @@
       <c r="AF10" t="n">
         <v>65</v>
       </c>
+      <c r="AG10" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -44850,6 +45467,9 @@
       <c r="AF11" t="n">
         <v>36</v>
       </c>
+      <c r="AG11" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -44952,6 +45572,9 @@
       <c r="AF12" t="n">
         <v>37</v>
       </c>
+      <c r="AG12" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -45054,6 +45677,9 @@
       <c r="AF13" t="n">
         <v>40</v>
       </c>
+      <c r="AG13" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -45156,6 +45782,9 @@
       <c r="AF14" t="n">
         <v>12</v>
       </c>
+      <c r="AG14" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -45258,6 +45887,9 @@
       <c r="AF15" t="n">
         <v>92</v>
       </c>
+      <c r="AG15" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -45360,6 +45992,9 @@
       <c r="AF16" t="n">
         <v>26</v>
       </c>
+      <c r="AG16" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -45462,6 +46097,9 @@
       <c r="AF17" t="n">
         <v>16</v>
       </c>
+      <c r="AG17" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -45564,6 +46202,9 @@
       <c r="AF18" t="n">
         <v>75</v>
       </c>
+      <c r="AG18" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -45665,6 +46306,9 @@
       </c>
       <c r="AF19" t="n">
         <v>91</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -45678,7 +46322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT19"/>
+  <dimension ref="A1:BU19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -45753,6 +46397,7 @@
     <col width="10" customWidth="1" min="70" max="70"/>
     <col width="10" customWidth="1" min="71" max="71"/>
     <col width="10" customWidth="1" min="72" max="72"/>
+    <col width="10" customWidth="1" min="73" max="73"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -45976,6 +46621,9 @@
       <c r="BT1" s="1" t="n">
         <v>20260112</v>
       </c>
+      <c r="BU1" s="1" t="n">
+        <v>20260113</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -46198,6 +46846,9 @@
       <c r="BT2" t="n">
         <v>48</v>
       </c>
+      <c r="BU2" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -46420,6 +47071,9 @@
       <c r="BT3" t="n">
         <v>63</v>
       </c>
+      <c r="BU3" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -46642,6 +47296,9 @@
       <c r="BT4" t="n">
         <v>56</v>
       </c>
+      <c r="BU4" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -46864,6 +47521,9 @@
       <c r="BT5" t="n">
         <v>39</v>
       </c>
+      <c r="BU5" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -47086,6 +47746,9 @@
       <c r="BT6" t="n">
         <v>60</v>
       </c>
+      <c r="BU6" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -47308,6 +47971,9 @@
       <c r="BT7" t="n">
         <v>68</v>
       </c>
+      <c r="BU7" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -47530,6 +48196,9 @@
       <c r="BT8" t="n">
         <v>64</v>
       </c>
+      <c r="BU8" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -47752,6 +48421,9 @@
       <c r="BT9" t="n">
         <v>-28</v>
       </c>
+      <c r="BU9" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -47974,6 +48646,9 @@
       <c r="BT10" t="n">
         <v>40</v>
       </c>
+      <c r="BU10" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -48196,6 +48871,9 @@
       <c r="BT11" t="n">
         <v>-27</v>
       </c>
+      <c r="BU11" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -48418,6 +49096,9 @@
       <c r="BT12" t="n">
         <v>-21</v>
       </c>
+      <c r="BU12" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -48640,6 +49321,9 @@
       <c r="BT13" t="n">
         <v>-27</v>
       </c>
+      <c r="BU13" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -48862,6 +49546,9 @@
       <c r="BT14" t="n">
         <v>-27</v>
       </c>
+      <c r="BU14" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -49084,6 +49771,9 @@
       <c r="BT15" t="n">
         <v>51</v>
       </c>
+      <c r="BU15" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -49306,6 +49996,9 @@
       <c r="BT16" t="n">
         <v>-19</v>
       </c>
+      <c r="BU16" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -49528,6 +50221,9 @@
       <c r="BT17" t="n">
         <v>-29</v>
       </c>
+      <c r="BU17" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -49750,6 +50446,9 @@
       <c r="BT18" t="n">
         <v>44</v>
       </c>
+      <c r="BU18" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -49971,6 +50670,9 @@
       </c>
       <c r="BT19" t="n">
         <v>51</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>-4</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG19"/>
+  <dimension ref="A1:AH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -745,6 +745,7 @@
     <col width="10" customWidth="1" min="31" max="31"/>
     <col width="10" customWidth="1" min="32" max="32"/>
     <col width="10" customWidth="1" min="33" max="33"/>
+    <col width="10" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -851,6 +852,9 @@
       <c r="AG1" s="1" t="n">
         <v>20260113</v>
       </c>
+      <c r="AH1" s="1" t="n">
+        <v>20260114</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -956,6 +960,9 @@
       <c r="AG2" t="n">
         <v>11</v>
       </c>
+      <c r="AH2" t="n">
+        <v>-20</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1061,6 +1068,9 @@
       <c r="AG3" t="n">
         <v>117</v>
       </c>
+      <c r="AH3" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1166,6 +1176,9 @@
       <c r="AG4" t="n">
         <v>22</v>
       </c>
+      <c r="AH4" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1271,6 +1284,9 @@
       <c r="AG5" t="n">
         <v>61</v>
       </c>
+      <c r="AH5" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1376,6 +1392,9 @@
       <c r="AG6" t="n">
         <v>115</v>
       </c>
+      <c r="AH6" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1481,6 +1500,9 @@
       <c r="AG7" t="n">
         <v>122</v>
       </c>
+      <c r="AH7" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1586,6 +1608,9 @@
       <c r="AG8" t="n">
         <v>118</v>
       </c>
+      <c r="AH8" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1691,6 +1716,9 @@
       <c r="AG9" t="n">
         <v>-23</v>
       </c>
+      <c r="AH9" t="n">
+        <v>-40</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1796,6 +1824,9 @@
       <c r="AG10" t="n">
         <v>91</v>
       </c>
+      <c r="AH10" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1901,6 +1932,9 @@
       <c r="AG11" t="n">
         <v>3</v>
       </c>
+      <c r="AH11" t="n">
+        <v>-23</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2006,6 +2040,9 @@
       <c r="AG12" t="n">
         <v>3</v>
       </c>
+      <c r="AH12" t="n">
+        <v>-27</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2111,6 +2148,9 @@
       <c r="AG13" t="n">
         <v>7</v>
       </c>
+      <c r="AH13" t="n">
+        <v>-21</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2216,6 +2256,9 @@
       <c r="AG14" t="n">
         <v>-29</v>
       </c>
+      <c r="AH14" t="n">
+        <v>-49</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2321,6 +2364,9 @@
       <c r="AG15" t="n">
         <v>37</v>
       </c>
+      <c r="AH15" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2426,6 +2472,9 @@
       <c r="AG16" t="n">
         <v>-5</v>
       </c>
+      <c r="AH16" t="n">
+        <v>-30</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2531,6 +2580,9 @@
       <c r="AG17" t="n">
         <v>-28</v>
       </c>
+      <c r="AH17" t="n">
+        <v>-45</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2636,6 +2688,9 @@
       <c r="AG18" t="n">
         <v>93</v>
       </c>
+      <c r="AH18" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2740,6 +2795,9 @@
       </c>
       <c r="AG19" t="n">
         <v>32</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2753,7 +2811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU19"/>
+  <dimension ref="A1:BV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2829,6 +2887,7 @@
     <col width="12" customWidth="1" min="71" max="71"/>
     <col width="12" customWidth="1" min="72" max="72"/>
     <col width="12" customWidth="1" min="73" max="73"/>
+    <col width="12" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3197,6 +3256,11 @@
           <t>20260113</t>
         </is>
       </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>20260114</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3422,6 +3486,9 @@
       <c r="BU2" t="n">
         <v>100</v>
       </c>
+      <c r="BV2" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3647,6 +3714,9 @@
       <c r="BU3" t="n">
         <v>112</v>
       </c>
+      <c r="BV3" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3872,6 +3942,9 @@
       <c r="BU4" t="n">
         <v>101</v>
       </c>
+      <c r="BV4" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4097,6 +4170,9 @@
       <c r="BU5" t="n">
         <v>105</v>
       </c>
+      <c r="BV5" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4322,6 +4398,9 @@
       <c r="BU6" t="n">
         <v>110</v>
       </c>
+      <c r="BV6" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4547,6 +4626,9 @@
       <c r="BU7" t="n">
         <v>112</v>
       </c>
+      <c r="BV7" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4772,6 +4854,9 @@
       <c r="BU8" t="n">
         <v>113</v>
       </c>
+      <c r="BV8" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4997,6 +5082,9 @@
       <c r="BU9" t="n">
         <v>108</v>
       </c>
+      <c r="BV9" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5222,6 +5310,9 @@
       <c r="BU10" t="n">
         <v>107</v>
       </c>
+      <c r="BV10" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5447,6 +5538,9 @@
       <c r="BU11" t="n">
         <v>103</v>
       </c>
+      <c r="BV11" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5672,6 +5766,9 @@
       <c r="BU12" t="n">
         <v>104</v>
       </c>
+      <c r="BV12" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5897,6 +5994,9 @@
       <c r="BU13" t="n">
         <v>103</v>
       </c>
+      <c r="BV13" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6122,6 +6222,9 @@
       <c r="BU14" t="n">
         <v>106</v>
       </c>
+      <c r="BV14" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6347,6 +6450,9 @@
       <c r="BU15" t="n">
         <v>101</v>
       </c>
+      <c r="BV15" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6572,6 +6678,9 @@
       <c r="BU16" t="n">
         <v>104</v>
       </c>
+      <c r="BV16" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6797,6 +6906,9 @@
       <c r="BU17" t="n">
         <v>102</v>
       </c>
+      <c r="BV17" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7022,6 +7134,9 @@
       <c r="BU18" t="n">
         <v>108</v>
       </c>
+      <c r="BV18" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7246,6 +7361,9 @@
       </c>
       <c r="BU19" t="n">
         <v>100</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -7259,7 +7377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB19"/>
+  <dimension ref="A1:BC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7267,6 +7385,7 @@
     <col width="12" customWidth="1" min="52" max="52"/>
     <col width="12" customWidth="1" min="53" max="53"/>
     <col width="12" customWidth="1" min="54" max="54"/>
+    <col width="12" customWidth="1" min="55" max="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7442,6 +7561,11 @@
           <t>20260113</t>
         </is>
       </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>20260114</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7610,6 +7734,9 @@
       <c r="BB2" t="n">
         <v>3.78</v>
       </c>
+      <c r="BC2" t="n">
+        <v>5.56</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7778,6 +7905,9 @@
       <c r="BB3" t="n">
         <v>117.01</v>
       </c>
+      <c r="BC3" t="n">
+        <v>106.13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7946,6 +8076,9 @@
       <c r="BB4" t="n">
         <v>-2.09</v>
       </c>
+      <c r="BC4" t="n">
+        <v>-2.42</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8114,6 +8247,9 @@
       <c r="BB5" t="n">
         <v>59.98</v>
       </c>
+      <c r="BC5" t="n">
+        <v>57.34</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8282,6 +8418,9 @@
       <c r="BB6" t="n">
         <v>107.33</v>
       </c>
+      <c r="BC6" t="n">
+        <v>99.06999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8450,6 +8589,9 @@
       <c r="BB7" t="n">
         <v>113.65</v>
       </c>
+      <c r="BC7" t="n">
+        <v>105.15</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8618,6 +8760,9 @@
       <c r="BB8" t="n">
         <v>126.37</v>
       </c>
+      <c r="BC8" t="n">
+        <v>113.02</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8786,6 +8931,9 @@
       <c r="BB9" t="n">
         <v>3.35</v>
       </c>
+      <c r="BC9" t="n">
+        <v>-12.39</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8954,6 +9102,9 @@
       <c r="BB10" t="n">
         <v>56.59</v>
       </c>
+      <c r="BC10" t="n">
+        <v>56.16</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9122,6 +9273,9 @@
       <c r="BB11" t="n">
         <v>-7.26</v>
       </c>
+      <c r="BC11" t="n">
+        <v>-18.26</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9290,6 +9444,9 @@
       <c r="BB12" t="n">
         <v>-7.72</v>
       </c>
+      <c r="BC12" t="n">
+        <v>-18.9</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9458,6 +9615,9 @@
       <c r="BB13" t="n">
         <v>-14.27</v>
       </c>
+      <c r="BC13" t="n">
+        <v>-24.02</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9626,6 +9786,9 @@
       <c r="BB14" t="n">
         <v>0.21</v>
       </c>
+      <c r="BC14" t="n">
+        <v>-15.16</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9794,6 +9957,9 @@
       <c r="BB15" t="n">
         <v>5.95</v>
       </c>
+      <c r="BC15" t="n">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9962,6 +10128,9 @@
       <c r="BB16" t="n">
         <v>-6.03</v>
       </c>
+      <c r="BC16" t="n">
+        <v>-18.74</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10130,6 +10299,9 @@
       <c r="BB17" t="n">
         <v>-2.97</v>
       </c>
+      <c r="BC17" t="n">
+        <v>-16.07</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10298,6 +10470,9 @@
       <c r="BB18" t="n">
         <v>59.72</v>
       </c>
+      <c r="BC18" t="n">
+        <v>58.55</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10465,6 +10640,9 @@
       </c>
       <c r="BB19" t="n">
         <v>-1.69</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>
@@ -10478,7 +10656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG19"/>
+  <dimension ref="A1:AH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10514,6 +10692,7 @@
     <col width="12" customWidth="1" min="31" max="31"/>
     <col width="12" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10682,6 +10861,11 @@
           <t>20260113</t>
         </is>
       </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>20260114</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10787,6 +10971,9 @@
       <c r="AG2" t="n">
         <v>137</v>
       </c>
+      <c r="AH2" t="n">
+        <v>152</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10892,6 +11079,9 @@
       <c r="AG3" t="n">
         <v>38</v>
       </c>
+      <c r="AH3" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10997,6 +11187,9 @@
       <c r="AG4" t="n">
         <v>52</v>
       </c>
+      <c r="AH4" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11102,6 +11295,9 @@
       <c r="AG5" t="n">
         <v>18</v>
       </c>
+      <c r="AH5" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11207,6 +11403,9 @@
       <c r="AG6" t="n">
         <v>98</v>
       </c>
+      <c r="AH6" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11312,6 +11511,9 @@
       <c r="AG7" t="n">
         <v>52</v>
       </c>
+      <c r="AH7" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11417,6 +11619,9 @@
       <c r="AG8" t="n">
         <v>75</v>
       </c>
+      <c r="AH8" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11522,6 +11727,9 @@
       <c r="AG9" t="n">
         <v>78</v>
       </c>
+      <c r="AH9" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11627,6 +11835,9 @@
       <c r="AG10" t="n">
         <v>47</v>
       </c>
+      <c r="AH10" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11732,6 +11943,9 @@
       <c r="AG11" t="n">
         <v>35</v>
       </c>
+      <c r="AH11" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11837,6 +12051,9 @@
       <c r="AG12" t="n">
         <v>41</v>
       </c>
+      <c r="AH12" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11942,6 +12159,9 @@
       <c r="AG13" t="n">
         <v>36</v>
       </c>
+      <c r="AH13" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12047,6 +12267,9 @@
       <c r="AG14" t="n">
         <v>52</v>
       </c>
+      <c r="AH14" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12152,6 +12375,9 @@
       <c r="AG15" t="n">
         <v>39</v>
       </c>
+      <c r="AH15" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12257,6 +12483,9 @@
       <c r="AG16" t="n">
         <v>40</v>
       </c>
+      <c r="AH16" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12362,6 +12591,9 @@
       <c r="AG17" t="n">
         <v>10</v>
       </c>
+      <c r="AH17" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12467,6 +12699,9 @@
       <c r="AG18" t="n">
         <v>27</v>
       </c>
+      <c r="AH18" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12571,6 +12806,9 @@
       </c>
       <c r="AG19" t="n">
         <v>111</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -12584,7 +12822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN19"/>
+  <dimension ref="A1:CO19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12679,6 +12917,7 @@
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
+    <col width="12" customWidth="1" min="93" max="93"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12962,6 +13201,9 @@
       <c r="CN1" s="1" t="n">
         <v>20260113</v>
       </c>
+      <c r="CO1" s="1" t="n">
+        <v>20260114</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13244,6 +13486,9 @@
       <c r="CN2" t="n">
         <v>15890</v>
       </c>
+      <c r="CO2" t="n">
+        <v>15485</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13526,6 +13771,9 @@
       <c r="CN3" t="n">
         <v>69950</v>
       </c>
+      <c r="CO3" t="n">
+        <v>69380</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13808,6 +14056,9 @@
       <c r="CN4" t="n">
         <v>18620</v>
       </c>
+      <c r="CO4" t="n">
+        <v>18355</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14090,6 +14341,9 @@
       <c r="CN5" t="n">
         <v>17155</v>
       </c>
+      <c r="CO5" t="n">
+        <v>17100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14372,6 +14626,9 @@
       <c r="CN6" t="n">
         <v>19990</v>
       </c>
+      <c r="CO6" t="n">
+        <v>20000</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14654,6 +14911,9 @@
       <c r="CN7" t="n">
         <v>24125</v>
       </c>
+      <c r="CO7" t="n">
+        <v>23935</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14936,6 +15196,9 @@
       <c r="CN8" t="n">
         <v>23340</v>
       </c>
+      <c r="CO8" t="n">
+        <v>23205</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15218,6 +15481,9 @@
       <c r="CN9" t="n">
         <v>1265</v>
       </c>
+      <c r="CO9" t="n">
+        <v>1440</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15500,6 +15766,9 @@
       <c r="CN10" t="n">
         <v>18250</v>
       </c>
+      <c r="CO10" t="n">
+        <v>18580</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15782,6 +16051,9 @@
       <c r="CN11" t="n">
         <v>5010</v>
       </c>
+      <c r="CO11" t="n">
+        <v>5260</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16064,6 +16336,9 @@
       <c r="CN12" t="n">
         <v>5380</v>
       </c>
+      <c r="CO12" t="n">
+        <v>5550</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16346,6 +16621,9 @@
       <c r="CN13" t="n">
         <v>5425</v>
       </c>
+      <c r="CO13" t="n">
+        <v>5650</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16628,6 +16906,9 @@
       <c r="CN14" t="n">
         <v>1374</v>
       </c>
+      <c r="CO14" t="n">
+        <v>1483</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -16910,6 +17191,9 @@
       <c r="CN15" t="n">
         <v>20055</v>
       </c>
+      <c r="CO15" t="n">
+        <v>19735</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -17192,6 +17476,9 @@
       <c r="CN16" t="n">
         <v>10205</v>
       </c>
+      <c r="CO16" t="n">
+        <v>10625</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17474,6 +17761,9 @@
       <c r="CN17" t="n">
         <v>5915</v>
       </c>
+      <c r="CO17" t="n">
+        <v>6135</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17756,6 +18046,9 @@
       <c r="CN18" t="n">
         <v>19670</v>
       </c>
+      <c r="CO18" t="n">
+        <v>20050</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -18037,6 +18330,9 @@
       </c>
       <c r="CN19" t="n">
         <v>16580</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>16190</v>
       </c>
     </row>
   </sheetData>
@@ -18050,7 +18346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN19"/>
+  <dimension ref="A1:CO19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18145,6 +18441,7 @@
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
+    <col width="12" customWidth="1" min="93" max="93"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18428,6 +18725,9 @@
       <c r="CN1" s="1" t="n">
         <v>20260113</v>
       </c>
+      <c r="CO1" s="1" t="n">
+        <v>20260114</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18710,6 +19010,9 @@
       <c r="CN2" t="n">
         <v>15910</v>
       </c>
+      <c r="CO2" t="n">
+        <v>15485</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18992,6 +19295,9 @@
       <c r="CN3" t="n">
         <v>70190</v>
       </c>
+      <c r="CO3" t="n">
+        <v>70770</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19274,6 +19580,9 @@
       <c r="CN4" t="n">
         <v>18640</v>
       </c>
+      <c r="CO4" t="n">
+        <v>18385</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19556,6 +19865,9 @@
       <c r="CN5" t="n">
         <v>17265</v>
       </c>
+      <c r="CO5" t="n">
+        <v>17320</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19838,6 +20150,9 @@
       <c r="CN6" t="n">
         <v>20170</v>
       </c>
+      <c r="CO6" t="n">
+        <v>20415</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20120,6 +20435,9 @@
       <c r="CN7" t="n">
         <v>24125</v>
       </c>
+      <c r="CO7" t="n">
+        <v>24310</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20402,6 +20720,9 @@
       <c r="CN8" t="n">
         <v>23410</v>
       </c>
+      <c r="CO8" t="n">
+        <v>23750</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20684,6 +21005,9 @@
       <c r="CN9" t="n">
         <v>1431</v>
       </c>
+      <c r="CO9" t="n">
+        <v>1440</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20966,6 +21290,9 @@
       <c r="CN10" t="n">
         <v>18525</v>
       </c>
+      <c r="CO10" t="n">
+        <v>18900</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -21248,6 +21575,9 @@
       <c r="CN11" t="n">
         <v>5280</v>
       </c>
+      <c r="CO11" t="n">
+        <v>5270</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -21530,6 +21860,9 @@
       <c r="CN12" t="n">
         <v>5660</v>
       </c>
+      <c r="CO12" t="n">
+        <v>5635</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -21812,6 +22145,9 @@
       <c r="CN13" t="n">
         <v>5670</v>
       </c>
+      <c r="CO13" t="n">
+        <v>5650</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -22094,6 +22430,9 @@
       <c r="CN14" t="n">
         <v>1498</v>
       </c>
+      <c r="CO14" t="n">
+        <v>1484</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -22376,6 +22715,9 @@
       <c r="CN15" t="n">
         <v>20160</v>
       </c>
+      <c r="CO15" t="n">
+        <v>19875</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -22658,6 +23000,9 @@
       <c r="CN16" t="n">
         <v>10680</v>
       </c>
+      <c r="CO16" t="n">
+        <v>10625</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -22940,6 +23285,9 @@
       <c r="CN17" t="n">
         <v>6160</v>
       </c>
+      <c r="CO17" t="n">
+        <v>6135</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -23222,6 +23570,9 @@
       <c r="CN18" t="n">
         <v>19860</v>
       </c>
+      <c r="CO18" t="n">
+        <v>20450</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -23503,6 +23854,9 @@
       </c>
       <c r="CN19" t="n">
         <v>16580</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>16200</v>
       </c>
     </row>
   </sheetData>
@@ -23516,7 +23870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN19"/>
+  <dimension ref="A1:CO19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23611,6 +23965,7 @@
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
+    <col width="12" customWidth="1" min="93" max="93"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23894,6 +24249,9 @@
       <c r="CN1" s="1" t="n">
         <v>20260113</v>
       </c>
+      <c r="CO1" s="1" t="n">
+        <v>20260114</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24176,6 +24534,9 @@
       <c r="CN2" t="n">
         <v>15240</v>
       </c>
+      <c r="CO2" t="n">
+        <v>14595</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24458,6 +24819,9 @@
       <c r="CN3" t="n">
         <v>68665</v>
       </c>
+      <c r="CO3" t="n">
+        <v>69300</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24740,6 +25104,9 @@
       <c r="CN4" t="n">
         <v>18195</v>
       </c>
+      <c r="CO4" t="n">
+        <v>17675</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25022,6 +25389,9 @@
       <c r="CN5" t="n">
         <v>16865</v>
       </c>
+      <c r="CO5" t="n">
+        <v>17065</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25304,6 +25674,9 @@
       <c r="CN6" t="n">
         <v>19740</v>
       </c>
+      <c r="CO6" t="n">
+        <v>20000</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25586,6 +25959,9 @@
       <c r="CN7" t="n">
         <v>23645</v>
       </c>
+      <c r="CO7" t="n">
+        <v>23850</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25868,6 +26244,9 @@
       <c r="CN8" t="n">
         <v>22880</v>
       </c>
+      <c r="CO8" t="n">
+        <v>23180</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26150,6 +26529,9 @@
       <c r="CN9" t="n">
         <v>1257</v>
       </c>
+      <c r="CO9" t="n">
+        <v>1347</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26432,6 +26814,9 @@
       <c r="CN10" t="n">
         <v>18150</v>
       </c>
+      <c r="CO10" t="n">
+        <v>18460</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26714,6 +27099,9 @@
       <c r="CN11" t="n">
         <v>4970</v>
       </c>
+      <c r="CO11" t="n">
+        <v>5095</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26996,6 +27384,9 @@
       <c r="CN12" t="n">
         <v>5320</v>
       </c>
+      <c r="CO12" t="n">
+        <v>5450</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27278,6 +27669,9 @@
       <c r="CN13" t="n">
         <v>5355</v>
       </c>
+      <c r="CO13" t="n">
+        <v>5460</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -27560,6 +27954,9 @@
       <c r="CN14" t="n">
         <v>1340</v>
       </c>
+      <c r="CO14" t="n">
+        <v>1402</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -27842,6 +28239,9 @@
       <c r="CN15" t="n">
         <v>19540</v>
       </c>
+      <c r="CO15" t="n">
+        <v>18930</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -28124,6 +28524,9 @@
       <c r="CN16" t="n">
         <v>10110</v>
       </c>
+      <c r="CO16" t="n">
+        <v>10335</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -28406,6 +28809,9 @@
       <c r="CN17" t="n">
         <v>5870</v>
       </c>
+      <c r="CO17" t="n">
+        <v>5955</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -28688,6 +29094,9 @@
       <c r="CN18" t="n">
         <v>19490</v>
       </c>
+      <c r="CO18" t="n">
+        <v>19900</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -28969,6 +29378,9 @@
       </c>
       <c r="CN19" t="n">
         <v>16060</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>15665</v>
       </c>
     </row>
   </sheetData>
@@ -28982,7 +29394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN19"/>
+  <dimension ref="A1:CO19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29077,6 +29489,7 @@
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
+    <col width="12" customWidth="1" min="93" max="93"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29360,6 +29773,9 @@
       <c r="CN1" s="1" t="n">
         <v>20260113</v>
       </c>
+      <c r="CO1" s="1" t="n">
+        <v>20260114</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29642,6 +30058,9 @@
       <c r="CN2" t="n">
         <v>15335</v>
       </c>
+      <c r="CO2" t="n">
+        <v>14790</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29924,6 +30343,9 @@
       <c r="CN3" t="n">
         <v>69400</v>
       </c>
+      <c r="CO3" t="n">
+        <v>70550</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -30206,6 +30628,9 @@
       <c r="CN4" t="n">
         <v>18265</v>
       </c>
+      <c r="CO4" t="n">
+        <v>17785</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -30488,6 +30913,9 @@
       <c r="CN5" t="n">
         <v>17030</v>
       </c>
+      <c r="CO5" t="n">
+        <v>17320</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -30770,6 +31198,9 @@
       <c r="CN6" t="n">
         <v>20000</v>
       </c>
+      <c r="CO6" t="n">
+        <v>20320</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -31052,6 +31483,9 @@
       <c r="CN7" t="n">
         <v>23935</v>
       </c>
+      <c r="CO7" t="n">
+        <v>24170</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -31334,6 +31768,9 @@
       <c r="CN8" t="n">
         <v>23205</v>
       </c>
+      <c r="CO8" t="n">
+        <v>23620</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -31616,6 +32053,9 @@
       <c r="CN9" t="n">
         <v>1431</v>
       </c>
+      <c r="CO9" t="n">
+        <v>1363</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31898,6 +32338,9 @@
       <c r="CN10" t="n">
         <v>18450</v>
       </c>
+      <c r="CO10" t="n">
+        <v>18715</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -32180,6 +32623,9 @@
       <c r="CN11" t="n">
         <v>5260</v>
       </c>
+      <c r="CO11" t="n">
+        <v>5120</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32462,6 +32908,9 @@
       <c r="CN12" t="n">
         <v>5660</v>
       </c>
+      <c r="CO12" t="n">
+        <v>5460</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32744,6 +33193,9 @@
       <c r="CN13" t="n">
         <v>5670</v>
       </c>
+      <c r="CO13" t="n">
+        <v>5480</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33026,6 +33478,9 @@
       <c r="CN14" t="n">
         <v>1498</v>
       </c>
+      <c r="CO14" t="n">
+        <v>1409</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -33308,6 +33763,9 @@
       <c r="CN15" t="n">
         <v>19625</v>
       </c>
+      <c r="CO15" t="n">
+        <v>19135</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -33590,6 +34048,9 @@
       <c r="CN16" t="n">
         <v>10675</v>
       </c>
+      <c r="CO16" t="n">
+        <v>10365</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -33872,6 +34333,9 @@
       <c r="CN17" t="n">
         <v>6135</v>
       </c>
+      <c r="CO17" t="n">
+        <v>5990</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -34154,6 +34618,9 @@
       <c r="CN18" t="n">
         <v>19785</v>
       </c>
+      <c r="CO18" t="n">
+        <v>20190</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -34435,6 +34902,9 @@
       </c>
       <c r="CN19" t="n">
         <v>16110</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>15790</v>
       </c>
     </row>
   </sheetData>
@@ -34448,7 +34918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN19"/>
+  <dimension ref="A1:CO19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34543,6 +35013,7 @@
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
+    <col width="12" customWidth="1" min="93" max="93"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34826,6 +35297,9 @@
       <c r="CN1" s="1" t="n">
         <v>20260113</v>
       </c>
+      <c r="CO1" s="1" t="n">
+        <v>20260114</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35108,6 +35582,9 @@
       <c r="CN2" t="n">
         <v>406544</v>
       </c>
+      <c r="CO2" t="n">
+        <v>471300</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -35390,6 +35867,9 @@
       <c r="CN3" t="n">
         <v>1824187</v>
       </c>
+      <c r="CO3" t="n">
+        <v>1578326</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -35672,6 +36152,9 @@
       <c r="CN4" t="n">
         <v>193077</v>
       </c>
+      <c r="CO4" t="n">
+        <v>153173</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -35954,6 +36437,9 @@
       <c r="CN5" t="n">
         <v>192340</v>
       </c>
+      <c r="CO5" t="n">
+        <v>248136</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -36236,6 +36722,9 @@
       <c r="CN6" t="n">
         <v>5006118</v>
       </c>
+      <c r="CO6" t="n">
+        <v>4222830</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -36518,6 +37007,9 @@
       <c r="CN7" t="n">
         <v>4151198</v>
       </c>
+      <c r="CO7" t="n">
+        <v>5061270</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -36800,6 +37292,9 @@
       <c r="CN8" t="n">
         <v>12180981</v>
       </c>
+      <c r="CO8" t="n">
+        <v>12397041</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -37082,6 +37577,9 @@
       <c r="CN9" t="n">
         <v>11753486</v>
       </c>
+      <c r="CO9" t="n">
+        <v>7727645</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -37364,6 +37862,9 @@
       <c r="CN10" t="n">
         <v>1192883</v>
       </c>
+      <c r="CO10" t="n">
+        <v>1307979</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -37646,6 +38147,9 @@
       <c r="CN11" t="n">
         <v>911249</v>
       </c>
+      <c r="CO11" t="n">
+        <v>557709</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -37928,6 +38432,9 @@
       <c r="CN12" t="n">
         <v>2422919</v>
       </c>
+      <c r="CO12" t="n">
+        <v>1601665</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -38210,6 +38717,9 @@
       <c r="CN13" t="n">
         <v>5168204</v>
       </c>
+      <c r="CO13" t="n">
+        <v>4187600</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -38492,6 +39002,9 @@
       <c r="CN14" t="n">
         <v>53194181</v>
       </c>
+      <c r="CO14" t="n">
+        <v>40969576</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -38774,6 +39287,9 @@
       <c r="CN15" t="n">
         <v>1453821</v>
       </c>
+      <c r="CO15" t="n">
+        <v>1370181</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -39056,6 +39572,9 @@
       <c r="CN16" t="n">
         <v>493730</v>
       </c>
+      <c r="CO16" t="n">
+        <v>365216</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -39338,6 +39857,9 @@
       <c r="CN17" t="n">
         <v>46247</v>
       </c>
+      <c r="CO17" t="n">
+        <v>40268</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -39620,6 +40142,9 @@
       <c r="CN18" t="n">
         <v>95145</v>
       </c>
+      <c r="CO18" t="n">
+        <v>134881</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -39901,6 +40426,9 @@
       </c>
       <c r="CN19" t="n">
         <v>113034</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>53158</v>
       </c>
     </row>
   </sheetData>
@@ -39914,7 +40442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU19"/>
+  <dimension ref="A1:BV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -39990,6 +40518,7 @@
     <col width="10" customWidth="1" min="71" max="71"/>
     <col width="10" customWidth="1" min="72" max="72"/>
     <col width="10" customWidth="1" min="73" max="73"/>
+    <col width="10" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40216,6 +40745,9 @@
       <c r="BU1" s="1" t="n">
         <v>20260113</v>
       </c>
+      <c r="BV1" s="1" t="n">
+        <v>20260114</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40441,6 +40973,9 @@
       <c r="BU2" t="n">
         <v>49</v>
       </c>
+      <c r="BV2" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40666,6 +41201,9 @@
       <c r="BU3" t="n">
         <v>92</v>
       </c>
+      <c r="BV3" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -40891,6 +41429,9 @@
       <c r="BU4" t="n">
         <v>58</v>
       </c>
+      <c r="BV4" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -41116,6 +41657,9 @@
       <c r="BU5" t="n">
         <v>77</v>
       </c>
+      <c r="BV5" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -41341,6 +41885,9 @@
       <c r="BU6" t="n">
         <v>92</v>
       </c>
+      <c r="BV6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -41566,6 +42113,9 @@
       <c r="BU7" t="n">
         <v>98</v>
       </c>
+      <c r="BV7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -41791,6 +42341,9 @@
       <c r="BU8" t="n">
         <v>92</v>
       </c>
+      <c r="BV8" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -42016,6 +42569,9 @@
       <c r="BU9" t="n">
         <v>60</v>
       </c>
+      <c r="BV9" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -42241,6 +42797,9 @@
       <c r="BU10" t="n">
         <v>80</v>
       </c>
+      <c r="BV10" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -42466,6 +43025,9 @@
       <c r="BU11" t="n">
         <v>56</v>
       </c>
+      <c r="BV11" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -42691,6 +43253,9 @@
       <c r="BU12" t="n">
         <v>56</v>
       </c>
+      <c r="BV12" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -42916,6 +43481,9 @@
       <c r="BU13" t="n">
         <v>51</v>
       </c>
+      <c r="BV13" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -43141,6 +43709,9 @@
       <c r="BU14" t="n">
         <v>50</v>
       </c>
+      <c r="BV14" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -43366,6 +43937,9 @@
       <c r="BU15" t="n">
         <v>53</v>
       </c>
+      <c r="BV15" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -43591,6 +44165,9 @@
       <c r="BU16" t="n">
         <v>60</v>
       </c>
+      <c r="BV16" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -43816,6 +44393,9 @@
       <c r="BU17" t="n">
         <v>47</v>
       </c>
+      <c r="BV17" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -44041,6 +44621,9 @@
       <c r="BU18" t="n">
         <v>81</v>
       </c>
+      <c r="BV18" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -44265,6 +44848,9 @@
       </c>
       <c r="BU19" t="n">
         <v>35</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -44278,7 +44864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG19"/>
+  <dimension ref="A1:AH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -44314,6 +44900,7 @@
     <col width="10" customWidth="1" min="31" max="31"/>
     <col width="10" customWidth="1" min="32" max="32"/>
     <col width="10" customWidth="1" min="33" max="33"/>
+    <col width="10" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -44420,6 +45007,9 @@
       <c r="AG1" s="1" t="n">
         <v>20260113</v>
       </c>
+      <c r="AH1" s="1" t="n">
+        <v>20260114</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -44525,6 +45115,9 @@
       <c r="AG2" t="n">
         <v>66</v>
       </c>
+      <c r="AH2" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -44630,6 +45223,9 @@
       <c r="AG3" t="n">
         <v>92</v>
       </c>
+      <c r="AH3" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -44735,6 +45331,9 @@
       <c r="AG4" t="n">
         <v>72</v>
       </c>
+      <c r="AH4" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -44840,6 +45439,9 @@
       <c r="AG5" t="n">
         <v>77</v>
       </c>
+      <c r="AH5" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -44945,6 +45547,9 @@
       <c r="AG6" t="n">
         <v>93</v>
       </c>
+      <c r="AH6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -45050,6 +45655,9 @@
       <c r="AG7" t="n">
         <v>99</v>
       </c>
+      <c r="AH7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -45155,6 +45763,9 @@
       <c r="AG8" t="n">
         <v>93</v>
       </c>
+      <c r="AH8" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -45260,6 +45871,9 @@
       <c r="AG9" t="n">
         <v>32</v>
       </c>
+      <c r="AH9" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -45365,6 +45979,9 @@
       <c r="AG10" t="n">
         <v>80</v>
       </c>
+      <c r="AH10" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -45470,6 +46087,9 @@
       <c r="AG11" t="n">
         <v>49</v>
       </c>
+      <c r="AH11" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -45575,6 +46195,9 @@
       <c r="AG12" t="n">
         <v>50</v>
       </c>
+      <c r="AH12" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -45680,6 +46303,9 @@
       <c r="AG13" t="n">
         <v>50</v>
       </c>
+      <c r="AH13" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -45785,6 +46411,9 @@
       <c r="AG14" t="n">
         <v>31</v>
       </c>
+      <c r="AH14" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -45890,6 +46519,9 @@
       <c r="AG15" t="n">
         <v>85</v>
       </c>
+      <c r="AH15" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -45995,6 +46627,9 @@
       <c r="AG16" t="n">
         <v>46</v>
       </c>
+      <c r="AH16" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -46100,6 +46735,9 @@
       <c r="AG17" t="n">
         <v>34</v>
       </c>
+      <c r="AH17" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -46205,6 +46843,9 @@
       <c r="AG18" t="n">
         <v>83</v>
       </c>
+      <c r="AH18" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -46309,6 +46950,9 @@
       </c>
       <c r="AG19" t="n">
         <v>82</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -46322,7 +46966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU19"/>
+  <dimension ref="A1:BV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -46398,6 +47042,7 @@
     <col width="10" customWidth="1" min="71" max="71"/>
     <col width="10" customWidth="1" min="72" max="72"/>
     <col width="10" customWidth="1" min="73" max="73"/>
+    <col width="10" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -46624,6 +47269,9 @@
       <c r="BU1" s="1" t="n">
         <v>20260113</v>
       </c>
+      <c r="BV1" s="1" t="n">
+        <v>20260114</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -46849,6 +47497,9 @@
       <c r="BU2" t="n">
         <v>-3</v>
       </c>
+      <c r="BV2" t="n">
+        <v>-51</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -47074,6 +47725,9 @@
       <c r="BU3" t="n">
         <v>59</v>
       </c>
+      <c r="BV3" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -47299,6 +47953,9 @@
       <c r="BU4" t="n">
         <v>22</v>
       </c>
+      <c r="BV4" t="n">
+        <v>-21</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -47524,6 +48181,9 @@
       <c r="BU5" t="n">
         <v>45</v>
       </c>
+      <c r="BV5" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -47749,6 +48409,9 @@
       <c r="BU6" t="n">
         <v>59</v>
       </c>
+      <c r="BV6" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -47974,6 +48637,9 @@
       <c r="BU7" t="n">
         <v>64</v>
       </c>
+      <c r="BV7" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -48199,6 +48865,9 @@
       <c r="BU8" t="n">
         <v>58</v>
       </c>
+      <c r="BV8" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -48424,6 +49093,9 @@
       <c r="BU9" t="n">
         <v>42</v>
       </c>
+      <c r="BV9" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -48649,6 +49321,9 @@
       <c r="BU10" t="n">
         <v>58</v>
       </c>
+      <c r="BV10" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -48874,6 +49549,9 @@
       <c r="BU11" t="n">
         <v>32</v>
       </c>
+      <c r="BV11" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -49099,6 +49777,9 @@
       <c r="BU12" t="n">
         <v>32</v>
       </c>
+      <c r="BV12" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -49324,6 +50005,9 @@
       <c r="BU13" t="n">
         <v>23</v>
       </c>
+      <c r="BV13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -49549,6 +50233,9 @@
       <c r="BU14" t="n">
         <v>25</v>
       </c>
+      <c r="BV14" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -49774,6 +50461,9 @@
       <c r="BU15" t="n">
         <v>16</v>
       </c>
+      <c r="BV15" t="n">
+        <v>-24</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -49999,6 +50689,9 @@
       <c r="BU16" t="n">
         <v>37</v>
       </c>
+      <c r="BV16" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -50224,6 +50917,9 @@
       <c r="BU17" t="n">
         <v>16</v>
       </c>
+      <c r="BV17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -50449,6 +51145,9 @@
       <c r="BU18" t="n">
         <v>55</v>
       </c>
+      <c r="BV18" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -50673,6 +51372,9 @@
       </c>
       <c r="BU19" t="n">
         <v>-4</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>-48</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH19"/>
+  <dimension ref="A1:AI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -746,6 +746,7 @@
     <col width="10" customWidth="1" min="32" max="32"/>
     <col width="10" customWidth="1" min="33" max="33"/>
     <col width="10" customWidth="1" min="34" max="34"/>
+    <col width="10" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,6 +856,9 @@
       <c r="AH1" s="1" t="n">
         <v>20260114</v>
       </c>
+      <c r="AI1" s="1" t="n">
+        <v>20260115</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -963,6 +967,9 @@
       <c r="AH2" t="n">
         <v>-20</v>
       </c>
+      <c r="AI2" t="n">
+        <v>-15</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1071,6 +1078,9 @@
       <c r="AH3" t="n">
         <v>121</v>
       </c>
+      <c r="AI3" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1179,6 +1189,9 @@
       <c r="AH4" t="n">
         <v>-4</v>
       </c>
+      <c r="AI4" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1287,6 +1300,9 @@
       <c r="AH5" t="n">
         <v>80</v>
       </c>
+      <c r="AI5" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1395,6 +1411,9 @@
       <c r="AH6" t="n">
         <v>120</v>
       </c>
+      <c r="AI6" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1503,6 +1522,9 @@
       <c r="AH7" t="n">
         <v>121</v>
       </c>
+      <c r="AI7" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1611,6 +1633,9 @@
       <c r="AH8" t="n">
         <v>121</v>
       </c>
+      <c r="AI8" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1719,6 +1744,9 @@
       <c r="AH9" t="n">
         <v>-40</v>
       </c>
+      <c r="AI9" t="n">
+        <v>-26</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1827,6 +1855,9 @@
       <c r="AH10" t="n">
         <v>104</v>
       </c>
+      <c r="AI10" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1935,6 +1966,9 @@
       <c r="AH11" t="n">
         <v>-23</v>
       </c>
+      <c r="AI11" t="n">
+        <v>-10</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2043,6 +2077,9 @@
       <c r="AH12" t="n">
         <v>-27</v>
       </c>
+      <c r="AI12" t="n">
+        <v>-10</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2151,6 +2188,9 @@
       <c r="AH13" t="n">
         <v>-21</v>
       </c>
+      <c r="AI13" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2259,6 +2299,9 @@
       <c r="AH14" t="n">
         <v>-49</v>
       </c>
+      <c r="AI14" t="n">
+        <v>-38</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2367,6 +2410,9 @@
       <c r="AH15" t="n">
         <v>22</v>
       </c>
+      <c r="AI15" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2475,6 +2521,9 @@
       <c r="AH16" t="n">
         <v>-30</v>
       </c>
+      <c r="AI16" t="n">
+        <v>-13</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2583,6 +2632,9 @@
       <c r="AH17" t="n">
         <v>-45</v>
       </c>
+      <c r="AI17" t="n">
+        <v>-34</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2691,6 +2743,9 @@
       <c r="AH18" t="n">
         <v>107</v>
       </c>
+      <c r="AI18" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2798,6 +2853,9 @@
       </c>
       <c r="AH19" t="n">
         <v>18</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -2811,7 +2869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV19"/>
+  <dimension ref="A1:BW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2888,6 +2946,7 @@
     <col width="12" customWidth="1" min="72" max="72"/>
     <col width="12" customWidth="1" min="73" max="73"/>
     <col width="12" customWidth="1" min="74" max="74"/>
+    <col width="12" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3261,6 +3320,11 @@
           <t>20260114</t>
         </is>
       </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>20260115</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3489,6 +3553,9 @@
       <c r="BV2" t="n">
         <v>96</v>
       </c>
+      <c r="BW2" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3717,6 +3784,9 @@
       <c r="BV3" t="n">
         <v>112</v>
       </c>
+      <c r="BW3" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3945,6 +4015,9 @@
       <c r="BV4" t="n">
         <v>99</v>
       </c>
+      <c r="BW4" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4173,6 +4246,9 @@
       <c r="BV5" t="n">
         <v>106</v>
       </c>
+      <c r="BW5" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4401,6 +4477,9 @@
       <c r="BV6" t="n">
         <v>111</v>
       </c>
+      <c r="BW6" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4629,6 +4708,9 @@
       <c r="BV7" t="n">
         <v>112</v>
       </c>
+      <c r="BW7" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4857,6 +4939,9 @@
       <c r="BV8" t="n">
         <v>114</v>
       </c>
+      <c r="BW8" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5085,6 +5170,9 @@
       <c r="BV9" t="n">
         <v>104</v>
       </c>
+      <c r="BW9" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5313,6 +5401,9 @@
       <c r="BV10" t="n">
         <v>108</v>
       </c>
+      <c r="BW10" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5541,6 +5632,9 @@
       <c r="BV11" t="n">
         <v>101</v>
       </c>
+      <c r="BW11" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5769,6 +5863,9 @@
       <c r="BV12" t="n">
         <v>101</v>
       </c>
+      <c r="BW12" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5997,6 +6094,9 @@
       <c r="BV13" t="n">
         <v>100</v>
       </c>
+      <c r="BW13" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6225,6 +6325,9 @@
       <c r="BV14" t="n">
         <v>101</v>
       </c>
+      <c r="BW14" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6453,6 +6556,9 @@
       <c r="BV15" t="n">
         <v>99</v>
       </c>
+      <c r="BW15" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6681,6 +6787,9 @@
       <c r="BV16" t="n">
         <v>101</v>
       </c>
+      <c r="BW16" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6909,6 +7018,9 @@
       <c r="BV17" t="n">
         <v>100</v>
       </c>
+      <c r="BW17" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7137,6 +7249,9 @@
       <c r="BV18" t="n">
         <v>109</v>
       </c>
+      <c r="BW18" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7363,6 +7478,9 @@
         <v>100</v>
       </c>
       <c r="BV19" t="n">
+        <v>98</v>
+      </c>
+      <c r="BW19" t="n">
         <v>98</v>
       </c>
     </row>
@@ -7377,7 +7495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC19"/>
+  <dimension ref="A1:BD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7386,6 +7504,7 @@
     <col width="12" customWidth="1" min="53" max="53"/>
     <col width="12" customWidth="1" min="54" max="54"/>
     <col width="12" customWidth="1" min="55" max="55"/>
+    <col width="12" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7566,6 +7685,11 @@
           <t>20260114</t>
         </is>
       </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>20260115</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7737,6 +7861,9 @@
       <c r="BC2" t="n">
         <v>5.56</v>
       </c>
+      <c r="BD2" t="n">
+        <v>3.78</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7908,6 +8035,9 @@
       <c r="BC3" t="n">
         <v>106.13</v>
       </c>
+      <c r="BD3" t="n">
+        <v>92.95</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8079,6 +8209,9 @@
       <c r="BC4" t="n">
         <v>-2.42</v>
       </c>
+      <c r="BD4" t="n">
+        <v>-2.49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8250,6 +8383,9 @@
       <c r="BC5" t="n">
         <v>57.34</v>
       </c>
+      <c r="BD5" t="n">
+        <v>50.39</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8421,6 +8557,9 @@
       <c r="BC6" t="n">
         <v>99.06999999999999</v>
       </c>
+      <c r="BD6" t="n">
+        <v>88.13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8592,6 +8731,9 @@
       <c r="BC7" t="n">
         <v>105.15</v>
       </c>
+      <c r="BD7" t="n">
+        <v>93.97</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8763,6 +8905,9 @@
       <c r="BC8" t="n">
         <v>113.02</v>
       </c>
+      <c r="BD8" t="n">
+        <v>97.41</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8934,6 +9079,9 @@
       <c r="BC9" t="n">
         <v>-12.39</v>
       </c>
+      <c r="BD9" t="n">
+        <v>-28.06</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9105,6 +9253,9 @@
       <c r="BC10" t="n">
         <v>56.16</v>
       </c>
+      <c r="BD10" t="n">
+        <v>53.24</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9276,6 +9427,9 @@
       <c r="BC11" t="n">
         <v>-18.26</v>
       </c>
+      <c r="BD11" t="n">
+        <v>-31.74</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9447,6 +9601,9 @@
       <c r="BC12" t="n">
         <v>-18.9</v>
       </c>
+      <c r="BD12" t="n">
+        <v>-33.28</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9618,6 +9775,9 @@
       <c r="BC13" t="n">
         <v>-24.02</v>
       </c>
+      <c r="BD13" t="n">
+        <v>-38.14</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9789,6 +9949,9 @@
       <c r="BC14" t="n">
         <v>-15.16</v>
       </c>
+      <c r="BD14" t="n">
+        <v>-33.16</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9960,6 +10123,9 @@
       <c r="BC15" t="n">
         <v>6.2</v>
       </c>
+      <c r="BD15" t="n">
+        <v>6.11</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10131,6 +10297,9 @@
       <c r="BC16" t="n">
         <v>-18.74</v>
       </c>
+      <c r="BD16" t="n">
+        <v>-33.38</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10302,6 +10471,9 @@
       <c r="BC17" t="n">
         <v>-16.07</v>
       </c>
+      <c r="BD17" t="n">
+        <v>-33.06</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10473,6 +10645,9 @@
       <c r="BC18" t="n">
         <v>58.55</v>
       </c>
+      <c r="BD18" t="n">
+        <v>56.57</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10643,6 +10818,9 @@
       </c>
       <c r="BC19" t="n">
         <v>1.31</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>3.32</v>
       </c>
     </row>
   </sheetData>
@@ -10656,7 +10834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH19"/>
+  <dimension ref="A1:AI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10693,6 +10871,7 @@
     <col width="12" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10866,6 +11045,11 @@
           <t>20260114</t>
         </is>
       </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>20260115</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10974,6 +11158,9 @@
       <c r="AH2" t="n">
         <v>152</v>
       </c>
+      <c r="AI2" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11082,6 +11269,9 @@
       <c r="AH3" t="n">
         <v>33</v>
       </c>
+      <c r="AI3" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11190,6 +11380,9 @@
       <c r="AH4" t="n">
         <v>41</v>
       </c>
+      <c r="AI4" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11298,6 +11491,9 @@
       <c r="AH5" t="n">
         <v>24</v>
       </c>
+      <c r="AI5" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11406,6 +11602,9 @@
       <c r="AH6" t="n">
         <v>82</v>
       </c>
+      <c r="AI6" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11514,6 +11713,9 @@
       <c r="AH7" t="n">
         <v>65</v>
       </c>
+      <c r="AI7" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11622,6 +11824,9 @@
       <c r="AH8" t="n">
         <v>76</v>
       </c>
+      <c r="AI8" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11730,6 +11935,9 @@
       <c r="AH9" t="n">
         <v>53</v>
       </c>
+      <c r="AI9" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11838,6 +12046,9 @@
       <c r="AH10" t="n">
         <v>52</v>
       </c>
+      <c r="AI10" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11946,6 +12157,9 @@
       <c r="AH11" t="n">
         <v>22</v>
       </c>
+      <c r="AI11" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12054,6 +12268,9 @@
       <c r="AH12" t="n">
         <v>29</v>
       </c>
+      <c r="AI12" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12162,6 +12379,9 @@
       <c r="AH13" t="n">
         <v>31</v>
       </c>
+      <c r="AI13" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12270,6 +12490,9 @@
       <c r="AH14" t="n">
         <v>42</v>
       </c>
+      <c r="AI14" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12378,6 +12601,9 @@
       <c r="AH15" t="n">
         <v>37</v>
       </c>
+      <c r="AI15" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12486,6 +12712,9 @@
       <c r="AH16" t="n">
         <v>31</v>
       </c>
+      <c r="AI16" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12594,6 +12823,9 @@
       <c r="AH17" t="n">
         <v>9</v>
       </c>
+      <c r="AI17" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12702,6 +12934,9 @@
       <c r="AH18" t="n">
         <v>39</v>
       </c>
+      <c r="AI18" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12809,6 +13044,9 @@
       </c>
       <c r="AH19" t="n">
         <v>52</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -12822,7 +13060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CO19"/>
+  <dimension ref="A1:CP19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12918,6 +13156,7 @@
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
+    <col width="12" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13204,6 +13443,9 @@
       <c r="CO1" s="1" t="n">
         <v>20260114</v>
       </c>
+      <c r="CP1" s="1" t="n">
+        <v>20260115</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13489,6 +13731,9 @@
       <c r="CO2" t="n">
         <v>15485</v>
       </c>
+      <c r="CP2" t="n">
+        <v>14870</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13774,6 +14019,9 @@
       <c r="CO3" t="n">
         <v>69380</v>
       </c>
+      <c r="CP3" t="n">
+        <v>69605</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14059,6 +14307,9 @@
       <c r="CO4" t="n">
         <v>18355</v>
       </c>
+      <c r="CP4" t="n">
+        <v>17940</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14344,6 +14595,9 @@
       <c r="CO5" t="n">
         <v>17100</v>
       </c>
+      <c r="CP5" t="n">
+        <v>17150</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14629,6 +14883,9 @@
       <c r="CO6" t="n">
         <v>20000</v>
       </c>
+      <c r="CP6" t="n">
+        <v>20110</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14914,6 +15171,9 @@
       <c r="CO7" t="n">
         <v>23935</v>
       </c>
+      <c r="CP7" t="n">
+        <v>23925</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15199,6 +15459,9 @@
       <c r="CO8" t="n">
         <v>23205</v>
       </c>
+      <c r="CP8" t="n">
+        <v>23270</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15484,6 +15747,9 @@
       <c r="CO9" t="n">
         <v>1440</v>
       </c>
+      <c r="CP9" t="n">
+        <v>1384</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15769,6 +16035,9 @@
       <c r="CO10" t="n">
         <v>18580</v>
       </c>
+      <c r="CP10" t="n">
+        <v>18435</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16054,6 +16323,9 @@
       <c r="CO11" t="n">
         <v>5260</v>
       </c>
+      <c r="CP11" t="n">
+        <v>5150</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16339,6 +16611,9 @@
       <c r="CO12" t="n">
         <v>5550</v>
       </c>
+      <c r="CP12" t="n">
+        <v>5505</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16624,6 +16899,9 @@
       <c r="CO13" t="n">
         <v>5650</v>
       </c>
+      <c r="CP13" t="n">
+        <v>5490</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16909,6 +17187,9 @@
       <c r="CO14" t="n">
         <v>1483</v>
       </c>
+      <c r="CP14" t="n">
+        <v>1418</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17194,6 +17475,9 @@
       <c r="CO15" t="n">
         <v>19735</v>
       </c>
+      <c r="CP15" t="n">
+        <v>19155</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -17479,6 +17763,9 @@
       <c r="CO16" t="n">
         <v>10625</v>
       </c>
+      <c r="CP16" t="n">
+        <v>10460</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17764,6 +18051,9 @@
       <c r="CO17" t="n">
         <v>6135</v>
       </c>
+      <c r="CP17" t="n">
+        <v>6015</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -18049,6 +18339,9 @@
       <c r="CO18" t="n">
         <v>20050</v>
       </c>
+      <c r="CP18" t="n">
+        <v>19935</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -18333,6 +18626,9 @@
       </c>
       <c r="CO19" t="n">
         <v>16190</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>15935</v>
       </c>
     </row>
   </sheetData>
@@ -18346,7 +18642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CO19"/>
+  <dimension ref="A1:CP19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18442,6 +18738,7 @@
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
+    <col width="12" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18728,6 +19025,9 @@
       <c r="CO1" s="1" t="n">
         <v>20260114</v>
       </c>
+      <c r="CP1" s="1" t="n">
+        <v>20260115</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19013,6 +19313,9 @@
       <c r="CO2" t="n">
         <v>15485</v>
       </c>
+      <c r="CP2" t="n">
+        <v>15000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19298,6 +19601,9 @@
       <c r="CO3" t="n">
         <v>70770</v>
       </c>
+      <c r="CP3" t="n">
+        <v>71150</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19583,6 +19889,9 @@
       <c r="CO4" t="n">
         <v>18385</v>
       </c>
+      <c r="CP4" t="n">
+        <v>18050</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19868,6 +20177,9 @@
       <c r="CO5" t="n">
         <v>17320</v>
       </c>
+      <c r="CP5" t="n">
+        <v>17480</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20153,6 +20465,9 @@
       <c r="CO6" t="n">
         <v>20415</v>
       </c>
+      <c r="CP6" t="n">
+        <v>20580</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20438,6 +20753,9 @@
       <c r="CO7" t="n">
         <v>24310</v>
       </c>
+      <c r="CP7" t="n">
+        <v>24440</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20723,6 +21041,9 @@
       <c r="CO8" t="n">
         <v>23750</v>
       </c>
+      <c r="CP8" t="n">
+        <v>23840</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21008,6 +21329,9 @@
       <c r="CO9" t="n">
         <v>1440</v>
       </c>
+      <c r="CP9" t="n">
+        <v>1432</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21293,6 +21617,9 @@
       <c r="CO10" t="n">
         <v>18900</v>
       </c>
+      <c r="CP10" t="n">
+        <v>18870</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -21578,6 +21905,9 @@
       <c r="CO11" t="n">
         <v>5270</v>
       </c>
+      <c r="CP11" t="n">
+        <v>5250</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -21863,6 +22193,9 @@
       <c r="CO12" t="n">
         <v>5635</v>
       </c>
+      <c r="CP12" t="n">
+        <v>5615</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -22148,6 +22481,9 @@
       <c r="CO13" t="n">
         <v>5650</v>
       </c>
+      <c r="CP13" t="n">
+        <v>5620</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -22433,6 +22769,9 @@
       <c r="CO14" t="n">
         <v>1484</v>
       </c>
+      <c r="CP14" t="n">
+        <v>1462</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -22718,6 +23057,9 @@
       <c r="CO15" t="n">
         <v>19875</v>
       </c>
+      <c r="CP15" t="n">
+        <v>19320</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -23003,6 +23345,9 @@
       <c r="CO16" t="n">
         <v>10625</v>
       </c>
+      <c r="CP16" t="n">
+        <v>10600</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -23288,6 +23633,9 @@
       <c r="CO17" t="n">
         <v>6135</v>
       </c>
+      <c r="CP17" t="n">
+        <v>6105</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -23573,6 +23921,9 @@
       <c r="CO18" t="n">
         <v>20450</v>
       </c>
+      <c r="CP18" t="n">
+        <v>20575</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -23857,6 +24208,9 @@
       </c>
       <c r="CO19" t="n">
         <v>16200</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>16005</v>
       </c>
     </row>
   </sheetData>
@@ -23870,7 +24224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CO19"/>
+  <dimension ref="A1:CP19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23966,6 +24320,7 @@
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
+    <col width="12" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24252,6 +24607,9 @@
       <c r="CO1" s="1" t="n">
         <v>20260114</v>
       </c>
+      <c r="CP1" s="1" t="n">
+        <v>20260115</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24537,6 +24895,9 @@
       <c r="CO2" t="n">
         <v>14595</v>
       </c>
+      <c r="CP2" t="n">
+        <v>14715</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24822,6 +25183,9 @@
       <c r="CO3" t="n">
         <v>69300</v>
       </c>
+      <c r="CP3" t="n">
+        <v>69175</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25107,6 +25471,9 @@
       <c r="CO4" t="n">
         <v>17675</v>
       </c>
+      <c r="CP4" t="n">
+        <v>17760</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25392,6 +25759,9 @@
       <c r="CO5" t="n">
         <v>17065</v>
       </c>
+      <c r="CP5" t="n">
+        <v>17075</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25677,6 +26047,9 @@
       <c r="CO6" t="n">
         <v>20000</v>
       </c>
+      <c r="CP6" t="n">
+        <v>19970</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25962,6 +26335,9 @@
       <c r="CO7" t="n">
         <v>23850</v>
       </c>
+      <c r="CP7" t="n">
+        <v>23760</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26247,6 +26623,9 @@
       <c r="CO8" t="n">
         <v>23180</v>
       </c>
+      <c r="CP8" t="n">
+        <v>23160</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26532,6 +26911,9 @@
       <c r="CO9" t="n">
         <v>1347</v>
       </c>
+      <c r="CP9" t="n">
+        <v>1368</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26817,6 +27199,9 @@
       <c r="CO10" t="n">
         <v>18460</v>
       </c>
+      <c r="CP10" t="n">
+        <v>18380</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27102,6 +27487,9 @@
       <c r="CO11" t="n">
         <v>5095</v>
       </c>
+      <c r="CP11" t="n">
+        <v>5097</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27387,6 +27775,9 @@
       <c r="CO12" t="n">
         <v>5450</v>
       </c>
+      <c r="CP12" t="n">
+        <v>5440</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27672,6 +28063,9 @@
       <c r="CO13" t="n">
         <v>5460</v>
       </c>
+      <c r="CP13" t="n">
+        <v>5440</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -27957,6 +28351,9 @@
       <c r="CO14" t="n">
         <v>1402</v>
       </c>
+      <c r="CP14" t="n">
+        <v>1396</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -28242,6 +28639,9 @@
       <c r="CO15" t="n">
         <v>18930</v>
       </c>
+      <c r="CP15" t="n">
+        <v>19045</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -28527,6 +28927,9 @@
       <c r="CO16" t="n">
         <v>10335</v>
       </c>
+      <c r="CP16" t="n">
+        <v>10330</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -28812,6 +29215,9 @@
       <c r="CO17" t="n">
         <v>5955</v>
       </c>
+      <c r="CP17" t="n">
+        <v>5950</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -29097,6 +29503,9 @@
       <c r="CO18" t="n">
         <v>19900</v>
       </c>
+      <c r="CP18" t="n">
+        <v>19930</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -29381,6 +29790,9 @@
       </c>
       <c r="CO19" t="n">
         <v>15665</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>15750</v>
       </c>
     </row>
   </sheetData>
@@ -29394,7 +29806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CO19"/>
+  <dimension ref="A1:CP19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29490,6 +29902,7 @@
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
+    <col width="12" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29776,6 +30189,9 @@
       <c r="CO1" s="1" t="n">
         <v>20260114</v>
       </c>
+      <c r="CP1" s="1" t="n">
+        <v>20260115</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30061,6 +30477,9 @@
       <c r="CO2" t="n">
         <v>14790</v>
       </c>
+      <c r="CP2" t="n">
+        <v>14920</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -30346,6 +30765,9 @@
       <c r="CO3" t="n">
         <v>70550</v>
       </c>
+      <c r="CP3" t="n">
+        <v>71150</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -30631,6 +31053,9 @@
       <c r="CO4" t="n">
         <v>17785</v>
       </c>
+      <c r="CP4" t="n">
+        <v>17825</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -30916,6 +31341,9 @@
       <c r="CO5" t="n">
         <v>17320</v>
       </c>
+      <c r="CP5" t="n">
+        <v>17480</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -31201,6 +31629,9 @@
       <c r="CO6" t="n">
         <v>20320</v>
       </c>
+      <c r="CP6" t="n">
+        <v>20580</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -31486,6 +31917,9 @@
       <c r="CO7" t="n">
         <v>24170</v>
       </c>
+      <c r="CP7" t="n">
+        <v>24440</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -31771,6 +32205,9 @@
       <c r="CO8" t="n">
         <v>23620</v>
       </c>
+      <c r="CP8" t="n">
+        <v>23840</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -32056,6 +32493,9 @@
       <c r="CO9" t="n">
         <v>1363</v>
       </c>
+      <c r="CP9" t="n">
+        <v>1416</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -32341,6 +32781,9 @@
       <c r="CO10" t="n">
         <v>18715</v>
       </c>
+      <c r="CP10" t="n">
+        <v>18835</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -32626,6 +33069,9 @@
       <c r="CO11" t="n">
         <v>5120</v>
       </c>
+      <c r="CP11" t="n">
+        <v>5195</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32911,6 +33357,9 @@
       <c r="CO12" t="n">
         <v>5460</v>
       </c>
+      <c r="CP12" t="n">
+        <v>5580</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33196,6 +33645,9 @@
       <c r="CO13" t="n">
         <v>5480</v>
       </c>
+      <c r="CP13" t="n">
+        <v>5575</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33481,6 +33933,9 @@
       <c r="CO14" t="n">
         <v>1409</v>
       </c>
+      <c r="CP14" t="n">
+        <v>1455</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -33766,6 +34221,9 @@
       <c r="CO15" t="n">
         <v>19135</v>
       </c>
+      <c r="CP15" t="n">
+        <v>19200</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -34051,6 +34509,9 @@
       <c r="CO16" t="n">
         <v>10365</v>
       </c>
+      <c r="CP16" t="n">
+        <v>10585</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -34336,6 +34797,9 @@
       <c r="CO17" t="n">
         <v>5990</v>
       </c>
+      <c r="CP17" t="n">
+        <v>6080</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -34621,6 +35085,9 @@
       <c r="CO18" t="n">
         <v>20190</v>
       </c>
+      <c r="CP18" t="n">
+        <v>20575</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -34905,6 +35372,9 @@
       </c>
       <c r="CO19" t="n">
         <v>15790</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>15860</v>
       </c>
     </row>
   </sheetData>
@@ -34918,7 +35388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CO19"/>
+  <dimension ref="A1:CP19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35014,6 +35484,7 @@
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
+    <col width="12" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35300,6 +35771,9 @@
       <c r="CO1" s="1" t="n">
         <v>20260114</v>
       </c>
+      <c r="CP1" s="1" t="n">
+        <v>20260115</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35585,6 +36059,9 @@
       <c r="CO2" t="n">
         <v>471300</v>
       </c>
+      <c r="CP2" t="n">
+        <v>227774</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -35870,6 +36347,9 @@
       <c r="CO3" t="n">
         <v>1578326</v>
       </c>
+      <c r="CP3" t="n">
+        <v>1656816</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -36155,6 +36635,9 @@
       <c r="CO4" t="n">
         <v>153173</v>
       </c>
+      <c r="CP4" t="n">
+        <v>95278</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -36440,6 +36923,9 @@
       <c r="CO5" t="n">
         <v>248136</v>
       </c>
+      <c r="CP5" t="n">
+        <v>224836</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -36725,6 +37211,9 @@
       <c r="CO6" t="n">
         <v>4222830</v>
       </c>
+      <c r="CP6" t="n">
+        <v>3807701</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -37010,6 +37499,9 @@
       <c r="CO7" t="n">
         <v>5061270</v>
       </c>
+      <c r="CP7" t="n">
+        <v>5496821</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -37295,6 +37787,9 @@
       <c r="CO8" t="n">
         <v>12397041</v>
       </c>
+      <c r="CP8" t="n">
+        <v>14519533</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -37580,6 +38075,9 @@
       <c r="CO9" t="n">
         <v>7727645</v>
       </c>
+      <c r="CP9" t="n">
+        <v>8762186</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -37865,6 +38363,9 @@
       <c r="CO10" t="n">
         <v>1307979</v>
       </c>
+      <c r="CP10" t="n">
+        <v>1076133</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -38150,6 +38651,9 @@
       <c r="CO11" t="n">
         <v>557709</v>
       </c>
+      <c r="CP11" t="n">
+        <v>728057</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -38435,6 +38939,9 @@
       <c r="CO12" t="n">
         <v>1601665</v>
       </c>
+      <c r="CP12" t="n">
+        <v>2429250</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -38720,6 +39227,9 @@
       <c r="CO13" t="n">
         <v>4187600</v>
       </c>
+      <c r="CP13" t="n">
+        <v>4490095</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39005,6 +39515,9 @@
       <c r="CO14" t="n">
         <v>40969576</v>
       </c>
+      <c r="CP14" t="n">
+        <v>42180563</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39290,6 +39803,9 @@
       <c r="CO15" t="n">
         <v>1370181</v>
       </c>
+      <c r="CP15" t="n">
+        <v>1024746</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -39575,6 +40091,9 @@
       <c r="CO16" t="n">
         <v>365216</v>
       </c>
+      <c r="CP16" t="n">
+        <v>263716</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -39860,6 +40379,9 @@
       <c r="CO17" t="n">
         <v>40268</v>
       </c>
+      <c r="CP17" t="n">
+        <v>62118</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -40145,6 +40667,9 @@
       <c r="CO18" t="n">
         <v>134881</v>
       </c>
+      <c r="CP18" t="n">
+        <v>98633</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -40429,6 +40954,9 @@
       </c>
       <c r="CO19" t="n">
         <v>53158</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>45070</v>
       </c>
     </row>
   </sheetData>
@@ -40442,7 +40970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV19"/>
+  <dimension ref="A1:BW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -40519,6 +41047,7 @@
     <col width="10" customWidth="1" min="72" max="72"/>
     <col width="10" customWidth="1" min="73" max="73"/>
     <col width="10" customWidth="1" min="74" max="74"/>
+    <col width="10" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40748,6 +41277,9 @@
       <c r="BV1" s="1" t="n">
         <v>20260114</v>
       </c>
+      <c r="BW1" s="1" t="n">
+        <v>20260115</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40976,6 +41508,9 @@
       <c r="BV2" t="n">
         <v>19</v>
       </c>
+      <c r="BW2" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -41204,6 +41739,9 @@
       <c r="BV3" t="n">
         <v>99</v>
       </c>
+      <c r="BW3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -41432,6 +41970,9 @@
       <c r="BV4" t="n">
         <v>31</v>
       </c>
+      <c r="BW4" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -41660,6 +42201,9 @@
       <c r="BV5" t="n">
         <v>87</v>
       </c>
+      <c r="BW5" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -41888,6 +42432,9 @@
       <c r="BV6" t="n">
         <v>100</v>
       </c>
+      <c r="BW6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -42116,6 +42663,9 @@
       <c r="BV7" t="n">
         <v>100</v>
       </c>
+      <c r="BW7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -42344,6 +42894,9 @@
       <c r="BV8" t="n">
         <v>99</v>
       </c>
+      <c r="BW8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -42572,6 +43125,9 @@
       <c r="BV9" t="n">
         <v>46</v>
       </c>
+      <c r="BW9" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -42800,6 +43356,9 @@
       <c r="BV10" t="n">
         <v>88</v>
       </c>
+      <c r="BW10" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -43028,6 +43587,9 @@
       <c r="BV11" t="n">
         <v>41</v>
       </c>
+      <c r="BW11" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -43256,6 +43818,9 @@
       <c r="BV12" t="n">
         <v>39</v>
       </c>
+      <c r="BW12" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -43484,6 +44049,9 @@
       <c r="BV13" t="n">
         <v>34</v>
       </c>
+      <c r="BW13" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -43712,6 +44280,9 @@
       <c r="BV14" t="n">
         <v>34</v>
       </c>
+      <c r="BW14" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -43940,6 +44511,9 @@
       <c r="BV15" t="n">
         <v>29</v>
       </c>
+      <c r="BW15" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -44168,6 +44742,9 @@
       <c r="BV16" t="n">
         <v>43</v>
       </c>
+      <c r="BW16" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -44396,6 +44973,9 @@
       <c r="BV17" t="n">
         <v>35</v>
       </c>
+      <c r="BW17" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -44624,6 +45204,9 @@
       <c r="BV18" t="n">
         <v>91</v>
       </c>
+      <c r="BW18" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -44851,6 +45434,9 @@
       </c>
       <c r="BV19" t="n">
         <v>8</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -44864,7 +45450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH19"/>
+  <dimension ref="A1:AI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -44901,6 +45487,7 @@
     <col width="10" customWidth="1" min="32" max="32"/>
     <col width="10" customWidth="1" min="33" max="33"/>
     <col width="10" customWidth="1" min="34" max="34"/>
+    <col width="10" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -45010,6 +45597,9 @@
       <c r="AH1" s="1" t="n">
         <v>20260114</v>
       </c>
+      <c r="AI1" s="1" t="n">
+        <v>20260115</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -45118,6 +45708,9 @@
       <c r="AH2" t="n">
         <v>49</v>
       </c>
+      <c r="AI2" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -45226,6 +45819,9 @@
       <c r="AH3" t="n">
         <v>99</v>
       </c>
+      <c r="AI3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -45334,6 +45930,9 @@
       <c r="AH4" t="n">
         <v>56</v>
       </c>
+      <c r="AI4" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -45442,6 +46041,9 @@
       <c r="AH5" t="n">
         <v>87</v>
       </c>
+      <c r="AI5" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -45550,6 +46152,9 @@
       <c r="AH6" t="n">
         <v>100</v>
       </c>
+      <c r="AI6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -45658,6 +46263,9 @@
       <c r="AH7" t="n">
         <v>100</v>
       </c>
+      <c r="AI7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -45766,6 +46374,9 @@
       <c r="AH8" t="n">
         <v>99</v>
       </c>
+      <c r="AI8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -45874,6 +46485,9 @@
       <c r="AH9" t="n">
         <v>24</v>
       </c>
+      <c r="AI9" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -45982,6 +46596,9 @@
       <c r="AH10" t="n">
         <v>88</v>
       </c>
+      <c r="AI10" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -46090,6 +46707,9 @@
       <c r="AH11" t="n">
         <v>35</v>
       </c>
+      <c r="AI11" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -46198,6 +46818,9 @@
       <c r="AH12" t="n">
         <v>35</v>
       </c>
+      <c r="AI12" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -46306,6 +46929,9 @@
       <c r="AH13" t="n">
         <v>36</v>
       </c>
+      <c r="AI13" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -46414,6 +47040,9 @@
       <c r="AH14" t="n">
         <v>20</v>
       </c>
+      <c r="AI14" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -46522,6 +47151,9 @@
       <c r="AH15" t="n">
         <v>77</v>
       </c>
+      <c r="AI15" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -46630,6 +47262,9 @@
       <c r="AH16" t="n">
         <v>33</v>
       </c>
+      <c r="AI16" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -46738,6 +47373,9 @@
       <c r="AH17" t="n">
         <v>26</v>
       </c>
+      <c r="AI17" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -46846,6 +47484,9 @@
       <c r="AH18" t="n">
         <v>92</v>
       </c>
+      <c r="AI18" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -46953,6 +47594,9 @@
       </c>
       <c r="AH19" t="n">
         <v>74</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -46966,7 +47610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV19"/>
+  <dimension ref="A1:BW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -47043,6 +47687,7 @@
     <col width="10" customWidth="1" min="72" max="72"/>
     <col width="10" customWidth="1" min="73" max="73"/>
     <col width="10" customWidth="1" min="74" max="74"/>
+    <col width="10" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -47272,6 +47917,9 @@
       <c r="BV1" s="1" t="n">
         <v>20260114</v>
       </c>
+      <c r="BW1" s="1" t="n">
+        <v>20260115</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -47500,6 +48148,9 @@
       <c r="BV2" t="n">
         <v>-51</v>
       </c>
+      <c r="BW2" t="n">
+        <v>-35</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -47728,6 +48379,9 @@
       <c r="BV3" t="n">
         <v>61</v>
       </c>
+      <c r="BW3" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -47956,6 +48610,9 @@
       <c r="BV4" t="n">
         <v>-21</v>
       </c>
+      <c r="BW4" t="n">
+        <v>-17</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -48184,6 +48841,9 @@
       <c r="BV5" t="n">
         <v>55</v>
       </c>
+      <c r="BW5" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -48412,6 +49072,9 @@
       <c r="BV6" t="n">
         <v>62</v>
       </c>
+      <c r="BW6" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -48640,6 +49303,9 @@
       <c r="BV7" t="n">
         <v>63</v>
       </c>
+      <c r="BW7" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -48868,6 +49534,9 @@
       <c r="BV8" t="n">
         <v>60</v>
       </c>
+      <c r="BW8" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -49096,6 +49765,9 @@
       <c r="BV9" t="n">
         <v>24</v>
       </c>
+      <c r="BW9" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -49324,6 +49996,9 @@
       <c r="BV10" t="n">
         <v>64</v>
       </c>
+      <c r="BW10" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -49552,6 +50227,9 @@
       <c r="BV11" t="n">
         <v>12</v>
       </c>
+      <c r="BW11" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -49780,6 +50458,9 @@
       <c r="BV12" t="n">
         <v>7</v>
       </c>
+      <c r="BW12" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -50008,6 +50689,9 @@
       <c r="BV13" t="n">
         <v>0</v>
       </c>
+      <c r="BW13" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -50236,6 +50920,9 @@
       <c r="BV14" t="n">
         <v>3</v>
       </c>
+      <c r="BW14" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -50464,6 +51151,9 @@
       <c r="BV15" t="n">
         <v>-24</v>
       </c>
+      <c r="BW15" t="n">
+        <v>-17</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -50692,6 +51382,9 @@
       <c r="BV16" t="n">
         <v>15</v>
       </c>
+      <c r="BW16" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -50920,6 +51613,9 @@
       <c r="BV17" t="n">
         <v>1</v>
       </c>
+      <c r="BW17" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -51148,6 +51844,9 @@
       <c r="BV18" t="n">
         <v>64</v>
       </c>
+      <c r="BW18" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -51375,6 +52074,9 @@
       </c>
       <c r="BV19" t="n">
         <v>-48</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>-35</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI19"/>
+  <dimension ref="A1:AJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -747,6 +747,7 @@
     <col width="10" customWidth="1" min="33" max="33"/>
     <col width="10" customWidth="1" min="34" max="34"/>
     <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -859,6 +860,9 @@
       <c r="AI1" s="1" t="n">
         <v>20260115</v>
       </c>
+      <c r="AJ1" s="1" t="n">
+        <v>20260116</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -970,6 +974,9 @@
       <c r="AI2" t="n">
         <v>-15</v>
       </c>
+      <c r="AJ2" t="n">
+        <v>-11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1081,6 +1088,9 @@
       <c r="AI3" t="n">
         <v>119</v>
       </c>
+      <c r="AJ3" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1192,6 +1202,9 @@
       <c r="AI4" t="n">
         <v>-4</v>
       </c>
+      <c r="AJ4" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1303,6 +1316,9 @@
       <c r="AI5" t="n">
         <v>88</v>
       </c>
+      <c r="AJ5" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1414,6 +1430,9 @@
       <c r="AI6" t="n">
         <v>121</v>
       </c>
+      <c r="AJ6" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1525,6 +1544,9 @@
       <c r="AI7" t="n">
         <v>120</v>
       </c>
+      <c r="AJ7" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1636,6 +1658,9 @@
       <c r="AI8" t="n">
         <v>119</v>
       </c>
+      <c r="AJ8" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1747,6 +1772,9 @@
       <c r="AI9" t="n">
         <v>-26</v>
       </c>
+      <c r="AJ9" t="n">
+        <v>-42</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1858,6 +1886,9 @@
       <c r="AI10" t="n">
         <v>106</v>
       </c>
+      <c r="AJ10" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1969,6 +2000,9 @@
       <c r="AI11" t="n">
         <v>-10</v>
       </c>
+      <c r="AJ11" t="n">
+        <v>-41</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2080,6 +2114,9 @@
       <c r="AI12" t="n">
         <v>-10</v>
       </c>
+      <c r="AJ12" t="n">
+        <v>-40</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2191,6 +2228,9 @@
       <c r="AI13" t="n">
         <v>-8</v>
       </c>
+      <c r="AJ13" t="n">
+        <v>-36</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2302,6 +2342,9 @@
       <c r="AI14" t="n">
         <v>-38</v>
       </c>
+      <c r="AJ14" t="n">
+        <v>-53</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2413,6 +2456,9 @@
       <c r="AI15" t="n">
         <v>23</v>
       </c>
+      <c r="AJ15" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2524,6 +2570,9 @@
       <c r="AI16" t="n">
         <v>-13</v>
       </c>
+      <c r="AJ16" t="n">
+        <v>-38</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2635,6 +2684,9 @@
       <c r="AI17" t="n">
         <v>-34</v>
       </c>
+      <c r="AJ17" t="n">
+        <v>-49</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2746,6 +2798,9 @@
       <c r="AI18" t="n">
         <v>118</v>
       </c>
+      <c r="AJ18" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2856,6 +2911,9 @@
       </c>
       <c r="AI19" t="n">
         <v>19</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2869,7 +2927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW19"/>
+  <dimension ref="A1:BX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2947,6 +3005,7 @@
     <col width="12" customWidth="1" min="73" max="73"/>
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
+    <col width="12" customWidth="1" min="76" max="76"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3325,6 +3384,11 @@
           <t>20260115</t>
         </is>
       </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>20260116</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3556,6 +3620,9 @@
       <c r="BW2" t="n">
         <v>98</v>
       </c>
+      <c r="BX2" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3787,6 +3854,9 @@
       <c r="BW3" t="n">
         <v>112</v>
       </c>
+      <c r="BX3" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4018,6 +4088,9 @@
       <c r="BW4" t="n">
         <v>99</v>
       </c>
+      <c r="BX4" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4249,6 +4322,9 @@
       <c r="BW5" t="n">
         <v>107</v>
       </c>
+      <c r="BX5" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4480,6 +4556,9 @@
       <c r="BW6" t="n">
         <v>111</v>
       </c>
+      <c r="BX6" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4711,6 +4790,9 @@
       <c r="BW7" t="n">
         <v>112</v>
       </c>
+      <c r="BX7" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4942,6 +5024,9 @@
       <c r="BW8" t="n">
         <v>113</v>
       </c>
+      <c r="BX8" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5173,6 +5258,9 @@
       <c r="BW9" t="n">
         <v>109</v>
       </c>
+      <c r="BX9" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5404,6 +5492,9 @@
       <c r="BW10" t="n">
         <v>108</v>
       </c>
+      <c r="BX10" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5635,6 +5726,9 @@
       <c r="BW11" t="n">
         <v>103</v>
       </c>
+      <c r="BX11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5866,6 +5960,9 @@
       <c r="BW12" t="n">
         <v>104</v>
       </c>
+      <c r="BX12" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6097,6 +6194,9 @@
       <c r="BW13" t="n">
         <v>102</v>
       </c>
+      <c r="BX13" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6328,6 +6428,9 @@
       <c r="BW14" t="n">
         <v>105</v>
       </c>
+      <c r="BX14" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6559,6 +6662,9 @@
       <c r="BW15" t="n">
         <v>99</v>
       </c>
+      <c r="BX15" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6790,6 +6896,9 @@
       <c r="BW16" t="n">
         <v>104</v>
       </c>
+      <c r="BX16" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7021,6 +7130,9 @@
       <c r="BW17" t="n">
         <v>102</v>
       </c>
+      <c r="BX17" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7252,6 +7364,9 @@
       <c r="BW18" t="n">
         <v>110</v>
       </c>
+      <c r="BX18" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7482,6 +7597,9 @@
       </c>
       <c r="BW19" t="n">
         <v>98</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -7495,7 +7613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD19"/>
+  <dimension ref="A1:BE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7505,6 +7623,7 @@
     <col width="12" customWidth="1" min="54" max="54"/>
     <col width="12" customWidth="1" min="55" max="55"/>
     <col width="12" customWidth="1" min="56" max="56"/>
+    <col width="12" customWidth="1" min="57" max="57"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7690,6 +7809,11 @@
           <t>20260115</t>
         </is>
       </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>20260116</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7864,6 +7988,9 @@
       <c r="BD2" t="n">
         <v>3.78</v>
       </c>
+      <c r="BE2" t="n">
+        <v>3.17</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8038,6 +8165,9 @@
       <c r="BD3" t="n">
         <v>92.95</v>
       </c>
+      <c r="BE3" t="n">
+        <v>76.11</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8212,6 +8342,9 @@
       <c r="BD4" t="n">
         <v>-2.49</v>
       </c>
+      <c r="BE4" t="n">
+        <v>-1.91</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8386,6 +8519,9 @@
       <c r="BD5" t="n">
         <v>50.39</v>
       </c>
+      <c r="BE5" t="n">
+        <v>37.82</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8560,6 +8696,9 @@
       <c r="BD6" t="n">
         <v>88.13</v>
       </c>
+      <c r="BE6" t="n">
+        <v>73.14</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8734,6 +8873,9 @@
       <c r="BD7" t="n">
         <v>93.97</v>
       </c>
+      <c r="BE7" t="n">
+        <v>79.48999999999999</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8908,6 +9050,9 @@
       <c r="BD8" t="n">
         <v>97.41</v>
       </c>
+      <c r="BE8" t="n">
+        <v>79.68000000000001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9082,6 +9227,9 @@
       <c r="BD9" t="n">
         <v>-28.06</v>
       </c>
+      <c r="BE9" t="n">
+        <v>-33.12</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9256,6 +9404,9 @@
       <c r="BD10" t="n">
         <v>53.24</v>
       </c>
+      <c r="BE10" t="n">
+        <v>44.88</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9430,6 +9581,9 @@
       <c r="BD11" t="n">
         <v>-31.74</v>
       </c>
+      <c r="BE11" t="n">
+        <v>-35.31</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9604,6 +9758,9 @@
       <c r="BD12" t="n">
         <v>-33.28</v>
       </c>
+      <c r="BE12" t="n">
+        <v>-37.18</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9778,6 +9935,9 @@
       <c r="BD13" t="n">
         <v>-38.14</v>
       </c>
+      <c r="BE13" t="n">
+        <v>-40.58</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9952,6 +10112,9 @@
       <c r="BD14" t="n">
         <v>-33.16</v>
       </c>
+      <c r="BE14" t="n">
+        <v>-40.15</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10126,6 +10289,9 @@
       <c r="BD15" t="n">
         <v>6.11</v>
       </c>
+      <c r="BE15" t="n">
+        <v>6.03</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10300,6 +10466,9 @@
       <c r="BD16" t="n">
         <v>-33.38</v>
       </c>
+      <c r="BE16" t="n">
+        <v>-37.49</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10474,6 +10643,9 @@
       <c r="BD17" t="n">
         <v>-33.06</v>
       </c>
+      <c r="BE17" t="n">
+        <v>-38.87</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10648,6 +10820,9 @@
       <c r="BD18" t="n">
         <v>56.57</v>
       </c>
+      <c r="BE18" t="n">
+        <v>46.62</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10821,6 +10996,9 @@
       </c>
       <c r="BD19" t="n">
         <v>3.32</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>4.67</v>
       </c>
     </row>
   </sheetData>
@@ -10834,7 +11012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI19"/>
+  <dimension ref="A1:AJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10872,6 +11050,7 @@
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
     <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11050,6 +11229,11 @@
           <t>20260115</t>
         </is>
       </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>20260116</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11161,6 +11345,9 @@
       <c r="AI2" t="n">
         <v>72</v>
       </c>
+      <c r="AJ2" t="n">
+        <v>165</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11272,6 +11459,9 @@
       <c r="AI3" t="n">
         <v>35</v>
       </c>
+      <c r="AJ3" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11383,6 +11573,9 @@
       <c r="AI4" t="n">
         <v>26</v>
       </c>
+      <c r="AJ4" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11494,6 +11687,9 @@
       <c r="AI5" t="n">
         <v>23</v>
       </c>
+      <c r="AJ5" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11605,6 +11801,9 @@
       <c r="AI6" t="n">
         <v>73</v>
       </c>
+      <c r="AJ6" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11716,6 +11915,9 @@
       <c r="AI7" t="n">
         <v>70</v>
       </c>
+      <c r="AJ7" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11827,6 +12029,9 @@
       <c r="AI8" t="n">
         <v>88</v>
       </c>
+      <c r="AJ8" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11938,6 +12143,9 @@
       <c r="AI9" t="n">
         <v>61</v>
       </c>
+      <c r="AJ9" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12049,6 +12257,9 @@
       <c r="AI10" t="n">
         <v>43</v>
       </c>
+      <c r="AJ10" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12160,6 +12371,9 @@
       <c r="AI11" t="n">
         <v>30</v>
       </c>
+      <c r="AJ11" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12271,6 +12485,9 @@
       <c r="AI12" t="n">
         <v>45</v>
       </c>
+      <c r="AJ12" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12382,6 +12599,9 @@
       <c r="AI13" t="n">
         <v>34</v>
       </c>
+      <c r="AJ13" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12493,6 +12713,9 @@
       <c r="AI14" t="n">
         <v>44</v>
       </c>
+      <c r="AJ14" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12604,6 +12827,9 @@
       <c r="AI15" t="n">
         <v>27</v>
       </c>
+      <c r="AJ15" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12715,6 +12941,9 @@
       <c r="AI16" t="n">
         <v>23</v>
       </c>
+      <c r="AJ16" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12826,6 +13055,9 @@
       <c r="AI17" t="n">
         <v>16</v>
       </c>
+      <c r="AJ17" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12937,6 +13169,9 @@
       <c r="AI18" t="n">
         <v>28</v>
       </c>
+      <c r="AJ18" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13047,6 +13282,9 @@
       </c>
       <c r="AI19" t="n">
         <v>43</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -13060,7 +13298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP19"/>
+  <dimension ref="A1:CQ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13157,6 +13395,7 @@
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
+    <col width="12" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13446,6 +13685,9 @@
       <c r="CP1" s="1" t="n">
         <v>20260115</v>
       </c>
+      <c r="CQ1" s="1" t="n">
+        <v>20260116</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13734,6 +13976,9 @@
       <c r="CP2" t="n">
         <v>14870</v>
       </c>
+      <c r="CQ2" t="n">
+        <v>14710</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14022,6 +14267,9 @@
       <c r="CP3" t="n">
         <v>69605</v>
       </c>
+      <c r="CQ3" t="n">
+        <v>71930</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14310,6 +14558,9 @@
       <c r="CP4" t="n">
         <v>17940</v>
       </c>
+      <c r="CQ4" t="n">
+        <v>17665</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14598,6 +14849,9 @@
       <c r="CP5" t="n">
         <v>17150</v>
       </c>
+      <c r="CQ5" t="n">
+        <v>17665</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14886,6 +15140,9 @@
       <c r="CP6" t="n">
         <v>20110</v>
       </c>
+      <c r="CQ6" t="n">
+        <v>20780</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15174,6 +15431,9 @@
       <c r="CP7" t="n">
         <v>23925</v>
       </c>
+      <c r="CQ7" t="n">
+        <v>24615</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15462,6 +15722,9 @@
       <c r="CP8" t="n">
         <v>23270</v>
       </c>
+      <c r="CQ8" t="n">
+        <v>24070</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15750,6 +16013,9 @@
       <c r="CP9" t="n">
         <v>1384</v>
       </c>
+      <c r="CQ9" t="n">
+        <v>1417</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16038,6 +16304,9 @@
       <c r="CP10" t="n">
         <v>18435</v>
       </c>
+      <c r="CQ10" t="n">
+        <v>19185</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16326,6 +16595,9 @@
       <c r="CP11" t="n">
         <v>5150</v>
       </c>
+      <c r="CQ11" t="n">
+        <v>5200</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16614,6 +16886,9 @@
       <c r="CP12" t="n">
         <v>5505</v>
       </c>
+      <c r="CQ12" t="n">
+        <v>5580</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16902,6 +17177,9 @@
       <c r="CP13" t="n">
         <v>5490</v>
       </c>
+      <c r="CQ13" t="n">
+        <v>5570</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17190,6 +17468,9 @@
       <c r="CP14" t="n">
         <v>1418</v>
       </c>
+      <c r="CQ14" t="n">
+        <v>1456</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17478,6 +17759,9 @@
       <c r="CP15" t="n">
         <v>19155</v>
       </c>
+      <c r="CQ15" t="n">
+        <v>18875</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -17766,6 +18050,9 @@
       <c r="CP16" t="n">
         <v>10460</v>
       </c>
+      <c r="CQ16" t="n">
+        <v>10595</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -18054,6 +18341,9 @@
       <c r="CP17" t="n">
         <v>6015</v>
       </c>
+      <c r="CQ17" t="n">
+        <v>6080</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -18342,6 +18632,9 @@
       <c r="CP18" t="n">
         <v>19935</v>
       </c>
+      <c r="CQ18" t="n">
+        <v>20890</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -18629,6 +18922,9 @@
       </c>
       <c r="CP19" t="n">
         <v>15935</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>15725</v>
       </c>
     </row>
   </sheetData>
@@ -18642,7 +18938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP19"/>
+  <dimension ref="A1:CQ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18739,6 +19035,7 @@
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
+    <col width="12" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19028,6 +19325,9 @@
       <c r="CP1" s="1" t="n">
         <v>20260115</v>
       </c>
+      <c r="CQ1" s="1" t="n">
+        <v>20260116</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19316,6 +19616,9 @@
       <c r="CP2" t="n">
         <v>15000</v>
       </c>
+      <c r="CQ2" t="n">
+        <v>15245</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19604,6 +19907,9 @@
       <c r="CP3" t="n">
         <v>71150</v>
       </c>
+      <c r="CQ3" t="n">
+        <v>72435</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19892,6 +20198,9 @@
       <c r="CP4" t="n">
         <v>18050</v>
       </c>
+      <c r="CQ4" t="n">
+        <v>18465</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20180,6 +20489,9 @@
       <c r="CP5" t="n">
         <v>17480</v>
       </c>
+      <c r="CQ5" t="n">
+        <v>17740</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20468,6 +20780,9 @@
       <c r="CP6" t="n">
         <v>20580</v>
       </c>
+      <c r="CQ6" t="n">
+        <v>20855</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20756,6 +21071,9 @@
       <c r="CP7" t="n">
         <v>24440</v>
       </c>
+      <c r="CQ7" t="n">
+        <v>24800</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21044,6 +21362,9 @@
       <c r="CP8" t="n">
         <v>23840</v>
       </c>
+      <c r="CQ8" t="n">
+        <v>24280</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21332,6 +21653,9 @@
       <c r="CP9" t="n">
         <v>1432</v>
       </c>
+      <c r="CQ9" t="n">
+        <v>1434</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21620,6 +21944,9 @@
       <c r="CP10" t="n">
         <v>18870</v>
       </c>
+      <c r="CQ10" t="n">
+        <v>19235</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -21908,6 +22235,9 @@
       <c r="CP11" t="n">
         <v>5250</v>
       </c>
+      <c r="CQ11" t="n">
+        <v>5230</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -22196,6 +22526,9 @@
       <c r="CP12" t="n">
         <v>5615</v>
       </c>
+      <c r="CQ12" t="n">
+        <v>5600</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -22484,6 +22817,9 @@
       <c r="CP13" t="n">
         <v>5620</v>
       </c>
+      <c r="CQ13" t="n">
+        <v>5620</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -22772,6 +23108,9 @@
       <c r="CP14" t="n">
         <v>1462</v>
       </c>
+      <c r="CQ14" t="n">
+        <v>1476</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -23060,6 +23399,9 @@
       <c r="CP15" t="n">
         <v>19320</v>
       </c>
+      <c r="CQ15" t="n">
+        <v>19870</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -23348,6 +23690,9 @@
       <c r="CP16" t="n">
         <v>10600</v>
       </c>
+      <c r="CQ16" t="n">
+        <v>10630</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -23636,6 +23981,9 @@
       <c r="CP17" t="n">
         <v>6105</v>
       </c>
+      <c r="CQ17" t="n">
+        <v>6095</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -23924,6 +24272,9 @@
       <c r="CP18" t="n">
         <v>20575</v>
       </c>
+      <c r="CQ18" t="n">
+        <v>20900</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -24211,6 +24562,9 @@
       </c>
       <c r="CP19" t="n">
         <v>16005</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>16420</v>
       </c>
     </row>
   </sheetData>
@@ -24224,7 +24578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP19"/>
+  <dimension ref="A1:CQ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24321,6 +24675,7 @@
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
+    <col width="12" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24610,6 +24965,9 @@
       <c r="CP1" s="1" t="n">
         <v>20260115</v>
       </c>
+      <c r="CQ1" s="1" t="n">
+        <v>20260116</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24898,6 +25256,9 @@
       <c r="CP2" t="n">
         <v>14715</v>
       </c>
+      <c r="CQ2" t="n">
+        <v>14340</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25186,6 +25547,9 @@
       <c r="CP3" t="n">
         <v>69175</v>
       </c>
+      <c r="CQ3" t="n">
+        <v>71205</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25474,6 +25838,9 @@
       <c r="CP4" t="n">
         <v>17760</v>
       </c>
+      <c r="CQ4" t="n">
+        <v>17370</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25762,6 +26129,9 @@
       <c r="CP5" t="n">
         <v>17075</v>
       </c>
+      <c r="CQ5" t="n">
+        <v>17390</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26050,6 +26420,9 @@
       <c r="CP6" t="n">
         <v>19970</v>
       </c>
+      <c r="CQ6" t="n">
+        <v>20540</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26338,6 +26711,9 @@
       <c r="CP7" t="n">
         <v>23760</v>
       </c>
+      <c r="CQ7" t="n">
+        <v>24370</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26626,6 +27002,9 @@
       <c r="CP8" t="n">
         <v>23160</v>
       </c>
+      <c r="CQ8" t="n">
+        <v>23840</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26914,6 +27293,9 @@
       <c r="CP9" t="n">
         <v>1368</v>
       </c>
+      <c r="CQ9" t="n">
+        <v>1332</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27202,6 +27584,9 @@
       <c r="CP10" t="n">
         <v>18380</v>
       </c>
+      <c r="CQ10" t="n">
+        <v>18685</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27490,6 +27875,9 @@
       <c r="CP11" t="n">
         <v>5097</v>
       </c>
+      <c r="CQ11" t="n">
+        <v>5015</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27778,6 +28166,9 @@
       <c r="CP12" t="n">
         <v>5440</v>
       </c>
+      <c r="CQ12" t="n">
+        <v>5350</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28066,6 +28457,9 @@
       <c r="CP13" t="n">
         <v>5440</v>
       </c>
+      <c r="CQ13" t="n">
+        <v>5375</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -28354,6 +28748,9 @@
       <c r="CP14" t="n">
         <v>1396</v>
       </c>
+      <c r="CQ14" t="n">
+        <v>1379</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -28642,6 +29039,9 @@
       <c r="CP15" t="n">
         <v>19045</v>
       </c>
+      <c r="CQ15" t="n">
+        <v>18550</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -28930,6 +29330,9 @@
       <c r="CP16" t="n">
         <v>10330</v>
       </c>
+      <c r="CQ16" t="n">
+        <v>10245</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -29218,6 +29621,9 @@
       <c r="CP17" t="n">
         <v>5950</v>
       </c>
+      <c r="CQ17" t="n">
+        <v>5905</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -29506,6 +29912,9 @@
       <c r="CP18" t="n">
         <v>19930</v>
       </c>
+      <c r="CQ18" t="n">
+        <v>20265</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -29793,6 +30202,9 @@
       </c>
       <c r="CP19" t="n">
         <v>15750</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>15415</v>
       </c>
     </row>
   </sheetData>
@@ -29806,7 +30218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP19"/>
+  <dimension ref="A1:CQ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29903,6 +30315,7 @@
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
+    <col width="12" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30192,6 +30605,9 @@
       <c r="CP1" s="1" t="n">
         <v>20260115</v>
       </c>
+      <c r="CQ1" s="1" t="n">
+        <v>20260116</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30480,6 +30896,9 @@
       <c r="CP2" t="n">
         <v>14920</v>
       </c>
+      <c r="CQ2" t="n">
+        <v>15035</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -30768,6 +31187,9 @@
       <c r="CP3" t="n">
         <v>71150</v>
       </c>
+      <c r="CQ3" t="n">
+        <v>71675</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -31056,6 +31478,9 @@
       <c r="CP4" t="n">
         <v>17825</v>
       </c>
+      <c r="CQ4" t="n">
+        <v>18370</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -31344,6 +31769,9 @@
       <c r="CP5" t="n">
         <v>17480</v>
       </c>
+      <c r="CQ5" t="n">
+        <v>17570</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -31632,6 +32060,9 @@
       <c r="CP6" t="n">
         <v>20580</v>
       </c>
+      <c r="CQ6" t="n">
+        <v>20735</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -31920,6 +32351,9 @@
       <c r="CP7" t="n">
         <v>24440</v>
       </c>
+      <c r="CQ7" t="n">
+        <v>24700</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -32208,6 +32642,9 @@
       <c r="CP8" t="n">
         <v>23840</v>
       </c>
+      <c r="CQ8" t="n">
+        <v>24100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -32496,6 +32933,9 @@
       <c r="CP9" t="n">
         <v>1416</v>
       </c>
+      <c r="CQ9" t="n">
+        <v>1346</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -32784,6 +33224,9 @@
       <c r="CP10" t="n">
         <v>18835</v>
       </c>
+      <c r="CQ10" t="n">
+        <v>18825</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -33072,6 +33515,9 @@
       <c r="CP11" t="n">
         <v>5195</v>
       </c>
+      <c r="CQ11" t="n">
+        <v>5025</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33360,6 +33806,9 @@
       <c r="CP12" t="n">
         <v>5580</v>
       </c>
+      <c r="CQ12" t="n">
+        <v>5375</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33648,6 +34097,9 @@
       <c r="CP13" t="n">
         <v>5575</v>
       </c>
+      <c r="CQ13" t="n">
+        <v>5390</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33936,6 +34388,9 @@
       <c r="CP14" t="n">
         <v>1455</v>
       </c>
+      <c r="CQ14" t="n">
+        <v>1387</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -34224,6 +34679,9 @@
       <c r="CP15" t="n">
         <v>19200</v>
       </c>
+      <c r="CQ15" t="n">
+        <v>19600</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -34512,6 +34970,9 @@
       <c r="CP16" t="n">
         <v>10585</v>
       </c>
+      <c r="CQ16" t="n">
+        <v>10280</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -34800,6 +35261,9 @@
       <c r="CP17" t="n">
         <v>6080</v>
       </c>
+      <c r="CQ17" t="n">
+        <v>5945</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -35088,6 +35552,9 @@
       <c r="CP18" t="n">
         <v>20575</v>
       </c>
+      <c r="CQ18" t="n">
+        <v>20410</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -35375,6 +35842,9 @@
       </c>
       <c r="CP19" t="n">
         <v>15860</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>16225</v>
       </c>
     </row>
   </sheetData>
@@ -35388,7 +35858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP19"/>
+  <dimension ref="A1:CQ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35485,6 +35955,7 @@
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
+    <col width="12" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35774,6 +36245,9 @@
       <c r="CP1" s="1" t="n">
         <v>20260115</v>
       </c>
+      <c r="CQ1" s="1" t="n">
+        <v>20260116</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -36062,6 +36536,9 @@
       <c r="CP2" t="n">
         <v>227774</v>
       </c>
+      <c r="CQ2" t="n">
+        <v>546950</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36350,6 +36827,9 @@
       <c r="CP3" t="n">
         <v>1656816</v>
       </c>
+      <c r="CQ3" t="n">
+        <v>1831701</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -36638,6 +37118,9 @@
       <c r="CP4" t="n">
         <v>95278</v>
       </c>
+      <c r="CQ4" t="n">
+        <v>326308</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -36926,6 +37409,9 @@
       <c r="CP5" t="n">
         <v>224836</v>
       </c>
+      <c r="CQ5" t="n">
+        <v>334232</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -37214,6 +37700,9 @@
       <c r="CP6" t="n">
         <v>3807701</v>
       </c>
+      <c r="CQ6" t="n">
+        <v>5795255</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -37502,6 +37991,9 @@
       <c r="CP7" t="n">
         <v>5496821</v>
       </c>
+      <c r="CQ7" t="n">
+        <v>6621592</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -37790,6 +38282,9 @@
       <c r="CP8" t="n">
         <v>14519533</v>
       </c>
+      <c r="CQ8" t="n">
+        <v>17892028</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -38078,6 +38573,9 @@
       <c r="CP9" t="n">
         <v>8762186</v>
       </c>
+      <c r="CQ9" t="n">
+        <v>5980212</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -38366,6 +38864,9 @@
       <c r="CP10" t="n">
         <v>1076133</v>
       </c>
+      <c r="CQ10" t="n">
+        <v>1346783</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -38654,6 +39155,9 @@
       <c r="CP11" t="n">
         <v>728057</v>
       </c>
+      <c r="CQ11" t="n">
+        <v>532296</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -38942,6 +39446,9 @@
       <c r="CP12" t="n">
         <v>2429250</v>
       </c>
+      <c r="CQ12" t="n">
+        <v>1986213</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -39230,6 +39737,9 @@
       <c r="CP13" t="n">
         <v>4490095</v>
       </c>
+      <c r="CQ13" t="n">
+        <v>4262416</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39518,6 +40028,9 @@
       <c r="CP14" t="n">
         <v>42180563</v>
       </c>
+      <c r="CQ14" t="n">
+        <v>34561442</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39806,6 +40319,9 @@
       <c r="CP15" t="n">
         <v>1024746</v>
       </c>
+      <c r="CQ15" t="n">
+        <v>3669797</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -40094,6 +40610,9 @@
       <c r="CP16" t="n">
         <v>263716</v>
       </c>
+      <c r="CQ16" t="n">
+        <v>239405</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -40382,6 +40901,9 @@
       <c r="CP17" t="n">
         <v>62118</v>
       </c>
+      <c r="CQ17" t="n">
+        <v>69146</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -40670,6 +41192,9 @@
       <c r="CP18" t="n">
         <v>98633</v>
       </c>
+      <c r="CQ18" t="n">
+        <v>135648</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -40957,6 +41482,9 @@
       </c>
       <c r="CP19" t="n">
         <v>45070</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>92699</v>
       </c>
     </row>
   </sheetData>
@@ -40970,7 +41498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW19"/>
+  <dimension ref="A1:BX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -41048,6 +41576,7 @@
     <col width="10" customWidth="1" min="73" max="73"/>
     <col width="10" customWidth="1" min="74" max="74"/>
     <col width="10" customWidth="1" min="75" max="75"/>
+    <col width="10" customWidth="1" min="76" max="76"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -41280,6 +41809,9 @@
       <c r="BW1" s="1" t="n">
         <v>20260115</v>
       </c>
+      <c r="BX1" s="1" t="n">
+        <v>20260116</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -41511,6 +42043,9 @@
       <c r="BW2" t="n">
         <v>26</v>
       </c>
+      <c r="BX2" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -41742,6 +42277,9 @@
       <c r="BW3" t="n">
         <v>100</v>
       </c>
+      <c r="BX3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -41973,6 +42511,9 @@
       <c r="BW4" t="n">
         <v>34</v>
       </c>
+      <c r="BX4" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -42204,6 +42745,9 @@
       <c r="BW5" t="n">
         <v>93</v>
       </c>
+      <c r="BX5" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -42435,6 +42979,9 @@
       <c r="BW6" t="n">
         <v>100</v>
       </c>
+      <c r="BX6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -42666,6 +43213,9 @@
       <c r="BW7" t="n">
         <v>100</v>
       </c>
+      <c r="BX7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -42897,6 +43447,9 @@
       <c r="BW8" t="n">
         <v>100</v>
       </c>
+      <c r="BX8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -43128,6 +43681,9 @@
       <c r="BW9" t="n">
         <v>82</v>
       </c>
+      <c r="BX9" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -43359,6 +43915,9 @@
       <c r="BW10" t="n">
         <v>92</v>
       </c>
+      <c r="BX10" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -43590,6 +44149,9 @@
       <c r="BW11" t="n">
         <v>67</v>
       </c>
+      <c r="BX11" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -43821,6 +44383,9 @@
       <c r="BW12" t="n">
         <v>69</v>
       </c>
+      <c r="BX12" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -44052,6 +44617,9 @@
       <c r="BW13" t="n">
         <v>59</v>
       </c>
+      <c r="BX13" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -44283,6 +44851,9 @@
       <c r="BW14" t="n">
         <v>61</v>
       </c>
+      <c r="BX14" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -44514,6 +45085,9 @@
       <c r="BW15" t="n">
         <v>32</v>
       </c>
+      <c r="BX15" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -44745,6 +45319,9 @@
       <c r="BW16" t="n">
         <v>78</v>
       </c>
+      <c r="BX16" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -44976,6 +45553,9 @@
       <c r="BW17" t="n">
         <v>60</v>
       </c>
+      <c r="BX17" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -45207,6 +45787,9 @@
       <c r="BW18" t="n">
         <v>100</v>
       </c>
+      <c r="BX18" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -45437,6 +46020,9 @@
       </c>
       <c r="BW19" t="n">
         <v>14</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -45450,7 +46036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI19"/>
+  <dimension ref="A1:AJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -45488,6 +46074,7 @@
     <col width="10" customWidth="1" min="33" max="33"/>
     <col width="10" customWidth="1" min="34" max="34"/>
     <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -45600,6 +46187,9 @@
       <c r="AI1" s="1" t="n">
         <v>20260115</v>
       </c>
+      <c r="AJ1" s="1" t="n">
+        <v>20260116</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -45711,6 +46301,9 @@
       <c r="AI2" t="n">
         <v>52</v>
       </c>
+      <c r="AJ2" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -45822,6 +46415,9 @@
       <c r="AI3" t="n">
         <v>100</v>
       </c>
+      <c r="AJ3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -45933,6 +46529,9 @@
       <c r="AI4" t="n">
         <v>57</v>
       </c>
+      <c r="AJ4" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -46044,6 +46643,9 @@
       <c r="AI5" t="n">
         <v>93</v>
       </c>
+      <c r="AJ5" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -46155,6 +46757,9 @@
       <c r="AI6" t="n">
         <v>100</v>
       </c>
+      <c r="AJ6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -46266,6 +46871,9 @@
       <c r="AI7" t="n">
         <v>100</v>
       </c>
+      <c r="AJ7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -46377,6 +46985,9 @@
       <c r="AI8" t="n">
         <v>100</v>
       </c>
+      <c r="AJ8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -46488,6 +47099,9 @@
       <c r="AI9" t="n">
         <v>31</v>
       </c>
+      <c r="AJ9" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -46599,6 +47213,9 @@
       <c r="AI10" t="n">
         <v>92</v>
       </c>
+      <c r="AJ10" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -46710,6 +47327,9 @@
       <c r="AI11" t="n">
         <v>43</v>
       </c>
+      <c r="AJ11" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -46821,6 +47441,9 @@
       <c r="AI12" t="n">
         <v>44</v>
       </c>
+      <c r="AJ12" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -46932,6 +47555,9 @@
       <c r="AI13" t="n">
         <v>43</v>
       </c>
+      <c r="AJ13" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -47043,6 +47669,9 @@
       <c r="AI14" t="n">
         <v>26</v>
       </c>
+      <c r="AJ14" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -47154,6 +47783,9 @@
       <c r="AI15" t="n">
         <v>78</v>
       </c>
+      <c r="AJ15" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -47265,6 +47897,9 @@
       <c r="AI16" t="n">
         <v>42</v>
       </c>
+      <c r="AJ16" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -47376,6 +48011,9 @@
       <c r="AI17" t="n">
         <v>31</v>
       </c>
+      <c r="AJ17" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -47487,6 +48125,9 @@
       <c r="AI18" t="n">
         <v>100</v>
       </c>
+      <c r="AJ18" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -47597,6 +48238,9 @@
       </c>
       <c r="AI19" t="n">
         <v>75</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -47610,7 +48254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW19"/>
+  <dimension ref="A1:BX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -47688,6 +48332,7 @@
     <col width="10" customWidth="1" min="73" max="73"/>
     <col width="10" customWidth="1" min="74" max="74"/>
     <col width="10" customWidth="1" min="75" max="75"/>
+    <col width="10" customWidth="1" min="76" max="76"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -47920,6 +48565,9 @@
       <c r="BW1" s="1" t="n">
         <v>20260115</v>
       </c>
+      <c r="BX1" s="1" t="n">
+        <v>20260116</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -48151,6 +48799,9 @@
       <c r="BW2" t="n">
         <v>-35</v>
       </c>
+      <c r="BX2" t="n">
+        <v>-23</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -48382,6 +49033,9 @@
       <c r="BW3" t="n">
         <v>59</v>
       </c>
+      <c r="BX3" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -48613,6 +49267,9 @@
       <c r="BW4" t="n">
         <v>-17</v>
       </c>
+      <c r="BX4" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -48844,6 +49501,9 @@
       <c r="BW5" t="n">
         <v>57</v>
       </c>
+      <c r="BX5" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -49075,6 +49735,9 @@
       <c r="BW6" t="n">
         <v>63</v>
       </c>
+      <c r="BX6" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -49306,6 +49969,9 @@
       <c r="BW7" t="n">
         <v>62</v>
       </c>
+      <c r="BX7" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -49537,6 +50203,9 @@
       <c r="BW8" t="n">
         <v>58</v>
       </c>
+      <c r="BX8" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -49768,6 +50437,9 @@
       <c r="BW9" t="n">
         <v>63</v>
       </c>
+      <c r="BX9" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -49999,6 +50671,9 @@
       <c r="BW10" t="n">
         <v>62</v>
       </c>
+      <c r="BX10" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -50230,6 +50905,9 @@
       <c r="BW11" t="n">
         <v>40</v>
       </c>
+      <c r="BX11" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -50461,6 +51139,9 @@
       <c r="BW12" t="n">
         <v>41</v>
       </c>
+      <c r="BX12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -50692,6 +51373,9 @@
       <c r="BW13" t="n">
         <v>28</v>
       </c>
+      <c r="BX13" t="n">
+        <v>-9</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -50923,6 +51607,9 @@
       <c r="BW14" t="n">
         <v>33</v>
       </c>
+      <c r="BX14" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -51154,6 +51841,9 @@
       <c r="BW15" t="n">
         <v>-17</v>
       </c>
+      <c r="BX15" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -51385,6 +52075,9 @@
       <c r="BW16" t="n">
         <v>54</v>
       </c>
+      <c r="BX16" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -51616,6 +52309,9 @@
       <c r="BW17" t="n">
         <v>28</v>
       </c>
+      <c r="BX17" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -51847,6 +52543,9 @@
       <c r="BW18" t="n">
         <v>70</v>
       </c>
+      <c r="BX18" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -52077,6 +52776,9 @@
       </c>
       <c r="BW19" t="n">
         <v>-35</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -36537,7 +36537,7 @@
         <v>227774</v>
       </c>
       <c r="CQ2" t="n">
-        <v>546950</v>
+        <v>547331</v>
       </c>
     </row>
     <row r="3">
@@ -36828,7 +36828,7 @@
         <v>1656816</v>
       </c>
       <c r="CQ3" t="n">
-        <v>1831701</v>
+        <v>1833306</v>
       </c>
     </row>
     <row r="4">
@@ -37119,7 +37119,7 @@
         <v>95278</v>
       </c>
       <c r="CQ4" t="n">
-        <v>326308</v>
+        <v>326831</v>
       </c>
     </row>
     <row r="5">
@@ -37410,7 +37410,7 @@
         <v>224836</v>
       </c>
       <c r="CQ5" t="n">
-        <v>334232</v>
+        <v>338742</v>
       </c>
     </row>
     <row r="6">
@@ -37701,7 +37701,7 @@
         <v>3807701</v>
       </c>
       <c r="CQ6" t="n">
-        <v>5795255</v>
+        <v>5822368</v>
       </c>
     </row>
     <row r="7">
@@ -37992,7 +37992,7 @@
         <v>5496821</v>
       </c>
       <c r="CQ7" t="n">
-        <v>6621592</v>
+        <v>6637912</v>
       </c>
     </row>
     <row r="8">
@@ -38283,7 +38283,7 @@
         <v>14519533</v>
       </c>
       <c r="CQ8" t="n">
-        <v>17892028</v>
+        <v>18102911</v>
       </c>
     </row>
     <row r="9">
@@ -38574,7 +38574,7 @@
         <v>8762186</v>
       </c>
       <c r="CQ9" t="n">
-        <v>5980212</v>
+        <v>5982270</v>
       </c>
     </row>
     <row r="10">
@@ -38865,7 +38865,7 @@
         <v>1076133</v>
       </c>
       <c r="CQ10" t="n">
-        <v>1346783</v>
+        <v>1347095</v>
       </c>
     </row>
     <row r="11">
@@ -39156,7 +39156,7 @@
         <v>728057</v>
       </c>
       <c r="CQ11" t="n">
-        <v>532296</v>
+        <v>532565</v>
       </c>
     </row>
     <row r="12">
@@ -39447,7 +39447,7 @@
         <v>2429250</v>
       </c>
       <c r="CQ12" t="n">
-        <v>1986213</v>
+        <v>1987441</v>
       </c>
     </row>
     <row r="13">
@@ -39738,7 +39738,7 @@
         <v>4490095</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4262416</v>
+        <v>4264432</v>
       </c>
     </row>
     <row r="14">
@@ -40029,7 +40029,7 @@
         <v>42180563</v>
       </c>
       <c r="CQ14" t="n">
-        <v>34561442</v>
+        <v>34608247</v>
       </c>
     </row>
     <row r="15">
@@ -40320,7 +40320,7 @@
         <v>1024746</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3669797</v>
+        <v>3670647</v>
       </c>
     </row>
     <row r="16">
@@ -40611,7 +40611,7 @@
         <v>263716</v>
       </c>
       <c r="CQ16" t="n">
-        <v>239405</v>
+        <v>239406</v>
       </c>
     </row>
     <row r="17">
@@ -41193,7 +41193,7 @@
         <v>98633</v>
       </c>
       <c r="CQ18" t="n">
-        <v>135648</v>
+        <v>135841</v>
       </c>
     </row>
     <row r="19">
@@ -41484,7 +41484,7 @@
         <v>45070</v>
       </c>
       <c r="CQ19" t="n">
-        <v>92699</v>
+        <v>92710</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ19"/>
+  <dimension ref="A1:AK19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -748,6 +748,7 @@
     <col width="10" customWidth="1" min="34" max="34"/>
     <col width="10" customWidth="1" min="35" max="35"/>
     <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="10" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -863,6 +864,9 @@
       <c r="AJ1" s="1" t="n">
         <v>20260116</v>
       </c>
+      <c r="AK1" s="1" t="n">
+        <v>20260119</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -977,6 +981,9 @@
       <c r="AJ2" t="n">
         <v>-11</v>
       </c>
+      <c r="AK2" t="n">
+        <v>-11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1091,6 +1098,9 @@
       <c r="AJ3" t="n">
         <v>116</v>
       </c>
+      <c r="AK3" t="n">
+        <v>115</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1205,6 +1215,9 @@
       <c r="AJ4" t="n">
         <v>25</v>
       </c>
+      <c r="AK4" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1319,6 +1332,9 @@
       <c r="AJ5" t="n">
         <v>90</v>
       </c>
+      <c r="AK5" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1433,6 +1449,9 @@
       <c r="AJ6" t="n">
         <v>119</v>
       </c>
+      <c r="AK6" t="n">
+        <v>115</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1547,6 +1566,9 @@
       <c r="AJ7" t="n">
         <v>119</v>
       </c>
+      <c r="AK7" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1661,6 +1683,9 @@
       <c r="AJ8" t="n">
         <v>118</v>
       </c>
+      <c r="AK8" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1775,6 +1800,9 @@
       <c r="AJ9" t="n">
         <v>-42</v>
       </c>
+      <c r="AK9" t="n">
+        <v>-18</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1889,6 +1917,9 @@
       <c r="AJ10" t="n">
         <v>100</v>
       </c>
+      <c r="AK10" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2003,6 +2034,9 @@
       <c r="AJ11" t="n">
         <v>-41</v>
       </c>
+      <c r="AK11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2117,6 +2151,9 @@
       <c r="AJ12" t="n">
         <v>-40</v>
       </c>
+      <c r="AK12" t="n">
+        <v>-7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2231,6 +2268,9 @@
       <c r="AJ13" t="n">
         <v>-36</v>
       </c>
+      <c r="AK13" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2345,6 +2385,9 @@
       <c r="AJ14" t="n">
         <v>-53</v>
       </c>
+      <c r="AK14" t="n">
+        <v>-26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2459,6 +2502,9 @@
       <c r="AJ15" t="n">
         <v>33</v>
       </c>
+      <c r="AK15" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2573,6 +2619,9 @@
       <c r="AJ16" t="n">
         <v>-38</v>
       </c>
+      <c r="AK16" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2687,6 +2736,9 @@
       <c r="AJ17" t="n">
         <v>-49</v>
       </c>
+      <c r="AK17" t="n">
+        <v>-19</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2801,6 +2853,9 @@
       <c r="AJ18" t="n">
         <v>106</v>
       </c>
+      <c r="AK18" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2914,6 +2969,9 @@
       </c>
       <c r="AJ19" t="n">
         <v>34</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -2927,7 +2985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX19"/>
+  <dimension ref="A1:BY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3006,6 +3064,7 @@
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
+    <col width="12" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3389,6 +3448,11 @@
           <t>20260116</t>
         </is>
       </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>20260119</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3623,6 +3687,9 @@
       <c r="BX2" t="n">
         <v>98</v>
       </c>
+      <c r="BY2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3857,6 +3924,9 @@
       <c r="BX3" t="n">
         <v>111</v>
       </c>
+      <c r="BY3" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4091,6 +4161,9 @@
       <c r="BX4" t="n">
         <v>102</v>
       </c>
+      <c r="BY4" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4325,6 +4398,9 @@
       <c r="BX5" t="n">
         <v>106</v>
       </c>
+      <c r="BY5" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4559,6 +4635,9 @@
       <c r="BX6" t="n">
         <v>111</v>
       </c>
+      <c r="BY6" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4793,6 +4872,9 @@
       <c r="BX7" t="n">
         <v>112</v>
       </c>
+      <c r="BY7" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5027,6 +5109,9 @@
       <c r="BX8" t="n">
         <v>113</v>
       </c>
+      <c r="BY8" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5261,6 +5346,9 @@
       <c r="BX9" t="n">
         <v>104</v>
       </c>
+      <c r="BY9" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5495,6 +5583,9 @@
       <c r="BX10" t="n">
         <v>107</v>
       </c>
+      <c r="BY10" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5729,6 +5820,9 @@
       <c r="BX11" t="n">
         <v>100</v>
       </c>
+      <c r="BY11" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5963,6 +6057,9 @@
       <c r="BX12" t="n">
         <v>100</v>
       </c>
+      <c r="BY12" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6197,6 +6294,9 @@
       <c r="BX13" t="n">
         <v>99</v>
       </c>
+      <c r="BY13" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6431,6 +6531,9 @@
       <c r="BX14" t="n">
         <v>101</v>
       </c>
+      <c r="BY14" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6665,6 +6768,9 @@
       <c r="BX15" t="n">
         <v>101</v>
       </c>
+      <c r="BY15" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6899,6 +7005,9 @@
       <c r="BX16" t="n">
         <v>101</v>
       </c>
+      <c r="BY16" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7133,6 +7242,9 @@
       <c r="BX17" t="n">
         <v>100</v>
       </c>
+      <c r="BY17" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7367,6 +7479,9 @@
       <c r="BX18" t="n">
         <v>108</v>
       </c>
+      <c r="BY18" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7600,6 +7715,9 @@
       </c>
       <c r="BX19" t="n">
         <v>101</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -7613,7 +7731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE19"/>
+  <dimension ref="A1:BF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7624,6 +7742,7 @@
     <col width="12" customWidth="1" min="55" max="55"/>
     <col width="12" customWidth="1" min="56" max="56"/>
     <col width="12" customWidth="1" min="57" max="57"/>
+    <col width="12" customWidth="1" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7814,6 +7933,11 @@
           <t>20260116</t>
         </is>
       </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>20260119</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7991,6 +8115,9 @@
       <c r="BE2" t="n">
         <v>3.17</v>
       </c>
+      <c r="BF2" t="n">
+        <v>0.83</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8168,6 +8295,9 @@
       <c r="BE3" t="n">
         <v>76.11</v>
       </c>
+      <c r="BF3" t="n">
+        <v>63.46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8345,6 +8475,9 @@
       <c r="BE4" t="n">
         <v>-1.91</v>
       </c>
+      <c r="BF4" t="n">
+        <v>-4.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8522,6 +8655,9 @@
       <c r="BE5" t="n">
         <v>37.82</v>
       </c>
+      <c r="BF5" t="n">
+        <v>30.75</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8699,6 +8835,9 @@
       <c r="BE6" t="n">
         <v>73.14</v>
       </c>
+      <c r="BF6" t="n">
+        <v>62.05</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8876,6 +9015,9 @@
       <c r="BE7" t="n">
         <v>79.48999999999999</v>
       </c>
+      <c r="BF7" t="n">
+        <v>67.90000000000001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9053,6 +9195,9 @@
       <c r="BE8" t="n">
         <v>79.68000000000001</v>
       </c>
+      <c r="BF8" t="n">
+        <v>65.62</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9230,6 +9375,9 @@
       <c r="BE9" t="n">
         <v>-33.12</v>
       </c>
+      <c r="BF9" t="n">
+        <v>-35.32</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9407,6 +9555,9 @@
       <c r="BE10" t="n">
         <v>44.88</v>
       </c>
+      <c r="BF10" t="n">
+        <v>38.88</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9584,6 +9735,9 @@
       <c r="BE11" t="n">
         <v>-35.31</v>
       </c>
+      <c r="BF11" t="n">
+        <v>-38.94</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9761,6 +9915,9 @@
       <c r="BE12" t="n">
         <v>-37.18</v>
       </c>
+      <c r="BF12" t="n">
+        <v>-42.08</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9938,6 +10095,9 @@
       <c r="BE13" t="n">
         <v>-40.58</v>
       </c>
+      <c r="BF13" t="n">
+        <v>-46.91</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10115,6 +10275,9 @@
       <c r="BE14" t="n">
         <v>-40.15</v>
       </c>
+      <c r="BF14" t="n">
+        <v>-46.27</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10292,6 +10455,9 @@
       <c r="BE15" t="n">
         <v>6.03</v>
       </c>
+      <c r="BF15" t="n">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10469,6 +10635,9 @@
       <c r="BE16" t="n">
         <v>-37.49</v>
       </c>
+      <c r="BF16" t="n">
+        <v>-39.23</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10646,6 +10815,9 @@
       <c r="BE17" t="n">
         <v>-38.87</v>
       </c>
+      <c r="BF17" t="n">
+        <v>-44.78</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10823,6 +10995,9 @@
       <c r="BE18" t="n">
         <v>46.62</v>
       </c>
+      <c r="BF18" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10999,6 +11174,9 @@
       </c>
       <c r="BE19" t="n">
         <v>4.67</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>3.54</v>
       </c>
     </row>
   </sheetData>
@@ -11012,7 +11190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ19"/>
+  <dimension ref="A1:AK19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11051,6 +11229,7 @@
     <col width="12" customWidth="1" min="34" max="34"/>
     <col width="12" customWidth="1" min="35" max="35"/>
     <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11234,6 +11413,11 @@
           <t>20260116</t>
         </is>
       </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>20260119</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11348,6 +11532,9 @@
       <c r="AJ2" t="n">
         <v>165</v>
       </c>
+      <c r="AK2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11462,6 +11649,9 @@
       <c r="AJ3" t="n">
         <v>39</v>
       </c>
+      <c r="AK3" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11576,6 +11766,9 @@
       <c r="AJ4" t="n">
         <v>87</v>
       </c>
+      <c r="AK4" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11690,6 +11883,9 @@
       <c r="AJ5" t="n">
         <v>35</v>
       </c>
+      <c r="AK5" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11804,6 +12000,9 @@
       <c r="AJ6" t="n">
         <v>108</v>
       </c>
+      <c r="AK6" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11918,6 +12117,9 @@
       <c r="AJ7" t="n">
         <v>84</v>
       </c>
+      <c r="AK7" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12032,6 +12234,9 @@
       <c r="AJ8" t="n">
         <v>107</v>
       </c>
+      <c r="AK8" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12146,6 +12351,9 @@
       <c r="AJ9" t="n">
         <v>42</v>
       </c>
+      <c r="AK9" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12260,6 +12468,9 @@
       <c r="AJ10" t="n">
         <v>54</v>
       </c>
+      <c r="AK10" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12374,6 +12585,9 @@
       <c r="AJ11" t="n">
         <v>22</v>
       </c>
+      <c r="AK11" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12488,6 +12702,9 @@
       <c r="AJ12" t="n">
         <v>38</v>
       </c>
+      <c r="AK12" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12602,6 +12819,9 @@
       <c r="AJ13" t="n">
         <v>33</v>
       </c>
+      <c r="AK13" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12716,6 +12936,9 @@
       <c r="AJ14" t="n">
         <v>37</v>
       </c>
+      <c r="AK14" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12830,6 +13053,9 @@
       <c r="AJ15" t="n">
         <v>96</v>
       </c>
+      <c r="AK15" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12944,6 +13170,9 @@
       <c r="AJ16" t="n">
         <v>22</v>
       </c>
+      <c r="AK16" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13058,6 +13287,9 @@
       <c r="AJ17" t="n">
         <v>19</v>
       </c>
+      <c r="AK17" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13172,6 +13404,9 @@
       <c r="AJ18" t="n">
         <v>39</v>
       </c>
+      <c r="AK18" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13285,6 +13520,9 @@
       </c>
       <c r="AJ19" t="n">
         <v>88</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -13298,7 +13536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CQ19"/>
+  <dimension ref="A1:CR19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13396,6 +13634,7 @@
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
+    <col width="12" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13688,6 +13927,9 @@
       <c r="CQ1" s="1" t="n">
         <v>20260116</v>
       </c>
+      <c r="CR1" s="1" t="n">
+        <v>20260119</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13979,6 +14221,9 @@
       <c r="CQ2" t="n">
         <v>14710</v>
       </c>
+      <c r="CR2" t="n">
+        <v>15005</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14270,6 +14515,9 @@
       <c r="CQ3" t="n">
         <v>71930</v>
       </c>
+      <c r="CR3" t="n">
+        <v>71275</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14561,6 +14809,9 @@
       <c r="CQ4" t="n">
         <v>17665</v>
       </c>
+      <c r="CR4" t="n">
+        <v>18205</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14852,6 +15103,9 @@
       <c r="CQ5" t="n">
         <v>17665</v>
       </c>
+      <c r="CR5" t="n">
+        <v>17515</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15143,6 +15397,9 @@
       <c r="CQ6" t="n">
         <v>20780</v>
       </c>
+      <c r="CR6" t="n">
+        <v>20580</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15434,6 +15691,9 @@
       <c r="CQ7" t="n">
         <v>24615</v>
       </c>
+      <c r="CR7" t="n">
+        <v>24610</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15725,6 +15985,9 @@
       <c r="CQ8" t="n">
         <v>24070</v>
       </c>
+      <c r="CR8" t="n">
+        <v>23895</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16016,6 +16279,9 @@
       <c r="CQ9" t="n">
         <v>1417</v>
       </c>
+      <c r="CR9" t="n">
+        <v>1338</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16307,6 +16573,9 @@
       <c r="CQ10" t="n">
         <v>19185</v>
       </c>
+      <c r="CR10" t="n">
+        <v>18680</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16598,6 +16867,9 @@
       <c r="CQ11" t="n">
         <v>5200</v>
       </c>
+      <c r="CR11" t="n">
+        <v>5000</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16889,6 +17161,9 @@
       <c r="CQ12" t="n">
         <v>5580</v>
       </c>
+      <c r="CR12" t="n">
+        <v>5360</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17180,6 +17455,9 @@
       <c r="CQ13" t="n">
         <v>5570</v>
       </c>
+      <c r="CR13" t="n">
+        <v>5385</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17471,6 +17749,9 @@
       <c r="CQ14" t="n">
         <v>1456</v>
       </c>
+      <c r="CR14" t="n">
+        <v>1377</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17762,6 +18043,9 @@
       <c r="CQ15" t="n">
         <v>18875</v>
       </c>
+      <c r="CR15" t="n">
+        <v>19360</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -18053,6 +18337,9 @@
       <c r="CQ16" t="n">
         <v>10595</v>
       </c>
+      <c r="CR16" t="n">
+        <v>10300</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -18344,6 +18631,9 @@
       <c r="CQ17" t="n">
         <v>6080</v>
       </c>
+      <c r="CR17" t="n">
+        <v>5925</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -18635,6 +18925,9 @@
       <c r="CQ18" t="n">
         <v>20890</v>
       </c>
+      <c r="CR18" t="n">
+        <v>20195</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -18925,6 +19218,9 @@
       </c>
       <c r="CQ19" t="n">
         <v>15725</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>16065</v>
       </c>
     </row>
   </sheetData>
@@ -18938,7 +19234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CQ19"/>
+  <dimension ref="A1:CR19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19036,6 +19332,7 @@
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
+    <col width="12" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19328,6 +19625,9 @@
       <c r="CQ1" s="1" t="n">
         <v>20260116</v>
       </c>
+      <c r="CR1" s="1" t="n">
+        <v>20260119</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19619,6 +19919,9 @@
       <c r="CQ2" t="n">
         <v>15245</v>
       </c>
+      <c r="CR2" t="n">
+        <v>15290</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19910,6 +20213,9 @@
       <c r="CQ3" t="n">
         <v>72435</v>
       </c>
+      <c r="CR3" t="n">
+        <v>72595</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20201,6 +20507,9 @@
       <c r="CQ4" t="n">
         <v>18465</v>
       </c>
+      <c r="CR4" t="n">
+        <v>18435</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20492,6 +20801,9 @@
       <c r="CQ5" t="n">
         <v>17740</v>
       </c>
+      <c r="CR5" t="n">
+        <v>17570</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20783,6 +21095,9 @@
       <c r="CQ6" t="n">
         <v>20855</v>
       </c>
+      <c r="CR6" t="n">
+        <v>20875</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21074,6 +21389,9 @@
       <c r="CQ7" t="n">
         <v>24800</v>
       </c>
+      <c r="CR7" t="n">
+        <v>24970</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21365,6 +21683,9 @@
       <c r="CQ8" t="n">
         <v>24280</v>
       </c>
+      <c r="CR8" t="n">
+        <v>24350</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21656,6 +21977,9 @@
       <c r="CQ9" t="n">
         <v>1434</v>
       </c>
+      <c r="CR9" t="n">
+        <v>1445</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21947,6 +22271,9 @@
       <c r="CQ10" t="n">
         <v>19235</v>
       </c>
+      <c r="CR10" t="n">
+        <v>18822</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22238,6 +22565,9 @@
       <c r="CQ11" t="n">
         <v>5230</v>
       </c>
+      <c r="CR11" t="n">
+        <v>5280</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -22529,6 +22859,9 @@
       <c r="CQ12" t="n">
         <v>5600</v>
       </c>
+      <c r="CR12" t="n">
+        <v>5600</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -22820,6 +23153,9 @@
       <c r="CQ13" t="n">
         <v>5620</v>
       </c>
+      <c r="CR13" t="n">
+        <v>5620</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -23111,6 +23447,9 @@
       <c r="CQ14" t="n">
         <v>1476</v>
       </c>
+      <c r="CR14" t="n">
+        <v>1503</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -23402,6 +23741,9 @@
       <c r="CQ15" t="n">
         <v>19870</v>
       </c>
+      <c r="CR15" t="n">
+        <v>19595</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -23693,6 +24035,9 @@
       <c r="CQ16" t="n">
         <v>10630</v>
       </c>
+      <c r="CR16" t="n">
+        <v>10740</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -23984,6 +24329,9 @@
       <c r="CQ17" t="n">
         <v>6095</v>
       </c>
+      <c r="CR17" t="n">
+        <v>6195</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24275,6 +24623,9 @@
       <c r="CQ18" t="n">
         <v>20900</v>
       </c>
+      <c r="CR18" t="n">
+        <v>20380</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -24565,6 +24916,9 @@
       </c>
       <c r="CQ19" t="n">
         <v>16420</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>16150</v>
       </c>
     </row>
   </sheetData>
@@ -24578,7 +24932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CQ19"/>
+  <dimension ref="A1:CR19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24676,6 +25030,7 @@
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
+    <col width="12" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24968,6 +25323,9 @@
       <c r="CQ1" s="1" t="n">
         <v>20260116</v>
       </c>
+      <c r="CR1" s="1" t="n">
+        <v>20260119</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25259,6 +25617,9 @@
       <c r="CQ2" t="n">
         <v>14340</v>
       </c>
+      <c r="CR2" t="n">
+        <v>14835</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25550,6 +25911,9 @@
       <c r="CQ3" t="n">
         <v>71205</v>
       </c>
+      <c r="CR3" t="n">
+        <v>71200</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25841,6 +26205,9 @@
       <c r="CQ4" t="n">
         <v>17370</v>
       </c>
+      <c r="CR4" t="n">
+        <v>18060</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26132,6 +26499,9 @@
       <c r="CQ5" t="n">
         <v>17390</v>
       </c>
+      <c r="CR5" t="n">
+        <v>17225</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26423,6 +26793,9 @@
       <c r="CQ6" t="n">
         <v>20540</v>
       </c>
+      <c r="CR6" t="n">
+        <v>20530</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26714,6 +27087,9 @@
       <c r="CQ7" t="n">
         <v>24370</v>
       </c>
+      <c r="CR7" t="n">
+        <v>24490</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27005,6 +27381,9 @@
       <c r="CQ8" t="n">
         <v>23840</v>
       </c>
+      <c r="CR8" t="n">
+        <v>23810</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27296,6 +27675,9 @@
       <c r="CQ9" t="n">
         <v>1332</v>
       </c>
+      <c r="CR9" t="n">
+        <v>1314</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27587,6 +27969,9 @@
       <c r="CQ10" t="n">
         <v>18685</v>
       </c>
+      <c r="CR10" t="n">
+        <v>18580</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27878,6 +28263,9 @@
       <c r="CQ11" t="n">
         <v>5015</v>
       </c>
+      <c r="CR11" t="n">
+        <v>5000</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28169,6 +28557,9 @@
       <c r="CQ12" t="n">
         <v>5350</v>
       </c>
+      <c r="CR12" t="n">
+        <v>5335</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28460,6 +28851,9 @@
       <c r="CQ13" t="n">
         <v>5375</v>
       </c>
+      <c r="CR13" t="n">
+        <v>5355</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -28751,6 +29145,9 @@
       <c r="CQ14" t="n">
         <v>1379</v>
       </c>
+      <c r="CR14" t="n">
+        <v>1367</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -29042,6 +29439,9 @@
       <c r="CQ15" t="n">
         <v>18550</v>
       </c>
+      <c r="CR15" t="n">
+        <v>19135</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -29333,6 +29733,9 @@
       <c r="CQ16" t="n">
         <v>10245</v>
       </c>
+      <c r="CR16" t="n">
+        <v>10220</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -29624,6 +30027,9 @@
       <c r="CQ17" t="n">
         <v>5905</v>
       </c>
+      <c r="CR17" t="n">
+        <v>5900</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -29915,6 +30321,9 @@
       <c r="CQ18" t="n">
         <v>20265</v>
       </c>
+      <c r="CR18" t="n">
+        <v>20055</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -30205,6 +30614,9 @@
       </c>
       <c r="CQ19" t="n">
         <v>15415</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>15895</v>
       </c>
     </row>
   </sheetData>
@@ -30218,7 +30630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CQ19"/>
+  <dimension ref="A1:CR19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -30316,6 +30728,7 @@
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
+    <col width="12" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30608,6 +31021,9 @@
       <c r="CQ1" s="1" t="n">
         <v>20260116</v>
       </c>
+      <c r="CR1" s="1" t="n">
+        <v>20260119</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30899,6 +31315,9 @@
       <c r="CQ2" t="n">
         <v>15035</v>
       </c>
+      <c r="CR2" t="n">
+        <v>15070</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31190,6 +31609,9 @@
       <c r="CQ3" t="n">
         <v>71675</v>
       </c>
+      <c r="CR3" t="n">
+        <v>72310</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -31481,6 +31903,9 @@
       <c r="CQ4" t="n">
         <v>18370</v>
       </c>
+      <c r="CR4" t="n">
+        <v>18255</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -31772,6 +32197,9 @@
       <c r="CQ5" t="n">
         <v>17570</v>
       </c>
+      <c r="CR5" t="n">
+        <v>17435</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32063,6 +32491,9 @@
       <c r="CQ6" t="n">
         <v>20735</v>
       </c>
+      <c r="CR6" t="n">
+        <v>20805</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -32354,6 +32785,9 @@
       <c r="CQ7" t="n">
         <v>24700</v>
       </c>
+      <c r="CR7" t="n">
+        <v>24850</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -32645,6 +33079,9 @@
       <c r="CQ8" t="n">
         <v>24100</v>
       </c>
+      <c r="CR8" t="n">
+        <v>24205</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -32936,6 +33373,9 @@
       <c r="CQ9" t="n">
         <v>1346</v>
       </c>
+      <c r="CR9" t="n">
+        <v>1443</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -33227,6 +33667,9 @@
       <c r="CQ10" t="n">
         <v>18825</v>
       </c>
+      <c r="CR10" t="n">
+        <v>18760</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -33518,6 +33961,9 @@
       <c r="CQ11" t="n">
         <v>5025</v>
       </c>
+      <c r="CR11" t="n">
+        <v>5270</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33809,6 +34255,9 @@
       <c r="CQ12" t="n">
         <v>5375</v>
       </c>
+      <c r="CR12" t="n">
+        <v>5600</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34100,6 +34549,9 @@
       <c r="CQ13" t="n">
         <v>5390</v>
       </c>
+      <c r="CR13" t="n">
+        <v>5600</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34391,6 +34843,9 @@
       <c r="CQ14" t="n">
         <v>1387</v>
       </c>
+      <c r="CR14" t="n">
+        <v>1500</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -34682,6 +35137,9 @@
       <c r="CQ15" t="n">
         <v>19600</v>
       </c>
+      <c r="CR15" t="n">
+        <v>19360</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -34973,6 +35431,9 @@
       <c r="CQ16" t="n">
         <v>10280</v>
       </c>
+      <c r="CR16" t="n">
+        <v>10720</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -35264,6 +35725,9 @@
       <c r="CQ17" t="n">
         <v>5945</v>
       </c>
+      <c r="CR17" t="n">
+        <v>6195</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -35555,6 +36019,9 @@
       <c r="CQ18" t="n">
         <v>20410</v>
       </c>
+      <c r="CR18" t="n">
+        <v>20275</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -35845,6 +36312,9 @@
       </c>
       <c r="CQ19" t="n">
         <v>16225</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>16000</v>
       </c>
     </row>
   </sheetData>
@@ -35858,7 +36328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CQ19"/>
+  <dimension ref="A1:CR19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35956,6 +36426,7 @@
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
+    <col width="12" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36248,6 +36719,9 @@
       <c r="CQ1" s="1" t="n">
         <v>20260116</v>
       </c>
+      <c r="CR1" s="1" t="n">
+        <v>20260119</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -36539,6 +37013,9 @@
       <c r="CQ2" t="n">
         <v>547331</v>
       </c>
+      <c r="CR2" t="n">
+        <v>338526</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36830,6 +37307,9 @@
       <c r="CQ3" t="n">
         <v>1833306</v>
       </c>
+      <c r="CR3" t="n">
+        <v>1831907</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -37121,6 +37601,9 @@
       <c r="CQ4" t="n">
         <v>326831</v>
       </c>
+      <c r="CR4" t="n">
+        <v>179883</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -37412,6 +37895,9 @@
       <c r="CQ5" t="n">
         <v>338742</v>
       </c>
+      <c r="CR5" t="n">
+        <v>232471</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -37703,6 +38189,9 @@
       <c r="CQ6" t="n">
         <v>5822368</v>
       </c>
+      <c r="CR6" t="n">
+        <v>4333889</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -37994,6 +38483,9 @@
       <c r="CQ7" t="n">
         <v>6637912</v>
       </c>
+      <c r="CR7" t="n">
+        <v>4115001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -38285,6 +38777,9 @@
       <c r="CQ8" t="n">
         <v>18102911</v>
       </c>
+      <c r="CR8" t="n">
+        <v>15181103</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -38576,6 +39071,9 @@
       <c r="CQ9" t="n">
         <v>5982270</v>
       </c>
+      <c r="CR9" t="n">
+        <v>9572667</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -38867,6 +39365,9 @@
       <c r="CQ10" t="n">
         <v>1347095</v>
       </c>
+      <c r="CR10" t="n">
+        <v>1506760</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -39158,6 +39659,9 @@
       <c r="CQ11" t="n">
         <v>532565</v>
       </c>
+      <c r="CR11" t="n">
+        <v>1101136</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -39449,6 +39953,9 @@
       <c r="CQ12" t="n">
         <v>1987441</v>
       </c>
+      <c r="CR12" t="n">
+        <v>3417073</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -39740,6 +40247,9 @@
       <c r="CQ13" t="n">
         <v>4264432</v>
       </c>
+      <c r="CR13" t="n">
+        <v>6814571</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -40031,6 +40541,9 @@
       <c r="CQ14" t="n">
         <v>34608247</v>
       </c>
+      <c r="CR14" t="n">
+        <v>58003650</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -40322,6 +40835,9 @@
       <c r="CQ15" t="n">
         <v>3670647</v>
       </c>
+      <c r="CR15" t="n">
+        <v>1653607</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -40613,6 +41129,9 @@
       <c r="CQ16" t="n">
         <v>239406</v>
       </c>
+      <c r="CR16" t="n">
+        <v>410296</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -40904,6 +41423,9 @@
       <c r="CQ17" t="n">
         <v>69146</v>
       </c>
+      <c r="CR17" t="n">
+        <v>100107</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41195,6 +41717,9 @@
       <c r="CQ18" t="n">
         <v>135841</v>
       </c>
+      <c r="CR18" t="n">
+        <v>95057</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -41485,6 +42010,9 @@
       </c>
       <c r="CQ19" t="n">
         <v>92710</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>52946</v>
       </c>
     </row>
   </sheetData>
@@ -41498,7 +42026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX19"/>
+  <dimension ref="A1:BY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -41577,6 +42105,7 @@
     <col width="10" customWidth="1" min="74" max="74"/>
     <col width="10" customWidth="1" min="75" max="75"/>
     <col width="10" customWidth="1" min="76" max="76"/>
+    <col width="10" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -41812,6 +42341,9 @@
       <c r="BX1" s="1" t="n">
         <v>20260116</v>
       </c>
+      <c r="BY1" s="1" t="n">
+        <v>20260119</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -42046,6 +42578,9 @@
       <c r="BX2" t="n">
         <v>32</v>
       </c>
+      <c r="BY2" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -42280,6 +42815,9 @@
       <c r="BX3" t="n">
         <v>100</v>
       </c>
+      <c r="BY3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -42514,6 +43052,9 @@
       <c r="BX4" t="n">
         <v>64</v>
       </c>
+      <c r="BY4" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -42748,6 +43289,9 @@
       <c r="BX5" t="n">
         <v>96</v>
       </c>
+      <c r="BY5" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -42982,6 +43526,9 @@
       <c r="BX6" t="n">
         <v>100</v>
       </c>
+      <c r="BY6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -43216,6 +43763,9 @@
       <c r="BX7" t="n">
         <v>100</v>
       </c>
+      <c r="BY7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -43450,6 +44000,9 @@
       <c r="BX8" t="n">
         <v>100</v>
       </c>
+      <c r="BY8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -43684,6 +44237,9 @@
       <c r="BX9" t="n">
         <v>59</v>
       </c>
+      <c r="BY9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -43918,6 +44474,9 @@
       <c r="BX10" t="n">
         <v>91</v>
       </c>
+      <c r="BY10" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -44152,6 +44711,9 @@
       <c r="BX11" t="n">
         <v>41</v>
       </c>
+      <c r="BY11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -44386,6 +44948,9 @@
       <c r="BX12" t="n">
         <v>44</v>
       </c>
+      <c r="BY12" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -44620,6 +45185,9 @@
       <c r="BX13" t="n">
         <v>37</v>
       </c>
+      <c r="BY13" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -44854,6 +45422,9 @@
       <c r="BX14" t="n">
         <v>42</v>
       </c>
+      <c r="BY14" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -45088,6 +45659,9 @@
       <c r="BX15" t="n">
         <v>52</v>
       </c>
+      <c r="BY15" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -45322,6 +45896,9 @@
       <c r="BX16" t="n">
         <v>55</v>
       </c>
+      <c r="BY16" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -45556,6 +46133,9 @@
       <c r="BX17" t="n">
         <v>44</v>
       </c>
+      <c r="BY17" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -45790,6 +46370,9 @@
       <c r="BX18" t="n">
         <v>96</v>
       </c>
+      <c r="BY18" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -46023,6 +46606,9 @@
       </c>
       <c r="BX19" t="n">
         <v>45</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -46036,7 +46622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ19"/>
+  <dimension ref="A1:AK19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -46075,6 +46661,7 @@
     <col width="10" customWidth="1" min="34" max="34"/>
     <col width="10" customWidth="1" min="35" max="35"/>
     <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="10" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -46190,6 +46777,9 @@
       <c r="AJ1" s="1" t="n">
         <v>20260116</v>
       </c>
+      <c r="AK1" s="1" t="n">
+        <v>20260119</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -46304,6 +46894,9 @@
       <c r="AJ2" t="n">
         <v>56</v>
       </c>
+      <c r="AK2" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -46418,6 +47011,9 @@
       <c r="AJ3" t="n">
         <v>100</v>
       </c>
+      <c r="AK3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -46532,6 +47128,9 @@
       <c r="AJ4" t="n">
         <v>72</v>
       </c>
+      <c r="AK4" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -46646,6 +47245,9 @@
       <c r="AJ5" t="n">
         <v>96</v>
       </c>
+      <c r="AK5" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -46760,6 +47362,9 @@
       <c r="AJ6" t="n">
         <v>100</v>
       </c>
+      <c r="AK6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -46874,6 +47479,9 @@
       <c r="AJ7" t="n">
         <v>100</v>
       </c>
+      <c r="AK7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -46988,6 +47596,9 @@
       <c r="AJ8" t="n">
         <v>100</v>
       </c>
+      <c r="AK8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -47102,6 +47713,9 @@
       <c r="AJ9" t="n">
         <v>22</v>
       </c>
+      <c r="AK9" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -47216,6 +47830,9 @@
       <c r="AJ10" t="n">
         <v>91</v>
       </c>
+      <c r="AK10" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -47330,6 +47947,9 @@
       <c r="AJ11" t="n">
         <v>26</v>
       </c>
+      <c r="AK11" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -47444,6 +48064,9 @@
       <c r="AJ12" t="n">
         <v>28</v>
       </c>
+      <c r="AK12" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -47558,6 +48181,9 @@
       <c r="AJ13" t="n">
         <v>29</v>
       </c>
+      <c r="AK13" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -47672,6 +48298,9 @@
       <c r="AJ14" t="n">
         <v>18</v>
       </c>
+      <c r="AK14" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -47786,6 +48415,9 @@
       <c r="AJ15" t="n">
         <v>85</v>
       </c>
+      <c r="AK15" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -47900,6 +48532,9 @@
       <c r="AJ16" t="n">
         <v>30</v>
       </c>
+      <c r="AK16" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -48014,6 +48649,9 @@
       <c r="AJ17" t="n">
         <v>23</v>
       </c>
+      <c r="AK17" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -48128,6 +48766,9 @@
       <c r="AJ18" t="n">
         <v>96</v>
       </c>
+      <c r="AK18" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -48241,6 +48882,9 @@
       </c>
       <c r="AJ19" t="n">
         <v>84</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -48254,7 +48898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX19"/>
+  <dimension ref="A1:BY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -48333,6 +48977,7 @@
     <col width="10" customWidth="1" min="74" max="74"/>
     <col width="10" customWidth="1" min="75" max="75"/>
     <col width="10" customWidth="1" min="76" max="76"/>
+    <col width="10" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -48568,6 +49213,9 @@
       <c r="BX1" s="1" t="n">
         <v>20260116</v>
       </c>
+      <c r="BY1" s="1" t="n">
+        <v>20260119</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -48802,6 +49450,9 @@
       <c r="BX2" t="n">
         <v>-23</v>
       </c>
+      <c r="BY2" t="n">
+        <v>-21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -49036,6 +49687,9 @@
       <c r="BX3" t="n">
         <v>58</v>
       </c>
+      <c r="BY3" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -49270,6 +49924,9 @@
       <c r="BX4" t="n">
         <v>30</v>
       </c>
+      <c r="BY4" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -49504,6 +50161,9 @@
       <c r="BX5" t="n">
         <v>58</v>
       </c>
+      <c r="BY5" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -49738,6 +50398,9 @@
       <c r="BX6" t="n">
         <v>62</v>
       </c>
+      <c r="BY6" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -49972,6 +50635,9 @@
       <c r="BX7" t="n">
         <v>62</v>
       </c>
+      <c r="BY7" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -50206,6 +50872,9 @@
       <c r="BX8" t="n">
         <v>58</v>
       </c>
+      <c r="BY8" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -50440,6 +51109,9 @@
       <c r="BX9" t="n">
         <v>30</v>
       </c>
+      <c r="BY9" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -50674,6 +51346,9 @@
       <c r="BX10" t="n">
         <v>56</v>
       </c>
+      <c r="BY10" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -50908,6 +51583,9 @@
       <c r="BX11" t="n">
         <v>-1</v>
       </c>
+      <c r="BY11" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -51142,6 +51820,9 @@
       <c r="BX12" t="n">
         <v>1</v>
       </c>
+      <c r="BY12" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -51376,6 +52057,9 @@
       <c r="BX13" t="n">
         <v>-9</v>
       </c>
+      <c r="BY13" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -51610,6 +52294,9 @@
       <c r="BX14" t="n">
         <v>6</v>
       </c>
+      <c r="BY14" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -51844,6 +52531,9 @@
       <c r="BX15" t="n">
         <v>15</v>
       </c>
+      <c r="BY15" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -52078,6 +52768,9 @@
       <c r="BX16" t="n">
         <v>17</v>
       </c>
+      <c r="BY16" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -52312,6 +53005,9 @@
       <c r="BX17" t="n">
         <v>4</v>
       </c>
+      <c r="BY17" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -52546,6 +53242,9 @@
       <c r="BX18" t="n">
         <v>58</v>
       </c>
+      <c r="BY18" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -52779,6 +53478,9 @@
       </c>
       <c r="BX19" t="n">
         <v>16</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>-18</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK19"/>
+  <dimension ref="A1:AL19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -749,6 +749,7 @@
     <col width="10" customWidth="1" min="35" max="35"/>
     <col width="10" customWidth="1" min="36" max="36"/>
     <col width="10" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -867,6 +868,9 @@
       <c r="AK1" s="1" t="n">
         <v>20260119</v>
       </c>
+      <c r="AL1" s="1" t="n">
+        <v>20260120</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -984,6 +988,9 @@
       <c r="AK2" t="n">
         <v>-11</v>
       </c>
+      <c r="AL2" t="n">
+        <v>-21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1101,6 +1108,9 @@
       <c r="AK3" t="n">
         <v>115</v>
       </c>
+      <c r="AL3" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1218,6 +1228,9 @@
       <c r="AK4" t="n">
         <v>17</v>
       </c>
+      <c r="AL4" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1335,6 +1348,9 @@
       <c r="AK5" t="n">
         <v>77</v>
       </c>
+      <c r="AL5" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1452,6 +1468,9 @@
       <c r="AK6" t="n">
         <v>115</v>
       </c>
+      <c r="AL6" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1569,6 +1588,9 @@
       <c r="AK7" t="n">
         <v>116</v>
       </c>
+      <c r="AL7" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1686,6 +1708,9 @@
       <c r="AK8" t="n">
         <v>113</v>
       </c>
+      <c r="AL8" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1803,6 +1828,9 @@
       <c r="AK9" t="n">
         <v>-18</v>
       </c>
+      <c r="AL9" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1920,6 +1948,9 @@
       <c r="AK10" t="n">
         <v>91</v>
       </c>
+      <c r="AL10" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2037,6 +2068,9 @@
       <c r="AK11" t="n">
         <v>4</v>
       </c>
+      <c r="AL11" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2154,6 +2188,9 @@
       <c r="AK12" t="n">
         <v>-7</v>
       </c>
+      <c r="AL12" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2271,6 +2308,9 @@
       <c r="AK13" t="n">
         <v>-5</v>
       </c>
+      <c r="AL13" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2388,6 +2428,9 @@
       <c r="AK14" t="n">
         <v>-26</v>
       </c>
+      <c r="AL14" t="n">
+        <v>-12</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2505,6 +2548,9 @@
       <c r="AK15" t="n">
         <v>25</v>
       </c>
+      <c r="AL15" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2622,6 +2668,9 @@
       <c r="AK16" t="n">
         <v>-2</v>
       </c>
+      <c r="AL16" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2739,6 +2788,9 @@
       <c r="AK17" t="n">
         <v>-19</v>
       </c>
+      <c r="AL17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2856,6 +2908,9 @@
       <c r="AK18" t="n">
         <v>96</v>
       </c>
+      <c r="AL18" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2972,6 +3027,9 @@
       </c>
       <c r="AK19" t="n">
         <v>22</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2985,7 +3043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY19"/>
+  <dimension ref="A1:BZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3065,6 +3123,7 @@
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
+    <col width="12" customWidth="1" min="78" max="78"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3453,6 +3512,11 @@
           <t>20260119</t>
         </is>
       </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>20260120</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3690,6 +3754,9 @@
       <c r="BY2" t="n">
         <v>99</v>
       </c>
+      <c r="BZ2" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3927,6 +3994,9 @@
       <c r="BY3" t="n">
         <v>111</v>
       </c>
+      <c r="BZ3" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4164,6 +4234,9 @@
       <c r="BY4" t="n">
         <v>101</v>
       </c>
+      <c r="BZ4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4401,6 +4474,9 @@
       <c r="BY5" t="n">
         <v>105</v>
       </c>
+      <c r="BZ5" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4638,6 +4714,9 @@
       <c r="BY6" t="n">
         <v>110</v>
       </c>
+      <c r="BZ6" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4875,6 +4954,9 @@
       <c r="BY7" t="n">
         <v>111</v>
       </c>
+      <c r="BZ7" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5112,6 +5194,9 @@
       <c r="BY8" t="n">
         <v>112</v>
       </c>
+      <c r="BZ8" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5349,6 +5434,9 @@
       <c r="BY9" t="n">
         <v>111</v>
       </c>
+      <c r="BZ9" t="n">
+        <v>115</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5586,6 +5674,9 @@
       <c r="BY10" t="n">
         <v>106</v>
       </c>
+      <c r="BZ10" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5823,6 +5914,9 @@
       <c r="BY11" t="n">
         <v>105</v>
       </c>
+      <c r="BZ11" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6060,6 +6154,9 @@
       <c r="BY12" t="n">
         <v>104</v>
       </c>
+      <c r="BZ12" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6297,6 +6394,9 @@
       <c r="BY13" t="n">
         <v>103</v>
       </c>
+      <c r="BZ13" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6534,6 +6634,9 @@
       <c r="BY14" t="n">
         <v>109</v>
       </c>
+      <c r="BZ14" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6771,6 +6874,9 @@
       <c r="BY15" t="n">
         <v>100</v>
       </c>
+      <c r="BZ15" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7008,6 +7114,9 @@
       <c r="BY16" t="n">
         <v>106</v>
       </c>
+      <c r="BZ16" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7245,6 +7354,9 @@
       <c r="BY17" t="n">
         <v>105</v>
       </c>
+      <c r="BZ17" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7482,6 +7594,9 @@
       <c r="BY18" t="n">
         <v>107</v>
       </c>
+      <c r="BZ18" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7717,6 +7832,9 @@
         <v>101</v>
       </c>
       <c r="BY19" t="n">
+        <v>99</v>
+      </c>
+      <c r="BZ19" t="n">
         <v>99</v>
       </c>
     </row>
@@ -7731,7 +7849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF19"/>
+  <dimension ref="A1:BG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7743,6 +7861,7 @@
     <col width="12" customWidth="1" min="56" max="56"/>
     <col width="12" customWidth="1" min="57" max="57"/>
     <col width="12" customWidth="1" min="58" max="58"/>
+    <col width="12" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7938,6 +8057,11 @@
           <t>20260119</t>
         </is>
       </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>20260120</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8118,6 +8242,9 @@
       <c r="BF2" t="n">
         <v>0.83</v>
       </c>
+      <c r="BG2" t="n">
+        <v>-0.54</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8298,6 +8425,9 @@
       <c r="BF3" t="n">
         <v>63.46</v>
       </c>
+      <c r="BG3" t="n">
+        <v>46.33</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8478,6 +8608,9 @@
       <c r="BF4" t="n">
         <v>-4.93</v>
       </c>
+      <c r="BG4" t="n">
+        <v>-9.4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8658,6 +8791,9 @@
       <c r="BF5" t="n">
         <v>30.75</v>
       </c>
+      <c r="BG5" t="n">
+        <v>17.42</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8838,6 +8974,9 @@
       <c r="BF6" t="n">
         <v>62.05</v>
       </c>
+      <c r="BG6" t="n">
+        <v>44.92</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9018,6 +9157,9 @@
       <c r="BF7" t="n">
         <v>67.90000000000001</v>
       </c>
+      <c r="BG7" t="n">
+        <v>50.94</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9198,6 +9340,9 @@
       <c r="BF8" t="n">
         <v>65.62</v>
       </c>
+      <c r="BG8" t="n">
+        <v>47.82</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9378,6 +9523,9 @@
       <c r="BF9" t="n">
         <v>-35.32</v>
       </c>
+      <c r="BG9" t="n">
+        <v>-26.01</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9558,6 +9706,9 @@
       <c r="BF10" t="n">
         <v>38.88</v>
       </c>
+      <c r="BG10" t="n">
+        <v>26.12</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9738,6 +9889,9 @@
       <c r="BF11" t="n">
         <v>-38.94</v>
       </c>
+      <c r="BG11" t="n">
+        <v>-29.99</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9918,6 +10072,9 @@
       <c r="BF12" t="n">
         <v>-42.08</v>
       </c>
+      <c r="BG12" t="n">
+        <v>-35.21</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10098,6 +10255,9 @@
       <c r="BF13" t="n">
         <v>-46.91</v>
       </c>
+      <c r="BG13" t="n">
+        <v>-40.18</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10278,6 +10438,9 @@
       <c r="BF14" t="n">
         <v>-46.27</v>
       </c>
+      <c r="BG14" t="n">
+        <v>-38.74</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10458,6 +10621,9 @@
       <c r="BF15" t="n">
         <v>0.85</v>
       </c>
+      <c r="BG15" t="n">
+        <v>-3.18</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10638,6 +10804,9 @@
       <c r="BF16" t="n">
         <v>-39.23</v>
       </c>
+      <c r="BG16" t="n">
+        <v>-27.29</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10818,6 +10987,9 @@
       <c r="BF17" t="n">
         <v>-44.78</v>
       </c>
+      <c r="BG17" t="n">
+        <v>-36.38</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10998,6 +11170,9 @@
       <c r="BF18" t="n">
         <v>39</v>
       </c>
+      <c r="BG18" t="n">
+        <v>25.76</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11177,6 +11352,9 @@
       </c>
       <c r="BF19" t="n">
         <v>3.54</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>2.12</v>
       </c>
     </row>
   </sheetData>
@@ -11190,7 +11368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK19"/>
+  <dimension ref="A1:AL19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11230,6 +11408,7 @@
     <col width="12" customWidth="1" min="35" max="35"/>
     <col width="12" customWidth="1" min="36" max="36"/>
     <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="12" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11418,6 +11597,11 @@
           <t>20260119</t>
         </is>
       </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>20260120</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11535,6 +11719,9 @@
       <c r="AK2" t="n">
         <v>99</v>
       </c>
+      <c r="AL2" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11652,6 +11839,9 @@
       <c r="AK3" t="n">
         <v>39</v>
       </c>
+      <c r="AL3" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11769,6 +11959,9 @@
       <c r="AK4" t="n">
         <v>47</v>
       </c>
+      <c r="AL4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11886,6 +12079,9 @@
       <c r="AK5" t="n">
         <v>25</v>
       </c>
+      <c r="AL5" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12003,6 +12199,9 @@
       <c r="AK6" t="n">
         <v>80</v>
       </c>
+      <c r="AL6" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12120,6 +12319,9 @@
       <c r="AK7" t="n">
         <v>52</v>
       </c>
+      <c r="AL7" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12237,6 +12439,9 @@
       <c r="AK8" t="n">
         <v>90</v>
       </c>
+      <c r="AL8" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12354,6 +12559,9 @@
       <c r="AK9" t="n">
         <v>69</v>
       </c>
+      <c r="AL9" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12471,6 +12679,9 @@
       <c r="AK10" t="n">
         <v>61</v>
       </c>
+      <c r="AL10" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12588,6 +12799,9 @@
       <c r="AK11" t="n">
         <v>47</v>
       </c>
+      <c r="AL11" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12705,6 +12919,9 @@
       <c r="AK12" t="n">
         <v>66</v>
       </c>
+      <c r="AL12" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12822,6 +13039,9 @@
       <c r="AK13" t="n">
         <v>54</v>
       </c>
+      <c r="AL13" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12939,6 +13159,9 @@
       <c r="AK14" t="n">
         <v>62</v>
       </c>
+      <c r="AL14" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13056,6 +13279,9 @@
       <c r="AK15" t="n">
         <v>43</v>
       </c>
+      <c r="AL15" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13173,6 +13399,9 @@
       <c r="AK16" t="n">
         <v>39</v>
       </c>
+      <c r="AL16" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13290,6 +13519,9 @@
       <c r="AK17" t="n">
         <v>30</v>
       </c>
+      <c r="AL17" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13407,6 +13639,9 @@
       <c r="AK18" t="n">
         <v>27</v>
       </c>
+      <c r="AL18" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13523,6 +13758,9 @@
       </c>
       <c r="AK19" t="n">
         <v>50</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -13536,7 +13774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR19"/>
+  <dimension ref="A1:CS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13635,6 +13873,7 @@
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
+    <col width="12" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13930,6 +14169,9 @@
       <c r="CR1" s="1" t="n">
         <v>20260119</v>
       </c>
+      <c r="CS1" s="1" t="n">
+        <v>20260120</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14224,6 +14466,9 @@
       <c r="CR2" t="n">
         <v>15005</v>
       </c>
+      <c r="CS2" t="n">
+        <v>15090</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14518,6 +14763,9 @@
       <c r="CR3" t="n">
         <v>71275</v>
       </c>
+      <c r="CS3" t="n">
+        <v>72035</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14812,6 +15060,9 @@
       <c r="CR4" t="n">
         <v>18205</v>
       </c>
+      <c r="CS4" t="n">
+        <v>18260</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15106,6 +15357,9 @@
       <c r="CR5" t="n">
         <v>17515</v>
       </c>
+      <c r="CS5" t="n">
+        <v>17240</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15400,6 +15654,9 @@
       <c r="CR6" t="n">
         <v>20580</v>
       </c>
+      <c r="CS6" t="n">
+        <v>20745</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15694,6 +15951,9 @@
       <c r="CR7" t="n">
         <v>24610</v>
       </c>
+      <c r="CS7" t="n">
+        <v>24795</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15988,6 +16248,9 @@
       <c r="CR8" t="n">
         <v>23895</v>
       </c>
+      <c r="CS8" t="n">
+        <v>24205</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16282,6 +16545,9 @@
       <c r="CR9" t="n">
         <v>1338</v>
       </c>
+      <c r="CS9" t="n">
+        <v>1451</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16576,6 +16842,9 @@
       <c r="CR10" t="n">
         <v>18680</v>
       </c>
+      <c r="CS10" t="n">
+        <v>18665</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16870,6 +17139,9 @@
       <c r="CR11" t="n">
         <v>5000</v>
       </c>
+      <c r="CS11" t="n">
+        <v>5275</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17164,6 +17436,9 @@
       <c r="CR12" t="n">
         <v>5360</v>
       </c>
+      <c r="CS12" t="n">
+        <v>5605</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17458,6 +17733,9 @@
       <c r="CR13" t="n">
         <v>5385</v>
       </c>
+      <c r="CS13" t="n">
+        <v>5635</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17752,6 +18030,9 @@
       <c r="CR14" t="n">
         <v>1377</v>
       </c>
+      <c r="CS14" t="n">
+        <v>1499</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18046,6 +18327,9 @@
       <c r="CR15" t="n">
         <v>19360</v>
       </c>
+      <c r="CS15" t="n">
+        <v>19525</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -18340,6 +18624,9 @@
       <c r="CR16" t="n">
         <v>10300</v>
       </c>
+      <c r="CS16" t="n">
+        <v>10775</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -18634,6 +18921,9 @@
       <c r="CR17" t="n">
         <v>5925</v>
       </c>
+      <c r="CS17" t="n">
+        <v>6225</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -18928,6 +19218,9 @@
       <c r="CR18" t="n">
         <v>20195</v>
       </c>
+      <c r="CS18" t="n">
+        <v>20140</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -19221,6 +19514,9 @@
       </c>
       <c r="CR19" t="n">
         <v>16065</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>16115</v>
       </c>
     </row>
   </sheetData>
@@ -19234,7 +19530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR19"/>
+  <dimension ref="A1:CS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19333,6 +19629,7 @@
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
+    <col width="12" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19628,6 +19925,9 @@
       <c r="CR1" s="1" t="n">
         <v>20260119</v>
       </c>
+      <c r="CS1" s="1" t="n">
+        <v>20260120</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19922,6 +20222,9 @@
       <c r="CR2" t="n">
         <v>15290</v>
       </c>
+      <c r="CS2" t="n">
+        <v>15435</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20216,6 +20519,9 @@
       <c r="CR3" t="n">
         <v>72595</v>
       </c>
+      <c r="CS3" t="n">
+        <v>72095</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20510,6 +20816,9 @@
       <c r="CR4" t="n">
         <v>18435</v>
       </c>
+      <c r="CS4" t="n">
+        <v>18745</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20804,6 +21113,9 @@
       <c r="CR5" t="n">
         <v>17570</v>
       </c>
+      <c r="CS5" t="n">
+        <v>17250</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21098,6 +21410,9 @@
       <c r="CR6" t="n">
         <v>20875</v>
       </c>
+      <c r="CS6" t="n">
+        <v>20745</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21392,6 +21707,9 @@
       <c r="CR7" t="n">
         <v>24970</v>
       </c>
+      <c r="CS7" t="n">
+        <v>24795</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21686,6 +22004,9 @@
       <c r="CR8" t="n">
         <v>24350</v>
       </c>
+      <c r="CS8" t="n">
+        <v>24205</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21980,6 +22301,9 @@
       <c r="CR9" t="n">
         <v>1445</v>
       </c>
+      <c r="CS9" t="n">
+        <v>1538</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22274,6 +22598,9 @@
       <c r="CR10" t="n">
         <v>18822</v>
       </c>
+      <c r="CS10" t="n">
+        <v>18695</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22568,6 +22895,9 @@
       <c r="CR11" t="n">
         <v>5280</v>
       </c>
+      <c r="CS11" t="n">
+        <v>5485</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -22862,6 +23192,9 @@
       <c r="CR12" t="n">
         <v>5600</v>
       </c>
+      <c r="CS12" t="n">
+        <v>5840</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -23156,6 +23489,9 @@
       <c r="CR13" t="n">
         <v>5620</v>
       </c>
+      <c r="CS13" t="n">
+        <v>5895</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -23450,6 +23786,9 @@
       <c r="CR14" t="n">
         <v>1503</v>
       </c>
+      <c r="CS14" t="n">
+        <v>1624</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -23744,6 +24083,9 @@
       <c r="CR15" t="n">
         <v>19595</v>
       </c>
+      <c r="CS15" t="n">
+        <v>19945</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24038,6 +24380,9 @@
       <c r="CR16" t="n">
         <v>10740</v>
       </c>
+      <c r="CS16" t="n">
+        <v>11240</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24332,6 +24677,9 @@
       <c r="CR17" t="n">
         <v>6195</v>
       </c>
+      <c r="CS17" t="n">
+        <v>6480</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24626,6 +24974,9 @@
       <c r="CR18" t="n">
         <v>20380</v>
       </c>
+      <c r="CS18" t="n">
+        <v>20140</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -24919,6 +25270,9 @@
       </c>
       <c r="CR19" t="n">
         <v>16150</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>16490</v>
       </c>
     </row>
   </sheetData>
@@ -24932,7 +25286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR19"/>
+  <dimension ref="A1:CS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25031,6 +25385,7 @@
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
+    <col width="12" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25326,6 +25681,9 @@
       <c r="CR1" s="1" t="n">
         <v>20260119</v>
       </c>
+      <c r="CS1" s="1" t="n">
+        <v>20260120</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25620,6 +25978,9 @@
       <c r="CR2" t="n">
         <v>14835</v>
       </c>
+      <c r="CS2" t="n">
+        <v>14880</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25914,6 +26275,9 @@
       <c r="CR3" t="n">
         <v>71200</v>
       </c>
+      <c r="CS3" t="n">
+        <v>69840</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26208,6 +26572,9 @@
       <c r="CR4" t="n">
         <v>18060</v>
       </c>
+      <c r="CS4" t="n">
+        <v>18160</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26502,6 +26869,9 @@
       <c r="CR5" t="n">
         <v>17225</v>
       </c>
+      <c r="CS5" t="n">
+        <v>16600</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26796,6 +27166,9 @@
       <c r="CR6" t="n">
         <v>20530</v>
       </c>
+      <c r="CS6" t="n">
+        <v>20070</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27090,6 +27463,9 @@
       <c r="CR7" t="n">
         <v>24490</v>
       </c>
+      <c r="CS7" t="n">
+        <v>23985</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27384,6 +27760,9 @@
       <c r="CR8" t="n">
         <v>23810</v>
       </c>
+      <c r="CS8" t="n">
+        <v>23390</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27678,6 +28057,9 @@
       <c r="CR9" t="n">
         <v>1314</v>
       </c>
+      <c r="CS9" t="n">
+        <v>1420</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27972,6 +28354,9 @@
       <c r="CR10" t="n">
         <v>18580</v>
       </c>
+      <c r="CS10" t="n">
+        <v>18035</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28266,6 +28651,9 @@
       <c r="CR11" t="n">
         <v>5000</v>
       </c>
+      <c r="CS11" t="n">
+        <v>5245</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28560,6 +28948,9 @@
       <c r="CR12" t="n">
         <v>5335</v>
       </c>
+      <c r="CS12" t="n">
+        <v>5560</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28854,6 +29245,9 @@
       <c r="CR13" t="n">
         <v>5355</v>
       </c>
+      <c r="CS13" t="n">
+        <v>5590</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29148,6 +29542,9 @@
       <c r="CR14" t="n">
         <v>1367</v>
       </c>
+      <c r="CS14" t="n">
+        <v>1495</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -29442,6 +29839,9 @@
       <c r="CR15" t="n">
         <v>19135</v>
       </c>
+      <c r="CS15" t="n">
+        <v>19190</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -29736,6 +30136,9 @@
       <c r="CR16" t="n">
         <v>10220</v>
       </c>
+      <c r="CS16" t="n">
+        <v>10720</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -30030,6 +30433,9 @@
       <c r="CR17" t="n">
         <v>5900</v>
       </c>
+      <c r="CS17" t="n">
+        <v>6160</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -30324,6 +30730,9 @@
       <c r="CR18" t="n">
         <v>20055</v>
       </c>
+      <c r="CS18" t="n">
+        <v>19390</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -30617,6 +31026,9 @@
       </c>
       <c r="CR19" t="n">
         <v>15895</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>15980</v>
       </c>
     </row>
   </sheetData>
@@ -30630,7 +31042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR19"/>
+  <dimension ref="A1:CS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -30729,6 +31141,7 @@
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
+    <col width="12" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31024,6 +31437,9 @@
       <c r="CR1" s="1" t="n">
         <v>20260119</v>
       </c>
+      <c r="CS1" s="1" t="n">
+        <v>20260120</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31318,6 +31734,9 @@
       <c r="CR2" t="n">
         <v>15070</v>
       </c>
+      <c r="CS2" t="n">
+        <v>14955</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31612,6 +32031,9 @@
       <c r="CR3" t="n">
         <v>72310</v>
       </c>
+      <c r="CS3" t="n">
+        <v>70500</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -31906,6 +32328,9 @@
       <c r="CR4" t="n">
         <v>18255</v>
       </c>
+      <c r="CS4" t="n">
+        <v>18215</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32200,6 +32625,9 @@
       <c r="CR5" t="n">
         <v>17435</v>
       </c>
+      <c r="CS5" t="n">
+        <v>16900</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32494,6 +32922,9 @@
       <c r="CR6" t="n">
         <v>20805</v>
       </c>
+      <c r="CS6" t="n">
+        <v>20305</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -32788,6 +33219,9 @@
       <c r="CR7" t="n">
         <v>24850</v>
       </c>
+      <c r="CS7" t="n">
+        <v>24230</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -33082,6 +33516,9 @@
       <c r="CR8" t="n">
         <v>24205</v>
       </c>
+      <c r="CS8" t="n">
+        <v>23680</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33376,6 +33813,9 @@
       <c r="CR9" t="n">
         <v>1443</v>
       </c>
+      <c r="CS9" t="n">
+        <v>1496</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -33670,6 +34110,9 @@
       <c r="CR10" t="n">
         <v>18760</v>
       </c>
+      <c r="CS10" t="n">
+        <v>18375</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -33964,6 +34407,9 @@
       <c r="CR11" t="n">
         <v>5270</v>
       </c>
+      <c r="CS11" t="n">
+        <v>5390</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -34258,6 +34704,9 @@
       <c r="CR12" t="n">
         <v>5600</v>
       </c>
+      <c r="CS12" t="n">
+        <v>5740</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34552,6 +35001,9 @@
       <c r="CR13" t="n">
         <v>5600</v>
       </c>
+      <c r="CS13" t="n">
+        <v>5770</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34846,6 +35298,9 @@
       <c r="CR14" t="n">
         <v>1500</v>
       </c>
+      <c r="CS14" t="n">
+        <v>1562</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35140,6 +35595,9 @@
       <c r="CR15" t="n">
         <v>19360</v>
       </c>
+      <c r="CS15" t="n">
+        <v>19190</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -35434,6 +35892,9 @@
       <c r="CR16" t="n">
         <v>10720</v>
       </c>
+      <c r="CS16" t="n">
+        <v>11055</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -35728,6 +36189,9 @@
       <c r="CR17" t="n">
         <v>6195</v>
       </c>
+      <c r="CS17" t="n">
+        <v>6370</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36022,6 +36486,9 @@
       <c r="CR18" t="n">
         <v>20275</v>
       </c>
+      <c r="CS18" t="n">
+        <v>19680</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -36315,6 +36782,9 @@
       </c>
       <c r="CR19" t="n">
         <v>16000</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>16030</v>
       </c>
     </row>
   </sheetData>
@@ -36328,7 +36798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR19"/>
+  <dimension ref="A1:CS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -36427,6 +36897,7 @@
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
+    <col width="12" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36722,6 +37193,9 @@
       <c r="CR1" s="1" t="n">
         <v>20260119</v>
       </c>
+      <c r="CS1" s="1" t="n">
+        <v>20260120</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37016,6 +37490,9 @@
       <c r="CR2" t="n">
         <v>338526</v>
       </c>
+      <c r="CS2" t="n">
+        <v>283210</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37310,6 +37787,9 @@
       <c r="CR3" t="n">
         <v>1831907</v>
       </c>
+      <c r="CS3" t="n">
+        <v>2145929</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -37604,6 +38084,9 @@
       <c r="CR4" t="n">
         <v>179883</v>
       </c>
+      <c r="CS4" t="n">
+        <v>368285</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -37898,6 +38381,9 @@
       <c r="CR5" t="n">
         <v>232471</v>
       </c>
+      <c r="CS5" t="n">
+        <v>321999</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -38192,6 +38678,9 @@
       <c r="CR6" t="n">
         <v>4333889</v>
       </c>
+      <c r="CS6" t="n">
+        <v>3512377</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -38486,6 +38975,9 @@
       <c r="CR7" t="n">
         <v>4115001</v>
       </c>
+      <c r="CS7" t="n">
+        <v>4680211</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -38780,6 +39272,9 @@
       <c r="CR8" t="n">
         <v>15181103</v>
       </c>
+      <c r="CS8" t="n">
+        <v>13561111</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -39074,6 +39569,9 @@
       <c r="CR9" t="n">
         <v>9572667</v>
       </c>
+      <c r="CS9" t="n">
+        <v>13997816</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -39368,6 +39866,9 @@
       <c r="CR10" t="n">
         <v>1506760</v>
       </c>
+      <c r="CS10" t="n">
+        <v>1081281</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -39662,6 +40163,9 @@
       <c r="CR11" t="n">
         <v>1101136</v>
       </c>
+      <c r="CS11" t="n">
+        <v>1432342</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -39956,6 +40460,9 @@
       <c r="CR12" t="n">
         <v>3417073</v>
       </c>
+      <c r="CS12" t="n">
+        <v>4774538</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -40250,6 +40757,9 @@
       <c r="CR13" t="n">
         <v>6814571</v>
       </c>
+      <c r="CS13" t="n">
+        <v>10737167</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -40544,6 +41054,9 @@
       <c r="CR14" t="n">
         <v>58003650</v>
       </c>
+      <c r="CS14" t="n">
+        <v>82431730</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -40838,6 +41351,9 @@
       <c r="CR15" t="n">
         <v>1653607</v>
       </c>
+      <c r="CS15" t="n">
+        <v>3009733</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -41132,6 +41648,9 @@
       <c r="CR16" t="n">
         <v>410296</v>
       </c>
+      <c r="CS16" t="n">
+        <v>1257726</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41426,6 +41945,9 @@
       <c r="CR17" t="n">
         <v>100107</v>
       </c>
+      <c r="CS17" t="n">
+        <v>161207</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41720,6 +42242,9 @@
       <c r="CR18" t="n">
         <v>95057</v>
       </c>
+      <c r="CS18" t="n">
+        <v>96459</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42013,6 +42538,9 @@
       </c>
       <c r="CR19" t="n">
         <v>52946</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>82902</v>
       </c>
     </row>
   </sheetData>
@@ -42026,7 +42554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY19"/>
+  <dimension ref="A1:BZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -42106,6 +42634,7 @@
     <col width="10" customWidth="1" min="75" max="75"/>
     <col width="10" customWidth="1" min="76" max="76"/>
     <col width="10" customWidth="1" min="77" max="77"/>
+    <col width="10" customWidth="1" min="78" max="78"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -42344,6 +42873,9 @@
       <c r="BY1" s="1" t="n">
         <v>20260119</v>
       </c>
+      <c r="BZ1" s="1" t="n">
+        <v>20260120</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -42581,6 +43113,9 @@
       <c r="BY2" t="n">
         <v>34</v>
       </c>
+      <c r="BZ2" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -42818,6 +43353,9 @@
       <c r="BY3" t="n">
         <v>100</v>
       </c>
+      <c r="BZ3" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -43055,6 +43593,9 @@
       <c r="BY4" t="n">
         <v>58</v>
       </c>
+      <c r="BZ4" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -43292,6 +43833,9 @@
       <c r="BY5" t="n">
         <v>90</v>
       </c>
+      <c r="BZ5" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -43529,6 +44073,9 @@
       <c r="BY6" t="n">
         <v>100</v>
       </c>
+      <c r="BZ6" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -43766,6 +44313,9 @@
       <c r="BY7" t="n">
         <v>100</v>
       </c>
+      <c r="BZ7" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -44003,6 +44553,9 @@
       <c r="BY8" t="n">
         <v>100</v>
       </c>
+      <c r="BZ8" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -44240,6 +44793,9 @@
       <c r="BY9" t="n">
         <v>100</v>
       </c>
+      <c r="BZ9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -44477,6 +45033,9 @@
       <c r="BY10" t="n">
         <v>89</v>
       </c>
+      <c r="BZ10" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -44714,6 +45273,9 @@
       <c r="BY11" t="n">
         <v>100</v>
       </c>
+      <c r="BZ11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -44951,6 +45513,9 @@
       <c r="BY12" t="n">
         <v>91</v>
       </c>
+      <c r="BZ12" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -45188,6 +45753,9 @@
       <c r="BY13" t="n">
         <v>88</v>
       </c>
+      <c r="BZ13" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -45425,6 +45993,9 @@
       <c r="BY14" t="n">
         <v>100</v>
       </c>
+      <c r="BZ14" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -45662,6 +46233,9 @@
       <c r="BY15" t="n">
         <v>40</v>
       </c>
+      <c r="BZ15" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -45899,6 +46473,9 @@
       <c r="BY16" t="n">
         <v>100</v>
       </c>
+      <c r="BZ16" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -46136,6 +46713,9 @@
       <c r="BY17" t="n">
         <v>100</v>
       </c>
+      <c r="BZ17" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -46373,6 +46953,9 @@
       <c r="BY18" t="n">
         <v>92</v>
       </c>
+      <c r="BZ18" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -46609,6 +47192,9 @@
       </c>
       <c r="BY19" t="n">
         <v>26</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -46622,7 +47208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK19"/>
+  <dimension ref="A1:AL19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -46662,6 +47248,7 @@
     <col width="10" customWidth="1" min="35" max="35"/>
     <col width="10" customWidth="1" min="36" max="36"/>
     <col width="10" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -46780,6 +47367,9 @@
       <c r="AK1" s="1" t="n">
         <v>20260119</v>
       </c>
+      <c r="AL1" s="1" t="n">
+        <v>20260120</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -46897,6 +47487,9 @@
       <c r="AK2" t="n">
         <v>57</v>
       </c>
+      <c r="AL2" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -47014,6 +47607,9 @@
       <c r="AK3" t="n">
         <v>100</v>
       </c>
+      <c r="AL3" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -47131,6 +47727,9 @@
       <c r="AK4" t="n">
         <v>69</v>
       </c>
+      <c r="AL4" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -47248,6 +47847,9 @@
       <c r="AK5" t="n">
         <v>91</v>
       </c>
+      <c r="AL5" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -47365,6 +47967,9 @@
       <c r="AK6" t="n">
         <v>100</v>
       </c>
+      <c r="AL6" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -47482,6 +48087,9 @@
       <c r="AK7" t="n">
         <v>100</v>
       </c>
+      <c r="AL7" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -47599,6 +48207,9 @@
       <c r="AK8" t="n">
         <v>100</v>
       </c>
+      <c r="AL8" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -47716,6 +48327,9 @@
       <c r="AK9" t="n">
         <v>34</v>
       </c>
+      <c r="AL9" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -47833,6 +48447,9 @@
       <c r="AK10" t="n">
         <v>89</v>
       </c>
+      <c r="AL10" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -47950,6 +48567,9 @@
       <c r="AK11" t="n">
         <v>50</v>
       </c>
+      <c r="AL11" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -48067,6 +48687,9 @@
       <c r="AK12" t="n">
         <v>46</v>
       </c>
+      <c r="AL12" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -48184,6 +48807,9 @@
       <c r="AK13" t="n">
         <v>45</v>
       </c>
+      <c r="AL13" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -48301,6 +48927,9 @@
       <c r="AK14" t="n">
         <v>31</v>
       </c>
+      <c r="AL14" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -48418,6 +49047,9 @@
       <c r="AK15" t="n">
         <v>81</v>
       </c>
+      <c r="AL15" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -48535,6 +49167,9 @@
       <c r="AK16" t="n">
         <v>48</v>
       </c>
+      <c r="AL16" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -48652,6 +49287,9 @@
       <c r="AK17" t="n">
         <v>38</v>
       </c>
+      <c r="AL17" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -48769,6 +49407,9 @@
       <c r="AK18" t="n">
         <v>93</v>
       </c>
+      <c r="AL18" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -48884,6 +49525,9 @@
         <v>84</v>
       </c>
       <c r="AK19" t="n">
+        <v>79</v>
+      </c>
+      <c r="AL19" t="n">
         <v>79</v>
       </c>
     </row>
@@ -48898,7 +49542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY19"/>
+  <dimension ref="A1:BZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -48978,6 +49622,7 @@
     <col width="10" customWidth="1" min="75" max="75"/>
     <col width="10" customWidth="1" min="76" max="76"/>
     <col width="10" customWidth="1" min="77" max="77"/>
+    <col width="10" customWidth="1" min="78" max="78"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -49216,6 +49861,9 @@
       <c r="BY1" s="1" t="n">
         <v>20260119</v>
       </c>
+      <c r="BZ1" s="1" t="n">
+        <v>20260120</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -49453,6 +50101,9 @@
       <c r="BY2" t="n">
         <v>-21</v>
       </c>
+      <c r="BZ2" t="n">
+        <v>-33</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -49690,6 +50341,9 @@
       <c r="BY3" t="n">
         <v>58</v>
       </c>
+      <c r="BZ3" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -49927,6 +50581,9 @@
       <c r="BY4" t="n">
         <v>16</v>
       </c>
+      <c r="BZ4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -50164,6 +50821,9 @@
       <c r="BY5" t="n">
         <v>45</v>
       </c>
+      <c r="BZ5" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -50401,6 +51061,9 @@
       <c r="BY6" t="n">
         <v>58</v>
       </c>
+      <c r="BZ6" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -50638,6 +51301,9 @@
       <c r="BY7" t="n">
         <v>60</v>
       </c>
+      <c r="BZ7" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -50875,6 +51541,9 @@
       <c r="BY8" t="n">
         <v>55</v>
       </c>
+      <c r="BZ8" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -51112,6 +51781,9 @@
       <c r="BY9" t="n">
         <v>91</v>
       </c>
+      <c r="BZ9" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -51349,6 +52021,9 @@
       <c r="BY10" t="n">
         <v>48</v>
       </c>
+      <c r="BZ10" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -51586,6 +52261,9 @@
       <c r="BY11" t="n">
         <v>77</v>
       </c>
+      <c r="BZ11" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -51823,6 +52501,9 @@
       <c r="BY12" t="n">
         <v>64</v>
       </c>
+      <c r="BZ12" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -52060,6 +52741,9 @@
       <c r="BY13" t="n">
         <v>52</v>
       </c>
+      <c r="BZ13" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -52297,6 +52981,9 @@
       <c r="BY14" t="n">
         <v>79</v>
       </c>
+      <c r="BZ14" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -52534,6 +53221,9 @@
       <c r="BY15" t="n">
         <v>-8</v>
       </c>
+      <c r="BZ15" t="n">
+        <v>-27</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -52771,6 +53461,9 @@
       <c r="BY16" t="n">
         <v>88</v>
       </c>
+      <c r="BZ16" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -53008,6 +53701,9 @@
       <c r="BY17" t="n">
         <v>74</v>
       </c>
+      <c r="BZ17" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -53245,6 +53941,9 @@
       <c r="BY18" t="n">
         <v>48</v>
       </c>
+      <c r="BZ18" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -53481,6 +54180,9 @@
       </c>
       <c r="BY19" t="n">
         <v>-18</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>-16</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL19"/>
+  <dimension ref="A1:AM19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -750,6 +750,7 @@
     <col width="10" customWidth="1" min="36" max="36"/>
     <col width="10" customWidth="1" min="37" max="37"/>
     <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -871,6 +872,9 @@
       <c r="AL1" s="1" t="n">
         <v>20260120</v>
       </c>
+      <c r="AM1" s="1" t="n">
+        <v>20260121</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -991,6 +995,9 @@
       <c r="AL2" t="n">
         <v>-21</v>
       </c>
+      <c r="AM2" t="n">
+        <v>-112</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1111,6 +1118,9 @@
       <c r="AL3" t="n">
         <v>93</v>
       </c>
+      <c r="AM3" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1231,6 +1241,9 @@
       <c r="AL4" t="n">
         <v>12</v>
       </c>
+      <c r="AM4" t="n">
+        <v>-93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1351,6 +1364,9 @@
       <c r="AL5" t="n">
         <v>39</v>
       </c>
+      <c r="AM5" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1471,6 +1487,9 @@
       <c r="AL6" t="n">
         <v>93</v>
       </c>
+      <c r="AM6" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1591,6 +1610,9 @@
       <c r="AL7" t="n">
         <v>96</v>
       </c>
+      <c r="AM7" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1711,6 +1733,9 @@
       <c r="AL8" t="n">
         <v>96</v>
       </c>
+      <c r="AM8" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1831,6 +1856,9 @@
       <c r="AL9" t="n">
         <v>-4</v>
       </c>
+      <c r="AM9" t="n">
+        <v>-17</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1951,6 +1979,9 @@
       <c r="AL10" t="n">
         <v>65</v>
       </c>
+      <c r="AM10" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2071,6 +2102,9 @@
       <c r="AL11" t="n">
         <v>25</v>
       </c>
+      <c r="AM11" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2191,6 +2225,9 @@
       <c r="AL12" t="n">
         <v>13</v>
       </c>
+      <c r="AM12" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2311,6 +2348,9 @@
       <c r="AL13" t="n">
         <v>20</v>
       </c>
+      <c r="AM13" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2431,6 +2471,9 @@
       <c r="AL14" t="n">
         <v>-12</v>
       </c>
+      <c r="AM14" t="n">
+        <v>-23</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2551,6 +2594,9 @@
       <c r="AL15" t="n">
         <v>18</v>
       </c>
+      <c r="AM15" t="n">
+        <v>-44</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2671,6 +2717,9 @@
       <c r="AL16" t="n">
         <v>24</v>
       </c>
+      <c r="AM16" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2791,6 +2840,9 @@
       <c r="AL17" t="n">
         <v>1</v>
       </c>
+      <c r="AM17" t="n">
+        <v>-15</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2911,6 +2963,9 @@
       <c r="AL18" t="n">
         <v>67</v>
       </c>
+      <c r="AM18" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3030,6 +3085,9 @@
       </c>
       <c r="AL19" t="n">
         <v>23</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-49</v>
       </c>
     </row>
   </sheetData>
@@ -3043,7 +3101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ19"/>
+  <dimension ref="A1:CA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3124,6 +3182,7 @@
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
+    <col width="12" customWidth="1" min="79" max="79"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3517,6 +3576,11 @@
           <t>20260120</t>
         </is>
       </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>20260121</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3757,6 +3821,9 @@
       <c r="BZ2" t="n">
         <v>98</v>
       </c>
+      <c r="CA2" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3997,6 +4064,9 @@
       <c r="BZ3" t="n">
         <v>107</v>
       </c>
+      <c r="CA3" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4237,6 +4307,9 @@
       <c r="BZ4" t="n">
         <v>100</v>
       </c>
+      <c r="CA4" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4477,6 +4550,9 @@
       <c r="BZ5" t="n">
         <v>101</v>
       </c>
+      <c r="CA5" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4717,6 +4793,9 @@
       <c r="BZ6" t="n">
         <v>106</v>
       </c>
+      <c r="CA6" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4957,6 +5036,9 @@
       <c r="BZ7" t="n">
         <v>107</v>
       </c>
+      <c r="CA7" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5197,6 +5279,9 @@
       <c r="BZ8" t="n">
         <v>108</v>
       </c>
+      <c r="CA8" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5437,6 +5522,9 @@
       <c r="BZ9" t="n">
         <v>115</v>
       </c>
+      <c r="CA9" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5677,6 +5765,9 @@
       <c r="BZ10" t="n">
         <v>103</v>
       </c>
+      <c r="CA10" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5917,6 +6008,9 @@
       <c r="BZ11" t="n">
         <v>107</v>
       </c>
+      <c r="CA11" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6157,6 +6251,9 @@
       <c r="BZ12" t="n">
         <v>107</v>
       </c>
+      <c r="CA12" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6397,6 +6494,9 @@
       <c r="BZ13" t="n">
         <v>106</v>
       </c>
+      <c r="CA13" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6637,6 +6737,9 @@
       <c r="BZ14" t="n">
         <v>113</v>
       </c>
+      <c r="CA14" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6877,6 +6980,9 @@
       <c r="BZ15" t="n">
         <v>98</v>
       </c>
+      <c r="CA15" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7117,6 +7223,9 @@
       <c r="BZ16" t="n">
         <v>108</v>
       </c>
+      <c r="CA16" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7357,6 +7466,9 @@
       <c r="BZ17" t="n">
         <v>107</v>
       </c>
+      <c r="CA17" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7597,6 +7709,9 @@
       <c r="BZ18" t="n">
         <v>103</v>
       </c>
+      <c r="CA18" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7836,6 +7951,9 @@
       </c>
       <c r="BZ19" t="n">
         <v>99</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -7849,7 +7967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG19"/>
+  <dimension ref="A1:BH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7862,6 +7980,7 @@
     <col width="12" customWidth="1" min="57" max="57"/>
     <col width="12" customWidth="1" min="58" max="58"/>
     <col width="12" customWidth="1" min="59" max="59"/>
+    <col width="12" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8062,6 +8181,11 @@
           <t>20260120</t>
         </is>
       </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>20260121</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8245,6 +8369,9 @@
       <c r="BG2" t="n">
         <v>-0.54</v>
       </c>
+      <c r="BH2" t="n">
+        <v>20.67</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8428,6 +8555,9 @@
       <c r="BG3" t="n">
         <v>46.33</v>
       </c>
+      <c r="BH3" t="n">
+        <v>27.56</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8611,6 +8741,9 @@
       <c r="BG4" t="n">
         <v>-9.4</v>
       </c>
+      <c r="BH4" t="n">
+        <v>8.470000000000001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8794,6 +8927,9 @@
       <c r="BG5" t="n">
         <v>17.42</v>
       </c>
+      <c r="BH5" t="n">
+        <v>0.83</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8977,6 +9113,9 @@
       <c r="BG6" t="n">
         <v>44.92</v>
       </c>
+      <c r="BH6" t="n">
+        <v>26.47</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9160,6 +9299,9 @@
       <c r="BG7" t="n">
         <v>50.94</v>
       </c>
+      <c r="BH7" t="n">
+        <v>32.95</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9343,6 +9485,9 @@
       <c r="BG8" t="n">
         <v>47.82</v>
       </c>
+      <c r="BH8" t="n">
+        <v>29.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9526,6 +9671,9 @@
       <c r="BG9" t="n">
         <v>-26.01</v>
       </c>
+      <c r="BH9" t="n">
+        <v>-22.04</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9709,6 +9857,9 @@
       <c r="BG10" t="n">
         <v>26.12</v>
       </c>
+      <c r="BH10" t="n">
+        <v>11.2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9892,6 +10043,9 @@
       <c r="BG11" t="n">
         <v>-29.99</v>
       </c>
+      <c r="BH11" t="n">
+        <v>-24.6</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10075,6 +10229,9 @@
       <c r="BG12" t="n">
         <v>-35.21</v>
       </c>
+      <c r="BH12" t="n">
+        <v>-31.6</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10258,6 +10415,9 @@
       <c r="BG13" t="n">
         <v>-40.18</v>
       </c>
+      <c r="BH13" t="n">
+        <v>-35.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10441,6 +10601,9 @@
       <c r="BG14" t="n">
         <v>-38.74</v>
       </c>
+      <c r="BH14" t="n">
+        <v>-34.99</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10624,6 +10787,9 @@
       <c r="BG15" t="n">
         <v>-3.18</v>
       </c>
+      <c r="BH15" t="n">
+        <v>24.7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10807,6 +10973,9 @@
       <c r="BG16" t="n">
         <v>-27.29</v>
       </c>
+      <c r="BH16" t="n">
+        <v>-20.91</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10990,6 +11159,9 @@
       <c r="BG17" t="n">
         <v>-36.38</v>
       </c>
+      <c r="BH17" t="n">
+        <v>-32.54</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11173,6 +11345,9 @@
       <c r="BG18" t="n">
         <v>25.76</v>
       </c>
+      <c r="BH18" t="n">
+        <v>9.99</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11355,6 +11530,9 @@
       </c>
       <c r="BG19" t="n">
         <v>2.12</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>41.94</v>
       </c>
     </row>
   </sheetData>
@@ -11368,7 +11546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL19"/>
+  <dimension ref="A1:AM19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11409,6 +11587,7 @@
     <col width="12" customWidth="1" min="36" max="36"/>
     <col width="12" customWidth="1" min="37" max="37"/>
     <col width="12" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11602,6 +11781,11 @@
           <t>20260120</t>
         </is>
       </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>20260121</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11722,6 +11906,9 @@
       <c r="AL2" t="n">
         <v>81</v>
       </c>
+      <c r="AM2" t="n">
+        <v>280</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11842,6 +12029,9 @@
       <c r="AL3" t="n">
         <v>46</v>
       </c>
+      <c r="AM3" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11962,6 +12152,9 @@
       <c r="AL4" t="n">
         <v>95</v>
       </c>
+      <c r="AM4" t="n">
+        <v>260</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12082,6 +12275,9 @@
       <c r="AL5" t="n">
         <v>35</v>
       </c>
+      <c r="AM5" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12202,6 +12398,9 @@
       <c r="AL6" t="n">
         <v>64</v>
       </c>
+      <c r="AM6" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12322,6 +12521,9 @@
       <c r="AL7" t="n">
         <v>59</v>
       </c>
+      <c r="AM7" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12442,6 +12644,9 @@
       <c r="AL8" t="n">
         <v>79</v>
       </c>
+      <c r="AM8" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12562,6 +12767,9 @@
       <c r="AL9" t="n">
         <v>99</v>
       </c>
+      <c r="AM9" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12682,6 +12890,9 @@
       <c r="AL10" t="n">
         <v>44</v>
       </c>
+      <c r="AM10" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12802,6 +13013,9 @@
       <c r="AL11" t="n">
         <v>62</v>
       </c>
+      <c r="AM11" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12922,6 +13136,9 @@
       <c r="AL12" t="n">
         <v>91</v>
       </c>
+      <c r="AM12" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13042,6 +13259,9 @@
       <c r="AL13" t="n">
         <v>85</v>
       </c>
+      <c r="AM13" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13162,6 +13382,9 @@
       <c r="AL14" t="n">
         <v>88</v>
       </c>
+      <c r="AM14" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13282,6 +13505,9 @@
       <c r="AL15" t="n">
         <v>77</v>
       </c>
+      <c r="AM15" t="n">
+        <v>191</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13402,6 +13628,9 @@
       <c r="AL16" t="n">
         <v>118</v>
       </c>
+      <c r="AM16" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13522,6 +13751,9 @@
       <c r="AL17" t="n">
         <v>49</v>
       </c>
+      <c r="AM17" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13642,6 +13874,9 @@
       <c r="AL18" t="n">
         <v>28</v>
       </c>
+      <c r="AM18" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13761,6 +13996,9 @@
       </c>
       <c r="AL19" t="n">
         <v>77</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -13774,7 +14012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS19"/>
+  <dimension ref="A1:CT19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13874,6 +14112,7 @@
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
+    <col width="12" customWidth="1" min="98" max="98"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14172,6 +14411,9 @@
       <c r="CS1" s="1" t="n">
         <v>20260120</v>
       </c>
+      <c r="CT1" s="1" t="n">
+        <v>20260121</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14469,6 +14711,9 @@
       <c r="CS2" t="n">
         <v>15090</v>
       </c>
+      <c r="CT2" t="n">
+        <v>14495</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14766,6 +15011,9 @@
       <c r="CS3" t="n">
         <v>72035</v>
       </c>
+      <c r="CT3" t="n">
+        <v>69000</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15063,6 +15311,9 @@
       <c r="CS4" t="n">
         <v>18260</v>
       </c>
+      <c r="CT4" t="n">
+        <v>17815</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15360,6 +15611,9 @@
       <c r="CS5" t="n">
         <v>17240</v>
       </c>
+      <c r="CT5" t="n">
+        <v>16335</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15657,6 +15911,9 @@
       <c r="CS6" t="n">
         <v>20745</v>
       </c>
+      <c r="CT6" t="n">
+        <v>19905</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15954,6 +16211,9 @@
       <c r="CS7" t="n">
         <v>24795</v>
       </c>
+      <c r="CT7" t="n">
+        <v>23670</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16251,6 +16511,9 @@
       <c r="CS8" t="n">
         <v>24205</v>
       </c>
+      <c r="CT8" t="n">
+        <v>23130</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16548,6 +16811,9 @@
       <c r="CS9" t="n">
         <v>1451</v>
       </c>
+      <c r="CT9" t="n">
+        <v>1405</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16845,6 +17111,9 @@
       <c r="CS10" t="n">
         <v>18665</v>
       </c>
+      <c r="CT10" t="n">
+        <v>17840</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17142,6 +17411,9 @@
       <c r="CS11" t="n">
         <v>5275</v>
       </c>
+      <c r="CT11" t="n">
+        <v>5285</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17439,6 +17711,9 @@
       <c r="CS12" t="n">
         <v>5605</v>
       </c>
+      <c r="CT12" t="n">
+        <v>5610</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17736,6 +18011,9 @@
       <c r="CS13" t="n">
         <v>5635</v>
       </c>
+      <c r="CT13" t="n">
+        <v>5670</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18033,6 +18311,9 @@
       <c r="CS14" t="n">
         <v>1499</v>
       </c>
+      <c r="CT14" t="n">
+        <v>1494</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18330,6 +18611,9 @@
       <c r="CS15" t="n">
         <v>19525</v>
       </c>
+      <c r="CT15" t="n">
+        <v>18845</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -18627,6 +18911,9 @@
       <c r="CS16" t="n">
         <v>10775</v>
       </c>
+      <c r="CT16" t="n">
+        <v>10805</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -18924,6 +19211,9 @@
       <c r="CS17" t="n">
         <v>6225</v>
       </c>
+      <c r="CT17" t="n">
+        <v>6190</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -19221,6 +19511,9 @@
       <c r="CS18" t="n">
         <v>20140</v>
       </c>
+      <c r="CT18" t="n">
+        <v>19050</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -19517,6 +19810,9 @@
       </c>
       <c r="CS19" t="n">
         <v>16115</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>15600</v>
       </c>
     </row>
   </sheetData>
@@ -19530,7 +19826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS19"/>
+  <dimension ref="A1:CT19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19630,6 +19926,7 @@
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
+    <col width="12" customWidth="1" min="98" max="98"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19928,6 +20225,9 @@
       <c r="CS1" s="1" t="n">
         <v>20260120</v>
       </c>
+      <c r="CT1" s="1" t="n">
+        <v>20260121</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20225,6 +20525,9 @@
       <c r="CS2" t="n">
         <v>15435</v>
       </c>
+      <c r="CT2" t="n">
+        <v>14600</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20522,6 +20825,9 @@
       <c r="CS3" t="n">
         <v>72095</v>
       </c>
+      <c r="CT3" t="n">
+        <v>71150</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20819,6 +21125,9 @@
       <c r="CS4" t="n">
         <v>18745</v>
       </c>
+      <c r="CT4" t="n">
+        <v>17875</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21116,6 +21425,9 @@
       <c r="CS5" t="n">
         <v>17250</v>
       </c>
+      <c r="CT5" t="n">
+        <v>16765</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21413,6 +21725,9 @@
       <c r="CS6" t="n">
         <v>20745</v>
       </c>
+      <c r="CT6" t="n">
+        <v>20425</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21710,6 +22025,9 @@
       <c r="CS7" t="n">
         <v>24795</v>
       </c>
+      <c r="CT7" t="n">
+        <v>24520</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22007,6 +22325,9 @@
       <c r="CS8" t="n">
         <v>24205</v>
       </c>
+      <c r="CT8" t="n">
+        <v>23980</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22304,6 +22625,9 @@
       <c r="CS9" t="n">
         <v>1538</v>
       </c>
+      <c r="CT9" t="n">
+        <v>1458</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22601,6 +22925,9 @@
       <c r="CS10" t="n">
         <v>18695</v>
       </c>
+      <c r="CT10" t="n">
+        <v>18240</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22898,6 +23225,9 @@
       <c r="CS11" t="n">
         <v>5485</v>
       </c>
+      <c r="CT11" t="n">
+        <v>5335</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -23195,6 +23525,9 @@
       <c r="CS12" t="n">
         <v>5840</v>
       </c>
+      <c r="CT12" t="n">
+        <v>5680</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -23492,6 +23825,9 @@
       <c r="CS13" t="n">
         <v>5895</v>
       </c>
+      <c r="CT13" t="n">
+        <v>5730</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -23789,6 +24125,9 @@
       <c r="CS14" t="n">
         <v>1624</v>
       </c>
+      <c r="CT14" t="n">
+        <v>1519</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24086,6 +24425,9 @@
       <c r="CS15" t="n">
         <v>19945</v>
       </c>
+      <c r="CT15" t="n">
+        <v>18910</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24383,6 +24725,9 @@
       <c r="CS16" t="n">
         <v>11240</v>
       </c>
+      <c r="CT16" t="n">
+        <v>10900</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24680,6 +25025,9 @@
       <c r="CS17" t="n">
         <v>6480</v>
       </c>
+      <c r="CT17" t="n">
+        <v>6242</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24977,6 +25325,9 @@
       <c r="CS18" t="n">
         <v>20140</v>
       </c>
+      <c r="CT18" t="n">
+        <v>19450</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25273,6 +25624,9 @@
       </c>
       <c r="CS19" t="n">
         <v>16490</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>15665</v>
       </c>
     </row>
   </sheetData>
@@ -25286,7 +25640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS19"/>
+  <dimension ref="A1:CT19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25386,6 +25740,7 @@
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
+    <col width="12" customWidth="1" min="98" max="98"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25684,6 +26039,9 @@
       <c r="CS1" s="1" t="n">
         <v>20260120</v>
       </c>
+      <c r="CT1" s="1" t="n">
+        <v>20260121</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25981,6 +26339,9 @@
       <c r="CS2" t="n">
         <v>14880</v>
       </c>
+      <c r="CT2" t="n">
+        <v>13250</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26278,6 +26639,9 @@
       <c r="CS3" t="n">
         <v>69840</v>
       </c>
+      <c r="CT3" t="n">
+        <v>68805</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26575,6 +26939,9 @@
       <c r="CS4" t="n">
         <v>18160</v>
       </c>
+      <c r="CT4" t="n">
+        <v>16275</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26872,6 +27239,9 @@
       <c r="CS5" t="n">
         <v>16600</v>
       </c>
+      <c r="CT5" t="n">
+        <v>16225</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27169,6 +27539,9 @@
       <c r="CS6" t="n">
         <v>20070</v>
       </c>
+      <c r="CT6" t="n">
+        <v>19870</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27466,6 +27839,9 @@
       <c r="CS7" t="n">
         <v>23985</v>
       </c>
+      <c r="CT7" t="n">
+        <v>23525</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27763,6 +28139,9 @@
       <c r="CS8" t="n">
         <v>23390</v>
       </c>
+      <c r="CT8" t="n">
+        <v>23100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28060,6 +28439,9 @@
       <c r="CS9" t="n">
         <v>1420</v>
       </c>
+      <c r="CT9" t="n">
+        <v>1381</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28357,6 +28739,9 @@
       <c r="CS10" t="n">
         <v>18035</v>
       </c>
+      <c r="CT10" t="n">
+        <v>17685</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28654,6 +29039,9 @@
       <c r="CS11" t="n">
         <v>5245</v>
       </c>
+      <c r="CT11" t="n">
+        <v>5175</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28951,6 +29339,9 @@
       <c r="CS12" t="n">
         <v>5560</v>
       </c>
+      <c r="CT12" t="n">
+        <v>5490</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29248,6 +29639,9 @@
       <c r="CS13" t="n">
         <v>5590</v>
       </c>
+      <c r="CT13" t="n">
+        <v>5545</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29545,6 +29939,9 @@
       <c r="CS14" t="n">
         <v>1495</v>
       </c>
+      <c r="CT14" t="n">
+        <v>1437</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -29842,6 +30239,9 @@
       <c r="CS15" t="n">
         <v>19190</v>
       </c>
+      <c r="CT15" t="n">
+        <v>16965</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -30139,6 +30539,9 @@
       <c r="CS16" t="n">
         <v>10720</v>
       </c>
+      <c r="CT16" t="n">
+        <v>10595</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -30436,6 +30839,9 @@
       <c r="CS17" t="n">
         <v>6160</v>
       </c>
+      <c r="CT17" t="n">
+        <v>6065</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -30733,6 +31139,9 @@
       <c r="CS18" t="n">
         <v>19390</v>
       </c>
+      <c r="CT18" t="n">
+        <v>18740</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -31029,6 +31438,9 @@
       </c>
       <c r="CS19" t="n">
         <v>15980</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>14460</v>
       </c>
     </row>
   </sheetData>
@@ -31042,7 +31454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS19"/>
+  <dimension ref="A1:CT19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31142,6 +31554,7 @@
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
+    <col width="12" customWidth="1" min="98" max="98"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31440,6 +31853,9 @@
       <c r="CS1" s="1" t="n">
         <v>20260120</v>
       </c>
+      <c r="CT1" s="1" t="n">
+        <v>20260121</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31737,6 +32153,9 @@
       <c r="CS2" t="n">
         <v>14955</v>
       </c>
+      <c r="CT2" t="n">
+        <v>13635</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32034,6 +32453,9 @@
       <c r="CS3" t="n">
         <v>70500</v>
       </c>
+      <c r="CT3" t="n">
+        <v>70705</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -32331,6 +32753,9 @@
       <c r="CS4" t="n">
         <v>18215</v>
       </c>
+      <c r="CT4" t="n">
+        <v>16620</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32628,6 +33053,9 @@
       <c r="CS5" t="n">
         <v>16900</v>
       </c>
+      <c r="CT5" t="n">
+        <v>16590</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32925,6 +33353,9 @@
       <c r="CS6" t="n">
         <v>20305</v>
       </c>
+      <c r="CT6" t="n">
+        <v>20410</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -33222,6 +33653,9 @@
       <c r="CS7" t="n">
         <v>24230</v>
       </c>
+      <c r="CT7" t="n">
+        <v>24430</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -33519,6 +33953,9 @@
       <c r="CS8" t="n">
         <v>23680</v>
       </c>
+      <c r="CT8" t="n">
+        <v>23980</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33816,6 +34253,9 @@
       <c r="CS9" t="n">
         <v>1496</v>
       </c>
+      <c r="CT9" t="n">
+        <v>1440</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34113,6 +34553,9 @@
       <c r="CS10" t="n">
         <v>18375</v>
       </c>
+      <c r="CT10" t="n">
+        <v>18215</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -34410,6 +34853,9 @@
       <c r="CS11" t="n">
         <v>5390</v>
       </c>
+      <c r="CT11" t="n">
+        <v>5315</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -34707,6 +35153,9 @@
       <c r="CS12" t="n">
         <v>5740</v>
       </c>
+      <c r="CT12" t="n">
+        <v>5615</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35004,6 +35453,9 @@
       <c r="CS13" t="n">
         <v>5770</v>
       </c>
+      <c r="CT13" t="n">
+        <v>5670</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35301,6 +35753,9 @@
       <c r="CS14" t="n">
         <v>1562</v>
       </c>
+      <c r="CT14" t="n">
+        <v>1508</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35598,6 +36053,9 @@
       <c r="CS15" t="n">
         <v>19190</v>
       </c>
+      <c r="CT15" t="n">
+        <v>17435</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -35895,6 +36353,9 @@
       <c r="CS16" t="n">
         <v>11055</v>
       </c>
+      <c r="CT16" t="n">
+        <v>10870</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36192,6 +36653,9 @@
       <c r="CS17" t="n">
         <v>6370</v>
       </c>
+      <c r="CT17" t="n">
+        <v>6220</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36489,6 +36953,9 @@
       <c r="CS18" t="n">
         <v>19680</v>
       </c>
+      <c r="CT18" t="n">
+        <v>19340</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -36785,6 +37252,9 @@
       </c>
       <c r="CS19" t="n">
         <v>16030</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>14645</v>
       </c>
     </row>
   </sheetData>
@@ -36798,7 +37268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS19"/>
+  <dimension ref="A1:CT19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -36898,6 +37368,7 @@
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
+    <col width="12" customWidth="1" min="98" max="98"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37196,6 +37667,9 @@
       <c r="CS1" s="1" t="n">
         <v>20260120</v>
       </c>
+      <c r="CT1" s="1" t="n">
+        <v>20260121</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37493,6 +37967,9 @@
       <c r="CS2" t="n">
         <v>283210</v>
       </c>
+      <c r="CT2" t="n">
+        <v>1063903</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37790,6 +38267,9 @@
       <c r="CS3" t="n">
         <v>2145929</v>
       </c>
+      <c r="CT3" t="n">
+        <v>2106599</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -38087,6 +38567,9 @@
       <c r="CS4" t="n">
         <v>368285</v>
       </c>
+      <c r="CT4" t="n">
+        <v>1098554</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -38384,6 +38867,9 @@
       <c r="CS5" t="n">
         <v>321999</v>
       </c>
+      <c r="CT5" t="n">
+        <v>368707</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -38681,6 +39167,9 @@
       <c r="CS6" t="n">
         <v>3512377</v>
       </c>
+      <c r="CT6" t="n">
+        <v>4384311</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -38978,6 +39467,9 @@
       <c r="CS7" t="n">
         <v>4680211</v>
       </c>
+      <c r="CT7" t="n">
+        <v>6524093</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -39275,6 +39767,9 @@
       <c r="CS8" t="n">
         <v>13561111</v>
       </c>
+      <c r="CT8" t="n">
+        <v>15729932</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -39572,6 +40067,9 @@
       <c r="CS9" t="n">
         <v>13997816</v>
       </c>
+      <c r="CT9" t="n">
+        <v>8842250</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -39869,6 +40367,9 @@
       <c r="CS10" t="n">
         <v>1081281</v>
       </c>
+      <c r="CT10" t="n">
+        <v>1787264</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -40166,6 +40667,9 @@
       <c r="CS11" t="n">
         <v>1432342</v>
       </c>
+      <c r="CT11" t="n">
+        <v>1464383</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -40463,6 +40967,9 @@
       <c r="CS12" t="n">
         <v>4774538</v>
       </c>
+      <c r="CT12" t="n">
+        <v>3024986</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -40760,6 +41267,9 @@
       <c r="CS13" t="n">
         <v>10737167</v>
       </c>
+      <c r="CT13" t="n">
+        <v>6030311</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -41057,6 +41567,9 @@
       <c r="CS14" t="n">
         <v>82431730</v>
       </c>
+      <c r="CT14" t="n">
+        <v>69552044</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41354,6 +41867,9 @@
       <c r="CS15" t="n">
         <v>3009733</v>
       </c>
+      <c r="CT15" t="n">
+        <v>8007101</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -41651,6 +42167,9 @@
       <c r="CS16" t="n">
         <v>1257726</v>
       </c>
+      <c r="CT16" t="n">
+        <v>594798</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41948,6 +42467,9 @@
       <c r="CS17" t="n">
         <v>161207</v>
       </c>
+      <c r="CT17" t="n">
+        <v>179228</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42245,6 +42767,9 @@
       <c r="CS18" t="n">
         <v>96459</v>
       </c>
+      <c r="CT18" t="n">
+        <v>72571</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42541,6 +43066,9 @@
       </c>
       <c r="CS19" t="n">
         <v>82902</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>236345</v>
       </c>
     </row>
   </sheetData>
@@ -42554,7 +43082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ19"/>
+  <dimension ref="A1:CA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -42635,6 +43163,7 @@
     <col width="10" customWidth="1" min="76" max="76"/>
     <col width="10" customWidth="1" min="77" max="77"/>
     <col width="10" customWidth="1" min="78" max="78"/>
+    <col width="10" customWidth="1" min="79" max="79"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -42876,6 +43405,9 @@
       <c r="BZ1" s="1" t="n">
         <v>20260120</v>
       </c>
+      <c r="CA1" s="1" t="n">
+        <v>20260121</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -43116,6 +43648,9 @@
       <c r="BZ2" t="n">
         <v>28</v>
       </c>
+      <c r="CA2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -43356,6 +43891,9 @@
       <c r="BZ3" t="n">
         <v>89</v>
       </c>
+      <c r="CA3" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -43596,6 +44134,9 @@
       <c r="BZ4" t="n">
         <v>55</v>
       </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -43836,6 +44377,9 @@
       <c r="BZ5" t="n">
         <v>70</v>
       </c>
+      <c r="CA5" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -44076,6 +44620,9 @@
       <c r="BZ6" t="n">
         <v>89</v>
       </c>
+      <c r="CA6" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -44316,6 +44863,9 @@
       <c r="BZ7" t="n">
         <v>89</v>
       </c>
+      <c r="CA7" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -44556,6 +45106,9 @@
       <c r="BZ8" t="n">
         <v>92</v>
       </c>
+      <c r="CA8" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -44796,6 +45349,9 @@
       <c r="BZ9" t="n">
         <v>100</v>
       </c>
+      <c r="CA9" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -45036,6 +45592,9 @@
       <c r="BZ10" t="n">
         <v>77</v>
       </c>
+      <c r="CA10" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -45276,6 +45835,9 @@
       <c r="BZ11" t="n">
         <v>100</v>
       </c>
+      <c r="CA11" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -45516,6 +46078,9 @@
       <c r="BZ12" t="n">
         <v>100</v>
       </c>
+      <c r="CA12" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -45756,6 +46321,9 @@
       <c r="BZ13" t="n">
         <v>100</v>
       </c>
+      <c r="CA13" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -45996,6 +46564,9 @@
       <c r="BZ14" t="n">
         <v>100</v>
       </c>
+      <c r="CA14" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -46236,6 +46807,9 @@
       <c r="BZ15" t="n">
         <v>31</v>
       </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -46476,6 +47050,9 @@
       <c r="BZ16" t="n">
         <v>100</v>
       </c>
+      <c r="CA16" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -46716,6 +47293,9 @@
       <c r="BZ17" t="n">
         <v>100</v>
       </c>
+      <c r="CA17" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -46956,6 +47536,9 @@
       <c r="BZ18" t="n">
         <v>76</v>
       </c>
+      <c r="CA18" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -47195,6 +47778,9 @@
       </c>
       <c r="BZ19" t="n">
         <v>28</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -47208,7 +47794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL19"/>
+  <dimension ref="A1:AM19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -47249,6 +47835,7 @@
     <col width="10" customWidth="1" min="36" max="36"/>
     <col width="10" customWidth="1" min="37" max="37"/>
     <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -47370,6 +47957,9 @@
       <c r="AL1" s="1" t="n">
         <v>20260120</v>
       </c>
+      <c r="AM1" s="1" t="n">
+        <v>20260121</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -47490,6 +48080,9 @@
       <c r="AL2" t="n">
         <v>53</v>
       </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -47610,6 +48203,9 @@
       <c r="AL3" t="n">
         <v>91</v>
       </c>
+      <c r="AM3" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -47730,6 +48326,9 @@
       <c r="AL4" t="n">
         <v>68</v>
       </c>
+      <c r="AM4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -47850,6 +48449,9 @@
       <c r="AL5" t="n">
         <v>73</v>
       </c>
+      <c r="AM5" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -47970,6 +48572,9 @@
       <c r="AL6" t="n">
         <v>91</v>
       </c>
+      <c r="AM6" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -48090,6 +48695,9 @@
       <c r="AL7" t="n">
         <v>92</v>
       </c>
+      <c r="AM7" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -48210,6 +48818,9 @@
       <c r="AL8" t="n">
         <v>93</v>
       </c>
+      <c r="AM8" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -48330,6 +48941,9 @@
       <c r="AL9" t="n">
         <v>40</v>
       </c>
+      <c r="AM9" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -48450,6 +49064,9 @@
       <c r="AL10" t="n">
         <v>77</v>
       </c>
+      <c r="AM10" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -48570,6 +49187,9 @@
       <c r="AL11" t="n">
         <v>62</v>
       </c>
+      <c r="AM11" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -48690,6 +49310,9 @@
       <c r="AL12" t="n">
         <v>57</v>
       </c>
+      <c r="AM12" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -48810,6 +49433,9 @@
       <c r="AL13" t="n">
         <v>57</v>
       </c>
+      <c r="AM13" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -48930,6 +49556,9 @@
       <c r="AL14" t="n">
         <v>38</v>
       </c>
+      <c r="AM14" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -49050,6 +49679,9 @@
       <c r="AL15" t="n">
         <v>78</v>
       </c>
+      <c r="AM15" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -49170,6 +49802,9 @@
       <c r="AL16" t="n">
         <v>62</v>
       </c>
+      <c r="AM16" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -49290,6 +49925,9 @@
       <c r="AL17" t="n">
         <v>48</v>
       </c>
+      <c r="AM17" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -49410,6 +50048,9 @@
       <c r="AL18" t="n">
         <v>78</v>
       </c>
+      <c r="AM18" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -49529,6 +50170,9 @@
       </c>
       <c r="AL19" t="n">
         <v>79</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -49542,7 +50186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ19"/>
+  <dimension ref="A1:CA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -49623,6 +50267,7 @@
     <col width="10" customWidth="1" min="76" max="76"/>
     <col width="10" customWidth="1" min="77" max="77"/>
     <col width="10" customWidth="1" min="78" max="78"/>
+    <col width="10" customWidth="1" min="79" max="79"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -49864,6 +50509,9 @@
       <c r="BZ1" s="1" t="n">
         <v>20260120</v>
       </c>
+      <c r="CA1" s="1" t="n">
+        <v>20260121</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -50104,6 +50752,9 @@
       <c r="BZ2" t="n">
         <v>-33</v>
       </c>
+      <c r="CA2" t="n">
+        <v>-124</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -50344,6 +50995,9 @@
       <c r="BZ3" t="n">
         <v>39</v>
       </c>
+      <c r="CA3" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -50584,6 +51238,9 @@
       <c r="BZ4" t="n">
         <v>9</v>
       </c>
+      <c r="CA4" t="n">
+        <v>-120</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -50824,6 +51481,9 @@
       <c r="BZ5" t="n">
         <v>11</v>
       </c>
+      <c r="CA5" t="n">
+        <v>-15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -51064,6 +51724,9 @@
       <c r="BZ6" t="n">
         <v>39</v>
       </c>
+      <c r="CA6" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -51304,6 +51967,9 @@
       <c r="BZ7" t="n">
         <v>41</v>
       </c>
+      <c r="CA7" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -51544,6 +52210,9 @@
       <c r="BZ8" t="n">
         <v>40</v>
       </c>
+      <c r="CA8" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -51784,6 +52453,9 @@
       <c r="BZ9" t="n">
         <v>103</v>
       </c>
+      <c r="CA9" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -52024,6 +52696,9 @@
       <c r="BZ10" t="n">
         <v>27</v>
       </c>
+      <c r="CA10" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -52264,6 +52939,9 @@
       <c r="BZ11" t="n">
         <v>97</v>
       </c>
+      <c r="CA11" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -52504,6 +53182,9 @@
       <c r="BZ12" t="n">
         <v>89</v>
       </c>
+      <c r="CA12" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -52744,6 +53425,9 @@
       <c r="BZ13" t="n">
         <v>88</v>
       </c>
+      <c r="CA13" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -52984,6 +53668,9 @@
       <c r="BZ14" t="n">
         <v>99</v>
       </c>
+      <c r="CA14" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -53224,6 +53911,9 @@
       <c r="BZ15" t="n">
         <v>-27</v>
       </c>
+      <c r="CA15" t="n">
+        <v>-138</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -53464,6 +54154,9 @@
       <c r="BZ16" t="n">
         <v>113</v>
       </c>
+      <c r="CA16" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -53704,6 +54397,9 @@
       <c r="BZ17" t="n">
         <v>103</v>
       </c>
+      <c r="CA17" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -53944,6 +54640,9 @@
       <c r="BZ18" t="n">
         <v>22</v>
       </c>
+      <c r="CA18" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -54183,6 +54882,9 @@
       </c>
       <c r="BZ19" t="n">
         <v>-16</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>-149</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM19"/>
+  <dimension ref="A1:AN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -751,6 +751,7 @@
     <col width="10" customWidth="1" min="37" max="37"/>
     <col width="10" customWidth="1" min="38" max="38"/>
     <col width="10" customWidth="1" min="39" max="39"/>
+    <col width="10" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -875,6 +876,9 @@
       <c r="AM1" s="1" t="n">
         <v>20260121</v>
       </c>
+      <c r="AN1" s="1" t="n">
+        <v>20260122</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -998,6 +1002,9 @@
       <c r="AM2" t="n">
         <v>-112</v>
       </c>
+      <c r="AN2" t="n">
+        <v>-91</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1121,6 +1128,9 @@
       <c r="AM3" t="n">
         <v>91</v>
       </c>
+      <c r="AN3" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1244,6 +1254,9 @@
       <c r="AM4" t="n">
         <v>-93</v>
       </c>
+      <c r="AN4" t="n">
+        <v>-58</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1367,6 +1380,9 @@
       <c r="AM5" t="n">
         <v>17</v>
       </c>
+      <c r="AN5" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1490,6 +1506,9 @@
       <c r="AM6" t="n">
         <v>92</v>
       </c>
+      <c r="AN6" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1613,6 +1632,9 @@
       <c r="AM7" t="n">
         <v>96</v>
       </c>
+      <c r="AN7" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1736,6 +1758,9 @@
       <c r="AM8" t="n">
         <v>97</v>
       </c>
+      <c r="AN8" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1859,6 +1884,9 @@
       <c r="AM9" t="n">
         <v>-17</v>
       </c>
+      <c r="AN9" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1982,6 +2010,9 @@
       <c r="AM10" t="n">
         <v>53</v>
       </c>
+      <c r="AN10" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2105,6 +2136,9 @@
       <c r="AM11" t="n">
         <v>12</v>
       </c>
+      <c r="AN11" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2228,6 +2262,9 @@
       <c r="AM12" t="n">
         <v>-4</v>
       </c>
+      <c r="AN12" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2351,6 +2388,9 @@
       <c r="AM13" t="n">
         <v>6</v>
       </c>
+      <c r="AN13" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2474,6 +2514,9 @@
       <c r="AM14" t="n">
         <v>-23</v>
       </c>
+      <c r="AN14" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2597,6 +2640,9 @@
       <c r="AM15" t="n">
         <v>-44</v>
       </c>
+      <c r="AN15" t="n">
+        <v>-38</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2720,6 +2766,9 @@
       <c r="AM16" t="n">
         <v>10</v>
       </c>
+      <c r="AN16" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2843,6 +2892,9 @@
       <c r="AM17" t="n">
         <v>-15</v>
       </c>
+      <c r="AN17" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2966,6 +3018,9 @@
       <c r="AM18" t="n">
         <v>50</v>
       </c>
+      <c r="AN18" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3088,6 +3143,9 @@
       </c>
       <c r="AM19" t="n">
         <v>-49</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-41</v>
       </c>
     </row>
   </sheetData>
@@ -3101,7 +3159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA19"/>
+  <dimension ref="A1:CB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3183,6 +3241,7 @@
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
+    <col width="12" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3581,6 +3640,11 @@
           <t>20260121</t>
         </is>
       </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>20260122</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3824,6 +3888,9 @@
       <c r="CA2" t="n">
         <v>90</v>
       </c>
+      <c r="CB2" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4067,6 +4134,9 @@
       <c r="CA3" t="n">
         <v>106</v>
       </c>
+      <c r="CB3" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4310,6 +4380,9 @@
       <c r="CA4" t="n">
         <v>92</v>
       </c>
+      <c r="CB4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4553,6 +4626,9 @@
       <c r="CA5" t="n">
         <v>99</v>
       </c>
+      <c r="CB5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4796,6 +4872,9 @@
       <c r="CA6" t="n">
         <v>106</v>
       </c>
+      <c r="CB6" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5039,6 +5118,9 @@
       <c r="CA7" t="n">
         <v>107</v>
       </c>
+      <c r="CB7" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5282,6 +5364,9 @@
       <c r="CA8" t="n">
         <v>108</v>
       </c>
+      <c r="CB8" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5525,6 +5610,9 @@
       <c r="CA9" t="n">
         <v>110</v>
       </c>
+      <c r="CB9" t="n">
+        <v>123</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5768,6 +5856,9 @@
       <c r="CA10" t="n">
         <v>102</v>
       </c>
+      <c r="CB10" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6011,6 +6102,9 @@
       <c r="CA11" t="n">
         <v>105</v>
       </c>
+      <c r="CB11" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6254,6 +6348,9 @@
       <c r="CA12" t="n">
         <v>104</v>
       </c>
+      <c r="CB12" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6497,6 +6594,9 @@
       <c r="CA13" t="n">
         <v>104</v>
       </c>
+      <c r="CB13" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6740,6 +6840,9 @@
       <c r="CA14" t="n">
         <v>109</v>
       </c>
+      <c r="CB14" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6983,6 +7086,9 @@
       <c r="CA15" t="n">
         <v>90</v>
       </c>
+      <c r="CB15" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7226,6 +7332,9 @@
       <c r="CA16" t="n">
         <v>106</v>
       </c>
+      <c r="CB16" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7469,6 +7578,9 @@
       <c r="CA17" t="n">
         <v>105</v>
       </c>
+      <c r="CB17" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7712,6 +7824,9 @@
       <c r="CA18" t="n">
         <v>100</v>
       </c>
+      <c r="CB18" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7954,6 +8069,9 @@
       </c>
       <c r="CA19" t="n">
         <v>91</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -7967,7 +8085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7981,6 +8099,7 @@
     <col width="12" customWidth="1" min="58" max="58"/>
     <col width="12" customWidth="1" min="59" max="59"/>
     <col width="12" customWidth="1" min="60" max="60"/>
+    <col width="12" customWidth="1" min="61" max="61"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8186,6 +8305,11 @@
           <t>20260121</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>20260122</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8372,6 +8496,9 @@
       <c r="BH2" t="n">
         <v>20.67</v>
       </c>
+      <c r="BI2" t="n">
+        <v>28.81</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8558,6 +8685,9 @@
       <c r="BH3" t="n">
         <v>27.56</v>
       </c>
+      <c r="BI3" t="n">
+        <v>15.05</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8744,6 +8874,9 @@
       <c r="BH4" t="n">
         <v>8.470000000000001</v>
       </c>
+      <c r="BI4" t="n">
+        <v>12.7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8930,6 +9063,9 @@
       <c r="BH5" t="n">
         <v>0.83</v>
       </c>
+      <c r="BI5" t="n">
+        <v>-6.93</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9116,6 +9252,9 @@
       <c r="BH6" t="n">
         <v>26.47</v>
       </c>
+      <c r="BI6" t="n">
+        <v>15.17</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9302,6 +9441,9 @@
       <c r="BH7" t="n">
         <v>32.95</v>
       </c>
+      <c r="BI7" t="n">
+        <v>19.85</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9488,6 +9630,9 @@
       <c r="BH8" t="n">
         <v>29.5</v>
       </c>
+      <c r="BI8" t="n">
+        <v>16.3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9674,6 +9819,9 @@
       <c r="BH9" t="n">
         <v>-22.04</v>
       </c>
+      <c r="BI9" t="n">
+        <v>-4.19</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9860,6 +10008,9 @@
       <c r="BH10" t="n">
         <v>11.2</v>
       </c>
+      <c r="BI10" t="n">
+        <v>3.53</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10046,6 +10197,9 @@
       <c r="BH11" t="n">
         <v>-24.6</v>
       </c>
+      <c r="BI11" t="n">
+        <v>-5.71</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10232,6 +10386,9 @@
       <c r="BH12" t="n">
         <v>-31.6</v>
       </c>
+      <c r="BI12" t="n">
+        <v>-16.49</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10418,6 +10575,9 @@
       <c r="BH13" t="n">
         <v>-35.97</v>
       </c>
+      <c r="BI13" t="n">
+        <v>-20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10604,6 +10764,9 @@
       <c r="BH14" t="n">
         <v>-34.99</v>
       </c>
+      <c r="BI14" t="n">
+        <v>-13.44</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10790,6 +10953,9 @@
       <c r="BH15" t="n">
         <v>24.7</v>
       </c>
+      <c r="BI15" t="n">
+        <v>37.35</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10976,6 +11142,9 @@
       <c r="BH16" t="n">
         <v>-20.91</v>
       </c>
+      <c r="BI16" t="n">
+        <v>2.59</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11162,6 +11331,9 @@
       <c r="BH17" t="n">
         <v>-32.54</v>
       </c>
+      <c r="BI17" t="n">
+        <v>-14.32</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11348,6 +11520,9 @@
       <c r="BH18" t="n">
         <v>9.99</v>
       </c>
+      <c r="BI18" t="n">
+        <v>1.25</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11533,6 +11708,9 @@
       </c>
       <c r="BH19" t="n">
         <v>41.94</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>59.76</v>
       </c>
     </row>
   </sheetData>
@@ -11546,7 +11724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM19"/>
+  <dimension ref="A1:AN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11588,6 +11766,7 @@
     <col width="12" customWidth="1" min="37" max="37"/>
     <col width="12" customWidth="1" min="38" max="38"/>
     <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="12" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11786,6 +11965,11 @@
           <t>20260121</t>
         </is>
       </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>20260122</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11909,6 +12093,9 @@
       <c r="AM2" t="n">
         <v>280</v>
       </c>
+      <c r="AN2" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12032,6 +12219,9 @@
       <c r="AM3" t="n">
         <v>46</v>
       </c>
+      <c r="AN3" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12155,6 +12345,9 @@
       <c r="AM4" t="n">
         <v>260</v>
       </c>
+      <c r="AN4" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12278,6 +12471,9 @@
       <c r="AM5" t="n">
         <v>41</v>
       </c>
+      <c r="AN5" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12401,6 +12597,9 @@
       <c r="AM6" t="n">
         <v>79</v>
       </c>
+      <c r="AN6" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12524,6 +12723,9 @@
       <c r="AM7" t="n">
         <v>82</v>
       </c>
+      <c r="AN7" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12647,6 +12849,9 @@
       <c r="AM8" t="n">
         <v>90</v>
       </c>
+      <c r="AN8" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12770,6 +12975,9 @@
       <c r="AM9" t="n">
         <v>64</v>
       </c>
+      <c r="AN9" t="n">
+        <v>136</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12893,6 +13101,9 @@
       <c r="AM10" t="n">
         <v>72</v>
       </c>
+      <c r="AN10" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13016,6 +13227,9 @@
       <c r="AM11" t="n">
         <v>66</v>
       </c>
+      <c r="AN11" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13139,6 +13353,9 @@
       <c r="AM12" t="n">
         <v>58</v>
       </c>
+      <c r="AN12" t="n">
+        <v>115</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13262,6 +13479,9 @@
       <c r="AM13" t="n">
         <v>49</v>
       </c>
+      <c r="AN13" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13385,6 +13605,9 @@
       <c r="AM14" t="n">
         <v>75</v>
       </c>
+      <c r="AN14" t="n">
+        <v>138</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13508,6 +13731,9 @@
       <c r="AM15" t="n">
         <v>191</v>
       </c>
+      <c r="AN15" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13631,6 +13857,9 @@
       <c r="AM16" t="n">
         <v>56</v>
       </c>
+      <c r="AN16" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13754,6 +13983,9 @@
       <c r="AM17" t="n">
         <v>66</v>
       </c>
+      <c r="AN17" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13877,6 +14109,9 @@
       <c r="AM18" t="n">
         <v>24</v>
       </c>
+      <c r="AN18" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13999,6 +14234,9 @@
       </c>
       <c r="AM19" t="n">
         <v>207</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -14012,7 +14250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CT19"/>
+  <dimension ref="A1:CU19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14113,6 +14351,7 @@
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
+    <col width="12" customWidth="1" min="99" max="99"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14414,6 +14653,9 @@
       <c r="CT1" s="1" t="n">
         <v>20260121</v>
       </c>
+      <c r="CU1" s="1" t="n">
+        <v>20260122</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14714,6 +14956,9 @@
       <c r="CT2" t="n">
         <v>14495</v>
       </c>
+      <c r="CU2" t="n">
+        <v>13860</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15014,6 +15259,9 @@
       <c r="CT3" t="n">
         <v>69000</v>
       </c>
+      <c r="CU3" t="n">
+        <v>72800</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15314,6 +15562,9 @@
       <c r="CT4" t="n">
         <v>17815</v>
       </c>
+      <c r="CU4" t="n">
+        <v>16800</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15614,6 +15865,9 @@
       <c r="CT5" t="n">
         <v>16335</v>
       </c>
+      <c r="CU5" t="n">
+        <v>17110</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15914,6 +16168,9 @@
       <c r="CT6" t="n">
         <v>19905</v>
       </c>
+      <c r="CU6" t="n">
+        <v>20890</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16214,6 +16471,9 @@
       <c r="CT7" t="n">
         <v>23670</v>
       </c>
+      <c r="CU7" t="n">
+        <v>25050</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16514,6 +16774,9 @@
       <c r="CT8" t="n">
         <v>23130</v>
       </c>
+      <c r="CU8" t="n">
+        <v>24580</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16814,6 +17077,9 @@
       <c r="CT9" t="n">
         <v>1405</v>
       </c>
+      <c r="CU9" t="n">
+        <v>1470</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17114,6 +17380,9 @@
       <c r="CT10" t="n">
         <v>17840</v>
       </c>
+      <c r="CU10" t="n">
+        <v>18600</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17414,6 +17683,9 @@
       <c r="CT11" t="n">
         <v>5285</v>
       </c>
+      <c r="CU11" t="n">
+        <v>5375</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17714,6 +17986,9 @@
       <c r="CT12" t="n">
         <v>5610</v>
       </c>
+      <c r="CU12" t="n">
+        <v>5705</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -18014,6 +18289,9 @@
       <c r="CT13" t="n">
         <v>5670</v>
       </c>
+      <c r="CU13" t="n">
+        <v>5770</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18314,6 +18592,9 @@
       <c r="CT14" t="n">
         <v>1494</v>
       </c>
+      <c r="CU14" t="n">
+        <v>1550</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18614,6 +18895,9 @@
       <c r="CT15" t="n">
         <v>18845</v>
       </c>
+      <c r="CU15" t="n">
+        <v>17605</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -18914,6 +19198,9 @@
       <c r="CT16" t="n">
         <v>10805</v>
       </c>
+      <c r="CU16" t="n">
+        <v>10970</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -19214,6 +19501,9 @@
       <c r="CT17" t="n">
         <v>6190</v>
       </c>
+      <c r="CU17" t="n">
+        <v>6260</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -19514,6 +19804,9 @@
       <c r="CT18" t="n">
         <v>19050</v>
       </c>
+      <c r="CU18" t="n">
+        <v>19935</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -19813,6 +20106,9 @@
       </c>
       <c r="CT19" t="n">
         <v>15600</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>14790</v>
       </c>
     </row>
   </sheetData>
@@ -19826,7 +20122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CT19"/>
+  <dimension ref="A1:CU19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19927,6 +20223,7 @@
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
+    <col width="12" customWidth="1" min="99" max="99"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20228,6 +20525,9 @@
       <c r="CT1" s="1" t="n">
         <v>20260121</v>
       </c>
+      <c r="CU1" s="1" t="n">
+        <v>20260122</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20528,6 +20828,9 @@
       <c r="CT2" t="n">
         <v>14600</v>
       </c>
+      <c r="CU2" t="n">
+        <v>14060</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20828,6 +21131,9 @@
       <c r="CT3" t="n">
         <v>71150</v>
       </c>
+      <c r="CU3" t="n">
+        <v>72900</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21128,6 +21434,9 @@
       <c r="CT4" t="n">
         <v>17875</v>
       </c>
+      <c r="CU4" t="n">
+        <v>17365</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21428,6 +21737,9 @@
       <c r="CT5" t="n">
         <v>16765</v>
       </c>
+      <c r="CU5" t="n">
+        <v>17125</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21728,6 +22040,9 @@
       <c r="CT6" t="n">
         <v>20425</v>
       </c>
+      <c r="CU6" t="n">
+        <v>21015</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22028,6 +22343,9 @@
       <c r="CT7" t="n">
         <v>24520</v>
       </c>
+      <c r="CU7" t="n">
+        <v>25140</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22328,6 +22646,9 @@
       <c r="CT8" t="n">
         <v>23980</v>
       </c>
+      <c r="CU8" t="n">
+        <v>24620</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22628,6 +22949,9 @@
       <c r="CT9" t="n">
         <v>1458</v>
       </c>
+      <c r="CU9" t="n">
+        <v>1630</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22928,6 +23252,9 @@
       <c r="CT10" t="n">
         <v>18240</v>
       </c>
+      <c r="CU10" t="n">
+        <v>18610</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23228,6 +23555,9 @@
       <c r="CT11" t="n">
         <v>5335</v>
       </c>
+      <c r="CU11" t="n">
+        <v>5715</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -23528,6 +23858,9 @@
       <c r="CT12" t="n">
         <v>5680</v>
       </c>
+      <c r="CU12" t="n">
+        <v>6040</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -23828,6 +24161,9 @@
       <c r="CT13" t="n">
         <v>5730</v>
       </c>
+      <c r="CU13" t="n">
+        <v>6110</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24128,6 +24464,9 @@
       <c r="CT14" t="n">
         <v>1519</v>
       </c>
+      <c r="CU14" t="n">
+        <v>1767</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24428,6 +24767,9 @@
       <c r="CT15" t="n">
         <v>18910</v>
       </c>
+      <c r="CU15" t="n">
+        <v>17895</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24728,6 +25070,9 @@
       <c r="CT16" t="n">
         <v>10900</v>
       </c>
+      <c r="CU16" t="n">
+        <v>11755</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -25028,6 +25373,9 @@
       <c r="CT17" t="n">
         <v>6242</v>
       </c>
+      <c r="CU17" t="n">
+        <v>6720</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25328,6 +25676,9 @@
       <c r="CT18" t="n">
         <v>19450</v>
       </c>
+      <c r="CU18" t="n">
+        <v>19935</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25627,6 +25978,9 @@
       </c>
       <c r="CT19" t="n">
         <v>15665</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>14980</v>
       </c>
     </row>
   </sheetData>
@@ -25640,7 +25994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CT19"/>
+  <dimension ref="A1:CU19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25741,6 +26095,7 @@
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
+    <col width="12" customWidth="1" min="99" max="99"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26042,6 +26397,9 @@
       <c r="CT1" s="1" t="n">
         <v>20260121</v>
       </c>
+      <c r="CU1" s="1" t="n">
+        <v>20260122</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26342,6 +26700,9 @@
       <c r="CT2" t="n">
         <v>13250</v>
       </c>
+      <c r="CU2" t="n">
+        <v>13270</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26642,6 +27003,9 @@
       <c r="CT3" t="n">
         <v>68805</v>
       </c>
+      <c r="CU3" t="n">
+        <v>71525</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26942,6 +27306,9 @@
       <c r="CT4" t="n">
         <v>16275</v>
       </c>
+      <c r="CU4" t="n">
+        <v>16410</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27242,6 +27609,9 @@
       <c r="CT5" t="n">
         <v>16225</v>
       </c>
+      <c r="CU5" t="n">
+        <v>16620</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27542,6 +27912,9 @@
       <c r="CT6" t="n">
         <v>19870</v>
       </c>
+      <c r="CU6" t="n">
+        <v>20710</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27842,6 +28215,9 @@
       <c r="CT7" t="n">
         <v>23525</v>
       </c>
+      <c r="CU7" t="n">
+        <v>24705</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28142,6 +28518,9 @@
       <c r="CT8" t="n">
         <v>23100</v>
       </c>
+      <c r="CU8" t="n">
+        <v>24105</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28442,6 +28821,9 @@
       <c r="CT9" t="n">
         <v>1381</v>
       </c>
+      <c r="CU9" t="n">
+        <v>1448</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28742,6 +29124,9 @@
       <c r="CT10" t="n">
         <v>17685</v>
       </c>
+      <c r="CU10" t="n">
+        <v>18145</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29042,6 +29427,9 @@
       <c r="CT11" t="n">
         <v>5175</v>
       </c>
+      <c r="CU11" t="n">
+        <v>5340</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29342,6 +29730,9 @@
       <c r="CT12" t="n">
         <v>5490</v>
       </c>
+      <c r="CU12" t="n">
+        <v>5645</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29642,6 +30033,9 @@
       <c r="CT13" t="n">
         <v>5545</v>
       </c>
+      <c r="CU13" t="n">
+        <v>5700</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29942,6 +30336,9 @@
       <c r="CT14" t="n">
         <v>1437</v>
       </c>
+      <c r="CU14" t="n">
+        <v>1532</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -30242,6 +30639,9 @@
       <c r="CT15" t="n">
         <v>16965</v>
       </c>
+      <c r="CU15" t="n">
+        <v>17180</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -30542,6 +30942,9 @@
       <c r="CT16" t="n">
         <v>10595</v>
       </c>
+      <c r="CU16" t="n">
+        <v>10900</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -30842,6 +31245,9 @@
       <c r="CT17" t="n">
         <v>6065</v>
       </c>
+      <c r="CU17" t="n">
+        <v>6255</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -31142,6 +31548,9 @@
       <c r="CT18" t="n">
         <v>18740</v>
       </c>
+      <c r="CU18" t="n">
+        <v>19170</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -31441,6 +31850,9 @@
       </c>
       <c r="CT19" t="n">
         <v>14460</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>14410</v>
       </c>
     </row>
   </sheetData>
@@ -31454,7 +31866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CT19"/>
+  <dimension ref="A1:CU19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31555,6 +31967,7 @@
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
+    <col width="12" customWidth="1" min="99" max="99"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31856,6 +32269,9 @@
       <c r="CT1" s="1" t="n">
         <v>20260121</v>
       </c>
+      <c r="CU1" s="1" t="n">
+        <v>20260122</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32156,6 +32572,9 @@
       <c r="CT2" t="n">
         <v>13635</v>
       </c>
+      <c r="CU2" t="n">
+        <v>13945</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32456,6 +32875,9 @@
       <c r="CT3" t="n">
         <v>70705</v>
       </c>
+      <c r="CU3" t="n">
+        <v>72025</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -32756,6 +33178,9 @@
       <c r="CT4" t="n">
         <v>16620</v>
       </c>
+      <c r="CU4" t="n">
+        <v>17165</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -33056,6 +33481,9 @@
       <c r="CT5" t="n">
         <v>16590</v>
       </c>
+      <c r="CU5" t="n">
+        <v>16795</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -33356,6 +33784,9 @@
       <c r="CT6" t="n">
         <v>20410</v>
       </c>
+      <c r="CU6" t="n">
+        <v>20895</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -33656,6 +34087,9 @@
       <c r="CT7" t="n">
         <v>24430</v>
       </c>
+      <c r="CU7" t="n">
+        <v>24805</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -33956,6 +34390,9 @@
       <c r="CT8" t="n">
         <v>23980</v>
       </c>
+      <c r="CU8" t="n">
+        <v>24275</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -34256,6 +34693,9 @@
       <c r="CT9" t="n">
         <v>1440</v>
       </c>
+      <c r="CU9" t="n">
+        <v>1628</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34556,6 +34996,9 @@
       <c r="CT10" t="n">
         <v>18215</v>
       </c>
+      <c r="CU10" t="n">
+        <v>18500</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -34856,6 +35299,9 @@
       <c r="CT11" t="n">
         <v>5315</v>
       </c>
+      <c r="CU11" t="n">
+        <v>5690</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -35156,6 +35602,9 @@
       <c r="CT12" t="n">
         <v>5615</v>
       </c>
+      <c r="CU12" t="n">
+        <v>6035</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35456,6 +35905,9 @@
       <c r="CT13" t="n">
         <v>5670</v>
       </c>
+      <c r="CU13" t="n">
+        <v>6085</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35756,6 +36208,9 @@
       <c r="CT14" t="n">
         <v>1508</v>
       </c>
+      <c r="CU14" t="n">
+        <v>1767</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36056,6 +36511,9 @@
       <c r="CT15" t="n">
         <v>17435</v>
       </c>
+      <c r="CU15" t="n">
+        <v>17705</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -36356,6 +36814,9 @@
       <c r="CT16" t="n">
         <v>10870</v>
       </c>
+      <c r="CU16" t="n">
+        <v>11750</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36656,6 +37117,9 @@
       <c r="CT17" t="n">
         <v>6220</v>
       </c>
+      <c r="CU17" t="n">
+        <v>6720</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36956,6 +37420,9 @@
       <c r="CT18" t="n">
         <v>19340</v>
       </c>
+      <c r="CU18" t="n">
+        <v>19610</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -37255,6 +37722,9 @@
       </c>
       <c r="CT19" t="n">
         <v>14645</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>14850</v>
       </c>
     </row>
   </sheetData>
@@ -37268,7 +37738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CT19"/>
+  <dimension ref="A1:CU19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37369,6 +37839,7 @@
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
+    <col width="12" customWidth="1" min="99" max="99"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37670,6 +38141,9 @@
       <c r="CT1" s="1" t="n">
         <v>20260121</v>
       </c>
+      <c r="CU1" s="1" t="n">
+        <v>20260122</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37970,6 +38444,9 @@
       <c r="CT2" t="n">
         <v>1063903</v>
       </c>
+      <c r="CU2" t="n">
+        <v>631089</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38270,6 +38747,9 @@
       <c r="CT3" t="n">
         <v>2106599</v>
       </c>
+      <c r="CU3" t="n">
+        <v>1597516</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -38570,6 +39050,9 @@
       <c r="CT4" t="n">
         <v>1098554</v>
       </c>
+      <c r="CU4" t="n">
+        <v>479179</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -38870,6 +39353,9 @@
       <c r="CT5" t="n">
         <v>368707</v>
       </c>
+      <c r="CU5" t="n">
+        <v>190204</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -39170,6 +39656,9 @@
       <c r="CT6" t="n">
         <v>4384311</v>
       </c>
+      <c r="CU6" t="n">
+        <v>5040216</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -39470,6 +39959,9 @@
       <c r="CT7" t="n">
         <v>6524093</v>
       </c>
+      <c r="CU7" t="n">
+        <v>3458993</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -39770,6 +40262,9 @@
       <c r="CT8" t="n">
         <v>15729932</v>
       </c>
+      <c r="CU8" t="n">
+        <v>14107305</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -40070,6 +40565,9 @@
       <c r="CT9" t="n">
         <v>8842250</v>
       </c>
+      <c r="CU9" t="n">
+        <v>18925878</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -40370,6 +40868,9 @@
       <c r="CT10" t="n">
         <v>1787264</v>
       </c>
+      <c r="CU10" t="n">
+        <v>941524</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -40670,6 +41171,9 @@
       <c r="CT11" t="n">
         <v>1464383</v>
       </c>
+      <c r="CU11" t="n">
+        <v>1955450</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -40970,6 +41474,9 @@
       <c r="CT12" t="n">
         <v>3024986</v>
       </c>
+      <c r="CU12" t="n">
+        <v>5924784</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -41270,6 +41777,9 @@
       <c r="CT13" t="n">
         <v>6030311</v>
       </c>
+      <c r="CU13" t="n">
+        <v>14088244</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -41570,6 +42080,9 @@
       <c r="CT14" t="n">
         <v>69552044</v>
       </c>
+      <c r="CU14" t="n">
+        <v>128917212</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41870,6 +42383,9 @@
       <c r="CT15" t="n">
         <v>8007101</v>
       </c>
+      <c r="CU15" t="n">
+        <v>3244449</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -42170,6 +42686,9 @@
       <c r="CT16" t="n">
         <v>594798</v>
       </c>
+      <c r="CU16" t="n">
+        <v>950159</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42470,6 +42989,9 @@
       <c r="CT17" t="n">
         <v>179228</v>
       </c>
+      <c r="CU17" t="n">
+        <v>230067</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42770,6 +43292,9 @@
       <c r="CT18" t="n">
         <v>72571</v>
       </c>
+      <c r="CU18" t="n">
+        <v>158597</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43069,6 +43594,9 @@
       </c>
       <c r="CT19" t="n">
         <v>236345</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>122803</v>
       </c>
     </row>
   </sheetData>
@@ -43082,7 +43610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA19"/>
+  <dimension ref="A1:CB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -43164,6 +43692,7 @@
     <col width="10" customWidth="1" min="77" max="77"/>
     <col width="10" customWidth="1" min="78" max="78"/>
     <col width="10" customWidth="1" min="79" max="79"/>
+    <col width="10" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43408,6 +43937,9 @@
       <c r="CA1" s="1" t="n">
         <v>20260121</v>
       </c>
+      <c r="CB1" s="1" t="n">
+        <v>20260122</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -43651,6 +44183,9 @@
       <c r="CA2" t="n">
         <v>0</v>
       </c>
+      <c r="CB2" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -43894,6 +44429,9 @@
       <c r="CA3" t="n">
         <v>89</v>
       </c>
+      <c r="CB3" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -44137,6 +44675,9 @@
       <c r="CA4" t="n">
         <v>0</v>
       </c>
+      <c r="CB4" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -44380,6 +44921,9 @@
       <c r="CA5" t="n">
         <v>49</v>
       </c>
+      <c r="CB5" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -44623,6 +45167,9 @@
       <c r="CA6" t="n">
         <v>90</v>
       </c>
+      <c r="CB6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -44866,6 +45413,9 @@
       <c r="CA7" t="n">
         <v>92</v>
       </c>
+      <c r="CB7" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -45109,6 +45659,9 @@
       <c r="CA8" t="n">
         <v>96</v>
       </c>
+      <c r="CB8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -45352,6 +45905,9 @@
       <c r="CA9" t="n">
         <v>83</v>
       </c>
+      <c r="CB9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -45595,6 +46151,9 @@
       <c r="CA10" t="n">
         <v>68</v>
       </c>
+      <c r="CB10" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -45838,6 +46397,9 @@
       <c r="CA11" t="n">
         <v>88</v>
       </c>
+      <c r="CB11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -46081,6 +46643,9 @@
       <c r="CA12" t="n">
         <v>83</v>
       </c>
+      <c r="CB12" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -46324,6 +46889,9 @@
       <c r="CA13" t="n">
         <v>85</v>
       </c>
+      <c r="CB13" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -46567,6 +47135,9 @@
       <c r="CA14" t="n">
         <v>84</v>
       </c>
+      <c r="CB14" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -46810,6 +47381,9 @@
       <c r="CA15" t="n">
         <v>0</v>
       </c>
+      <c r="CB15" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -47053,6 +47627,9 @@
       <c r="CA16" t="n">
         <v>88</v>
       </c>
+      <c r="CB16" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -47296,6 +47873,9 @@
       <c r="CA17" t="n">
         <v>81</v>
       </c>
+      <c r="CB17" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -47539,6 +48119,9 @@
       <c r="CA18" t="n">
         <v>60</v>
       </c>
+      <c r="CB18" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -47781,6 +48364,9 @@
       </c>
       <c r="CA19" t="n">
         <v>0</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -47794,7 +48380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM19"/>
+  <dimension ref="A1:AN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -47836,6 +48422,7 @@
     <col width="10" customWidth="1" min="37" max="37"/>
     <col width="10" customWidth="1" min="38" max="38"/>
     <col width="10" customWidth="1" min="39" max="39"/>
+    <col width="10" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -47960,6 +48547,9 @@
       <c r="AM1" s="1" t="n">
         <v>20260121</v>
       </c>
+      <c r="AN1" s="1" t="n">
+        <v>20260122</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -48083,6 +48673,9 @@
       <c r="AM2" t="n">
         <v>0</v>
       </c>
+      <c r="AN2" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -48206,6 +48799,9 @@
       <c r="AM3" t="n">
         <v>92</v>
       </c>
+      <c r="AN3" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -48329,6 +48925,9 @@
       <c r="AM4" t="n">
         <v>4</v>
       </c>
+      <c r="AN4" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -48452,6 +49051,9 @@
       <c r="AM5" t="n">
         <v>62</v>
       </c>
+      <c r="AN5" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -48575,6 +49177,9 @@
       <c r="AM6" t="n">
         <v>93</v>
       </c>
+      <c r="AN6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -48698,6 +49303,9 @@
       <c r="AM7" t="n">
         <v>94</v>
       </c>
+      <c r="AN7" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -48821,6 +49429,9 @@
       <c r="AM8" t="n">
         <v>97</v>
       </c>
+      <c r="AN8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -48944,6 +49555,9 @@
       <c r="AM9" t="n">
         <v>33</v>
       </c>
+      <c r="AN9" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -49067,6 +49681,9 @@
       <c r="AM10" t="n">
         <v>72</v>
       </c>
+      <c r="AN10" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -49190,6 +49807,9 @@
       <c r="AM11" t="n">
         <v>54</v>
       </c>
+      <c r="AN11" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -49313,6 +49933,9 @@
       <c r="AM12" t="n">
         <v>47</v>
       </c>
+      <c r="AN12" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -49436,6 +50059,9 @@
       <c r="AM13" t="n">
         <v>50</v>
       </c>
+      <c r="AN13" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -49559,6 +50185,9 @@
       <c r="AM14" t="n">
         <v>32</v>
       </c>
+      <c r="AN14" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -49682,6 +50311,9 @@
       <c r="AM15" t="n">
         <v>42</v>
       </c>
+      <c r="AN15" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -49805,6 +50437,9 @@
       <c r="AM16" t="n">
         <v>54</v>
       </c>
+      <c r="AN16" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -49928,6 +50563,9 @@
       <c r="AM17" t="n">
         <v>39</v>
       </c>
+      <c r="AN17" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -50051,6 +50689,9 @@
       <c r="AM18" t="n">
         <v>69</v>
       </c>
+      <c r="AN18" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -50173,6 +50814,9 @@
       </c>
       <c r="AM19" t="n">
         <v>37</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -50186,7 +50830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA19"/>
+  <dimension ref="A1:CB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -50268,6 +50912,7 @@
     <col width="10" customWidth="1" min="77" max="77"/>
     <col width="10" customWidth="1" min="78" max="78"/>
     <col width="10" customWidth="1" min="79" max="79"/>
+    <col width="10" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -50512,6 +51157,9 @@
       <c r="CA1" s="1" t="n">
         <v>20260121</v>
       </c>
+      <c r="CB1" s="1" t="n">
+        <v>20260122</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -50755,6 +51403,9 @@
       <c r="CA2" t="n">
         <v>-124</v>
       </c>
+      <c r="CB2" t="n">
+        <v>-89</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -50998,6 +51649,9 @@
       <c r="CA3" t="n">
         <v>37</v>
       </c>
+      <c r="CB3" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -51241,6 +51895,9 @@
       <c r="CA4" t="n">
         <v>-120</v>
       </c>
+      <c r="CB4" t="n">
+        <v>-70</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -51484,6 +52141,9 @@
       <c r="CA5" t="n">
         <v>-15</v>
       </c>
+      <c r="CB5" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -51727,6 +52387,9 @@
       <c r="CA6" t="n">
         <v>39</v>
       </c>
+      <c r="CB6" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -51970,6 +52633,9 @@
       <c r="CA7" t="n">
         <v>42</v>
       </c>
+      <c r="CB7" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -52213,6 +52879,9 @@
       <c r="CA8" t="n">
         <v>43</v>
       </c>
+      <c r="CB8" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -52456,6 +53125,9 @@
       <c r="CA9" t="n">
         <v>65</v>
       </c>
+      <c r="CB9" t="n">
+        <v>125</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -52699,6 +53371,9 @@
       <c r="CA10" t="n">
         <v>15</v>
       </c>
+      <c r="CB10" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -52942,6 +53617,9 @@
       <c r="CA11" t="n">
         <v>69</v>
       </c>
+      <c r="CB11" t="n">
+        <v>129</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -53185,6 +53863,9 @@
       <c r="CA12" t="n">
         <v>54</v>
       </c>
+      <c r="CB12" t="n">
+        <v>122</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -53428,6 +54109,9 @@
       <c r="CA13" t="n">
         <v>58</v>
       </c>
+      <c r="CB13" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -53671,6 +54355,9 @@
       <c r="CA14" t="n">
         <v>63</v>
       </c>
+      <c r="CB14" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -53914,6 +54601,9 @@
       <c r="CA15" t="n">
         <v>-138</v>
       </c>
+      <c r="CB15" t="n">
+        <v>-103</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -54157,6 +54847,9 @@
       <c r="CA16" t="n">
         <v>78</v>
       </c>
+      <c r="CB16" t="n">
+        <v>136</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -54400,6 +55093,9 @@
       <c r="CA17" t="n">
         <v>62</v>
       </c>
+      <c r="CB17" t="n">
+        <v>133</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -54643,6 +55339,9 @@
       <c r="CA18" t="n">
         <v>3</v>
       </c>
+      <c r="CB18" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -54885,6 +55584,9 @@
       </c>
       <c r="CA19" t="n">
         <v>-149</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>-106</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN19"/>
+  <dimension ref="A1:AO19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -752,6 +752,7 @@
     <col width="10" customWidth="1" min="38" max="38"/>
     <col width="10" customWidth="1" min="39" max="39"/>
     <col width="10" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -879,6 +880,9 @@
       <c r="AN1" s="1" t="n">
         <v>20260122</v>
       </c>
+      <c r="AO1" s="1" t="n">
+        <v>20260123</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1005,6 +1009,9 @@
       <c r="AN2" t="n">
         <v>-91</v>
       </c>
+      <c r="AO2" t="n">
+        <v>-20</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1131,6 +1138,9 @@
       <c r="AN3" t="n">
         <v>97</v>
       </c>
+      <c r="AO3" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1257,6 +1267,9 @@
       <c r="AN4" t="n">
         <v>-58</v>
       </c>
+      <c r="AO4" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1383,6 +1396,9 @@
       <c r="AN5" t="n">
         <v>31</v>
       </c>
+      <c r="AO5" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1509,6 +1525,9 @@
       <c r="AN6" t="n">
         <v>102</v>
       </c>
+      <c r="AO6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1635,6 +1654,9 @@
       <c r="AN7" t="n">
         <v>99</v>
       </c>
+      <c r="AO7" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1761,6 +1783,9 @@
       <c r="AN8" t="n">
         <v>98</v>
       </c>
+      <c r="AO8" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1887,6 +1912,9 @@
       <c r="AN9" t="n">
         <v>32</v>
       </c>
+      <c r="AO9" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2013,6 +2041,9 @@
       <c r="AN10" t="n">
         <v>68</v>
       </c>
+      <c r="AO10" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2139,6 +2170,9 @@
       <c r="AN11" t="n">
         <v>81</v>
       </c>
+      <c r="AO11" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2265,6 +2299,9 @@
       <c r="AN12" t="n">
         <v>60</v>
       </c>
+      <c r="AO12" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2391,6 +2428,9 @@
       <c r="AN13" t="n">
         <v>68</v>
       </c>
+      <c r="AO13" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2517,6 +2557,9 @@
       <c r="AN14" t="n">
         <v>37</v>
       </c>
+      <c r="AO14" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2643,6 +2686,9 @@
       <c r="AN15" t="n">
         <v>-38</v>
       </c>
+      <c r="AO15" t="n">
+        <v>-7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2769,6 +2815,9 @@
       <c r="AN16" t="n">
         <v>82</v>
       </c>
+      <c r="AO16" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2895,6 +2944,9 @@
       <c r="AN17" t="n">
         <v>46</v>
       </c>
+      <c r="AO17" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3021,6 +3073,9 @@
       <c r="AN18" t="n">
         <v>61</v>
       </c>
+      <c r="AO18" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3146,6 +3201,9 @@
       </c>
       <c r="AN19" t="n">
         <v>-41</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -3159,7 +3217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB19"/>
+  <dimension ref="A1:CC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3242,6 +3300,7 @@
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
+    <col width="12" customWidth="1" min="81" max="81"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3645,6 +3704,11 @@
           <t>20260122</t>
         </is>
       </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>20260123</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3891,6 +3955,9 @@
       <c r="CB2" t="n">
         <v>92</v>
       </c>
+      <c r="CC2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4137,6 +4204,9 @@
       <c r="CB3" t="n">
         <v>107</v>
       </c>
+      <c r="CC3" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4383,6 +4453,9 @@
       <c r="CB4" t="n">
         <v>95</v>
       </c>
+      <c r="CC4" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4629,6 +4702,9 @@
       <c r="CB5" t="n">
         <v>100</v>
       </c>
+      <c r="CC5" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4875,6 +4951,9 @@
       <c r="CB6" t="n">
         <v>107</v>
       </c>
+      <c r="CC6" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5121,6 +5200,9 @@
       <c r="CB7" t="n">
         <v>107</v>
       </c>
+      <c r="CC7" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5367,6 +5449,9 @@
       <c r="CB8" t="n">
         <v>108</v>
       </c>
+      <c r="CC8" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5613,6 +5698,9 @@
       <c r="CB9" t="n">
         <v>123</v>
       </c>
+      <c r="CC9" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5859,6 +5947,9 @@
       <c r="CB10" t="n">
         <v>103</v>
       </c>
+      <c r="CC10" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6105,6 +6196,9 @@
       <c r="CB11" t="n">
         <v>112</v>
       </c>
+      <c r="CC11" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6351,6 +6445,9 @@
       <c r="CB12" t="n">
         <v>112</v>
       </c>
+      <c r="CC12" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6597,6 +6694,9 @@
       <c r="CB13" t="n">
         <v>111</v>
       </c>
+      <c r="CC13" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6843,6 +6943,9 @@
       <c r="CB14" t="n">
         <v>126</v>
       </c>
+      <c r="CC14" t="n">
+        <v>124</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7089,6 +7192,9 @@
       <c r="CB15" t="n">
         <v>92</v>
       </c>
+      <c r="CC15" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7335,6 +7441,9 @@
       <c r="CB16" t="n">
         <v>114</v>
       </c>
+      <c r="CC16" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7581,6 +7690,9 @@
       <c r="CB17" t="n">
         <v>112</v>
       </c>
+      <c r="CC17" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7827,6 +7939,9 @@
       <c r="CB18" t="n">
         <v>101</v>
       </c>
+      <c r="CC18" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8072,6 +8187,9 @@
       </c>
       <c r="CB19" t="n">
         <v>93</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -8085,7 +8203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI19"/>
+  <dimension ref="A1:BJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8100,6 +8218,7 @@
     <col width="12" customWidth="1" min="59" max="59"/>
     <col width="12" customWidth="1" min="60" max="60"/>
     <col width="12" customWidth="1" min="61" max="61"/>
+    <col width="12" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8310,6 +8429,11 @@
           <t>20260122</t>
         </is>
       </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>20260123</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8499,6 +8623,9 @@
       <c r="BI2" t="n">
         <v>28.81</v>
       </c>
+      <c r="BJ2" t="n">
+        <v>24.04</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8688,6 +8815,9 @@
       <c r="BI3" t="n">
         <v>15.05</v>
       </c>
+      <c r="BJ3" t="n">
+        <v>1.91</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8877,6 +9007,9 @@
       <c r="BI4" t="n">
         <v>12.7</v>
       </c>
+      <c r="BJ4" t="n">
+        <v>9.880000000000001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9066,6 +9199,9 @@
       <c r="BI5" t="n">
         <v>-6.93</v>
       </c>
+      <c r="BJ5" t="n">
+        <v>-18.11</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9255,6 +9391,9 @@
       <c r="BI6" t="n">
         <v>15.17</v>
       </c>
+      <c r="BJ6" t="n">
+        <v>2.67</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9444,6 +9583,9 @@
       <c r="BI7" t="n">
         <v>19.85</v>
       </c>
+      <c r="BJ7" t="n">
+        <v>5.12</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9633,6 +9775,9 @@
       <c r="BI8" t="n">
         <v>16.3</v>
       </c>
+      <c r="BJ8" t="n">
+        <v>2.73</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9822,6 +9967,9 @@
       <c r="BI9" t="n">
         <v>-4.19</v>
       </c>
+      <c r="BJ9" t="n">
+        <v>7.83</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10011,6 +10159,9 @@
       <c r="BI10" t="n">
         <v>3.53</v>
       </c>
+      <c r="BJ10" t="n">
+        <v>-4.95</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10200,6 +10351,9 @@
       <c r="BI11" t="n">
         <v>-5.71</v>
       </c>
+      <c r="BJ11" t="n">
+        <v>9.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10389,6 +10543,9 @@
       <c r="BI12" t="n">
         <v>-16.49</v>
       </c>
+      <c r="BJ12" t="n">
+        <v>-4.46</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10578,6 +10735,9 @@
       <c r="BI13" t="n">
         <v>-20.2</v>
       </c>
+      <c r="BJ13" t="n">
+        <v>-7.5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10767,6 +10927,9 @@
       <c r="BI14" t="n">
         <v>-13.44</v>
       </c>
+      <c r="BJ14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10956,6 +11119,9 @@
       <c r="BI15" t="n">
         <v>37.35</v>
       </c>
+      <c r="BJ15" t="n">
+        <v>34.75</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11145,6 +11311,9 @@
       <c r="BI16" t="n">
         <v>2.59</v>
       </c>
+      <c r="BJ16" t="n">
+        <v>17.4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11334,6 +11503,9 @@
       <c r="BI17" t="n">
         <v>-14.32</v>
       </c>
+      <c r="BJ17" t="n">
+        <v>-2.58</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11523,6 +11695,9 @@
       <c r="BI18" t="n">
         <v>1.25</v>
       </c>
+      <c r="BJ18" t="n">
+        <v>-9.130000000000001</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11711,6 +11886,9 @@
       </c>
       <c r="BI19" t="n">
         <v>59.76</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>54.13</v>
       </c>
     </row>
   </sheetData>
@@ -11724,7 +11902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN19"/>
+  <dimension ref="A1:AO19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11767,6 +11945,7 @@
     <col width="12" customWidth="1" min="38" max="38"/>
     <col width="12" customWidth="1" min="39" max="39"/>
     <col width="12" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11970,6 +12149,11 @@
           <t>20260122</t>
         </is>
       </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>20260123</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12096,6 +12280,9 @@
       <c r="AN2" t="n">
         <v>160</v>
       </c>
+      <c r="AO2" t="n">
+        <v>216</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12222,6 +12409,9 @@
       <c r="AN3" t="n">
         <v>35</v>
       </c>
+      <c r="AO3" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12348,6 +12538,9 @@
       <c r="AN4" t="n">
         <v>113</v>
       </c>
+      <c r="AO4" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12474,6 +12667,9 @@
       <c r="AN5" t="n">
         <v>22</v>
       </c>
+      <c r="AO5" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12600,6 +12796,9 @@
       <c r="AN6" t="n">
         <v>89</v>
       </c>
+      <c r="AO6" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12726,6 +12925,9 @@
       <c r="AN7" t="n">
         <v>44</v>
       </c>
+      <c r="AO7" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12852,6 +13054,9 @@
       <c r="AN8" t="n">
         <v>80</v>
       </c>
+      <c r="AO8" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12978,6 +13183,9 @@
       <c r="AN9" t="n">
         <v>136</v>
       </c>
+      <c r="AO9" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13104,6 +13312,9 @@
       <c r="AN10" t="n">
         <v>39</v>
       </c>
+      <c r="AO10" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13230,6 +13441,9 @@
       <c r="AN11" t="n">
         <v>89</v>
       </c>
+      <c r="AO11" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13356,6 +13570,9 @@
       <c r="AN12" t="n">
         <v>115</v>
       </c>
+      <c r="AO12" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13482,6 +13699,9 @@
       <c r="AN13" t="n">
         <v>114</v>
       </c>
+      <c r="AO13" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13608,6 +13828,9 @@
       <c r="AN14" t="n">
         <v>138</v>
       </c>
+      <c r="AO14" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13734,6 +13957,9 @@
       <c r="AN15" t="n">
         <v>77</v>
       </c>
+      <c r="AO15" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13860,6 +14086,9 @@
       <c r="AN16" t="n">
         <v>92</v>
       </c>
+      <c r="AO16" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13986,6 +14215,9 @@
       <c r="AN17" t="n">
         <v>86</v>
       </c>
+      <c r="AO17" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14112,6 +14344,9 @@
       <c r="AN18" t="n">
         <v>51</v>
       </c>
+      <c r="AO18" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14237,6 +14472,9 @@
       </c>
       <c r="AN19" t="n">
         <v>107</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -14250,7 +14488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU19"/>
+  <dimension ref="A1:CV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14352,6 +14590,7 @@
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
+    <col width="12" customWidth="1" min="100" max="100"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14656,6 +14895,9 @@
       <c r="CU1" s="1" t="n">
         <v>20260122</v>
       </c>
+      <c r="CV1" s="1" t="n">
+        <v>20260123</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14959,6 +15201,9 @@
       <c r="CU2" t="n">
         <v>13860</v>
       </c>
+      <c r="CV2" t="n">
+        <v>14000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15262,6 +15507,9 @@
       <c r="CU3" t="n">
         <v>72800</v>
       </c>
+      <c r="CV3" t="n">
+        <v>72050</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15565,6 +15813,9 @@
       <c r="CU4" t="n">
         <v>16800</v>
       </c>
+      <c r="CV4" t="n">
+        <v>17180</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15868,6 +16119,9 @@
       <c r="CU5" t="n">
         <v>17110</v>
       </c>
+      <c r="CV5" t="n">
+        <v>16870</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16171,6 +16425,9 @@
       <c r="CU6" t="n">
         <v>20890</v>
       </c>
+      <c r="CV6" t="n">
+        <v>20920</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16474,6 +16731,9 @@
       <c r="CU7" t="n">
         <v>25050</v>
       </c>
+      <c r="CV7" t="n">
+        <v>24900</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16777,6 +17037,9 @@
       <c r="CU8" t="n">
         <v>24580</v>
       </c>
+      <c r="CV8" t="n">
+        <v>24285</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17080,6 +17343,9 @@
       <c r="CU9" t="n">
         <v>1470</v>
       </c>
+      <c r="CV9" t="n">
+        <v>1687</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17383,6 +17649,9 @@
       <c r="CU10" t="n">
         <v>18600</v>
       </c>
+      <c r="CV10" t="n">
+        <v>18500</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17686,6 +17955,9 @@
       <c r="CU11" t="n">
         <v>5375</v>
       </c>
+      <c r="CV11" t="n">
+        <v>5860</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17989,6 +18261,9 @@
       <c r="CU12" t="n">
         <v>5705</v>
       </c>
+      <c r="CV12" t="n">
+        <v>6205</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -18292,6 +18567,9 @@
       <c r="CU13" t="n">
         <v>5770</v>
       </c>
+      <c r="CV13" t="n">
+        <v>6265</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18595,6 +18873,9 @@
       <c r="CU14" t="n">
         <v>1550</v>
       </c>
+      <c r="CV14" t="n">
+        <v>1857</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18898,6 +19179,9 @@
       <c r="CU15" t="n">
         <v>17605</v>
       </c>
+      <c r="CV15" t="n">
+        <v>17750</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -19201,6 +19485,9 @@
       <c r="CU16" t="n">
         <v>10970</v>
       </c>
+      <c r="CV16" t="n">
+        <v>12200</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -19504,6 +19791,9 @@
       <c r="CU17" t="n">
         <v>6260</v>
       </c>
+      <c r="CV17" t="n">
+        <v>6900</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -19807,6 +20097,9 @@
       <c r="CU18" t="n">
         <v>19935</v>
       </c>
+      <c r="CV18" t="n">
+        <v>19610</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -20109,6 +20402,9 @@
       </c>
       <c r="CU19" t="n">
         <v>14790</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>14900</v>
       </c>
     </row>
   </sheetData>
@@ -20122,7 +20418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU19"/>
+  <dimension ref="A1:CV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20224,6 +20520,7 @@
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
+    <col width="12" customWidth="1" min="100" max="100"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20528,6 +20825,9 @@
       <c r="CU1" s="1" t="n">
         <v>20260122</v>
       </c>
+      <c r="CV1" s="1" t="n">
+        <v>20260123</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20831,6 +21131,9 @@
       <c r="CU2" t="n">
         <v>14060</v>
       </c>
+      <c r="CV2" t="n">
+        <v>15060</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21134,6 +21437,9 @@
       <c r="CU3" t="n">
         <v>72900</v>
       </c>
+      <c r="CV3" t="n">
+        <v>72370</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21437,6 +21743,9 @@
       <c r="CU4" t="n">
         <v>17365</v>
       </c>
+      <c r="CV4" t="n">
+        <v>18490</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21740,6 +22049,9 @@
       <c r="CU5" t="n">
         <v>17125</v>
       </c>
+      <c r="CV5" t="n">
+        <v>17030</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22043,6 +22355,9 @@
       <c r="CU6" t="n">
         <v>21015</v>
       </c>
+      <c r="CV6" t="n">
+        <v>21020</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22346,6 +22661,9 @@
       <c r="CU7" t="n">
         <v>25140</v>
       </c>
+      <c r="CV7" t="n">
+        <v>25060</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22649,6 +22967,9 @@
       <c r="CU8" t="n">
         <v>24620</v>
       </c>
+      <c r="CV8" t="n">
+        <v>24450</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22952,6 +23273,9 @@
       <c r="CU9" t="n">
         <v>1630</v>
       </c>
+      <c r="CV9" t="n">
+        <v>1732</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23255,6 +23579,9 @@
       <c r="CU10" t="n">
         <v>18610</v>
       </c>
+      <c r="CV10" t="n">
+        <v>18750</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23558,6 +23885,9 @@
       <c r="CU11" t="n">
         <v>5715</v>
       </c>
+      <c r="CV11" t="n">
+        <v>5880</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -23861,6 +24191,9 @@
       <c r="CU12" t="n">
         <v>6040</v>
       </c>
+      <c r="CV12" t="n">
+        <v>6220</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24164,6 +24497,9 @@
       <c r="CU13" t="n">
         <v>6110</v>
       </c>
+      <c r="CV13" t="n">
+        <v>6270</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24467,6 +24803,9 @@
       <c r="CU14" t="n">
         <v>1767</v>
       </c>
+      <c r="CV14" t="n">
+        <v>1870</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24770,6 +25109,9 @@
       <c r="CU15" t="n">
         <v>17895</v>
       </c>
+      <c r="CV15" t="n">
+        <v>18630</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25073,6 +25415,9 @@
       <c r="CU16" t="n">
         <v>11755</v>
       </c>
+      <c r="CV16" t="n">
+        <v>12200</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -25376,6 +25721,9 @@
       <c r="CU17" t="n">
         <v>6720</v>
       </c>
+      <c r="CV17" t="n">
+        <v>6920</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25679,6 +26027,9 @@
       <c r="CU18" t="n">
         <v>19935</v>
       </c>
+      <c r="CV18" t="n">
+        <v>19910</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25981,6 +26332,9 @@
       </c>
       <c r="CU19" t="n">
         <v>14980</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>15890</v>
       </c>
     </row>
   </sheetData>
@@ -25994,7 +26348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU19"/>
+  <dimension ref="A1:CV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26096,6 +26450,7 @@
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
+    <col width="12" customWidth="1" min="100" max="100"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26400,6 +26755,9 @@
       <c r="CU1" s="1" t="n">
         <v>20260122</v>
       </c>
+      <c r="CV1" s="1" t="n">
+        <v>20260123</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26703,6 +27061,9 @@
       <c r="CU2" t="n">
         <v>13270</v>
       </c>
+      <c r="CV2" t="n">
+        <v>14000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27006,6 +27367,9 @@
       <c r="CU3" t="n">
         <v>71525</v>
       </c>
+      <c r="CV3" t="n">
+        <v>71135</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -27309,6 +27673,9 @@
       <c r="CU4" t="n">
         <v>16410</v>
       </c>
+      <c r="CV4" t="n">
+        <v>17180</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27612,6 +27979,9 @@
       <c r="CU5" t="n">
         <v>16620</v>
       </c>
+      <c r="CV5" t="n">
+        <v>16620</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27915,6 +28285,9 @@
       <c r="CU6" t="n">
         <v>20710</v>
       </c>
+      <c r="CV6" t="n">
+        <v>20675</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28218,6 +28591,9 @@
       <c r="CU7" t="n">
         <v>24705</v>
       </c>
+      <c r="CV7" t="n">
+        <v>24400</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28521,6 +28897,9 @@
       <c r="CU8" t="n">
         <v>24105</v>
       </c>
+      <c r="CV8" t="n">
+        <v>23975</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28824,6 +29203,9 @@
       <c r="CU9" t="n">
         <v>1448</v>
       </c>
+      <c r="CV9" t="n">
+        <v>1570</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -29127,6 +29509,9 @@
       <c r="CU10" t="n">
         <v>18145</v>
       </c>
+      <c r="CV10" t="n">
+        <v>18340</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29430,6 +29815,9 @@
       <c r="CU11" t="n">
         <v>5340</v>
       </c>
+      <c r="CV11" t="n">
+        <v>5610</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29733,6 +30121,9 @@
       <c r="CU12" t="n">
         <v>5645</v>
       </c>
+      <c r="CV12" t="n">
+        <v>5930</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30036,6 +30427,9 @@
       <c r="CU13" t="n">
         <v>5700</v>
       </c>
+      <c r="CV13" t="n">
+        <v>5970</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30339,6 +30733,9 @@
       <c r="CU14" t="n">
         <v>1532</v>
       </c>
+      <c r="CV14" t="n">
+        <v>1693</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -30642,6 +31039,9 @@
       <c r="CU15" t="n">
         <v>17180</v>
       </c>
+      <c r="CV15" t="n">
+        <v>17750</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -30945,6 +31345,9 @@
       <c r="CU16" t="n">
         <v>10900</v>
       </c>
+      <c r="CV16" t="n">
+        <v>11475</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -31248,6 +31651,9 @@
       <c r="CU17" t="n">
         <v>6255</v>
       </c>
+      <c r="CV17" t="n">
+        <v>6575</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -31551,6 +31957,9 @@
       <c r="CU18" t="n">
         <v>19170</v>
       </c>
+      <c r="CV18" t="n">
+        <v>19475</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -31853,6 +32262,9 @@
       </c>
       <c r="CU19" t="n">
         <v>14410</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>14900</v>
       </c>
     </row>
   </sheetData>
@@ -31866,7 +32278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU19"/>
+  <dimension ref="A1:CV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31968,6 +32380,7 @@
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
+    <col width="12" customWidth="1" min="100" max="100"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32272,6 +32685,9 @@
       <c r="CU1" s="1" t="n">
         <v>20260122</v>
       </c>
+      <c r="CV1" s="1" t="n">
+        <v>20260123</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32575,6 +32991,9 @@
       <c r="CU2" t="n">
         <v>13945</v>
       </c>
+      <c r="CV2" t="n">
+        <v>15020</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32878,6 +33297,9 @@
       <c r="CU3" t="n">
         <v>72025</v>
       </c>
+      <c r="CV3" t="n">
+        <v>72200</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -33181,6 +33603,9 @@
       <c r="CU4" t="n">
         <v>17165</v>
       </c>
+      <c r="CV4" t="n">
+        <v>18465</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -33484,6 +33909,9 @@
       <c r="CU5" t="n">
         <v>16795</v>
       </c>
+      <c r="CV5" t="n">
+        <v>16795</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -33787,6 +34215,9 @@
       <c r="CU6" t="n">
         <v>20895</v>
       </c>
+      <c r="CV6" t="n">
+        <v>21000</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -34090,6 +34521,9 @@
       <c r="CU7" t="n">
         <v>24805</v>
       </c>
+      <c r="CV7" t="n">
+        <v>24765</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -34393,6 +34827,9 @@
       <c r="CU8" t="n">
         <v>24275</v>
       </c>
+      <c r="CV8" t="n">
+        <v>24450</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -34696,6 +35133,9 @@
       <c r="CU9" t="n">
         <v>1628</v>
       </c>
+      <c r="CV9" t="n">
+        <v>1618</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34999,6 +35439,9 @@
       <c r="CU10" t="n">
         <v>18500</v>
       </c>
+      <c r="CV10" t="n">
+        <v>18700</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -35302,6 +35745,9 @@
       <c r="CU11" t="n">
         <v>5690</v>
       </c>
+      <c r="CV11" t="n">
+        <v>5720</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -35605,6 +36051,9 @@
       <c r="CU12" t="n">
         <v>6035</v>
       </c>
+      <c r="CV12" t="n">
+        <v>6050</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35908,6 +36357,9 @@
       <c r="CU13" t="n">
         <v>6085</v>
       </c>
+      <c r="CV13" t="n">
+        <v>6095</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36211,6 +36663,9 @@
       <c r="CU14" t="n">
         <v>1767</v>
       </c>
+      <c r="CV14" t="n">
+        <v>1755</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36514,6 +36969,9 @@
       <c r="CU15" t="n">
         <v>17705</v>
       </c>
+      <c r="CV15" t="n">
+        <v>18600</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -36817,6 +37275,9 @@
       <c r="CU16" t="n">
         <v>11750</v>
       </c>
+      <c r="CV16" t="n">
+        <v>11700</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37120,6 +37581,9 @@
       <c r="CU17" t="n">
         <v>6720</v>
       </c>
+      <c r="CV17" t="n">
+        <v>6670</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -37423,6 +37887,9 @@
       <c r="CU18" t="n">
         <v>19610</v>
       </c>
+      <c r="CV18" t="n">
+        <v>19875</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -37725,6 +38192,9 @@
       </c>
       <c r="CU19" t="n">
         <v>14850</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>15890</v>
       </c>
     </row>
   </sheetData>
@@ -37738,7 +38208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU19"/>
+  <dimension ref="A1:CV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37840,6 +38310,7 @@
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
+    <col width="12" customWidth="1" min="100" max="100"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38144,6 +38615,9 @@
       <c r="CU1" s="1" t="n">
         <v>20260122</v>
       </c>
+      <c r="CV1" s="1" t="n">
+        <v>20260123</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -38447,6 +38921,9 @@
       <c r="CU2" t="n">
         <v>631089</v>
       </c>
+      <c r="CV2" t="n">
+        <v>903869</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38750,6 +39227,9 @@
       <c r="CU3" t="n">
         <v>1597516</v>
       </c>
+      <c r="CV3" t="n">
+        <v>1358170</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -39053,6 +39533,9 @@
       <c r="CU4" t="n">
         <v>479179</v>
       </c>
+      <c r="CV4" t="n">
+        <v>626655</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -39356,6 +39839,9 @@
       <c r="CU5" t="n">
         <v>190204</v>
       </c>
+      <c r="CV5" t="n">
+        <v>223762</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -39659,6 +40145,9 @@
       <c r="CU6" t="n">
         <v>5040216</v>
       </c>
+      <c r="CV6" t="n">
+        <v>3328998</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -39962,6 +40451,9 @@
       <c r="CU7" t="n">
         <v>3458993</v>
       </c>
+      <c r="CV7" t="n">
+        <v>4128682</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40265,6 +40757,9 @@
       <c r="CU8" t="n">
         <v>14107305</v>
       </c>
+      <c r="CV8" t="n">
+        <v>12730031</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -40568,6 +41063,9 @@
       <c r="CU9" t="n">
         <v>18925878</v>
       </c>
+      <c r="CV9" t="n">
+        <v>18111191</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -40871,6 +41369,9 @@
       <c r="CU10" t="n">
         <v>941524</v>
       </c>
+      <c r="CV10" t="n">
+        <v>1018856</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -41174,6 +41675,9 @@
       <c r="CU11" t="n">
         <v>1955450</v>
       </c>
+      <c r="CV11" t="n">
+        <v>1366207</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -41477,6 +41981,9 @@
       <c r="CU12" t="n">
         <v>5924784</v>
       </c>
+      <c r="CV12" t="n">
+        <v>5094276</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -41780,6 +42287,9 @@
       <c r="CU13" t="n">
         <v>14088244</v>
       </c>
+      <c r="CV13" t="n">
+        <v>10648476</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -42083,6 +42593,9 @@
       <c r="CU14" t="n">
         <v>128917212</v>
       </c>
+      <c r="CV14" t="n">
+        <v>107003251</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42386,6 +42899,9 @@
       <c r="CU15" t="n">
         <v>3244449</v>
       </c>
+      <c r="CV15" t="n">
+        <v>3598386</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -42689,6 +43205,9 @@
       <c r="CU16" t="n">
         <v>950159</v>
       </c>
+      <c r="CV16" t="n">
+        <v>1180798</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42992,6 +43511,9 @@
       <c r="CU17" t="n">
         <v>230067</v>
       </c>
+      <c r="CV17" t="n">
+        <v>262572</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -43295,6 +43817,9 @@
       <c r="CU18" t="n">
         <v>158597</v>
       </c>
+      <c r="CV18" t="n">
+        <v>52784</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43597,6 +44122,9 @@
       </c>
       <c r="CU19" t="n">
         <v>122803</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>78548</v>
       </c>
     </row>
   </sheetData>
@@ -43610,7 +44138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB19"/>
+  <dimension ref="A1:CC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -43693,6 +44221,7 @@
     <col width="10" customWidth="1" min="78" max="78"/>
     <col width="10" customWidth="1" min="79" max="79"/>
     <col width="10" customWidth="1" min="80" max="80"/>
+    <col width="10" customWidth="1" min="81" max="81"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43940,6 +44469,9 @@
       <c r="CB1" s="1" t="n">
         <v>20260122</v>
       </c>
+      <c r="CC1" s="1" t="n">
+        <v>20260123</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -44186,6 +44718,9 @@
       <c r="CB2" t="n">
         <v>12</v>
       </c>
+      <c r="CC2" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -44432,6 +44967,9 @@
       <c r="CB3" t="n">
         <v>98</v>
       </c>
+      <c r="CC3" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -44678,6 +45216,9 @@
       <c r="CB4" t="n">
         <v>23</v>
       </c>
+      <c r="CC4" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -44924,6 +45465,9 @@
       <c r="CB5" t="n">
         <v>58</v>
       </c>
+      <c r="CC5" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -45170,6 +45714,9 @@
       <c r="CB6" t="n">
         <v>100</v>
       </c>
+      <c r="CC6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -45416,6 +45963,9 @@
       <c r="CB7" t="n">
         <v>99</v>
       </c>
+      <c r="CC7" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -45662,6 +46212,9 @@
       <c r="CB8" t="n">
         <v>100</v>
       </c>
+      <c r="CC8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -45908,6 +46461,9 @@
       <c r="CB9" t="n">
         <v>100</v>
       </c>
+      <c r="CC9" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -46154,6 +46710,9 @@
       <c r="CB10" t="n">
         <v>78</v>
       </c>
+      <c r="CC10" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -46400,6 +46959,9 @@
       <c r="CB11" t="n">
         <v>100</v>
       </c>
+      <c r="CC11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -46646,6 +47208,9 @@
       <c r="CB12" t="n">
         <v>100</v>
       </c>
+      <c r="CC12" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -46892,6 +47457,9 @@
       <c r="CB13" t="n">
         <v>100</v>
       </c>
+      <c r="CC13" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -47138,6 +47706,9 @@
       <c r="CB14" t="n">
         <v>100</v>
       </c>
+      <c r="CC14" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -47384,6 +47955,9 @@
       <c r="CB15" t="n">
         <v>9</v>
       </c>
+      <c r="CC15" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -47630,6 +48204,9 @@
       <c r="CB16" t="n">
         <v>100</v>
       </c>
+      <c r="CC16" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -47876,6 +48453,9 @@
       <c r="CB17" t="n">
         <v>100</v>
       </c>
+      <c r="CC17" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -48122,6 +48702,9 @@
       <c r="CB18" t="n">
         <v>69</v>
       </c>
+      <c r="CC18" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -48367,6 +48950,9 @@
       </c>
       <c r="CB19" t="n">
         <v>9</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -48380,7 +48966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN19"/>
+  <dimension ref="A1:AO19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -48423,6 +49009,7 @@
     <col width="10" customWidth="1" min="38" max="38"/>
     <col width="10" customWidth="1" min="39" max="39"/>
     <col width="10" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -48550,6 +49137,9 @@
       <c r="AN1" s="1" t="n">
         <v>20260122</v>
       </c>
+      <c r="AO1" s="1" t="n">
+        <v>20260123</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -48676,6 +49266,9 @@
       <c r="AN2" t="n">
         <v>11</v>
       </c>
+      <c r="AO2" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -48802,6 +49395,9 @@
       <c r="AN3" t="n">
         <v>99</v>
       </c>
+      <c r="AO3" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -48928,6 +49524,9 @@
       <c r="AN4" t="n">
         <v>23</v>
       </c>
+      <c r="AO4" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -49054,6 +49653,9 @@
       <c r="AN5" t="n">
         <v>69</v>
       </c>
+      <c r="AO5" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -49180,6 +49782,9 @@
       <c r="AN6" t="n">
         <v>100</v>
       </c>
+      <c r="AO6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -49306,6 +49911,9 @@
       <c r="AN7" t="n">
         <v>99</v>
       </c>
+      <c r="AO7" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -49432,6 +50040,9 @@
       <c r="AN8" t="n">
         <v>100</v>
       </c>
+      <c r="AO8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -49558,6 +50169,9 @@
       <c r="AN9" t="n">
         <v>57</v>
       </c>
+      <c r="AO9" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -49684,6 +50298,9 @@
       <c r="AN10" t="n">
         <v>81</v>
       </c>
+      <c r="AO10" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -49810,6 +50427,9 @@
       <c r="AN11" t="n">
         <v>91</v>
       </c>
+      <c r="AO11" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -49936,6 +50556,9 @@
       <c r="AN12" t="n">
         <v>80</v>
       </c>
+      <c r="AO12" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -50062,6 +50685,9 @@
       <c r="AN13" t="n">
         <v>80</v>
       </c>
+      <c r="AO13" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -50188,6 +50814,9 @@
       <c r="AN14" t="n">
         <v>62</v>
       </c>
+      <c r="AO14" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -50314,6 +50943,9 @@
       <c r="AN15" t="n">
         <v>47</v>
       </c>
+      <c r="AO15" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -50440,6 +51072,9 @@
       <c r="AN16" t="n">
         <v>90</v>
       </c>
+      <c r="AO16" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -50566,6 +51201,9 @@
       <c r="AN17" t="n">
         <v>69</v>
       </c>
+      <c r="AO17" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -50692,6 +51330,9 @@
       <c r="AN18" t="n">
         <v>76</v>
       </c>
+      <c r="AO18" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -50817,6 +51458,9 @@
       </c>
       <c r="AN19" t="n">
         <v>43</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -50830,7 +51474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB19"/>
+  <dimension ref="A1:CC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -50913,6 +51557,7 @@
     <col width="10" customWidth="1" min="78" max="78"/>
     <col width="10" customWidth="1" min="79" max="79"/>
     <col width="10" customWidth="1" min="80" max="80"/>
+    <col width="10" customWidth="1" min="81" max="81"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -51160,6 +51805,9 @@
       <c r="CB1" s="1" t="n">
         <v>20260122</v>
       </c>
+      <c r="CC1" s="1" t="n">
+        <v>20260123</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -51406,6 +52054,9 @@
       <c r="CB2" t="n">
         <v>-89</v>
       </c>
+      <c r="CC2" t="n">
+        <v>-14</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -51652,6 +52303,9 @@
       <c r="CB3" t="n">
         <v>46</v>
       </c>
+      <c r="CC3" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -51898,6 +52552,9 @@
       <c r="CB4" t="n">
         <v>-70</v>
       </c>
+      <c r="CC4" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -52144,6 +52801,9 @@
       <c r="CB5" t="n">
         <v>-4</v>
       </c>
+      <c r="CC5" t="n">
+        <v>-10</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -52390,6 +53050,9 @@
       <c r="CB6" t="n">
         <v>52</v>
       </c>
+      <c r="CC6" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -52636,6 +53299,9 @@
       <c r="CB7" t="n">
         <v>48</v>
       </c>
+      <c r="CC7" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -52882,6 +53548,9 @@
       <c r="CB8" t="n">
         <v>46</v>
       </c>
+      <c r="CC8" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -53128,6 +53797,9 @@
       <c r="CB9" t="n">
         <v>125</v>
       </c>
+      <c r="CC9" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -53374,6 +54046,9 @@
       <c r="CB10" t="n">
         <v>27</v>
       </c>
+      <c r="CC10" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -53620,6 +54295,9 @@
       <c r="CB11" t="n">
         <v>129</v>
       </c>
+      <c r="CC11" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -53866,6 +54544,9 @@
       <c r="CB12" t="n">
         <v>122</v>
       </c>
+      <c r="CC12" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -54112,6 +54793,9 @@
       <c r="CB13" t="n">
         <v>126</v>
       </c>
+      <c r="CC13" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -54358,6 +55042,9 @@
       <c r="CB14" t="n">
         <v>142</v>
       </c>
+      <c r="CC14" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -54604,6 +55291,9 @@
       <c r="CB15" t="n">
         <v>-103</v>
       </c>
+      <c r="CC15" t="n">
+        <v>-47</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -54850,6 +55540,9 @@
       <c r="CB16" t="n">
         <v>136</v>
       </c>
+      <c r="CC16" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -55096,6 +55789,9 @@
       <c r="CB17" t="n">
         <v>133</v>
       </c>
+      <c r="CC17" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -55342,6 +56038,9 @@
       <c r="CB18" t="n">
         <v>12</v>
       </c>
+      <c r="CC18" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -55587,6 +56286,9 @@
       </c>
       <c r="CB19" t="n">
         <v>-106</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>-13</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -38922,7 +38922,7 @@
         <v>631089</v>
       </c>
       <c r="CV2" t="n">
-        <v>903869</v>
+        <v>904226</v>
       </c>
     </row>
     <row r="3">
@@ -39228,7 +39228,7 @@
         <v>1597516</v>
       </c>
       <c r="CV3" t="n">
-        <v>1358170</v>
+        <v>1527427</v>
       </c>
     </row>
     <row r="4">
@@ -39534,7 +39534,7 @@
         <v>479179</v>
       </c>
       <c r="CV4" t="n">
-        <v>626655</v>
+        <v>626786</v>
       </c>
     </row>
     <row r="5">
@@ -39840,7 +39840,7 @@
         <v>190204</v>
       </c>
       <c r="CV5" t="n">
-        <v>223762</v>
+        <v>227781</v>
       </c>
     </row>
     <row r="6">
@@ -40146,7 +40146,7 @@
         <v>5040216</v>
       </c>
       <c r="CV6" t="n">
-        <v>3328998</v>
+        <v>3379498</v>
       </c>
     </row>
     <row r="7">
@@ -40452,7 +40452,7 @@
         <v>3458993</v>
       </c>
       <c r="CV7" t="n">
-        <v>4128682</v>
+        <v>4143659</v>
       </c>
     </row>
     <row r="8">
@@ -40758,7 +40758,7 @@
         <v>14107305</v>
       </c>
       <c r="CV8" t="n">
-        <v>12730031</v>
+        <v>12840724</v>
       </c>
     </row>
     <row r="9">
@@ -41064,7 +41064,7 @@
         <v>18925878</v>
       </c>
       <c r="CV9" t="n">
-        <v>18111191</v>
+        <v>18143262</v>
       </c>
     </row>
     <row r="10">
@@ -41370,7 +41370,7 @@
         <v>941524</v>
       </c>
       <c r="CV10" t="n">
-        <v>1018856</v>
+        <v>1019516</v>
       </c>
     </row>
     <row r="11">
@@ -41676,7 +41676,7 @@
         <v>1955450</v>
       </c>
       <c r="CV11" t="n">
-        <v>1366207</v>
+        <v>1366637</v>
       </c>
     </row>
     <row r="12">
@@ -41982,7 +41982,7 @@
         <v>5924784</v>
       </c>
       <c r="CV12" t="n">
-        <v>5094276</v>
+        <v>5096058</v>
       </c>
     </row>
     <row r="13">
@@ -42288,7 +42288,7 @@
         <v>14088244</v>
       </c>
       <c r="CV13" t="n">
-        <v>10648476</v>
+        <v>10652711</v>
       </c>
     </row>
     <row r="14">
@@ -42594,7 +42594,7 @@
         <v>128917212</v>
       </c>
       <c r="CV14" t="n">
-        <v>107003251</v>
+        <v>107281191</v>
       </c>
     </row>
     <row r="15">
@@ -42900,7 +42900,7 @@
         <v>3244449</v>
       </c>
       <c r="CV15" t="n">
-        <v>3598386</v>
+        <v>3598967</v>
       </c>
     </row>
     <row r="16">
@@ -43206,7 +43206,7 @@
         <v>950159</v>
       </c>
       <c r="CV16" t="n">
-        <v>1180798</v>
+        <v>1181219</v>
       </c>
     </row>
     <row r="17">
@@ -43818,7 +43818,7 @@
         <v>158597</v>
       </c>
       <c r="CV18" t="n">
-        <v>52784</v>
+        <v>52826</v>
       </c>
     </row>
     <row r="19">
@@ -44124,7 +44124,7 @@
         <v>122803</v>
       </c>
       <c r="CV19" t="n">
-        <v>78548</v>
+        <v>78637</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -16,6 +16,7 @@
     <sheet name="gap" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="std" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="quant" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="z30" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -14482,6 +14483,4254 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BS19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
+    <col width="10" customWidth="1" min="33" max="33"/>
+    <col width="10" customWidth="1" min="34" max="34"/>
+    <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="10" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
+    <col width="10" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="42" max="42"/>
+    <col width="10" customWidth="1" min="43" max="43"/>
+    <col width="10" customWidth="1" min="44" max="44"/>
+    <col width="10" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="10" customWidth="1" min="47" max="47"/>
+    <col width="10" customWidth="1" min="48" max="48"/>
+    <col width="10" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
+    <col width="10" customWidth="1" min="51" max="51"/>
+    <col width="10" customWidth="1" min="52" max="52"/>
+    <col width="10" customWidth="1" min="53" max="53"/>
+    <col width="10" customWidth="1" min="54" max="54"/>
+    <col width="10" customWidth="1" min="55" max="55"/>
+    <col width="10" customWidth="1" min="56" max="56"/>
+    <col width="10" customWidth="1" min="57" max="57"/>
+    <col width="10" customWidth="1" min="58" max="58"/>
+    <col width="10" customWidth="1" min="59" max="59"/>
+    <col width="10" customWidth="1" min="60" max="60"/>
+    <col width="10" customWidth="1" min="61" max="61"/>
+    <col width="10" customWidth="1" min="62" max="62"/>
+    <col width="10" customWidth="1" min="63" max="63"/>
+    <col width="10" customWidth="1" min="64" max="64"/>
+    <col width="10" customWidth="1" min="65" max="65"/>
+    <col width="10" customWidth="1" min="66" max="66"/>
+    <col width="10" customWidth="1" min="67" max="67"/>
+    <col width="10" customWidth="1" min="68" max="68"/>
+    <col width="10" customWidth="1" min="69" max="69"/>
+    <col width="10" customWidth="1" min="70" max="70"/>
+    <col width="10" customWidth="1" min="71" max="71"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>종목코드</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>20251016</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>20251017</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>20251020</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>20251021</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>20251022</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>20251023</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>20251024</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>20251027</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>20251028</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>20251029</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>20251030</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>20251031</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>20251103</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>20251104</v>
+      </c>
+      <c r="Q1" s="1" t="n">
+        <v>20251105</v>
+      </c>
+      <c r="R1" s="1" t="n">
+        <v>20251106</v>
+      </c>
+      <c r="S1" s="1" t="n">
+        <v>20251107</v>
+      </c>
+      <c r="T1" s="1" t="n">
+        <v>20251110</v>
+      </c>
+      <c r="U1" s="1" t="n">
+        <v>20251111</v>
+      </c>
+      <c r="V1" s="1" t="n">
+        <v>20251112</v>
+      </c>
+      <c r="W1" s="1" t="n">
+        <v>20251113</v>
+      </c>
+      <c r="X1" s="1" t="n">
+        <v>20251114</v>
+      </c>
+      <c r="Y1" s="1" t="n">
+        <v>20251117</v>
+      </c>
+      <c r="Z1" s="1" t="n">
+        <v>20251118</v>
+      </c>
+      <c r="AA1" s="1" t="n">
+        <v>20251119</v>
+      </c>
+      <c r="AB1" s="1" t="n">
+        <v>20251120</v>
+      </c>
+      <c r="AC1" s="1" t="n">
+        <v>20251121</v>
+      </c>
+      <c r="AD1" s="1" t="n">
+        <v>20251124</v>
+      </c>
+      <c r="AE1" s="1" t="n">
+        <v>20251125</v>
+      </c>
+      <c r="AF1" s="1" t="n">
+        <v>20251126</v>
+      </c>
+      <c r="AG1" s="1" t="n">
+        <v>20251127</v>
+      </c>
+      <c r="AH1" s="1" t="n">
+        <v>20251128</v>
+      </c>
+      <c r="AI1" s="1" t="n">
+        <v>20251201</v>
+      </c>
+      <c r="AJ1" s="1" t="n">
+        <v>20251202</v>
+      </c>
+      <c r="AK1" s="1" t="n">
+        <v>20251203</v>
+      </c>
+      <c r="AL1" s="1" t="n">
+        <v>20251204</v>
+      </c>
+      <c r="AM1" s="1" t="n">
+        <v>20251205</v>
+      </c>
+      <c r="AN1" s="1" t="n">
+        <v>20251208</v>
+      </c>
+      <c r="AO1" s="1" t="n">
+        <v>20251209</v>
+      </c>
+      <c r="AP1" s="1" t="n">
+        <v>20251210</v>
+      </c>
+      <c r="AQ1" s="1" t="n">
+        <v>20251211</v>
+      </c>
+      <c r="AR1" s="1" t="n">
+        <v>20251212</v>
+      </c>
+      <c r="AS1" s="1" t="n">
+        <v>20251215</v>
+      </c>
+      <c r="AT1" s="1" t="n">
+        <v>20251216</v>
+      </c>
+      <c r="AU1" s="1" t="n">
+        <v>20251217</v>
+      </c>
+      <c r="AV1" s="1" t="n">
+        <v>20251218</v>
+      </c>
+      <c r="AW1" s="1" t="n">
+        <v>20251219</v>
+      </c>
+      <c r="AX1" s="1" t="n">
+        <v>20251222</v>
+      </c>
+      <c r="AY1" s="1" t="n">
+        <v>20251223</v>
+      </c>
+      <c r="AZ1" s="1" t="n">
+        <v>20251224</v>
+      </c>
+      <c r="BA1" s="1" t="n">
+        <v>20251226</v>
+      </c>
+      <c r="BB1" s="1" t="n">
+        <v>20251229</v>
+      </c>
+      <c r="BC1" s="1" t="n">
+        <v>20251230</v>
+      </c>
+      <c r="BD1" s="1" t="n">
+        <v>20260102</v>
+      </c>
+      <c r="BE1" s="1" t="n">
+        <v>20260105</v>
+      </c>
+      <c r="BF1" s="1" t="n">
+        <v>20260106</v>
+      </c>
+      <c r="BG1" s="1" t="n">
+        <v>20260107</v>
+      </c>
+      <c r="BH1" s="1" t="n">
+        <v>20260108</v>
+      </c>
+      <c r="BI1" s="1" t="n">
+        <v>20260109</v>
+      </c>
+      <c r="BJ1" s="1" t="n">
+        <v>20260112</v>
+      </c>
+      <c r="BK1" s="1" t="n">
+        <v>20260113</v>
+      </c>
+      <c r="BL1" s="1" t="n">
+        <v>20260114</v>
+      </c>
+      <c r="BM1" s="1" t="n">
+        <v>20260115</v>
+      </c>
+      <c r="BN1" s="1" t="n">
+        <v>20260116</v>
+      </c>
+      <c r="BO1" s="1" t="n">
+        <v>20260119</v>
+      </c>
+      <c r="BP1" s="1" t="n">
+        <v>20260120</v>
+      </c>
+      <c r="BQ1" s="1" t="n">
+        <v>20260121</v>
+      </c>
+      <c r="BR1" s="1" t="n">
+        <v>20260122</v>
+      </c>
+      <c r="BS1" s="1" t="n">
+        <v>20260123</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RISE 바이오TOP10액티브</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0000Z0</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G2" t="n">
+        <v>56</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36</v>
+      </c>
+      <c r="I2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J2" t="n">
+        <v>156</v>
+      </c>
+      <c r="K2" t="n">
+        <v>130</v>
+      </c>
+      <c r="L2" t="n">
+        <v>95</v>
+      </c>
+      <c r="M2" t="n">
+        <v>101</v>
+      </c>
+      <c r="N2" t="n">
+        <v>140</v>
+      </c>
+      <c r="O2" t="n">
+        <v>144</v>
+      </c>
+      <c r="P2" t="n">
+        <v>149</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>117</v>
+      </c>
+      <c r="R2" t="n">
+        <v>97</v>
+      </c>
+      <c r="S2" t="n">
+        <v>76</v>
+      </c>
+      <c r="T2" t="n">
+        <v>75</v>
+      </c>
+      <c r="U2" t="n">
+        <v>63</v>
+      </c>
+      <c r="V2" t="n">
+        <v>114</v>
+      </c>
+      <c r="W2" t="n">
+        <v>121</v>
+      </c>
+      <c r="X2" t="n">
+        <v>119</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>116</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>98</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>87</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>71</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>62</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>54</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>57</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>56</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>52</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>66</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-23</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-17</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-28</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-70</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-70</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-39</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>-85</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-112</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-90</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-42</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>-11</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>-29</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>19</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>35</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>70</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>66</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>32</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>-61</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>-46</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>-33</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>-27</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>-37</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>-145</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>-105</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KODEX 반도체</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>091160</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>93</v>
+      </c>
+      <c r="D3" t="n">
+        <v>84</v>
+      </c>
+      <c r="E3" t="n">
+        <v>89</v>
+      </c>
+      <c r="F3" t="n">
+        <v>78</v>
+      </c>
+      <c r="G3" t="n">
+        <v>77</v>
+      </c>
+      <c r="H3" t="n">
+        <v>70</v>
+      </c>
+      <c r="I3" t="n">
+        <v>81</v>
+      </c>
+      <c r="J3" t="n">
+        <v>87</v>
+      </c>
+      <c r="K3" t="n">
+        <v>71</v>
+      </c>
+      <c r="L3" t="n">
+        <v>80</v>
+      </c>
+      <c r="M3" t="n">
+        <v>81</v>
+      </c>
+      <c r="N3" t="n">
+        <v>78</v>
+      </c>
+      <c r="O3" t="n">
+        <v>92</v>
+      </c>
+      <c r="P3" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>56</v>
+      </c>
+      <c r="R3" t="n">
+        <v>60</v>
+      </c>
+      <c r="S3" t="n">
+        <v>42</v>
+      </c>
+      <c r="T3" t="n">
+        <v>53</v>
+      </c>
+      <c r="U3" t="n">
+        <v>59</v>
+      </c>
+      <c r="V3" t="n">
+        <v>55</v>
+      </c>
+      <c r="W3" t="n">
+        <v>50</v>
+      </c>
+      <c r="X3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-80</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-71</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-61</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-42</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-23</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-27</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-17</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-17</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-22</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-66</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-13</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-27</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-32</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>52</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>42</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>92</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>112</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>115</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>165</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>168</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>157</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>129</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>113</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>94</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>85</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>80</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>83</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>81</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>78</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>77</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>58</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>56</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>62</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TIGER 코스닥150바이오테크</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>261070</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>-91</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-93</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-41</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-42</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-45</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-56</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-53</v>
+      </c>
+      <c r="J4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K4" t="n">
+        <v>28</v>
+      </c>
+      <c r="L4" t="n">
+        <v>17</v>
+      </c>
+      <c r="M4" t="n">
+        <v>15</v>
+      </c>
+      <c r="N4" t="n">
+        <v>54</v>
+      </c>
+      <c r="O4" t="n">
+        <v>76</v>
+      </c>
+      <c r="P4" t="n">
+        <v>136</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>88</v>
+      </c>
+      <c r="R4" t="n">
+        <v>71</v>
+      </c>
+      <c r="S4" t="n">
+        <v>52</v>
+      </c>
+      <c r="T4" t="n">
+        <v>58</v>
+      </c>
+      <c r="U4" t="n">
+        <v>38</v>
+      </c>
+      <c r="V4" t="n">
+        <v>134</v>
+      </c>
+      <c r="W4" t="n">
+        <v>131</v>
+      </c>
+      <c r="X4" t="n">
+        <v>117</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>108</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>89</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>71</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>41</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>31</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>41</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>37</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>81</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>74</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>66</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>53</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>49</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-34</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-31</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-34</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-67</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-71</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-41</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-61</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-86</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-86</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-58</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-22</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-19</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>54</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>63</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>31</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-35</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>-29</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>24</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>16</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>-130</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>-74</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RISE 비메모리반도체액티브</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>388420</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>93</v>
+      </c>
+      <c r="D5" t="n">
+        <v>80</v>
+      </c>
+      <c r="E5" t="n">
+        <v>84</v>
+      </c>
+      <c r="F5" t="n">
+        <v>71</v>
+      </c>
+      <c r="G5" t="n">
+        <v>70</v>
+      </c>
+      <c r="H5" t="n">
+        <v>70</v>
+      </c>
+      <c r="I5" t="n">
+        <v>81</v>
+      </c>
+      <c r="J5" t="n">
+        <v>80</v>
+      </c>
+      <c r="K5" t="n">
+        <v>67</v>
+      </c>
+      <c r="L5" t="n">
+        <v>78</v>
+      </c>
+      <c r="M5" t="n">
+        <v>76</v>
+      </c>
+      <c r="N5" t="n">
+        <v>75</v>
+      </c>
+      <c r="O5" t="n">
+        <v>77</v>
+      </c>
+      <c r="P5" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>41</v>
+      </c>
+      <c r="R5" t="n">
+        <v>47</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="n">
+        <v>34</v>
+      </c>
+      <c r="U5" t="n">
+        <v>41</v>
+      </c>
+      <c r="V5" t="n">
+        <v>44</v>
+      </c>
+      <c r="W5" t="n">
+        <v>37</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-9</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-27</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-19</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-116</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-99</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-56</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-43</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-28</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-27</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-43</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-37</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-47</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-22</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-27</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-87</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-122</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-52</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-73</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-80</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-28</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-28</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>46</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>57</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>138</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>144</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>134</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>103</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>75</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>58</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>72</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>76</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>63</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>29</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KODEX AI 반도체</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>395160</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>97</v>
+      </c>
+      <c r="D6" t="n">
+        <v>90</v>
+      </c>
+      <c r="E6" t="n">
+        <v>92</v>
+      </c>
+      <c r="F6" t="n">
+        <v>80</v>
+      </c>
+      <c r="G6" t="n">
+        <v>80</v>
+      </c>
+      <c r="H6" t="n">
+        <v>71</v>
+      </c>
+      <c r="I6" t="n">
+        <v>86</v>
+      </c>
+      <c r="J6" t="n">
+        <v>92</v>
+      </c>
+      <c r="K6" t="n">
+        <v>77</v>
+      </c>
+      <c r="L6" t="n">
+        <v>88</v>
+      </c>
+      <c r="M6" t="n">
+        <v>88</v>
+      </c>
+      <c r="N6" t="n">
+        <v>86</v>
+      </c>
+      <c r="O6" t="n">
+        <v>97</v>
+      </c>
+      <c r="P6" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>54</v>
+      </c>
+      <c r="R6" t="n">
+        <v>56</v>
+      </c>
+      <c r="S6" t="n">
+        <v>37</v>
+      </c>
+      <c r="T6" t="n">
+        <v>57</v>
+      </c>
+      <c r="U6" t="n">
+        <v>61</v>
+      </c>
+      <c r="V6" t="n">
+        <v>59</v>
+      </c>
+      <c r="W6" t="n">
+        <v>53</v>
+      </c>
+      <c r="X6" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-46</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-43</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-17</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>53</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>39</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>51</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>33</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-24</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-70</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-37</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-40</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>33</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>83</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>104</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>107</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>160</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>166</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>152</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>127</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>111</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>90</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>81</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>80</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>84</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>85</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>82</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>77</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>58</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>57</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>66</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HANARO Fn K-반도체</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>395270</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>95</v>
+      </c>
+      <c r="D7" t="n">
+        <v>89</v>
+      </c>
+      <c r="E7" t="n">
+        <v>92</v>
+      </c>
+      <c r="F7" t="n">
+        <v>84</v>
+      </c>
+      <c r="G7" t="n">
+        <v>80</v>
+      </c>
+      <c r="H7" t="n">
+        <v>75</v>
+      </c>
+      <c r="I7" t="n">
+        <v>85</v>
+      </c>
+      <c r="J7" t="n">
+        <v>91</v>
+      </c>
+      <c r="K7" t="n">
+        <v>78</v>
+      </c>
+      <c r="L7" t="n">
+        <v>85</v>
+      </c>
+      <c r="M7" t="n">
+        <v>85</v>
+      </c>
+      <c r="N7" t="n">
+        <v>86</v>
+      </c>
+      <c r="O7" t="n">
+        <v>98</v>
+      </c>
+      <c r="P7" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>58</v>
+      </c>
+      <c r="R7" t="n">
+        <v>58</v>
+      </c>
+      <c r="S7" t="n">
+        <v>39</v>
+      </c>
+      <c r="T7" t="n">
+        <v>53</v>
+      </c>
+      <c r="U7" t="n">
+        <v>61</v>
+      </c>
+      <c r="V7" t="n">
+        <v>54</v>
+      </c>
+      <c r="W7" t="n">
+        <v>51</v>
+      </c>
+      <c r="X7" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-40</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-21</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>45</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>63</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>56</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>61</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>43</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>49</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>56</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>55</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>93</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>112</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>108</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>156</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>160</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>147</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>131</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>117</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>98</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>91</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>86</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>84</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>83</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>82</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>79</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>60</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>60</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>64</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TIGER 반도체 TOP10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>396500</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>99</v>
+      </c>
+      <c r="D8" t="n">
+        <v>90</v>
+      </c>
+      <c r="E8" t="n">
+        <v>92</v>
+      </c>
+      <c r="F8" t="n">
+        <v>82</v>
+      </c>
+      <c r="G8" t="n">
+        <v>79</v>
+      </c>
+      <c r="H8" t="n">
+        <v>72</v>
+      </c>
+      <c r="I8" t="n">
+        <v>80</v>
+      </c>
+      <c r="J8" t="n">
+        <v>86</v>
+      </c>
+      <c r="K8" t="n">
+        <v>72</v>
+      </c>
+      <c r="L8" t="n">
+        <v>77</v>
+      </c>
+      <c r="M8" t="n">
+        <v>80</v>
+      </c>
+      <c r="N8" t="n">
+        <v>76</v>
+      </c>
+      <c r="O8" t="n">
+        <v>87</v>
+      </c>
+      <c r="P8" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>52</v>
+      </c>
+      <c r="R8" t="n">
+        <v>51</v>
+      </c>
+      <c r="S8" t="n">
+        <v>34</v>
+      </c>
+      <c r="T8" t="n">
+        <v>53</v>
+      </c>
+      <c r="U8" t="n">
+        <v>59</v>
+      </c>
+      <c r="V8" t="n">
+        <v>55</v>
+      </c>
+      <c r="W8" t="n">
+        <v>55</v>
+      </c>
+      <c r="X8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-73</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-73</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-26</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-16</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-22</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-15</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-21</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>-62</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-21</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>-26</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>51</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>61</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>61</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>105</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>127</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>123</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>169</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>172</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>158</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>134</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>118</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>97</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>86</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>79</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>81</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>79</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>78</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>74</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>59</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>61</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>62</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TIGER 2차전지TOP10레버리지</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>412570</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>217</v>
+      </c>
+      <c r="D9" t="n">
+        <v>201</v>
+      </c>
+      <c r="E9" t="n">
+        <v>165</v>
+      </c>
+      <c r="F9" t="n">
+        <v>146</v>
+      </c>
+      <c r="G9" t="n">
+        <v>152</v>
+      </c>
+      <c r="H9" t="n">
+        <v>119</v>
+      </c>
+      <c r="I9" t="n">
+        <v>152</v>
+      </c>
+      <c r="J9" t="n">
+        <v>126</v>
+      </c>
+      <c r="K9" t="n">
+        <v>122</v>
+      </c>
+      <c r="L9" t="n">
+        <v>116</v>
+      </c>
+      <c r="M9" t="n">
+        <v>84</v>
+      </c>
+      <c r="N9" t="n">
+        <v>64</v>
+      </c>
+      <c r="O9" t="n">
+        <v>62</v>
+      </c>
+      <c r="P9" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>41</v>
+      </c>
+      <c r="R9" t="n">
+        <v>41</v>
+      </c>
+      <c r="S9" t="n">
+        <v>23</v>
+      </c>
+      <c r="T9" t="n">
+        <v>33</v>
+      </c>
+      <c r="U9" t="n">
+        <v>35</v>
+      </c>
+      <c r="V9" t="n">
+        <v>44</v>
+      </c>
+      <c r="W9" t="n">
+        <v>52</v>
+      </c>
+      <c r="X9" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-39</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-60</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-66</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-26</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-34</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-56</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-53</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-49</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-42</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-54</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-33</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>-58</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-46</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-110</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-102</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-77</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-74</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-65</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-82</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-80</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-100</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-107</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>-79</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-62</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-68</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-72</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-76</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-48</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-10</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-13</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>37</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>84</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SOL AI반도체소부장</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>455850</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>91</v>
+      </c>
+      <c r="D10" t="n">
+        <v>78</v>
+      </c>
+      <c r="E10" t="n">
+        <v>80</v>
+      </c>
+      <c r="F10" t="n">
+        <v>69</v>
+      </c>
+      <c r="G10" t="n">
+        <v>72</v>
+      </c>
+      <c r="H10" t="n">
+        <v>65</v>
+      </c>
+      <c r="I10" t="n">
+        <v>80</v>
+      </c>
+      <c r="J10" t="n">
+        <v>80</v>
+      </c>
+      <c r="K10" t="n">
+        <v>73</v>
+      </c>
+      <c r="L10" t="n">
+        <v>84</v>
+      </c>
+      <c r="M10" t="n">
+        <v>80</v>
+      </c>
+      <c r="N10" t="n">
+        <v>84</v>
+      </c>
+      <c r="O10" t="n">
+        <v>82</v>
+      </c>
+      <c r="P10" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>46</v>
+      </c>
+      <c r="R10" t="n">
+        <v>52</v>
+      </c>
+      <c r="S10" t="n">
+        <v>17</v>
+      </c>
+      <c r="T10" t="n">
+        <v>44</v>
+      </c>
+      <c r="U10" t="n">
+        <v>46</v>
+      </c>
+      <c r="V10" t="n">
+        <v>45</v>
+      </c>
+      <c r="W10" t="n">
+        <v>46</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-91</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-80</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>33</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-32</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-69</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-118</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-62</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-99</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-95</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-28</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-31</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-49</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-10</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-9</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>134</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>140</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>97</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>81</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>53</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>46</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>69</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>79</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>79</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>73</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>66</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>44</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>34</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>45</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SOL 2차전지소부장Fn</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>455860</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>208</v>
+      </c>
+      <c r="D11" t="n">
+        <v>210</v>
+      </c>
+      <c r="E11" t="n">
+        <v>168</v>
+      </c>
+      <c r="F11" t="n">
+        <v>142</v>
+      </c>
+      <c r="G11" t="n">
+        <v>150</v>
+      </c>
+      <c r="H11" t="n">
+        <v>117</v>
+      </c>
+      <c r="I11" t="n">
+        <v>136</v>
+      </c>
+      <c r="J11" t="n">
+        <v>123</v>
+      </c>
+      <c r="K11" t="n">
+        <v>112</v>
+      </c>
+      <c r="L11" t="n">
+        <v>97</v>
+      </c>
+      <c r="M11" t="n">
+        <v>71</v>
+      </c>
+      <c r="N11" t="n">
+        <v>60</v>
+      </c>
+      <c r="O11" t="n">
+        <v>63</v>
+      </c>
+      <c r="P11" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>45</v>
+      </c>
+      <c r="R11" t="n">
+        <v>44</v>
+      </c>
+      <c r="S11" t="n">
+        <v>32</v>
+      </c>
+      <c r="T11" t="n">
+        <v>38</v>
+      </c>
+      <c r="U11" t="n">
+        <v>39</v>
+      </c>
+      <c r="V11" t="n">
+        <v>42</v>
+      </c>
+      <c r="W11" t="n">
+        <v>53</v>
+      </c>
+      <c r="X11" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-25</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-49</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-52</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-18</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-27</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>93</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>105</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>63</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>66</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>64</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-47</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-48</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-33</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-29</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>-35</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-32</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-65</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-86</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-66</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-52</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-63</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-72</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-76</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-42</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>-15</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-28</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>12</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>31</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>19</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>81</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KODEX2차전지핵심소재10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>461950</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>217</v>
+      </c>
+      <c r="D12" t="n">
+        <v>212</v>
+      </c>
+      <c r="E12" t="n">
+        <v>169</v>
+      </c>
+      <c r="F12" t="n">
+        <v>143</v>
+      </c>
+      <c r="G12" t="n">
+        <v>148</v>
+      </c>
+      <c r="H12" t="n">
+        <v>117</v>
+      </c>
+      <c r="I12" t="n">
+        <v>136</v>
+      </c>
+      <c r="J12" t="n">
+        <v>126</v>
+      </c>
+      <c r="K12" t="n">
+        <v>113</v>
+      </c>
+      <c r="L12" t="n">
+        <v>99</v>
+      </c>
+      <c r="M12" t="n">
+        <v>70</v>
+      </c>
+      <c r="N12" t="n">
+        <v>60</v>
+      </c>
+      <c r="O12" t="n">
+        <v>63</v>
+      </c>
+      <c r="P12" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>48</v>
+      </c>
+      <c r="R12" t="n">
+        <v>46</v>
+      </c>
+      <c r="S12" t="n">
+        <v>32</v>
+      </c>
+      <c r="T12" t="n">
+        <v>36</v>
+      </c>
+      <c r="U12" t="n">
+        <v>37</v>
+      </c>
+      <c r="V12" t="n">
+        <v>38</v>
+      </c>
+      <c r="W12" t="n">
+        <v>49</v>
+      </c>
+      <c r="X12" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-25</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-58</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-22</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-25</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>93</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>102</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>87</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>68</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>68</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-42</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-47</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-33</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-37</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-28</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-35</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-34</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-70</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-87</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-69</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-53</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>-58</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-65</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-71</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-36</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>-18</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-28</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>65</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TIGER 2차전지소재Fn</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>462010</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>215</v>
+      </c>
+      <c r="D13" t="n">
+        <v>214</v>
+      </c>
+      <c r="E13" t="n">
+        <v>170</v>
+      </c>
+      <c r="F13" t="n">
+        <v>140</v>
+      </c>
+      <c r="G13" t="n">
+        <v>149</v>
+      </c>
+      <c r="H13" t="n">
+        <v>116</v>
+      </c>
+      <c r="I13" t="n">
+        <v>135</v>
+      </c>
+      <c r="J13" t="n">
+        <v>124</v>
+      </c>
+      <c r="K13" t="n">
+        <v>113</v>
+      </c>
+      <c r="L13" t="n">
+        <v>95</v>
+      </c>
+      <c r="M13" t="n">
+        <v>71</v>
+      </c>
+      <c r="N13" t="n">
+        <v>61</v>
+      </c>
+      <c r="O13" t="n">
+        <v>67</v>
+      </c>
+      <c r="P13" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>48</v>
+      </c>
+      <c r="R13" t="n">
+        <v>48</v>
+      </c>
+      <c r="S13" t="n">
+        <v>31</v>
+      </c>
+      <c r="T13" t="n">
+        <v>36</v>
+      </c>
+      <c r="U13" t="n">
+        <v>39</v>
+      </c>
+      <c r="V13" t="n">
+        <v>41</v>
+      </c>
+      <c r="W13" t="n">
+        <v>47</v>
+      </c>
+      <c r="X13" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-28</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-53</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-59</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-13</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-23</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-27</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>114</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>99</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>73</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>73</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-24</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-29</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-19</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-12</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-18</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-17</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-49</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-71</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-54</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-43</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>-51</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-58</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-75</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-38</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>-22</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>-9</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-32</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>63</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KODEX 2차전지산업레버리지</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>462330</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>214</v>
+      </c>
+      <c r="D14" t="n">
+        <v>207</v>
+      </c>
+      <c r="E14" t="n">
+        <v>167</v>
+      </c>
+      <c r="F14" t="n">
+        <v>141</v>
+      </c>
+      <c r="G14" t="n">
+        <v>151</v>
+      </c>
+      <c r="H14" t="n">
+        <v>117</v>
+      </c>
+      <c r="I14" t="n">
+        <v>148</v>
+      </c>
+      <c r="J14" t="n">
+        <v>129</v>
+      </c>
+      <c r="K14" t="n">
+        <v>125</v>
+      </c>
+      <c r="L14" t="n">
+        <v>114</v>
+      </c>
+      <c r="M14" t="n">
+        <v>81</v>
+      </c>
+      <c r="N14" t="n">
+        <v>67</v>
+      </c>
+      <c r="O14" t="n">
+        <v>69</v>
+      </c>
+      <c r="P14" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>48</v>
+      </c>
+      <c r="R14" t="n">
+        <v>46</v>
+      </c>
+      <c r="S14" t="n">
+        <v>29</v>
+      </c>
+      <c r="T14" t="n">
+        <v>38</v>
+      </c>
+      <c r="U14" t="n">
+        <v>40</v>
+      </c>
+      <c r="V14" t="n">
+        <v>43</v>
+      </c>
+      <c r="W14" t="n">
+        <v>55</v>
+      </c>
+      <c r="X14" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-36</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-60</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-64</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-24</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-31</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-46</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-37</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-33</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-31</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-43</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-25</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-41</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-102</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-93</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-69</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-70</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-60</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-75</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-71</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-95</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>-77</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-63</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-71</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-74</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-77</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-46</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>-25</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>-12</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-27</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>81</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TIMEFOLIO K바이오액티브</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>463050</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>-62</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-73</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-42</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-48</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-54</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-63</v>
+      </c>
+      <c r="J15" t="n">
+        <v>84</v>
+      </c>
+      <c r="K15" t="n">
+        <v>77</v>
+      </c>
+      <c r="L15" t="n">
+        <v>40</v>
+      </c>
+      <c r="M15" t="n">
+        <v>55</v>
+      </c>
+      <c r="N15" t="n">
+        <v>133</v>
+      </c>
+      <c r="O15" t="n">
+        <v>137</v>
+      </c>
+      <c r="P15" t="n">
+        <v>158</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>119</v>
+      </c>
+      <c r="R15" t="n">
+        <v>101</v>
+      </c>
+      <c r="S15" t="n">
+        <v>74</v>
+      </c>
+      <c r="T15" t="n">
+        <v>70</v>
+      </c>
+      <c r="U15" t="n">
+        <v>50</v>
+      </c>
+      <c r="V15" t="n">
+        <v>136</v>
+      </c>
+      <c r="W15" t="n">
+        <v>130</v>
+      </c>
+      <c r="X15" t="n">
+        <v>124</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>124</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>99</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>79</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>89</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>78</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>51</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>71</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>62</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>78</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>73</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>69</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>33</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-22</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-56</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-50</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>53</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>37</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>58</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>87</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>87</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>42</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-32</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>-152</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>-116</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>-48</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>RISE 2차전지TOP10</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>465330</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>217</v>
+      </c>
+      <c r="D16" t="n">
+        <v>205</v>
+      </c>
+      <c r="E16" t="n">
+        <v>165</v>
+      </c>
+      <c r="F16" t="n">
+        <v>140</v>
+      </c>
+      <c r="G16" t="n">
+        <v>139</v>
+      </c>
+      <c r="H16" t="n">
+        <v>109</v>
+      </c>
+      <c r="I16" t="n">
+        <v>140</v>
+      </c>
+      <c r="J16" t="n">
+        <v>121</v>
+      </c>
+      <c r="K16" t="n">
+        <v>117</v>
+      </c>
+      <c r="L16" t="n">
+        <v>106</v>
+      </c>
+      <c r="M16" t="n">
+        <v>80</v>
+      </c>
+      <c r="N16" t="n">
+        <v>67</v>
+      </c>
+      <c r="O16" t="n">
+        <v>71</v>
+      </c>
+      <c r="P16" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>51</v>
+      </c>
+      <c r="R16" t="n">
+        <v>49</v>
+      </c>
+      <c r="S16" t="n">
+        <v>32</v>
+      </c>
+      <c r="T16" t="n">
+        <v>37</v>
+      </c>
+      <c r="U16" t="n">
+        <v>40</v>
+      </c>
+      <c r="V16" t="n">
+        <v>44</v>
+      </c>
+      <c r="W16" t="n">
+        <v>50</v>
+      </c>
+      <c r="X16" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-29</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-52</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-57</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-19</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-25</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-37</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-18</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-33</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>57</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>67</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>62</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>49</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>-13</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>-67</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>-70</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-47</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-41</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>-51</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-49</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>-82</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-96</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>-67</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-49</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-57</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>-65</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>-74</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>-36</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>-14</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>-19</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>17</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>43</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>28</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>98</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BNK2차전지양극재</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>466810</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>210</v>
+      </c>
+      <c r="D17" t="n">
+        <v>202</v>
+      </c>
+      <c r="E17" t="n">
+        <v>162</v>
+      </c>
+      <c r="F17" t="n">
+        <v>141</v>
+      </c>
+      <c r="G17" t="n">
+        <v>143</v>
+      </c>
+      <c r="H17" t="n">
+        <v>110</v>
+      </c>
+      <c r="I17" t="n">
+        <v>135</v>
+      </c>
+      <c r="J17" t="n">
+        <v>121</v>
+      </c>
+      <c r="K17" t="n">
+        <v>114</v>
+      </c>
+      <c r="L17" t="n">
+        <v>101</v>
+      </c>
+      <c r="M17" t="n">
+        <v>73</v>
+      </c>
+      <c r="N17" t="n">
+        <v>62</v>
+      </c>
+      <c r="O17" t="n">
+        <v>62</v>
+      </c>
+      <c r="P17" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>47</v>
+      </c>
+      <c r="R17" t="n">
+        <v>45</v>
+      </c>
+      <c r="S17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T17" t="n">
+        <v>35</v>
+      </c>
+      <c r="U17" t="n">
+        <v>37</v>
+      </c>
+      <c r="V17" t="n">
+        <v>40</v>
+      </c>
+      <c r="W17" t="n">
+        <v>54</v>
+      </c>
+      <c r="X17" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-33</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-60</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-66</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-23</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-31</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-18</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-16</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-31</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-17</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>52</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>63</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>57</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>43</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>45</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-17</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-71</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-69</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-51</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-51</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-45</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-58</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>-57</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>-89</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-101</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>-75</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>-58</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-64</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>-71</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>-74</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>-46</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>-9</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>-25</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>-13</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>-27</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>26</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>72</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SOL반도체후공정</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>475310</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>106</v>
+      </c>
+      <c r="D18" t="n">
+        <v>89</v>
+      </c>
+      <c r="E18" t="n">
+        <v>90</v>
+      </c>
+      <c r="F18" t="n">
+        <v>74</v>
+      </c>
+      <c r="G18" t="n">
+        <v>78</v>
+      </c>
+      <c r="H18" t="n">
+        <v>77</v>
+      </c>
+      <c r="I18" t="n">
+        <v>90</v>
+      </c>
+      <c r="J18" t="n">
+        <v>90</v>
+      </c>
+      <c r="K18" t="n">
+        <v>85</v>
+      </c>
+      <c r="L18" t="n">
+        <v>86</v>
+      </c>
+      <c r="M18" t="n">
+        <v>82</v>
+      </c>
+      <c r="N18" t="n">
+        <v>86</v>
+      </c>
+      <c r="O18" t="n">
+        <v>86</v>
+      </c>
+      <c r="P18" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>49</v>
+      </c>
+      <c r="R18" t="n">
+        <v>59</v>
+      </c>
+      <c r="S18" t="n">
+        <v>28</v>
+      </c>
+      <c r="T18" t="n">
+        <v>62</v>
+      </c>
+      <c r="U18" t="n">
+        <v>64</v>
+      </c>
+      <c r="V18" t="n">
+        <v>64</v>
+      </c>
+      <c r="W18" t="n">
+        <v>59</v>
+      </c>
+      <c r="X18" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>78</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>45</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>64</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>69</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>86</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>89</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>89</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>66</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>41</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>52</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>49</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>-45</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-96</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>-52</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-75</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>-83</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>-17</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>-26</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>-24</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>94</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>131</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>140</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>104</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>85</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>67</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>53</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>67</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>81</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>90</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>76</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>66</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>40</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>24</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>33</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HANARO 바이오코리아액티브</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>498050</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>-54</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-64</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-33</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-47</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-33</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-53</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-55</v>
+      </c>
+      <c r="J19" t="n">
+        <v>64</v>
+      </c>
+      <c r="K19" t="n">
+        <v>63</v>
+      </c>
+      <c r="L19" t="n">
+        <v>34</v>
+      </c>
+      <c r="M19" t="n">
+        <v>25</v>
+      </c>
+      <c r="N19" t="n">
+        <v>87</v>
+      </c>
+      <c r="O19" t="n">
+        <v>101</v>
+      </c>
+      <c r="P19" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>99</v>
+      </c>
+      <c r="R19" t="n">
+        <v>90</v>
+      </c>
+      <c r="S19" t="n">
+        <v>63</v>
+      </c>
+      <c r="T19" t="n">
+        <v>59</v>
+      </c>
+      <c r="U19" t="n">
+        <v>47</v>
+      </c>
+      <c r="V19" t="n">
+        <v>149</v>
+      </c>
+      <c r="W19" t="n">
+        <v>139</v>
+      </c>
+      <c r="X19" t="n">
+        <v>135</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>125</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>101</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>82</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>89</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>74</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>59</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>57</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>77</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>86</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>76</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>72</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>69</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>35</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>51</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>49</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-38</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>-36</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>-16</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>-7</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>52</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>29</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>85</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>97</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>43</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>-16</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>-59</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>-46</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>-22</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>-15</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>-174</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>-15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO19"/>
+  <dimension ref="A1:AP19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -754,6 +754,7 @@
     <col width="10" customWidth="1" min="39" max="39"/>
     <col width="10" customWidth="1" min="40" max="40"/>
     <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -884,6 +885,9 @@
       <c r="AO1" s="1" t="n">
         <v>20260123</v>
       </c>
+      <c r="AP1" s="1" t="n">
+        <v>20260126</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1013,6 +1017,9 @@
       <c r="AO2" t="n">
         <v>-20</v>
       </c>
+      <c r="AP2" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1142,6 +1149,9 @@
       <c r="AO3" t="n">
         <v>94</v>
       </c>
+      <c r="AP3" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1271,6 +1281,9 @@
       <c r="AO4" t="n">
         <v>27</v>
       </c>
+      <c r="AP4" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1400,6 +1413,9 @@
       <c r="AO5" t="n">
         <v>30</v>
       </c>
+      <c r="AP5" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1529,6 +1545,9 @@
       <c r="AO6" t="n">
         <v>100</v>
       </c>
+      <c r="AP6" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1658,6 +1677,9 @@
       <c r="AO7" t="n">
         <v>93</v>
       </c>
+      <c r="AP7" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1787,6 +1809,9 @@
       <c r="AO8" t="n">
         <v>97</v>
       </c>
+      <c r="AP8" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1916,6 +1941,9 @@
       <c r="AO9" t="n">
         <v>32</v>
       </c>
+      <c r="AP9" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2045,6 +2073,9 @@
       <c r="AO10" t="n">
         <v>77</v>
       </c>
+      <c r="AP10" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2174,6 +2205,9 @@
       <c r="AO11" t="n">
         <v>87</v>
       </c>
+      <c r="AP11" t="n">
+        <v>155</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2303,6 +2337,9 @@
       <c r="AO12" t="n">
         <v>64</v>
       </c>
+      <c r="AP12" t="n">
+        <v>138</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2432,6 +2469,9 @@
       <c r="AO13" t="n">
         <v>71</v>
       </c>
+      <c r="AP13" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2561,6 +2601,9 @@
       <c r="AO14" t="n">
         <v>36</v>
       </c>
+      <c r="AP14" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2690,6 +2733,9 @@
       <c r="AO15" t="n">
         <v>-7</v>
       </c>
+      <c r="AP15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2819,6 +2865,9 @@
       <c r="AO16" t="n">
         <v>79</v>
       </c>
+      <c r="AP16" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2948,6 +2997,9 @@
       <c r="AO17" t="n">
         <v>43</v>
       </c>
+      <c r="AP17" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3077,6 +3129,9 @@
       <c r="AO18" t="n">
         <v>70</v>
       </c>
+      <c r="AP18" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3205,6 +3260,9 @@
       </c>
       <c r="AO19" t="n">
         <v>13</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -3218,7 +3276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC19"/>
+  <dimension ref="A1:CD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3302,6 +3360,7 @@
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
+    <col width="12" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3710,6 +3769,11 @@
           <t>20260123</t>
         </is>
       </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>20260126</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3959,6 +4023,9 @@
       <c r="CC2" t="n">
         <v>99</v>
       </c>
+      <c r="CD2" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4208,6 +4275,9 @@
       <c r="CC3" t="n">
         <v>106</v>
       </c>
+      <c r="CD3" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4457,6 +4527,9 @@
       <c r="CC4" t="n">
         <v>102</v>
       </c>
+      <c r="CD4" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4706,6 +4779,9 @@
       <c r="CC5" t="n">
         <v>99</v>
       </c>
+      <c r="CD5" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4955,6 +5031,9 @@
       <c r="CC6" t="n">
         <v>106</v>
       </c>
+      <c r="CD6" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5204,6 +5283,9 @@
       <c r="CC7" t="n">
         <v>106</v>
       </c>
+      <c r="CD7" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5453,6 +5535,9 @@
       <c r="CC8" t="n">
         <v>107</v>
       </c>
+      <c r="CD8" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5702,6 +5787,9 @@
       <c r="CC9" t="n">
         <v>121</v>
       </c>
+      <c r="CD9" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5951,6 +6039,9 @@
       <c r="CC10" t="n">
         <v>103</v>
       </c>
+      <c r="CD10" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6200,6 +6291,9 @@
       <c r="CC11" t="n">
         <v>112</v>
       </c>
+      <c r="CD11" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6449,6 +6543,9 @@
       <c r="CC12" t="n">
         <v>111</v>
       </c>
+      <c r="CD12" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6698,6 +6795,9 @@
       <c r="CC13" t="n">
         <v>111</v>
       </c>
+      <c r="CD13" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6947,6 +7047,9 @@
       <c r="CC14" t="n">
         <v>124</v>
       </c>
+      <c r="CD14" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7196,6 +7299,9 @@
       <c r="CC15" t="n">
         <v>96</v>
       </c>
+      <c r="CD15" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7445,6 +7551,9 @@
       <c r="CC16" t="n">
         <v>113</v>
       </c>
+      <c r="CD16" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7694,6 +7803,9 @@
       <c r="CC17" t="n">
         <v>111</v>
       </c>
+      <c r="CD17" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7943,6 +8055,9 @@
       <c r="CC18" t="n">
         <v>102</v>
       </c>
+      <c r="CD18" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8191,6 +8306,9 @@
       </c>
       <c r="CC19" t="n">
         <v>99</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -8204,7 +8322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ19"/>
+  <dimension ref="A1:BK19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8220,6 +8338,7 @@
     <col width="12" customWidth="1" min="60" max="60"/>
     <col width="12" customWidth="1" min="61" max="61"/>
     <col width="12" customWidth="1" min="62" max="62"/>
+    <col width="12" customWidth="1" min="63" max="63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8435,6 +8554,11 @@
           <t>20260123</t>
         </is>
       </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>20260126</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8627,6 +8751,9 @@
       <c r="BJ2" t="n">
         <v>24.04</v>
       </c>
+      <c r="BK2" t="n">
+        <v>34.24</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8819,6 +8946,9 @@
       <c r="BJ3" t="n">
         <v>1.91</v>
       </c>
+      <c r="BK3" t="n">
+        <v>-13.46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9011,6 +9141,9 @@
       <c r="BJ4" t="n">
         <v>9.880000000000001</v>
       </c>
+      <c r="BK4" t="n">
+        <v>41.14</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9203,6 +9336,9 @@
       <c r="BJ5" t="n">
         <v>-18.11</v>
       </c>
+      <c r="BK5" t="n">
+        <v>-31.25</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9395,6 +9531,9 @@
       <c r="BJ6" t="n">
         <v>2.67</v>
       </c>
+      <c r="BK6" t="n">
+        <v>-11.93</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9587,6 +9726,9 @@
       <c r="BJ7" t="n">
         <v>5.12</v>
       </c>
+      <c r="BK7" t="n">
+        <v>-11.13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9779,6 +9921,9 @@
       <c r="BJ8" t="n">
         <v>2.73</v>
       </c>
+      <c r="BK8" t="n">
+        <v>-12.87</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9971,6 +10116,9 @@
       <c r="BJ9" t="n">
         <v>7.83</v>
       </c>
+      <c r="BK9" t="n">
+        <v>24.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10163,6 +10311,9 @@
       <c r="BJ10" t="n">
         <v>-4.95</v>
       </c>
+      <c r="BK10" t="n">
+        <v>-12.83</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10355,6 +10506,9 @@
       <c r="BJ11" t="n">
         <v>9.19</v>
       </c>
+      <c r="BK11" t="n">
+        <v>39.08</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10547,6 +10701,9 @@
       <c r="BJ12" t="n">
         <v>-4.46</v>
       </c>
+      <c r="BK12" t="n">
+        <v>23.91</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10739,6 +10896,9 @@
       <c r="BJ13" t="n">
         <v>-7.5</v>
       </c>
+      <c r="BK13" t="n">
+        <v>27.48</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10931,6 +11091,9 @@
       <c r="BJ14" t="n">
         <v>1</v>
       </c>
+      <c r="BK14" t="n">
+        <v>25.09</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11123,6 +11286,9 @@
       <c r="BJ15" t="n">
         <v>34.75</v>
       </c>
+      <c r="BK15" t="n">
+        <v>31.25</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11315,6 +11481,9 @@
       <c r="BJ16" t="n">
         <v>17.4</v>
       </c>
+      <c r="BK16" t="n">
+        <v>45.46</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11507,6 +11676,9 @@
       <c r="BJ17" t="n">
         <v>-2.58</v>
       </c>
+      <c r="BK17" t="n">
+        <v>20.4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11699,6 +11871,9 @@
       <c r="BJ18" t="n">
         <v>-9.130000000000001</v>
       </c>
+      <c r="BK18" t="n">
+        <v>-19.12</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11890,6 +12065,9 @@
       </c>
       <c r="BJ19" t="n">
         <v>54.13</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>62.34</v>
       </c>
     </row>
   </sheetData>
@@ -11903,7 +12081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO19"/>
+  <dimension ref="A1:AP19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11947,6 +12125,7 @@
     <col width="12" customWidth="1" min="39" max="39"/>
     <col width="12" customWidth="1" min="40" max="40"/>
     <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12155,6 +12334,11 @@
           <t>20260123</t>
         </is>
       </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>20260126</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12284,6 +12468,9 @@
       <c r="AO2" t="n">
         <v>216</v>
       </c>
+      <c r="AP2" t="n">
+        <v>285</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12413,6 +12600,9 @@
       <c r="AO3" t="n">
         <v>30</v>
       </c>
+      <c r="AP3" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12542,6 +12732,9 @@
       <c r="AO4" t="n">
         <v>142</v>
       </c>
+      <c r="AP4" t="n">
+        <v>432</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12671,6 +12864,9 @@
       <c r="AO5" t="n">
         <v>27</v>
       </c>
+      <c r="AP5" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12800,6 +12996,9 @@
       <c r="AO6" t="n">
         <v>58</v>
       </c>
+      <c r="AP6" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12929,6 +13128,9 @@
       <c r="AO7" t="n">
         <v>53</v>
       </c>
+      <c r="AP7" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13058,6 +13260,9 @@
       <c r="AO8" t="n">
         <v>72</v>
       </c>
+      <c r="AP8" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13187,6 +13392,9 @@
       <c r="AO9" t="n">
         <v>128</v>
       </c>
+      <c r="AP9" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13316,6 +13524,9 @@
       <c r="AO10" t="n">
         <v>42</v>
       </c>
+      <c r="AP10" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13445,6 +13656,9 @@
       <c r="AO11" t="n">
         <v>63</v>
       </c>
+      <c r="AP11" t="n">
+        <v>123</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13574,6 +13788,9 @@
       <c r="AO12" t="n">
         <v>99</v>
       </c>
+      <c r="AP12" t="n">
+        <v>133</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13703,6 +13920,9 @@
       <c r="AO13" t="n">
         <v>87</v>
       </c>
+      <c r="AP13" t="n">
+        <v>135</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13832,6 +14052,9 @@
       <c r="AO14" t="n">
         <v>114</v>
       </c>
+      <c r="AP14" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13961,6 +14184,9 @@
       <c r="AO15" t="n">
         <v>85</v>
       </c>
+      <c r="AP15" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14090,6 +14316,9 @@
       <c r="AO16" t="n">
         <v>116</v>
       </c>
+      <c r="AP16" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14219,6 +14448,9 @@
       <c r="AO17" t="n">
         <v>97</v>
       </c>
+      <c r="AP17" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14348,6 +14580,9 @@
       <c r="AO18" t="n">
         <v>18</v>
       </c>
+      <c r="AP18" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14476,6 +14711,9 @@
       </c>
       <c r="AO19" t="n">
         <v>68</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -14489,7 +14727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS19"/>
+  <dimension ref="A1:BT19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14563,6 +14801,7 @@
     <col width="10" customWidth="1" min="69" max="69"/>
     <col width="10" customWidth="1" min="70" max="70"/>
     <col width="10" customWidth="1" min="71" max="71"/>
+    <col width="10" customWidth="1" min="72" max="72"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14783,6 +15022,9 @@
       <c r="BS1" s="1" t="n">
         <v>20260123</v>
       </c>
+      <c r="BT1" s="1" t="n">
+        <v>20260126</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15002,6 +15244,9 @@
       <c r="BS2" t="n">
         <v>-15</v>
       </c>
+      <c r="BT2" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15221,6 +15466,9 @@
       <c r="BS3" t="n">
         <v>59</v>
       </c>
+      <c r="BT3" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15440,6 +15688,9 @@
       <c r="BS4" t="n">
         <v>42</v>
       </c>
+      <c r="BT4" t="n">
+        <v>172</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15659,6 +15910,9 @@
       <c r="BS5" t="n">
         <v>20</v>
       </c>
+      <c r="BT5" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15878,6 +16132,9 @@
       <c r="BS6" t="n">
         <v>65</v>
       </c>
+      <c r="BT6" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16097,6 +16354,9 @@
       <c r="BS7" t="n">
         <v>59</v>
       </c>
+      <c r="BT7" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16316,6 +16576,9 @@
       <c r="BS8" t="n">
         <v>61</v>
       </c>
+      <c r="BT8" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16535,6 +16798,9 @@
       <c r="BS9" t="n">
         <v>81</v>
       </c>
+      <c r="BT9" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16754,6 +17020,9 @@
       <c r="BS10" t="n">
         <v>52</v>
       </c>
+      <c r="BT10" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16973,6 +17242,9 @@
       <c r="BS11" t="n">
         <v>87</v>
       </c>
+      <c r="BT11" t="n">
+        <v>141</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17192,6 +17464,9 @@
       <c r="BS12" t="n">
         <v>71</v>
       </c>
+      <c r="BT12" t="n">
+        <v>133</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17411,6 +17686,9 @@
       <c r="BS13" t="n">
         <v>69</v>
       </c>
+      <c r="BT13" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17630,6 +17908,9 @@
       <c r="BS14" t="n">
         <v>80</v>
       </c>
+      <c r="BT14" t="n">
+        <v>122</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17849,6 +18130,9 @@
       <c r="BS15" t="n">
         <v>-48</v>
       </c>
+      <c r="BT15" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -18068,6 +18352,9 @@
       <c r="BS16" t="n">
         <v>93</v>
       </c>
+      <c r="BT16" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -18287,6 +18574,9 @@
       <c r="BS17" t="n">
         <v>70</v>
       </c>
+      <c r="BT17" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -18506,6 +18796,9 @@
       <c r="BS18" t="n">
         <v>42</v>
       </c>
+      <c r="BT18" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -18724,6 +19017,9 @@
       </c>
       <c r="BS19" t="n">
         <v>-15</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -18737,7 +19033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV19"/>
+  <dimension ref="A1:CW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18840,6 +19136,7 @@
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
+    <col width="12" customWidth="1" min="101" max="101"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19147,6 +19444,9 @@
       <c r="CV1" s="1" t="n">
         <v>20260123</v>
       </c>
+      <c r="CW1" s="1" t="n">
+        <v>20260126</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19453,6 +19753,9 @@
       <c r="CV2" t="n">
         <v>14000</v>
       </c>
+      <c r="CW2" t="n">
+        <v>15425</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19759,6 +20062,9 @@
       <c r="CV3" t="n">
         <v>72050</v>
       </c>
+      <c r="CW3" t="n">
+        <v>72200</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20065,6 +20371,9 @@
       <c r="CV4" t="n">
         <v>17180</v>
       </c>
+      <c r="CW4" t="n">
+        <v>18985</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20371,6 +20680,9 @@
       <c r="CV5" t="n">
         <v>16870</v>
       </c>
+      <c r="CW5" t="n">
+        <v>16885</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20677,6 +20989,9 @@
       <c r="CV6" t="n">
         <v>20920</v>
       </c>
+      <c r="CW6" t="n">
+        <v>21025</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20983,6 +21298,9 @@
       <c r="CV7" t="n">
         <v>24900</v>
       </c>
+      <c r="CW7" t="n">
+        <v>24855</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21289,6 +21607,9 @@
       <c r="CV8" t="n">
         <v>24285</v>
       </c>
+      <c r="CW8" t="n">
+        <v>24450</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21595,6 +21916,9 @@
       <c r="CV9" t="n">
         <v>1687</v>
       </c>
+      <c r="CW9" t="n">
+        <v>1666</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21901,6 +22225,9 @@
       <c r="CV10" t="n">
         <v>18500</v>
       </c>
+      <c r="CW10" t="n">
+        <v>18920</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22207,6 +22534,9 @@
       <c r="CV11" t="n">
         <v>5860</v>
       </c>
+      <c r="CW11" t="n">
+        <v>5800</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -22513,6 +22843,9 @@
       <c r="CV12" t="n">
         <v>6205</v>
       </c>
+      <c r="CW12" t="n">
+        <v>6175</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -22819,6 +23152,9 @@
       <c r="CV13" t="n">
         <v>6265</v>
       </c>
+      <c r="CW13" t="n">
+        <v>6220</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -23125,6 +23461,9 @@
       <c r="CV14" t="n">
         <v>1857</v>
       </c>
+      <c r="CW14" t="n">
+        <v>1809</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -23431,6 +23770,9 @@
       <c r="CV15" t="n">
         <v>17750</v>
       </c>
+      <c r="CW15" t="n">
+        <v>18830</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -23737,6 +24079,9 @@
       <c r="CV16" t="n">
         <v>12200</v>
       </c>
+      <c r="CW16" t="n">
+        <v>11895</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24043,6 +24388,9 @@
       <c r="CV17" t="n">
         <v>6900</v>
       </c>
+      <c r="CW17" t="n">
+        <v>6810</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24349,6 +24697,9 @@
       <c r="CV18" t="n">
         <v>19610</v>
       </c>
+      <c r="CW18" t="n">
+        <v>20145</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -24654,6 +25005,9 @@
       </c>
       <c r="CV19" t="n">
         <v>14900</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>16080</v>
       </c>
     </row>
   </sheetData>
@@ -24667,7 +25021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV19"/>
+  <dimension ref="A1:CW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24770,6 +25124,7 @@
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
+    <col width="12" customWidth="1" min="101" max="101"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25077,6 +25432,9 @@
       <c r="CV1" s="1" t="n">
         <v>20260123</v>
       </c>
+      <c r="CW1" s="1" t="n">
+        <v>20260126</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25383,6 +25741,9 @@
       <c r="CV2" t="n">
         <v>15060</v>
       </c>
+      <c r="CW2" t="n">
+        <v>16735</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25689,6 +26050,9 @@
       <c r="CV3" t="n">
         <v>72370</v>
       </c>
+      <c r="CW3" t="n">
+        <v>73530</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25995,6 +26359,9 @@
       <c r="CV4" t="n">
         <v>18490</v>
       </c>
+      <c r="CW4" t="n">
+        <v>20585</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26301,6 +26668,9 @@
       <c r="CV5" t="n">
         <v>17030</v>
       </c>
+      <c r="CW5" t="n">
+        <v>17335</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26607,6 +26977,9 @@
       <c r="CV6" t="n">
         <v>21020</v>
       </c>
+      <c r="CW6" t="n">
+        <v>21280</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26913,6 +27286,9 @@
       <c r="CV7" t="n">
         <v>25060</v>
       </c>
+      <c r="CW7" t="n">
+        <v>25070</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27219,6 +27595,9 @@
       <c r="CV8" t="n">
         <v>24450</v>
       </c>
+      <c r="CW8" t="n">
+        <v>24625</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27525,6 +27904,9 @@
       <c r="CV9" t="n">
         <v>1732</v>
       </c>
+      <c r="CW9" t="n">
+        <v>1721</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27831,6 +28213,9 @@
       <c r="CV10" t="n">
         <v>18750</v>
       </c>
+      <c r="CW10" t="n">
+        <v>19550</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28137,6 +28522,9 @@
       <c r="CV11" t="n">
         <v>5880</v>
       </c>
+      <c r="CW11" t="n">
+        <v>6150</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28443,6 +28831,9 @@
       <c r="CV12" t="n">
         <v>6220</v>
       </c>
+      <c r="CW12" t="n">
+        <v>6565</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28749,6 +29140,9 @@
       <c r="CV13" t="n">
         <v>6270</v>
       </c>
+      <c r="CW13" t="n">
+        <v>6730</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29055,6 +29449,9 @@
       <c r="CV14" t="n">
         <v>1870</v>
       </c>
+      <c r="CW14" t="n">
+        <v>1935</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -29361,6 +29758,9 @@
       <c r="CV15" t="n">
         <v>18630</v>
       </c>
+      <c r="CW15" t="n">
+        <v>19820</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -29667,6 +30067,9 @@
       <c r="CV16" t="n">
         <v>12200</v>
       </c>
+      <c r="CW16" t="n">
+        <v>12550</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -29973,6 +30376,9 @@
       <c r="CV17" t="n">
         <v>6920</v>
       </c>
+      <c r="CW17" t="n">
+        <v>7090</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -30279,6 +30685,9 @@
       <c r="CV18" t="n">
         <v>19910</v>
       </c>
+      <c r="CW18" t="n">
+        <v>20535</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -30584,6 +30993,9 @@
       </c>
       <c r="CV19" t="n">
         <v>15890</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>17225</v>
       </c>
     </row>
   </sheetData>
@@ -30597,7 +31009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV19"/>
+  <dimension ref="A1:CW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -30700,6 +31112,7 @@
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
+    <col width="12" customWidth="1" min="101" max="101"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31007,6 +31420,9 @@
       <c r="CV1" s="1" t="n">
         <v>20260123</v>
       </c>
+      <c r="CW1" s="1" t="n">
+        <v>20260126</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31313,6 +31729,9 @@
       <c r="CV2" t="n">
         <v>14000</v>
       </c>
+      <c r="CW2" t="n">
+        <v>15300</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31619,6 +32038,9 @@
       <c r="CV3" t="n">
         <v>71135</v>
       </c>
+      <c r="CW3" t="n">
+        <v>72100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -31925,6 +32347,9 @@
       <c r="CV4" t="n">
         <v>17180</v>
       </c>
+      <c r="CW4" t="n">
+        <v>18900</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32231,6 +32656,9 @@
       <c r="CV5" t="n">
         <v>16620</v>
       </c>
+      <c r="CW5" t="n">
+        <v>16805</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32537,6 +32965,9 @@
       <c r="CV6" t="n">
         <v>20675</v>
       </c>
+      <c r="CW6" t="n">
+        <v>20965</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -32843,6 +33274,9 @@
       <c r="CV7" t="n">
         <v>24400</v>
       </c>
+      <c r="CW7" t="n">
+        <v>24780</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -33149,6 +33583,9 @@
       <c r="CV8" t="n">
         <v>23975</v>
       </c>
+      <c r="CW8" t="n">
+        <v>24340</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33455,6 +33892,9 @@
       <c r="CV9" t="n">
         <v>1570</v>
       </c>
+      <c r="CW9" t="n">
+        <v>1637</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -33761,6 +34201,9 @@
       <c r="CV10" t="n">
         <v>18340</v>
       </c>
+      <c r="CW10" t="n">
+        <v>18730</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -34067,6 +34510,9 @@
       <c r="CV11" t="n">
         <v>5610</v>
       </c>
+      <c r="CW11" t="n">
+        <v>5780</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -34373,6 +34819,9 @@
       <c r="CV12" t="n">
         <v>5930</v>
       </c>
+      <c r="CW12" t="n">
+        <v>6125</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34679,6 +35128,9 @@
       <c r="CV13" t="n">
         <v>5970</v>
       </c>
+      <c r="CW13" t="n">
+        <v>6175</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34985,6 +35437,9 @@
       <c r="CV14" t="n">
         <v>1693</v>
       </c>
+      <c r="CW14" t="n">
+        <v>1785</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35291,6 +35746,9 @@
       <c r="CV15" t="n">
         <v>17750</v>
       </c>
+      <c r="CW15" t="n">
+        <v>18775</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -35597,6 +36055,9 @@
       <c r="CV16" t="n">
         <v>11475</v>
       </c>
+      <c r="CW16" t="n">
+        <v>11840</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -35903,6 +36364,9 @@
       <c r="CV17" t="n">
         <v>6575</v>
       </c>
+      <c r="CW17" t="n">
+        <v>6790</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36209,6 +36673,9 @@
       <c r="CV18" t="n">
         <v>19475</v>
       </c>
+      <c r="CW18" t="n">
+        <v>19890</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -36514,6 +36981,9 @@
       </c>
       <c r="CV19" t="n">
         <v>14900</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>16080</v>
       </c>
     </row>
   </sheetData>
@@ -36527,7 +36997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV19"/>
+  <dimension ref="A1:CW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -36630,6 +37100,7 @@
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
+    <col width="12" customWidth="1" min="101" max="101"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36937,6 +37408,9 @@
       <c r="CV1" s="1" t="n">
         <v>20260123</v>
       </c>
+      <c r="CW1" s="1" t="n">
+        <v>20260126</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37243,6 +37717,9 @@
       <c r="CV2" t="n">
         <v>15020</v>
       </c>
+      <c r="CW2" t="n">
+        <v>16735</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37549,6 +38026,9 @@
       <c r="CV3" t="n">
         <v>72200</v>
       </c>
+      <c r="CW3" t="n">
+        <v>73445</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -37855,6 +38335,9 @@
       <c r="CV4" t="n">
         <v>18465</v>
       </c>
+      <c r="CW4" t="n">
+        <v>20585</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -38161,6 +38644,9 @@
       <c r="CV5" t="n">
         <v>16795</v>
       </c>
+      <c r="CW5" t="n">
+        <v>17280</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -38467,6 +38953,9 @@
       <c r="CV6" t="n">
         <v>21000</v>
       </c>
+      <c r="CW6" t="n">
+        <v>21280</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -38773,6 +39262,9 @@
       <c r="CV7" t="n">
         <v>24765</v>
       </c>
+      <c r="CW7" t="n">
+        <v>25020</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -39079,6 +39571,9 @@
       <c r="CV8" t="n">
         <v>24450</v>
       </c>
+      <c r="CW8" t="n">
+        <v>24575</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -39385,6 +39880,9 @@
       <c r="CV9" t="n">
         <v>1618</v>
       </c>
+      <c r="CW9" t="n">
+        <v>1719</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -39691,6 +40189,9 @@
       <c r="CV10" t="n">
         <v>18700</v>
       </c>
+      <c r="CW10" t="n">
+        <v>19550</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -39997,6 +40498,9 @@
       <c r="CV11" t="n">
         <v>5720</v>
       </c>
+      <c r="CW11" t="n">
+        <v>6150</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -40303,6 +40807,9 @@
       <c r="CV12" t="n">
         <v>6050</v>
       </c>
+      <c r="CW12" t="n">
+        <v>6565</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -40609,6 +41116,9 @@
       <c r="CV13" t="n">
         <v>6095</v>
       </c>
+      <c r="CW13" t="n">
+        <v>6730</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -40915,6 +41425,9 @@
       <c r="CV14" t="n">
         <v>1755</v>
       </c>
+      <c r="CW14" t="n">
+        <v>1935</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41221,6 +41734,9 @@
       <c r="CV15" t="n">
         <v>18600</v>
       </c>
+      <c r="CW15" t="n">
+        <v>19810</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -41527,6 +42043,9 @@
       <c r="CV16" t="n">
         <v>11700</v>
       </c>
+      <c r="CW16" t="n">
+        <v>12550</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41833,6 +42352,9 @@
       <c r="CV17" t="n">
         <v>6670</v>
       </c>
+      <c r="CW17" t="n">
+        <v>7090</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42139,6 +42661,9 @@
       <c r="CV18" t="n">
         <v>19875</v>
       </c>
+      <c r="CW18" t="n">
+        <v>20535</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42444,6 +42969,9 @@
       </c>
       <c r="CV19" t="n">
         <v>15890</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>17140</v>
       </c>
     </row>
   </sheetData>
@@ -42457,7 +42985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV19"/>
+  <dimension ref="A1:CW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -42560,6 +43088,7 @@
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
+    <col width="12" customWidth="1" min="101" max="101"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -42867,6 +43396,9 @@
       <c r="CV1" s="1" t="n">
         <v>20260123</v>
       </c>
+      <c r="CW1" s="1" t="n">
+        <v>20260126</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -43173,6 +43705,9 @@
       <c r="CV2" t="n">
         <v>904226</v>
       </c>
+      <c r="CW2" t="n">
+        <v>1308638</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -43479,6 +44014,9 @@
       <c r="CV3" t="n">
         <v>1527427</v>
       </c>
+      <c r="CW3" t="n">
+        <v>1543357</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -43785,6 +44323,9 @@
       <c r="CV4" t="n">
         <v>626786</v>
       </c>
+      <c r="CW4" t="n">
+        <v>2205191</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -44091,6 +44632,9 @@
       <c r="CV5" t="n">
         <v>227781</v>
       </c>
+      <c r="CW5" t="n">
+        <v>400924</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -44397,6 +44941,9 @@
       <c r="CV6" t="n">
         <v>3379498</v>
       </c>
+      <c r="CW6" t="n">
+        <v>6049845</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -44703,6 +45250,9 @@
       <c r="CV7" t="n">
         <v>4143659</v>
       </c>
+      <c r="CW7" t="n">
+        <v>2281948</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -45009,6 +45559,9 @@
       <c r="CV8" t="n">
         <v>12840724</v>
       </c>
+      <c r="CW8" t="n">
+        <v>11093930</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -45315,6 +45868,9 @@
       <c r="CV9" t="n">
         <v>18143262</v>
       </c>
+      <c r="CW9" t="n">
+        <v>14988528</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -45621,6 +46177,9 @@
       <c r="CV10" t="n">
         <v>1019516</v>
       </c>
+      <c r="CW10" t="n">
+        <v>3886528</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -45927,6 +46486,9 @@
       <c r="CV11" t="n">
         <v>1366637</v>
       </c>
+      <c r="CW11" t="n">
+        <v>2742216</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -46233,6 +46795,9 @@
       <c r="CV12" t="n">
         <v>5096058</v>
       </c>
+      <c r="CW12" t="n">
+        <v>7016669</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -46539,6 +47104,9 @@
       <c r="CV13" t="n">
         <v>10652711</v>
       </c>
+      <c r="CW13" t="n">
+        <v>16922355</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -46845,6 +47413,9 @@
       <c r="CV14" t="n">
         <v>107281191</v>
       </c>
+      <c r="CW14" t="n">
+        <v>98497868</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -47151,6 +47722,9 @@
       <c r="CV15" t="n">
         <v>3598967</v>
       </c>
+      <c r="CW15" t="n">
+        <v>5611328</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -47457,6 +48031,9 @@
       <c r="CV16" t="n">
         <v>1181219</v>
       </c>
+      <c r="CW16" t="n">
+        <v>1084470</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -47763,6 +48340,9 @@
       <c r="CV17" t="n">
         <v>262572</v>
       </c>
+      <c r="CW17" t="n">
+        <v>248965</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -48069,6 +48649,9 @@
       <c r="CV18" t="n">
         <v>52826</v>
       </c>
+      <c r="CW18" t="n">
+        <v>170338</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -48374,6 +48957,9 @@
       </c>
       <c r="CV19" t="n">
         <v>78637</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>220664</v>
       </c>
     </row>
   </sheetData>
@@ -48387,7 +48973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC19"/>
+  <dimension ref="A1:CD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -48471,6 +49057,7 @@
     <col width="10" customWidth="1" min="79" max="79"/>
     <col width="10" customWidth="1" min="80" max="80"/>
     <col width="10" customWidth="1" min="81" max="81"/>
+    <col width="10" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -48721,6 +49308,9 @@
       <c r="CC1" s="1" t="n">
         <v>20260123</v>
       </c>
+      <c r="CD1" s="1" t="n">
+        <v>20260126</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -48970,6 +49560,9 @@
       <c r="CC2" t="n">
         <v>53</v>
       </c>
+      <c r="CD2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -49219,6 +49812,9 @@
       <c r="CC3" t="n">
         <v>99</v>
       </c>
+      <c r="CD3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -49468,6 +50064,9 @@
       <c r="CC4" t="n">
         <v>77</v>
       </c>
+      <c r="CD4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -49717,6 +50316,9 @@
       <c r="CC5" t="n">
         <v>58</v>
       </c>
+      <c r="CD5" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -49966,6 +50568,9 @@
       <c r="CC6" t="n">
         <v>100</v>
       </c>
+      <c r="CD6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -50215,6 +50820,9 @@
       <c r="CC7" t="n">
         <v>98</v>
       </c>
+      <c r="CD7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -50464,6 +51072,9 @@
       <c r="CC8" t="n">
         <v>100</v>
       </c>
+      <c r="CD8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -50713,6 +51324,9 @@
       <c r="CC9" t="n">
         <v>98</v>
       </c>
+      <c r="CD9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -50962,6 +51576,9 @@
       <c r="CC10" t="n">
         <v>86</v>
       </c>
+      <c r="CD10" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -51211,6 +51828,9 @@
       <c r="CC11" t="n">
         <v>100</v>
       </c>
+      <c r="CD11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -51460,6 +52080,9 @@
       <c r="CC12" t="n">
         <v>100</v>
       </c>
+      <c r="CD12" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -51709,6 +52332,9 @@
       <c r="CC13" t="n">
         <v>100</v>
       </c>
+      <c r="CD13" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -51958,6 +52584,9 @@
       <c r="CC14" t="n">
         <v>98</v>
       </c>
+      <c r="CD14" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -52207,6 +52836,9 @@
       <c r="CC15" t="n">
         <v>37</v>
       </c>
+      <c r="CD15" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -52456,6 +53088,9 @@
       <c r="CC16" t="n">
         <v>98</v>
       </c>
+      <c r="CD16" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -52705,6 +53340,9 @@
       <c r="CC17" t="n">
         <v>96</v>
       </c>
+      <c r="CD17" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -52954,6 +53592,9 @@
       <c r="CC18" t="n">
         <v>77</v>
       </c>
+      <c r="CD18" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -53202,6 +53843,9 @@
       </c>
       <c r="CC19" t="n">
         <v>56</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -53215,7 +53859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO19"/>
+  <dimension ref="A1:AP19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -53259,6 +53903,7 @@
     <col width="10" customWidth="1" min="39" max="39"/>
     <col width="10" customWidth="1" min="40" max="40"/>
     <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -53389,6 +54034,9 @@
       <c r="AO1" s="1" t="n">
         <v>20260123</v>
       </c>
+      <c r="AP1" s="1" t="n">
+        <v>20260126</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -53518,6 +54166,9 @@
       <c r="AO2" t="n">
         <v>47</v>
       </c>
+      <c r="AP2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -53647,6 +54298,9 @@
       <c r="AO3" t="n">
         <v>99</v>
       </c>
+      <c r="AP3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -53776,6 +54430,9 @@
       <c r="AO4" t="n">
         <v>69</v>
       </c>
+      <c r="AP4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -53905,6 +54562,9 @@
       <c r="AO5" t="n">
         <v>69</v>
       </c>
+      <c r="AP5" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -54034,6 +54694,9 @@
       <c r="AO6" t="n">
         <v>100</v>
       </c>
+      <c r="AP6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -54163,6 +54826,9 @@
       <c r="AO7" t="n">
         <v>99</v>
       </c>
+      <c r="AP7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -54292,6 +54958,9 @@
       <c r="AO8" t="n">
         <v>100</v>
       </c>
+      <c r="AP8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -54421,6 +55090,9 @@
       <c r="AO9" t="n">
         <v>55</v>
       </c>
+      <c r="AP9" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -54550,6 +55222,9 @@
       <c r="AO10" t="n">
         <v>87</v>
       </c>
+      <c r="AP10" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -54679,6 +55354,9 @@
       <c r="AO11" t="n">
         <v>94</v>
       </c>
+      <c r="AP11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -54808,6 +55486,9 @@
       <c r="AO12" t="n">
         <v>81</v>
       </c>
+      <c r="AP12" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -54937,6 +55618,9 @@
       <c r="AO13" t="n">
         <v>81</v>
       </c>
+      <c r="AP13" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -55066,6 +55750,9 @@
       <c r="AO14" t="n">
         <v>60</v>
       </c>
+      <c r="AP14" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -55195,6 +55882,9 @@
       <c r="AO15" t="n">
         <v>64</v>
       </c>
+      <c r="AP15" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -55324,6 +56014,9 @@
       <c r="AO16" t="n">
         <v>88</v>
       </c>
+      <c r="AP16" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -55453,6 +56146,9 @@
       <c r="AO17" t="n">
         <v>67</v>
       </c>
+      <c r="AP17" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -55582,6 +56278,9 @@
       <c r="AO18" t="n">
         <v>82</v>
       </c>
+      <c r="AP18" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -55710,6 +56409,9 @@
       </c>
       <c r="AO19" t="n">
         <v>72</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -55723,7 +56425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC19"/>
+  <dimension ref="A1:CD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -55807,6 +56509,7 @@
     <col width="10" customWidth="1" min="79" max="79"/>
     <col width="10" customWidth="1" min="80" max="80"/>
     <col width="10" customWidth="1" min="81" max="81"/>
+    <col width="10" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -56057,6 +56760,9 @@
       <c r="CC1" s="1" t="n">
         <v>20260123</v>
       </c>
+      <c r="CD1" s="1" t="n">
+        <v>20260126</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -56306,6 +57012,9 @@
       <c r="CC2" t="n">
         <v>-14</v>
       </c>
+      <c r="CD2" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -56555,6 +57264,9 @@
       <c r="CC3" t="n">
         <v>44</v>
       </c>
+      <c r="CD3" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -56804,6 +57516,9 @@
       <c r="CC4" t="n">
         <v>29</v>
       </c>
+      <c r="CD4" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -57053,6 +57768,9 @@
       <c r="CC5" t="n">
         <v>-10</v>
       </c>
+      <c r="CD5" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -57302,6 +58020,9 @@
       <c r="CC6" t="n">
         <v>52</v>
       </c>
+      <c r="CD6" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -57551,6 +58272,9 @@
       <c r="CC7" t="n">
         <v>44</v>
       </c>
+      <c r="CD7" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -57800,6 +58524,9 @@
       <c r="CC8" t="n">
         <v>47</v>
       </c>
+      <c r="CD8" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -58049,6 +58776,9 @@
       <c r="CC9" t="n">
         <v>101</v>
       </c>
+      <c r="CD9" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -58298,6 +59028,9 @@
       <c r="CC10" t="n">
         <v>34</v>
       </c>
+      <c r="CD10" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -58547,6 +59280,9 @@
       <c r="CC11" t="n">
         <v>110</v>
       </c>
+      <c r="CD11" t="n">
+        <v>137</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -58796,6 +59532,9 @@
       <c r="CC12" t="n">
         <v>104</v>
       </c>
+      <c r="CD12" t="n">
+        <v>138</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -59045,6 +59784,9 @@
       <c r="CC13" t="n">
         <v>106</v>
       </c>
+      <c r="CD13" t="n">
+        <v>149</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -59294,6 +60036,9 @@
       <c r="CC14" t="n">
         <v>111</v>
       </c>
+      <c r="CD14" t="n">
+        <v>129</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -59543,6 +60288,9 @@
       <c r="CC15" t="n">
         <v>-47</v>
       </c>
+      <c r="CD15" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -59792,6 +60540,9 @@
       <c r="CC16" t="n">
         <v>108</v>
       </c>
+      <c r="CD16" t="n">
+        <v>132</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -60041,6 +60792,9 @@
       <c r="CC17" t="n">
         <v>104</v>
       </c>
+      <c r="CD17" t="n">
+        <v>129</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -60290,6 +61044,9 @@
       <c r="CC18" t="n">
         <v>21</v>
       </c>
+      <c r="CD18" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -60538,6 +61295,9 @@
       </c>
       <c r="CC19" t="n">
         <v>-13</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP19"/>
+  <dimension ref="A1:AQ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -755,6 +755,7 @@
     <col width="10" customWidth="1" min="40" max="40"/>
     <col width="10" customWidth="1" min="41" max="41"/>
     <col width="10" customWidth="1" min="42" max="42"/>
+    <col width="10" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -888,6 +889,9 @@
       <c r="AP1" s="1" t="n">
         <v>20260126</v>
       </c>
+      <c r="AQ1" s="1" t="n">
+        <v>20260127</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1020,6 +1024,9 @@
       <c r="AP2" t="n">
         <v>97</v>
       </c>
+      <c r="AQ2" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1152,6 +1159,9 @@
       <c r="AP3" t="n">
         <v>98</v>
       </c>
+      <c r="AQ3" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1284,6 +1294,9 @@
       <c r="AP4" t="n">
         <v>159</v>
       </c>
+      <c r="AQ4" t="n">
+        <v>165</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1416,6 +1429,9 @@
       <c r="AP5" t="n">
         <v>63</v>
       </c>
+      <c r="AQ5" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1548,6 +1564,9 @@
       <c r="AP6" t="n">
         <v>103</v>
       </c>
+      <c r="AQ6" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1680,6 +1699,9 @@
       <c r="AP7" t="n">
         <v>94</v>
       </c>
+      <c r="AQ7" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1812,6 +1834,9 @@
       <c r="AP8" t="n">
         <v>95</v>
       </c>
+      <c r="AQ8" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1944,6 +1969,9 @@
       <c r="AP9" t="n">
         <v>63</v>
       </c>
+      <c r="AQ9" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2076,6 +2104,9 @@
       <c r="AP10" t="n">
         <v>120</v>
       </c>
+      <c r="AQ10" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2208,6 +2239,9 @@
       <c r="AP11" t="n">
         <v>155</v>
       </c>
+      <c r="AQ11" t="n">
+        <v>149</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2340,6 +2374,9 @@
       <c r="AP12" t="n">
         <v>138</v>
       </c>
+      <c r="AQ12" t="n">
+        <v>135</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2472,6 +2509,9 @@
       <c r="AP13" t="n">
         <v>154</v>
       </c>
+      <c r="AQ13" t="n">
+        <v>151</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2604,6 +2644,9 @@
       <c r="AP14" t="n">
         <v>82</v>
       </c>
+      <c r="AQ14" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2736,6 +2779,9 @@
       <c r="AP15" t="n">
         <v>39</v>
       </c>
+      <c r="AQ15" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2868,6 +2914,9 @@
       <c r="AP16" t="n">
         <v>142</v>
       </c>
+      <c r="AQ16" t="n">
+        <v>136</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3000,6 +3049,9 @@
       <c r="AP17" t="n">
         <v>96</v>
       </c>
+      <c r="AQ17" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3132,6 +3184,9 @@
       <c r="AP18" t="n">
         <v>95</v>
       </c>
+      <c r="AQ18" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3263,6 +3318,9 @@
       </c>
       <c r="AP19" t="n">
         <v>81</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -3276,7 +3334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD19"/>
+  <dimension ref="A1:CE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3361,6 +3419,7 @@
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
+    <col width="12" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3774,6 +3833,11 @@
           <t>20260126</t>
         </is>
       </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>20260127</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4026,6 +4090,9 @@
       <c r="CD2" t="n">
         <v>109</v>
       </c>
+      <c r="CE2" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4278,6 +4345,9 @@
       <c r="CD3" t="n">
         <v>106</v>
       </c>
+      <c r="CE3" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4530,6 +4600,9 @@
       <c r="CD4" t="n">
         <v>113</v>
       </c>
+      <c r="CE4" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4782,6 +4855,9 @@
       <c r="CD5" t="n">
         <v>102</v>
       </c>
+      <c r="CE5" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5034,6 +5110,9 @@
       <c r="CD6" t="n">
         <v>107</v>
       </c>
+      <c r="CE6" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5286,6 +5365,9 @@
       <c r="CD7" t="n">
         <v>106</v>
       </c>
+      <c r="CE7" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5538,6 +5620,9 @@
       <c r="CD8" t="n">
         <v>107</v>
       </c>
+      <c r="CE8" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5790,6 +5875,9 @@
       <c r="CD9" t="n">
         <v>126</v>
       </c>
+      <c r="CE9" t="n">
+        <v>122</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6042,6 +6130,9 @@
       <c r="CD10" t="n">
         <v>107</v>
       </c>
+      <c r="CE10" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6294,6 +6385,9 @@
       <c r="CD11" t="n">
         <v>119</v>
       </c>
+      <c r="CE11" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6546,6 +6640,9 @@
       <c r="CD12" t="n">
         <v>120</v>
       </c>
+      <c r="CE12" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6798,6 +6895,9 @@
       <c r="CD13" t="n">
         <v>121</v>
       </c>
+      <c r="CE13" t="n">
+        <v>122</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7050,6 +7150,9 @@
       <c r="CD14" t="n">
         <v>134</v>
       </c>
+      <c r="CE14" t="n">
+        <v>132</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7302,6 +7405,9 @@
       <c r="CD15" t="n">
         <v>102</v>
       </c>
+      <c r="CE15" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7554,6 +7660,9 @@
       <c r="CD16" t="n">
         <v>120</v>
       </c>
+      <c r="CE16" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7806,6 +7915,9 @@
       <c r="CD17" t="n">
         <v>117</v>
       </c>
+      <c r="CE17" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8058,6 +8170,9 @@
       <c r="CD18" t="n">
         <v>105</v>
       </c>
+      <c r="CE18" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8308,6 +8423,9 @@
         <v>99</v>
       </c>
       <c r="CD19" t="n">
+        <v>106</v>
+      </c>
+      <c r="CE19" t="n">
         <v>106</v>
       </c>
     </row>
@@ -8322,7 +8440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK19"/>
+  <dimension ref="A1:BL19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8339,6 +8457,7 @@
     <col width="12" customWidth="1" min="61" max="61"/>
     <col width="12" customWidth="1" min="62" max="62"/>
     <col width="12" customWidth="1" min="63" max="63"/>
+    <col width="12" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8559,6 +8678,11 @@
           <t>20260126</t>
         </is>
       </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>20260127</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8754,6 +8878,9 @@
       <c r="BK2" t="n">
         <v>34.24</v>
       </c>
+      <c r="BL2" t="n">
+        <v>46.05</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8949,6 +9076,9 @@
       <c r="BK3" t="n">
         <v>-13.46</v>
       </c>
+      <c r="BL3" t="n">
+        <v>-19.01</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9144,6 +9274,9 @@
       <c r="BK4" t="n">
         <v>41.14</v>
       </c>
+      <c r="BL4" t="n">
+        <v>68.52</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9339,6 +9472,9 @@
       <c r="BK5" t="n">
         <v>-31.25</v>
       </c>
+      <c r="BL5" t="n">
+        <v>-34.65</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9534,6 +9670,9 @@
       <c r="BK6" t="n">
         <v>-11.93</v>
       </c>
+      <c r="BL6" t="n">
+        <v>-16.89</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9729,6 +9868,9 @@
       <c r="BK7" t="n">
         <v>-11.13</v>
       </c>
+      <c r="BL7" t="n">
+        <v>-19.41</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9924,6 +10066,9 @@
       <c r="BK8" t="n">
         <v>-12.87</v>
       </c>
+      <c r="BL8" t="n">
+        <v>-21.77</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10119,6 +10264,9 @@
       <c r="BK9" t="n">
         <v>24.5</v>
       </c>
+      <c r="BL9" t="n">
+        <v>32.63</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10314,6 +10462,9 @@
       <c r="BK10" t="n">
         <v>-12.83</v>
       </c>
+      <c r="BL10" t="n">
+        <v>-8.710000000000001</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10509,6 +10660,9 @@
       <c r="BK11" t="n">
         <v>39.08</v>
       </c>
+      <c r="BL11" t="n">
+        <v>59.25</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10704,6 +10858,9 @@
       <c r="BK12" t="n">
         <v>23.91</v>
       </c>
+      <c r="BL12" t="n">
+        <v>43.98</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10899,6 +11056,9 @@
       <c r="BK13" t="n">
         <v>27.48</v>
       </c>
+      <c r="BL13" t="n">
+        <v>52.72</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11094,6 +11254,9 @@
       <c r="BK14" t="n">
         <v>25.09</v>
       </c>
+      <c r="BL14" t="n">
+        <v>41.62</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11289,6 +11452,9 @@
       <c r="BK15" t="n">
         <v>31.25</v>
       </c>
+      <c r="BL15" t="n">
+        <v>30.28</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11484,6 +11650,9 @@
       <c r="BK16" t="n">
         <v>45.46</v>
       </c>
+      <c r="BL16" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11679,6 +11848,9 @@
       <c r="BK17" t="n">
         <v>20.4</v>
       </c>
+      <c r="BL17" t="n">
+        <v>35.46</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11874,6 +12046,9 @@
       <c r="BK18" t="n">
         <v>-19.12</v>
       </c>
+      <c r="BL18" t="n">
+        <v>-21.75</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12068,6 +12243,9 @@
       </c>
       <c r="BK19" t="n">
         <v>62.34</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>68.28</v>
       </c>
     </row>
   </sheetData>
@@ -12081,7 +12259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP19"/>
+  <dimension ref="A1:AQ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12126,6 +12304,7 @@
     <col width="12" customWidth="1" min="40" max="40"/>
     <col width="12" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12339,6 +12518,11 @@
           <t>20260126</t>
         </is>
       </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>20260127</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12471,6 +12655,9 @@
       <c r="AP2" t="n">
         <v>285</v>
       </c>
+      <c r="AQ2" t="n">
+        <v>211</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12603,6 +12790,9 @@
       <c r="AP3" t="n">
         <v>35</v>
       </c>
+      <c r="AQ3" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12735,6 +12925,9 @@
       <c r="AP4" t="n">
         <v>432</v>
       </c>
+      <c r="AQ4" t="n">
+        <v>336</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12867,6 +13060,9 @@
       <c r="AP5" t="n">
         <v>48</v>
       </c>
+      <c r="AQ5" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12999,6 +13195,9 @@
       <c r="AP6" t="n">
         <v>104</v>
       </c>
+      <c r="AQ6" t="n">
+        <v>194</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13131,6 +13330,9 @@
       <c r="AP7" t="n">
         <v>30</v>
       </c>
+      <c r="AQ7" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13263,6 +13465,9 @@
       <c r="AP8" t="n">
         <v>63</v>
       </c>
+      <c r="AQ8" t="n">
+        <v>135</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13395,6 +13600,9 @@
       <c r="AP9" t="n">
         <v>105</v>
       </c>
+      <c r="AQ9" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13527,6 +13735,9 @@
       <c r="AP10" t="n">
         <v>156</v>
       </c>
+      <c r="AQ10" t="n">
+        <v>211</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13659,6 +13870,9 @@
       <c r="AP11" t="n">
         <v>123</v>
       </c>
+      <c r="AQ11" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13791,6 +14005,9 @@
       <c r="AP12" t="n">
         <v>133</v>
       </c>
+      <c r="AQ12" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13923,6 +14140,9 @@
       <c r="AP13" t="n">
         <v>135</v>
       </c>
+      <c r="AQ13" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14055,6 +14275,9 @@
       <c r="AP14" t="n">
         <v>103</v>
       </c>
+      <c r="AQ14" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14187,6 +14410,9 @@
       <c r="AP15" t="n">
         <v>128</v>
       </c>
+      <c r="AQ15" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14319,6 +14545,9 @@
       <c r="AP16" t="n">
         <v>105</v>
       </c>
+      <c r="AQ16" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14451,6 +14680,9 @@
       <c r="AP17" t="n">
         <v>105</v>
       </c>
+      <c r="AQ17" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14583,6 +14815,9 @@
       <c r="AP18" t="n">
         <v>62</v>
       </c>
+      <c r="AQ18" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14714,6 +14949,9 @@
       </c>
       <c r="AP19" t="n">
         <v>182</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -14727,7 +14965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT19"/>
+  <dimension ref="A1:BU19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14802,6 +15040,7 @@
     <col width="10" customWidth="1" min="70" max="70"/>
     <col width="10" customWidth="1" min="71" max="71"/>
     <col width="10" customWidth="1" min="72" max="72"/>
+    <col width="10" customWidth="1" min="73" max="73"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15025,6 +15264,9 @@
       <c r="BT1" s="1" t="n">
         <v>20260126</v>
       </c>
+      <c r="BU1" s="1" t="n">
+        <v>20260127</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15247,6 +15489,9 @@
       <c r="BT2" t="n">
         <v>114</v>
       </c>
+      <c r="BU2" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15469,6 +15714,9 @@
       <c r="BT3" t="n">
         <v>63</v>
       </c>
+      <c r="BU3" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15691,6 +15939,9 @@
       <c r="BT4" t="n">
         <v>172</v>
       </c>
+      <c r="BU4" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15913,6 +16164,9 @@
       <c r="BT5" t="n">
         <v>46</v>
       </c>
+      <c r="BU5" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16135,6 +16389,9 @@
       <c r="BT6" t="n">
         <v>67</v>
       </c>
+      <c r="BU6" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16357,6 +16614,9 @@
       <c r="BT7" t="n">
         <v>60</v>
       </c>
+      <c r="BU7" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16579,6 +16839,9 @@
       <c r="BT8" t="n">
         <v>59</v>
       </c>
+      <c r="BU8" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16801,6 +17064,9 @@
       <c r="BT9" t="n">
         <v>110</v>
       </c>
+      <c r="BU9" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17023,6 +17289,9 @@
       <c r="BT10" t="n">
         <v>84</v>
       </c>
+      <c r="BU10" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17245,6 +17514,9 @@
       <c r="BT11" t="n">
         <v>141</v>
       </c>
+      <c r="BU11" t="n">
+        <v>130</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17467,6 +17739,9 @@
       <c r="BT12" t="n">
         <v>133</v>
       </c>
+      <c r="BU12" t="n">
+        <v>125</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17689,6 +17964,9 @@
       <c r="BT13" t="n">
         <v>143</v>
       </c>
+      <c r="BU13" t="n">
+        <v>136</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17911,6 +18189,9 @@
       <c r="BT14" t="n">
         <v>122</v>
       </c>
+      <c r="BU14" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18133,6 +18414,9 @@
       <c r="BT15" t="n">
         <v>38</v>
       </c>
+      <c r="BU15" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -18355,6 +18639,9 @@
       <c r="BT16" t="n">
         <v>140</v>
       </c>
+      <c r="BU16" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -18577,6 +18864,9 @@
       <c r="BT17" t="n">
         <v>119</v>
       </c>
+      <c r="BU17" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -18799,6 +19089,9 @@
       <c r="BT18" t="n">
         <v>63</v>
       </c>
+      <c r="BU18" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -19020,6 +19313,9 @@
       </c>
       <c r="BT19" t="n">
         <v>108</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -19033,7 +19329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW19"/>
+  <dimension ref="A1:CX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19137,6 +19433,7 @@
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
+    <col width="12" customWidth="1" min="102" max="102"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19447,6 +19744,9 @@
       <c r="CW1" s="1" t="n">
         <v>20260126</v>
       </c>
+      <c r="CX1" s="1" t="n">
+        <v>20260127</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19756,6 +20056,9 @@
       <c r="CW2" t="n">
         <v>15425</v>
       </c>
+      <c r="CX2" t="n">
+        <v>16520</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20065,6 +20368,9 @@
       <c r="CW3" t="n">
         <v>72200</v>
       </c>
+      <c r="CX3" t="n">
+        <v>73190</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20374,6 +20680,9 @@
       <c r="CW4" t="n">
         <v>18985</v>
       </c>
+      <c r="CX4" t="n">
+        <v>20305</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20683,6 +20992,9 @@
       <c r="CW5" t="n">
         <v>16885</v>
       </c>
+      <c r="CX5" t="n">
+        <v>17340</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20992,6 +21304,9 @@
       <c r="CW6" t="n">
         <v>21025</v>
       </c>
+      <c r="CX6" t="n">
+        <v>21230</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21301,6 +21616,9 @@
       <c r="CW7" t="n">
         <v>24855</v>
       </c>
+      <c r="CX7" t="n">
+        <v>24985</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21610,6 +21928,9 @@
       <c r="CW8" t="n">
         <v>24450</v>
       </c>
+      <c r="CX8" t="n">
+        <v>24510</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21919,6 +22240,9 @@
       <c r="CW9" t="n">
         <v>1666</v>
       </c>
+      <c r="CX9" t="n">
+        <v>1678</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22228,6 +22552,9 @@
       <c r="CW10" t="n">
         <v>18920</v>
       </c>
+      <c r="CX10" t="n">
+        <v>19555</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22537,6 +22864,9 @@
       <c r="CW11" t="n">
         <v>5800</v>
       </c>
+      <c r="CX11" t="n">
+        <v>6040</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -22846,6 +23176,9 @@
       <c r="CW12" t="n">
         <v>6175</v>
       </c>
+      <c r="CX12" t="n">
+        <v>6440</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -23155,6 +23488,9 @@
       <c r="CW13" t="n">
         <v>6220</v>
       </c>
+      <c r="CX13" t="n">
+        <v>6560</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -23464,6 +23800,9 @@
       <c r="CW14" t="n">
         <v>1809</v>
       </c>
+      <c r="CX14" t="n">
+        <v>1864</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -23773,6 +24112,9 @@
       <c r="CW15" t="n">
         <v>18830</v>
       </c>
+      <c r="CX15" t="n">
+        <v>19555</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24082,6 +24424,9 @@
       <c r="CW16" t="n">
         <v>11895</v>
       </c>
+      <c r="CX16" t="n">
+        <v>12285</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24391,6 +24736,9 @@
       <c r="CW17" t="n">
         <v>6810</v>
       </c>
+      <c r="CX17" t="n">
+        <v>6955</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24700,6 +25048,9 @@
       <c r="CW18" t="n">
         <v>20145</v>
       </c>
+      <c r="CX18" t="n">
+        <v>20495</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25008,6 +25359,9 @@
       </c>
       <c r="CW19" t="n">
         <v>16080</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>16950</v>
       </c>
     </row>
   </sheetData>
@@ -25021,7 +25375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW19"/>
+  <dimension ref="A1:CX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25125,6 +25479,7 @@
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
+    <col width="12" customWidth="1" min="102" max="102"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25435,6 +25790,9 @@
       <c r="CW1" s="1" t="n">
         <v>20260126</v>
       </c>
+      <c r="CX1" s="1" t="n">
+        <v>20260127</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25744,6 +26102,9 @@
       <c r="CW2" t="n">
         <v>16735</v>
       </c>
+      <c r="CX2" t="n">
+        <v>18100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26053,6 +26414,9 @@
       <c r="CW3" t="n">
         <v>73530</v>
       </c>
+      <c r="CX3" t="n">
+        <v>78155</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26362,6 +26726,9 @@
       <c r="CW4" t="n">
         <v>20585</v>
       </c>
+      <c r="CX4" t="n">
+        <v>22325</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26671,6 +27038,9 @@
       <c r="CW5" t="n">
         <v>17335</v>
       </c>
+      <c r="CX5" t="n">
+        <v>18090</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26980,6 +27350,9 @@
       <c r="CW6" t="n">
         <v>21280</v>
       </c>
+      <c r="CX6" t="n">
+        <v>22395</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27289,6 +27662,9 @@
       <c r="CW7" t="n">
         <v>25070</v>
       </c>
+      <c r="CX7" t="n">
+        <v>26385</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27598,6 +27974,9 @@
       <c r="CW8" t="n">
         <v>24625</v>
       </c>
+      <c r="CX8" t="n">
+        <v>26085</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27907,6 +28286,9 @@
       <c r="CW9" t="n">
         <v>1721</v>
       </c>
+      <c r="CX9" t="n">
+        <v>1712</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28216,6 +28598,9 @@
       <c r="CW10" t="n">
         <v>19550</v>
       </c>
+      <c r="CX10" t="n">
+        <v>20420</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28525,6 +28910,9 @@
       <c r="CW11" t="n">
         <v>6150</v>
       </c>
+      <c r="CX11" t="n">
+        <v>6255</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28834,6 +29222,9 @@
       <c r="CW12" t="n">
         <v>6565</v>
       </c>
+      <c r="CX12" t="n">
+        <v>6670</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29143,6 +29534,9 @@
       <c r="CW13" t="n">
         <v>6730</v>
       </c>
+      <c r="CX13" t="n">
+        <v>6880</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29452,6 +29846,9 @@
       <c r="CW14" t="n">
         <v>1935</v>
       </c>
+      <c r="CX14" t="n">
+        <v>1979</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -29761,6 +30158,9 @@
       <c r="CW15" t="n">
         <v>19820</v>
       </c>
+      <c r="CX15" t="n">
+        <v>20110</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -30070,6 +30470,9 @@
       <c r="CW16" t="n">
         <v>12550</v>
       </c>
+      <c r="CX16" t="n">
+        <v>12705</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -30379,6 +30782,9 @@
       <c r="CW17" t="n">
         <v>7090</v>
       </c>
+      <c r="CX17" t="n">
+        <v>7155</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -30688,6 +31094,9 @@
       <c r="CW18" t="n">
         <v>20535</v>
       </c>
+      <c r="CX18" t="n">
+        <v>21545</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -30996,6 +31405,9 @@
       </c>
       <c r="CW19" t="n">
         <v>17225</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>17525</v>
       </c>
     </row>
   </sheetData>
@@ -31009,7 +31421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW19"/>
+  <dimension ref="A1:CX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31113,6 +31525,7 @@
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
+    <col width="12" customWidth="1" min="102" max="102"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31423,6 +31836,9 @@
       <c r="CW1" s="1" t="n">
         <v>20260126</v>
       </c>
+      <c r="CX1" s="1" t="n">
+        <v>20260127</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31732,6 +32148,9 @@
       <c r="CW2" t="n">
         <v>15300</v>
       </c>
+      <c r="CX2" t="n">
+        <v>16435</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32041,6 +32460,9 @@
       <c r="CW3" t="n">
         <v>72100</v>
       </c>
+      <c r="CX3" t="n">
+        <v>73065</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -32350,6 +32772,9 @@
       <c r="CW4" t="n">
         <v>18900</v>
       </c>
+      <c r="CX4" t="n">
+        <v>20200</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32659,6 +33084,9 @@
       <c r="CW5" t="n">
         <v>16805</v>
       </c>
+      <c r="CX5" t="n">
+        <v>17200</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32968,6 +33396,9 @@
       <c r="CW6" t="n">
         <v>20965</v>
       </c>
+      <c r="CX6" t="n">
+        <v>21165</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -33277,6 +33708,9 @@
       <c r="CW7" t="n">
         <v>24780</v>
       </c>
+      <c r="CX7" t="n">
+        <v>24780</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -33586,6 +34020,9 @@
       <c r="CW8" t="n">
         <v>24340</v>
       </c>
+      <c r="CX8" t="n">
+        <v>24445</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33895,6 +34332,9 @@
       <c r="CW9" t="n">
         <v>1637</v>
       </c>
+      <c r="CX9" t="n">
+        <v>1618</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34204,6 +34644,9 @@
       <c r="CW10" t="n">
         <v>18730</v>
       </c>
+      <c r="CX10" t="n">
+        <v>19430</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -34513,6 +34956,9 @@
       <c r="CW11" t="n">
         <v>5780</v>
       </c>
+      <c r="CX11" t="n">
+        <v>5995</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -34822,6 +35268,9 @@
       <c r="CW12" t="n">
         <v>6125</v>
       </c>
+      <c r="CX12" t="n">
+        <v>6345</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35131,6 +35580,9 @@
       <c r="CW13" t="n">
         <v>6175</v>
       </c>
+      <c r="CX13" t="n">
+        <v>6545</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35440,6 +35892,9 @@
       <c r="CW14" t="n">
         <v>1785</v>
       </c>
+      <c r="CX14" t="n">
+        <v>1822</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35749,6 +36204,9 @@
       <c r="CW15" t="n">
         <v>18775</v>
       </c>
+      <c r="CX15" t="n">
+        <v>19475</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -36058,6 +36516,9 @@
       <c r="CW16" t="n">
         <v>11840</v>
       </c>
+      <c r="CX16" t="n">
+        <v>12160</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36367,6 +36828,9 @@
       <c r="CW17" t="n">
         <v>6790</v>
       </c>
+      <c r="CX17" t="n">
+        <v>6900</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36676,6 +37140,9 @@
       <c r="CW18" t="n">
         <v>19890</v>
       </c>
+      <c r="CX18" t="n">
+        <v>20380</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -36984,6 +37451,9 @@
       </c>
       <c r="CW19" t="n">
         <v>16080</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>16925</v>
       </c>
     </row>
   </sheetData>
@@ -36997,7 +37467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW19"/>
+  <dimension ref="A1:CX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37101,6 +37571,7 @@
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
+    <col width="12" customWidth="1" min="102" max="102"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37411,6 +37882,9 @@
       <c r="CW1" s="1" t="n">
         <v>20260126</v>
       </c>
+      <c r="CX1" s="1" t="n">
+        <v>20260127</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37720,6 +38194,9 @@
       <c r="CW2" t="n">
         <v>16735</v>
       </c>
+      <c r="CX2" t="n">
+        <v>16915</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38029,6 +38506,9 @@
       <c r="CW3" t="n">
         <v>73445</v>
       </c>
+      <c r="CX3" t="n">
+        <v>78105</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -38338,6 +38818,9 @@
       <c r="CW4" t="n">
         <v>20585</v>
       </c>
+      <c r="CX4" t="n">
+        <v>20915</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -38647,6 +39130,9 @@
       <c r="CW5" t="n">
         <v>17280</v>
       </c>
+      <c r="CX5" t="n">
+        <v>18065</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -38956,6 +39442,9 @@
       <c r="CW6" t="n">
         <v>21280</v>
       </c>
+      <c r="CX6" t="n">
+        <v>22395</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -39265,6 +39754,9 @@
       <c r="CW7" t="n">
         <v>25020</v>
       </c>
+      <c r="CX7" t="n">
+        <v>26385</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -39574,6 +40066,9 @@
       <c r="CW8" t="n">
         <v>24575</v>
       </c>
+      <c r="CX8" t="n">
+        <v>26025</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -39883,6 +40378,9 @@
       <c r="CW9" t="n">
         <v>1719</v>
       </c>
+      <c r="CX9" t="n">
+        <v>1677</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -40192,6 +40690,9 @@
       <c r="CW10" t="n">
         <v>19550</v>
       </c>
+      <c r="CX10" t="n">
+        <v>20420</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -40501,6 +41002,9 @@
       <c r="CW11" t="n">
         <v>6150</v>
       </c>
+      <c r="CX11" t="n">
+        <v>6200</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -40810,6 +41314,9 @@
       <c r="CW12" t="n">
         <v>6565</v>
       </c>
+      <c r="CX12" t="n">
+        <v>6620</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -41119,6 +41626,9 @@
       <c r="CW13" t="n">
         <v>6730</v>
       </c>
+      <c r="CX13" t="n">
+        <v>6825</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -41428,6 +41938,9 @@
       <c r="CW14" t="n">
         <v>1935</v>
       </c>
+      <c r="CX14" t="n">
+        <v>1946</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41737,6 +42250,9 @@
       <c r="CW15" t="n">
         <v>19810</v>
       </c>
+      <c r="CX15" t="n">
+        <v>19855</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -42046,6 +42562,9 @@
       <c r="CW16" t="n">
         <v>12550</v>
       </c>
+      <c r="CX16" t="n">
+        <v>12600</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42355,6 +42874,9 @@
       <c r="CW17" t="n">
         <v>7090</v>
       </c>
+      <c r="CX17" t="n">
+        <v>7080</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42664,6 +43186,9 @@
       <c r="CW18" t="n">
         <v>20535</v>
       </c>
+      <c r="CX18" t="n">
+        <v>21480</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42972,6 +43497,9 @@
       </c>
       <c r="CW19" t="n">
         <v>17140</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>17200</v>
       </c>
     </row>
   </sheetData>
@@ -42985,7 +43513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW19"/>
+  <dimension ref="A1:CX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -43089,6 +43617,7 @@
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
+    <col width="12" customWidth="1" min="102" max="102"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43399,6 +43928,9 @@
       <c r="CW1" s="1" t="n">
         <v>20260126</v>
       </c>
+      <c r="CX1" s="1" t="n">
+        <v>20260127</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -43708,6 +44240,9 @@
       <c r="CW2" t="n">
         <v>1308638</v>
       </c>
+      <c r="CX2" t="n">
+        <v>1034218</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -44017,6 +44552,9 @@
       <c r="CW3" t="n">
         <v>1543357</v>
       </c>
+      <c r="CX3" t="n">
+        <v>2988042</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -44326,6 +44864,9 @@
       <c r="CW4" t="n">
         <v>2205191</v>
       </c>
+      <c r="CX4" t="n">
+        <v>1916678</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -44635,6 +45176,9 @@
       <c r="CW5" t="n">
         <v>400924</v>
       </c>
+      <c r="CX5" t="n">
+        <v>910042</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -44944,6 +45488,9 @@
       <c r="CW6" t="n">
         <v>6049845</v>
       </c>
+      <c r="CX6" t="n">
+        <v>11863352</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -45253,6 +45800,9 @@
       <c r="CW7" t="n">
         <v>2281948</v>
       </c>
+      <c r="CX7" t="n">
+        <v>8937379</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -45562,6 +46112,9 @@
       <c r="CW8" t="n">
         <v>11093930</v>
       </c>
+      <c r="CX8" t="n">
+        <v>24475177</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -45871,6 +46424,9 @@
       <c r="CW9" t="n">
         <v>14988528</v>
       </c>
+      <c r="CX9" t="n">
+        <v>10243012</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -46180,6 +46736,9 @@
       <c r="CW10" t="n">
         <v>3886528</v>
       </c>
+      <c r="CX10" t="n">
+        <v>5480397</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -46489,6 +47048,9 @@
       <c r="CW11" t="n">
         <v>2742216</v>
       </c>
+      <c r="CX11" t="n">
+        <v>1269672</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -46798,6 +47360,9 @@
       <c r="CW12" t="n">
         <v>7016669</v>
       </c>
+      <c r="CX12" t="n">
+        <v>5354605</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -47107,6 +47672,9 @@
       <c r="CW13" t="n">
         <v>16922355</v>
       </c>
+      <c r="CX13" t="n">
+        <v>13742765</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -47416,6 +47984,9 @@
       <c r="CW14" t="n">
         <v>98497868</v>
       </c>
+      <c r="CX14" t="n">
+        <v>74291863</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -47725,6 +48296,9 @@
       <c r="CW15" t="n">
         <v>5611328</v>
       </c>
+      <c r="CX15" t="n">
+        <v>2772735</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -48034,6 +48608,9 @@
       <c r="CW16" t="n">
         <v>1084470</v>
       </c>
+      <c r="CX16" t="n">
+        <v>670193</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -48343,6 +48920,9 @@
       <c r="CW17" t="n">
         <v>248965</v>
       </c>
+      <c r="CX17" t="n">
+        <v>155465</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -48652,6 +49232,9 @@
       <c r="CW18" t="n">
         <v>170338</v>
       </c>
+      <c r="CX18" t="n">
+        <v>394889</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -48960,6 +49543,9 @@
       </c>
       <c r="CW19" t="n">
         <v>220664</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>162310</v>
       </c>
     </row>
   </sheetData>
@@ -48973,7 +49559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD19"/>
+  <dimension ref="A1:CE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -49058,6 +49644,7 @@
     <col width="10" customWidth="1" min="80" max="80"/>
     <col width="10" customWidth="1" min="81" max="81"/>
     <col width="10" customWidth="1" min="82" max="82"/>
+    <col width="10" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -49311,6 +49898,9 @@
       <c r="CD1" s="1" t="n">
         <v>20260126</v>
       </c>
+      <c r="CE1" s="1" t="n">
+        <v>20260127</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -49563,6 +50153,9 @@
       <c r="CD2" t="n">
         <v>100</v>
       </c>
+      <c r="CE2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -49815,6 +50408,9 @@
       <c r="CD3" t="n">
         <v>100</v>
       </c>
+      <c r="CE3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -50067,6 +50663,9 @@
       <c r="CD4" t="n">
         <v>100</v>
       </c>
+      <c r="CE4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -50319,6 +50918,9 @@
       <c r="CD5" t="n">
         <v>78</v>
       </c>
+      <c r="CE5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -50571,6 +51173,9 @@
       <c r="CD6" t="n">
         <v>100</v>
       </c>
+      <c r="CE6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -50823,6 +51428,9 @@
       <c r="CD7" t="n">
         <v>100</v>
       </c>
+      <c r="CE7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -51075,6 +51683,9 @@
       <c r="CD8" t="n">
         <v>100</v>
       </c>
+      <c r="CE8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -51327,6 +51938,9 @@
       <c r="CD9" t="n">
         <v>100</v>
       </c>
+      <c r="CE9" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -51579,6 +52193,9 @@
       <c r="CD10" t="n">
         <v>100</v>
       </c>
+      <c r="CE10" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -51831,6 +52448,9 @@
       <c r="CD11" t="n">
         <v>100</v>
       </c>
+      <c r="CE11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -52083,6 +52703,9 @@
       <c r="CD12" t="n">
         <v>100</v>
       </c>
+      <c r="CE12" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -52335,6 +52958,9 @@
       <c r="CD13" t="n">
         <v>100</v>
       </c>
+      <c r="CE13" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -52587,6 +53213,9 @@
       <c r="CD14" t="n">
         <v>100</v>
       </c>
+      <c r="CE14" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -52839,6 +53468,9 @@
       <c r="CD15" t="n">
         <v>76</v>
       </c>
+      <c r="CE15" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -53091,6 +53723,9 @@
       <c r="CD16" t="n">
         <v>100</v>
       </c>
+      <c r="CE16" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -53343,6 +53978,9 @@
       <c r="CD17" t="n">
         <v>100</v>
       </c>
+      <c r="CE17" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -53595,6 +54233,9 @@
       <c r="CD18" t="n">
         <v>99</v>
       </c>
+      <c r="CE18" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -53845,6 +54486,9 @@
         <v>56</v>
       </c>
       <c r="CD19" t="n">
+        <v>100</v>
+      </c>
+      <c r="CE19" t="n">
         <v>100</v>
       </c>
     </row>
@@ -53859,7 +54503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP19"/>
+  <dimension ref="A1:AQ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -53904,6 +54548,7 @@
     <col width="10" customWidth="1" min="40" max="40"/>
     <col width="10" customWidth="1" min="41" max="41"/>
     <col width="10" customWidth="1" min="42" max="42"/>
+    <col width="10" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -54037,6 +54682,9 @@
       <c r="AP1" s="1" t="n">
         <v>20260126</v>
       </c>
+      <c r="AQ1" s="1" t="n">
+        <v>20260127</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -54169,6 +54817,9 @@
       <c r="AP2" t="n">
         <v>100</v>
       </c>
+      <c r="AQ2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -54301,6 +54952,9 @@
       <c r="AP3" t="n">
         <v>100</v>
       </c>
+      <c r="AQ3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -54433,6 +55087,9 @@
       <c r="AP4" t="n">
         <v>100</v>
       </c>
+      <c r="AQ4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -54565,6 +55222,9 @@
       <c r="AP5" t="n">
         <v>86</v>
       </c>
+      <c r="AQ5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -54697,6 +55357,9 @@
       <c r="AP6" t="n">
         <v>100</v>
       </c>
+      <c r="AQ6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -54829,6 +55492,9 @@
       <c r="AP7" t="n">
         <v>100</v>
       </c>
+      <c r="AQ7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -54961,6 +55627,9 @@
       <c r="AP8" t="n">
         <v>100</v>
       </c>
+      <c r="AQ8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -55093,6 +55762,9 @@
       <c r="AP9" t="n">
         <v>82</v>
       </c>
+      <c r="AQ9" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -55225,6 +55897,9 @@
       <c r="AP10" t="n">
         <v>100</v>
       </c>
+      <c r="AQ10" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -55357,6 +56032,9 @@
       <c r="AP11" t="n">
         <v>100</v>
       </c>
+      <c r="AQ11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -55489,6 +56167,9 @@
       <c r="AP12" t="n">
         <v>100</v>
       </c>
+      <c r="AQ12" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -55621,6 +56302,9 @@
       <c r="AP13" t="n">
         <v>100</v>
       </c>
+      <c r="AQ13" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -55753,6 +56437,9 @@
       <c r="AP14" t="n">
         <v>93</v>
       </c>
+      <c r="AQ14" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -55885,6 +56572,9 @@
       <c r="AP15" t="n">
         <v>86</v>
       </c>
+      <c r="AQ15" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -56017,6 +56707,9 @@
       <c r="AP16" t="n">
         <v>100</v>
       </c>
+      <c r="AQ16" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -56149,6 +56842,9 @@
       <c r="AP17" t="n">
         <v>100</v>
       </c>
+      <c r="AQ17" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -56281,6 +56977,9 @@
       <c r="AP18" t="n">
         <v>99</v>
       </c>
+      <c r="AQ18" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -56411,6 +57110,9 @@
         <v>72</v>
       </c>
       <c r="AP19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>100</v>
       </c>
     </row>
@@ -56425,7 +57127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD19"/>
+  <dimension ref="A1:CE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -56510,6 +57212,7 @@
     <col width="10" customWidth="1" min="80" max="80"/>
     <col width="10" customWidth="1" min="81" max="81"/>
     <col width="10" customWidth="1" min="82" max="82"/>
+    <col width="10" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -56763,6 +57466,9 @@
       <c r="CD1" s="1" t="n">
         <v>20260126</v>
       </c>
+      <c r="CE1" s="1" t="n">
+        <v>20260127</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -57015,6 +57721,9 @@
       <c r="CD2" t="n">
         <v>96</v>
       </c>
+      <c r="CE2" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -57267,6 +57976,9 @@
       <c r="CD3" t="n">
         <v>56</v>
       </c>
+      <c r="CE3" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -57519,6 +58231,9 @@
       <c r="CD4" t="n">
         <v>146</v>
       </c>
+      <c r="CE4" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -57771,6 +58486,9 @@
       <c r="CD5" t="n">
         <v>28</v>
       </c>
+      <c r="CE5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -58023,6 +58741,9 @@
       <c r="CD6" t="n">
         <v>62</v>
       </c>
+      <c r="CE6" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -58275,6 +58996,9 @@
       <c r="CD7" t="n">
         <v>50</v>
       </c>
+      <c r="CE7" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -58527,6 +59251,9 @@
       <c r="CD8" t="n">
         <v>49</v>
       </c>
+      <c r="CE8" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -58779,6 +59506,9 @@
       <c r="CD9" t="n">
         <v>111</v>
       </c>
+      <c r="CE9" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -59031,6 +59761,9 @@
       <c r="CD10" t="n">
         <v>82</v>
       </c>
+      <c r="CE10" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -59283,6 +60016,9 @@
       <c r="CD11" t="n">
         <v>137</v>
       </c>
+      <c r="CE11" t="n">
+        <v>115</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -59535,6 +60271,9 @@
       <c r="CD12" t="n">
         <v>138</v>
       </c>
+      <c r="CE12" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -59787,6 +60526,9 @@
       <c r="CD13" t="n">
         <v>149</v>
       </c>
+      <c r="CE13" t="n">
+        <v>124</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -60039,6 +60781,9 @@
       <c r="CD14" t="n">
         <v>129</v>
       </c>
+      <c r="CE14" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -60291,6 +61036,9 @@
       <c r="CD15" t="n">
         <v>26</v>
       </c>
+      <c r="CE15" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -60543,6 +61291,9 @@
       <c r="CD16" t="n">
         <v>132</v>
       </c>
+      <c r="CE16" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -60795,6 +61546,9 @@
       <c r="CD17" t="n">
         <v>129</v>
       </c>
+      <c r="CE17" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -61047,6 +61801,9 @@
       <c r="CD18" t="n">
         <v>53</v>
       </c>
+      <c r="CE18" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -61298,6 +62055,9 @@
       </c>
       <c r="CD19" t="n">
         <v>88</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ19"/>
+  <dimension ref="A1:AR19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -756,6 +756,7 @@
     <col width="10" customWidth="1" min="41" max="41"/>
     <col width="10" customWidth="1" min="42" max="42"/>
     <col width="10" customWidth="1" min="43" max="43"/>
+    <col width="10" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -892,6 +893,9 @@
       <c r="AQ1" s="1" t="n">
         <v>20260127</v>
       </c>
+      <c r="AR1" s="1" t="n">
+        <v>20260128</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1027,6 +1031,9 @@
       <c r="AQ2" t="n">
         <v>106</v>
       </c>
+      <c r="AR2" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1162,6 +1169,9 @@
       <c r="AQ3" t="n">
         <v>126</v>
       </c>
+      <c r="AR3" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1297,6 +1307,9 @@
       <c r="AQ4" t="n">
         <v>165</v>
       </c>
+      <c r="AR4" t="n">
+        <v>190</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1432,6 +1445,9 @@
       <c r="AQ5" t="n">
         <v>111</v>
       </c>
+      <c r="AR5" t="n">
+        <v>163</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1567,6 +1583,9 @@
       <c r="AQ6" t="n">
         <v>126</v>
       </c>
+      <c r="AR6" t="n">
+        <v>149</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1702,6 +1721,9 @@
       <c r="AQ7" t="n">
         <v>116</v>
       </c>
+      <c r="AR7" t="n">
+        <v>130</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1837,6 +1859,9 @@
       <c r="AQ8" t="n">
         <v>116</v>
       </c>
+      <c r="AR8" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1972,6 +1997,9 @@
       <c r="AQ9" t="n">
         <v>53</v>
       </c>
+      <c r="AR9" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2107,6 +2135,9 @@
       <c r="AQ10" t="n">
         <v>153</v>
       </c>
+      <c r="AR10" t="n">
+        <v>197</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2242,6 +2273,9 @@
       <c r="AQ11" t="n">
         <v>149</v>
       </c>
+      <c r="AR11" t="n">
+        <v>198</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2377,6 +2411,9 @@
       <c r="AQ12" t="n">
         <v>135</v>
       </c>
+      <c r="AR12" t="n">
+        <v>190</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2512,6 +2549,9 @@
       <c r="AQ13" t="n">
         <v>151</v>
       </c>
+      <c r="AR13" t="n">
+        <v>196</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2647,6 +2687,9 @@
       <c r="AQ14" t="n">
         <v>84</v>
       </c>
+      <c r="AR14" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2782,6 +2825,9 @@
       <c r="AQ15" t="n">
         <v>41</v>
       </c>
+      <c r="AR15" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2917,6 +2963,9 @@
       <c r="AQ16" t="n">
         <v>136</v>
       </c>
+      <c r="AR16" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3052,6 +3101,9 @@
       <c r="AQ17" t="n">
         <v>93</v>
       </c>
+      <c r="AR17" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3187,6 +3239,9 @@
       <c r="AQ18" t="n">
         <v>127</v>
       </c>
+      <c r="AR18" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3321,6 +3376,9 @@
       </c>
       <c r="AQ19" t="n">
         <v>85</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -3334,7 +3392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE19"/>
+  <dimension ref="A1:CF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3420,6 +3478,7 @@
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
+    <col width="12" customWidth="1" min="84" max="84"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3838,6 +3897,11 @@
           <t>20260127</t>
         </is>
       </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>20260128</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4093,6 +4157,9 @@
       <c r="CE2" t="n">
         <v>110</v>
       </c>
+      <c r="CF2" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4348,6 +4415,9 @@
       <c r="CE3" t="n">
         <v>112</v>
       </c>
+      <c r="CF3" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4603,6 +4673,9 @@
       <c r="CE4" t="n">
         <v>113</v>
       </c>
+      <c r="CF4" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4858,6 +4931,9 @@
       <c r="CE5" t="n">
         <v>106</v>
       </c>
+      <c r="CF5" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5113,6 +5189,9 @@
       <c r="CE6" t="n">
         <v>111</v>
       </c>
+      <c r="CF6" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5368,6 +5447,9 @@
       <c r="CE7" t="n">
         <v>110</v>
       </c>
+      <c r="CF7" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5623,6 +5705,9 @@
       <c r="CE8" t="n">
         <v>111</v>
       </c>
+      <c r="CF8" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5878,6 +5963,9 @@
       <c r="CE9" t="n">
         <v>122</v>
       </c>
+      <c r="CF9" t="n">
+        <v>130</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6133,6 +6221,9 @@
       <c r="CE10" t="n">
         <v>110</v>
       </c>
+      <c r="CF10" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6388,6 +6479,9 @@
       <c r="CE11" t="n">
         <v>119</v>
       </c>
+      <c r="CF11" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6643,6 +6737,9 @@
       <c r="CE12" t="n">
         <v>119</v>
       </c>
+      <c r="CF12" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6898,6 +6995,9 @@
       <c r="CE13" t="n">
         <v>122</v>
       </c>
+      <c r="CF13" t="n">
+        <v>131</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7153,6 +7253,9 @@
       <c r="CE14" t="n">
         <v>132</v>
       </c>
+      <c r="CF14" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7408,6 +7511,9 @@
       <c r="CE15" t="n">
         <v>102</v>
       </c>
+      <c r="CF15" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7663,6 +7769,9 @@
       <c r="CE16" t="n">
         <v>119</v>
       </c>
+      <c r="CF16" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7918,6 +8027,9 @@
       <c r="CE17" t="n">
         <v>116</v>
       </c>
+      <c r="CF17" t="n">
+        <v>123</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8173,6 +8285,9 @@
       <c r="CE18" t="n">
         <v>108</v>
       </c>
+      <c r="CF18" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8427,6 +8542,9 @@
       </c>
       <c r="CE19" t="n">
         <v>106</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -8440,7 +8558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL19"/>
+  <dimension ref="A1:BM19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8458,6 +8576,7 @@
     <col width="12" customWidth="1" min="62" max="62"/>
     <col width="12" customWidth="1" min="63" max="63"/>
     <col width="12" customWidth="1" min="64" max="64"/>
+    <col width="12" customWidth="1" min="65" max="65"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8683,6 +8802,11 @@
           <t>20260127</t>
         </is>
       </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>20260128</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8881,6 +9005,9 @@
       <c r="BL2" t="n">
         <v>46.05</v>
       </c>
+      <c r="BM2" t="n">
+        <v>56.92</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9079,6 +9206,9 @@
       <c r="BL3" t="n">
         <v>-19.01</v>
       </c>
+      <c r="BM3" t="n">
+        <v>-13.07</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9277,6 +9407,9 @@
       <c r="BL4" t="n">
         <v>68.52</v>
       </c>
+      <c r="BM4" t="n">
+        <v>102.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9475,6 +9608,9 @@
       <c r="BL5" t="n">
         <v>-34.65</v>
       </c>
+      <c r="BM5" t="n">
+        <v>-17.13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9673,6 +9809,9 @@
       <c r="BL6" t="n">
         <v>-16.89</v>
       </c>
+      <c r="BM6" t="n">
+        <v>-9.48</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9871,6 +10010,9 @@
       <c r="BL7" t="n">
         <v>-19.41</v>
       </c>
+      <c r="BM7" t="n">
+        <v>-19.51</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10069,6 +10211,9 @@
       <c r="BL8" t="n">
         <v>-21.77</v>
       </c>
+      <c r="BM8" t="n">
+        <v>-21.28</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10267,6 +10412,9 @@
       <c r="BL9" t="n">
         <v>32.63</v>
       </c>
+      <c r="BM9" t="n">
+        <v>48.08</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10465,6 +10613,9 @@
       <c r="BL10" t="n">
         <v>-8.710000000000001</v>
       </c>
+      <c r="BM10" t="n">
+        <v>14.13</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10663,6 +10814,9 @@
       <c r="BL11" t="n">
         <v>59.25</v>
       </c>
+      <c r="BM11" t="n">
+        <v>91.84</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10861,6 +11015,9 @@
       <c r="BL12" t="n">
         <v>43.98</v>
       </c>
+      <c r="BM12" t="n">
+        <v>77.5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11059,6 +11216,9 @@
       <c r="BL13" t="n">
         <v>52.72</v>
       </c>
+      <c r="BM13" t="n">
+        <v>89.62</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11257,6 +11417,9 @@
       <c r="BL14" t="n">
         <v>41.62</v>
       </c>
+      <c r="BM14" t="n">
+        <v>65.72</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11455,6 +11618,9 @@
       <c r="BL15" t="n">
         <v>30.28</v>
       </c>
+      <c r="BM15" t="n">
+        <v>32.22</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11653,6 +11819,9 @@
       <c r="BL16" t="n">
         <v>63</v>
       </c>
+      <c r="BM16" t="n">
+        <v>89.31</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11851,6 +12020,9 @@
       <c r="BL17" t="n">
         <v>35.46</v>
       </c>
+      <c r="BM17" t="n">
+        <v>61.21</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12049,6 +12221,9 @@
       <c r="BL18" t="n">
         <v>-21.75</v>
       </c>
+      <c r="BM18" t="n">
+        <v>-11.83</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12246,6 +12421,9 @@
       </c>
       <c r="BL19" t="n">
         <v>68.28</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>82.28</v>
       </c>
     </row>
   </sheetData>
@@ -12259,7 +12437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ19"/>
+  <dimension ref="A1:AR19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12305,6 +12483,7 @@
     <col width="12" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="12" customWidth="1" min="43" max="43"/>
+    <col width="12" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12523,6 +12702,11 @@
           <t>20260127</t>
         </is>
       </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>20260128</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12658,6 +12842,9 @@
       <c r="AQ2" t="n">
         <v>211</v>
       </c>
+      <c r="AR2" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12793,6 +12980,9 @@
       <c r="AQ3" t="n">
         <v>67</v>
       </c>
+      <c r="AR3" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12928,6 +13118,9 @@
       <c r="AQ4" t="n">
         <v>336</v>
       </c>
+      <c r="AR4" t="n">
+        <v>238</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13063,6 +13256,9 @@
       <c r="AQ5" t="n">
         <v>111</v>
       </c>
+      <c r="AR5" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13198,6 +13394,9 @@
       <c r="AQ6" t="n">
         <v>194</v>
       </c>
+      <c r="AR6" t="n">
+        <v>124</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13333,6 +13532,9 @@
       <c r="AQ7" t="n">
         <v>118</v>
       </c>
+      <c r="AR7" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13468,6 +13670,9 @@
       <c r="AQ8" t="n">
         <v>135</v>
       </c>
+      <c r="AR8" t="n">
+        <v>136</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13603,6 +13808,9 @@
       <c r="AQ9" t="n">
         <v>73</v>
       </c>
+      <c r="AR9" t="n">
+        <v>172</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13738,6 +13946,9 @@
       <c r="AQ10" t="n">
         <v>211</v>
       </c>
+      <c r="AR10" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13873,6 +14084,9 @@
       <c r="AQ11" t="n">
         <v>58</v>
       </c>
+      <c r="AR11" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14008,6 +14222,9 @@
       <c r="AQ12" t="n">
         <v>101</v>
       </c>
+      <c r="AR12" t="n">
+        <v>132</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14143,6 +14360,9 @@
       <c r="AQ13" t="n">
         <v>110</v>
       </c>
+      <c r="AR13" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14278,6 +14498,9 @@
       <c r="AQ14" t="n">
         <v>78</v>
       </c>
+      <c r="AR14" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14413,6 +14636,9 @@
       <c r="AQ15" t="n">
         <v>62</v>
       </c>
+      <c r="AR15" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14548,6 +14774,9 @@
       <c r="AQ16" t="n">
         <v>66</v>
       </c>
+      <c r="AR16" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14683,6 +14912,9 @@
       <c r="AQ17" t="n">
         <v>87</v>
       </c>
+      <c r="AR17" t="n">
+        <v>184</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14818,6 +15050,9 @@
       <c r="AQ18" t="n">
         <v>140</v>
       </c>
+      <c r="AR18" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14952,6 +15187,9 @@
       </c>
       <c r="AQ19" t="n">
         <v>130</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -14965,7 +15203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU19"/>
+  <dimension ref="A1:BV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15041,6 +15279,7 @@
     <col width="10" customWidth="1" min="71" max="71"/>
     <col width="10" customWidth="1" min="72" max="72"/>
     <col width="10" customWidth="1" min="73" max="73"/>
+    <col width="10" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15267,6 +15506,9 @@
       <c r="BU1" s="1" t="n">
         <v>20260127</v>
       </c>
+      <c r="BV1" s="1" t="n">
+        <v>20260128</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15492,6 +15734,9 @@
       <c r="BU2" t="n">
         <v>113</v>
       </c>
+      <c r="BV2" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15717,6 +15962,9 @@
       <c r="BU3" t="n">
         <v>89</v>
       </c>
+      <c r="BV3" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15942,6 +16190,9 @@
       <c r="BU4" t="n">
         <v>154</v>
       </c>
+      <c r="BV4" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16167,6 +16418,9 @@
       <c r="BU5" t="n">
         <v>83</v>
       </c>
+      <c r="BV5" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16392,6 +16646,9 @@
       <c r="BU6" t="n">
         <v>89</v>
       </c>
+      <c r="BV6" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16617,6 +16874,9 @@
       <c r="BU7" t="n">
         <v>82</v>
       </c>
+      <c r="BV7" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16842,6 +17102,9 @@
       <c r="BU8" t="n">
         <v>80</v>
       </c>
+      <c r="BV8" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17067,6 +17330,9 @@
       <c r="BU9" t="n">
         <v>92</v>
       </c>
+      <c r="BV9" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17292,6 +17558,9 @@
       <c r="BU10" t="n">
         <v>109</v>
       </c>
+      <c r="BV10" t="n">
+        <v>141</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17517,6 +17786,9 @@
       <c r="BU11" t="n">
         <v>130</v>
       </c>
+      <c r="BV11" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17742,6 +18014,9 @@
       <c r="BU12" t="n">
         <v>125</v>
       </c>
+      <c r="BV12" t="n">
+        <v>161</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17967,6 +18242,9 @@
       <c r="BU13" t="n">
         <v>136</v>
       </c>
+      <c r="BV13" t="n">
+        <v>164</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18192,6 +18470,9 @@
       <c r="BU14" t="n">
         <v>116</v>
       </c>
+      <c r="BV14" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18417,6 +18698,9 @@
       <c r="BU15" t="n">
         <v>41</v>
       </c>
+      <c r="BV15" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -18642,6 +18926,9 @@
       <c r="BU16" t="n">
         <v>127</v>
       </c>
+      <c r="BV16" t="n">
+        <v>152</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -18867,6 +19154,9 @@
       <c r="BU17" t="n">
         <v>110</v>
       </c>
+      <c r="BV17" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -19092,6 +19382,9 @@
       <c r="BU18" t="n">
         <v>90</v>
       </c>
+      <c r="BV18" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -19316,6 +19609,9 @@
       </c>
       <c r="BU19" t="n">
         <v>104</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -19329,7 +19625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX19"/>
+  <dimension ref="A1:CY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19434,6 +19730,7 @@
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
     <col width="12" customWidth="1" min="102" max="102"/>
+    <col width="12" customWidth="1" min="103" max="103"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19747,6 +20044,9 @@
       <c r="CX1" s="1" t="n">
         <v>20260127</v>
       </c>
+      <c r="CY1" s="1" t="n">
+        <v>20260128</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20059,6 +20359,9 @@
       <c r="CX2" t="n">
         <v>16520</v>
       </c>
+      <c r="CY2" t="n">
+        <v>16775</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20371,6 +20674,9 @@
       <c r="CX3" t="n">
         <v>73190</v>
       </c>
+      <c r="CY3" t="n">
+        <v>79680</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20683,6 +20989,9 @@
       <c r="CX4" t="n">
         <v>20305</v>
       </c>
+      <c r="CY4" t="n">
+        <v>20950</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20995,6 +21304,9 @@
       <c r="CX5" t="n">
         <v>17340</v>
       </c>
+      <c r="CY5" t="n">
+        <v>18610</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21307,6 +21619,9 @@
       <c r="CX6" t="n">
         <v>21230</v>
       </c>
+      <c r="CY6" t="n">
+        <v>22855</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21619,6 +21934,9 @@
       <c r="CX7" t="n">
         <v>24985</v>
       </c>
+      <c r="CY7" t="n">
+        <v>26830</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21931,6 +22249,9 @@
       <c r="CX8" t="n">
         <v>24510</v>
       </c>
+      <c r="CY8" t="n">
+        <v>26485</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22243,6 +22564,9 @@
       <c r="CX9" t="n">
         <v>1678</v>
       </c>
+      <c r="CY9" t="n">
+        <v>1740</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22555,6 +22879,9 @@
       <c r="CX10" t="n">
         <v>19555</v>
       </c>
+      <c r="CY10" t="n">
+        <v>20855</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22867,6 +23194,9 @@
       <c r="CX11" t="n">
         <v>6040</v>
       </c>
+      <c r="CY11" t="n">
+        <v>6260</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -23179,6 +23509,9 @@
       <c r="CX12" t="n">
         <v>6440</v>
       </c>
+      <c r="CY12" t="n">
+        <v>6735</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -23491,6 +23824,9 @@
       <c r="CX13" t="n">
         <v>6560</v>
       </c>
+      <c r="CY13" t="n">
+        <v>6915</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -23803,6 +24139,9 @@
       <c r="CX14" t="n">
         <v>1864</v>
       </c>
+      <c r="CY14" t="n">
+        <v>1997</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24115,6 +24454,9 @@
       <c r="CX15" t="n">
         <v>19555</v>
       </c>
+      <c r="CY15" t="n">
+        <v>19855</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24427,6 +24769,9 @@
       <c r="CX16" t="n">
         <v>12285</v>
       </c>
+      <c r="CY16" t="n">
+        <v>12780</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24739,6 +25084,9 @@
       <c r="CX17" t="n">
         <v>6955</v>
       </c>
+      <c r="CY17" t="n">
+        <v>7185</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25051,6 +25399,9 @@
       <c r="CX18" t="n">
         <v>20495</v>
       </c>
+      <c r="CY18" t="n">
+        <v>22235</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25362,6 +25713,9 @@
       </c>
       <c r="CX19" t="n">
         <v>16950</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>17255</v>
       </c>
     </row>
   </sheetData>
@@ -25375,7 +25729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX19"/>
+  <dimension ref="A1:CY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25480,6 +25834,7 @@
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
     <col width="12" customWidth="1" min="102" max="102"/>
+    <col width="12" customWidth="1" min="103" max="103"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25793,6 +26148,9 @@
       <c r="CX1" s="1" t="n">
         <v>20260127</v>
       </c>
+      <c r="CY1" s="1" t="n">
+        <v>20260128</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26105,6 +26463,9 @@
       <c r="CX2" t="n">
         <v>18100</v>
       </c>
+      <c r="CY2" t="n">
+        <v>17445</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26417,6 +26778,9 @@
       <c r="CX3" t="n">
         <v>78155</v>
       </c>
+      <c r="CY3" t="n">
+        <v>83155</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26729,6 +27093,9 @@
       <c r="CX4" t="n">
         <v>22325</v>
       </c>
+      <c r="CY4" t="n">
+        <v>21960</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27041,6 +27408,9 @@
       <c r="CX5" t="n">
         <v>18090</v>
       </c>
+      <c r="CY5" t="n">
+        <v>19165</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27353,6 +27723,9 @@
       <c r="CX6" t="n">
         <v>22395</v>
       </c>
+      <c r="CY6" t="n">
+        <v>23770</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27665,6 +28038,9 @@
       <c r="CX7" t="n">
         <v>26385</v>
       </c>
+      <c r="CY7" t="n">
+        <v>27635</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27977,6 +28353,9 @@
       <c r="CX8" t="n">
         <v>26085</v>
       </c>
+      <c r="CY8" t="n">
+        <v>27560</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28289,6 +28668,9 @@
       <c r="CX9" t="n">
         <v>1712</v>
       </c>
+      <c r="CY9" t="n">
+        <v>1876</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28601,6 +28983,9 @@
       <c r="CX10" t="n">
         <v>20420</v>
       </c>
+      <c r="CY10" t="n">
+        <v>21995</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28913,6 +29298,9 @@
       <c r="CX11" t="n">
         <v>6255</v>
       </c>
+      <c r="CY11" t="n">
+        <v>6750</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29225,6 +29613,9 @@
       <c r="CX12" t="n">
         <v>6670</v>
       </c>
+      <c r="CY12" t="n">
+        <v>7240</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29537,6 +29928,9 @@
       <c r="CX13" t="n">
         <v>6880</v>
       </c>
+      <c r="CY13" t="n">
+        <v>7495</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29849,6 +30243,9 @@
       <c r="CX14" t="n">
         <v>1979</v>
       </c>
+      <c r="CY14" t="n">
+        <v>2175</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -30161,6 +30558,9 @@
       <c r="CX15" t="n">
         <v>20110</v>
       </c>
+      <c r="CY15" t="n">
+        <v>20560</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -30473,6 +30873,9 @@
       <c r="CX16" t="n">
         <v>12705</v>
       </c>
+      <c r="CY16" t="n">
+        <v>13545</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -30785,6 +31188,9 @@
       <c r="CX17" t="n">
         <v>7155</v>
       </c>
+      <c r="CY17" t="n">
+        <v>7625</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -31097,6 +31503,9 @@
       <c r="CX18" t="n">
         <v>21545</v>
       </c>
+      <c r="CY18" t="n">
+        <v>22680</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -31408,6 +31817,9 @@
       </c>
       <c r="CX19" t="n">
         <v>17525</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>17975</v>
       </c>
     </row>
   </sheetData>
@@ -31421,7 +31833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX19"/>
+  <dimension ref="A1:CY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31526,6 +31938,7 @@
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
     <col width="12" customWidth="1" min="102" max="102"/>
+    <col width="12" customWidth="1" min="103" max="103"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31839,6 +32252,9 @@
       <c r="CX1" s="1" t="n">
         <v>20260127</v>
       </c>
+      <c r="CY1" s="1" t="n">
+        <v>20260128</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32151,6 +32567,9 @@
       <c r="CX2" t="n">
         <v>16435</v>
       </c>
+      <c r="CY2" t="n">
+        <v>16760</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32463,6 +32882,9 @@
       <c r="CX3" t="n">
         <v>73065</v>
       </c>
+      <c r="CY3" t="n">
+        <v>79040</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -32775,6 +33197,9 @@
       <c r="CX4" t="n">
         <v>20200</v>
       </c>
+      <c r="CY4" t="n">
+        <v>20950</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -33087,6 +33512,9 @@
       <c r="CX5" t="n">
         <v>17200</v>
       </c>
+      <c r="CY5" t="n">
+        <v>18450</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -33399,6 +33827,9 @@
       <c r="CX6" t="n">
         <v>21165</v>
       </c>
+      <c r="CY6" t="n">
+        <v>22685</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -33711,6 +34142,9 @@
       <c r="CX7" t="n">
         <v>24780</v>
       </c>
+      <c r="CY7" t="n">
+        <v>26605</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -34023,6 +34457,9 @@
       <c r="CX8" t="n">
         <v>24445</v>
       </c>
+      <c r="CY8" t="n">
+        <v>26350</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -34335,6 +34772,9 @@
       <c r="CX9" t="n">
         <v>1618</v>
       </c>
+      <c r="CY9" t="n">
+        <v>1727</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34647,6 +35087,9 @@
       <c r="CX10" t="n">
         <v>19430</v>
       </c>
+      <c r="CY10" t="n">
+        <v>20775</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -34959,6 +35402,9 @@
       <c r="CX11" t="n">
         <v>5995</v>
       </c>
+      <c r="CY11" t="n">
+        <v>6260</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -35271,6 +35717,9 @@
       <c r="CX12" t="n">
         <v>6345</v>
       </c>
+      <c r="CY12" t="n">
+        <v>6680</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35583,6 +36032,9 @@
       <c r="CX13" t="n">
         <v>6545</v>
       </c>
+      <c r="CY13" t="n">
+        <v>6900</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35895,6 +36347,9 @@
       <c r="CX14" t="n">
         <v>1822</v>
       </c>
+      <c r="CY14" t="n">
+        <v>1995</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36207,6 +36662,9 @@
       <c r="CX15" t="n">
         <v>19475</v>
       </c>
+      <c r="CY15" t="n">
+        <v>19850</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -36519,6 +36977,9 @@
       <c r="CX16" t="n">
         <v>12160</v>
       </c>
+      <c r="CY16" t="n">
+        <v>12755</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36831,6 +37292,9 @@
       <c r="CX17" t="n">
         <v>6900</v>
       </c>
+      <c r="CY17" t="n">
+        <v>7180</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -37143,6 +37607,9 @@
       <c r="CX18" t="n">
         <v>20380</v>
       </c>
+      <c r="CY18" t="n">
+        <v>21790</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -37454,6 +37921,9 @@
       </c>
       <c r="CX19" t="n">
         <v>16925</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>17250</v>
       </c>
     </row>
   </sheetData>
@@ -37467,7 +37937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX19"/>
+  <dimension ref="A1:CY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37572,6 +38042,7 @@
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
     <col width="12" customWidth="1" min="102" max="102"/>
+    <col width="12" customWidth="1" min="103" max="103"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37885,6 +38356,9 @@
       <c r="CX1" s="1" t="n">
         <v>20260127</v>
       </c>
+      <c r="CY1" s="1" t="n">
+        <v>20260128</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -38197,6 +38671,9 @@
       <c r="CX2" t="n">
         <v>16915</v>
       </c>
+      <c r="CY2" t="n">
+        <v>17115</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38509,6 +38986,9 @@
       <c r="CX3" t="n">
         <v>78105</v>
       </c>
+      <c r="CY3" t="n">
+        <v>82950</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -38821,6 +39301,9 @@
       <c r="CX4" t="n">
         <v>20915</v>
       </c>
+      <c r="CY4" t="n">
+        <v>21825</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -39133,6 +39616,9 @@
       <c r="CX5" t="n">
         <v>18065</v>
       </c>
+      <c r="CY5" t="n">
+        <v>19120</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -39445,6 +39931,9 @@
       <c r="CX6" t="n">
         <v>22395</v>
       </c>
+      <c r="CY6" t="n">
+        <v>23770</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -39757,6 +40246,9 @@
       <c r="CX7" t="n">
         <v>26385</v>
       </c>
+      <c r="CY7" t="n">
+        <v>27605</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40069,6 +40561,9 @@
       <c r="CX8" t="n">
         <v>26025</v>
       </c>
+      <c r="CY8" t="n">
+        <v>27560</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -40381,6 +40876,9 @@
       <c r="CX9" t="n">
         <v>1677</v>
       </c>
+      <c r="CY9" t="n">
+        <v>1833</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -40693,6 +41191,9 @@
       <c r="CX10" t="n">
         <v>20420</v>
       </c>
+      <c r="CY10" t="n">
+        <v>21975</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -41005,6 +41506,9 @@
       <c r="CX11" t="n">
         <v>6200</v>
       </c>
+      <c r="CY11" t="n">
+        <v>6740</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -41317,6 +41821,9 @@
       <c r="CX12" t="n">
         <v>6620</v>
       </c>
+      <c r="CY12" t="n">
+        <v>7240</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -41629,6 +42136,9 @@
       <c r="CX13" t="n">
         <v>6825</v>
       </c>
+      <c r="CY13" t="n">
+        <v>7455</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -41941,6 +42451,9 @@
       <c r="CX14" t="n">
         <v>1946</v>
       </c>
+      <c r="CY14" t="n">
+        <v>2155</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42253,6 +42766,9 @@
       <c r="CX15" t="n">
         <v>19855</v>
       </c>
+      <c r="CY15" t="n">
+        <v>20350</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -42565,6 +43081,9 @@
       <c r="CX16" t="n">
         <v>12600</v>
       </c>
+      <c r="CY16" t="n">
+        <v>13530</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42877,6 +43396,9 @@
       <c r="CX17" t="n">
         <v>7080</v>
       </c>
+      <c r="CY17" t="n">
+        <v>7610</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -43189,6 +43711,9 @@
       <c r="CX18" t="n">
         <v>21480</v>
       </c>
+      <c r="CY18" t="n">
+        <v>22680</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43500,6 +44025,9 @@
       </c>
       <c r="CX19" t="n">
         <v>17200</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>17730</v>
       </c>
     </row>
   </sheetData>
@@ -43513,7 +44041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX19"/>
+  <dimension ref="A1:CY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -43618,6 +44146,7 @@
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
     <col width="12" customWidth="1" min="102" max="102"/>
+    <col width="12" customWidth="1" min="103" max="103"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43931,6 +44460,9 @@
       <c r="CX1" s="1" t="n">
         <v>20260127</v>
       </c>
+      <c r="CY1" s="1" t="n">
+        <v>20260128</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -44243,6 +44775,9 @@
       <c r="CX2" t="n">
         <v>1034218</v>
       </c>
+      <c r="CY2" t="n">
+        <v>903983</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -44555,6 +45090,9 @@
       <c r="CX3" t="n">
         <v>2988042</v>
       </c>
+      <c r="CY3" t="n">
+        <v>4172849</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -44867,6 +45405,9 @@
       <c r="CX4" t="n">
         <v>1916678</v>
       </c>
+      <c r="CY4" t="n">
+        <v>1464437</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -45179,6 +45720,9 @@
       <c r="CX5" t="n">
         <v>910042</v>
       </c>
+      <c r="CY5" t="n">
+        <v>935370</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -45491,6 +46035,9 @@
       <c r="CX6" t="n">
         <v>11863352</v>
       </c>
+      <c r="CY6" t="n">
+        <v>7837678</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -45803,6 +46350,9 @@
       <c r="CX7" t="n">
         <v>8937379</v>
       </c>
+      <c r="CY7" t="n">
+        <v>8474595</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -46115,6 +46665,9 @@
       <c r="CX8" t="n">
         <v>24475177</v>
       </c>
+      <c r="CY8" t="n">
+        <v>25442471</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -46427,6 +46980,9 @@
       <c r="CX9" t="n">
         <v>10243012</v>
       </c>
+      <c r="CY9" t="n">
+        <v>24882626</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -46739,6 +47295,9 @@
       <c r="CX10" t="n">
         <v>5480397</v>
       </c>
+      <c r="CY10" t="n">
+        <v>6965037</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -47051,6 +47610,9 @@
       <c r="CX11" t="n">
         <v>1269672</v>
       </c>
+      <c r="CY11" t="n">
+        <v>3158457</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -47363,6 +47925,9 @@
       <c r="CX12" t="n">
         <v>5354605</v>
       </c>
+      <c r="CY12" t="n">
+        <v>7132728</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -47675,6 +48240,9 @@
       <c r="CX13" t="n">
         <v>13742765</v>
       </c>
+      <c r="CY13" t="n">
+        <v>19045119</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -47987,6 +48555,9 @@
       <c r="CX14" t="n">
         <v>74291863</v>
       </c>
+      <c r="CY14" t="n">
+        <v>80993918</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -48299,6 +48870,9 @@
       <c r="CX15" t="n">
         <v>2772735</v>
       </c>
+      <c r="CY15" t="n">
+        <v>3584409</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -48611,6 +49185,9 @@
       <c r="CX16" t="n">
         <v>670193</v>
       </c>
+      <c r="CY16" t="n">
+        <v>1124498</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -48923,6 +49500,9 @@
       <c r="CX17" t="n">
         <v>155465</v>
       </c>
+      <c r="CY17" t="n">
+        <v>337373</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -49235,6 +49815,9 @@
       <c r="CX18" t="n">
         <v>394889</v>
       </c>
+      <c r="CY18" t="n">
+        <v>319219</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -49546,6 +50129,9 @@
       </c>
       <c r="CX19" t="n">
         <v>162310</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>134546</v>
       </c>
     </row>
   </sheetData>
@@ -49559,7 +50145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE19"/>
+  <dimension ref="A1:CF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -49645,6 +50231,7 @@
     <col width="10" customWidth="1" min="81" max="81"/>
     <col width="10" customWidth="1" min="82" max="82"/>
     <col width="10" customWidth="1" min="83" max="83"/>
+    <col width="10" customWidth="1" min="84" max="84"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -49901,6 +50488,9 @@
       <c r="CE1" s="1" t="n">
         <v>20260127</v>
       </c>
+      <c r="CF1" s="1" t="n">
+        <v>20260128</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -50156,6 +50746,9 @@
       <c r="CE2" t="n">
         <v>100</v>
       </c>
+      <c r="CF2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -50411,6 +51004,9 @@
       <c r="CE3" t="n">
         <v>100</v>
       </c>
+      <c r="CF3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -50666,6 +51262,9 @@
       <c r="CE4" t="n">
         <v>100</v>
       </c>
+      <c r="CF4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -50921,6 +51520,9 @@
       <c r="CE5" t="n">
         <v>100</v>
       </c>
+      <c r="CF5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -51176,6 +51778,9 @@
       <c r="CE6" t="n">
         <v>100</v>
       </c>
+      <c r="CF6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -51431,6 +52036,9 @@
       <c r="CE7" t="n">
         <v>100</v>
       </c>
+      <c r="CF7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -51686,6 +52294,9 @@
       <c r="CE8" t="n">
         <v>100</v>
       </c>
+      <c r="CF8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -51941,6 +52552,9 @@
       <c r="CE9" t="n">
         <v>92</v>
       </c>
+      <c r="CF9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -52196,6 +52810,9 @@
       <c r="CE10" t="n">
         <v>100</v>
       </c>
+      <c r="CF10" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -52451,6 +53068,9 @@
       <c r="CE11" t="n">
         <v>100</v>
       </c>
+      <c r="CF11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -52706,6 +53326,9 @@
       <c r="CE12" t="n">
         <v>100</v>
       </c>
+      <c r="CF12" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -52961,6 +53584,9 @@
       <c r="CE13" t="n">
         <v>100</v>
       </c>
+      <c r="CF13" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -53216,6 +53842,9 @@
       <c r="CE14" t="n">
         <v>100</v>
       </c>
+      <c r="CF14" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -53471,6 +54100,9 @@
       <c r="CE15" t="n">
         <v>78</v>
       </c>
+      <c r="CF15" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -53726,6 +54358,9 @@
       <c r="CE16" t="n">
         <v>100</v>
       </c>
+      <c r="CF16" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -53981,6 +54616,9 @@
       <c r="CE17" t="n">
         <v>99</v>
       </c>
+      <c r="CF17" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -54236,6 +54874,9 @@
       <c r="CE18" t="n">
         <v>100</v>
       </c>
+      <c r="CF18" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -54489,6 +55130,9 @@
         <v>100</v>
       </c>
       <c r="CE19" t="n">
+        <v>100</v>
+      </c>
+      <c r="CF19" t="n">
         <v>100</v>
       </c>
     </row>
@@ -54503,7 +55147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ19"/>
+  <dimension ref="A1:AR19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -54549,6 +55193,7 @@
     <col width="10" customWidth="1" min="41" max="41"/>
     <col width="10" customWidth="1" min="42" max="42"/>
     <col width="10" customWidth="1" min="43" max="43"/>
+    <col width="10" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -54685,6 +55330,9 @@
       <c r="AQ1" s="1" t="n">
         <v>20260127</v>
       </c>
+      <c r="AR1" s="1" t="n">
+        <v>20260128</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -54820,6 +55468,9 @@
       <c r="AQ2" t="n">
         <v>100</v>
       </c>
+      <c r="AR2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -54955,6 +55606,9 @@
       <c r="AQ3" t="n">
         <v>100</v>
       </c>
+      <c r="AR3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -55090,6 +55744,9 @@
       <c r="AQ4" t="n">
         <v>100</v>
       </c>
+      <c r="AR4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -55225,6 +55882,9 @@
       <c r="AQ5" t="n">
         <v>100</v>
       </c>
+      <c r="AR5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -55360,6 +56020,9 @@
       <c r="AQ6" t="n">
         <v>100</v>
       </c>
+      <c r="AR6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -55495,6 +56158,9 @@
       <c r="AQ7" t="n">
         <v>100</v>
       </c>
+      <c r="AR7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -55630,6 +56296,9 @@
       <c r="AQ8" t="n">
         <v>100</v>
       </c>
+      <c r="AR8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -55765,6 +56434,9 @@
       <c r="AQ9" t="n">
         <v>76</v>
       </c>
+      <c r="AR9" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -55900,6 +56572,9 @@
       <c r="AQ10" t="n">
         <v>100</v>
       </c>
+      <c r="AR10" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -56035,6 +56710,9 @@
       <c r="AQ11" t="n">
         <v>100</v>
       </c>
+      <c r="AR11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -56170,6 +56848,9 @@
       <c r="AQ12" t="n">
         <v>100</v>
       </c>
+      <c r="AR12" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -56305,6 +56986,9 @@
       <c r="AQ13" t="n">
         <v>100</v>
       </c>
+      <c r="AR13" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -56440,6 +57124,9 @@
       <c r="AQ14" t="n">
         <v>94</v>
       </c>
+      <c r="AR14" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -56575,6 +57262,9 @@
       <c r="AQ15" t="n">
         <v>84</v>
       </c>
+      <c r="AR15" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -56710,6 +57400,9 @@
       <c r="AQ16" t="n">
         <v>100</v>
       </c>
+      <c r="AR16" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -56845,6 +57538,9 @@
       <c r="AQ17" t="n">
         <v>99</v>
       </c>
+      <c r="AR17" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -56980,6 +57676,9 @@
       <c r="AQ18" t="n">
         <v>100</v>
       </c>
+      <c r="AR18" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -57113,6 +57812,9 @@
         <v>100</v>
       </c>
       <c r="AQ19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR19" t="n">
         <v>100</v>
       </c>
     </row>
@@ -57127,7 +57829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE19"/>
+  <dimension ref="A1:CF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -57213,6 +57915,7 @@
     <col width="10" customWidth="1" min="81" max="81"/>
     <col width="10" customWidth="1" min="82" max="82"/>
     <col width="10" customWidth="1" min="83" max="83"/>
+    <col width="10" customWidth="1" min="84" max="84"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -57469,6 +58172,9 @@
       <c r="CE1" s="1" t="n">
         <v>20260127</v>
       </c>
+      <c r="CF1" s="1" t="n">
+        <v>20260128</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -57724,6 +58430,9 @@
       <c r="CE2" t="n">
         <v>92</v>
       </c>
+      <c r="CF2" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -57979,6 +58688,9 @@
       <c r="CE3" t="n">
         <v>106</v>
       </c>
+      <c r="CF3" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -58234,6 +58946,9 @@
       <c r="CE4" t="n">
         <v>128</v>
       </c>
+      <c r="CF4" t="n">
+        <v>131</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -58489,6 +59204,9 @@
       <c r="CE5" t="n">
         <v>100</v>
       </c>
+      <c r="CF5" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -58744,6 +59462,9 @@
       <c r="CE6" t="n">
         <v>106</v>
       </c>
+      <c r="CF6" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -58999,6 +59720,9 @@
       <c r="CE7" t="n">
         <v>95</v>
       </c>
+      <c r="CF7" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -59254,6 +59978,9 @@
       <c r="CE8" t="n">
         <v>92</v>
       </c>
+      <c r="CF8" t="n">
+        <v>129</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -59509,6 +60236,9 @@
       <c r="CE9" t="n">
         <v>85</v>
       </c>
+      <c r="CF9" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -59764,6 +60494,9 @@
       <c r="CE10" t="n">
         <v>120</v>
       </c>
+      <c r="CF10" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -60019,6 +60752,9 @@
       <c r="CE11" t="n">
         <v>115</v>
       </c>
+      <c r="CF11" t="n">
+        <v>132</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -60274,6 +61010,9 @@
       <c r="CE12" t="n">
         <v>116</v>
       </c>
+      <c r="CF12" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -60529,6 +61268,9 @@
       <c r="CE13" t="n">
         <v>124</v>
       </c>
+      <c r="CF13" t="n">
+        <v>137</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -60784,6 +61526,9 @@
       <c r="CE14" t="n">
         <v>108</v>
       </c>
+      <c r="CF14" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -61039,6 +61784,9 @@
       <c r="CE15" t="n">
         <v>27</v>
       </c>
+      <c r="CF15" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -61294,6 +62042,9 @@
       <c r="CE16" t="n">
         <v>109</v>
       </c>
+      <c r="CF16" t="n">
+        <v>124</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -61549,6 +62300,9 @@
       <c r="CE17" t="n">
         <v>105</v>
       </c>
+      <c r="CF17" t="n">
+        <v>125</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -61804,6 +62558,9 @@
       <c r="CE18" t="n">
         <v>101</v>
       </c>
+      <c r="CF18" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -62058,6 +62815,9 @@
       </c>
       <c r="CE19" t="n">
         <v>81</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/KR_Stocks_ETF.xlsx
+++ b/KR_Stocks_ETF.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR19"/>
+  <dimension ref="A1:AS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -757,6 +757,7 @@
     <col width="10" customWidth="1" min="42" max="42"/>
     <col width="10" customWidth="1" min="43" max="43"/>
     <col width="10" customWidth="1" min="44" max="44"/>
+    <col width="10" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -896,6 +897,9 @@
       <c r="AR1" s="1" t="n">
         <v>20260128</v>
       </c>
+      <c r="AS1" s="1" t="n">
+        <v>20260129</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1034,6 +1038,9 @@
       <c r="AR2" t="n">
         <v>114</v>
       </c>
+      <c r="AS2" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1172,6 +1179,9 @@
       <c r="AR3" t="n">
         <v>147</v>
       </c>
+      <c r="AS3" t="n">
+        <v>145</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1310,6 +1320,9 @@
       <c r="AR4" t="n">
         <v>190</v>
       </c>
+      <c r="AS4" t="n">
+        <v>193</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1448,6 +1461,9 @@
       <c r="AR5" t="n">
         <v>163</v>
       </c>
+      <c r="AS5" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1586,6 +1602,9 @@
       <c r="AR6" t="n">
         <v>149</v>
       </c>
+      <c r="AS6" t="n">
+        <v>145</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1724,6 +1743,9 @@
       <c r="AR7" t="n">
         <v>130</v>
       </c>
+      <c r="AS7" t="n">
+        <v>131</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1862,6 +1884,9 @@
       <c r="AR8" t="n">
         <v>134</v>
       </c>
+      <c r="AS8" t="n">
+        <v>137</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2000,6 +2025,9 @@
       <c r="AR9" t="n">
         <v>96</v>
       </c>
+      <c r="AS9" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2138,6 +2166,9 @@
       <c r="AR10" t="n">
         <v>197</v>
       </c>
+      <c r="AS10" t="n">
+        <v>191</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2276,6 +2307,9 @@
       <c r="AR11" t="n">
         <v>198</v>
       </c>
+      <c r="AS11" t="n">
+        <v>172</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2414,6 +2448,9 @@
       <c r="AR12" t="n">
         <v>190</v>
       </c>
+      <c r="AS12" t="n">
+        <v>164</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2552,6 +2589,9 @@
       <c r="AR13" t="n">
         <v>196</v>
       </c>
+      <c r="AS13" t="n">
+        <v>178</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2690,6 +2730,9 @@
       <c r="AR14" t="n">
         <v>128</v>
       </c>
+      <c r="AS14" t="n">
+        <v>123</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2828,6 +2871,9 @@
       <c r="AR15" t="n">
         <v>62</v>
       </c>
+      <c r="AS15" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2966,6 +3012,9 @@
       <c r="AR16" t="n">
         <v>180</v>
       </c>
+      <c r="AS16" t="n">
+        <v>161</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3104,6 +3153,9 @@
       <c r="AR17" t="n">
         <v>146</v>
       </c>
+      <c r="AS17" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3242,6 +3294,9 @@
       <c r="AR18" t="n">
         <v>159</v>
       </c>
+      <c r="AS18" t="n">
+        <v>167</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3379,6 +3434,9 @@
       </c>
       <c r="AR19" t="n">
         <v>113</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -3392,7 +3450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF19"/>
+  <dimension ref="A1:CG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3479,6 +3537,7 @@
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
+    <col width="12" customWidth="1" min="85" max="85"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3902,6 +3961,11 @@
           <t>20260128</t>
         </is>
       </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>20260129</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4160,6 +4224,9 @@
       <c r="CF2" t="n">
         <v>111</v>
       </c>
+      <c r="CG2" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4418,6 +4485,9 @@
       <c r="CF3" t="n">
         <v>117</v>
       </c>
+      <c r="CG3" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4676,6 +4746,9 @@
       <c r="CF4" t="n">
         <v>117</v>
       </c>
+      <c r="CG4" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4934,6 +5007,9 @@
       <c r="CF5" t="n">
         <v>111</v>
       </c>
+      <c r="CG5" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5192,6 +5268,9 @@
       <c r="CF6" t="n">
         <v>116</v>
       </c>
+      <c r="CG6" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5450,6 +5529,9 @@
       <c r="CF7" t="n">
         <v>114</v>
       </c>
+      <c r="CG7" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5708,6 +5790,9 @@
       <c r="CF8" t="n">
         <v>116</v>
       </c>
+      <c r="CG8" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5966,6 +6051,9 @@
       <c r="CF9" t="n">
         <v>130</v>
       </c>
+      <c r="CG9" t="n">
+        <v>125</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6224,6 +6312,9 @@
       <c r="CF10" t="n">
         <v>117</v>
       </c>
+      <c r="CG10" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6482,6 +6573,9 @@
       <c r="CF11" t="n">
         <v>127</v>
       </c>
+      <c r="CG11" t="n">
+        <v>125</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6740,6 +6834,9 @@
       <c r="CF12" t="n">
         <v>128</v>
       </c>
+      <c r="CG12" t="n">
+        <v>125</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6998,6 +7095,9 @@
       <c r="CF13" t="n">
         <v>131</v>
       </c>
+      <c r="CG13" t="n">
+        <v>129</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7256,6 +7356,9 @@
       <c r="CF14" t="n">
         <v>143</v>
       </c>
+      <c r="CG14" t="n">
+        <v>139</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7514,6 +7617,9 @@
       <c r="CF15" t="n">
         <v>105</v>
       </c>
+      <c r="CG15" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7772,6 +7878,9 @@
       <c r="CF16" t="n">
         <v>126</v>
       </c>
+      <c r="CG16" t="n">
+        <v>123</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8030,6 +8139,9 @@
       <c r="CF17" t="n">
         <v>123</v>
       </c>
+      <c r="CG17" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8288,6 +8400,9 @@
       <c r="CF18" t="n">
         <v>113</v>
       </c>
+      <c r="CG18" t="n">
+        <v>115</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8545,6 +8660,9 @@
       </c>
       <c r="CF19" t="n">
         <v>109</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -8558,7 +8676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM19"/>
+  <dimension ref="A1:BN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8577,6 +8695,7 @@
